--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2523994445801</t>
+    <t xml:space="preserve">13.2523975372314</t>
   </si>
   <si>
     <t xml:space="preserve">BSS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9788007736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7479515075684</t>
+    <t xml:space="preserve">12.9787998199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7479524612427</t>
   </si>
   <si>
     <t xml:space="preserve">12.3974046707153</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2435054779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2606067657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.140905380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4825611114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8584146499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79822444915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3539705276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84952449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4736671447754</t>
+    <t xml:space="preserve">12.2435064315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2606048583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1409063339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4825630187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8584156036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7982234954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3539686203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84952354431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4736680984497</t>
   </si>
   <si>
     <t xml:space="preserve">10.2941207885742</t>
@@ -86,34 +86,34 @@
     <t xml:space="preserve">10.7814664840698</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8156671524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.730167388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.576268196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6361169815063</t>
+    <t xml:space="preserve">10.8156661987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7301664352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5762672424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6361179351807</t>
   </si>
   <si>
     <t xml:space="preserve">10.191520690918</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4565687179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4907693862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0205240249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03727912902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97743129730225</t>
+    <t xml:space="preserve">10.4565677642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4907703399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0205230712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03728008270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97743034362793</t>
   </si>
   <si>
     <t xml:space="preserve">9.40492820739746</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">9.14842796325684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43057632446289</t>
+    <t xml:space="preserve">9.43057727813721</t>
   </si>
   <si>
     <t xml:space="preserve">9.90082263946533</t>
@@ -134,43 +134,43 @@
     <t xml:space="preserve">10.4394693374634</t>
   </si>
   <si>
-    <t xml:space="preserve">10.345419883728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2000732421875</t>
+    <t xml:space="preserve">10.3454217910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2000713348389</t>
   </si>
   <si>
     <t xml:space="preserve">11.0037641525269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5506181716919</t>
+    <t xml:space="preserve">10.5506191253662</t>
   </si>
   <si>
     <t xml:space="preserve">10.2257213592529</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1829719543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0379638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9097156524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8074588775635</t>
+    <t xml:space="preserve">10.1829690933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0379648208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9097146987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8074607849121</t>
   </si>
   <si>
     <t xml:space="preserve">11.9442577362061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1067056655884</t>
+    <t xml:space="preserve">12.106707572937</t>
   </si>
   <si>
     <t xml:space="preserve">11.7732610702515</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9699087142944</t>
+    <t xml:space="preserve">11.9699077606201</t>
   </si>
   <si>
     <t xml:space="preserve">11.627911567688</t>
@@ -188,46 +188,46 @@
     <t xml:space="preserve">11.8416585922241</t>
   </si>
   <si>
-    <t xml:space="preserve">11.918607711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7989082336426</t>
+    <t xml:space="preserve">11.9186086654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7989091873169</t>
   </si>
   <si>
     <t xml:space="preserve">12.046856880188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1922073364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2007551193237</t>
+    <t xml:space="preserve">12.1922063827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.200756072998</t>
   </si>
   <si>
     <t xml:space="preserve">12.3375549316406</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1323575973511</t>
+    <t xml:space="preserve">12.1323556900024</t>
   </si>
   <si>
     <t xml:space="preserve">12.1665563583374</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2178564071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9015083312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5680599212646</t>
+    <t xml:space="preserve">12.2178554534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9015092849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.568060874939</t>
   </si>
   <si>
     <t xml:space="preserve">11.2859125137329</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7390594482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.884407043457</t>
+    <t xml:space="preserve">11.7390584945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8844079971313</t>
   </si>
   <si>
     <t xml:space="preserve">11.8160095214844</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">11.7048597335815</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6022605895996</t>
+    <t xml:space="preserve">11.6022615432739</t>
   </si>
   <si>
     <t xml:space="preserve">11.6364603042603</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">11.4740123748779</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1918621063232</t>
+    <t xml:space="preserve">11.1918640136719</t>
   </si>
   <si>
     <t xml:space="preserve">11.1063642501831</t>
@@ -257,16 +257,16 @@
     <t xml:space="preserve">11.3201122283936</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457632064819</t>
+    <t xml:space="preserve">11.3457622528076</t>
   </si>
   <si>
     <t xml:space="preserve">11.1576633453369</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0550661087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9866647720337</t>
+    <t xml:space="preserve">11.055064201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.986665725708</t>
   </si>
   <si>
     <t xml:space="preserve">11.1405639648438</t>
@@ -278,25 +278,25 @@
     <t xml:space="preserve">10.9541397094727</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4346122741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3553609848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2232780456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2673063278198</t>
+    <t xml:space="preserve">10.4346132278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3553619384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.22327709198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2673053741455</t>
   </si>
   <si>
     <t xml:space="preserve">9.92388916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3201398849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0031366348267</t>
+    <t xml:space="preserve">10.320140838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.003137588501</t>
   </si>
   <si>
     <t xml:space="preserve">10.3025274276733</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">11.4120311737061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1302537918091</t>
+    <t xml:space="preserve">11.1302528381348</t>
   </si>
   <si>
     <t xml:space="preserve">10.9189186096191</t>
@@ -320,49 +320,49 @@
     <t xml:space="preserve">11.2359199523926</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2799482345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0069751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8308620452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8396701812744</t>
+    <t xml:space="preserve">11.2799491882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0069742202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8308639526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8396692276001</t>
   </si>
   <si>
     <t xml:space="preserve">10.9277238845825</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9101133346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8132514953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5138626098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0647773742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99433326721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95030403137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68613815307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0383596420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4962511062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3465566635132</t>
+    <t xml:space="preserve">10.9101142883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.81325340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.513861656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0647783279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99433135986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95030689239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68613719940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0383605957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4962520599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3465557098389</t>
   </si>
   <si>
     <t xml:space="preserve">10.4522228240967</t>
@@ -374,52 +374,52 @@
     <t xml:space="preserve">9.87986087799072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12257957458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67733287811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57166385650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93269443511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1880559921265</t>
+    <t xml:space="preserve">9.12258148193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67733192443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57166481018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.932692527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1880550384521</t>
   </si>
   <si>
     <t xml:space="preserve">9.98552799224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1842212677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14019298553467</t>
+    <t xml:space="preserve">9.18422031402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14019107818604</t>
   </si>
   <si>
     <t xml:space="preserve">9.721360206604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0823879241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3817777633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2849168777466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1352233886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2144718170166</t>
+    <t xml:space="preserve">10.0823888778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.381778717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2849178314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1352224349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2144727706909</t>
   </si>
   <si>
     <t xml:space="preserve">10.1528329849243</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6987791061401</t>
+    <t xml:space="preserve">10.6987781524658</t>
   </si>
   <si>
     <t xml:space="preserve">11.0774183273315</t>
@@ -428,16 +428,16 @@
     <t xml:space="preserve">11.0157804489136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0333909988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9893617630005</t>
+    <t xml:space="preserve">11.033390045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9893636703491</t>
   </si>
   <si>
     <t xml:space="preserve">10.8748903274536</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0950317382812</t>
+    <t xml:space="preserve">11.0950298309326</t>
   </si>
   <si>
     <t xml:space="preserve">11.2535305023193</t>
@@ -452,22 +452,22 @@
     <t xml:space="preserve">11.0510025024414</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9013071060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1654739379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0598096847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2183074951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1214466094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1830863952637</t>
+    <t xml:space="preserve">10.9013080596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1654758453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0598077774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2183084487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1214475631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1830854415894</t>
   </si>
   <si>
     <t xml:space="preserve">11.2623357772827</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">11.5265035629272</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7466440200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7730598449707</t>
+    <t xml:space="preserve">11.7466449737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.773060798645</t>
   </si>
   <si>
     <t xml:space="preserve">11.6850051879883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7994775772095</t>
+    <t xml:space="preserve">11.7994756698608</t>
   </si>
   <si>
     <t xml:space="preserve">11.6497812271118</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">11.6673936843872</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4472541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.323974609375</t>
+    <t xml:space="preserve">11.4472532272339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3239755630493</t>
   </si>
   <si>
     <t xml:space="preserve">11.3680028915405</t>
@@ -506,49 +506,49 @@
     <t xml:space="preserve">11.1390590667725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6938095092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6145582199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8258943557739</t>
+    <t xml:space="preserve">11.6938104629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.614559173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8258934020996</t>
   </si>
   <si>
     <t xml:space="preserve">12.0372266769409</t>
   </si>
   <si>
-    <t xml:space="preserve">12.054838180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0636434555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5039215087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5303382873535</t>
+    <t xml:space="preserve">12.0548372268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0636444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5039224624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5303401947021</t>
   </si>
   <si>
     <t xml:space="preserve">12.4070606231689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2837839126587</t>
+    <t xml:space="preserve">12.2837829589844</t>
   </si>
   <si>
     <t xml:space="preserve">12.6007852554321</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9177856445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8121175765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8561458587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0322580337524</t>
+    <t xml:space="preserve">12.9177846908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8121185302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8561477661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0322570800781</t>
   </si>
   <si>
     <t xml:space="preserve">13.4108972549438</t>
@@ -557,28 +557,28 @@
     <t xml:space="preserve">13.5782041549683</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6838693618774</t>
+    <t xml:space="preserve">13.6838703155518</t>
   </si>
   <si>
     <t xml:space="preserve">13.4285087585449</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3707046508789</t>
+    <t xml:space="preserve">14.3707056045532</t>
   </si>
   <si>
     <t xml:space="preserve">14.2210102081299</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2562341690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1329545974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1241493225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0713148117065</t>
+    <t xml:space="preserve">14.256233215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1329555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1241512298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0713157653809</t>
   </si>
   <si>
     <t xml:space="preserve">13.9216222763062</t>
@@ -587,46 +587,46 @@
     <t xml:space="preserve">13.7807312011719</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6046209335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7631196975708</t>
+    <t xml:space="preserve">13.6046190261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7631206512451</t>
   </si>
   <si>
     <t xml:space="preserve">13.8335666656494</t>
   </si>
   <si>
-    <t xml:space="preserve">13.727897644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1995649337769</t>
+    <t xml:space="preserve">13.7278985977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1995639801025</t>
   </si>
   <si>
     <t xml:space="preserve">13.375675201416</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1555347442627</t>
+    <t xml:space="preserve">13.155535697937</t>
   </si>
   <si>
     <t xml:space="preserve">13.6486492156982</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5605916976929</t>
+    <t xml:space="preserve">13.5605926513672</t>
   </si>
   <si>
     <t xml:space="preserve">13.7367038726807</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8775939941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.176983833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0977334976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7845687866211</t>
+    <t xml:space="preserve">13.8775930404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1769828796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0977325439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7845678329468</t>
   </si>
   <si>
     <t xml:space="preserve">15.3040962219238</t>
@@ -635,25 +635,25 @@
     <t xml:space="preserve">15.2776803970337</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4890165328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4978189468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3657341003418</t>
+    <t xml:space="preserve">15.489013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4978199005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3657379150391</t>
   </si>
   <si>
     <t xml:space="preserve">15.4449882507324</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3393201828003</t>
+    <t xml:space="preserve">15.339319229126</t>
   </si>
   <si>
     <t xml:space="preserve">15.5330429077148</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6651268005371</t>
+    <t xml:space="preserve">15.6651277542114</t>
   </si>
   <si>
     <t xml:space="preserve">15.5418491363525</t>
@@ -662,19 +662,19 @@
     <t xml:space="preserve">15.2424573898315</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8060150146484</t>
+    <t xml:space="preserve">15.8060178756714</t>
   </si>
   <si>
     <t xml:space="preserve">16.1934604644775</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3695755004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4664344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5104598999023</t>
+    <t xml:space="preserve">16.369571685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4664363861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.510461807251</t>
   </si>
   <si>
     <t xml:space="preserve">17.0387954711914</t>
@@ -686,10 +686,10 @@
     <t xml:space="preserve">17.1532688140869</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7746295928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5544910430908</t>
+    <t xml:space="preserve">16.7746315002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5544891357422</t>
   </si>
   <si>
     <t xml:space="preserve">16.2374897003174</t>
@@ -701,10 +701,10 @@
     <t xml:space="preserve">16.6513519287109</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5721015930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9947681427002</t>
+    <t xml:space="preserve">16.5720977783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9947700500488</t>
   </si>
   <si>
     <t xml:space="preserve">16.7041835784912</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">16.880298614502</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8538799285889</t>
+    <t xml:space="preserve">16.8538761138916</t>
   </si>
   <si>
     <t xml:space="preserve">17.012378692627</t>
@@ -722,34 +722,34 @@
     <t xml:space="preserve">17.2941589355469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1268539428711</t>
+    <t xml:space="preserve">17.1268520355225</t>
   </si>
   <si>
     <t xml:space="preserve">16.5368804931641</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0828247070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8626861572266</t>
+    <t xml:space="preserve">17.0828227996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8626823425293</t>
   </si>
   <si>
     <t xml:space="preserve">17.2061042785645</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3469924926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6551876068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5407161712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5054912567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7168273925781</t>
+    <t xml:space="preserve">17.3469944000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6551856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.540714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5054931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7168292999268</t>
   </si>
   <si>
     <t xml:space="preserve">17.4526596069336</t>
@@ -764,19 +764,19 @@
     <t xml:space="preserve">17.8401050567627</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5759353637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7482147216797</t>
+    <t xml:space="preserve">17.5759372711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7482128143311</t>
   </si>
   <si>
     <t xml:space="preserve">16.7658252716064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.950740814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1620750427246</t>
+    <t xml:space="preserve">16.9507427215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.162073135376</t>
   </si>
   <si>
     <t xml:space="preserve">17.2765483856201</t>
@@ -791,19 +791,19 @@
     <t xml:space="preserve">16.8186569213867</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2325191497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2853546142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3910179138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.250129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4350471496582</t>
+    <t xml:space="preserve">17.2325210571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2853507995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3910217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2501335144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4350452423096</t>
   </si>
   <si>
     <t xml:space="preserve">17.3734092712402</t>
@@ -812,16 +812,16 @@
     <t xml:space="preserve">17.6463813781738</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9457721710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3722763061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9358329772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3849182128906</t>
+    <t xml:space="preserve">17.9457702636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3722743988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9358310699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.384916305542</t>
   </si>
   <si>
     <t xml:space="preserve">20.5962505340576</t>
@@ -833,16 +833,16 @@
     <t xml:space="preserve">20.8340034484863</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0453357696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5824756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0893630981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.327112197876</t>
+    <t xml:space="preserve">21.0453338623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5824775695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0893650054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3271141052246</t>
   </si>
   <si>
     <t xml:space="preserve">21.6529216766357</t>
@@ -854,31 +854,31 @@
     <t xml:space="preserve">21.917085647583</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8114204406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0139503479004</t>
+    <t xml:space="preserve">21.8114242553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0139484405518</t>
   </si>
   <si>
     <t xml:space="preserve">22.286922454834</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2605075836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.348560333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3221416473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1900634765625</t>
+    <t xml:space="preserve">22.2605056762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3485622406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3221454620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1900596618652</t>
   </si>
   <si>
     <t xml:space="preserve">22.6303386688232</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4366149902344</t>
+    <t xml:space="preserve">22.436616897583</t>
   </si>
   <si>
     <t xml:space="preserve">22.4806461334229</t>
@@ -893,37 +893,37 @@
     <t xml:space="preserve">22.6743679046631</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8945083618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0970344543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8328704833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3749771118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1938972473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3876190185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5108985900879</t>
+    <t xml:space="preserve">22.8945064544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0970325469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8328685760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3749752044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1938991546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3876209259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5109004974365</t>
   </si>
   <si>
     <t xml:space="preserve">23.9159526824951</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2417621612549</t>
+    <t xml:space="preserve">24.2417602539062</t>
   </si>
   <si>
     <t xml:space="preserve">24.7084541320801</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6556262969971</t>
+    <t xml:space="preserve">24.6556224822998</t>
   </si>
   <si>
     <t xml:space="preserve">24.9197902679443</t>
@@ -935,28 +935,28 @@
     <t xml:space="preserve">24.9638175964355</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8933753967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4255466461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4879302978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3970050811768</t>
+    <t xml:space="preserve">24.8933734893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4255447387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4879322052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3970069885254</t>
   </si>
   <si>
     <t xml:space="preserve">27.6287326812744</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1545715332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6732940673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6804065704346</t>
+    <t xml:space="preserve">28.1545696258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6732959747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6804046630859</t>
   </si>
   <si>
     <t xml:space="preserve">29.3666706085205</t>
@@ -965,22 +965,22 @@
     <t xml:space="preserve">27.8069820404053</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4665088653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0190830230713</t>
+    <t xml:space="preserve">28.4665069580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.019079208374</t>
   </si>
   <si>
     <t xml:space="preserve">29.4914417266846</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7677345275879</t>
+    <t xml:space="preserve">29.7677326202393</t>
   </si>
   <si>
     <t xml:space="preserve">29.8746814727783</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3024806976318</t>
+    <t xml:space="preserve">30.3024826049805</t>
   </si>
   <si>
     <t xml:space="preserve">30.7748413085938</t>
@@ -989,61 +989,61 @@
     <t xml:space="preserve">30.2400932312012</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6678924560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8283195495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8996181488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0154800415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9976577758789</t>
+    <t xml:space="preserve">30.6678943634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8283176422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8996162414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0154819488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9976558685303</t>
   </si>
   <si>
     <t xml:space="preserve">30.935266494751</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6500644683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7481060028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6857204437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3577556610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5003509521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.313196182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2775402069092</t>
+    <t xml:space="preserve">30.6500701904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.748104095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.685718536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3577537536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5003547668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3131923675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2775421142578</t>
   </si>
   <si>
     <t xml:space="preserve">30.1687927246094</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1331462860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.999454498291</t>
+    <t xml:space="preserve">30.1331424713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9994525909424</t>
   </si>
   <si>
     <t xml:space="preserve">29.9281558990479</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0529327392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4825325012207</t>
+    <t xml:space="preserve">30.0529346466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4825286865234</t>
   </si>
   <si>
     <t xml:space="preserve">29.8122940063477</t>
@@ -1052,40 +1052,40 @@
     <t xml:space="preserve">28.912130355835</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1260299682617</t>
+    <t xml:space="preserve">29.1260318756104</t>
   </si>
   <si>
     <t xml:space="preserve">27.7713298797607</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9674053192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2544078826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6911201477051</t>
+    <t xml:space="preserve">27.9674072265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2544059753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6911182403564</t>
   </si>
   <si>
     <t xml:space="preserve">27.4861335754395</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5752582550049</t>
+    <t xml:space="preserve">27.5752563476562</t>
   </si>
   <si>
     <t xml:space="preserve">28.11891746521</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3506412506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7178554534912</t>
+    <t xml:space="preserve">28.350643157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7178592681885</t>
   </si>
   <si>
     <t xml:space="preserve">28.5734577178955</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6180191040039</t>
+    <t xml:space="preserve">28.6180210113525</t>
   </si>
   <si>
     <t xml:space="preserve">28.5199813842773</t>
@@ -1094,43 +1094,43 @@
     <t xml:space="preserve">28.7873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7855548858643</t>
+    <t xml:space="preserve">29.7855529785156</t>
   </si>
   <si>
     <t xml:space="preserve">29.5360069274902</t>
   </si>
   <si>
-    <t xml:space="preserve">29.331018447876</t>
+    <t xml:space="preserve">29.3310165405273</t>
   </si>
   <si>
     <t xml:space="preserve">29.1705932617188</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2329807281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1438579559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3221092224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9656066894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7071437835693</t>
+    <t xml:space="preserve">29.232982635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.143856048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3221073150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9656047821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.707145690918</t>
   </si>
   <si>
     <t xml:space="preserve">28.9923419952393</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9477787017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6073093414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8568553924561</t>
+    <t xml:space="preserve">28.9477825164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6073036193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8568592071533</t>
   </si>
   <si>
     <t xml:space="preserve">29.4023208618164</t>
@@ -1139,97 +1139,97 @@
     <t xml:space="preserve">29.4112300872803</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8140964508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6875190734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6162185668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6786041259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6964282989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1420574188232</t>
+    <t xml:space="preserve">28.814094543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6875228881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6162166595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6786060333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6964302062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1420555114746</t>
   </si>
   <si>
     <t xml:space="preserve">29.8390312194824</t>
   </si>
   <si>
-    <t xml:space="preserve">30.186616897583</t>
+    <t xml:space="preserve">30.1866188049316</t>
   </si>
   <si>
     <t xml:space="preserve">29.5181789398193</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1795063018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.437967300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3648681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4629058837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4718170166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2935676574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0974922180176</t>
+    <t xml:space="preserve">29.1795082092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4379653930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3648700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4629020690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4718151092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2935657501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0974903106689</t>
   </si>
   <si>
     <t xml:space="preserve">30.0618419647217</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2311782836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0849800109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4967498779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8194065093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9958534240723</t>
+    <t xml:space="preserve">30.2311763763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0849761962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.496753692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.819408416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9958591461182</t>
   </si>
   <si>
     <t xml:space="preserve">31.773042678833</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6928310394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1830139160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0760688781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9512901306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3077926635742</t>
+    <t xml:space="preserve">31.6928329467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1830177307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0760650634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9512882232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.307788848877</t>
   </si>
   <si>
     <t xml:space="preserve">33.1990432739258</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3951187133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.758731842041</t>
+    <t xml:space="preserve">33.3951148986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7587242126465</t>
   </si>
   <si>
     <t xml:space="preserve">34.6963386535645</t>
@@ -1238,13 +1238,13 @@
     <t xml:space="preserve">34.7319946289062</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5804786682129</t>
+    <t xml:space="preserve">34.5804748535156</t>
   </si>
   <si>
     <t xml:space="preserve">34.2239799499512</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4378700256348</t>
+    <t xml:space="preserve">34.4378776550293</t>
   </si>
   <si>
     <t xml:space="preserve">34.5448265075684</t>
@@ -1253,46 +1253,46 @@
     <t xml:space="preserve">35.4271659851074</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2221832275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6606941223145</t>
+    <t xml:space="preserve">35.2221794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">34.3754920959473</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8674774169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8496513366699</t>
+    <t xml:space="preserve">33.8674736022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8496551513672</t>
   </si>
   <si>
     <t xml:space="preserve">34.1437683105469</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7159690856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0635566711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3131065368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1170310974121</t>
+    <t xml:space="preserve">33.7159729003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0635528564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.313102722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1170234680176</t>
   </si>
   <si>
     <t xml:space="preserve">34.420051574707</t>
   </si>
   <si>
-    <t xml:space="preserve">34.776554107666</t>
+    <t xml:space="preserve">34.7765502929688</t>
   </si>
   <si>
     <t xml:space="preserve">34.6161270141602</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3041915893555</t>
+    <t xml:space="preserve">34.3041877746582</t>
   </si>
   <si>
     <t xml:space="preserve">34.1081199645996</t>
@@ -1301,25 +1301,25 @@
     <t xml:space="preserve">32.8425407409668</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0902938842773</t>
+    <t xml:space="preserve">34.0902900695801</t>
   </si>
   <si>
     <t xml:space="preserve">35.106315612793</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2471122741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3005905151367</t>
+    <t xml:space="preserve">36.2471084594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3005867004395</t>
   </si>
   <si>
     <t xml:space="preserve">36.1847229003906</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4966659545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4146537780762</t>
+    <t xml:space="preserve">36.4966621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4146575927734</t>
   </si>
   <si>
     <t xml:space="preserve">38.8584747314453</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">38.9208602905273</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6178398132324</t>
+    <t xml:space="preserve">38.6178359985352</t>
   </si>
   <si>
     <t xml:space="preserve">38.5821914672852</t>
@@ -1349,22 +1349,22 @@
     <t xml:space="preserve">37.8067970275879</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3504638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0563507080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3682899475098</t>
+    <t xml:space="preserve">38.3504600524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0563545227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3682823181152</t>
   </si>
   <si>
     <t xml:space="preserve">38.341552734375</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5198059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5643615722656</t>
+    <t xml:space="preserve">38.5197982788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5643653869629</t>
   </si>
   <si>
     <t xml:space="preserve">38.6089248657227</t>
@@ -1376,40 +1376,40 @@
     <t xml:space="preserve">38.733699798584</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4377899169922</t>
+    <t xml:space="preserve">39.4377861022949</t>
   </si>
   <si>
     <t xml:space="preserve">39.0812835693359</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0545463562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3219261169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5554504394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2880783081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3772010803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6998481750488</t>
+    <t xml:space="preserve">39.0545501708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3219299316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5554466247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2880744934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3772087097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6998519897461</t>
   </si>
   <si>
     <t xml:space="preserve">36.6125259399414</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6820259094238</t>
+    <t xml:space="preserve">37.6820220947266</t>
   </si>
   <si>
     <t xml:space="preserve">38.4663238525391</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9956703186035</t>
+    <t xml:space="preserve">41.9956741333008</t>
   </si>
   <si>
     <t xml:space="preserve">42.6551971435547</t>
@@ -1421,28 +1421,28 @@
     <t xml:space="preserve">42.423469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0313262939453</t>
+    <t xml:space="preserve">42.031322479248</t>
   </si>
   <si>
     <t xml:space="preserve">42.0848007202148</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9243774414062</t>
+    <t xml:space="preserve">41.9243698120117</t>
   </si>
   <si>
     <t xml:space="preserve">41.6213493347168</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7639465332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1382751464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6926498413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5322227478027</t>
+    <t xml:space="preserve">41.7639503479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1382675170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6926460266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5322265625</t>
   </si>
   <si>
     <t xml:space="preserve">41.7817764282227</t>
@@ -1451,34 +1451,34 @@
     <t xml:space="preserve">41.3539733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8192253112793</t>
+    <t xml:space="preserve">40.819221496582</t>
   </si>
   <si>
     <t xml:space="preserve">40.3557739257812</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5874977111816</t>
+    <t xml:space="preserve">40.5875015258789</t>
   </si>
   <si>
     <t xml:space="preserve">39.8031997680664</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1436767578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6784286499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7799758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4787521362305</t>
+    <t xml:space="preserve">39.1436729431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6784248352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.779972076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4787483215332</t>
   </si>
   <si>
     <t xml:space="preserve">38.6802291870117</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5750770568848</t>
+    <t xml:space="preserve">37.5750732421875</t>
   </si>
   <si>
     <t xml:space="preserve">37.2898750305176</t>
@@ -1487,55 +1487,55 @@
     <t xml:space="preserve">39.5892944335938</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1953468322754</t>
+    <t xml:space="preserve">40.1953506469727</t>
   </si>
   <si>
     <t xml:space="preserve">40.1062240600586</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5696754455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8013954162598</t>
+    <t xml:space="preserve">40.5696716308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.801399230957</t>
   </si>
   <si>
     <t xml:space="preserve">40.9439964294434</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1400718688965</t>
+    <t xml:space="preserve">41.1400756835938</t>
   </si>
   <si>
     <t xml:space="preserve">40.9974746704102</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5161933898926</t>
+    <t xml:space="preserve">40.5161972045898</t>
   </si>
   <si>
     <t xml:space="preserve">40.9618225097656</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2506256103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1793251037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2131729125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3914260864258</t>
+    <t xml:space="preserve">39.2506294250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1793212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2131690979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3914222717285</t>
   </si>
   <si>
     <t xml:space="preserve">41.3896217346191</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6017265319824</t>
+    <t xml:space="preserve">42.6017189025879</t>
   </si>
   <si>
     <t xml:space="preserve">44.5446472167969</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9029502868652</t>
+    <t xml:space="preserve">43.9029426574707</t>
   </si>
   <si>
     <t xml:space="preserve">45.2309074401855</t>
@@ -1544,10 +1544,10 @@
     <t xml:space="preserve">43.8851203918457</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9635314941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0330390930176</t>
+    <t xml:space="preserve">44.9635353088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0330352783203</t>
   </si>
   <si>
     <t xml:space="preserve">47.3253440856934</t>
@@ -1556,28 +1556,28 @@
     <t xml:space="preserve">45.9439086914062</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5874137878418</t>
+    <t xml:space="preserve">45.5874099731445</t>
   </si>
   <si>
     <t xml:space="preserve">44.696159362793</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0098991394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8494720458984</t>
+    <t xml:space="preserve">44.009895324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8494758605957</t>
   </si>
   <si>
     <t xml:space="preserve">42.9582214355469</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4609260559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.175724029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1578941345215</t>
+    <t xml:space="preserve">41.4609222412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1757202148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1578979492188</t>
   </si>
   <si>
     <t xml:space="preserve">41.0152969360352</t>
@@ -1589,55 +1589,55 @@
     <t xml:space="preserve">39.108024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7479209899902</t>
+    <t xml:space="preserve">40.7479248046875</t>
   </si>
   <si>
     <t xml:space="preserve">39.7853736877441</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5518531799316</t>
+    <t xml:space="preserve">40.5518455505371</t>
   </si>
   <si>
     <t xml:space="preserve">39.7319030761719</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3040962219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2488212585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9101486206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4288787841797</t>
+    <t xml:space="preserve">39.3041000366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2488250732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9101448059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4288749694824</t>
   </si>
   <si>
     <t xml:space="preserve">39.0367240905762</t>
   </si>
   <si>
-    <t xml:space="preserve">42.387825012207</t>
+    <t xml:space="preserve">42.3878211975098</t>
   </si>
   <si>
     <t xml:space="preserve">41.0509490966797</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9335784912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0149230957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7087059020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6366577148438</t>
+    <t xml:space="preserve">41.9335670471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0149269104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7087135314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6366539001465</t>
   </si>
   <si>
     <t xml:space="preserve">40.5285797119141</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8441009521484</t>
+    <t xml:space="preserve">39.8440971374512</t>
   </si>
   <si>
     <t xml:space="preserve">37.7366142272949</t>
@@ -1646,16 +1646,16 @@
     <t xml:space="preserve">37.484432220459</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3316192626953</t>
+    <t xml:space="preserve">36.3316230773926</t>
   </si>
   <si>
     <t xml:space="preserve">37.0521240234375</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4757232666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6018142700195</t>
+    <t xml:space="preserve">36.4757194519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6018104553223</t>
   </si>
   <si>
     <t xml:space="preserve">36.0073928833008</t>
@@ -1667,25 +1667,25 @@
     <t xml:space="preserve">35.3589324951172</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2241363525391</t>
+    <t xml:space="preserve">34.2241325378418</t>
   </si>
   <si>
     <t xml:space="preserve">33.4135627746582</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6657409667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8818893432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4763145446777</t>
+    <t xml:space="preserve">33.6657447814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.881893157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4763069152832</t>
   </si>
   <si>
     <t xml:space="preserve">34.6924667358398</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1427841186523</t>
+    <t xml:space="preserve">35.1427803039551</t>
   </si>
   <si>
     <t xml:space="preserve">34.7284927368164</t>
@@ -1700,61 +1700,61 @@
     <t xml:space="preserve">33.8278579711914</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4402923583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1247711181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5036315917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4048538208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3868370056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4681930541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7744064331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5315341949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.486795425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9371147155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.234619140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.153263092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2166042327881</t>
+    <t xml:space="preserve">34.4402885437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1247673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5036239624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4048500061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3868408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4681911468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7744083404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5315322875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4867973327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9371128082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2346172332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1532649993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2166023254395</t>
   </si>
   <si>
     <t xml:space="preserve">29.4147434234619</t>
   </si>
   <si>
-    <t xml:space="preserve">27.829626083374</t>
+    <t xml:space="preserve">27.8296222686768</t>
   </si>
   <si>
     <t xml:space="preserve">29.1265411376953</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5408325195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6035842895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2520408630371</t>
+    <t xml:space="preserve">29.5408344268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6035823822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2520389556885</t>
   </si>
   <si>
     <t xml:space="preserve">29.6489086151123</t>
@@ -1763,46 +1763,46 @@
     <t xml:space="preserve">29.9551239013672</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1172370910645</t>
+    <t xml:space="preserve">30.1172351837158</t>
   </si>
   <si>
     <t xml:space="preserve">30.4054412841797</t>
   </si>
   <si>
-    <t xml:space="preserve">31.666332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6483154296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0806198120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1079368591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3601112365723</t>
+    <t xml:space="preserve">31.6663303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6483211517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.080623626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1079406738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3601150512695</t>
   </si>
   <si>
     <t xml:space="preserve">30.9818496704102</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7383861541748</t>
+    <t xml:space="preserve">31.7383842468262</t>
   </si>
   <si>
     <t xml:space="preserve">31.6122913360596</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8377475738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9191017150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9010887145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6669216156006</t>
+    <t xml:space="preserve">30.8377494812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9190979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.901086807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.666919708252</t>
   </si>
   <si>
     <t xml:space="preserve">29.0905132293701</t>
@@ -1811,7 +1811,7 @@
     <t xml:space="preserve">28.730260848999</t>
   </si>
   <si>
-    <t xml:space="preserve">28.099817276001</t>
+    <t xml:space="preserve">28.0998153686523</t>
   </si>
   <si>
     <t xml:space="preserve">27.595458984375</t>
@@ -1829,1894 +1829,1897 @@
     <t xml:space="preserve">26.5146999359131</t>
   </si>
   <si>
+    <t xml:space="preserve">27.2352046966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0550804138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1091175079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0190525054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7488632202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4693717956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9196891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5774478912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9377021789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8476390838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7936019897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0457782745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0097541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7755889892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6041717529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5501365661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1805820465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1625652313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6401958465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6762218475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6675090789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.451358795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5594348907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7581653594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7320308685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7413311004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7233200073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7860698699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4165115356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7047176361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5606174468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2363872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4345283508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5158786773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7053070068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8226871490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3630657196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2369766235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3450546264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5972309112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7239093780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.318920135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2828922271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5437850952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8773097991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3909702301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0034008026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0036964416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.139087677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1120662689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2651767730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.661750793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2024250030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9502458572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7160844802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6800575256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6170129776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1573963165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6077117919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4005641937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4723205566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5533771514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.490629196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9406509399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8232746124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6614570617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7968463897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0132942199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9052152633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2654705047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1934204101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7250890731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.400860786438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0496120452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7524032592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5899934768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1486825942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4639053344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1661071777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7875461578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1568031311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6434440612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.391263961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0127029418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0487270355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2288551330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0307159423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9226398468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4543075561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6791706085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8052616119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6251354217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3369331359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9493637084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7872505187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6971855163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3549423217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4269962310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9856834411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3552379608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7244987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3009052276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6071224212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3996829986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6698703765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2462768554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0661525726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9220485687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4176921844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4537181854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2823028564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7515163421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7425136566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7965507507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5083484649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.418285369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8508834838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9859790802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8688945770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0490245819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9409465789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3462333679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2741813659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3822593688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2831897735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1748161315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.976676940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6164245605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4272899627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1387920379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.913631439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6974792480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1928291320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9496593475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2381534576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1300811767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6794662475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9676723480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0847549438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0667400360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8686027526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5173530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6074180603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5894031524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6365585327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2434272766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6621875762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2249774932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5330257415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1916618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6842317581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6232395172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8021230697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9405136108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7836713790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3131456375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8943843841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8390283584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4792137145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.953330039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0732688903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0179128646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.303918838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3777275085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1009464263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1378498077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9220628738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7006387710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4756231307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4202671051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.577109336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8298015594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7928972244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6914129257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5125274658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1803913116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0989007949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7575378417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1486215591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2132024765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4069480895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4161758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5914688110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8590240478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9236068725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4807558059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6837301254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5361137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2962369918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.370044708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0471353530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1762981414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9087438583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65964126586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53047657012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0932645797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4899835586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5730171203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4254007339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5176601409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3054628372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4438524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6652784347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0286827087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96410083770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.056360244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.120943069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50280094146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29059982299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5766077041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21218109130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40131282806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43821620941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47512149810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20295333862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94001197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9861421585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88004398345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53970336914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24447059631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28137588500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11530685424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88106632232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97332668304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99177837371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2408809661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.434627532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0840396881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1024904251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61351108551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66886711120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52125072479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7980318069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56738090515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2629222869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39208793640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65041542053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31827926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71499729156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81648445129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68732070922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98255157470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75190162658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49357223510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2777853012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0655860900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5822439193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7298603057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2870101928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5084362030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3515930175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4310369491577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6340093612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2337007522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.993824005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1322145462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.086085319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1414403915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1875705718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9661464691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9569206237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7539472579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8277568817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7354965209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0676326751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4551248550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2577877044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2485628128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0824947357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5991516113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4054050445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2024335861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7559928894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7098627090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7744464874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3408241271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7190895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7283163070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0143222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1342601776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1250343322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9497404098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6637334823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.682186126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4571714401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1158094406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8482542037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0512266159058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0327739715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9312896728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6473274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7303600311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0865859985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7913551330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8651638031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7452239990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8190307617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1086292266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9979162216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9333343505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4720344543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.678596496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3187808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8446645736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2967405319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2044792175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7247257232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8538904190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1491222381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2506093978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9830551147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1583480834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0753145217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1065835952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6027421951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0399541854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9753713607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5878791809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.301872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6006956100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1301679611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30905342102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0635404586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97589349746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8928599357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5504732131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93796634674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90567541122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98409605026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91028785705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01177453994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47307538986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05431461334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85697841644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33673095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01382064819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39567756652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40028953552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34954738616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25728702545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.118896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74985504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92976331710815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78675937652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10967063903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84211587905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42694520950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28855466842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26087713241577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32545900344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33468389511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1132607460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5561089515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77753448486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93437719345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60223960876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33929824829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51920461654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3070068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14555168151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10403394699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15939044952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06713008880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92874002456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56533527374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54227018356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.445396900177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27010250091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72217750549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46948623657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66784381866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90310764312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54329299926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69090938568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87542915344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32750511169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0066404342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4863939285278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4956197738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2557430267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9420576095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82570934295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74267578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.462306022644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1947507858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0194549560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89029216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3792715072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3608179092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2224292755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.674503326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5453395843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7667636871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0215015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4402627944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5417499542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6155576705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8093032836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.818531036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7078170776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6616878509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5694274902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3480024337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2741947174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1450309753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8128938674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0030508041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3167362213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8241662979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7042284011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0548162460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3961791992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2854671478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4423084259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1286239624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2301120758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0086870193481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1932077407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5437955856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3500499725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5714740753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3685007095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1470766067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4976654052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1101732254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1655292510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2670154571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2762413024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0455904006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1747541427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3315963745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3869533538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5104818344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3813171386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6304187774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.335186958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7872619628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5068912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.433084487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4515342712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2690591812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5735187530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8318471908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1455326080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3613204956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4628076553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7616300582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5217542648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5955619812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7154998779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3556852340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9128360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6545085906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5033016204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4110412597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.650918006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1860265731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6750059127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4166774749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1029939651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9184722900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3889989852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7764940261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5827445983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1547584533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8133955001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8410730361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9241075515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1178550720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8502998352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8779783248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3520936965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6381034851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4351301193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5919713973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9517869949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.099401473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0717239379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5145740509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7877655029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3910465240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4648532867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1142635345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2618808746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5386619567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4464015960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5663394927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3725929260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6216983795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5478897094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.036865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.415132522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7657222747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9835567474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4299945831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4484481811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.728816986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.245475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1901187896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3377342224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2639274597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5443000793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5627517700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2029361724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4704914093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9722843170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1844806671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2823791503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9651031494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6109256744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9430618286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2567481994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2198429107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3121013641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1829376220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7513637542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7698135375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2900619506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8472137451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4745826721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7180480957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5371189117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6293773651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7216358184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1865291595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1275825500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6847343444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2013912200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4633102416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8728446960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6478290557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8508014678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0906791687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.109130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2234325408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9466533660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1311721801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.112720489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6145172119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8543930053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.795446395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3156929016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8323516845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.179349899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5483894348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0686378479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.216251373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1424446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0132808685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2531566619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0317325592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1942119598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7846755981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.729320526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3935947418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8953895568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0465927124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9174308776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3049240112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3971843719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5817050933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1388549804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5852928161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8067188262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3454170227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.489444732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7477722167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7662239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2311153411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7144565582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6370620727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0763187408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7554550170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4786758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9768772125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1613998413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3828258514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4935359954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.157808303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.04709815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2721099853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5673427581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4012775421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1060409545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9030685424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4971256256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9251136779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7221393585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6447410583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4602241516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3864154815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9989223480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5007133483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9066600799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2572479248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1280860900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9620151519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6631927490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3310585021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5155754089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4453582763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7370014190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7185497283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8292617797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4417667388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5340309143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4269065856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3715515136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5893859863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1983032226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4750843048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.914342880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4643135070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9625205993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5970726013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0322360992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8846168518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3459167480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6227016448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7923583984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9399757385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1798496246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8994808197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5857944488525</t>
+  </si>
+  <si>
     <t xml:space="preserve">27.2352066040039</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0550785064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1091194152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0190544128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7488651275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4693737030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9196910858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5774478912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9377002716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8476390838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7936019897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0457782745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0097541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7755889892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6041717529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5501327514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1805782318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1625690460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6401958465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6762218475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6675109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.451358795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5594367980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7581653594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7320327758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7413330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7233180999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7860698699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4165134429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7047157287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5606136322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2363872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4345264434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5158786773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7053070068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8226852416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3630638122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2369785308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3450527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5972309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7239112854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3189163208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2828922271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5437831878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.877311706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3909702301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0034008026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0036964416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1390857696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1120681762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2651767730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6617488861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2024269104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9502487182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7160835266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6800556182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6170148849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1573944091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6077117919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4005661010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4723205566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5533790588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4906272888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.94065284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8232746124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6614551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7968444824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0132923126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9052152633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2654685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1934185028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7250881195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4008617401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0496129989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.752402305603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.589994430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1486835479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4639043807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1661052703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7875442504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1568031311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6434421539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.391263961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0127029418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0487270355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2288551330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0307178497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9226398468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.454309463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6791744232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8052616119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6251373291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3369331359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9493618011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7872505187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6971855163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.354944229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4269924163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9856853485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3552379608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7244987487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3009071350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6071224212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3996810913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6698703765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2462768554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0661525726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9220504760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4176940917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4537181854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2823028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7515163421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7425136566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7965507507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5083465576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4182834625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8508815765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9859790802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.868896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0490226745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9409446716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3462333679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2741813659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3822574615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2831878662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1748180389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9766750335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6164226531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4272899627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1387901306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.913631439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6974811553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1928310394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9496574401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2381572723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1300811767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6794662475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9676723480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.084753036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0667400360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8686008453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5173530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6074161529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5894050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7695331573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6365585327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.24342918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6621875762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2249774932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5330257415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1916618347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6842317581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6232395172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8021230697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9405136108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7836713790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3131446838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8943843841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8390283584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4792137145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9533309936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0732679367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0179128646851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.303918838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3777265548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1009464263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1378507614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9220628738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7006387710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4756231307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4202671051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.577109336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8298015594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7928981781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6914129257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5125274658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1803903579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0989007949829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7575368881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1486206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2132024765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4069490432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4161748886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5914697647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8590240478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9236068725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4807567596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6837301254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5361127853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.296236038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.370044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0471353530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1762990951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90874481201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65964126586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53047752380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0932645797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4899835586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5730171203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4254007339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5176610946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3054628372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4438533782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6652784347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286827087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9640998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.056360244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1209421157837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50280094146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29059982299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5766077041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21218013763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40131282806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43821620941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47512149810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20295429229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94001197814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9861421585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88004398345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53970432281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24447059631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28137683868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11530685424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88106632232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97332668304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99177837371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2408809661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.434627532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.084038734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1024913787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61351108551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66886711120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52125072479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7980318069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56738185882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2629222869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39208793640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65041542053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31827926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71499729156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81648445129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68732070922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98255252838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75190162658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49357318878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2777853012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0655860900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5822439193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7298603057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2870101928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5084362030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3515930175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4310369491577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6340093612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2337007522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.993824005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1322145462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.086085319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1414403915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1875715255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9661474227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9569206237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7539472579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8277568817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7354965209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0676317214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4551248550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2577877044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2485637664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0824947357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5991516113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.40540599823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2024335861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7559938430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7098627090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7744464874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3408241271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7190895080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7283153533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0143222808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1342601776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1250343322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9497404098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6637334823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6821851730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4571723937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1158094406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8482542037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0512256622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0327739715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9312896728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6473264694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7303609848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0865879058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.791353225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.865161895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7452239990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8190307617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1086273193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9979181289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9333343505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4720335006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.678596496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3187808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8446645736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2967395782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2044792175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7247247695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8538904190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1491222381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2506093978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9830541610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1583490371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0753145217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1065835952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6027421951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0399541854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9753713607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5878791809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.301872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6006946563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1301679611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30905342102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0635404586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97589349746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89285945892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5504732131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93796634674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90567541122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98409652709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91028785705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01177406311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4730749130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05431365966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85697841644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33673095703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01382064819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.395676612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40029048919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34954738616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25728702545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11889743804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74985456466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.929762840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78675937652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10967063903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84211587905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42694520950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28855466842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26087713241577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32545900344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33468437194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1132607460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5561089515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77753448486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93437623977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60223960876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33929824829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51920509338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3070068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14555168151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10403442382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15939044952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06713008880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92874002456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56533527374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54227066040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.445396900177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27010250091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72217750549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46948528289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66784381866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90310764312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54329395294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69090938568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87542915344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32750511169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0066413879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4863939285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4956188201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2557430267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9420576095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82571029663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74267578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.462306022644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1947507858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.019455909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89029216766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3792705535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.360818862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2224283218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.674503326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5453395843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7667636871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0215015411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4402627944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5417499542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6155576705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8093042373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8185300827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7078170776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6616878509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5694274902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3480024337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2741947174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1450309753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.812894821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0030508041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3167362213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8241662979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7042284011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.054817199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3961791992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2854671478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4423084259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1286239624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2301111221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0086870193481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1932067871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5437955856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3500490188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5714731216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.368501663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1470766067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4976654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1101732254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1655292510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.267014503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2762413024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0455904006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1747550964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.331597328186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3869533538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5104818344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3813180923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6304187774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.335186958313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7872619628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5068912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.433084487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4515342712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2690591812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5735187530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8318481445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1455326080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3613204956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4628076553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7616291046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5217542648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5955610275269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7154998779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3556852340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9128360748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6545085906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5033016204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4110412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.650918006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1860265731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6750068664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4166774749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1029930114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9184722900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3889999389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7764930725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5827445983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1547584533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8133945465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8410730361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9241094589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1178550720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8503007888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8779783248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3520936965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6381034851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4351301193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5919704437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9517869949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0994033813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0717258453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5145740509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7877655029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3910465240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4648532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1142635345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2618789672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5386619567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4464015960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5663394927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3725929260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.621696472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.547887802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.036865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4151306152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7657203674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9835567474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4299945831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4484481811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.728816986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.245475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1901187896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3377342224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2639274597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5443000793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5627536773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2029361724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4704914093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9722843170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1844806671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2823791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9651050567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6109256744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9430618286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2567481994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2198429107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3121032714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1829395294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7513637542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7698135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2900619506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8472137451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4745807647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7180480957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5371189117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6293773651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7216377258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1865291595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1275825500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6847324371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2013893127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4633102416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8728446960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6478309631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8508014678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0906791687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1091327667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2234325408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9466533660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1311721801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.112720489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6145153045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8543910980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7954483032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3156929016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8323497772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.179349899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5483894348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0686378479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.216251373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1424446105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0132827758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2531566619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0317325592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1942119598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7846775054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.729320526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3935947418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8953876495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0465927124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9174308776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3049221038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3971843719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5817050933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1388549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5852928161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8067169189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3454151153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.489444732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7477722167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7662239074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2311153411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7144584655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6370601654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0763206481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7554531097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4786758422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9768772125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1613998413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3828258514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4935359954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1578102111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0470962524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2721099853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5673427581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4012775421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1060428619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9030685424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.497127532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9251117706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7221393585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6447410583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4602222442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3864135742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9989204406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5007133483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9066619873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2572479248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1280860900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9620151519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6631946563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3310585021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5155754089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4453601837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.737003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7185497283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8292617797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4417667388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.534029006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4269065856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3715515136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5893878936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1983032226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4750843048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9143447875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4643135070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9625225067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5970706939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0322360992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8846168518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3459167480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6227016448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7923583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.939977645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1798515319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8994808197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5857963562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2167549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3643703460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6262893676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2536602020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7703189849854</t>
+    <t xml:space="preserve">27.2167568206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.364372253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6262912750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2536582946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7703170776367</t>
   </si>
   <si>
     <t xml:space="preserve">27.3090171813965</t>
@@ -3734,7 +3737,7 @@
     <t xml:space="preserve">27.8072185516357</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3423290252686</t>
+    <t xml:space="preserve">28.3423271179199</t>
   </si>
   <si>
     <t xml:space="preserve">27.917932510376</t>
@@ -3752,7 +3755,7 @@
     <t xml:space="preserve">27.8256721496582</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9732875823975</t>
+    <t xml:space="preserve">27.9732894897461</t>
   </si>
   <si>
     <t xml:space="preserve">28.3054275512695</t>
@@ -3761,7 +3764,7 @@
     <t xml:space="preserve">28.2869739532471</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0840034484863</t>
+    <t xml:space="preserve">28.0840015411377</t>
   </si>
   <si>
     <t xml:space="preserve">27.7887687683105</t>
@@ -3776,16 +3779,16 @@
     <t xml:space="preserve">26.2203464508057</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5191688537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6150188446045</t>
+    <t xml:space="preserve">25.5191669464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6150169372559</t>
   </si>
   <si>
     <t xml:space="preserve">24.0983619689941</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9656047821045</t>
+    <t xml:space="preserve">24.9656066894531</t>
   </si>
   <si>
     <t xml:space="preserve">24.356689453125</t>
@@ -3812,10 +3815,10 @@
     <t xml:space="preserve">24.633472442627</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2423858642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0947704315186</t>
+    <t xml:space="preserve">25.2423877716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0947723388672</t>
   </si>
   <si>
     <t xml:space="preserve">24.910249710083</t>
@@ -3836,7 +3839,7 @@
     <t xml:space="preserve">25.5376205444336</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8733444213867</t>
+    <t xml:space="preserve">24.8733463287354</t>
   </si>
   <si>
     <t xml:space="preserve">24.9287033081055</t>
@@ -3851,7 +3854,7 @@
     <t xml:space="preserve">24.3013343811035</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8769359588623</t>
+    <t xml:space="preserve">23.8769340515137</t>
   </si>
   <si>
     <t xml:space="preserve">23.526346206665</t>
@@ -3869,13 +3872,13 @@
     <t xml:space="preserve">21.8841152191162</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0353221893311</t>
+    <t xml:space="preserve">21.0353202819824</t>
   </si>
   <si>
     <t xml:space="preserve">20.7031860351562</t>
   </si>
   <si>
-    <t xml:space="preserve">21.736499786377</t>
+    <t xml:space="preserve">21.7365016937256</t>
   </si>
   <si>
     <t xml:space="preserve">21.4597206115723</t>
@@ -3890,7 +3893,7 @@
     <t xml:space="preserve">21.4412670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3525981903076</t>
+    <t xml:space="preserve">20.352596282959</t>
   </si>
   <si>
     <t xml:space="preserve">20.9799671173096</t>
@@ -3899,7 +3902,7 @@
     <t xml:space="preserve">21.9948291778564</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5299396514893</t>
+    <t xml:space="preserve">22.5299377441406</t>
   </si>
   <si>
     <t xml:space="preserve">22.5114860534668</t>
@@ -3917,7 +3920,7 @@
     <t xml:space="preserve">22.9358825683594</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3085136413574</t>
+    <t xml:space="preserve">22.3085117340088</t>
   </si>
   <si>
     <t xml:space="preserve">21.3859119415283</t>
@@ -3929,49 +3932,49 @@
     <t xml:space="preserve">21.8103084564209</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9281997680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0758171081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8877067565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4448566436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2787895202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8174896240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8138980865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2049827575684</t>
+    <t xml:space="preserve">19.928201675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0758190155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8877048492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4448585510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.278787612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8174877166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8138961791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2049808502197</t>
   </si>
   <si>
     <t xml:space="preserve">20.5002117156982</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7585411071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3710479736328</t>
+    <t xml:space="preserve">20.7585430145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3710498809814</t>
   </si>
   <si>
     <t xml:space="preserve">20.0204620361328</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9871463775635</t>
+    <t xml:space="preserve">18.9871444702148</t>
   </si>
   <si>
     <t xml:space="preserve">18.5073928833008</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6770496368408</t>
+    <t xml:space="preserve">17.6770515441895</t>
   </si>
   <si>
     <t xml:space="preserve">18.1291275024414</t>
@@ -3986,7 +3989,7 @@
     <t xml:space="preserve">17.3633670806885</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0845413208008</t>
+    <t xml:space="preserve">15.0845403671265</t>
   </si>
   <si>
     <t xml:space="preserve">15.23215675354</t>
@@ -3998,13 +4001,13 @@
     <t xml:space="preserve">15.3705463409424</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2377948760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.469988822937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2172946929932</t>
+    <t xml:space="preserve">16.23779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4699878692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2172956466675</t>
   </si>
   <si>
     <t xml:space="preserve">14.0604524612427</t>
@@ -4013,7 +4016,7 @@
     <t xml:space="preserve">14.337233543396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6878213882446</t>
+    <t xml:space="preserve">14.6878223419189</t>
   </si>
   <si>
     <t xml:space="preserve">14.8169851303101</t>
@@ -4028,13 +4031,13 @@
     <t xml:space="preserve">14.6601438522339</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8226222991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6565542221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0420017242432</t>
+    <t xml:space="preserve">15.82262134552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6565532684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0420007705688</t>
   </si>
   <si>
     <t xml:space="preserve">13.99587059021</t>
@@ -4043,7 +4046,7 @@
     <t xml:space="preserve">13.8205757141113</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3649110794067</t>
+    <t xml:space="preserve">14.3649101257324</t>
   </si>
   <si>
     <t xml:space="preserve">13.8667058944702</t>
@@ -4064,19 +4067,19 @@
     <t xml:space="preserve">13.3592748641968</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9461498260498</t>
+    <t xml:space="preserve">14.9461507797241</t>
   </si>
   <si>
     <t xml:space="preserve">15.0476360321045</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3059644699097</t>
+    <t xml:space="preserve">15.305965423584</t>
   </si>
   <si>
     <t xml:space="preserve">15.3428688049316</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0384101867676</t>
+    <t xml:space="preserve">15.0384092330933</t>
   </si>
   <si>
     <t xml:space="preserve">15.234112739563</t>
@@ -4401,9 +4404,6 @@
   </si>
   <si>
     <t xml:space="preserve">12.2314186096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.106707572937</t>
   </si>
   <si>
     <t xml:space="preserve">12.7686433792114</t>
@@ -43416,7 +43416,7 @@
         <v>29.5200004577637</v>
       </c>
       <c r="G1428" t="s">
-        <v>605</v>
+        <v>1230</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -43468,7 +43468,7 @@
         <v>29.5</v>
       </c>
       <c r="G1430" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -43494,7 +43494,7 @@
         <v>29.6599998474121</v>
       </c>
       <c r="G1431" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -43546,7 +43546,7 @@
         <v>28.8600006103516</v>
       </c>
       <c r="G1433" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -43572,7 +43572,7 @@
         <v>29.5</v>
       </c>
       <c r="G1434" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -43598,7 +43598,7 @@
         <v>29.5400009155273</v>
       </c>
       <c r="G1435" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -43624,7 +43624,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1436" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -43650,7 +43650,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1437" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -43676,7 +43676,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1438" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -43702,7 +43702,7 @@
         <v>31.0799999237061</v>
       </c>
       <c r="G1439" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -43728,7 +43728,7 @@
         <v>30.3799991607666</v>
       </c>
       <c r="G1440" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -43754,7 +43754,7 @@
         <v>30.1399993896484</v>
       </c>
       <c r="G1441" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -43780,7 +43780,7 @@
         <v>30.7199993133545</v>
       </c>
       <c r="G1442" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -43806,7 +43806,7 @@
         <v>30.2600002288818</v>
       </c>
       <c r="G1443" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -43832,7 +43832,7 @@
         <v>30.3799991607666</v>
       </c>
       <c r="G1444" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -43858,7 +43858,7 @@
         <v>30.0200004577637</v>
       </c>
       <c r="G1445" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -43884,7 +43884,7 @@
         <v>29.3199996948242</v>
       </c>
       <c r="G1446" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -43910,7 +43910,7 @@
         <v>30.0799999237061</v>
       </c>
       <c r="G1447" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -43936,7 +43936,7 @@
         <v>30.1599998474121</v>
       </c>
       <c r="G1448" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -43962,7 +43962,7 @@
         <v>30.3199996948242</v>
       </c>
       <c r="G1449" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -43988,7 +43988,7 @@
         <v>30.6800003051758</v>
       </c>
       <c r="G1450" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -44014,7 +44014,7 @@
         <v>30.6599998474121</v>
       </c>
       <c r="G1451" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -44040,7 +44040,7 @@
         <v>30.4400005340576</v>
       </c>
       <c r="G1452" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -44066,7 +44066,7 @@
         <v>30.1200008392334</v>
       </c>
       <c r="G1453" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -44092,7 +44092,7 @@
         <v>28.5</v>
       </c>
       <c r="G1454" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -44170,7 +44170,7 @@
         <v>29.2600002288818</v>
       </c>
       <c r="G1457" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -44196,7 +44196,7 @@
         <v>28.4200000762939</v>
       </c>
       <c r="G1458" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -44222,7 +44222,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G1459" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -44248,7 +44248,7 @@
         <v>26.6800003051758</v>
       </c>
       <c r="G1460" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -44274,7 +44274,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G1461" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -44300,7 +44300,7 @@
         <v>27.0599994659424</v>
       </c>
       <c r="G1462" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -44326,7 +44326,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1463" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -44352,7 +44352,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1464" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -44404,7 +44404,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1466" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -44430,7 +44430,7 @@
         <v>25.2199993133545</v>
       </c>
       <c r="G1467" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -44508,7 +44508,7 @@
         <v>26.0799999237061</v>
       </c>
       <c r="G1470" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -44534,7 +44534,7 @@
         <v>26.2399997711182</v>
       </c>
       <c r="G1471" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -44560,7 +44560,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G1472" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -44586,7 +44586,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1473" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -44612,7 +44612,7 @@
         <v>27.3600006103516</v>
       </c>
       <c r="G1474" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -44638,7 +44638,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1475" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -44664,7 +44664,7 @@
         <v>27</v>
       </c>
       <c r="G1476" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -44690,7 +44690,7 @@
         <v>27.0799999237061</v>
       </c>
       <c r="G1477" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -44742,7 +44742,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1479" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -44768,7 +44768,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1480" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -44794,7 +44794,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1481" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -44820,7 +44820,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1482" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -44846,7 +44846,7 @@
         <v>26.7399997711182</v>
       </c>
       <c r="G1483" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -44872,7 +44872,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G1484" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -44898,7 +44898,7 @@
         <v>27</v>
       </c>
       <c r="G1485" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -44924,7 +44924,7 @@
         <v>26.9599990844727</v>
       </c>
       <c r="G1486" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -44950,7 +44950,7 @@
         <v>27.0799999237061</v>
       </c>
       <c r="G1487" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -44976,7 +44976,7 @@
         <v>27.0200004577637</v>
       </c>
       <c r="G1488" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -45002,7 +45002,7 @@
         <v>26.9200000762939</v>
       </c>
       <c r="G1489" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -45028,7 +45028,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1490" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -45054,7 +45054,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G1491" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -45080,7 +45080,7 @@
         <v>25.8799991607666</v>
       </c>
       <c r="G1492" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -45158,7 +45158,7 @@
         <v>25.8799991607666</v>
       </c>
       <c r="G1495" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -45184,7 +45184,7 @@
         <v>25.5</v>
       </c>
       <c r="G1496" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -45210,7 +45210,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1497" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -45288,7 +45288,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1500" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -45314,7 +45314,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1501" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -45340,7 +45340,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G1502" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -45392,7 +45392,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1504" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -45418,7 +45418,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G1505" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -45444,7 +45444,7 @@
         <v>23.5599994659424</v>
       </c>
       <c r="G1506" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -45470,7 +45470,7 @@
         <v>23.2600002288818</v>
       </c>
       <c r="G1507" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -45496,7 +45496,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1508" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -45522,7 +45522,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G1509" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -45548,7 +45548,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G1510" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -45574,7 +45574,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1511" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -45600,7 +45600,7 @@
         <v>23.2399997711182</v>
       </c>
       <c r="G1512" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -45652,7 +45652,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G1514" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -45678,7 +45678,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1515" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -45782,7 +45782,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1519" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -45808,7 +45808,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G1520" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -45834,7 +45834,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G1521" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -45886,7 +45886,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G1523" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -45912,7 +45912,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1524" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -45938,7 +45938,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G1525" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -45964,7 +45964,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G1526" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -45990,7 +45990,7 @@
         <v>25.0599994659424</v>
       </c>
       <c r="G1527" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -46016,7 +46016,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G1528" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -46042,7 +46042,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G1529" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -46068,7 +46068,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G1530" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -46094,7 +46094,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1531" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -46120,7 +46120,7 @@
         <v>23.1800003051758</v>
       </c>
       <c r="G1532" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -46146,7 +46146,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G1533" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -46276,7 +46276,7 @@
         <v>23.2399997711182</v>
       </c>
       <c r="G1538" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -46302,7 +46302,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G1539" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -46328,7 +46328,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G1540" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -46354,7 +46354,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1541" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -46380,7 +46380,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1542" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -46406,7 +46406,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G1543" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -46458,7 +46458,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G1545" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -46614,7 +46614,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G1551" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -46640,7 +46640,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G1552" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -46666,7 +46666,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G1553" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -46692,7 +46692,7 @@
         <v>22.5599994659424</v>
       </c>
       <c r="G1554" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -46744,7 +46744,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1556" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -46796,7 +46796,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G1558" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -46822,7 +46822,7 @@
         <v>22.5</v>
       </c>
       <c r="G1559" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -46848,7 +46848,7 @@
         <v>22.0799999237061</v>
       </c>
       <c r="G1560" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -46874,7 +46874,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1561" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -46900,7 +46900,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G1562" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -46926,7 +46926,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G1563" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -46952,7 +46952,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G1564" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -46978,7 +46978,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1565" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -47004,7 +47004,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G1566" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -47030,7 +47030,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G1567" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -47056,7 +47056,7 @@
         <v>18.5</v>
       </c>
       <c r="G1568" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -47082,7 +47082,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1569" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -47160,7 +47160,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1572" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -47186,7 +47186,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G1573" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -47212,7 +47212,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1574" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -47264,7 +47264,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1576" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -47290,7 +47290,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1577" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -47316,7 +47316,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1578" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -47342,7 +47342,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G1579" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -47368,7 +47368,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1580" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -47394,7 +47394,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G1581" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -47420,7 +47420,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1582" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -47446,7 +47446,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1583" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -47498,7 +47498,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1585" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -47524,7 +47524,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1586" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -47550,7 +47550,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G1587" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -47576,7 +47576,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1588" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -47602,7 +47602,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G1589" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -47810,7 +47810,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1597" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -47836,7 +47836,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1598" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -47862,7 +47862,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1599" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -47940,7 +47940,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1602" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -47992,7 +47992,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G1604" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -48018,7 +48018,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G1605" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -48044,7 +48044,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1606" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -48174,7 +48174,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G1611" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -48278,7 +48278,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G1615" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -48304,7 +48304,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1616" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -48330,7 +48330,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1617" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -48382,7 +48382,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1619" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -48408,7 +48408,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G1620" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -48460,7 +48460,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G1622" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -48486,7 +48486,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G1623" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -48512,7 +48512,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1624" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -48538,7 +48538,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1625" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -48564,7 +48564,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1626" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -48590,7 +48590,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G1627" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -48616,7 +48616,7 @@
         <v>16</v>
       </c>
       <c r="G1628" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -48642,7 +48642,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G1629" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -48668,7 +48668,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1630" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -48694,7 +48694,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1631" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -48720,7 +48720,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1632" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -48746,7 +48746,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1633" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -48772,7 +48772,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1634" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -48798,7 +48798,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1635" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -48824,7 +48824,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1636" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -48850,7 +48850,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G1637" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -48876,7 +48876,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G1638" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -48902,7 +48902,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1639" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -48928,7 +48928,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G1640" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -48954,7 +48954,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1641" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -48980,7 +48980,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G1642" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -49006,7 +49006,7 @@
         <v>13.5</v>
       </c>
       <c r="G1643" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -49032,7 +49032,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1644" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -49058,7 +49058,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G1645" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -49084,7 +49084,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1646" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -49110,7 +49110,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1647" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -49136,7 +49136,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1648" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -49162,7 +49162,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1649" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -49188,7 +49188,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G1650" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -49214,7 +49214,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G1651" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -49240,7 +49240,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G1652" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -49266,7 +49266,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1653" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -49292,7 +49292,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G1654" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -49318,7 +49318,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1655" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -49344,7 +49344,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1656" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -49370,7 +49370,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1657" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -49396,7 +49396,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1658" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -49422,7 +49422,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1659" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -49448,7 +49448,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1660" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -49474,7 +49474,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G1661" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -49500,7 +49500,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1662" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -49526,7 +49526,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1663" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -49552,7 +49552,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G1664" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -49578,7 +49578,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1665" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -49604,7 +49604,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G1666" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -49630,7 +49630,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G1667" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -49656,7 +49656,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1668" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -49682,7 +49682,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1669" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -49708,7 +49708,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1670" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -49734,7 +49734,7 @@
         <v>13</v>
       </c>
       <c r="G1671" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -49760,7 +49760,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1672" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -49786,7 +49786,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1673" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -49812,7 +49812,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G1674" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -49838,7 +49838,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G1675" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -49864,7 +49864,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1676" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -49890,7 +49890,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G1677" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -49916,7 +49916,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1678" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -49942,7 +49942,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G1679" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -49968,7 +49968,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1680" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -49994,7 +49994,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G1681" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -50020,7 +50020,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G1682" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -50046,7 +50046,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1683" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -50072,7 +50072,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1684" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -50098,7 +50098,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1685" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -50124,7 +50124,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1686" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -50150,7 +50150,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G1687" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -50176,7 +50176,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1688" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -50202,7 +50202,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1689" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -50228,7 +50228,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G1690" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -50254,7 +50254,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1691" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -50280,7 +50280,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G1692" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -50306,7 +50306,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1693" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -50332,7 +50332,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G1694" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -50358,7 +50358,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G1695" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -50384,7 +50384,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1696" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -50410,7 +50410,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1697" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -50436,7 +50436,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1698" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -50462,7 +50462,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1699" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -50488,7 +50488,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1700" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -50514,7 +50514,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1701" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -50540,7 +50540,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G1702" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -50566,7 +50566,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1703" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -50592,7 +50592,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1704" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -50618,7 +50618,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1705" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -50644,7 +50644,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G1706" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -50670,7 +50670,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1707" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -50696,7 +50696,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G1708" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -50722,7 +50722,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G1709" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -50748,7 +50748,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1710" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -50774,7 +50774,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1711" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -50800,7 +50800,7 @@
         <v>11.75</v>
       </c>
       <c r="G1712" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -50826,7 +50826,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1713" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -50852,7 +50852,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1714" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -50878,7 +50878,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G1715" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -50904,7 +50904,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1716" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -50930,7 +50930,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G1717" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -50956,7 +50956,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1718" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -50982,7 +50982,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1719" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -51008,7 +51008,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1720" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -51034,7 +51034,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1721" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -51060,7 +51060,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1722" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -51086,7 +51086,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1723" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -51112,7 +51112,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1724" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -51138,7 +51138,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1725" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -51164,7 +51164,7 @@
         <v>11.75</v>
       </c>
       <c r="G1726" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -51190,7 +51190,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1727" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -51216,7 +51216,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1728" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -51242,7 +51242,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1729" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -51268,7 +51268,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1730" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -51294,7 +51294,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1731" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -51320,7 +51320,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G1732" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -51346,7 +51346,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G1733" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -51372,7 +51372,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1734" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -51398,7 +51398,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1735" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -51424,7 +51424,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G1736" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -51450,7 +51450,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G1737" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -51476,7 +51476,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1738" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -51502,7 +51502,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G1739" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -51528,7 +51528,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G1740" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -51554,7 +51554,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G1741" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -51580,7 +51580,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1742" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -51606,7 +51606,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1743" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -51632,7 +51632,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1744" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -51658,7 +51658,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1745" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -51684,7 +51684,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1746" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -51710,7 +51710,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1747" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -51736,7 +51736,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1748" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -51762,7 +51762,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G1749" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -51788,7 +51788,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G1750" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -51814,7 +51814,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1751" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -51840,7 +51840,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1752" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -51866,7 +51866,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G1753" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -51892,7 +51892,7 @@
         <v>12.710000038147</v>
       </c>
       <c r="G1754" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -51918,7 +51918,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1755" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -51944,7 +51944,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1756" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -51970,7 +51970,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1757" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -51996,7 +51996,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1758" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -52022,7 +52022,7 @@
         <v>12.75</v>
       </c>
       <c r="G1759" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -52048,7 +52048,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1760" t="s">
-        <v>1463</v>
+        <v>50</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -52074,7 +52074,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1761" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -52126,7 +52126,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1763" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -52178,7 +52178,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1765" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -52308,7 +52308,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1770" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -52386,7 +52386,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1773" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -52412,7 +52412,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1774" t="s">
-        <v>1463</v>
+        <v>50</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -52464,7 +52464,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G1776" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -52568,7 +52568,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G1780" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -52594,7 +52594,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G1781" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -52620,7 +52620,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1782" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -52646,7 +52646,7 @@
         <v>13</v>
       </c>
       <c r="G1783" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -52724,7 +52724,7 @@
         <v>13.5</v>
       </c>
       <c r="G1786" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -53270,7 +53270,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1807" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -53764,7 +53764,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1826" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -54154,7 +54154,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1841" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -54388,7 +54388,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1850" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -54648,7 +54648,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -54804,7 +54804,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G1866" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -54856,7 +54856,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G1868" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -71010,7 +71010,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.649375</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>65808</v>
@@ -71031,6 +71031,32 @@
         <v>1981</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6496412037</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>56230</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>7.94999980926514</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>7.78000020980835</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>7.92000007629395</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>7.84000015258789</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>1981</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -44,28 +44,28 @@
     <t xml:space="preserve">BSS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9787998199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.747950553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3974046707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.243504524231</t>
+    <t xml:space="preserve">12.9788007736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.747953414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3974027633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2435054779053</t>
   </si>
   <si>
     <t xml:space="preserve">12.2606058120728</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1409063339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4825630187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.858416557312</t>
+    <t xml:space="preserve">12.140905380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4825620651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8584175109863</t>
   </si>
   <si>
     <t xml:space="preserve">9.79822540283203</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">10.3539695739746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84952354431152</t>
+    <t xml:space="preserve">9.84952449798584</t>
   </si>
   <si>
     <t xml:space="preserve">10.473669052124</t>
@@ -89,28 +89,28 @@
     <t xml:space="preserve">10.8156661987305</t>
   </si>
   <si>
-    <t xml:space="preserve">10.730167388916</t>
+    <t xml:space="preserve">10.7301683425903</t>
   </si>
   <si>
     <t xml:space="preserve">10.576268196106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.636116027832</t>
+    <t xml:space="preserve">10.6361169815063</t>
   </si>
   <si>
     <t xml:space="preserve">10.191520690918</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4565696716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4907693862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0205230712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03728103637695</t>
+    <t xml:space="preserve">10.4565687179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4907703399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0205221176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03728008270264</t>
   </si>
   <si>
     <t xml:space="preserve">8.97743129730225</t>
@@ -119,28 +119,28 @@
     <t xml:space="preserve">9.40492725372314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14842796325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43057727813721</t>
+    <t xml:space="preserve">9.14842987060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43057632446289</t>
   </si>
   <si>
     <t xml:space="preserve">9.90082359313965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66142654418945</t>
+    <t xml:space="preserve">9.66142463684082</t>
   </si>
   <si>
     <t xml:space="preserve">10.4394693374634</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3454208374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2000713348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0037651062012</t>
+    <t xml:space="preserve">10.345419883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2000722885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0037641525269</t>
   </si>
   <si>
     <t xml:space="preserve">10.5506181716919</t>
@@ -155,37 +155,37 @@
     <t xml:space="preserve">11.0379638671875</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9097156524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8074598312378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9442586898804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.106707572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7732601165771</t>
+    <t xml:space="preserve">10.9097166061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8074588775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9442577362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1067066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7732610702515</t>
   </si>
   <si>
     <t xml:space="preserve">11.9699077606201</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6279125213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.371413230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3799629211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8416585922241</t>
+    <t xml:space="preserve">11.6279106140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3714122772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3799619674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6621103286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8416595458984</t>
   </si>
   <si>
     <t xml:space="preserve">11.918607711792</t>
@@ -194,13 +194,13 @@
     <t xml:space="preserve">11.7989091873169</t>
   </si>
   <si>
-    <t xml:space="preserve">12.046856880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1922063827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2007570266724</t>
+    <t xml:space="preserve">12.0468578338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1922054290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.200756072998</t>
   </si>
   <si>
     <t xml:space="preserve">12.3375558853149</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">12.1323556900024</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1665554046631</t>
+    <t xml:space="preserve">12.1665563583374</t>
   </si>
   <si>
     <t xml:space="preserve">12.2178564071655</t>
@@ -218,40 +218,40 @@
     <t xml:space="preserve">11.9015083312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5680618286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2859125137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7390594482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8844079971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8160095214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7048597335815</t>
+    <t xml:space="preserve">11.568060874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2859115600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7390584945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8844089508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8160076141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7048587799072</t>
   </si>
   <si>
     <t xml:space="preserve">11.6022605895996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6364603042603</t>
+    <t xml:space="preserve">11.6364612579346</t>
   </si>
   <si>
     <t xml:space="preserve">11.4740114212036</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1918659210205</t>
+    <t xml:space="preserve">11.1918630599976</t>
   </si>
   <si>
     <t xml:space="preserve">11.1063642501831</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1149158477783</t>
+    <t xml:space="preserve">11.1149129867554</t>
   </si>
   <si>
     <t xml:space="preserve">11.3201122283936</t>
@@ -263,28 +263,28 @@
     <t xml:space="preserve">11.1576642990112</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0550651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9866647720337</t>
+    <t xml:space="preserve">11.055064201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.986665725708</t>
   </si>
   <si>
     <t xml:space="preserve">11.1405639648438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6019191741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9541416168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4346132278442</t>
+    <t xml:space="preserve">10.60191822052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.954140663147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4346113204956</t>
   </si>
   <si>
     <t xml:space="preserve">10.3553619384766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2232780456543</t>
+    <t xml:space="preserve">10.22327709198</t>
   </si>
   <si>
     <t xml:space="preserve">10.2673053741455</t>
@@ -299,22 +299,22 @@
     <t xml:space="preserve">10.0031385421753</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3025274276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2496938705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6107234954834</t>
+    <t xml:space="preserve">10.302529335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2496957778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6107244491577</t>
   </si>
   <si>
     <t xml:space="preserve">11.4120321273804</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1302528381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9189176559448</t>
+    <t xml:space="preserve">11.1302547454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9189195632935</t>
   </si>
   <si>
     <t xml:space="preserve">11.2359199523926</t>
@@ -323,70 +323,70 @@
     <t xml:space="preserve">11.2799472808838</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0069751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8308639526367</t>
+    <t xml:space="preserve">11.0069742202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8308629989624</t>
   </si>
   <si>
     <t xml:space="preserve">10.8396682739258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9277238845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9101123809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8132524490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5138626098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0647783279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9943323135376</t>
+    <t xml:space="preserve">10.9277229309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9101142883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8132514953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.513861656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0647773742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99433326721191</t>
   </si>
   <si>
     <t xml:space="preserve">9.95030498504639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68613910675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0383596420288</t>
+    <t xml:space="preserve">9.68613719940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0383605957031</t>
   </si>
   <si>
     <t xml:space="preserve">10.4962501525879</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3465557098389</t>
+    <t xml:space="preserve">10.3465566635132</t>
   </si>
   <si>
     <t xml:space="preserve">10.4522228240967</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5843076705933</t>
+    <t xml:space="preserve">10.5843067169189</t>
   </si>
   <si>
     <t xml:space="preserve">9.87986087799072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12257957458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67733192443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57166576385498</t>
+    <t xml:space="preserve">9.12258052825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67733097076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5716667175293</t>
   </si>
   <si>
     <t xml:space="preserve">9.93269348144531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1880550384521</t>
+    <t xml:space="preserve">10.1880559921265</t>
   </si>
   <si>
     <t xml:space="preserve">9.98552703857422</t>
@@ -395,67 +395,67 @@
     <t xml:space="preserve">9.18421936035156</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14019107818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72136116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0823888778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3817777633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2849178314209</t>
+    <t xml:space="preserve">9.14019203186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72135925292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.082389831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.381778717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2849168777466</t>
   </si>
   <si>
     <t xml:space="preserve">10.1352224349976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2144718170166</t>
+    <t xml:space="preserve">10.2144727706909</t>
   </si>
   <si>
     <t xml:space="preserve">10.1528339385986</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6987791061401</t>
+    <t xml:space="preserve">10.6987781524658</t>
   </si>
   <si>
     <t xml:space="preserve">11.0774192810059</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0157794952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.033390045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9893627166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8748922348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0950288772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2535305023193</t>
+    <t xml:space="preserve">11.0157814025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0333909988403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9893617630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8748903274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0950307846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.253529548645</t>
   </si>
   <si>
     <t xml:space="preserve">11.3151702880859</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7251968383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0510034561157</t>
+    <t xml:space="preserve">10.7251958847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0510025024414</t>
   </si>
   <si>
     <t xml:space="preserve">10.9013080596924</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1654748916626</t>
+    <t xml:space="preserve">11.1654739379883</t>
   </si>
   <si>
     <t xml:space="preserve">11.0598087310791</t>
@@ -464,25 +464,25 @@
     <t xml:space="preserve">11.2183074951172</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1214466094971</t>
+    <t xml:space="preserve">11.1214456558228</t>
   </si>
   <si>
     <t xml:space="preserve">11.1830863952637</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2623357772827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5265045166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7466430664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.773060798645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6850051879883</t>
+    <t xml:space="preserve">11.262336730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5265035629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7466440200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7730588912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.685004234314</t>
   </si>
   <si>
     <t xml:space="preserve">11.7994766235352</t>
@@ -491,19 +491,19 @@
     <t xml:space="preserve">11.6497821807861</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6673936843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4472522735596</t>
+    <t xml:space="preserve">11.6673927307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4472532272339</t>
   </si>
   <si>
     <t xml:space="preserve">11.323974609375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3680038452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1390571594238</t>
+    <t xml:space="preserve">11.3680028915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1390581130981</t>
   </si>
   <si>
     <t xml:space="preserve">11.6938095092773</t>
@@ -515,49 +515,49 @@
     <t xml:space="preserve">11.8258943557739</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0372266769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0548391342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.063645362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5039234161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5303392410278</t>
+    <t xml:space="preserve">12.0372285842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.054838180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0636434555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5039215087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5303401947021</t>
   </si>
   <si>
     <t xml:space="preserve">12.4070615768433</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2837820053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6007862091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9177856445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8121194839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8561477661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0322580337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4108963012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5782041549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6838712692261</t>
+    <t xml:space="preserve">12.2837829589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6007843017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9177865982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8121175765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.856146812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0322570800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4108972549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5782051086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6838703155518</t>
   </si>
   <si>
     <t xml:space="preserve">13.4285087585449</t>
@@ -566,37 +566,37 @@
     <t xml:space="preserve">14.3707056045532</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2210111618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2562351226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1329545974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1241493225098</t>
+    <t xml:space="preserve">14.2210102081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2562341690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1329555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1241512298584</t>
   </si>
   <si>
     <t xml:space="preserve">14.0713157653809</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9216213226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7807321548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6046209335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7631206512451</t>
+    <t xml:space="preserve">13.9216222763062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7807302474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6046199798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7631196975708</t>
   </si>
   <si>
     <t xml:space="preserve">13.8335657119751</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7278995513916</t>
+    <t xml:space="preserve">13.7278985977173</t>
   </si>
   <si>
     <t xml:space="preserve">13.1995639801025</t>
@@ -605,52 +605,52 @@
     <t xml:space="preserve">13.375675201416</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1555347442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6486492156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5605926513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.736704826355</t>
+    <t xml:space="preserve">13.155535697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6486482620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5605916976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7367057800293</t>
   </si>
   <si>
     <t xml:space="preserve">13.8775939941406</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1769828796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0977334976196</t>
+    <t xml:space="preserve">14.1769847869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0977344512939</t>
   </si>
   <si>
     <t xml:space="preserve">14.7845697402954</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3040943145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2776803970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.489013671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4978189468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3657388687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4449882507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3393201828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5330438613892</t>
+    <t xml:space="preserve">15.3040962219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.277681350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4890146255493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4978199005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3657360076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4449872970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.339319229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5330419540405</t>
   </si>
   <si>
     <t xml:space="preserve">15.6651268005371</t>
@@ -659,76 +659,76 @@
     <t xml:space="preserve">15.5418472290039</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2424564361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8060159683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1934604644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3695755004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4664344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5104637145996</t>
+    <t xml:space="preserve">15.2424592971802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8060169219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1934585571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.369571685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4664325714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.510461807251</t>
   </si>
   <si>
     <t xml:space="preserve">17.03879737854</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8891010284424</t>
+    <t xml:space="preserve">16.889102935791</t>
   </si>
   <si>
     <t xml:space="preserve">17.1532688140869</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7746295928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5544910430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.237491607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5897121429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6513519287109</t>
+    <t xml:space="preserve">16.7746276855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5544872283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2374877929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.589714050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6513538360596</t>
   </si>
   <si>
     <t xml:space="preserve">16.5720996856689</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9947681427002</t>
+    <t xml:space="preserve">16.9947662353516</t>
   </si>
   <si>
     <t xml:space="preserve">16.7041835784912</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8802947998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8538799285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0123825073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2941570281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1268539428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5368804931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0828227996826</t>
+    <t xml:space="preserve">16.8802967071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8538780212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0123767852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2941589355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1268520355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5368785858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">16.8626842498779</t>
@@ -746,25 +746,25 @@
     <t xml:space="preserve">17.540714263916</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5054912567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7168273925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4526596069336</t>
+    <t xml:space="preserve">17.5054931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7168254852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4526557922363</t>
   </si>
   <si>
     <t xml:space="preserve">17.5583267211914</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7432441711426</t>
+    <t xml:space="preserve">17.7432403564453</t>
   </si>
   <si>
     <t xml:space="preserve">17.8401050567627</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5759372711182</t>
+    <t xml:space="preserve">17.5759334564209</t>
   </si>
   <si>
     <t xml:space="preserve">16.7482128143311</t>
@@ -773,19 +773,19 @@
     <t xml:space="preserve">16.7658252716064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9507369995117</t>
+    <t xml:space="preserve">16.950740814209</t>
   </si>
   <si>
     <t xml:space="preserve">17.1620750427246</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2765502929688</t>
+    <t xml:space="preserve">17.2765464782715</t>
   </si>
   <si>
     <t xml:space="preserve">16.6865749359131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1092414855957</t>
+    <t xml:space="preserve">17.1092433929443</t>
   </si>
   <si>
     <t xml:space="preserve">16.8186569213867</t>
@@ -794,10 +794,10 @@
     <t xml:space="preserve">17.2325172424316</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2853527069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3910217285156</t>
+    <t xml:space="preserve">17.2853507995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.391019821167</t>
   </si>
   <si>
     <t xml:space="preserve">17.250129699707</t>
@@ -809,16 +809,16 @@
     <t xml:space="preserve">17.3734092712402</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6463813781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9457702636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.372278213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9358291625977</t>
+    <t xml:space="preserve">17.6463832855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9457721710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3722743988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9358329772949</t>
   </si>
   <si>
     <t xml:space="preserve">20.3849182128906</t>
@@ -830,40 +830,40 @@
     <t xml:space="preserve">20.3408889770508</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8340034484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0453357696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5824737548828</t>
+    <t xml:space="preserve">20.8340015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.045337677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5824775695801</t>
   </si>
   <si>
     <t xml:space="preserve">21.0893630981445</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3271160125732</t>
+    <t xml:space="preserve">21.327112197876</t>
   </si>
   <si>
     <t xml:space="preserve">21.6529197692871</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7497844696045</t>
+    <t xml:space="preserve">21.7497806549072</t>
   </si>
   <si>
     <t xml:space="preserve">21.9170875549316</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8114223480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0139503479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.286922454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2605056762695</t>
+    <t xml:space="preserve">21.8114204406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0139484405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2869205474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2605094909668</t>
   </si>
   <si>
     <t xml:space="preserve">22.348560333252</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">22.3221454620361</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1900577545166</t>
+    <t xml:space="preserve">22.1900615692139</t>
   </si>
   <si>
     <t xml:space="preserve">22.6303405761719</t>
@@ -881,28 +881,28 @@
     <t xml:space="preserve">22.4366149902344</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4806480407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.665563583374</t>
+    <t xml:space="preserve">22.4806461334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6655616760254</t>
   </si>
   <si>
     <t xml:space="preserve">22.6215343475342</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6743679046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8945045471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0970344543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8328685760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.374979019165</t>
+    <t xml:space="preserve">22.6743659973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8945064544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0970363616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8328666687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3749771118164</t>
   </si>
   <si>
     <t xml:space="preserve">23.1938972473145</t>
@@ -911,10 +911,10 @@
     <t xml:space="preserve">23.3876190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5108985900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9159526824951</t>
+    <t xml:space="preserve">23.5108966827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9159564971924</t>
   </si>
   <si>
     <t xml:space="preserve">24.2417621612549</t>
@@ -926,37 +926,37 @@
     <t xml:space="preserve">24.6556224822998</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9197883605957</t>
+    <t xml:space="preserve">24.9197902679443</t>
   </si>
   <si>
     <t xml:space="preserve">25.0870971679688</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9638175964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8933753967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4255466461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4879341125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3970069885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.628734588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1545715332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6732921600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6804084777832</t>
+    <t xml:space="preserve">24.9638195037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8933734893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4255447387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4879322052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.397008895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6287326812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1545696258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6732940673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6804046630859</t>
   </si>
   <si>
     <t xml:space="preserve">29.3666687011719</t>
@@ -965,34 +965,34 @@
     <t xml:space="preserve">27.8069820404053</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4665088653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0190811157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4914455413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7677364349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8746814727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3024806976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7748413085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2400932312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6678943634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8283157348633</t>
+    <t xml:space="preserve">28.4665069580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0190830230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4914436340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7677326202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8746795654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3024826049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7748394012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2400951385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6678905487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8283233642578</t>
   </si>
   <si>
     <t xml:space="preserve">30.8996162414551</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">31.0154800415039</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9976539611816</t>
+    <t xml:space="preserve">30.9976577758789</t>
   </si>
   <si>
     <t xml:space="preserve">30.9352684020996</t>
@@ -1010,49 +1010,49 @@
     <t xml:space="preserve">30.6500663757324</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7481060028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6857204437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3577537536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5003566741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3131923675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2775440216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1687870025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1331443786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9994525909424</t>
+    <t xml:space="preserve">30.748104095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6857223510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3577556610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5003509521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3131942749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2775402069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1687927246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1331424713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9994583129883</t>
   </si>
   <si>
     <t xml:space="preserve">29.9281578063965</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0529327392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4825344085693</t>
+    <t xml:space="preserve">30.0529308319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4825325012207</t>
   </si>
   <si>
     <t xml:space="preserve">29.8122940063477</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9121322631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1260318756104</t>
+    <t xml:space="preserve">28.912130355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1260299682617</t>
   </si>
   <si>
     <t xml:space="preserve">27.7713317871094</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">27.9674053192139</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2544040679932</t>
+    <t xml:space="preserve">27.2544078826904</t>
   </si>
   <si>
     <t xml:space="preserve">27.6911182403564</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">27.5752582550049</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1189212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.350643157959</t>
+    <t xml:space="preserve">28.1189155578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3506393432617</t>
   </si>
   <si>
     <t xml:space="preserve">27.7178554534912</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5734596252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6180210113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.519983291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7873573303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7855529785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.536003112793</t>
+    <t xml:space="preserve">28.5734558105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6180191040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5199813842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.787353515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7855548858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5360088348389</t>
   </si>
   <si>
     <t xml:space="preserve">29.3310203552246</t>
@@ -1106,31 +1106,31 @@
     <t xml:space="preserve">29.1705932617188</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2329769134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1438579559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3221073150635</t>
+    <t xml:space="preserve">29.2329788208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.143856048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3221111297607</t>
   </si>
   <si>
     <t xml:space="preserve">28.9656066894531</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7071437835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9923439025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9477787017822</t>
+    <t xml:space="preserve">28.7071418762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9923419952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9477825164795</t>
   </si>
   <si>
     <t xml:space="preserve">29.607307434082</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8568572998047</t>
+    <t xml:space="preserve">29.8568553924561</t>
   </si>
   <si>
     <t xml:space="preserve">29.4023208618164</t>
@@ -1142,55 +1142,55 @@
     <t xml:space="preserve">28.814094543457</t>
   </si>
   <si>
-    <t xml:space="preserve">29.687520980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6162185668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6786041259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6964302062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1420555114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8390293121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1866188049316</t>
+    <t xml:space="preserve">29.6875190734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6162204742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6786060333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6964321136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1420574188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8390312194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1866149902344</t>
   </si>
   <si>
     <t xml:space="preserve">29.5181789398193</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1795043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4379692077637</t>
+    <t xml:space="preserve">29.1795082092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.437967300415</t>
   </si>
   <si>
     <t xml:space="preserve">30.3648681640625</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4629058837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4718189239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2935676574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0974922180176</t>
+    <t xml:space="preserve">30.4629096984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4718170166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.293571472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0974960327148</t>
   </si>
   <si>
     <t xml:space="preserve">30.0618419647217</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2311763763428</t>
+    <t xml:space="preserve">30.23118019104</t>
   </si>
   <si>
     <t xml:space="preserve">32.0849800109863</t>
@@ -1202,52 +1202,52 @@
     <t xml:space="preserve">30.819408416748</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9958572387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7730464935303</t>
+    <t xml:space="preserve">31.9958553314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7730388641357</t>
   </si>
   <si>
     <t xml:space="preserve">31.6928272247314</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1830139160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0760612487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9512901306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3077926635742</t>
+    <t xml:space="preserve">32.1830177307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0760726928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9512882232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3077964782715</t>
   </si>
   <si>
     <t xml:space="preserve">33.1990394592285</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3951148986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.758731842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6963386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7319869995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5804748535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2239837646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4378814697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5448303222656</t>
+    <t xml:space="preserve">33.3951187133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7587242126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6963424682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.731990814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5804786682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2239799499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.437873840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5448265075684</t>
   </si>
   <si>
     <t xml:space="preserve">35.4271659851074</t>
@@ -1259,19 +1259,19 @@
     <t xml:space="preserve">34.6606903076172</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3754920959473</t>
+    <t xml:space="preserve">34.37548828125</t>
   </si>
   <si>
     <t xml:space="preserve">33.8674774169922</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8496551513672</t>
+    <t xml:space="preserve">33.8496513366699</t>
   </si>
   <si>
     <t xml:space="preserve">34.1437644958496</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7159690856934</t>
+    <t xml:space="preserve">33.7159652709961</t>
   </si>
   <si>
     <t xml:space="preserve">34.0635528564453</t>
@@ -1280,64 +1280,64 @@
     <t xml:space="preserve">34.3130989074707</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1170234680176</t>
+    <t xml:space="preserve">34.1170272827148</t>
   </si>
   <si>
     <t xml:space="preserve">34.420051574707</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7765579223633</t>
+    <t xml:space="preserve">34.7765502929688</t>
   </si>
   <si>
     <t xml:space="preserve">34.6161270141602</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3041915893555</t>
+    <t xml:space="preserve">34.3041877746582</t>
   </si>
   <si>
     <t xml:space="preserve">34.1081161499023</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8425369262695</t>
+    <t xml:space="preserve">32.8425407409668</t>
   </si>
   <si>
     <t xml:space="preserve">34.0902900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1063194274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2471160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3005905151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1847267150879</t>
+    <t xml:space="preserve">35.106315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2471122741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.300594329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1847229003906</t>
   </si>
   <si>
     <t xml:space="preserve">36.4966659545898</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4146461486816</t>
+    <t xml:space="preserve">37.4146499633789</t>
   </si>
   <si>
     <t xml:space="preserve">38.8584747314453</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9208641052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6178359985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5821914672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2702484130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4306755065918</t>
+    <t xml:space="preserve">38.9208602905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6178398132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5821876525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2702445983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4306716918945</t>
   </si>
   <si>
     <t xml:space="preserve">39.2149772644043</t>
@@ -1352,16 +1352,16 @@
     <t xml:space="preserve">38.3504638671875</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0563468933105</t>
+    <t xml:space="preserve">38.0563507080078</t>
   </si>
   <si>
     <t xml:space="preserve">38.3682899475098</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3415451049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5197982788086</t>
+    <t xml:space="preserve">38.341552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5198059082031</t>
   </si>
   <si>
     <t xml:space="preserve">38.5643615722656</t>
@@ -1373,19 +1373,19 @@
     <t xml:space="preserve">38.689136505127</t>
   </si>
   <si>
-    <t xml:space="preserve">38.733699798584</t>
+    <t xml:space="preserve">38.7336959838867</t>
   </si>
   <si>
     <t xml:space="preserve">39.4377899169922</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0812911987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0545539855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3219261169434</t>
+    <t xml:space="preserve">39.0812873840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0545501708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3219223022461</t>
   </si>
   <si>
     <t xml:space="preserve">38.5554504394531</t>
@@ -1397,25 +1397,25 @@
     <t xml:space="preserve">38.3772048950195</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6998519897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6125335693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6820220947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4663238525391</t>
+    <t xml:space="preserve">37.6998481750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6125297546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6820259094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4663276672363</t>
   </si>
   <si>
     <t xml:space="preserve">41.9956703186035</t>
   </si>
   <si>
-    <t xml:space="preserve">42.655200958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8156204223633</t>
+    <t xml:space="preserve">42.6551933288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8156242370605</t>
   </si>
   <si>
     <t xml:space="preserve">42.423469543457</t>
@@ -1424,16 +1424,16 @@
     <t xml:space="preserve">42.031322479248</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0848007202148</t>
+    <t xml:space="preserve">42.0847969055176</t>
   </si>
   <si>
     <t xml:space="preserve">41.924373626709</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6213493347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7639465332031</t>
+    <t xml:space="preserve">41.6213455200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7639503479004</t>
   </si>
   <si>
     <t xml:space="preserve">42.1382713317871</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">41.6926460266113</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5322227478027</t>
+    <t xml:space="preserve">41.5322189331055</t>
   </si>
   <si>
     <t xml:space="preserve">41.7817687988281</t>
@@ -1451,40 +1451,40 @@
     <t xml:space="preserve">41.3539733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8192291259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.355770111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5875015258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8031959533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1436729431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6784210205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7799758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4787483215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6802215576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5750770568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2898788452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5892944335938</t>
+    <t xml:space="preserve">40.819221496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3557739257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5874977111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8031997680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.143669128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6784286499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7799682617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4787521362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6802253723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5750732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2898750305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.589298248291</t>
   </si>
   <si>
     <t xml:space="preserve">40.1953468322754</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">40.8013954162598</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9439964294434</t>
+    <t xml:space="preserve">40.9439926147461</t>
   </si>
   <si>
     <t xml:space="preserve">41.1400718688965</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">39.2506256103516</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1793212890625</t>
+    <t xml:space="preserve">39.1793251037598</t>
   </si>
   <si>
     <t xml:space="preserve">40.2131729125977</t>
@@ -1526,19 +1526,19 @@
     <t xml:space="preserve">40.3914260864258</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3896217346191</t>
+    <t xml:space="preserve">41.3896141052246</t>
   </si>
   <si>
     <t xml:space="preserve">42.6017227172852</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5446472167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9029426574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2309112548828</t>
+    <t xml:space="preserve">44.5446434020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.902946472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2309074401855</t>
   </si>
   <si>
     <t xml:space="preserve">43.8851203918457</t>
@@ -1550,10 +1550,10 @@
     <t xml:space="preserve">46.0330352783203</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3253402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.943904876709</t>
+    <t xml:space="preserve">47.3253440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9439086914062</t>
   </si>
   <si>
     <t xml:space="preserve">45.5874061584473</t>
@@ -1568,37 +1568,37 @@
     <t xml:space="preserve">43.8494720458984</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9582176208496</t>
+    <t xml:space="preserve">42.9582214355469</t>
   </si>
   <si>
     <t xml:space="preserve">41.4609222412109</t>
   </si>
   <si>
-    <t xml:space="preserve">41.175724029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.157901763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0152969360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7675514221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1080207824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7479248046875</t>
+    <t xml:space="preserve">41.1757202148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1578979492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0153007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7675476074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1080284118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7479209899902</t>
   </si>
   <si>
     <t xml:space="preserve">39.7853736877441</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5518493652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7318992614746</t>
+    <t xml:space="preserve">40.5518531799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7319030761719</t>
   </si>
   <si>
     <t xml:space="preserve">39.3041000366211</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">40.2488250732422</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9101448059082</t>
+    <t xml:space="preserve">39.9101486206055</t>
   </si>
   <si>
     <t xml:space="preserve">39.4288787841797</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">39.0367240905762</t>
   </si>
   <si>
-    <t xml:space="preserve">42.387825012207</t>
+    <t xml:space="preserve">42.3878211975098</t>
   </si>
   <si>
     <t xml:space="preserve">41.0509490966797</t>
@@ -1628,22 +1628,22 @@
     <t xml:space="preserve">41.0149230957031</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7087059020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6366539001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5285835266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8440971374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7366142272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.484432220459</t>
+    <t xml:space="preserve">40.7087097167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6366577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5285797119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8441047668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7366104125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4844360351562</t>
   </si>
   <si>
     <t xml:space="preserve">36.3316230773926</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">36.6018104553223</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0073890686035</t>
+    <t xml:space="preserve">36.007396697998</t>
   </si>
   <si>
     <t xml:space="preserve">35.6651496887207</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">35.3589324951172</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2241401672363</t>
+    <t xml:space="preserve">34.2241363525391</t>
   </si>
   <si>
     <t xml:space="preserve">33.4135627746582</t>
@@ -1676,13 +1676,13 @@
     <t xml:space="preserve">33.6657409667969</t>
   </si>
   <si>
-    <t xml:space="preserve">33.881893157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4763107299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6924629211426</t>
+    <t xml:space="preserve">33.8818893432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4763145446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6924705505371</t>
   </si>
   <si>
     <t xml:space="preserve">35.1427841186523</t>
@@ -1703,16 +1703,16 @@
     <t xml:space="preserve">34.4402885437012</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1247711181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5036239624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4048500061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3868370056152</t>
+    <t xml:space="preserve">35.1247749328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5036277770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4048538208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3868408203125</t>
   </si>
   <si>
     <t xml:space="preserve">31.468189239502</t>
@@ -1724,22 +1724,22 @@
     <t xml:space="preserve">30.5315341949463</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4867935180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9371166229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2346172332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.153263092041</t>
+    <t xml:space="preserve">29.486795425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9371128082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2346153259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1532649993896</t>
   </si>
   <si>
     <t xml:space="preserve">29.2166042327881</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4147415161133</t>
+    <t xml:space="preserve">29.4147434234619</t>
   </si>
   <si>
     <t xml:space="preserve">27.829626083374</t>
@@ -1751,34 +1751,34 @@
     <t xml:space="preserve">29.5408325195312</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6035804748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2520408630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6489067077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9551239013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1172351837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4054374694824</t>
+    <t xml:space="preserve">30.6035823822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2520427703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6489086151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9551219940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1172409057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4054393768311</t>
   </si>
   <si>
     <t xml:space="preserve">31.666332244873</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6483211517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.080623626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1079387664795</t>
+    <t xml:space="preserve">31.6483154296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0806198120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1079368591309</t>
   </si>
   <si>
     <t xml:space="preserve">31.3601169586182</t>
@@ -1787,25 +1787,25 @@
     <t xml:space="preserve">30.9818515777588</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7383842468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6122875213623</t>
+    <t xml:space="preserve">31.7383861541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6122894287109</t>
   </si>
   <si>
     <t xml:space="preserve">30.8377475738525</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9190998077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.901086807251</t>
+    <t xml:space="preserve">29.9191017150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9010887145996</t>
   </si>
   <si>
     <t xml:space="preserve">29.6669216156006</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0905151367188</t>
+    <t xml:space="preserve">29.0905132293701</t>
   </si>
   <si>
     <t xml:space="preserve">28.730260848999</t>
@@ -1817,55 +1817,55 @@
     <t xml:space="preserve">27.5954608917236</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6407890319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2805347442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0463695526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5146980285645</t>
+    <t xml:space="preserve">26.6407871246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2805328369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0463676452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5146999359131</t>
   </si>
   <si>
     <t xml:space="preserve">27.2352066040039</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0550804138184</t>
+    <t xml:space="preserve">27.055082321167</t>
   </si>
   <si>
     <t xml:space="preserve">27.1091175079346</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0190544128418</t>
+    <t xml:space="preserve">27.0190525054932</t>
   </si>
   <si>
     <t xml:space="preserve">26.7488651275635</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4693717956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9196891784668</t>
+    <t xml:space="preserve">27.4693698883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9196872711182</t>
   </si>
   <si>
     <t xml:space="preserve">27.5774478912354</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9377021789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8476409912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7936000823975</t>
+    <t xml:space="preserve">27.9377002716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8476371765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7936019897461</t>
   </si>
   <si>
     <t xml:space="preserve">28.0457782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0097522735596</t>
+    <t xml:space="preserve">28.0097541809082</t>
   </si>
   <si>
     <t xml:space="preserve">27.7755889892578</t>
@@ -1874,25 +1874,25 @@
     <t xml:space="preserve">28.6041717529297</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5501327514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1805820465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1625671386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6401977539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6762218475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6675109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4513607025146</t>
+    <t xml:space="preserve">28.5501346588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1805801391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1625690460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6401958465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6762237548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6675090789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4513568878174</t>
   </si>
   <si>
     <t xml:space="preserve">27.5594367980957</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">25.7581653594971</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7320308685303</t>
+    <t xml:space="preserve">22.7320289611816</t>
   </si>
   <si>
     <t xml:space="preserve">21.7413330078125</t>
@@ -1910,16 +1910,16 @@
     <t xml:space="preserve">21.7233200073242</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7860679626465</t>
+    <t xml:space="preserve">22.7860698699951</t>
   </si>
   <si>
     <t xml:space="preserve">23.4165134429932</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7047157287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5606174468994</t>
+    <t xml:space="preserve">23.7047176361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5606136322021</t>
   </si>
   <si>
     <t xml:space="preserve">23.236385345459</t>
@@ -1940,43 +1940,43 @@
     <t xml:space="preserve">21.3630638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2369747161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3450546264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5972309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7239074707031</t>
+    <t xml:space="preserve">21.2369766235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3450527191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5972290039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7239093780518</t>
   </si>
   <si>
     <t xml:space="preserve">18.3189182281494</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2828941345215</t>
+    <t xml:space="preserve">18.2828922271729</t>
   </si>
   <si>
     <t xml:space="preserve">19.5437831878662</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8773136138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3909683227539</t>
+    <t xml:space="preserve">18.8773097991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3909702301025</t>
   </si>
   <si>
     <t xml:space="preserve">19.0034027099609</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0036945343018</t>
+    <t xml:space="preserve">18.003698348999</t>
   </si>
   <si>
     <t xml:space="preserve">17.139087677002</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1120700836182</t>
+    <t xml:space="preserve">17.1120681762695</t>
   </si>
   <si>
     <t xml:space="preserve">17.2651748657227</t>
@@ -1985,31 +1985,31 @@
     <t xml:space="preserve">16.661750793457</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2024250030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9502458572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7160844802856</t>
+    <t xml:space="preserve">16.2024269104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.950249671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.716082572937</t>
   </si>
   <si>
     <t xml:space="preserve">15.6800584793091</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6170148849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1573925018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6077117919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4005641937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4723224639893</t>
+    <t xml:space="preserve">15.6170139312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1573963165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6077136993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4005680084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4723205566406</t>
   </si>
   <si>
     <t xml:space="preserve">17.5533809661865</t>
@@ -2018,64 +2018,64 @@
     <t xml:space="preserve">16.4906272888184</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9406490325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8232727050781</t>
+    <t xml:space="preserve">17.9406509399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8232746124268</t>
   </si>
   <si>
     <t xml:space="preserve">17.6614551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7968444824219</t>
+    <t xml:space="preserve">16.7968463897705</t>
   </si>
   <si>
     <t xml:space="preserve">16.0132923126221</t>
   </si>
   <si>
-    <t xml:space="preserve">15.905216217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2654705047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1934185028076</t>
+    <t xml:space="preserve">15.9052171707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2654685974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1934204101562</t>
   </si>
   <si>
     <t xml:space="preserve">15.7250881195068</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4008617401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0496129989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7524032592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5899934768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1486825942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4639053344727</t>
+    <t xml:space="preserve">15.4008626937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0496139526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.752402305603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5899925231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1486835479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4639024734497</t>
   </si>
   <si>
     <t xml:space="preserve">17.1661052703857</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7875442504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1568031311035</t>
+    <t xml:space="preserve">17.7875461578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1568050384521</t>
   </si>
   <si>
     <t xml:space="preserve">17.643440246582</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3912658691406</t>
+    <t xml:space="preserve">17.3912620544434</t>
   </si>
   <si>
     <t xml:space="preserve">18.0127029418945</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">18.0487289428711</t>
   </si>
   <si>
-    <t xml:space="preserve">18.228853225708</t>
+    <t xml:space="preserve">18.2288551330566</t>
   </si>
   <si>
     <t xml:space="preserve">18.0307159423828</t>
@@ -2093,16 +2093,16 @@
     <t xml:space="preserve">17.9226379394531</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4543113708496</t>
+    <t xml:space="preserve">17.4543075561523</t>
   </si>
   <si>
     <t xml:space="preserve">18.6791725158691</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8052635192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6251335144043</t>
+    <t xml:space="preserve">18.8052616119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6251354217529</t>
   </si>
   <si>
     <t xml:space="preserve">18.3369312286377</t>
@@ -2114,13 +2114,13 @@
     <t xml:space="preserve">18.7872486114502</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6971855163574</t>
+    <t xml:space="preserve">18.6971874237061</t>
   </si>
   <si>
     <t xml:space="preserve">18.354944229126</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4269943237305</t>
+    <t xml:space="preserve">18.4269924163818</t>
   </si>
   <si>
     <t xml:space="preserve">17.9856834411621</t>
@@ -2135,70 +2135,70 @@
     <t xml:space="preserve">18.3009052276611</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6071224212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3996810913086</t>
+    <t xml:space="preserve">18.607120513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3996829986572</t>
   </si>
   <si>
     <t xml:space="preserve">19.6698703765869</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2462787628174</t>
+    <t xml:space="preserve">20.2462749481201</t>
   </si>
   <si>
     <t xml:space="preserve">20.0661506652832</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9220485687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4176940917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4537220001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2823028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7515201568604</t>
+    <t xml:space="preserve">19.9220523834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4176921844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4537200927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2823047637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7515163421631</t>
   </si>
   <si>
     <t xml:space="preserve">17.7425117492676</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7965488433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5083484649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4182834625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8508815765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9859771728516</t>
+    <t xml:space="preserve">17.7965526580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5083465576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.418285369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8508834838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9859809875488</t>
   </si>
   <si>
     <t xml:space="preserve">16.868896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0490207672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9409465789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3462314605713</t>
+    <t xml:space="preserve">17.0490245819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9409446716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3462352752686</t>
   </si>
   <si>
     <t xml:space="preserve">17.2741813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3822574615479</t>
+    <t xml:space="preserve">17.3822555541992</t>
   </si>
   <si>
     <t xml:space="preserve">17.2831878662109</t>
@@ -2207,19 +2207,19 @@
     <t xml:space="preserve">18.1748180389404</t>
   </si>
   <si>
-    <t xml:space="preserve">17.976676940918</t>
+    <t xml:space="preserve">17.9766750335693</t>
   </si>
   <si>
     <t xml:space="preserve">17.6164245605469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4272899627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1387920379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9136333465576</t>
+    <t xml:space="preserve">17.4272918701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1387901306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.913631439209</t>
   </si>
   <si>
     <t xml:space="preserve">17.6974792480469</t>
@@ -2228,10 +2228,10 @@
     <t xml:space="preserve">18.1928291320801</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9496593475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2381553649902</t>
+    <t xml:space="preserve">17.9496555328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2381572723389</t>
   </si>
   <si>
     <t xml:space="preserve">17.1300792694092</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">17.6794662475586</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9676723480225</t>
+    <t xml:space="preserve">17.9676685333252</t>
   </si>
   <si>
     <t xml:space="preserve">18.084753036499</t>
@@ -2264,49 +2264,49 @@
     <t xml:space="preserve">17.76953125</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6365585327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.24342918396</t>
+    <t xml:space="preserve">18.6365566253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2434272766113</t>
   </si>
   <si>
     <t xml:space="preserve">16.6621894836426</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2249774932861</t>
+    <t xml:space="preserve">17.2249755859375</t>
   </si>
   <si>
     <t xml:space="preserve">16.5330257415771</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1916618347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.684232711792</t>
+    <t xml:space="preserve">16.1916599273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6842317581177</t>
   </si>
   <si>
     <t xml:space="preserve">14.6232395172119</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8021240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9405145645142</t>
+    <t xml:space="preserve">13.8021230697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9405136108398</t>
   </si>
   <si>
     <t xml:space="preserve">13.7836713790894</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3131456375122</t>
+    <t xml:space="preserve">13.3131446838379</t>
   </si>
   <si>
     <t xml:space="preserve">13.8943843841553</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8390274047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4792137145996</t>
+    <t xml:space="preserve">13.8390283584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4792127609253</t>
   </si>
   <si>
     <t xml:space="preserve">12.9533309936523</t>
@@ -2321,10 +2321,10 @@
     <t xml:space="preserve">13.303918838501</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3777265548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1009464263916</t>
+    <t xml:space="preserve">13.3777275085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1009454727173</t>
   </si>
   <si>
     <t xml:space="preserve">13.1378507614136</t>
@@ -2333,10 +2333,10 @@
     <t xml:space="preserve">13.9220628738403</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7006378173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.475622177124</t>
+    <t xml:space="preserve">13.7006387710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4756231307983</t>
   </si>
   <si>
     <t xml:space="preserve">14.4202671051025</t>
@@ -2351,10 +2351,10 @@
     <t xml:space="preserve">13.7928981781006</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6914110183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5125274658203</t>
+    <t xml:space="preserve">13.6914129257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.512526512146</t>
   </si>
   <si>
     <t xml:space="preserve">14.1803903579712</t>
@@ -2366,58 +2366,58 @@
     <t xml:space="preserve">10.7575378417969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1486196517944</t>
+    <t xml:space="preserve">10.1486215591431</t>
   </si>
   <si>
     <t xml:space="preserve">10.2132024765015</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4069480895996</t>
+    <t xml:space="preserve">10.4069490432739</t>
   </si>
   <si>
     <t xml:space="preserve">10.4161748886108</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5914697647095</t>
+    <t xml:space="preserve">10.5914688110352</t>
   </si>
   <si>
     <t xml:space="preserve">10.8590250015259</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9236068725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4807567596436</t>
+    <t xml:space="preserve">10.9236059188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4807558059692</t>
   </si>
   <si>
     <t xml:space="preserve">10.6837291717529</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5361127853394</t>
+    <t xml:space="preserve">10.5361137390137</t>
   </si>
   <si>
     <t xml:space="preserve">10.2962369918823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3700456619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0471343994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1762981414795</t>
+    <t xml:space="preserve">10.3700437545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0471353530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1762971878052</t>
   </si>
   <si>
     <t xml:space="preserve">9.9087438583374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65964221954346</t>
+    <t xml:space="preserve">9.65964126586914</t>
   </si>
   <si>
     <t xml:space="preserve">9.53047752380371</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0932636260986</t>
+    <t xml:space="preserve">10.0932645797729</t>
   </si>
   <si>
     <t xml:space="preserve">10.4899835586548</t>
@@ -2432,79 +2432,79 @@
     <t xml:space="preserve">10.5176610946655</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3054618835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4438533782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6652774810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286817550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96410083770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0563611984253</t>
+    <t xml:space="preserve">10.3054628372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4438543319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6652784347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0286827087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9640998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.056360244751</t>
   </si>
   <si>
     <t xml:space="preserve">10.120943069458</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50279903411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29059982299805</t>
+    <t xml:space="preserve">9.50279998779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29060077667236</t>
   </si>
   <si>
     <t xml:space="preserve">9.5766077041626</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21217823028564</t>
+    <t xml:space="preserve">9.21217918395996</t>
   </si>
   <si>
     <t xml:space="preserve">9.40131282806396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43821620941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47512245178223</t>
+    <t xml:space="preserve">9.43821716308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47512149810791</t>
   </si>
   <si>
     <t xml:space="preserve">9.20295333862305</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94001293182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98614120483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88004302978516</t>
+    <t xml:space="preserve">8.94001197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9861421585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88004398345947</t>
   </si>
   <si>
     <t xml:space="preserve">9.53970336914062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24447059631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28137493133545</t>
+    <t xml:space="preserve">9.24447154998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28137588500977</t>
   </si>
   <si>
     <t xml:space="preserve">9.11530685424805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88106536865234</t>
+    <t xml:space="preserve">9.88106632232666</t>
   </si>
   <si>
     <t xml:space="preserve">9.97332668304443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99177742004395</t>
+    <t xml:space="preserve">9.99177837371826</t>
   </si>
   <si>
     <t xml:space="preserve">10.2408809661865</t>
@@ -2513,37 +2513,37 @@
     <t xml:space="preserve">10.4346284866333</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0840377807617</t>
+    <t xml:space="preserve">10.084038734436</t>
   </si>
   <si>
     <t xml:space="preserve">10.1024904251099</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61351203918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66886806488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52125072479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79803276062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56738090515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26292324066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39208698272705</t>
+    <t xml:space="preserve">9.61351108551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66886615753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5212516784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7980318069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56738185882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2629222869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39208793640137</t>
   </si>
   <si>
     <t xml:space="preserve">9.65041637420654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31827926635742</t>
+    <t xml:space="preserve">9.31827831268311</t>
   </si>
   <si>
     <t xml:space="preserve">9.71499729156494</t>
@@ -2558,28 +2558,28 @@
     <t xml:space="preserve">9.98255252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7519006729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49357318878174</t>
+    <t xml:space="preserve">9.75190162658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49357223510742</t>
   </si>
   <si>
     <t xml:space="preserve">10.2777853012085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0655860900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5822448730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7298603057861</t>
+    <t xml:space="preserve">10.0655851364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5822439193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7298612594604</t>
   </si>
   <si>
     <t xml:space="preserve">10.2870101928711</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5084362030029</t>
+    <t xml:space="preserve">10.5084352493286</t>
   </si>
   <si>
     <t xml:space="preserve">10.3515930175781</t>
@@ -2588,10 +2588,10 @@
     <t xml:space="preserve">11.431037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6340084075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2337017059326</t>
+    <t xml:space="preserve">11.6340093612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2337007522583</t>
   </si>
   <si>
     <t xml:space="preserve">11.993824005127</t>
@@ -2600,10 +2600,10 @@
     <t xml:space="preserve">12.1322145462036</t>
   </si>
   <si>
-    <t xml:space="preserve">12.086085319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1414403915405</t>
+    <t xml:space="preserve">12.0860843658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1414413452148</t>
   </si>
   <si>
     <t xml:space="preserve">12.1875705718994</t>
@@ -2612,10 +2612,10 @@
     <t xml:space="preserve">11.9661474227905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.956919670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7539482116699</t>
+    <t xml:space="preserve">11.9569206237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7539472579956</t>
   </si>
   <si>
     <t xml:space="preserve">11.8277559280396</t>
@@ -2636,19 +2636,19 @@
     <t xml:space="preserve">13.2485628128052</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0824956893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5991506576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.40540599823</t>
+    <t xml:space="preserve">13.0824947357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5991516113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4054050445557</t>
   </si>
   <si>
     <t xml:space="preserve">13.2024326324463</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7559928894043</t>
+    <t xml:space="preserve">13.7559938430786</t>
   </si>
   <si>
     <t xml:space="preserve">13.7098636627197</t>
@@ -2657,28 +2657,28 @@
     <t xml:space="preserve">13.7744464874268</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3408241271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.719090461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7283163070679</t>
+    <t xml:space="preserve">13.3408231735229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7190895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7283153533936</t>
   </si>
   <si>
     <t xml:space="preserve">14.0143213272095</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1342620849609</t>
+    <t xml:space="preserve">14.1342601776123</t>
   </si>
   <si>
     <t xml:space="preserve">14.1250352859497</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9497394561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6637353897095</t>
+    <t xml:space="preserve">13.9497404098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6637344360352</t>
   </si>
   <si>
     <t xml:space="preserve">13.682186126709</t>
@@ -2687,40 +2687,40 @@
     <t xml:space="preserve">14.4571714401245</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1158094406128</t>
+    <t xml:space="preserve">14.1158084869385</t>
   </si>
   <si>
     <t xml:space="preserve">13.8482542037964</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0512266159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0327749252319</t>
+    <t xml:space="preserve">14.0512256622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0327739715576</t>
   </si>
   <si>
     <t xml:space="preserve">13.9312887191772</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6473264694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7303628921509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0865879058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7913551330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.865161895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7452220916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8190307617188</t>
+    <t xml:space="preserve">15.64732837677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7303609848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0865859985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.791353225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8651638031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7452239990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8190326690674</t>
   </si>
   <si>
     <t xml:space="preserve">16.1086273193359</t>
@@ -2729,16 +2729,16 @@
     <t xml:space="preserve">15.997917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9333353042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4720335006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6785955429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3187818527222</t>
+    <t xml:space="preserve">15.9333333969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4720344543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.678596496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3187808990479</t>
   </si>
   <si>
     <t xml:space="preserve">14.8446645736694</t>
@@ -2747,37 +2747,37 @@
     <t xml:space="preserve">15.2967395782471</t>
   </si>
   <si>
-    <t xml:space="preserve">15.204478263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7247266769409</t>
+    <t xml:space="preserve">15.2044792175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7247247695923</t>
   </si>
   <si>
     <t xml:space="preserve">14.8538913726807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1491241455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2506093978882</t>
+    <t xml:space="preserve">15.1491222381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2506084442139</t>
   </si>
   <si>
     <t xml:space="preserve">14.9830551147461</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1583490371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0753154754639</t>
+    <t xml:space="preserve">15.1583480834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0753145217896</t>
   </si>
   <si>
     <t xml:space="preserve">14.1065826416016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6027421951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0399551391602</t>
+    <t xml:space="preserve">12.6027412414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0399541854858</t>
   </si>
   <si>
     <t xml:space="preserve">11.9753723144531</t>
@@ -2789,10 +2789,10 @@
     <t xml:space="preserve">11.3018732070923</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6006956100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1301689147949</t>
+    <t xml:space="preserve">10.6006946563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1301679611206</t>
   </si>
   <si>
     <t xml:space="preserve">9.30905342102051</t>
@@ -2801,13 +2801,13 @@
     <t xml:space="preserve">8.06353950500488</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9758939743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89285898208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5504732131958</t>
+    <t xml:space="preserve">7.97589349746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8928599357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55047273635864</t>
   </si>
   <si>
     <t xml:space="preserve">6.93796634674072</t>
@@ -2816,13 +2816,13 @@
     <t xml:space="preserve">6.90567541122437</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98409605026245</t>
+    <t xml:space="preserve">6.98409652709961</t>
   </si>
   <si>
     <t xml:space="preserve">6.91028785705566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01177406311035</t>
+    <t xml:space="preserve">7.01177358627319</t>
   </si>
   <si>
     <t xml:space="preserve">7.47307538986206</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">8.05431365966797</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85697841644287</t>
+    <t xml:space="preserve">8.85697746276855</t>
   </si>
   <si>
     <t xml:space="preserve">9.33673095703125</t>
@@ -2840,34 +2840,34 @@
     <t xml:space="preserve">9.01382160186768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39567756652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40029048919678</t>
+    <t xml:space="preserve">8.395676612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40028953552246</t>
   </si>
   <si>
     <t xml:space="preserve">8.34954643249512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25728702545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11889553070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74985504150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92976331710815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78675889968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10966968536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.842116355896</t>
+    <t xml:space="preserve">8.25728607177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11889743804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74985551834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.929762840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78675937652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10967063903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84211587905884</t>
   </si>
   <si>
     <t xml:space="preserve">7.42694568634033</t>
@@ -2876,13 +2876,13 @@
     <t xml:space="preserve">7.28855514526367</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26087713241577</t>
+    <t xml:space="preserve">7.26087665557861</t>
   </si>
   <si>
     <t xml:space="preserve">7.32545900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33468532562256</t>
+    <t xml:space="preserve">7.3346848487854</t>
   </si>
   <si>
     <t xml:space="preserve">7.11326026916504</t>
@@ -2894,52 +2894,52 @@
     <t xml:space="preserve">7.77753353118896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93437623977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60223913192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33929777145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51920557022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3070068359375</t>
+    <t xml:space="preserve">7.93437719345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60223960876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33929824829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51920461654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30700635910034</t>
   </si>
   <si>
     <t xml:space="preserve">7.14555168151855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10403490066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15939092636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06713104248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92874002456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56533479690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54227018356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44539737701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27010250091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72217750549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46948623657227</t>
+    <t xml:space="preserve">7.10403394699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15939044952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06713008880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92874050140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56533527374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54227066040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.445396900177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27010297775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72217798233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46948528289795</t>
   </si>
   <si>
     <t xml:space="preserve">8.66784477233887</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">8.90310764312744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54329395294189</t>
+    <t xml:space="preserve">8.54329299926758</t>
   </si>
   <si>
     <t xml:space="preserve">8.69091033935547</t>
@@ -2966,13 +2966,13 @@
     <t xml:space="preserve">11.4863929748535</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4956197738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2557420730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9420566558838</t>
+    <t xml:space="preserve">11.4956188201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2557430267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9420576095581</t>
   </si>
   <si>
     <t xml:space="preserve">9.82570934295654</t>
@@ -2984,13 +2984,13 @@
     <t xml:space="preserve">10.4623050689697</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1947507858276</t>
+    <t xml:space="preserve">10.1947498321533</t>
   </si>
   <si>
     <t xml:space="preserve">10.019455909729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89029216766357</t>
+    <t xml:space="preserve">9.89029121398926</t>
   </si>
   <si>
     <t xml:space="preserve">10.3792715072632</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">10.360818862915</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2224283218384</t>
+    <t xml:space="preserve">10.2224292755127</t>
   </si>
   <si>
     <t xml:space="preserve">10.674503326416</t>
@@ -3008,10 +3008,10 @@
     <t xml:space="preserve">10.5453395843506</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7667646408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.021502494812</t>
+    <t xml:space="preserve">10.7667636871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0215015411377</t>
   </si>
   <si>
     <t xml:space="preserve">11.4402637481689</t>
@@ -3026,22 +3026,22 @@
     <t xml:space="preserve">11.8093042373657</t>
   </si>
   <si>
-    <t xml:space="preserve">11.818531036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.707818031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6616878509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5694274902344</t>
+    <t xml:space="preserve">11.8185300827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7078170776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6616888046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5694284439087</t>
   </si>
   <si>
     <t xml:space="preserve">11.3480033874512</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2741956710815</t>
+    <t xml:space="preserve">11.2741947174072</t>
   </si>
   <si>
     <t xml:space="preserve">11.1450309753418</t>
@@ -3062,37 +3062,37 @@
     <t xml:space="preserve">12.7042284011841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0548152923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3961801528931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2854671478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4423084259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1286239624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.230110168457</t>
+    <t xml:space="preserve">13.0548162460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3961791992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2854681015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4423093795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1286249160767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2301111221313</t>
   </si>
   <si>
     <t xml:space="preserve">13.0086870193481</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1932077407837</t>
+    <t xml:space="preserve">13.1932067871094</t>
   </si>
   <si>
     <t xml:space="preserve">13.5437955856323</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3500509262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5714740753174</t>
+    <t xml:space="preserve">13.3500499725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5714750289917</t>
   </si>
   <si>
     <t xml:space="preserve">13.3685007095337</t>
@@ -3101,28 +3101,28 @@
     <t xml:space="preserve">13.1470766067505</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4976663589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1101722717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1655282974243</t>
+    <t xml:space="preserve">13.4976654052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1101732254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1655292510986</t>
   </si>
   <si>
     <t xml:space="preserve">13.2670154571533</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2762403488159</t>
+    <t xml:space="preserve">13.2762413024902</t>
   </si>
   <si>
     <t xml:space="preserve">13.0455904006958</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1747541427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.331597328186</t>
+    <t xml:space="preserve">13.1747550964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3315963745117</t>
   </si>
   <si>
     <t xml:space="preserve">13.3869533538818</t>
@@ -3131,10 +3131,10 @@
     <t xml:space="preserve">12.5104808807373</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3813161849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6304197311401</t>
+    <t xml:space="preserve">12.3813180923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6304187774658</t>
   </si>
   <si>
     <t xml:space="preserve">12.335186958313</t>
@@ -3143,22 +3143,22 @@
     <t xml:space="preserve">12.7872619628906</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5068922042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4330825805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4515352249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2690601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5735177993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8318462371826</t>
+    <t xml:space="preserve">13.5068912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4330835342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4515342712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2690591812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5735187530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8318471908569</t>
   </si>
   <si>
     <t xml:space="preserve">16.1455326080322</t>
@@ -3173,16 +3173,16 @@
     <t xml:space="preserve">14.7616300582886</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5217542648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5955619812012</t>
+    <t xml:space="preserve">14.5217533111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5955610275269</t>
   </si>
   <si>
     <t xml:space="preserve">14.7154998779297</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3556861877441</t>
+    <t xml:space="preserve">14.3556852340698</t>
   </si>
   <si>
     <t xml:space="preserve">13.9128351211548</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">13.6545076370239</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5033016204834</t>
+    <t xml:space="preserve">14.5033025741577</t>
   </si>
   <si>
     <t xml:space="preserve">14.4110412597656</t>
@@ -3203,82 +3203,82 @@
     <t xml:space="preserve">15.1860265731812</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6750059127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4166765213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1029930114746</t>
+    <t xml:space="preserve">15.6750068664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4166774749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1029939651489</t>
   </si>
   <si>
     <t xml:space="preserve">14.9184722900391</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3889989852905</t>
+    <t xml:space="preserve">15.3889999389648</t>
   </si>
   <si>
     <t xml:space="preserve">15.7764930725098</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5827465057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1547584533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8133964538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8410758972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9241094589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1178531646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8502998352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8779783248901</t>
+    <t xml:space="preserve">15.582745552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1547603607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8133945465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8410720825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.924108505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1178550720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8502988815308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8779773712158</t>
   </si>
   <si>
     <t xml:space="preserve">15.3520946502686</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6381015777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4351282119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5919713973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9517879486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0994033813477</t>
+    <t xml:space="preserve">15.6381034851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4351291656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5919704437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9517869949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.099401473999</t>
   </si>
   <si>
     <t xml:space="preserve">16.0717258453369</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5145740509033</t>
+    <t xml:space="preserve">16.5145721435547</t>
   </si>
   <si>
     <t xml:space="preserve">17.7877635955811</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3910446166992</t>
+    <t xml:space="preserve">17.3910465240479</t>
   </si>
   <si>
     <t xml:space="preserve">17.4648532867432</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1142654418945</t>
+    <t xml:space="preserve">17.1142635345459</t>
   </si>
   <si>
     <t xml:space="preserve">17.2618808746338</t>
@@ -3287,31 +3287,34 @@
     <t xml:space="preserve">17.5386619567871</t>
   </si>
   <si>
-    <t xml:space="preserve">17.446403503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5663414001465</t>
+    <t xml:space="preserve">17.4464015960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5663394927979</t>
   </si>
   <si>
     <t xml:space="preserve">17.3725929260254</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6216945648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5478858947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0368671417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.415132522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7657222747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9835548400879</t>
+    <t xml:space="preserve">17.621696472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.547887802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.036865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4151306152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7657203674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6698722839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9835567474365</t>
   </si>
   <si>
     <t xml:space="preserve">19.4299945831299</t>
@@ -3323,31 +3326,31 @@
     <t xml:space="preserve">18.728816986084</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2454738616943</t>
+    <t xml:space="preserve">19.245475769043</t>
   </si>
   <si>
     <t xml:space="preserve">19.1901187896729</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3377361297607</t>
+    <t xml:space="preserve">19.3377323150635</t>
   </si>
   <si>
     <t xml:space="preserve">19.2639274597168</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5443000793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5627498626709</t>
+    <t xml:space="preserve">18.5442981719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5627517700195</t>
   </si>
   <si>
     <t xml:space="preserve">18.2029342651367</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4704895019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.972282409668</t>
+    <t xml:space="preserve">18.4704914093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9722843170166</t>
   </si>
   <si>
     <t xml:space="preserve">18.1844825744629</t>
@@ -3359,37 +3362,37 @@
     <t xml:space="preserve">19.9651050567627</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6109237670898</t>
+    <t xml:space="preserve">20.6109256744385</t>
   </si>
   <si>
     <t xml:space="preserve">20.9430618286133</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2567462921143</t>
+    <t xml:space="preserve">21.2567481994629</t>
   </si>
   <si>
     <t xml:space="preserve">21.2198429107666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.312105178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1829395294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7513637542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7698173522949</t>
+    <t xml:space="preserve">21.3121032714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1829376220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7513618469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7698135375977</t>
   </si>
   <si>
     <t xml:space="preserve">22.2900619506836</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8472137451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4745845794678</t>
+    <t xml:space="preserve">21.8472118377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4745826721191</t>
   </si>
   <si>
     <t xml:space="preserve">21.7180500030518</t>
@@ -3404,7 +3407,7 @@
     <t xml:space="preserve">20.7216377258301</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1865272521973</t>
+    <t xml:space="preserve">20.1865291595459</t>
   </si>
   <si>
     <t xml:space="preserve">21.1275825500488</t>
@@ -3413,10 +3416,10 @@
     <t xml:space="preserve">20.6847343444824</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2013912200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4633083343506</t>
+    <t xml:space="preserve">21.2013893127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4633102416992</t>
   </si>
   <si>
     <t xml:space="preserve">19.8728446960449</t>
@@ -3431,19 +3434,19 @@
     <t xml:space="preserve">21.0906791687012</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1091289520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2234344482422</t>
+    <t xml:space="preserve">21.1091327667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2234325408936</t>
   </si>
   <si>
     <t xml:space="preserve">19.9466533660889</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1311721801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1127223968506</t>
+    <t xml:space="preserve">20.1311702728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.112720489502</t>
   </si>
   <si>
     <t xml:space="preserve">19.6145172119141</t>
@@ -3452,10 +3455,10 @@
     <t xml:space="preserve">19.8543930053711</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7954483032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3156929016113</t>
+    <t xml:space="preserve">20.795446395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.31569480896</t>
   </si>
   <si>
     <t xml:space="preserve">20.8323497772217</t>
@@ -3464,7 +3467,7 @@
     <t xml:space="preserve">22.179349899292</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5483913421631</t>
+    <t xml:space="preserve">22.5483894348145</t>
   </si>
   <si>
     <t xml:space="preserve">22.0686359405518</t>
@@ -3473,7 +3476,7 @@
     <t xml:space="preserve">22.2162532806396</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1424465179443</t>
+    <t xml:space="preserve">22.1424446105957</t>
   </si>
   <si>
     <t xml:space="preserve">22.0132808685303</t>
@@ -3482,13 +3485,13 @@
     <t xml:space="preserve">22.2531585693359</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0317306518555</t>
+    <t xml:space="preserve">22.0317344665527</t>
   </si>
   <si>
     <t xml:space="preserve">23.1942100524902</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7846775054932</t>
+    <t xml:space="preserve">23.7846755981445</t>
   </si>
   <si>
     <t xml:space="preserve">23.729320526123</t>
@@ -3497,10 +3500,10 @@
     <t xml:space="preserve">24.3935928344727</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8953876495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0465927124023</t>
+    <t xml:space="preserve">23.8953895568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.046594619751</t>
   </si>
   <si>
     <t xml:space="preserve">22.9174308776855</t>
@@ -3509,16 +3512,16 @@
     <t xml:space="preserve">23.3049221038818</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3971862792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5817012786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1388549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5852947235107</t>
+    <t xml:space="preserve">23.3971843719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5817031860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1388568878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5852928161621</t>
   </si>
   <si>
     <t xml:space="preserve">22.8067169189453</t>
@@ -3527,13 +3530,13 @@
     <t xml:space="preserve">22.3454170227051</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4894409179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7477722167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7662239074707</t>
+    <t xml:space="preserve">23.4894428253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7477741241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7662220001221</t>
   </si>
   <si>
     <t xml:space="preserve">23.2311153411865</t>
@@ -3542,91 +3545,91 @@
     <t xml:space="preserve">22.7144584655762</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6370620727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0763187408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7554531097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4786739349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9768772125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1613998413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3828220367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4935340881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.157808303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0470962524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2721099853516</t>
+    <t xml:space="preserve">23.6370601654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0763206481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7554550170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4786758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.976879119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1614017486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3828258514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4935359954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1578102111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0470943450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2721118927002</t>
   </si>
   <si>
     <t xml:space="preserve">27.5673427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4012756347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1060447692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9030704498291</t>
+    <t xml:space="preserve">27.4012775421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1060428619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9030685424805</t>
   </si>
   <si>
     <t xml:space="preserve">26.4971256256104</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9251098632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7221412658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6447410583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4602203369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3864154815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9989204406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5007152557373</t>
+    <t xml:space="preserve">25.9251136779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7221393585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.644739151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4602222442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3864135742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9989223480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5007133483887</t>
   </si>
   <si>
     <t xml:space="preserve">25.9066619873047</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2572479248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1280841827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9620151519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6631946563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3310565948486</t>
+    <t xml:space="preserve">26.2572498321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1280860900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9620170593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6631927490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3310585021973</t>
   </si>
   <si>
     <t xml:space="preserve">26.5155773162842</t>
@@ -3638,7 +3641,7 @@
     <t xml:space="preserve">26.7370014190674</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7185478210449</t>
+    <t xml:space="preserve">26.7185497283936</t>
   </si>
   <si>
     <t xml:space="preserve">26.8292636871338</t>
@@ -3659,28 +3662,28 @@
     <t xml:space="preserve">26.5893859863281</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1983013153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4750862121582</t>
+    <t xml:space="preserve">27.1983032226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4750823974609</t>
   </si>
   <si>
     <t xml:space="preserve">28.914342880249</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4643135070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9625205993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5970687866211</t>
+    <t xml:space="preserve">30.4643115997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9625225067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5970706939697</t>
   </si>
   <si>
     <t xml:space="preserve">27.0322341918945</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8846168518066</t>
+    <t xml:space="preserve">26.8846187591553</t>
   </si>
   <si>
     <t xml:space="preserve">27.3459186553955</t>
@@ -3689,34 +3692,31 @@
     <t xml:space="preserve">27.6227016448975</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7923603057861</t>
+    <t xml:space="preserve">26.7923583984375</t>
   </si>
   <si>
     <t xml:space="preserve">26.9399757385254</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1798496246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8994789123535</t>
+    <t xml:space="preserve">27.1798515319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8994808197021</t>
   </si>
   <si>
     <t xml:space="preserve">27.5857963562012</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2352085113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2167568206787</t>
+    <t xml:space="preserve">27.2167530059814</t>
   </si>
   <si>
     <t xml:space="preserve">27.364372253418</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6262912750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2536602020264</t>
+    <t xml:space="preserve">26.6262893676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2536582946777</t>
   </si>
   <si>
     <t xml:space="preserve">27.7703170776367</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">27.9548377990723</t>
   </si>
   <si>
-    <t xml:space="preserve">28.674467086792</t>
+    <t xml:space="preserve">28.6744651794434</t>
   </si>
   <si>
     <t xml:space="preserve">28.0286426544189</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">27.6965084075928</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0506858825684</t>
+    <t xml:space="preserve">27.050687789917</t>
   </si>
   <si>
     <t xml:space="preserve">27.7518653869629</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">27.8256702423096</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9732875823975</t>
+    <t xml:space="preserve">27.9732913970947</t>
   </si>
   <si>
     <t xml:space="preserve">28.3054256439209</t>
@@ -3764,7 +3764,7 @@
     <t xml:space="preserve">28.2869739532471</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0840034484863</t>
+    <t xml:space="preserve">28.0840015411377</t>
   </si>
   <si>
     <t xml:space="preserve">27.7887687683105</t>
@@ -3773,10 +3773,10 @@
     <t xml:space="preserve">26.294153213501</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9953327178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.220344543457</t>
+    <t xml:space="preserve">26.9953308105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2203464508057</t>
   </si>
   <si>
     <t xml:space="preserve">25.5191688537598</t>
@@ -3785,7 +3785,7 @@
     <t xml:space="preserve">24.6150169372559</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0983600616455</t>
+    <t xml:space="preserve">24.0983619689941</t>
   </si>
   <si>
     <t xml:space="preserve">24.9656066894531</t>
@@ -3797,10 +3797,10 @@
     <t xml:space="preserve">23.7108707427979</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3418254852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2680168151855</t>
+    <t xml:space="preserve">23.3418273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2680187225342</t>
   </si>
   <si>
     <t xml:space="preserve">24.0614566802979</t>
@@ -3809,13 +3809,13 @@
     <t xml:space="preserve">24.2090721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7441806793213</t>
+    <t xml:space="preserve">24.7441825866699</t>
   </si>
   <si>
     <t xml:space="preserve">24.6334705352783</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2423896789551</t>
+    <t xml:space="preserve">25.2423858642578</t>
   </si>
   <si>
     <t xml:space="preserve">25.0947723388672</t>
@@ -3842,10 +3842,10 @@
     <t xml:space="preserve">24.8733463287354</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9287033081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8364410400391</t>
+    <t xml:space="preserve">24.9287014007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8364429473877</t>
   </si>
   <si>
     <t xml:space="preserve">24.2644290924072</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">24.3013343811035</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8769359588623</t>
+    <t xml:space="preserve">23.8769340515137</t>
   </si>
   <si>
     <t xml:space="preserve">23.5263481140137</t>
@@ -3863,13 +3863,13 @@
     <t xml:space="preserve">23.1573066711426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8656635284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8287620544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8841133117676</t>
+    <t xml:space="preserve">21.865665435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8287601470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8841152191162</t>
   </si>
   <si>
     <t xml:space="preserve">21.0353221893311</t>
@@ -3878,13 +3878,13 @@
     <t xml:space="preserve">20.7031860351562</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7364978790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4597206115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5335292816162</t>
+    <t xml:space="preserve">21.736499786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4597225189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5335273742676</t>
   </si>
   <si>
     <t xml:space="preserve">22.6591014862061</t>
@@ -3893,25 +3893,25 @@
     <t xml:space="preserve">21.4412670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">20.352596282959</t>
+    <t xml:space="preserve">20.3525943756104</t>
   </si>
   <si>
     <t xml:space="preserve">20.9799671173096</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9948272705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.529935836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5114841461182</t>
+    <t xml:space="preserve">21.9948291778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5299396514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5114860534668</t>
   </si>
   <si>
     <t xml:space="preserve">22.6775531768799</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1204013824463</t>
+    <t xml:space="preserve">23.1204032897949</t>
   </si>
   <si>
     <t xml:space="preserve">22.8620758056641</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">22.9358825683594</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3085136413574</t>
+    <t xml:space="preserve">22.3085155487061</t>
   </si>
   <si>
     <t xml:space="preserve">21.3859119415283</t>
@@ -3932,16 +3932,16 @@
     <t xml:space="preserve">21.8103084564209</t>
   </si>
   <si>
-    <t xml:space="preserve">19.928201675415</t>
+    <t xml:space="preserve">19.9281997680664</t>
   </si>
   <si>
     <t xml:space="preserve">20.0758171081543</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8877067565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4448566436768</t>
+    <t xml:space="preserve">20.8877086639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4448585510254</t>
   </si>
   <si>
     <t xml:space="preserve">20.2787895202637</t>
@@ -3950,79 +3950,79 @@
     <t xml:space="preserve">19.8174877166748</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8138961791992</t>
+    <t xml:space="preserve">20.8138980865479</t>
   </si>
   <si>
     <t xml:space="preserve">20.2049808502197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5002117156982</t>
+    <t xml:space="preserve">20.5002136230469</t>
   </si>
   <si>
     <t xml:space="preserve">20.7585430145264</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3710498809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0204601287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9871463775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5073947906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6770515441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1291236877441</t>
+    <t xml:space="preserve">20.3710479736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0204620361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9871444702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5073909759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6770534515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1291255950928</t>
   </si>
   <si>
     <t xml:space="preserve">18.1198997497559</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0681343078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3633670806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0845403671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.23215675354</t>
+    <t xml:space="preserve">17.06813621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3633651733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0845413208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2321557998657</t>
   </si>
   <si>
     <t xml:space="preserve">16.2839221954346</t>
   </si>
   <si>
-    <t xml:space="preserve">15.370548248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2377910614014</t>
+    <t xml:space="preserve">15.3705463409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2377948760986</t>
   </si>
   <si>
     <t xml:space="preserve">13.4699878692627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2172937393188</t>
+    <t xml:space="preserve">14.2172946929932</t>
   </si>
   <si>
     <t xml:space="preserve">14.0604524612427</t>
   </si>
   <si>
-    <t xml:space="preserve">14.337233543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6878213882446</t>
+    <t xml:space="preserve">14.3372325897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6878223419189</t>
   </si>
   <si>
     <t xml:space="preserve">14.8169851303101</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2634258270264</t>
+    <t xml:space="preserve">14.2634248733521</t>
   </si>
   <si>
     <t xml:space="preserve">14.2541990280151</t>
@@ -4031,16 +4031,16 @@
     <t xml:space="preserve">14.6601438522339</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8226222991943</t>
+    <t xml:space="preserve">15.82262134552</t>
   </si>
   <si>
     <t xml:space="preserve">15.6565532684326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0420017242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.99587059021</t>
+    <t xml:space="preserve">14.0420007705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9958715438843</t>
   </si>
   <si>
     <t xml:space="preserve">13.8205757141113</t>
@@ -4049,10 +4049,10 @@
     <t xml:space="preserve">14.3649110794067</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8667058944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6176042556763</t>
+    <t xml:space="preserve">13.8667068481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.617603302002</t>
   </si>
   <si>
     <t xml:space="preserve">13.8113508224487</t>
@@ -4064,28 +4064,28 @@
     <t xml:space="preserve">12.713454246521</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3592739105225</t>
+    <t xml:space="preserve">13.3592748641968</t>
   </si>
   <si>
     <t xml:space="preserve">14.9461507797241</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0476369857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3059663772583</t>
+    <t xml:space="preserve">15.0476360321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.305965423584</t>
   </si>
   <si>
     <t xml:space="preserve">15.3428678512573</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0384111404419</t>
+    <t xml:space="preserve">15.0384092330933</t>
   </si>
   <si>
     <t xml:space="preserve">15.2341136932373</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7736368179321</t>
+    <t xml:space="preserve">14.7736358642578</t>
   </si>
   <si>
     <t xml:space="preserve">14.9367218017578</t>
@@ -4103,13 +4103,13 @@
     <t xml:space="preserve">15.5410985946655</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7137775421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.780930519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0303535461426</t>
+    <t xml:space="preserve">15.7137765884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7809314727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0303554534912</t>
   </si>
   <si>
     <t xml:space="preserve">15.8576755523682</t>
@@ -4121,22 +4121,22 @@
     <t xml:space="preserve">15.3204526901245</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5529909133911</t>
+    <t xml:space="preserve">14.5529918670654</t>
   </si>
   <si>
     <t xml:space="preserve">13.612850189209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5456981658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.843090057373</t>
+    <t xml:space="preserve">13.5456972122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8430891036987</t>
   </si>
   <si>
     <t xml:space="preserve">12.9509143829346</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1427803039551</t>
+    <t xml:space="preserve">13.1427793502808</t>
   </si>
   <si>
     <t xml:space="preserve">13.0180673599243</t>
@@ -4148,7 +4148,7 @@
     <t xml:space="preserve">12.7590503692627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4040994644165</t>
+    <t xml:space="preserve">12.4040985107422</t>
   </si>
   <si>
     <t xml:space="preserve">12.8070163726807</t>
@@ -4160,7 +4160,7 @@
     <t xml:space="preserve">12.8453893661499</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5959644317627</t>
+    <t xml:space="preserve">12.5959634780884</t>
   </si>
   <si>
     <t xml:space="preserve">12.1258945465088</t>
@@ -4169,19 +4169,19 @@
     <t xml:space="preserve">11.8093156814575</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7805366516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5502986907959</t>
+    <t xml:space="preserve">11.780535697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5502977371216</t>
   </si>
   <si>
     <t xml:space="preserve">11.9724006652832</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6247434616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0468473434448</t>
+    <t xml:space="preserve">12.6247444152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0468482971191</t>
   </si>
   <si>
     <t xml:space="preserve">12.7974224090576</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">13.1715602874756</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1044082641602</t>
+    <t xml:space="preserve">13.1044073104858</t>
   </si>
   <si>
     <t xml:space="preserve">13.0948133468628</t>
@@ -4223,13 +4223,13 @@
     <t xml:space="preserve">13.0372552871704</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3154602050781</t>
+    <t xml:space="preserve">13.3154592514038</t>
   </si>
   <si>
     <t xml:space="preserve">12.480845451355</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6055574417114</t>
+    <t xml:space="preserve">12.6055583953857</t>
   </si>
   <si>
     <t xml:space="preserve">12.1738595962524</t>
@@ -4244,7 +4244,7 @@
     <t xml:space="preserve">12.3945055007935</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2506055831909</t>
+    <t xml:space="preserve">12.2506065368652</t>
   </si>
   <si>
     <t xml:space="preserve">11.8668756484985</t>
@@ -4256,7 +4256,7 @@
     <t xml:space="preserve">12.154673576355</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2218265533447</t>
+    <t xml:space="preserve">12.2218255996704</t>
   </si>
   <si>
     <t xml:space="preserve">12.3081665039062</t>
@@ -4265,7 +4265,7 @@
     <t xml:space="preserve">12.1162996292114</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1834526062012</t>
+    <t xml:space="preserve">12.1834535598755</t>
   </si>
   <si>
     <t xml:space="preserve">11.8476896286011</t>
@@ -4280,13 +4280,13 @@
     <t xml:space="preserve">11.4639577865601</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3296527862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6654176712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1354856491089</t>
+    <t xml:space="preserve">11.3296518325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6654167175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1354866027832</t>
   </si>
   <si>
     <t xml:space="preserve">11.7421627044678</t>
@@ -4307,7 +4307,7 @@
     <t xml:space="preserve">11.3680257797241</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2720928192139</t>
+    <t xml:space="preserve">11.2720937728882</t>
   </si>
   <si>
     <t xml:space="preserve">10.9363279342651</t>
@@ -4319,25 +4319,25 @@
     <t xml:space="preserve">10.8499898910522</t>
   </si>
   <si>
-    <t xml:space="preserve">10.754056930542</t>
+    <t xml:space="preserve">10.7540559768677</t>
   </si>
   <si>
     <t xml:space="preserve">10.9555149078369</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1090059280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4159908294678</t>
+    <t xml:space="preserve">11.1090068817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4159917831421</t>
   </si>
   <si>
     <t xml:space="preserve">11.6558227539062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5694856643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5790767669678</t>
+    <t xml:space="preserve">11.5694847106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5790777206421</t>
   </si>
   <si>
     <t xml:space="preserve">11.5311117172241</t>
@@ -4346,7 +4346,7 @@
     <t xml:space="preserve">11.7613496780396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8764686584473</t>
+    <t xml:space="preserve">11.8764696121216</t>
   </si>
   <si>
     <t xml:space="preserve">12.0491485595703</t>
@@ -4358,10 +4358,10 @@
     <t xml:space="preserve">12.9413223266602</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2003412246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6941957473755</t>
+    <t xml:space="preserve">13.2003402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6941967010498</t>
   </si>
   <si>
     <t xml:space="preserve">11.3104658126831</t>
@@ -4379,10 +4379,10 @@
     <t xml:space="preserve">11.7229766845703</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7398624420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2889804840088</t>
+    <t xml:space="preserve">12.7398633956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2889795303345</t>
   </si>
   <si>
     <t xml:space="preserve">12.0875205993652</t>
@@ -4391,7 +4391,7 @@
     <t xml:space="preserve">12.260199546814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1930465698242</t>
+    <t xml:space="preserve">12.1930475234985</t>
   </si>
   <si>
     <t xml:space="preserve">12.3369455337524</t>
@@ -4424,19 +4424,19 @@
     <t xml:space="preserve">12.4616584777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9915885925293</t>
+    <t xml:space="preserve">11.991587638855</t>
   </si>
   <si>
     <t xml:space="preserve">11.9244346618652</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0395536422729</t>
+    <t xml:space="preserve">12.0395545959473</t>
   </si>
   <si>
     <t xml:space="preserve">12.0587406158447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5000314712524</t>
+    <t xml:space="preserve">12.5000305175781</t>
   </si>
   <si>
     <t xml:space="preserve">12.8262023925781</t>
@@ -4454,7 +4454,7 @@
     <t xml:space="preserve">13.8718690872192</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7663431167603</t>
+    <t xml:space="preserve">13.7663440704346</t>
   </si>
   <si>
     <t xml:space="preserve">14.0733280181885</t>
@@ -4466,13 +4466,13 @@
     <t xml:space="preserve">14.2172260284424</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2364130020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7855281829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8143091201782</t>
+    <t xml:space="preserve">14.2364139556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7855291366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8143100738525</t>
   </si>
   <si>
     <t xml:space="preserve">14.1404800415039</t>
@@ -4484,25 +4484,25 @@
     <t xml:space="preserve">14.4090929031372</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3707180023193</t>
+    <t xml:space="preserve">14.3707189559937</t>
   </si>
   <si>
     <t xml:space="preserve">14.2939729690552</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1692609786987</t>
+    <t xml:space="preserve">14.1692600250244</t>
   </si>
   <si>
     <t xml:space="preserve">14.7160768508911</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9463157653809</t>
+    <t xml:space="preserve">14.9463148117065</t>
   </si>
   <si>
     <t xml:space="preserve">14.4378719329834</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3899049758911</t>
+    <t xml:space="preserve">14.3899059295654</t>
   </si>
   <si>
     <t xml:space="preserve">14.3131589889526</t>
@@ -4517,7 +4517,7 @@
     <t xml:space="preserve">14.3515319824219</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5721778869629</t>
+    <t xml:space="preserve">14.5721769332886</t>
   </si>
   <si>
     <t xml:space="preserve">14.5242118835449</t>
@@ -4529,25 +4529,25 @@
     <t xml:space="preserve">14.3611268997192</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0879135131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8288974761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2510013580322</t>
+    <t xml:space="preserve">16.0879154205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8288955688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2509994506836</t>
   </si>
   <si>
     <t xml:space="preserve">16.3373394012451</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7210712432861</t>
+    <t xml:space="preserve">16.7210693359375</t>
   </si>
   <si>
     <t xml:space="preserve">16.3277473449707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2030353546143</t>
+    <t xml:space="preserve">16.2030334472656</t>
   </si>
   <si>
     <t xml:space="preserve">16.2318134307861</t>
@@ -4559,10 +4559,10 @@
     <t xml:space="preserve">16.0207633972168</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3588266372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0783195495605</t>
+    <t xml:space="preserve">15.3588256835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0783214569092</t>
   </si>
   <si>
     <t xml:space="preserve">14.6297369003296</t>
@@ -4571,13 +4571,13 @@
     <t xml:space="preserve">14.6105499267578</t>
   </si>
   <si>
-    <t xml:space="preserve">14.639331817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1308879852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9486150741577</t>
+    <t xml:space="preserve">14.6393308639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1308870315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.948616027832</t>
   </si>
   <si>
     <t xml:space="preserve">14.044548034668</t>
@@ -4601,7 +4601,7 @@
     <t xml:space="preserve">13.555290222168</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4593572616577</t>
+    <t xml:space="preserve">13.459358215332</t>
   </si>
   <si>
     <t xml:space="preserve">13.4497661590576</t>
@@ -4610,7 +4610,7 @@
     <t xml:space="preserve">13.3826122283936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4305791854858</t>
+    <t xml:space="preserve">13.4305782318115</t>
   </si>
   <si>
     <t xml:space="preserve">13.3538331985474</t>
@@ -4625,13 +4625,13 @@
     <t xml:space="preserve">13.190746307373</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9701013565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2578992843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.027660369873</t>
+    <t xml:space="preserve">12.9701023101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2578983306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0276613235474</t>
   </si>
   <si>
     <t xml:space="preserve">13.1811532974243</t>
@@ -39464,7 +39464,7 @@
         <v>21.3199996948242</v>
       </c>
       <c r="G1276" t="s">
-        <v>709</v>
+        <v>1099</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -39490,7 +39490,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1277" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -39516,7 +39516,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G1278" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -39542,7 +39542,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G1279" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -39568,7 +39568,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1280" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -39594,7 +39594,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G1281" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -39620,7 +39620,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1282" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -39646,7 +39646,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G1283" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -39672,7 +39672,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1284" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -39698,7 +39698,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1285" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -39724,7 +39724,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1286" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -39750,7 +39750,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G1287" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -39776,7 +39776,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G1288" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -39802,7 +39802,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G1289" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -39828,7 +39828,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1290" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -39854,7 +39854,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G1291" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -39880,7 +39880,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1292" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -39906,7 +39906,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G1293" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -39932,7 +39932,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G1294" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -39958,7 +39958,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1295" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -39984,7 +39984,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G1296" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -40010,7 +40010,7 @@
         <v>23</v>
       </c>
       <c r="G1297" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -40036,7 +40036,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1298" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -40062,7 +40062,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G1299" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -40088,7 +40088,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G1300" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -40114,7 +40114,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G1301" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -40140,7 +40140,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G1302" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -40166,7 +40166,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G1303" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -40192,7 +40192,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1304" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -40218,7 +40218,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G1305" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -40244,7 +40244,7 @@
         <v>23.5400009155273</v>
       </c>
       <c r="G1306" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -40270,7 +40270,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G1307" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -40296,7 +40296,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G1308" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -40322,7 +40322,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G1309" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -40348,7 +40348,7 @@
         <v>21.8799991607666</v>
       </c>
       <c r="G1310" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -40374,7 +40374,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1311" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -40400,7 +40400,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G1312" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -40426,7 +40426,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G1313" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -40452,7 +40452,7 @@
         <v>22.1800003051758</v>
       </c>
       <c r="G1314" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -40478,7 +40478,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1315" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -40504,7 +40504,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G1316" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -40530,7 +40530,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1317" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -40556,7 +40556,7 @@
         <v>22.8600006103516</v>
       </c>
       <c r="G1318" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -40582,7 +40582,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1319" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -40608,7 +40608,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1320" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -40634,7 +40634,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G1321" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -40660,7 +40660,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1322" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -40686,7 +40686,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G1323" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -40712,7 +40712,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1324" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -40738,7 +40738,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1325" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -40764,7 +40764,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G1326" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -40790,7 +40790,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G1327" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -40816,7 +40816,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1328" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -40842,7 +40842,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G1329" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -40868,7 +40868,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1330" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -40894,7 +40894,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G1331" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -40920,7 +40920,7 @@
         <v>24.0400009155273</v>
       </c>
       <c r="G1332" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -40946,7 +40946,7 @@
         <v>24.4400005340576</v>
       </c>
       <c r="G1333" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -40972,7 +40972,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G1334" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -40998,7 +40998,7 @@
         <v>24.0799999237061</v>
       </c>
       <c r="G1335" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -41024,7 +41024,7 @@
         <v>24</v>
       </c>
       <c r="G1336" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -41050,7 +41050,7 @@
         <v>23.8600006103516</v>
       </c>
       <c r="G1337" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -41076,7 +41076,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G1338" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -41102,7 +41102,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G1339" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -41128,7 +41128,7 @@
         <v>25.1399993896484</v>
       </c>
       <c r="G1340" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -41154,7 +41154,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G1341" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -41180,7 +41180,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1342" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -41206,7 +41206,7 @@
         <v>26.4400005340576</v>
       </c>
       <c r="G1343" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -41232,7 +41232,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1344" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -41258,7 +41258,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G1345" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -41284,7 +41284,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G1346" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -41310,7 +41310,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G1347" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -41336,7 +41336,7 @@
         <v>25.1399993896484</v>
       </c>
       <c r="G1348" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -41362,7 +41362,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G1349" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -41388,7 +41388,7 @@
         <v>25.5599994659424</v>
       </c>
       <c r="G1350" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -41414,7 +41414,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G1351" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -41440,7 +41440,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G1352" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -41466,7 +41466,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G1353" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -41492,7 +41492,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G1354" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -41518,7 +41518,7 @@
         <v>24.2199993133545</v>
       </c>
       <c r="G1355" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -41544,7 +41544,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G1356" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -41570,7 +41570,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1357" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -41596,7 +41596,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1358" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -41622,7 +41622,7 @@
         <v>25.7600002288818</v>
       </c>
       <c r="G1359" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -41648,7 +41648,7 @@
         <v>25.1800003051758</v>
       </c>
       <c r="G1360" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -41674,7 +41674,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G1361" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -41700,7 +41700,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G1362" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -41726,7 +41726,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1363" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -41752,7 +41752,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1364" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -41778,7 +41778,7 @@
         <v>29</v>
       </c>
       <c r="G1365" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -41804,7 +41804,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1366" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -41830,7 +41830,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1367" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -41856,7 +41856,7 @@
         <v>29.4400005340576</v>
       </c>
       <c r="G1368" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -41882,7 +41882,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G1369" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -41908,7 +41908,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1370" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -41934,7 +41934,7 @@
         <v>30.5200004577637</v>
       </c>
       <c r="G1371" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -41960,7 +41960,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1372" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -41986,7 +41986,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1373" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -42012,7 +42012,7 @@
         <v>29.5599994659424</v>
       </c>
       <c r="G1374" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -42038,7 +42038,7 @@
         <v>29.8799991607666</v>
       </c>
       <c r="G1375" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -42064,7 +42064,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G1376" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -42090,7 +42090,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1377" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -42116,7 +42116,7 @@
         <v>29.3799991607666</v>
       </c>
       <c r="G1378" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -42142,7 +42142,7 @@
         <v>29.1599998474121</v>
       </c>
       <c r="G1379" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -42168,7 +42168,7 @@
         <v>28.7199993133545</v>
       </c>
       <c r="G1380" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -42194,7 +42194,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1381" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -42220,7 +42220,7 @@
         <v>27.8799991607666</v>
       </c>
       <c r="G1382" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -42246,7 +42246,7 @@
         <v>28.7199993133545</v>
       </c>
       <c r="G1383" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -42272,7 +42272,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1384" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -42298,7 +42298,7 @@
         <v>28.6800003051758</v>
       </c>
       <c r="G1385" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -42324,7 +42324,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1386" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -42350,7 +42350,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G1387" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -42376,7 +42376,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G1388" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -42402,7 +42402,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G1389" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -42428,7 +42428,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G1390" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -42454,7 +42454,7 @@
         <v>27.8799991607666</v>
       </c>
       <c r="G1391" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -42480,7 +42480,7 @@
         <v>28.4599990844727</v>
       </c>
       <c r="G1392" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -42506,7 +42506,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1393" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -42532,7 +42532,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G1394" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -42558,7 +42558,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1395" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -42584,7 +42584,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G1396" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -42610,7 +42610,7 @@
         <v>28.5400009155273</v>
       </c>
       <c r="G1397" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -42636,7 +42636,7 @@
         <v>28.6800003051758</v>
       </c>
       <c r="G1398" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -42662,7 +42662,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G1399" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -42688,7 +42688,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1400" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -42714,7 +42714,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1401" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -42740,7 +42740,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G1402" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -42766,7 +42766,7 @@
         <v>28.9799995422363</v>
       </c>
       <c r="G1403" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -42792,7 +42792,7 @@
         <v>28.9599990844727</v>
       </c>
       <c r="G1404" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -42818,7 +42818,7 @@
         <v>29.0799999237061</v>
       </c>
       <c r="G1405" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -42844,7 +42844,7 @@
         <v>29</v>
       </c>
       <c r="G1406" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -42870,7 +42870,7 @@
         <v>28.6599998474121</v>
       </c>
       <c r="G1407" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -42896,7 +42896,7 @@
         <v>28.7600002288818</v>
       </c>
       <c r="G1408" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -42922,7 +42922,7 @@
         <v>27.5599994659424</v>
       </c>
       <c r="G1409" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -42948,7 +42948,7 @@
         <v>27.5</v>
       </c>
       <c r="G1410" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -42974,7 +42974,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G1411" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -43000,7 +43000,7 @@
         <v>28.8199996948242</v>
       </c>
       <c r="G1412" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -43026,7 +43026,7 @@
         <v>29.4799995422363</v>
       </c>
       <c r="G1413" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -43052,7 +43052,7 @@
         <v>29.7800006866455</v>
       </c>
       <c r="G1414" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -43078,7 +43078,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G1415" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -43104,7 +43104,7 @@
         <v>33.0200004577637</v>
       </c>
       <c r="G1416" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -43130,7 +43130,7 @@
         <v>33.560001373291</v>
       </c>
       <c r="G1417" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -43156,7 +43156,7 @@
         <v>32.0800018310547</v>
       </c>
       <c r="G1418" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -43182,7 +43182,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1419" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -43208,7 +43208,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G1420" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -43234,7 +43234,7 @@
         <v>29.6399993896484</v>
       </c>
       <c r="G1421" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -43260,7 +43260,7 @@
         <v>29.9400005340576</v>
       </c>
       <c r="G1422" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -43286,7 +43286,7 @@
         <v>29.0400009155273</v>
       </c>
       <c r="G1423" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -43312,7 +43312,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1424" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -43338,7 +43338,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G1425" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -43364,7 +43364,7 @@
         <v>30.2399997711182</v>
       </c>
       <c r="G1426" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -43390,7 +43390,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1427" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -43416,7 +43416,7 @@
         <v>29.5200004577637</v>
       </c>
       <c r="G1428" t="s">
-        <v>1230</v>
+        <v>605</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -43442,7 +43442,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1429" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -43520,7 +43520,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1432" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -44118,7 +44118,7 @@
         <v>28.6599998474121</v>
       </c>
       <c r="G1455" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -44144,7 +44144,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G1456" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -44378,7 +44378,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1465" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -44456,7 +44456,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G1468" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -44482,7 +44482,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G1469" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -44716,7 +44716,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1478" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -45106,7 +45106,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1493" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -45132,7 +45132,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1494" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -45236,7 +45236,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G1498" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -45262,7 +45262,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G1499" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -45366,7 +45366,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1503" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -45626,7 +45626,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1513" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -45704,7 +45704,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1516" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -45730,7 +45730,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G1517" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -45756,7 +45756,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G1518" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -45860,7 +45860,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G1522" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -46172,7 +46172,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1534" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -46198,7 +46198,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1535" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -46224,7 +46224,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1536" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -46250,7 +46250,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G1537" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -46432,7 +46432,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1544" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -46484,7 +46484,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G1546" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -46510,7 +46510,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1547" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -46536,7 +46536,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1548" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -46562,7 +46562,7 @@
         <v>23</v>
       </c>
       <c r="G1549" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -46588,7 +46588,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1550" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -46718,7 +46718,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G1555" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -46770,7 +46770,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1557" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -71088,7 +71088,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6494444444</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>60876</v>
@@ -71109,6 +71109,32 @@
         <v>1968</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6493171296</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>82273</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>7.69000005722046</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>7.48000001907349</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>7.59999990463257</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>7.53999996185303</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1958</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="1982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="1983">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,49 +47,49 @@
     <t xml:space="preserve">12.9788007736206</t>
   </si>
   <si>
-    <t xml:space="preserve">12.747953414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3974027633667</t>
+    <t xml:space="preserve">12.747950553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3974046707153</t>
   </si>
   <si>
     <t xml:space="preserve">12.2435054779053</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2606058120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.140905380249</t>
+    <t xml:space="preserve">12.2606048583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1409063339233</t>
   </si>
   <si>
     <t xml:space="preserve">11.4825620651245</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8584175109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79822540283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3539695739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84952449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.473669052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2941198348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7814664840698</t>
+    <t xml:space="preserve">10.8584156036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7982234954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3539686203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84952354431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4736680984497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2941217422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7814674377441</t>
   </si>
   <si>
     <t xml:space="preserve">10.8156661987305</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7301683425903</t>
+    <t xml:space="preserve">10.730167388916</t>
   </si>
   <si>
     <t xml:space="preserve">10.576268196106</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">10.6361169815063</t>
   </si>
   <si>
-    <t xml:space="preserve">10.191520690918</t>
+    <t xml:space="preserve">10.1915216445923</t>
   </si>
   <si>
     <t xml:space="preserve">10.4565687179565</t>
@@ -107,52 +107,52 @@
     <t xml:space="preserve">10.4907703399658</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0205221176147</t>
+    <t xml:space="preserve">10.0205230712891</t>
   </si>
   <si>
     <t xml:space="preserve">9.03728008270264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97743129730225</t>
+    <t xml:space="preserve">8.97743034362793</t>
   </si>
   <si>
     <t xml:space="preserve">9.40492725372314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14842987060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43057632446289</t>
+    <t xml:space="preserve">9.14842796325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43057727813721</t>
   </si>
   <si>
     <t xml:space="preserve">9.90082359313965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66142463684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4394693374634</t>
+    <t xml:space="preserve">9.66142559051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4394702911377</t>
   </si>
   <si>
     <t xml:space="preserve">10.345419883728</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2000722885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0037641525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5506181716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2257204055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1829719543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0379638671875</t>
+    <t xml:space="preserve">10.2000732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0037651062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5506191253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2257213592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1829710006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0379657745361</t>
   </si>
   <si>
     <t xml:space="preserve">10.9097166061401</t>
@@ -164,121 +164,121 @@
     <t xml:space="preserve">11.9442577362061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1067066192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7732610702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9699077606201</t>
+    <t xml:space="preserve">12.106707572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7732591629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9699068069458</t>
   </si>
   <si>
     <t xml:space="preserve">11.6279106140137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3714122772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3799619674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6621103286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8416595458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.918607711792</t>
+    <t xml:space="preserve">11.371413230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3799629211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6621112823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8416576385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9186067581177</t>
   </si>
   <si>
     <t xml:space="preserve">11.7989091873169</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0468578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1922054290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.200756072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3375558853149</t>
+    <t xml:space="preserve">12.046856880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1922063827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2007551193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3375549316406</t>
   </si>
   <si>
     <t xml:space="preserve">12.1323556900024</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1665563583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2178564071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9015083312988</t>
+    <t xml:space="preserve">12.1665554046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2178554534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9015092849731</t>
   </si>
   <si>
     <t xml:space="preserve">11.568060874939</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2859115600586</t>
+    <t xml:space="preserve">11.2859125137329</t>
   </si>
   <si>
     <t xml:space="preserve">11.7390584945679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8844089508057</t>
+    <t xml:space="preserve">11.884407043457</t>
   </si>
   <si>
     <t xml:space="preserve">11.8160076141357</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7048587799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6022605895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6364612579346</t>
+    <t xml:space="preserve">11.7048597335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6022615432739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6364603042603</t>
   </si>
   <si>
     <t xml:space="preserve">11.4740114212036</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1918630599976</t>
+    <t xml:space="preserve">11.1918640136719</t>
   </si>
   <si>
     <t xml:space="preserve">11.1063642501831</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1149129867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3201122283936</t>
+    <t xml:space="preserve">11.1149139404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3201131820679</t>
   </si>
   <si>
     <t xml:space="preserve">11.3457622528076</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1576642990112</t>
+    <t xml:space="preserve">11.1576633453369</t>
   </si>
   <si>
     <t xml:space="preserve">11.055064201355</t>
   </si>
   <si>
-    <t xml:space="preserve">10.986665725708</t>
+    <t xml:space="preserve">10.9866647720337</t>
   </si>
   <si>
     <t xml:space="preserve">11.1405639648438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.60191822052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.954140663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4346113204956</t>
+    <t xml:space="preserve">10.6019172668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9541397094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4346122741699</t>
   </si>
   <si>
     <t xml:space="preserve">10.3553619384766</t>
@@ -287,34 +287,34 @@
     <t xml:space="preserve">10.22327709198</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2673053741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92389011383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3201389312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0031385421753</t>
+    <t xml:space="preserve">10.2673072814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92388916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3201398849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0031394958496</t>
   </si>
   <si>
     <t xml:space="preserve">10.302529335022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2496957778931</t>
+    <t xml:space="preserve">10.2496948242188</t>
   </si>
   <si>
     <t xml:space="preserve">10.6107244491577</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4120321273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1302547454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9189195632935</t>
+    <t xml:space="preserve">11.4120311737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1302528381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9189186096191</t>
   </si>
   <si>
     <t xml:space="preserve">11.2359199523926</t>
@@ -338,13 +338,13 @@
     <t xml:space="preserve">10.9101142883301</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8132514953613</t>
+    <t xml:space="preserve">10.813250541687</t>
   </si>
   <si>
     <t xml:space="preserve">10.513861656189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0647773742676</t>
+    <t xml:space="preserve">10.0647783279419</t>
   </si>
   <si>
     <t xml:space="preserve">9.99433326721191</t>
@@ -353,25 +353,25 @@
     <t xml:space="preserve">9.95030498504639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68613719940186</t>
+    <t xml:space="preserve">9.68613815307617</t>
   </si>
   <si>
     <t xml:space="preserve">10.0383605957031</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4962501525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3465566635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4522228240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5843067169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87986087799072</t>
+    <t xml:space="preserve">10.4962511062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3465557098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.452223777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5843076705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87985992431641</t>
   </si>
   <si>
     <t xml:space="preserve">9.12258052825928</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">9.67733097076416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5716667175293</t>
+    <t xml:space="preserve">9.57166481018066</t>
   </si>
   <si>
     <t xml:space="preserve">9.93269348144531</t>
@@ -401,16 +401,16 @@
     <t xml:space="preserve">9.72135925292969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.082389831543</t>
+    <t xml:space="preserve">10.0823888778687</t>
   </si>
   <si>
     <t xml:space="preserve">10.381778717041</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2849168777466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1352224349976</t>
+    <t xml:space="preserve">10.2849178314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1352233886719</t>
   </si>
   <si>
     <t xml:space="preserve">10.2144727706909</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">10.1528339385986</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6987781524658</t>
+    <t xml:space="preserve">10.6987791061401</t>
   </si>
   <si>
     <t xml:space="preserve">11.0774192810059</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">11.0333909988403</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9893617630005</t>
+    <t xml:space="preserve">10.9893627166748</t>
   </si>
   <si>
     <t xml:space="preserve">10.8748903274536</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">11.0950307846069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.253529548645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3151702880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7251958847046</t>
+    <t xml:space="preserve">11.2535305023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3151693344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7251968383789</t>
   </si>
   <si>
     <t xml:space="preserve">11.0510025024414</t>
@@ -455,22 +455,22 @@
     <t xml:space="preserve">10.9013080596924</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1654739379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0598087310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2183074951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1214456558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1830863952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.262336730957</t>
+    <t xml:space="preserve">11.1654758453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0598077774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2183084487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1214475631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1830854415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2623357772827</t>
   </si>
   <si>
     <t xml:space="preserve">11.5265035629272</t>
@@ -479,28 +479,28 @@
     <t xml:space="preserve">11.7466440200806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7730588912964</t>
+    <t xml:space="preserve">11.773060798645</t>
   </si>
   <si>
     <t xml:space="preserve">11.685004234314</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7994766235352</t>
+    <t xml:space="preserve">11.7994775772095</t>
   </si>
   <si>
     <t xml:space="preserve">11.6497821807861</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6673927307129</t>
+    <t xml:space="preserve">11.6673936843872</t>
   </si>
   <si>
     <t xml:space="preserve">11.4472532272339</t>
   </si>
   <si>
-    <t xml:space="preserve">11.323974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3680028915405</t>
+    <t xml:space="preserve">11.3239755630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3680038452148</t>
   </si>
   <si>
     <t xml:space="preserve">11.1390581130981</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">11.6938095092773</t>
   </si>
   <si>
-    <t xml:space="preserve">11.614559173584</t>
+    <t xml:space="preserve">11.6145601272583</t>
   </si>
   <si>
     <t xml:space="preserve">11.8258943557739</t>
@@ -524,25 +524,25 @@
     <t xml:space="preserve">12.0636434555054</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5039215087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5303401947021</t>
+    <t xml:space="preserve">12.5039234161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5303382873535</t>
   </si>
   <si>
     <t xml:space="preserve">12.4070615768433</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2837829589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6007843017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9177865982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8121175765991</t>
+    <t xml:space="preserve">12.283784866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6007862091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9177856445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8121185302734</t>
   </si>
   <si>
     <t xml:space="preserve">12.856146812439</t>
@@ -551,10 +551,10 @@
     <t xml:space="preserve">13.0322570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4108972549438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5782051086426</t>
+    <t xml:space="preserve">13.4108982086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5782032012939</t>
   </si>
   <si>
     <t xml:space="preserve">13.6838703155518</t>
@@ -566,22 +566,22 @@
     <t xml:space="preserve">14.3707056045532</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2210102081299</t>
+    <t xml:space="preserve">14.2210111618042</t>
   </si>
   <si>
     <t xml:space="preserve">14.2562341690063</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1329555511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1241512298584</t>
+    <t xml:space="preserve">14.1329536437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1241502761841</t>
   </si>
   <si>
     <t xml:space="preserve">14.0713157653809</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9216222763062</t>
+    <t xml:space="preserve">13.9216232299805</t>
   </si>
   <si>
     <t xml:space="preserve">13.7807302474976</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">13.7631196975708</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8335657119751</t>
+    <t xml:space="preserve">13.8335638046265</t>
   </si>
   <si>
     <t xml:space="preserve">13.7278985977173</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">13.375675201416</t>
   </si>
   <si>
-    <t xml:space="preserve">13.155535697937</t>
+    <t xml:space="preserve">13.1555366516113</t>
   </si>
   <si>
     <t xml:space="preserve">13.6486482620239</t>
@@ -614,43 +614,43 @@
     <t xml:space="preserve">13.5605916976929</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7367057800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8775939941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1769847869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0977344512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7845697402954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3040962219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.277681350708</t>
+    <t xml:space="preserve">13.7367038726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8775930404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1769828796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0977325439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7845678329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3040971755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2776832580566</t>
   </si>
   <si>
     <t xml:space="preserve">15.4890146255493</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4978199005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3657360076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4449872970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.339319229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5330419540405</t>
+    <t xml:space="preserve">15.4978218078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.365740776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4449892044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3393201828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5330438613892</t>
   </si>
   <si>
     <t xml:space="preserve">15.6651268005371</t>
@@ -659,19 +659,19 @@
     <t xml:space="preserve">15.5418472290039</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2424592971802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8060169219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1934585571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.369571685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4664325714111</t>
+    <t xml:space="preserve">15.2424573898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8060150146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1934604644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3695735931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4664344787598</t>
   </si>
   <si>
     <t xml:space="preserve">16.510461807251</t>
@@ -680,31 +680,31 @@
     <t xml:space="preserve">17.03879737854</t>
   </si>
   <si>
-    <t xml:space="preserve">16.889102935791</t>
+    <t xml:space="preserve">16.8891010284424</t>
   </si>
   <si>
     <t xml:space="preserve">17.1532688140869</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7746276855469</t>
+    <t xml:space="preserve">16.7746295928955</t>
   </si>
   <si>
     <t xml:space="preserve">16.5544872283936</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2374877929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.589714050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6513538360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5720996856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9947662353516</t>
+    <t xml:space="preserve">16.2374897003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5897102355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6513500213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5721015930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9947700500488</t>
   </si>
   <si>
     <t xml:space="preserve">16.7041835784912</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">16.8538780212402</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0123767852783</t>
+    <t xml:space="preserve">17.012378692627</t>
   </si>
   <si>
     <t xml:space="preserve">17.2941589355469</t>
@@ -734,40 +734,40 @@
     <t xml:space="preserve">16.8626842498779</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2061042785645</t>
+    <t xml:space="preserve">17.2061023712158</t>
   </si>
   <si>
     <t xml:space="preserve">17.3469924926758</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6551856994629</t>
+    <t xml:space="preserve">17.6551876068115</t>
   </si>
   <si>
     <t xml:space="preserve">17.540714263916</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5054931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7168254852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4526557922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5583267211914</t>
+    <t xml:space="preserve">17.5054912567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7168273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4526596069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5583248138428</t>
   </si>
   <si>
     <t xml:space="preserve">17.7432403564453</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8401050567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5759334564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7482128143311</t>
+    <t xml:space="preserve">17.8401069641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5759372711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7482109069824</t>
   </si>
   <si>
     <t xml:space="preserve">16.7658252716064</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">16.950740814209</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1620750427246</t>
+    <t xml:space="preserve">17.1620769500732</t>
   </si>
   <si>
     <t xml:space="preserve">17.2765464782715</t>
@@ -788,16 +788,16 @@
     <t xml:space="preserve">17.1092433929443</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8186569213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2325172424316</t>
+    <t xml:space="preserve">16.8186588287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2325191497803</t>
   </si>
   <si>
     <t xml:space="preserve">17.2853507995605</t>
   </si>
   <si>
-    <t xml:space="preserve">17.391019821167</t>
+    <t xml:space="preserve">17.3910217285156</t>
   </si>
   <si>
     <t xml:space="preserve">17.250129699707</t>
@@ -812,37 +812,37 @@
     <t xml:space="preserve">17.6463832855225</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9457721710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3722743988037</t>
+    <t xml:space="preserve">17.9457702636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3722763061523</t>
   </si>
   <si>
     <t xml:space="preserve">19.9358329772949</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3849182128906</t>
+    <t xml:space="preserve">20.384916305542</t>
   </si>
   <si>
     <t xml:space="preserve">20.5962505340576</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3408889770508</t>
+    <t xml:space="preserve">20.3408908843994</t>
   </si>
   <si>
     <t xml:space="preserve">20.8340015411377</t>
   </si>
   <si>
-    <t xml:space="preserve">21.045337677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5824775695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0893630981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.327112197876</t>
+    <t xml:space="preserve">21.0453357696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5824756622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0893650054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3271102905273</t>
   </si>
   <si>
     <t xml:space="preserve">21.6529197692871</t>
@@ -854,34 +854,34 @@
     <t xml:space="preserve">21.9170875549316</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8114204406738</t>
+    <t xml:space="preserve">21.8114223480225</t>
   </si>
   <si>
     <t xml:space="preserve">22.0139484405518</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2869205474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2605094909668</t>
+    <t xml:space="preserve">22.286922454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2605056762695</t>
   </si>
   <si>
     <t xml:space="preserve">22.348560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3221454620361</t>
+    <t xml:space="preserve">22.3221416473389</t>
   </si>
   <si>
     <t xml:space="preserve">22.1900615692139</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6303405761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4366149902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4806461334229</t>
+    <t xml:space="preserve">22.6303386688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.436616897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4806442260742</t>
   </si>
   <si>
     <t xml:space="preserve">22.6655616760254</t>
@@ -890,13 +890,13 @@
     <t xml:space="preserve">22.6215343475342</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6743659973145</t>
+    <t xml:space="preserve">22.6743679046631</t>
   </si>
   <si>
     <t xml:space="preserve">22.8945064544678</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0970363616943</t>
+    <t xml:space="preserve">23.0970344543457</t>
   </si>
   <si>
     <t xml:space="preserve">22.8328666687012</t>
@@ -905,28 +905,28 @@
     <t xml:space="preserve">22.3749771118164</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1938972473145</t>
+    <t xml:space="preserve">23.1938953399658</t>
   </si>
   <si>
     <t xml:space="preserve">23.3876190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5108966827393</t>
+    <t xml:space="preserve">23.5108985900879</t>
   </si>
   <si>
     <t xml:space="preserve">23.9159564971924</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2417621612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7084560394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6556224822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9197902679443</t>
+    <t xml:space="preserve">24.2417583465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7084541320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6556205749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9197883605957</t>
   </si>
   <si>
     <t xml:space="preserve">25.0870971679688</t>
@@ -941,13 +941,13 @@
     <t xml:space="preserve">26.4255447387695</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4879322052002</t>
+    <t xml:space="preserve">26.4879341125488</t>
   </si>
   <si>
     <t xml:space="preserve">27.397008895874</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6287326812744</t>
+    <t xml:space="preserve">27.6287307739258</t>
   </si>
   <si>
     <t xml:space="preserve">28.1545696258545</t>
@@ -956,22 +956,22 @@
     <t xml:space="preserve">27.6732940673828</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6804046630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3666687011719</t>
+    <t xml:space="preserve">28.6804084777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3666706085205</t>
   </si>
   <si>
     <t xml:space="preserve">27.8069820404053</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4665069580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0190830230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4914436340332</t>
+    <t xml:space="preserve">28.4665050506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0190811157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4914455413818</t>
   </si>
   <si>
     <t xml:space="preserve">29.7677326202393</t>
@@ -980,19 +980,19 @@
     <t xml:space="preserve">29.8746795654297</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3024826049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7748394012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2400951385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6678905487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8283233642578</t>
+    <t xml:space="preserve">30.3024806976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7748413085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2400932312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6678943634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8283157348633</t>
   </si>
   <si>
     <t xml:space="preserve">30.8996162414551</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">31.0154800415039</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9976577758789</t>
+    <t xml:space="preserve">30.9976539611816</t>
   </si>
   <si>
     <t xml:space="preserve">30.9352684020996</t>
@@ -1010,37 +1010,37 @@
     <t xml:space="preserve">30.6500663757324</t>
   </si>
   <si>
-    <t xml:space="preserve">30.748104095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6857223510742</t>
+    <t xml:space="preserve">30.7481060028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6857204437256</t>
   </si>
   <si>
     <t xml:space="preserve">29.3577556610107</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5003509521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3131942749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2775402069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1687927246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1331424713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9994583129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9281578063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0529308319092</t>
+    <t xml:space="preserve">29.5003547668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3131923675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2775421142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1687889099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1331462860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.999454498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9281539916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0529346466064</t>
   </si>
   <si>
     <t xml:space="preserve">29.4825325012207</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">29.8122940063477</t>
   </si>
   <si>
-    <t xml:space="preserve">28.912130355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1260299682617</t>
+    <t xml:space="preserve">28.9121284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1260318756104</t>
   </si>
   <si>
     <t xml:space="preserve">27.7713317871094</t>
@@ -1073,40 +1073,40 @@
     <t xml:space="preserve">27.5752582550049</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1189155578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3506393432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7178554534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5734558105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6180191040039</t>
+    <t xml:space="preserve">28.11891746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3506450653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7178573608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5734577178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6180210113525</t>
   </si>
   <si>
     <t xml:space="preserve">28.5199813842773</t>
   </si>
   <si>
-    <t xml:space="preserve">28.787353515625</t>
+    <t xml:space="preserve">28.7873554229736</t>
   </si>
   <si>
     <t xml:space="preserve">29.7855548858643</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5360088348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3310203552246</t>
+    <t xml:space="preserve">29.5360069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3310165405273</t>
   </si>
   <si>
     <t xml:space="preserve">29.1705932617188</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2329788208008</t>
+    <t xml:space="preserve">29.232982635498</t>
   </si>
   <si>
     <t xml:space="preserve">29.143856048584</t>
@@ -1118,52 +1118,52 @@
     <t xml:space="preserve">28.9656066894531</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7071418762207</t>
+    <t xml:space="preserve">28.7071437835693</t>
   </si>
   <si>
     <t xml:space="preserve">28.9923419952393</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9477825164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.607307434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8568553924561</t>
+    <t xml:space="preserve">28.9477806091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6073036193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8568572998047</t>
   </si>
   <si>
     <t xml:space="preserve">29.4023208618164</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4112319946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.814094543457</t>
+    <t xml:space="preserve">29.4112281799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8140964508057</t>
   </si>
   <si>
     <t xml:space="preserve">29.6875190734863</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6162204742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6786060333252</t>
+    <t xml:space="preserve">29.6162185668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6786041259766</t>
   </si>
   <si>
     <t xml:space="preserve">29.6964321136475</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1420574188232</t>
+    <t xml:space="preserve">30.1420497894287</t>
   </si>
   <si>
     <t xml:space="preserve">29.8390312194824</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1866149902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5181789398193</t>
+    <t xml:space="preserve">30.186616897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5181770324707</t>
   </si>
   <si>
     <t xml:space="preserve">29.1795082092285</t>
@@ -1175,16 +1175,16 @@
     <t xml:space="preserve">30.3648681640625</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4629096984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4718170166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.293571472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0974960327148</t>
+    <t xml:space="preserve">30.4629039764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4718189239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2935676574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0974941253662</t>
   </si>
   <si>
     <t xml:space="preserve">30.0618419647217</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">30.23118019104</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0849800109863</t>
+    <t xml:space="preserve">32.0849838256836</t>
   </si>
   <si>
     <t xml:space="preserve">31.4967517852783</t>
@@ -1211,28 +1211,28 @@
     <t xml:space="preserve">31.6928272247314</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1830177307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0760726928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9512882232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3077964782715</t>
+    <t xml:space="preserve">32.1830139160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0760688781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9512920379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.307788848877</t>
   </si>
   <si>
     <t xml:space="preserve">33.1990394592285</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3951187133789</t>
+    <t xml:space="preserve">33.3951148986816</t>
   </si>
   <si>
     <t xml:space="preserve">34.7587242126465</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6963424682617</t>
+    <t xml:space="preserve">34.6963348388672</t>
   </si>
   <si>
     <t xml:space="preserve">34.731990814209</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">34.5804786682129</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2239799499512</t>
+    <t xml:space="preserve">34.2239761352539</t>
   </si>
   <si>
     <t xml:space="preserve">34.437873840332</t>
@@ -1250,16 +1250,16 @@
     <t xml:space="preserve">34.5448265075684</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4271659851074</t>
+    <t xml:space="preserve">35.4271621704102</t>
   </si>
   <si>
     <t xml:space="preserve">35.2221755981445</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6606903076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.37548828125</t>
+    <t xml:space="preserve">34.6606941223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3754920959473</t>
   </si>
   <si>
     <t xml:space="preserve">33.8674774169922</t>
@@ -1277,13 +1277,13 @@
     <t xml:space="preserve">34.0635528564453</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3130989074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1170272827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.420051574707</t>
+    <t xml:space="preserve">34.313102722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1170196533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4200553894043</t>
   </si>
   <si>
     <t xml:space="preserve">34.7765502929688</t>
@@ -1292,67 +1292,67 @@
     <t xml:space="preserve">34.6161270141602</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3041877746582</t>
+    <t xml:space="preserve">34.3041915893555</t>
   </si>
   <si>
     <t xml:space="preserve">34.1081161499023</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8425407409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0902900695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.106315612793</t>
+    <t xml:space="preserve">32.8425445556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0902862548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1063079833984</t>
   </si>
   <si>
     <t xml:space="preserve">36.2471122741699</t>
   </si>
   <si>
-    <t xml:space="preserve">36.300594329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1847229003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4966659545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4146499633789</t>
+    <t xml:space="preserve">36.3005905151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1847267150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4966621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4146537780762</t>
   </si>
   <si>
     <t xml:space="preserve">38.8584747314453</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9208602905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6178398132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5821876525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2702445983887</t>
+    <t xml:space="preserve">38.9208564758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6178359985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5821914672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2702522277832</t>
   </si>
   <si>
     <t xml:space="preserve">38.4306716918945</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2149772644043</t>
+    <t xml:space="preserve">39.2149810791016</t>
   </si>
   <si>
     <t xml:space="preserve">38.805004119873</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8068008422852</t>
+    <t xml:space="preserve">37.8067970275879</t>
   </si>
   <si>
     <t xml:space="preserve">38.3504638671875</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0563507080078</t>
+    <t xml:space="preserve">38.0563545227051</t>
   </si>
   <si>
     <t xml:space="preserve">38.3682899475098</t>
@@ -1364,22 +1364,22 @@
     <t xml:space="preserve">38.5198059082031</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5643615722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6089248657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.689136505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7336959838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4377899169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0812873840332</t>
+    <t xml:space="preserve">38.5643653869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6089286804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6891441345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.733699798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4377861022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0812835693359</t>
   </si>
   <si>
     <t xml:space="preserve">39.0545501708984</t>
@@ -1391,19 +1391,19 @@
     <t xml:space="preserve">38.5554504394531</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2880744934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3772048950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6998481750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6125297546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6820259094238</t>
+    <t xml:space="preserve">38.2880783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3772010803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6998519897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6125259399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6820220947266</t>
   </si>
   <si>
     <t xml:space="preserve">38.4663276672363</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">42.6551933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8156242370605</t>
+    <t xml:space="preserve">42.8156204223633</t>
   </si>
   <si>
     <t xml:space="preserve">42.423469543457</t>
@@ -1445,13 +1445,13 @@
     <t xml:space="preserve">41.5322189331055</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7817687988281</t>
+    <t xml:space="preserve">41.7817726135254</t>
   </si>
   <si>
     <t xml:space="preserve">41.3539733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">40.819221496582</t>
+    <t xml:space="preserve">40.8192253112793</t>
   </si>
   <si>
     <t xml:space="preserve">40.3557739257812</t>
@@ -1460,25 +1460,25 @@
     <t xml:space="preserve">40.5874977111816</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8031997680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.143669128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6784286499023</t>
+    <t xml:space="preserve">39.8032035827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1436729431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6784248352051</t>
   </si>
   <si>
     <t xml:space="preserve">42.7799682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4787521362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6802253723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5750732421875</t>
+    <t xml:space="preserve">41.4787445068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6802291870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5750770568848</t>
   </si>
   <si>
     <t xml:space="preserve">37.2898750305176</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">40.1953468322754</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1062278747559</t>
+    <t xml:space="preserve">40.1062240600586</t>
   </si>
   <si>
     <t xml:space="preserve">40.5696754455566</t>
@@ -1499,46 +1499,46 @@
     <t xml:space="preserve">40.8013954162598</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9439926147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1400718688965</t>
+    <t xml:space="preserve">40.9439964294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1400680541992</t>
   </si>
   <si>
     <t xml:space="preserve">40.9974746704102</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5161933898926</t>
+    <t xml:space="preserve">40.5161972045898</t>
   </si>
   <si>
     <t xml:space="preserve">40.9618186950684</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2506256103516</t>
+    <t xml:space="preserve">39.2506217956543</t>
   </si>
   <si>
     <t xml:space="preserve">39.1793251037598</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2131729125977</t>
+    <t xml:space="preserve">40.2131767272949</t>
   </si>
   <si>
     <t xml:space="preserve">40.3914260864258</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3896141052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6017227172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.5446434020996</t>
+    <t xml:space="preserve">41.3896217346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6017189025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.5446472167969</t>
   </si>
   <si>
     <t xml:space="preserve">43.902946472168</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2309074401855</t>
+    <t xml:space="preserve">45.2309036254883</t>
   </si>
   <si>
     <t xml:space="preserve">43.8851203918457</t>
@@ -1553,22 +1553,22 @@
     <t xml:space="preserve">47.3253440856934</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9439086914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5874061584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6961631774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0098991394043</t>
+    <t xml:space="preserve">45.9439125061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5874099731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6961555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.009895324707</t>
   </si>
   <si>
     <t xml:space="preserve">43.8494720458984</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9582214355469</t>
+    <t xml:space="preserve">42.9582252502441</t>
   </si>
   <si>
     <t xml:space="preserve">41.4609222412109</t>
@@ -1580,28 +1580,28 @@
     <t xml:space="preserve">41.1578979492188</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0153007507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7675476074219</t>
+    <t xml:space="preserve">41.0152931213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7675514221191</t>
   </si>
   <si>
     <t xml:space="preserve">39.1080284118652</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7479209899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7853736877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5518531799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7319030761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3041000366211</t>
+    <t xml:space="preserve">40.7479248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7853698730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5518493652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7318992614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3040962219238</t>
   </si>
   <si>
     <t xml:space="preserve">40.2488250732422</t>
@@ -1616,19 +1616,19 @@
     <t xml:space="preserve">39.0367240905762</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3878211975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0509490966797</t>
+    <t xml:space="preserve">42.387825012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0509452819824</t>
   </si>
   <si>
     <t xml:space="preserve">41.9335708618164</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0149230957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7087097167969</t>
+    <t xml:space="preserve">41.0149269104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7087135314941</t>
   </si>
   <si>
     <t xml:space="preserve">40.6366577148438</t>
@@ -1640,22 +1640,22 @@
     <t xml:space="preserve">39.8441047668457</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7366104125977</t>
+    <t xml:space="preserve">37.7366142272949</t>
   </si>
   <si>
     <t xml:space="preserve">37.4844360351562</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3316230773926</t>
+    <t xml:space="preserve">36.3316192626953</t>
   </si>
   <si>
     <t xml:space="preserve">37.0521278381348</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4757232666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6018104553223</t>
+    <t xml:space="preserve">36.4757270812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6018142700195</t>
   </si>
   <si>
     <t xml:space="preserve">36.007396697998</t>
@@ -1667,37 +1667,37 @@
     <t xml:space="preserve">35.3589324951172</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2241363525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4135627746582</t>
+    <t xml:space="preserve">34.2241401672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4135589599609</t>
   </si>
   <si>
     <t xml:space="preserve">33.6657409667969</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8818893432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4763145446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6924705505371</t>
+    <t xml:space="preserve">33.881893157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4763069152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6924667358398</t>
   </si>
   <si>
     <t xml:space="preserve">35.1427841186523</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7284927368164</t>
+    <t xml:space="preserve">34.7284965515137</t>
   </si>
   <si>
     <t xml:space="preserve">34.5483627319336</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9899711608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8278579711914</t>
+    <t xml:space="preserve">33.9899749755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8278541564941</t>
   </si>
   <si>
     <t xml:space="preserve">34.4402885437012</t>
@@ -1712,10 +1712,10 @@
     <t xml:space="preserve">32.4048538208008</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3868408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.468189239502</t>
+    <t xml:space="preserve">32.3868446350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4681930541992</t>
   </si>
   <si>
     <t xml:space="preserve">31.7744083404541</t>
@@ -1724,28 +1724,28 @@
     <t xml:space="preserve">30.5315341949463</t>
   </si>
   <si>
-    <t xml:space="preserve">29.486795425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9371128082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2346153259277</t>
+    <t xml:space="preserve">29.4867992401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9371109008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2346172332764</t>
   </si>
   <si>
     <t xml:space="preserve">30.1532649993896</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2166042327881</t>
+    <t xml:space="preserve">29.2166023254395</t>
   </si>
   <si>
     <t xml:space="preserve">29.4147434234619</t>
   </si>
   <si>
-    <t xml:space="preserve">27.829626083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1265392303467</t>
+    <t xml:space="preserve">27.8296241760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1265411376953</t>
   </si>
   <si>
     <t xml:space="preserve">29.5408325195312</t>
@@ -1760,43 +1760,43 @@
     <t xml:space="preserve">29.6489086151123</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9551219940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1172409057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4054393768311</t>
+    <t xml:space="preserve">29.9551258087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1172370910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4054431915283</t>
   </si>
   <si>
     <t xml:space="preserve">31.666332244873</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6483154296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0806198120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1079368591309</t>
+    <t xml:space="preserve">31.6483192443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.080623626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1079406738281</t>
   </si>
   <si>
     <t xml:space="preserve">31.3601169586182</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9818515777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7383861541748</t>
+    <t xml:space="preserve">30.9818477630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7383823394775</t>
   </si>
   <si>
     <t xml:space="preserve">31.6122894287109</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8377475738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9191017150879</t>
+    <t xml:space="preserve">30.8377513885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9190998077393</t>
   </si>
   <si>
     <t xml:space="preserve">29.9010887145996</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">26.6407871246338</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2805328369141</t>
+    <t xml:space="preserve">26.2805309295654</t>
   </si>
   <si>
     <t xml:space="preserve">26.0463676452637</t>
@@ -1829,1900 +1829,1900 @@
     <t xml:space="preserve">26.5146999359131</t>
   </si>
   <si>
+    <t xml:space="preserve">27.2352046966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0550804138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1091194152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0190544128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7488632202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4693698883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9196872711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.577449798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9377002716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8476409912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7936038970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0457782745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0097541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7755870819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6041698455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5501346588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1805820465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1625671386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6401958465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6762237548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6675090789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4513568878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5594348907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7581653594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7320327758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7413330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7233238220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7860679626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4165153503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7047157287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5606136322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.236385345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4345283508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5158767700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7053070068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8226871490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3630657196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2369747161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3450508117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5972290039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7239093780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3189182281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2828941345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5437831878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8773097991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3909702301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0034027099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.003698348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.139087677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1120700836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2651767730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.661750793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2024269104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9502477645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7160863876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6800584793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6170139312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1573963165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6077136993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4005661010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4723224639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5533790588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.490629196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9406509399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8232727050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6614551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7968444824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0132942199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9052152633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2654685974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1934223175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7250890731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4008626937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0496120452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7524032592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5899925231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1486835479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.463906288147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1661052703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7875461578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1568031311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6434421539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3912620544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0127029418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0487289428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2288570404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0307178497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9226379394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4543075561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6791706085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8052616119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6251335144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3369312286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9493656158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7872486114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6971874237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3549423217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4269924163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9856815338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3552398681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7244987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3009071350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.607120513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3996829986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6698741912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2462768554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0661487579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9220523834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4176940917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4537200927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2823028564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7515163421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7425117492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7965526580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5083465576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4182834625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8508834838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9859771728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.868896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0490245819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9409465789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3462333679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2741813659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3822574615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2831878662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1748180389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.976676940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6164226531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4272899627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1387901306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.913631439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6974792480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1928291320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9496593475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2381534576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1300811767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6794662475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9676723480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.084753036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0667419433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8686008453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5173530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6074180603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5894069671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7695331573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6365585327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.24342918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6621894836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2249774932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5330257415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1916618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6842317581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6232395172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8021230697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9405145645142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7836713790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3131456375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8943853378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8390283584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4792137145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9533309936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0732688903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0179119110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.303918838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3777275085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1009454727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1378507614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.922061920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7006378173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4756231307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4202671051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5771102905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8298015594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7928981781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6914119720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.512526512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1803913116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0988998413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7575378417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1486206054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2132015228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4069490432739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4161748886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5914688110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8590250015259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9236068725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4807567596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6837291717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5361127853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.296236038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.370044708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0471343994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1762981414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9087438583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65964126586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53047847747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0932636260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4899835586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5730171203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4254016876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5176601409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3054628372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4438533782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6652774810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0286817550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9640998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0563611984253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.120943069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50279903411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29060077667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57660675048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21217918395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40131282806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43821716308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47512149810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20295333862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94001197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9861421585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88004302978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53970336914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24447059631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28137493133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11530685424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88106536865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97332572937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99177742004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2408819198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.434627532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.084038734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1024904251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61351203918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66886711120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52125072479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7980318069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56738090515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2629222869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39208698272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65041637420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31827926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71499824523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81648540496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6873197555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98255157470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75190258026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49357318878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2777853012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0655851364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5822439193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7298603057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2870101928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5084362030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3515930175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.431037902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6340093612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2337007522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9938230514526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1322145462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0860843658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1414403915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1875705718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9661474227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9569206237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7539482116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8277559280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7354965209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0676326751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4551248550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2577886581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2485628128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0824947357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5991516113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4054050445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2024326324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7559947967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7098627090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7744474411011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3408231735229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7190895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7283153533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0143213272095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1342601776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1250352859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9497394561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6637344360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.682186126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4571704864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1158084869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8482542037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0512256622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0327739715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9312877655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6473264694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7303609848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0865879058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7913551330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8651638031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7452220916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8190307617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1086273193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.997917175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9333333969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4720325469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6785955429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3187808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8446655273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2967395782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2044773101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7247257232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8538913726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1491241455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2506093978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9830541610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1583490371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0753164291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1065816879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6027421951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0399551391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9753723144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5878791809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.301872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6006956100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1301679611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30905342102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06353950500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97589445114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8928599357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55047273635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93796634674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90567493438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98409605026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91028738021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01177453994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47307586669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05431365966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85697746276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33673095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01382160186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39567756652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40028953552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34954643249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25728702545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.118896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74985456466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.929762840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78675937652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10967063903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84211587905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42694568634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28855514526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26087665557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32545900344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3346848487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1132607460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55610942840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77753448486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93437623977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60223865509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33929777145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51920557022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3070068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1455512046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10403442382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15939044952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06713008880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92874050140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56533479690552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54227066040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44539737701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27010250091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72217798233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46948528289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66784572601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90310859680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54329395294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69090938568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87542915344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32750511169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0066413879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4863920211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4956197738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2557430267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9420576095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82570934295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74267673492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4623050689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1947498321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0194568634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89029216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3792715072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3608198165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2224292755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.674503326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5453405380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7667636871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.021502494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4402627944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5417490005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6155576705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8093032836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.818531036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7078161239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6616888046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5694274902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3480033874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2741956710815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1450309753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8128938674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0030508041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3167352676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8241662979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7042284011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0548162460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3961791992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2854671478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4423093795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1286239624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2301111221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0086870193481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1932067871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5437955856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3500499725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5714750289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3685007095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1470766067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4976654052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1101722717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1655282974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.267014503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2762413024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0455913543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1747550964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.331597328186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3869543075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5104808807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3813180923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6304187774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.335186958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7872619628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5068912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4330835342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4515352249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2690601348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5735187530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8318471908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1455326080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3613195419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4628076553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7616300582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5217533111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5955619812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7154989242554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3556852340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9128351211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6545085906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5033025741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4110412597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.650918006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1860265731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6750068664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4166765213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1029920578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9184713363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3889999389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7764930725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5827474594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1547603607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8133964538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8410739898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.924108505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1178550720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8503007888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8779792785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3520946502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6381015777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4351272583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5919723510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9517889022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0994033813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0717258453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5145740509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7877655029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3910446166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4648532867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1142635345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2618808746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5386619567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4464015960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5663414001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.372594833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.621696472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5478858947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.036865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.415132522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7657222747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9835548400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4299964904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4484481811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.728816986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.245475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1901187896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3377342224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2639293670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5442981719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5627498626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2029342651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4704914093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9722843170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1844825744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2823791503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9651031494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6109256744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9430637359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2567481994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2198429107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.312105178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1829376220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7513618469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7698135375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2900619506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8472137451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4745826721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7180500030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5371170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6293773651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7216396331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1865272521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1275825500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6847362518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2013912200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4633083343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8728466033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6478290557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8508033752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0906810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.109130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2234325408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9466514587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1311702728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1127223968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6145153045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8543930053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.795446395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.31569480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8323497772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1793518066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5483913421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0686359405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2162551879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1424446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0132827758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2531604766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0317306518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1942100524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7846755981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.729320526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3935947418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8953895568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0465927124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9174327850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3049240112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3971843719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5817012786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1388549804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5852947235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8067169189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3454170227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4894428253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7477741241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7662239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2311153411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7144584655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6370620727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0763187408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7554550170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4786739349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.976879119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1613998413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3828239440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4935340881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1578121185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.04709815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2721099853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5673427581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4012756347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1060428619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9030704498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4971256256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9251117706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7221393585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6447410583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4602222442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3864135742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9989185333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5007171630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9066619873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2572479248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1280841827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9620151519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6631946563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3310565948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5155773162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4453601837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7370014190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7185497283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8292617797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4417686462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.534029006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4269065856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3715515136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5893859863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1983032226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4750843048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9143409729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4643135070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9625225067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5970706939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0322341918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8846187591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3459205627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6226997375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7923583984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9399757385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1798515319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8994789123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5857963562012</t>
+  </si>
+  <si>
     <t xml:space="preserve">27.2352066040039</t>
   </si>
   <si>
-    <t xml:space="preserve">27.055082321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1091175079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0190525054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7488651275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4693698883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9196872711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5774478912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9377002716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8476371765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7936019897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0457782745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0097541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7755889892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6041717529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5501346588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1805801391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1625690460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6401958465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6762237548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6675090789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4513568878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5594367980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7581653594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7320289611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7413330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7233200073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7860698699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4165134429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7047176361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5606136322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.236385345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4345283508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5158786773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7053070068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8226852416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3630638122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2369766235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3450527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5972290039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7239093780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3189182281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2828922271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5437831878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8773097991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3909702301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0034027099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.003698348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.139087677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1120681762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2651748657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.661750793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2024269104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.950249671936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.716082572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6800584793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6170139312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1573963165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6077136993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4005680084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4723205566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5533809661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4906272888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9406509399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8232746124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6614551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7968463897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0132923126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9052171707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2654685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1934204101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7250881195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4008626937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0496139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.752402305603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5899925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1486835479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4639024734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1661052703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7875461578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1568050384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.643440246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3912620544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0127029418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0487289428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2288551330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0307159423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9226379394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4543075561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6791725158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8052616119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6251354217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3369312286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9493656158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7872486114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6971874237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.354944229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4269924163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9856834411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3552417755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7244987487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3009052276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.607120513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3996829986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6698703765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2462749481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0661506652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9220523834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4176921844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4537200927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2823047637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7515163421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7425117492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7965526580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5083465576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.418285369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8508834838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9859809875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.868896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0490245819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9409446716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3462352752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2741813659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3822555541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2831878662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1748180389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9766750335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6164245605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4272918701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1387901306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.913631439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6974792480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1928291320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9496555328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2381572723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1300792694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6794662475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9676685333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.084753036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0667419433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8686008453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5173530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6074180603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5894050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6365566253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2434272766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6621894836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2249755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5330257415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1916599273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6842317581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6232395172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8021230697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9405136108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7836713790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3131446838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8943843841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8390283584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4792127609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9533309936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0732688903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0179119110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.303918838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3777275085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1009454727173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1378507614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9220628738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7006387710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4756231307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4202671051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5771102905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8298015594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7928981781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6914129257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.512526512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1803903579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0988998413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7575378417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1486215591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2132024765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4069490432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4161748886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5914688110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8590250015259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9236059188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4807558059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6837291717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5361137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2962369918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3700437545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0471353530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1762971878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9087438583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65964126586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53047752380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0932645797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4899835586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5730171203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4254016876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5176610946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3054628372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4438543319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6652784347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286827087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9640998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.056360244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.120943069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50279998779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29060077667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5766077041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21217918395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40131282806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43821716308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47512149810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20295333862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94001197814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9861421585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88004398345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53970336914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24447154998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28137588500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11530685424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88106632232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97332668304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99177837371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2408809661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4346284866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.084038734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1024904251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61351108551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66886615753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5212516784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7980318069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56738185882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2629222869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39208793640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65041637420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31827831268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71499729156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81648445129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6873197555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98255252838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75190162658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49357223510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2777853012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0655851364136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5822439193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7298612594604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2870101928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5084352493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3515930175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.431037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6340093612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2337007522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.993824005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1322145462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0860843658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1414413452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1875705718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9661474227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9569206237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7539472579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8277559280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7354955673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0676326751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4551248550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2577886581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2485628128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0824947357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5991516113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4054050445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2024326324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7559938430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7098636627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7744464874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3408231735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7190895080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7283153533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0143213272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1342601776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1250352859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9497404098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6637344360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.682186126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4571714401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1158084869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8482542037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0512256622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0327739715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9312887191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.64732837677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7303609848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0865859985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.791353225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8651638031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7452239990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8190326690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1086273193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.997917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9333333969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4720344543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.678596496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3187808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8446645736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2967395782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2044792175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7247247695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8538913726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1491222381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2506084442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9830551147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1583480834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0753145217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1065826416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6027412414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0399541854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9753723144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5878801345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3018732070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6006946563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1301679611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30905342102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06353950500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97589349746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8928599357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55047273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93796634674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90567541122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98409652709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91028785705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01177358627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47307538986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05431365966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85697746276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33673095703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01382160186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.395676612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40028953552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34954643249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25728607177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11889743804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74985551834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.929762840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78675937652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10967063903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84211587905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42694568634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28855514526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26087665557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32545900344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3346848487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11326026916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55610942840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77753353118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93437719345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60223960876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33929824829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51920461654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30700635910034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14555168151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10403394699097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15939044952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06713008880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92874050140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56533527374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54227066040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.445396900177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27010297775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72217798233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46948528289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66784477233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90310764312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54329299926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69091033935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8754301071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32750511169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0066404342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4863929748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4956188201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2557430267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9420576095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82570934295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74267768859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4623050689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1947498321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.019455909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89029121398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3792715072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.360818862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2224292755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.674503326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5453395843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7667636871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0215015411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4402637481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5417499542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6155576705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8093042373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8185300827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7078170776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6616888046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5694284439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3480033874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2741947174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1450309753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8128938674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0030508041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3167352676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8241662979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7042284011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0548162460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3961791992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2854681015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4423093795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1286249160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2301111221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0086870193481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1932067871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5437955856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3500499725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5714750289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3685007095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1470766067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4976654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1101732254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1655292510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2670154571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2762413024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0455904006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1747550964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3315963745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3869533538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5104808807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3813180923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6304187774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.335186958313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7872619628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5068912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4330835342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4515342712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2690591812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5735187530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8318471908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1455326080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3613204956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4628076553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7616300582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5217533111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5955610275269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7154998779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3556852340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9128351211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6545076370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5033025741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4110412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.650918006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1860265731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6750068664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4166774749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1029939651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9184722900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3889999389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7764930725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.582745552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1547603607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8133945465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8410720825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.924108505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1178550720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8502988815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8779773712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3520946502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6381034851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4351291656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5919704437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9517869949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.099401473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0717258453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5145721435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7877635955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3910465240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4648532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1142635345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2618808746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5386619567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4464015960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5663394927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3725929260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.621696472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.547887802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.036865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4151306152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7657203674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6698722839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9835567474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4299945831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4484481811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.728816986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.245475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1901187896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3377323150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2639274597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5442981719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5627517700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2029342651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4704914093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9722843170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1844825744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2823791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9651050567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6109256744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9430618286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2567481994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2198429107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3121032714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1829376220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7513618469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7698135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2900619506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8472118377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4745826721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7180500030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5371189117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6293773651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7216377258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1865291595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1275825500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6847343444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2013893127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4633102416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8728446960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6478290557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8508033752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0906791687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1091327667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2234325408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9466533660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1311702728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.112720489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6145172119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8543930053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.795446395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.31569480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8323497772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.179349899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5483894348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0686359405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2162532806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1424446105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0132808685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2531585693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0317344665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1942100524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7846755981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.729320526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3935928344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8953895568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.046594619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9174308776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3049221038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3971843719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5817031860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1388568878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5852928161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8067169189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3454170227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4894428253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7477741241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7662220001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2311153411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7144584655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6370601654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0763206481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7554550170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4786758422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.976879119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1614017486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3828258514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4935359954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1578102111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0470943450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2721118927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5673427581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4012775421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1060428619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9030685424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4971256256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9251136779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7221393585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.644739151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4602222442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3864135742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9989223480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5007133483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9066619873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2572498321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1280860900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9620170593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6631927490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3310585021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5155773162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4453601837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7370014190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7185497283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8292636871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4417686462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5340309143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.426908493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3715515136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5893859863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1983032226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4750823974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.914342880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4643115997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9625225067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5970706939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0322341918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8846187591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3459186553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6227016448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7923583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9399757385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1798515319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8994808197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5857963562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2167530059814</t>
+    <t xml:space="preserve">27.2167549133301</t>
   </si>
   <si>
     <t xml:space="preserve">27.364372253418</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6262893676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2536582946777</t>
+    <t xml:space="preserve">26.6262912750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2536602020264</t>
   </si>
   <si>
     <t xml:space="preserve">27.7703170776367</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3090152740479</t>
+    <t xml:space="preserve">27.3090171813965</t>
   </si>
   <si>
     <t xml:space="preserve">27.9548377990723</t>
@@ -3740,13 +3740,13 @@
     <t xml:space="preserve">28.3423290252686</t>
   </si>
   <si>
-    <t xml:space="preserve">27.917932510376</t>
+    <t xml:space="preserve">27.9179344177246</t>
   </si>
   <si>
     <t xml:space="preserve">27.6965084075928</t>
   </si>
   <si>
-    <t xml:space="preserve">27.050687789917</t>
+    <t xml:space="preserve">27.0506858825684</t>
   </si>
   <si>
     <t xml:space="preserve">27.7518653869629</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">27.8256702423096</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9732913970947</t>
+    <t xml:space="preserve">27.9732875823975</t>
   </si>
   <si>
     <t xml:space="preserve">28.3054256439209</t>
@@ -3764,10 +3764,10 @@
     <t xml:space="preserve">28.2869739532471</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0840015411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7887687683105</t>
+    <t xml:space="preserve">28.0840034484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7887706756592</t>
   </si>
   <si>
     <t xml:space="preserve">26.294153213501</t>
@@ -3776,10 +3776,10 @@
     <t xml:space="preserve">26.9953308105469</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2203464508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5191688537598</t>
+    <t xml:space="preserve">26.220344543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5191669464111</t>
   </si>
   <si>
     <t xml:space="preserve">24.6150169372559</t>
@@ -3788,7 +3788,7 @@
     <t xml:space="preserve">24.0983619689941</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9656066894531</t>
+    <t xml:space="preserve">24.9656085968018</t>
   </si>
   <si>
     <t xml:space="preserve">24.356689453125</t>
@@ -3815,19 +3815,19 @@
     <t xml:space="preserve">24.6334705352783</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2423858642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0947723388672</t>
+    <t xml:space="preserve">25.2423877716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0947704315186</t>
   </si>
   <si>
     <t xml:space="preserve">24.910249710083</t>
   </si>
   <si>
-    <t xml:space="preserve">24.984058380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8179912567139</t>
+    <t xml:space="preserve">24.9840564727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8179893493652</t>
   </si>
   <si>
     <t xml:space="preserve">25.1870288848877</t>
@@ -3836,16 +3836,16 @@
     <t xml:space="preserve">24.670373916626</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5376205444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8733463287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9287014007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8364429473877</t>
+    <t xml:space="preserve">25.5376224517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8733444213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9287052154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8364410400391</t>
   </si>
   <si>
     <t xml:space="preserve">24.2644290924072</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">24.3013343811035</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8769340515137</t>
+    <t xml:space="preserve">23.8769359588623</t>
   </si>
   <si>
     <t xml:space="preserve">23.5263481140137</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">21.8841152191162</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0353221893311</t>
+    <t xml:space="preserve">21.0353202819824</t>
   </si>
   <si>
     <t xml:space="preserve">20.7031860351562</t>
@@ -3881,28 +3881,28 @@
     <t xml:space="preserve">21.736499786377</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4597225189209</t>
+    <t xml:space="preserve">21.4597206115723</t>
   </si>
   <si>
     <t xml:space="preserve">21.5335273742676</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6591014862061</t>
+    <t xml:space="preserve">22.6591033935547</t>
   </si>
   <si>
     <t xml:space="preserve">21.4412670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3525943756104</t>
+    <t xml:space="preserve">20.352596282959</t>
   </si>
   <si>
     <t xml:space="preserve">20.9799671173096</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9948291778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5299396514893</t>
+    <t xml:space="preserve">21.9948272705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5299377441406</t>
   </si>
   <si>
     <t xml:space="preserve">22.5114860534668</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">22.9358825683594</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3085155487061</t>
+    <t xml:space="preserve">22.3085136413574</t>
   </si>
   <si>
     <t xml:space="preserve">21.3859119415283</t>
@@ -3935,10 +3935,10 @@
     <t xml:space="preserve">19.9281997680664</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0758171081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8877086639404</t>
+    <t xml:space="preserve">20.0758190155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8877067565918</t>
   </si>
   <si>
     <t xml:space="preserve">20.4448585510254</t>
@@ -3956,61 +3956,61 @@
     <t xml:space="preserve">20.2049808502197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5002136230469</t>
+    <t xml:space="preserve">20.5002117156982</t>
   </si>
   <si>
     <t xml:space="preserve">20.7585430145264</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3710479736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0204620361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9871444702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5073909759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6770534515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1291255950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1198997497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.06813621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3633651733398</t>
+    <t xml:space="preserve">20.3710498809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0204601287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9871463775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5073928833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6770515441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1291275024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1198978424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0681343078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3633670806885</t>
   </si>
   <si>
     <t xml:space="preserve">15.0845413208008</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2321557998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2839221954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3705463409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2377948760986</t>
+    <t xml:space="preserve">15.23215675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2839241027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3705472946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.23779296875</t>
   </si>
   <si>
     <t xml:space="preserve">13.4699878692627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2172946929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0604524612427</t>
+    <t xml:space="preserve">14.2172937393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.060453414917</t>
   </si>
   <si>
     <t xml:space="preserve">14.3372325897217</t>
@@ -4022,10 +4022,10 @@
     <t xml:space="preserve">14.8169851303101</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2634248733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2541990280151</t>
+    <t xml:space="preserve">14.2634258270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2541980743408</t>
   </si>
   <si>
     <t xml:space="preserve">14.6601438522339</t>
@@ -4037,55 +4037,55 @@
     <t xml:space="preserve">15.6565532684326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0420007705688</t>
+    <t xml:space="preserve">14.0420017242432</t>
   </si>
   <si>
     <t xml:space="preserve">13.9958715438843</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8205757141113</t>
+    <t xml:space="preserve">13.820574760437</t>
   </si>
   <si>
     <t xml:space="preserve">14.3649110794067</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8667068481445</t>
+    <t xml:space="preserve">13.8667058944702</t>
   </si>
   <si>
     <t xml:space="preserve">13.617603302002</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8113508224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8057136535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.713454246521</t>
+    <t xml:space="preserve">13.8113498687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8057146072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7134532928467</t>
   </si>
   <si>
     <t xml:space="preserve">13.3592748641968</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9461507797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0476360321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.305965423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3428678512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0384092330933</t>
+    <t xml:space="preserve">14.9461517333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0476369857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3059663772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3428688049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0384111404419</t>
   </si>
   <si>
     <t xml:space="preserve">15.2341136932373</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7736358642578</t>
+    <t xml:space="preserve">14.7736368179321</t>
   </si>
   <si>
     <t xml:space="preserve">14.9367218017578</t>
@@ -4097,25 +4097,25 @@
     <t xml:space="preserve">15.4739437103271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9823875427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5410985946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7137765884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7809314727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0303554534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8576755523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6466236114502</t>
+    <t xml:space="preserve">15.9823884963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5410995483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7137775421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.780930519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0303535461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8576765060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6466245651245</t>
   </si>
   <si>
     <t xml:space="preserve">15.3204526901245</t>
@@ -4127,28 +4127,28 @@
     <t xml:space="preserve">13.612850189209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5456972122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8430891036987</t>
+    <t xml:space="preserve">13.5456981658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.843090057373</t>
   </si>
   <si>
     <t xml:space="preserve">12.9509143829346</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1427793502808</t>
+    <t xml:space="preserve">13.1427803039551</t>
   </si>
   <si>
     <t xml:space="preserve">13.0180673599243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0660343170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7590503692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4040985107422</t>
+    <t xml:space="preserve">13.0660352706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7590494155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4040994644165</t>
   </si>
   <si>
     <t xml:space="preserve">12.8070163726807</t>
@@ -4160,7 +4160,7 @@
     <t xml:space="preserve">12.8453893661499</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5959634780884</t>
+    <t xml:space="preserve">12.5959644317627</t>
   </si>
   <si>
     <t xml:space="preserve">12.1258945465088</t>
@@ -4169,19 +4169,19 @@
     <t xml:space="preserve">11.8093156814575</t>
   </si>
   <si>
-    <t xml:space="preserve">11.780535697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5502977371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9724006652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6247444152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0468482971191</t>
+    <t xml:space="preserve">11.7805366516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5502986907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9724016189575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6247434616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0468473434448</t>
   </si>
   <si>
     <t xml:space="preserve">12.7974224090576</t>
@@ -4190,25 +4190,25 @@
     <t xml:space="preserve">12.7206764221191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6823034286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2026395797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8933544158936</t>
+    <t xml:space="preserve">12.6823043823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2026405334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8933553695679</t>
   </si>
   <si>
     <t xml:space="preserve">13.1715602874756</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1044073104858</t>
+    <t xml:space="preserve">13.1044082641602</t>
   </si>
   <si>
     <t xml:space="preserve">13.0948133468628</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4712514877319</t>
+    <t xml:space="preserve">12.4712505340576</t>
   </si>
   <si>
     <t xml:space="preserve">12.4328784942627</t>
@@ -4220,25 +4220,25 @@
     <t xml:space="preserve">13.3058652877808</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0372552871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3154592514038</t>
+    <t xml:space="preserve">13.0372543334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3154602050781</t>
   </si>
   <si>
     <t xml:space="preserve">12.480845451355</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6055583953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1738595962524</t>
+    <t xml:space="preserve">12.6055574417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1738586425781</t>
   </si>
   <si>
     <t xml:space="preserve">12.5096244812012</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2793865203857</t>
+    <t xml:space="preserve">12.2793855667114</t>
   </si>
   <si>
     <t xml:space="preserve">12.3945055007935</t>
@@ -4253,16 +4253,16 @@
     <t xml:space="preserve">12.0107755661011</t>
   </si>
   <si>
-    <t xml:space="preserve">12.154673576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2218255996704</t>
+    <t xml:space="preserve">12.1546726226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2218265533447</t>
   </si>
   <si>
     <t xml:space="preserve">12.3081665039062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1162996292114</t>
+    <t xml:space="preserve">12.1163005828857</t>
   </si>
   <si>
     <t xml:space="preserve">12.1834535598755</t>
@@ -4277,10 +4277,10 @@
     <t xml:space="preserve">11.4927368164062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4639577865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3296518325806</t>
+    <t xml:space="preserve">11.4639587402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3296527862549</t>
   </si>
   <si>
     <t xml:space="preserve">11.6654167175293</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">12.1354866027832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7421627044678</t>
+    <t xml:space="preserve">11.7421636581421</t>
   </si>
   <si>
     <t xml:space="preserve">11.7709426879883</t>
@@ -4307,55 +4307,55 @@
     <t xml:space="preserve">11.3680257797241</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2720937728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9363279342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9459209442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8499898910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7540559768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9555149078369</t>
+    <t xml:space="preserve">11.2720928192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9363269805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9459218978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8499889373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.754056930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9555139541626</t>
   </si>
   <si>
     <t xml:space="preserve">11.1090068817139</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4159917831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6558227539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5694847106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5790777206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5311117172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7613496780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8764696121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0491485595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9628086090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9413223266602</t>
+    <t xml:space="preserve">11.4159908294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6558237075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5694856643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5790767669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5311126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7613506317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8764686584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.049147605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9628076553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9413213729858</t>
   </si>
   <si>
     <t xml:space="preserve">13.2003402709961</t>
@@ -4367,37 +4367,37 @@
     <t xml:space="preserve">11.3104658126831</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9267349243164</t>
+    <t xml:space="preserve">10.9267358779907</t>
   </si>
   <si>
     <t xml:space="preserve">10.8212089538574</t>
   </si>
   <si>
-    <t xml:space="preserve">11.895655632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7229766845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7398633956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2889795303345</t>
+    <t xml:space="preserve">11.8956546783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7229776382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7398624420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2889804840088</t>
   </si>
   <si>
     <t xml:space="preserve">12.0875205993652</t>
   </si>
   <si>
-    <t xml:space="preserve">12.260199546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1930475234985</t>
+    <t xml:space="preserve">12.2601985931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1930456161499</t>
   </si>
   <si>
     <t xml:space="preserve">12.3369455337524</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136905670166</t>
+    <t xml:space="preserve">12.4136915206909</t>
   </si>
   <si>
     <t xml:space="preserve">12.5671844482422</t>
@@ -4406,7 +4406,7 @@
     <t xml:space="preserve">12.2314195632935</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7686433792114</t>
+    <t xml:space="preserve">12.7686443328857</t>
   </si>
   <si>
     <t xml:space="preserve">12.7014894485474</t>
@@ -4424,7 +4424,7 @@
     <t xml:space="preserve">12.4616584777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.991587638855</t>
+    <t xml:space="preserve">11.9915885925293</t>
   </si>
   <si>
     <t xml:space="preserve">11.9244346618652</t>
@@ -4436,7 +4436,7 @@
     <t xml:space="preserve">12.0587406158447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5000305175781</t>
+    <t xml:space="preserve">12.5000314712524</t>
   </si>
   <si>
     <t xml:space="preserve">12.8262023925781</t>
@@ -4454,7 +4454,7 @@
     <t xml:space="preserve">13.8718690872192</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7663440704346</t>
+    <t xml:space="preserve">13.7663431167603</t>
   </si>
   <si>
     <t xml:space="preserve">14.0733280181885</t>
@@ -4463,34 +4463,34 @@
     <t xml:space="preserve">14.3803119659424</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2172260284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2364139556885</t>
+    <t xml:space="preserve">14.2172269821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2364130020142</t>
   </si>
   <si>
     <t xml:space="preserve">13.7855291366577</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8143100738525</t>
+    <t xml:space="preserve">13.8143091201782</t>
   </si>
   <si>
     <t xml:space="preserve">14.1404800415039</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1980400085449</t>
+    <t xml:space="preserve">14.1980409622192</t>
   </si>
   <si>
     <t xml:space="preserve">14.4090929031372</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3707189559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2939729690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1692600250244</t>
+    <t xml:space="preserve">14.3707180023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2939720153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1692609786987</t>
   </si>
   <si>
     <t xml:space="preserve">14.7160768508911</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">14.3131589889526</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4474649429321</t>
+    <t xml:space="preserve">14.4474658966064</t>
   </si>
   <si>
     <t xml:space="preserve">14.3323450088501</t>
@@ -4520,34 +4520,34 @@
     <t xml:space="preserve">14.5721769332886</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5242118835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6009578704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3611268997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0879154205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8288955688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2509994506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3373394012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7210693359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3277473449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2030334472656</t>
+    <t xml:space="preserve">14.5242109298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6009588241577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3611259460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0879135131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.828896522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2510013580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3373413085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7210712432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3277454376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2030353546143</t>
   </si>
   <si>
     <t xml:space="preserve">16.2318134307861</t>
@@ -4559,7 +4559,7 @@
     <t xml:space="preserve">16.0207633972168</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3588256835938</t>
+    <t xml:space="preserve">15.3588266372681</t>
   </si>
   <si>
     <t xml:space="preserve">16.0783214569092</t>
@@ -4571,13 +4571,13 @@
     <t xml:space="preserve">14.6105499267578</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6393308639526</t>
+    <t xml:space="preserve">14.639331817627</t>
   </si>
   <si>
     <t xml:space="preserve">14.1308870315552</t>
   </si>
   <si>
-    <t xml:space="preserve">13.948616027832</t>
+    <t xml:space="preserve">13.9486150741577</t>
   </si>
   <si>
     <t xml:space="preserve">14.044548034668</t>
@@ -4598,7 +4598,7 @@
     <t xml:space="preserve">13.6416311264038</t>
   </si>
   <si>
-    <t xml:space="preserve">13.555290222168</t>
+    <t xml:space="preserve">13.5552911758423</t>
   </si>
   <si>
     <t xml:space="preserve">13.459358215332</t>
@@ -4613,25 +4613,25 @@
     <t xml:space="preserve">13.4305782318115</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3538331985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2195272445679</t>
+    <t xml:space="preserve">13.353832244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2195262908936</t>
   </si>
   <si>
     <t xml:space="preserve">13.1619672775269</t>
   </si>
   <si>
-    <t xml:space="preserve">13.190746307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9701023101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2578983306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0276613235474</t>
+    <t xml:space="preserve">13.1907472610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9701013565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2579002380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.027660369873</t>
   </si>
   <si>
     <t xml:space="preserve">13.1811532974243</t>
@@ -5958,6 +5958,9 @@
   </si>
   <si>
     <t xml:space="preserve">7.84000015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5</t>
   </si>
 </sst>
 </file>
@@ -39464,7 +39467,7 @@
         <v>21.3199996948242</v>
       </c>
       <c r="G1276" t="s">
-        <v>1099</v>
+        <v>709</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -39490,7 +39493,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1277" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -39516,7 +39519,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G1278" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -39542,7 +39545,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G1279" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -39568,7 +39571,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1280" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -39594,7 +39597,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G1281" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -39620,7 +39623,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1282" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -39646,7 +39649,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G1283" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -39672,7 +39675,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1284" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -39698,7 +39701,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1285" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -39724,7 +39727,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1286" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -39750,7 +39753,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G1287" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -39776,7 +39779,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G1288" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -39802,7 +39805,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G1289" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -39828,7 +39831,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1290" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -39854,7 +39857,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G1291" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -39880,7 +39883,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1292" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -39906,7 +39909,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G1293" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -39932,7 +39935,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G1294" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -39958,7 +39961,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1295" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -39984,7 +39987,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G1296" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -40010,7 +40013,7 @@
         <v>23</v>
       </c>
       <c r="G1297" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -40036,7 +40039,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1298" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -40062,7 +40065,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G1299" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -40088,7 +40091,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G1300" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -40114,7 +40117,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G1301" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -40140,7 +40143,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G1302" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -40166,7 +40169,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G1303" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -40192,7 +40195,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1304" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -40218,7 +40221,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G1305" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -40244,7 +40247,7 @@
         <v>23.5400009155273</v>
       </c>
       <c r="G1306" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -40270,7 +40273,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G1307" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -40296,7 +40299,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G1308" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -40322,7 +40325,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G1309" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -40348,7 +40351,7 @@
         <v>21.8799991607666</v>
       </c>
       <c r="G1310" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -40374,7 +40377,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1311" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -40400,7 +40403,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G1312" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -40426,7 +40429,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G1313" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -40452,7 +40455,7 @@
         <v>22.1800003051758</v>
       </c>
       <c r="G1314" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -40478,7 +40481,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1315" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -40504,7 +40507,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G1316" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -40530,7 +40533,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1317" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -40556,7 +40559,7 @@
         <v>22.8600006103516</v>
       </c>
       <c r="G1318" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -40582,7 +40585,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1319" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -40608,7 +40611,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1320" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -40634,7 +40637,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G1321" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -40660,7 +40663,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1322" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -40686,7 +40689,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G1323" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -40712,7 +40715,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1324" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -40738,7 +40741,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1325" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -40764,7 +40767,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G1326" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -40790,7 +40793,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G1327" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -40816,7 +40819,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1328" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -40842,7 +40845,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G1329" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -40868,7 +40871,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1330" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -40894,7 +40897,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G1331" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -40920,7 +40923,7 @@
         <v>24.0400009155273</v>
       </c>
       <c r="G1332" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -40946,7 +40949,7 @@
         <v>24.4400005340576</v>
       </c>
       <c r="G1333" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -40972,7 +40975,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G1334" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -40998,7 +41001,7 @@
         <v>24.0799999237061</v>
       </c>
       <c r="G1335" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -41024,7 +41027,7 @@
         <v>24</v>
       </c>
       <c r="G1336" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -41050,7 +41053,7 @@
         <v>23.8600006103516</v>
       </c>
       <c r="G1337" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -41076,7 +41079,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G1338" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -41102,7 +41105,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G1339" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -41128,7 +41131,7 @@
         <v>25.1399993896484</v>
       </c>
       <c r="G1340" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -41154,7 +41157,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G1341" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -41180,7 +41183,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1342" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -41206,7 +41209,7 @@
         <v>26.4400005340576</v>
       </c>
       <c r="G1343" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -41232,7 +41235,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1344" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -41258,7 +41261,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G1345" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -41284,7 +41287,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G1346" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -41310,7 +41313,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G1347" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -41336,7 +41339,7 @@
         <v>25.1399993896484</v>
       </c>
       <c r="G1348" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -41362,7 +41365,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G1349" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -41388,7 +41391,7 @@
         <v>25.5599994659424</v>
       </c>
       <c r="G1350" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -41414,7 +41417,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G1351" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -41440,7 +41443,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G1352" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -41466,7 +41469,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G1353" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -41492,7 +41495,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G1354" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -41518,7 +41521,7 @@
         <v>24.2199993133545</v>
       </c>
       <c r="G1355" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -41544,7 +41547,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G1356" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -41570,7 +41573,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1357" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -41596,7 +41599,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1358" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -41622,7 +41625,7 @@
         <v>25.7600002288818</v>
       </c>
       <c r="G1359" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -41648,7 +41651,7 @@
         <v>25.1800003051758</v>
       </c>
       <c r="G1360" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -41674,7 +41677,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G1361" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -41700,7 +41703,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G1362" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -41726,7 +41729,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1363" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -41752,7 +41755,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1364" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -41778,7 +41781,7 @@
         <v>29</v>
       </c>
       <c r="G1365" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -41804,7 +41807,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1366" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -41830,7 +41833,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1367" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -41856,7 +41859,7 @@
         <v>29.4400005340576</v>
       </c>
       <c r="G1368" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -41882,7 +41885,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G1369" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -41908,7 +41911,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1370" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -41934,7 +41937,7 @@
         <v>30.5200004577637</v>
       </c>
       <c r="G1371" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -41960,7 +41963,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1372" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -41986,7 +41989,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1373" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -42012,7 +42015,7 @@
         <v>29.5599994659424</v>
       </c>
       <c r="G1374" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -42038,7 +42041,7 @@
         <v>29.8799991607666</v>
       </c>
       <c r="G1375" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -42064,7 +42067,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G1376" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -42090,7 +42093,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1377" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -42116,7 +42119,7 @@
         <v>29.3799991607666</v>
       </c>
       <c r="G1378" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -42142,7 +42145,7 @@
         <v>29.1599998474121</v>
       </c>
       <c r="G1379" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -42168,7 +42171,7 @@
         <v>28.7199993133545</v>
       </c>
       <c r="G1380" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -42194,7 +42197,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1381" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -42220,7 +42223,7 @@
         <v>27.8799991607666</v>
       </c>
       <c r="G1382" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -42246,7 +42249,7 @@
         <v>28.7199993133545</v>
       </c>
       <c r="G1383" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -42272,7 +42275,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1384" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -42298,7 +42301,7 @@
         <v>28.6800003051758</v>
       </c>
       <c r="G1385" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -42324,7 +42327,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1386" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -42350,7 +42353,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G1387" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -42376,7 +42379,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G1388" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -42402,7 +42405,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G1389" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -42428,7 +42431,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G1390" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -42454,7 +42457,7 @@
         <v>27.8799991607666</v>
       </c>
       <c r="G1391" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -42480,7 +42483,7 @@
         <v>28.4599990844727</v>
       </c>
       <c r="G1392" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -42506,7 +42509,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1393" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -42532,7 +42535,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G1394" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -42558,7 +42561,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1395" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -42584,7 +42587,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G1396" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -42610,7 +42613,7 @@
         <v>28.5400009155273</v>
       </c>
       <c r="G1397" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -42636,7 +42639,7 @@
         <v>28.6800003051758</v>
       </c>
       <c r="G1398" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -42662,7 +42665,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G1399" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -42688,7 +42691,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1400" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -42714,7 +42717,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1401" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -42740,7 +42743,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G1402" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -42766,7 +42769,7 @@
         <v>28.9799995422363</v>
       </c>
       <c r="G1403" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -42792,7 +42795,7 @@
         <v>28.9599990844727</v>
       </c>
       <c r="G1404" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -42818,7 +42821,7 @@
         <v>29.0799999237061</v>
       </c>
       <c r="G1405" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -42844,7 +42847,7 @@
         <v>29</v>
       </c>
       <c r="G1406" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -42870,7 +42873,7 @@
         <v>28.6599998474121</v>
       </c>
       <c r="G1407" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -42896,7 +42899,7 @@
         <v>28.7600002288818</v>
       </c>
       <c r="G1408" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -42922,7 +42925,7 @@
         <v>27.5599994659424</v>
       </c>
       <c r="G1409" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -42948,7 +42951,7 @@
         <v>27.5</v>
       </c>
       <c r="G1410" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -42974,7 +42977,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G1411" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -43000,7 +43003,7 @@
         <v>28.8199996948242</v>
       </c>
       <c r="G1412" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -43026,7 +43029,7 @@
         <v>29.4799995422363</v>
       </c>
       <c r="G1413" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -43052,7 +43055,7 @@
         <v>29.7800006866455</v>
       </c>
       <c r="G1414" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -43078,7 +43081,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G1415" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -43104,7 +43107,7 @@
         <v>33.0200004577637</v>
       </c>
       <c r="G1416" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -43130,7 +43133,7 @@
         <v>33.560001373291</v>
       </c>
       <c r="G1417" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -43156,7 +43159,7 @@
         <v>32.0800018310547</v>
       </c>
       <c r="G1418" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -43182,7 +43185,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1419" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -43208,7 +43211,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G1420" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -43234,7 +43237,7 @@
         <v>29.6399993896484</v>
       </c>
       <c r="G1421" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -43260,7 +43263,7 @@
         <v>29.9400005340576</v>
       </c>
       <c r="G1422" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -43286,7 +43289,7 @@
         <v>29.0400009155273</v>
       </c>
       <c r="G1423" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -43312,7 +43315,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1424" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -43338,7 +43341,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G1425" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -43364,7 +43367,7 @@
         <v>30.2399997711182</v>
       </c>
       <c r="G1426" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -43390,7 +43393,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1427" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -43416,7 +43419,7 @@
         <v>29.5200004577637</v>
       </c>
       <c r="G1428" t="s">
-        <v>605</v>
+        <v>1230</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -43442,7 +43445,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1429" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -43520,7 +43523,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1432" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -44118,7 +44121,7 @@
         <v>28.6599998474121</v>
       </c>
       <c r="G1455" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -44144,7 +44147,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G1456" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -44378,7 +44381,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1465" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -44456,7 +44459,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G1468" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -44482,7 +44485,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G1469" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -44716,7 +44719,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1478" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -45106,7 +45109,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1493" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -45132,7 +45135,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1494" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -45236,7 +45239,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G1498" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -45262,7 +45265,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G1499" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -45366,7 +45369,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1503" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -45626,7 +45629,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1513" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -45704,7 +45707,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1516" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -45730,7 +45733,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G1517" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -45756,7 +45759,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G1518" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -45860,7 +45863,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G1522" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -46172,7 +46175,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1534" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -46198,7 +46201,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1535" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -46224,7 +46227,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1536" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -46250,7 +46253,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G1537" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -46432,7 +46435,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1544" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -46484,7 +46487,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G1546" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -46510,7 +46513,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1547" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -46536,7 +46539,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1548" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -46562,7 +46565,7 @@
         <v>23</v>
       </c>
       <c r="G1549" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -46588,7 +46591,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1550" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -46718,7 +46721,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G1555" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -46770,7 +46773,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1557" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -71114,7 +71117,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6493171296</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>82273</v>
@@ -71135,6 +71138,32 @@
         <v>1958</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6493287037</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>53890</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>7.59999990463257</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>7.46000003814697</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>7.46000003814697</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>1982</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2523975372314</t>
+    <t xml:space="preserve">13.2523984909058</t>
   </si>
   <si>
     <t xml:space="preserve">BSS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.978798866272</t>
+    <t xml:space="preserve">12.9788007736206</t>
   </si>
   <si>
     <t xml:space="preserve">12.7479515075684</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">12.3974046707153</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2435054779053</t>
+    <t xml:space="preserve">12.243504524231</t>
   </si>
   <si>
     <t xml:space="preserve">12.2606058120728</t>
@@ -65,28 +65,28 @@
     <t xml:space="preserve">11.4825620651245</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8584156036377</t>
+    <t xml:space="preserve">10.858416557312</t>
   </si>
   <si>
     <t xml:space="preserve">9.79822540283203</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3539705276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84952449798584</t>
+    <t xml:space="preserve">10.3539695739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84952354431152</t>
   </si>
   <si>
     <t xml:space="preserve">10.4736700057983</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2941198348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7814655303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8156661987305</t>
+    <t xml:space="preserve">10.2941207885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7814664840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8156652450562</t>
   </si>
   <si>
     <t xml:space="preserve">10.730167388916</t>
@@ -95,46 +95,46 @@
     <t xml:space="preserve">10.5762691497803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6361169815063</t>
+    <t xml:space="preserve">10.6361198425293</t>
   </si>
   <si>
     <t xml:space="preserve">10.1915225982666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4565696716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4907703399658</t>
+    <t xml:space="preserve">10.4565677642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4907693862915</t>
   </si>
   <si>
     <t xml:space="preserve">10.0205221176147</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03728008270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97743225097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40492820739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14842891693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43057727813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90082359313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66142559051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4394693374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3454217910767</t>
+    <t xml:space="preserve">9.03727912902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97743034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40492725372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14842987060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43057632446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90082263946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66142749786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4394702911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3454208374023</t>
   </si>
   <si>
     <t xml:space="preserve">10.2000713348389</t>
@@ -143,13 +143,13 @@
     <t xml:space="preserve">11.0037651062012</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5506181716919</t>
+    <t xml:space="preserve">10.5506191253662</t>
   </si>
   <si>
     <t xml:space="preserve">10.2257213592529</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1829700469971</t>
+    <t xml:space="preserve">10.1829710006714</t>
   </si>
   <si>
     <t xml:space="preserve">11.0379648208618</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">10.9097166061401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8074598312378</t>
+    <t xml:space="preserve">11.8074588775635</t>
   </si>
   <si>
     <t xml:space="preserve">11.9442586898804</t>
@@ -167,49 +167,49 @@
     <t xml:space="preserve">12.1067066192627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7732591629028</t>
+    <t xml:space="preserve">11.7732601165771</t>
   </si>
   <si>
     <t xml:space="preserve">11.9699077606201</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6279106140137</t>
+    <t xml:space="preserve">11.6279096603394</t>
   </si>
   <si>
     <t xml:space="preserve">11.3714122772217</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3799629211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6621112823486</t>
+    <t xml:space="preserve">11.3799619674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6621103286743</t>
   </si>
   <si>
     <t xml:space="preserve">11.8416595458984</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9186086654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7989101409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0468559265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1922063827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2007551193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3375558853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1323556900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1665554046631</t>
+    <t xml:space="preserve">11.918607711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7989091873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.046856880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1922073364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2007570266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3375549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1323566436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1665563583374</t>
   </si>
   <si>
     <t xml:space="preserve">12.2178554534912</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">11.9015083312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5680599212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2859134674072</t>
+    <t xml:space="preserve">11.568060874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2859144210815</t>
   </si>
   <si>
     <t xml:space="preserve">11.7390584945679</t>
@@ -230,16 +230,16 @@
     <t xml:space="preserve">11.8844089508057</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8160095214844</t>
+    <t xml:space="preserve">11.8160085678101</t>
   </si>
   <si>
     <t xml:space="preserve">11.7048597335815</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6022605895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6364593505859</t>
+    <t xml:space="preserve">11.6022615432739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6364603042603</t>
   </si>
   <si>
     <t xml:space="preserve">11.4740114212036</t>
@@ -248,67 +248,67 @@
     <t xml:space="preserve">11.1918630599976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1063661575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1149129867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3201122283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3457622528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1576633453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.055064201355</t>
+    <t xml:space="preserve">11.1063652038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1149139404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3201131820679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3457632064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1576642990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0550661087036</t>
   </si>
   <si>
     <t xml:space="preserve">10.986665725708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1405630111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.60191822052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9541397094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4346122741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3553619384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.22327709198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2673063278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92388916015625</t>
+    <t xml:space="preserve">11.1405639648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6019172668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9541425704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4346113204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3553628921509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2232789993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2673053741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92388820648193</t>
   </si>
   <si>
     <t xml:space="preserve">10.3201389312744</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0031385421753</t>
+    <t xml:space="preserve">10.003137588501</t>
   </si>
   <si>
     <t xml:space="preserve">10.3025283813477</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2496948242188</t>
+    <t xml:space="preserve">10.2496957778931</t>
   </si>
   <si>
     <t xml:space="preserve">10.6107234954834</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4120292663574</t>
+    <t xml:space="preserve">11.4120302200317</t>
   </si>
   <si>
     <t xml:space="preserve">11.1302537918091</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">11.2359199523926</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2799491882324</t>
+    <t xml:space="preserve">11.2799472808838</t>
   </si>
   <si>
     <t xml:space="preserve">11.0069751739502</t>
@@ -329,46 +329,46 @@
     <t xml:space="preserve">10.8308629989624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8396692276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9277257919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9101133346558</t>
+    <t xml:space="preserve">10.8396682739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9277238845825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9101123809814</t>
   </si>
   <si>
     <t xml:space="preserve">10.8132514953613</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5138626098633</t>
+    <t xml:space="preserve">10.513861656189</t>
   </si>
   <si>
     <t xml:space="preserve">10.0647773742676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99433326721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95030498504639</t>
+    <t xml:space="preserve">9.99433422088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95030689239502</t>
   </si>
   <si>
     <t xml:space="preserve">9.68613815307617</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0383605957031</t>
+    <t xml:space="preserve">10.0383586883545</t>
   </si>
   <si>
     <t xml:space="preserve">10.4962520599365</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3465566635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4522218704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5843067169189</t>
+    <t xml:space="preserve">10.3465557098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4522228240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5843076705933</t>
   </si>
   <si>
     <t xml:space="preserve">9.87986087799072</t>
@@ -380,73 +380,73 @@
     <t xml:space="preserve">9.67733192443848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57166576385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93269348144531</t>
+    <t xml:space="preserve">9.57166481018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93269443511963</t>
   </si>
   <si>
     <t xml:space="preserve">10.1880559921265</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98552799224854</t>
+    <t xml:space="preserve">9.98552703857422</t>
   </si>
   <si>
     <t xml:space="preserve">9.18422031402588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14019107818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72135925292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0823888778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.381778717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2849187850952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1352214813232</t>
+    <t xml:space="preserve">9.14019203186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72136116027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.082389831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3817777633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2849178314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1352224349976</t>
   </si>
   <si>
     <t xml:space="preserve">10.2144727706909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1528329849243</t>
+    <t xml:space="preserve">10.1528339385986</t>
   </si>
   <si>
     <t xml:space="preserve">10.6987800598145</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0774192810059</t>
+    <t xml:space="preserve">11.0774183273315</t>
   </si>
   <si>
     <t xml:space="preserve">11.0157804489136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0333909988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9893636703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8748903274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0950298309326</t>
+    <t xml:space="preserve">11.0333919525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9893627166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8748922348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0950317382812</t>
   </si>
   <si>
     <t xml:space="preserve">11.253529548645</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3151702880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7251968383789</t>
+    <t xml:space="preserve">11.3151712417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7251958847046</t>
   </si>
   <si>
     <t xml:space="preserve">11.0510025024414</t>
@@ -455,55 +455,55 @@
     <t xml:space="preserve">10.9013071060181</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1654748916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0598077774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2183074951172</t>
+    <t xml:space="preserve">11.1654758453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0598087310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2183084487915</t>
   </si>
   <si>
     <t xml:space="preserve">11.1214466094971</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1830854415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2623357772827</t>
+    <t xml:space="preserve">11.1830863952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2623376846313</t>
   </si>
   <si>
     <t xml:space="preserve">11.5265035629272</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7466440200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7730598449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.685004234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7994756698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6497821807861</t>
+    <t xml:space="preserve">11.7466430664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.773060798645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6850051879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7994766235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6497812271118</t>
   </si>
   <si>
     <t xml:space="preserve">11.6673927307129</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4472522735596</t>
+    <t xml:space="preserve">11.4472532272339</t>
   </si>
   <si>
     <t xml:space="preserve">11.3239755630493</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3680028915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1390581130981</t>
+    <t xml:space="preserve">11.3680038452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1390571594238</t>
   </si>
   <si>
     <t xml:space="preserve">11.6938104629517</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">12.054838180542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0636434555054</t>
+    <t xml:space="preserve">12.0636444091797</t>
   </si>
   <si>
     <t xml:space="preserve">12.5039224624634</t>
@@ -530,28 +530,28 @@
     <t xml:space="preserve">12.5303392410278</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4070606231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2837839126587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6007833480835</t>
+    <t xml:space="preserve">12.4070615768433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.283784866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6007843017578</t>
   </si>
   <si>
     <t xml:space="preserve">12.9177856445312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8121204376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8561458587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0322570800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4108972549438</t>
+    <t xml:space="preserve">12.8121185302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8561477661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0322580337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4108963012695</t>
   </si>
   <si>
     <t xml:space="preserve">13.5782041549683</t>
@@ -569,19 +569,19 @@
     <t xml:space="preserve">14.2210102081299</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2562322616577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1329545974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1241521835327</t>
+    <t xml:space="preserve">14.2562341690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1329536437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1241502761841</t>
   </si>
   <si>
     <t xml:space="preserve">14.0713157653809</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9216222763062</t>
+    <t xml:space="preserve">13.9216213226318</t>
   </si>
   <si>
     <t xml:space="preserve">13.7807321548462</t>
@@ -590,40 +590,40 @@
     <t xml:space="preserve">13.6046190261841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7631206512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8335666656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7278985977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1995649337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3756742477417</t>
+    <t xml:space="preserve">13.7631216049194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8335657119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7278995513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1995639801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.375675201416</t>
   </si>
   <si>
     <t xml:space="preserve">13.155535697937</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6486482620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5605907440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.736704826355</t>
+    <t xml:space="preserve">13.6486492156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5605926513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7367038726807</t>
   </si>
   <si>
     <t xml:space="preserve">13.8775939941406</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1769828796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0977325439453</t>
+    <t xml:space="preserve">14.1769847869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0977344512939</t>
   </si>
   <si>
     <t xml:space="preserve">14.7845697402954</t>
@@ -632,58 +632,58 @@
     <t xml:space="preserve">15.3040981292725</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2776794433594</t>
+    <t xml:space="preserve">15.2776803970337</t>
   </si>
   <si>
     <t xml:space="preserve">15.4890165328979</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4978218078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3657369613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4449872970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3393201828003</t>
+    <t xml:space="preserve">15.497820854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3657360076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4449882507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3393211364746</t>
   </si>
   <si>
     <t xml:space="preserve">15.5330419540405</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6651248931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5418453216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2424583435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8060150146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1934585571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.369571685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4664325714111</t>
+    <t xml:space="preserve">15.6651277542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5418472290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2424564361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8060159683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1934604644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3695735931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4664344787598</t>
   </si>
   <si>
     <t xml:space="preserve">16.510461807251</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0387954711914</t>
+    <t xml:space="preserve">17.03879737854</t>
   </si>
   <si>
     <t xml:space="preserve">16.889102935791</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1532707214355</t>
+    <t xml:space="preserve">17.1532669067383</t>
   </si>
   <si>
     <t xml:space="preserve">16.7746276855469</t>
@@ -692,22 +692,22 @@
     <t xml:space="preserve">16.5544891357422</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2374897003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5897121429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6513500213623</t>
+    <t xml:space="preserve">16.237491607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5897102355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6513519287109</t>
   </si>
   <si>
     <t xml:space="preserve">16.5720996856689</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9947681427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7041854858398</t>
+    <t xml:space="preserve">16.9947643280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7041835784912</t>
   </si>
   <si>
     <t xml:space="preserve">16.8802967071533</t>
@@ -716,67 +716,67 @@
     <t xml:space="preserve">16.8538780212402</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0123805999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2941589355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1268539428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5368766784668</t>
+    <t xml:space="preserve">17.012378692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2941570281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1268520355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5368804931641</t>
   </si>
   <si>
     <t xml:space="preserve">17.0828247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8626861572266</t>
+    <t xml:space="preserve">16.8626842498779</t>
   </si>
   <si>
     <t xml:space="preserve">17.2061023712158</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3469944000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6551837921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5407161712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5054912567139</t>
+    <t xml:space="preserve">17.3469924926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6551856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.540714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5054931640625</t>
   </si>
   <si>
     <t xml:space="preserve">17.7168254852295</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4526615142822</t>
+    <t xml:space="preserve">17.4526596069336</t>
   </si>
   <si>
     <t xml:space="preserve">17.5583248138428</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7432403564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8401050567627</t>
+    <t xml:space="preserve">17.7432441711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8401069641113</t>
   </si>
   <si>
     <t xml:space="preserve">17.5759353637695</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7482109069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7658271789551</t>
+    <t xml:space="preserve">16.7482128143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7658233642578</t>
   </si>
   <si>
     <t xml:space="preserve">16.9507427215576</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1620750427246</t>
+    <t xml:space="preserve">17.162073135376</t>
   </si>
   <si>
     <t xml:space="preserve">17.2765464782715</t>
@@ -785,31 +785,31 @@
     <t xml:space="preserve">16.6865749359131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1092433929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8186550140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2325210571289</t>
+    <t xml:space="preserve">17.1092414855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8186588287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2325191497803</t>
   </si>
   <si>
     <t xml:space="preserve">17.2853507995605</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3910217285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2501316070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4350433349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3734111785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6463832855225</t>
+    <t xml:space="preserve">17.391019821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2501277923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4350471496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3734092712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6463813781738</t>
   </si>
   <si>
     <t xml:space="preserve">17.9457702636719</t>
@@ -818,22 +818,22 @@
     <t xml:space="preserve">19.3722763061523</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9358329772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3849182128906</t>
+    <t xml:space="preserve">19.9358310699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3849143981934</t>
   </si>
   <si>
     <t xml:space="preserve">20.5962505340576</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3408870697021</t>
+    <t xml:space="preserve">20.3408889770508</t>
   </si>
   <si>
     <t xml:space="preserve">20.8340015411377</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0453338623047</t>
+    <t xml:space="preserve">21.0453357696533</t>
   </si>
   <si>
     <t xml:space="preserve">21.5824737548828</t>
@@ -842,19 +842,19 @@
     <t xml:space="preserve">21.0893650054932</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3271141052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6529178619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7497806549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9170894622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8114204406738</t>
+    <t xml:space="preserve">21.327112197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6529197692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7497844696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9170875549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8114223480225</t>
   </si>
   <si>
     <t xml:space="preserve">22.0139503479004</t>
@@ -872,13 +872,13 @@
     <t xml:space="preserve">22.3221454620361</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1900596618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6303405761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4366149902344</t>
+    <t xml:space="preserve">22.1900634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6303424835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.436616897583</t>
   </si>
   <si>
     <t xml:space="preserve">22.4806461334229</t>
@@ -890,19 +890,19 @@
     <t xml:space="preserve">22.6215343475342</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6743659973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8945045471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.097038269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8328666687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.374979019165</t>
+    <t xml:space="preserve">22.6743679046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8945064544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0970363616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8328685760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3749771118164</t>
   </si>
   <si>
     <t xml:space="preserve">23.1938972473145</t>
@@ -911,28 +911,28 @@
     <t xml:space="preserve">23.3876209259033</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5108985900879</t>
+    <t xml:space="preserve">23.5109004974365</t>
   </si>
   <si>
     <t xml:space="preserve">23.9159545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2417621612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7084541320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6556224822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.919792175293</t>
+    <t xml:space="preserve">24.2417602539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7084579467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6556243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9197902679443</t>
   </si>
   <si>
     <t xml:space="preserve">25.0870971679688</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9638195037842</t>
+    <t xml:space="preserve">24.9638214111328</t>
   </si>
   <si>
     <t xml:space="preserve">24.8933734893799</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">27.6287326812744</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1545677185059</t>
+    <t xml:space="preserve">28.1545715332031</t>
   </si>
   <si>
     <t xml:space="preserve">27.6732940673828</t>
@@ -971,100 +971,100 @@
     <t xml:space="preserve">29.0190830230713</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4914455413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7677345275879</t>
+    <t xml:space="preserve">29.4914417266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7677307128906</t>
   </si>
   <si>
     <t xml:space="preserve">29.8746795654297</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3024826049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7748394012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2400970458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6678924560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8283157348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8996162414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0154800415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9976539611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9352645874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6500644683838</t>
+    <t xml:space="preserve">30.3024787902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7748413085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2400951385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6678886413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8283195495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8996143341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0154781341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9976577758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9352626800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6500663757324</t>
   </si>
   <si>
     <t xml:space="preserve">30.748104095459</t>
   </si>
   <si>
-    <t xml:space="preserve">30.685718536377</t>
+    <t xml:space="preserve">30.6857166290283</t>
   </si>
   <si>
     <t xml:space="preserve">29.3577556610107</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5003509521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3131904602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2775402069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1687908172607</t>
+    <t xml:space="preserve">29.5003528594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3131942749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2775440216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.168794631958</t>
   </si>
   <si>
     <t xml:space="preserve">30.1331424713135</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9994564056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9281578063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0529346466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4825325012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.812292098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.912130355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1260318756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7713317871094</t>
+    <t xml:space="preserve">29.999454498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9281597137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0529308319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4825305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8122940063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9121322631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.126033782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.771333694458</t>
   </si>
   <si>
     <t xml:space="preserve">27.9674053192139</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2544078826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6911182403564</t>
+    <t xml:space="preserve">27.2544059753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6911201477051</t>
   </si>
   <si>
     <t xml:space="preserve">27.4861335754395</t>
@@ -1073,109 +1073,109 @@
     <t xml:space="preserve">27.5752582550049</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1189193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3506412506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7178573608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5734558105469</t>
+    <t xml:space="preserve">28.11891746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.350643157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7178554534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5734596252441</t>
   </si>
   <si>
     <t xml:space="preserve">28.6180191040039</t>
   </si>
   <si>
-    <t xml:space="preserve">28.519983291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7873554229736</t>
+    <t xml:space="preserve">28.5199794769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.787353515625</t>
   </si>
   <si>
     <t xml:space="preserve">29.7855529785156</t>
   </si>
   <si>
-    <t xml:space="preserve">29.536003112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3310203552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1705932617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2329807281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.143856048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3221073150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9656066894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7071418762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9923458099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9477806091309</t>
+    <t xml:space="preserve">29.5360050201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.331018447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1705913543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2329788208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1438541412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3221054077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9656047821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7071437835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9923419952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9477787017822</t>
   </si>
   <si>
     <t xml:space="preserve">29.6073093414307</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8568572998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4023189544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4112339019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8140964508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.687520980835</t>
+    <t xml:space="preserve">29.8568534851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4023208618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4112319946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.814094543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6875190734863</t>
   </si>
   <si>
     <t xml:space="preserve">29.6162166595459</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6786041259766</t>
+    <t xml:space="preserve">29.6786060333252</t>
   </si>
   <si>
     <t xml:space="preserve">29.6964302062988</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1420593261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8390293121338</t>
+    <t xml:space="preserve">30.1420574188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8390312194824</t>
   </si>
   <si>
     <t xml:space="preserve">30.186616897583</t>
   </si>
   <si>
-    <t xml:space="preserve">29.518180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1795063018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.437967300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3648719787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4629077911377</t>
+    <t xml:space="preserve">29.5181789398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1795120239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4379692077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3648681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4629096984863</t>
   </si>
   <si>
     <t xml:space="preserve">30.4718170166016</t>
@@ -1184,22 +1184,22 @@
     <t xml:space="preserve">30.2935657501221</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0974941253662</t>
+    <t xml:space="preserve">30.0974903106689</t>
   </si>
   <si>
     <t xml:space="preserve">30.0618419647217</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2311763763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0849838256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4967555999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8194046020508</t>
+    <t xml:space="preserve">30.2311820983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0849800109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4967498779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8194103240967</t>
   </si>
   <si>
     <t xml:space="preserve">31.9958515167236</t>
@@ -1208,25 +1208,25 @@
     <t xml:space="preserve">31.773042678833</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6928272247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1830177307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0760688781738</t>
+    <t xml:space="preserve">31.6928329467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1830215454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0760726928711</t>
   </si>
   <si>
     <t xml:space="preserve">31.9512920379639</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3077926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1990394592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3951148986816</t>
+    <t xml:space="preserve">32.307788848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1990432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3951187133789</t>
   </si>
   <si>
     <t xml:space="preserve">34.7587280273438</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">34.6963386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">34.731990814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5804748535156</t>
+    <t xml:space="preserve">34.7319946289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5804786682129</t>
   </si>
   <si>
     <t xml:space="preserve">34.2239799499512</t>
@@ -1250,13 +1250,13 @@
     <t xml:space="preserve">34.5448265075684</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4271659851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2221755981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6606903076172</t>
+    <t xml:space="preserve">35.4271697998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2221794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6606864929199</t>
   </si>
   <si>
     <t xml:space="preserve">34.37548828125</t>
@@ -1268,13 +1268,13 @@
     <t xml:space="preserve">33.8496513366699</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1437644958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7159652709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.063549041748</t>
+    <t xml:space="preserve">34.1437683105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7159690856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0635566711426</t>
   </si>
   <si>
     <t xml:space="preserve">34.313102722168</t>
@@ -1289,46 +1289,46 @@
     <t xml:space="preserve">34.7765502929688</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6161308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3041915893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1081161499023</t>
+    <t xml:space="preserve">34.6161270141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3041954040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1081123352051</t>
   </si>
   <si>
     <t xml:space="preserve">32.8425407409668</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0902900695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.106315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2471084594727</t>
+    <t xml:space="preserve">34.0902938842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1063194274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2471122741699</t>
   </si>
   <si>
     <t xml:space="preserve">36.3005867004395</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1847267150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4966621398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4146537780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8584785461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9208641052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6178436279297</t>
+    <t xml:space="preserve">36.1847305297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4966659545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4146499633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8584747314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9208602905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6178398132324</t>
   </si>
   <si>
     <t xml:space="preserve">38.5821876525879</t>
@@ -1340,25 +1340,25 @@
     <t xml:space="preserve">38.4306755065918</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2149772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.805004119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8067970275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3504676818848</t>
+    <t xml:space="preserve">39.214973449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8050003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8068008422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3504638671875</t>
   </si>
   <si>
     <t xml:space="preserve">38.0563545227051</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3682861328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.341552734375</t>
+    <t xml:space="preserve">38.3682899475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3415565490723</t>
   </si>
   <si>
     <t xml:space="preserve">38.5198020935059</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">38.6089286804199</t>
   </si>
   <si>
-    <t xml:space="preserve">38.689136505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.733699798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4377861022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0812873840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0545539855957</t>
+    <t xml:space="preserve">38.6891403198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7336959838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4377822875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0812835693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0545501708984</t>
   </si>
   <si>
     <t xml:space="preserve">39.3219223022461</t>
@@ -1391,58 +1391,58 @@
     <t xml:space="preserve">38.5554504394531</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2880744934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.377197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6998519897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6125297546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6820259094238</t>
+    <t xml:space="preserve">38.2880783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3772048950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6998481750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6125259399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6820220947266</t>
   </si>
   <si>
     <t xml:space="preserve">38.4663238525391</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9956703186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6551971435547</t>
+    <t xml:space="preserve">41.9956665039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.655200958252</t>
   </si>
   <si>
     <t xml:space="preserve">42.8156242370605</t>
   </si>
   <si>
-    <t xml:space="preserve">42.423469543457</t>
+    <t xml:space="preserve">42.4234733581543</t>
   </si>
   <si>
     <t xml:space="preserve">42.031322479248</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0848007202148</t>
+    <t xml:space="preserve">42.0847969055176</t>
   </si>
   <si>
     <t xml:space="preserve">41.924373626709</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6213455200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7639465332031</t>
+    <t xml:space="preserve">41.6213531494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7639503479004</t>
   </si>
   <si>
     <t xml:space="preserve">42.1382713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6926460266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5322189331055</t>
+    <t xml:space="preserve">41.6926498413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5322227478027</t>
   </si>
   <si>
     <t xml:space="preserve">41.7817726135254</t>
@@ -1457,43 +1457,43 @@
     <t xml:space="preserve">40.3557739257812</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5874977111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8031959533691</t>
+    <t xml:space="preserve">40.5875015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8031997680664</t>
   </si>
   <si>
     <t xml:space="preserve">39.1436767578125</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6784248352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.779972076416</t>
+    <t xml:space="preserve">39.6784286499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7799682617188</t>
   </si>
   <si>
     <t xml:space="preserve">41.4787483215332</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6802291870117</t>
+    <t xml:space="preserve">38.6802253723145</t>
   </si>
   <si>
     <t xml:space="preserve">37.5750770568848</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2898712158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5893020629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1953506469727</t>
+    <t xml:space="preserve">37.2898788452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5892944335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1953544616699</t>
   </si>
   <si>
     <t xml:space="preserve">40.1062240600586</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5696716308594</t>
+    <t xml:space="preserve">40.5696754455566</t>
   </si>
   <si>
     <t xml:space="preserve">40.801399230957</t>
@@ -1505,16 +1505,16 @@
     <t xml:space="preserve">41.1400718688965</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9974746704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5161972045898</t>
+    <t xml:space="preserve">40.9974784851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5162048339844</t>
   </si>
   <si>
     <t xml:space="preserve">40.9618225097656</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2506294250488</t>
+    <t xml:space="preserve">39.2506256103516</t>
   </si>
   <si>
     <t xml:space="preserve">39.1793251037598</t>
@@ -1523,16 +1523,16 @@
     <t xml:space="preserve">40.2131767272949</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3914260864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3896179199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6017189025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.5446434020996</t>
+    <t xml:space="preserve">40.3914184570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3896217346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6017265319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.5446472167969</t>
   </si>
   <si>
     <t xml:space="preserve">43.902946472168</t>
@@ -1541,13 +1541,13 @@
     <t xml:space="preserve">45.2309074401855</t>
   </si>
   <si>
-    <t xml:space="preserve">43.885124206543</t>
+    <t xml:space="preserve">43.8851203918457</t>
   </si>
   <si>
     <t xml:space="preserve">44.9635353088379</t>
   </si>
   <si>
-    <t xml:space="preserve">46.033031463623</t>
+    <t xml:space="preserve">46.0330352783203</t>
   </si>
   <si>
     <t xml:space="preserve">47.3253440856934</t>
@@ -1556,31 +1556,31 @@
     <t xml:space="preserve">45.9439086914062</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5874099731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.696159362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.009895324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8494720458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9582214355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4609222412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1757164001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.157901763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0153007507324</t>
+    <t xml:space="preserve">45.5874061584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6961555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0098991394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8494758605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9582252502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4609184265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.175724029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1578979492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0152969360352</t>
   </si>
   <si>
     <t xml:space="preserve">39.7675514221191</t>
@@ -1589,61 +1589,61 @@
     <t xml:space="preserve">39.108024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7479209899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7853775024414</t>
+    <t xml:space="preserve">40.7479248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7853736877441</t>
   </si>
   <si>
     <t xml:space="preserve">40.5518493652344</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7319030761719</t>
+    <t xml:space="preserve">39.7318992614746</t>
   </si>
   <si>
     <t xml:space="preserve">39.3041000366211</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2488212585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9101524353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4288787841797</t>
+    <t xml:space="preserve">40.2488288879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9101448059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4288749694824</t>
   </si>
   <si>
     <t xml:space="preserve">39.0367240905762</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3878211975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0509452819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9335746765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0149230957031</t>
+    <t xml:space="preserve">42.387825012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0509567260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9335708618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0149269104004</t>
   </si>
   <si>
     <t xml:space="preserve">40.7087135314941</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6366577148438</t>
+    <t xml:space="preserve">40.6366539001465</t>
   </si>
   <si>
     <t xml:space="preserve">40.5285797119141</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8441009521484</t>
+    <t xml:space="preserve">39.8440971374512</t>
   </si>
   <si>
     <t xml:space="preserve">37.7366142272949</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4844360351562</t>
+    <t xml:space="preserve">37.484432220459</t>
   </si>
   <si>
     <t xml:space="preserve">36.3316230773926</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">37.0521278381348</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4757270812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6018104553223</t>
+    <t xml:space="preserve">36.4757232666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6018142700195</t>
   </si>
   <si>
     <t xml:space="preserve">36.0073928833008</t>
@@ -1664,10 +1664,10 @@
     <t xml:space="preserve">35.6651496887207</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3589363098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2241363525391</t>
+    <t xml:space="preserve">35.3589324951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2241287231445</t>
   </si>
   <si>
     <t xml:space="preserve">33.4135589599609</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">33.6657409667969</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8818969726562</t>
+    <t xml:space="preserve">33.881893157959</t>
   </si>
   <si>
     <t xml:space="preserve">34.4763069152832</t>
@@ -1685,10 +1685,10 @@
     <t xml:space="preserve">34.6924705505371</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1427879333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7284927368164</t>
+    <t xml:space="preserve">35.1427803039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7284889221191</t>
   </si>
   <si>
     <t xml:space="preserve">34.5483627319336</t>
@@ -1697,25 +1697,25 @@
     <t xml:space="preserve">33.9899711608887</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8278579711914</t>
+    <t xml:space="preserve">33.8278541564941</t>
   </si>
   <si>
     <t xml:space="preserve">34.4402885437012</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1247711181641</t>
+    <t xml:space="preserve">35.1247673034668</t>
   </si>
   <si>
     <t xml:space="preserve">33.5036277770996</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4048538208008</t>
+    <t xml:space="preserve">32.404857635498</t>
   </si>
   <si>
     <t xml:space="preserve">32.3868370056152</t>
   </si>
   <si>
-    <t xml:space="preserve">31.468189239502</t>
+    <t xml:space="preserve">31.4681873321533</t>
   </si>
   <si>
     <t xml:space="preserve">31.7744083404541</t>
@@ -1724,19 +1724,19 @@
     <t xml:space="preserve">30.5315322875977</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4867973327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9371128082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2346134185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1532649993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2166061401367</t>
+    <t xml:space="preserve">29.486795425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9371109008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2346153259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1532669067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2166042327881</t>
   </si>
   <si>
     <t xml:space="preserve">29.4147434234619</t>
@@ -1766,25 +1766,25 @@
     <t xml:space="preserve">30.1172351837158</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4054393768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.666332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6483154296875</t>
+    <t xml:space="preserve">30.4054412841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6663341522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6483173370361</t>
   </si>
   <si>
     <t xml:space="preserve">32.080623626709</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1079406738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3601169586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9818515777588</t>
+    <t xml:space="preserve">31.1079387664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3601150512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9818496704102</t>
   </si>
   <si>
     <t xml:space="preserve">31.7383823394775</t>
@@ -1793,10 +1793,10 @@
     <t xml:space="preserve">31.6122932434082</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8377513885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9191017150879</t>
+    <t xml:space="preserve">30.8377494812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9190998077393</t>
   </si>
   <si>
     <t xml:space="preserve">29.901086807251</t>
@@ -1811,22 +1811,22 @@
     <t xml:space="preserve">28.730260848999</t>
   </si>
   <si>
-    <t xml:space="preserve">28.099817276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.595458984375</t>
+    <t xml:space="preserve">28.0998153686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5954608917236</t>
   </si>
   <si>
     <t xml:space="preserve">26.6407871246338</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2805328369141</t>
+    <t xml:space="preserve">26.2805347442627</t>
   </si>
   <si>
     <t xml:space="preserve">26.0463676452637</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5146980285645</t>
+    <t xml:space="preserve">26.5146999359131</t>
   </si>
   <si>
     <t xml:space="preserve">27.2352066040039</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">27.4693737030029</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9196891784668</t>
+    <t xml:space="preserve">27.9196910858154</t>
   </si>
   <si>
     <t xml:space="preserve">27.577449798584</t>
@@ -1856,16 +1856,16 @@
     <t xml:space="preserve">27.9377021789551</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8476390838623</t>
+    <t xml:space="preserve">27.8476371765137</t>
   </si>
   <si>
     <t xml:space="preserve">27.7936000823975</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0457801818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0097541809082</t>
+    <t xml:space="preserve">28.0457782745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0097522735596</t>
   </si>
   <si>
     <t xml:space="preserve">27.7755889892578</t>
@@ -1880,22 +1880,22 @@
     <t xml:space="preserve">29.1805820465088</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1625690460205</t>
+    <t xml:space="preserve">29.1625671386719</t>
   </si>
   <si>
     <t xml:space="preserve">28.6401958465576</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6762237548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6675090789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.451358795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5594367980957</t>
+    <t xml:space="preserve">28.6762218475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6675109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4513568878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5594348907471</t>
   </si>
   <si>
     <t xml:space="preserve">25.7581653594971</t>
@@ -1904,25 +1904,25 @@
     <t xml:space="preserve">22.7320289611816</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7413330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7233219146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7860679626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4165134429932</t>
+    <t xml:space="preserve">21.7413311004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7233200073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7860698699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4165153503418</t>
   </si>
   <si>
     <t xml:space="preserve">23.7047176361084</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5606136322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.236385345459</t>
+    <t xml:space="preserve">23.5606155395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2363872528076</t>
   </si>
   <si>
     <t xml:space="preserve">23.4345264434814</t>
@@ -1931,7 +1931,7 @@
     <t xml:space="preserve">22.5158786773682</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7053070068359</t>
+    <t xml:space="preserve">21.7053089141846</t>
   </si>
   <si>
     <t xml:space="preserve">20.8226852416992</t>
@@ -1952,13 +1952,13 @@
     <t xml:space="preserve">19.7239093780518</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3189182281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2828941345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5437831878662</t>
+    <t xml:space="preserve">18.318920135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2828922271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5437850952148</t>
   </si>
   <si>
     <t xml:space="preserve">18.8773097991943</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">18.3909683227539</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0034027099609</t>
+    <t xml:space="preserve">19.0034008026123</t>
   </si>
   <si>
     <t xml:space="preserve">18.0036964416504</t>
@@ -1976,46 +1976,46 @@
     <t xml:space="preserve">17.139087677002</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1120681762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.265172958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.661750793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2024269104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9502477645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.716082572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6800584793091</t>
+    <t xml:space="preserve">17.1120643615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2651748657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6617527008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.202428817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.950249671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7160835266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6800575256348</t>
   </si>
   <si>
     <t xml:space="preserve">15.6170129776001</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1573944091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6077136993408</t>
+    <t xml:space="preserve">16.1573963165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6077117919922</t>
   </si>
   <si>
     <t xml:space="preserve">16.4005680084229</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4723205566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5533790588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.490629196167</t>
+    <t xml:space="preserve">17.4723224639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5533771514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4906311035156</t>
   </si>
   <si>
     <t xml:space="preserve">17.9406509399414</t>
@@ -2027,31 +2027,31 @@
     <t xml:space="preserve">17.6614570617676</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7968444824219</t>
+    <t xml:space="preserve">16.7968463897705</t>
   </si>
   <si>
     <t xml:space="preserve">16.0132942199707</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9052171707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2654685974121</t>
+    <t xml:space="preserve">15.905216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2654705047607</t>
   </si>
   <si>
     <t xml:space="preserve">16.1934185028076</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7250881195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4008626937866</t>
+    <t xml:space="preserve">15.7250890731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4008617401123</t>
   </si>
   <si>
     <t xml:space="preserve">15.0496120452881</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7524032592773</t>
+    <t xml:space="preserve">14.7524042129517</t>
   </si>
   <si>
     <t xml:space="preserve">15.5899925231934</t>
@@ -2063,10 +2063,10 @@
     <t xml:space="preserve">15.4639043807983</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1661071777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7875423431396</t>
+    <t xml:space="preserve">17.1661052703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7875442504883</t>
   </si>
   <si>
     <t xml:space="preserve">18.1568050384521</t>
@@ -2078,22 +2078,22 @@
     <t xml:space="preserve">17.391263961792</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0127048492432</t>
+    <t xml:space="preserve">18.0127029418945</t>
   </si>
   <si>
     <t xml:space="preserve">18.0487270355225</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2288551330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0307159423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9226379394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4543075561523</t>
+    <t xml:space="preserve">18.228853225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0307140350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9226398468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.454309463501</t>
   </si>
   <si>
     <t xml:space="preserve">18.6791706085205</t>
@@ -2120,10 +2120,10 @@
     <t xml:space="preserve">18.3549423217773</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4269943237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9856815338135</t>
+    <t xml:space="preserve">18.4269962310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9856834411621</t>
   </si>
   <si>
     <t xml:space="preserve">17.3552398681641</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">17.7245006561279</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3009052276611</t>
+    <t xml:space="preserve">18.3009071350098</t>
   </si>
   <si>
     <t xml:space="preserve">18.6071224212646</t>
@@ -2147,13 +2147,13 @@
     <t xml:space="preserve">20.2462768554688</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0661506652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9220504760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4176940917969</t>
+    <t xml:space="preserve">20.0661544799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9220485687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4176959991455</t>
   </si>
   <si>
     <t xml:space="preserve">19.4537181854248</t>
@@ -2165,31 +2165,31 @@
     <t xml:space="preserve">17.7515182495117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7425136566162</t>
+    <t xml:space="preserve">17.7425117492676</t>
   </si>
   <si>
     <t xml:space="preserve">17.7965507507324</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5083446502686</t>
+    <t xml:space="preserve">17.5083465576172</t>
   </si>
   <si>
     <t xml:space="preserve">17.4182815551758</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8508834838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9859790802002</t>
+    <t xml:space="preserve">16.8508815765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9859809875488</t>
   </si>
   <si>
     <t xml:space="preserve">16.868896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0490245819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9409484863281</t>
+    <t xml:space="preserve">17.0490226745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9409465789795</t>
   </si>
   <si>
     <t xml:space="preserve">17.3462352752686</t>
@@ -2201,19 +2201,19 @@
     <t xml:space="preserve">17.3822574615479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2831859588623</t>
+    <t xml:space="preserve">17.2831878662109</t>
   </si>
   <si>
     <t xml:space="preserve">18.1748180389404</t>
   </si>
   <si>
-    <t xml:space="preserve">17.976676940918</t>
+    <t xml:space="preserve">17.9766788482666</t>
   </si>
   <si>
     <t xml:space="preserve">17.6164245605469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4272899627686</t>
+    <t xml:space="preserve">17.4272880554199</t>
   </si>
   <si>
     <t xml:space="preserve">18.1387901306152</t>
@@ -2222,13 +2222,13 @@
     <t xml:space="preserve">17.9136295318604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6974811553955</t>
+    <t xml:space="preserve">17.6974792480469</t>
   </si>
   <si>
     <t xml:space="preserve">18.1928291320801</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9496574401855</t>
+    <t xml:space="preserve">17.9496593475342</t>
   </si>
   <si>
     <t xml:space="preserve">17.2381534576416</t>
@@ -2237,10 +2237,10 @@
     <t xml:space="preserve">17.1300811767578</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6794681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9676704406738</t>
+    <t xml:space="preserve">17.6794662475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9676723480225</t>
   </si>
   <si>
     <t xml:space="preserve">18.084753036499</t>
@@ -2252,40 +2252,40 @@
     <t xml:space="preserve">17.8686008453369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5173530578613</t>
+    <t xml:space="preserve">17.51735496521</t>
   </si>
   <si>
     <t xml:space="preserve">17.6074180603027</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5894069671631</t>
+    <t xml:space="preserve">17.5894050598145</t>
   </si>
   <si>
     <t xml:space="preserve">17.76953125</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6365566253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.24342918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6621894836426</t>
+    <t xml:space="preserve">18.6365585327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2434272766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6621875762939</t>
   </si>
   <si>
     <t xml:space="preserve">17.2249755859375</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5330238342285</t>
+    <t xml:space="preserve">16.5330257415771</t>
   </si>
   <si>
     <t xml:space="preserve">16.1916618347168</t>
   </si>
   <si>
-    <t xml:space="preserve">15.684229850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6232404708862</t>
+    <t xml:space="preserve">15.6842317581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6232395172119</t>
   </si>
   <si>
     <t xml:space="preserve">13.8021240234375</t>
@@ -2294,13 +2294,13 @@
     <t xml:space="preserve">13.9405136108398</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7836723327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3131446838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8943843841553</t>
+    <t xml:space="preserve">13.7836713790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3131456375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.894383430481</t>
   </si>
   <si>
     <t xml:space="preserve">13.8390283584595</t>
@@ -2312,52 +2312,52 @@
     <t xml:space="preserve">12.9533309936523</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0732688903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0179119110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.303918838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3777284622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1009464263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1378507614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.922061920166</t>
+    <t xml:space="preserve">13.0732679367065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0179128646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3039197921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3777275085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1009473800659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1378498077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9220628738403</t>
   </si>
   <si>
     <t xml:space="preserve">13.7006378173828</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4756231307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4202671051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5771112442017</t>
+    <t xml:space="preserve">14.4756240844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4202680587769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5771102905273</t>
   </si>
   <si>
     <t xml:space="preserve">13.8298015594482</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7928991317749</t>
+    <t xml:space="preserve">13.7928981781006</t>
   </si>
   <si>
     <t xml:space="preserve">13.6914119720459</t>
   </si>
   <si>
-    <t xml:space="preserve">14.512526512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1803913116455</t>
+    <t xml:space="preserve">14.5125274658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1803903579712</t>
   </si>
   <si>
     <t xml:space="preserve">11.0988998413086</t>
@@ -2366,10 +2366,10 @@
     <t xml:space="preserve">10.7575378417969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1486206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2132034301758</t>
+    <t xml:space="preserve">10.1486215591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2132024765015</t>
   </si>
   <si>
     <t xml:space="preserve">10.4069490432739</t>
@@ -2378,10 +2378,10 @@
     <t xml:space="preserve">10.4161758422852</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5914688110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8590259552002</t>
+    <t xml:space="preserve">10.5914697647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8590250015259</t>
   </si>
   <si>
     <t xml:space="preserve">10.9236068725586</t>
@@ -2393,13 +2393,13 @@
     <t xml:space="preserve">10.6837291717529</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5361137390137</t>
+    <t xml:space="preserve">10.5361127853394</t>
   </si>
   <si>
     <t xml:space="preserve">10.2962369918823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3700437545776</t>
+    <t xml:space="preserve">10.370044708252</t>
   </si>
   <si>
     <t xml:space="preserve">10.0471353530884</t>
@@ -2414,10 +2414,10 @@
     <t xml:space="preserve">9.65964221954346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53047657012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0932636260986</t>
+    <t xml:space="preserve">9.53047752380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0932645797729</t>
   </si>
   <si>
     <t xml:space="preserve">10.4899835586548</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">10.5730171203613</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4254016876221</t>
+    <t xml:space="preserve">10.4254007339478</t>
   </si>
   <si>
     <t xml:space="preserve">10.5176601409912</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">10.3054628372192</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4438533782959</t>
+    <t xml:space="preserve">10.4438524246216</t>
   </si>
   <si>
     <t xml:space="preserve">10.6652774810791</t>
@@ -2444,16 +2444,16 @@
     <t xml:space="preserve">10.0286827087402</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9640998840332</t>
+    <t xml:space="preserve">9.96410083770752</t>
   </si>
   <si>
     <t xml:space="preserve">10.056360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">10.120943069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50279903411865</t>
+    <t xml:space="preserve">10.1209421157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50279998779297</t>
   </si>
   <si>
     <t xml:space="preserve">9.29060077667236</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">9.5766077041626</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21217823028564</t>
+    <t xml:space="preserve">9.21218013763428</t>
   </si>
   <si>
     <t xml:space="preserve">9.40131282806396</t>
@@ -2474,34 +2474,34 @@
     <t xml:space="preserve">9.47512149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20295333862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94001293182373</t>
+    <t xml:space="preserve">9.20295429229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94001197814941</t>
   </si>
   <si>
     <t xml:space="preserve">8.9861421585083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88004398345947</t>
+    <t xml:space="preserve">8.88004302978516</t>
   </si>
   <si>
     <t xml:space="preserve">9.53970336914062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24447154998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28137493133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11530590057373</t>
+    <t xml:space="preserve">9.24447059631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28137588500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11530685424805</t>
   </si>
   <si>
     <t xml:space="preserve">9.88106536865234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97332668304443</t>
+    <t xml:space="preserve">9.97332572937012</t>
   </si>
   <si>
     <t xml:space="preserve">9.99177837371826</t>
@@ -2510,16 +2510,16 @@
     <t xml:space="preserve">10.2408809661865</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4346284866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.084038734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1024894714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61351203918457</t>
+    <t xml:space="preserve">10.434627532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0840396881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1024904251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61351108551025</t>
   </si>
   <si>
     <t xml:space="preserve">9.66886615753174</t>
@@ -2528,10 +2528,10 @@
     <t xml:space="preserve">9.5212516784668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79803276062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56738185882568</t>
+    <t xml:space="preserve">9.7980318069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56738090515137</t>
   </si>
   <si>
     <t xml:space="preserve">9.2629222869873</t>
@@ -2540,25 +2540,25 @@
     <t xml:space="preserve">9.39208698272705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65041637420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31827831268311</t>
+    <t xml:space="preserve">9.65041542053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31827926635742</t>
   </si>
   <si>
     <t xml:space="preserve">9.71499729156494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81648445129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68731880187988</t>
+    <t xml:space="preserve">9.81648349761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6873197555542</t>
   </si>
   <si>
     <t xml:space="preserve">9.98255252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75190258026123</t>
+    <t xml:space="preserve">9.7519006729126</t>
   </si>
   <si>
     <t xml:space="preserve">9.49357318878174</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">10.7298593521118</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2870101928711</t>
+    <t xml:space="preserve">10.2870111465454</t>
   </si>
   <si>
     <t xml:space="preserve">10.5084362030029</t>
@@ -2585,55 +2585,55 @@
     <t xml:space="preserve">10.3515939712524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.431037902832</t>
+    <t xml:space="preserve">11.4310369491577</t>
   </si>
   <si>
     <t xml:space="preserve">11.6340093612671</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2337007522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9938230514526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1322135925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0860843658447</t>
+    <t xml:space="preserve">12.2337017059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.993824005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1322145462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.086085319519</t>
   </si>
   <si>
     <t xml:space="preserve">12.1414403915405</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1875705718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9661474227905</t>
+    <t xml:space="preserve">12.1875715255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9661464691162</t>
   </si>
   <si>
     <t xml:space="preserve">11.9569206237793</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7539482116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8277559280396</t>
+    <t xml:space="preserve">11.7539472579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8277568817139</t>
   </si>
   <si>
     <t xml:space="preserve">11.7354965209961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0676326751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4551248550415</t>
+    <t xml:space="preserve">12.0676317214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4551258087158</t>
   </si>
   <si>
     <t xml:space="preserve">13.2577886581421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2485628128052</t>
+    <t xml:space="preserve">13.2485637664795</t>
   </si>
   <si>
     <t xml:space="preserve">13.0824947357178</t>
@@ -2642,16 +2642,16 @@
     <t xml:space="preserve">13.5991516113281</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4054040908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2024326324463</t>
+    <t xml:space="preserve">13.4054050445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2024335861206</t>
   </si>
   <si>
     <t xml:space="preserve">13.7559938430786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7098627090454</t>
+    <t xml:space="preserve">13.7098636627197</t>
   </si>
   <si>
     <t xml:space="preserve">13.7744464874268</t>
@@ -2663,19 +2663,19 @@
     <t xml:space="preserve">13.7190895080566</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7283153533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0143222808838</t>
+    <t xml:space="preserve">13.7283163070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0143232345581</t>
   </si>
   <si>
     <t xml:space="preserve">14.1342601776123</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1250343322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9497413635254</t>
+    <t xml:space="preserve">14.1250352859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9497404098511</t>
   </si>
   <si>
     <t xml:space="preserve">13.6637344360352</t>
@@ -2684,13 +2684,13 @@
     <t xml:space="preserve">13.6821851730347</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4571714401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1158084869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8482542037964</t>
+    <t xml:space="preserve">14.4571704864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1158094406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8482532501221</t>
   </si>
   <si>
     <t xml:space="preserve">14.0512256622314</t>
@@ -2699,13 +2699,13 @@
     <t xml:space="preserve">14.0327739715576</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9312887191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6473264694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7303609848022</t>
+    <t xml:space="preserve">13.9312896728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6473274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7303619384766</t>
   </si>
   <si>
     <t xml:space="preserve">17.0865859985352</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">16.7913551330566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8651638031006</t>
+    <t xml:space="preserve">16.865161895752</t>
   </si>
   <si>
     <t xml:space="preserve">16.7452239990234</t>
@@ -2723,28 +2723,28 @@
     <t xml:space="preserve">16.8190307617188</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1086254119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.997917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9333333969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4720325469971</t>
+    <t xml:space="preserve">16.1086273193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9979162216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9333362579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4720344543457</t>
   </si>
   <si>
     <t xml:space="preserve">14.6785955429077</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3187808990479</t>
+    <t xml:space="preserve">14.3187818527222</t>
   </si>
   <si>
     <t xml:space="preserve">14.8446645736694</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2967386245728</t>
+    <t xml:space="preserve">15.2967395782471</t>
   </si>
   <si>
     <t xml:space="preserve">15.2044792175293</t>
@@ -2753,37 +2753,37 @@
     <t xml:space="preserve">14.7247257232666</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8538913726807</t>
+    <t xml:space="preserve">14.8538904190063</t>
   </si>
   <si>
     <t xml:space="preserve">15.1491222381592</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2506103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9830532073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1583480834961</t>
+    <t xml:space="preserve">15.2506113052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9830541610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1583490371704</t>
   </si>
   <si>
     <t xml:space="preserve">15.0753154754639</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1065816879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6027412414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0399541854858</t>
+    <t xml:space="preserve">14.1065826416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6027421951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0399551391602</t>
   </si>
   <si>
     <t xml:space="preserve">11.9753723144531</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5878791809082</t>
+    <t xml:space="preserve">11.5878801345825</t>
   </si>
   <si>
     <t xml:space="preserve">11.301872253418</t>
@@ -2804,10 +2804,10 @@
     <t xml:space="preserve">7.97589445114136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8928599357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5504732131958</t>
+    <t xml:space="preserve">7.89285945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55047369003296</t>
   </si>
   <si>
     <t xml:space="preserve">6.93796634674072</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">6.98409652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91028738021851</t>
+    <t xml:space="preserve">6.91028785705566</t>
   </si>
   <si>
     <t xml:space="preserve">7.01177453994751</t>
@@ -2828,28 +2828,28 @@
     <t xml:space="preserve">7.47307586669922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05431270599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85697746276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33673191070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01382160186768</t>
+    <t xml:space="preserve">8.05431365966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85697937011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33673000335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01382064819336</t>
   </si>
   <si>
     <t xml:space="preserve">8.39567756652832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40029048919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34954643249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25728607177734</t>
+    <t xml:space="preserve">8.40028953552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34954738616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25728702545166</t>
   </si>
   <si>
     <t xml:space="preserve">8.118896484375</t>
@@ -2858,31 +2858,31 @@
     <t xml:space="preserve">7.74985551834106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.929762840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78675937652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1096715927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84211492538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42694568634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28855562210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26087617874146</t>
+    <t xml:space="preserve">7.92976331710815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78675985336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10967063903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84211587905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42694520950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28855514526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26087665557861</t>
   </si>
   <si>
     <t xml:space="preserve">7.32545900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3346848487854</t>
+    <t xml:space="preserve">7.33468437194824</t>
   </si>
   <si>
     <t xml:space="preserve">7.1132607460022</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">7.77753353118896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93437623977661</t>
+    <t xml:space="preserve">7.93437576293945</t>
   </si>
   <si>
     <t xml:space="preserve">7.60223960876465</t>
@@ -2915,52 +2915,52 @@
     <t xml:space="preserve">7.10403442382812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15939044952393</t>
+    <t xml:space="preserve">7.15939092636108</t>
   </si>
   <si>
     <t xml:space="preserve">7.06713008880615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92874050140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56533479690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54227113723755</t>
+    <t xml:space="preserve">6.92874002456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56533432006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54227066040039</t>
   </si>
   <si>
     <t xml:space="preserve">7.445396900177</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27010250091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72217798233032</t>
+    <t xml:space="preserve">7.27010297775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72217750549316</t>
   </si>
   <si>
     <t xml:space="preserve">8.46948528289795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66784572601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90310668945312</t>
+    <t xml:space="preserve">8.66784477233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90310764312744</t>
   </si>
   <si>
     <t xml:space="preserve">8.54329299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69090938568115</t>
+    <t xml:space="preserve">8.69090843200684</t>
   </si>
   <si>
     <t xml:space="preserve">8.8754301071167</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32750415802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0066394805908</t>
+    <t xml:space="preserve">9.32750511169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0066404342651</t>
   </si>
   <si>
     <t xml:space="preserve">11.4863929748535</t>
@@ -2972,28 +2972,28 @@
     <t xml:space="preserve">11.2557430267334</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9420576095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82570934295654</t>
+    <t xml:space="preserve">10.9420566558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82571029663086</t>
   </si>
   <si>
     <t xml:space="preserve">9.74267578125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4623050689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1947507858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.019455909729</t>
+    <t xml:space="preserve">10.462306022644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.194751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0194549560547</t>
   </si>
   <si>
     <t xml:space="preserve">9.89029216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3792705535889</t>
+    <t xml:space="preserve">10.3792695999146</t>
   </si>
   <si>
     <t xml:space="preserve">10.360818862915</t>
@@ -3005,13 +3005,13 @@
     <t xml:space="preserve">10.674503326416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5453395843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7667636871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0215015411377</t>
+    <t xml:space="preserve">10.5453405380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7667646408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.021502494812</t>
   </si>
   <si>
     <t xml:space="preserve">11.4402627944946</t>
@@ -3026,13 +3026,13 @@
     <t xml:space="preserve">11.8093032836914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8185300827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7078170776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6616888046265</t>
+    <t xml:space="preserve">11.818531036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7078161239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6616868972778</t>
   </si>
   <si>
     <t xml:space="preserve">11.5694274902344</t>
@@ -3047,10 +3047,10 @@
     <t xml:space="preserve">11.1450300216675</t>
   </si>
   <si>
-    <t xml:space="preserve">10.812894821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0030498504639</t>
+    <t xml:space="preserve">10.8128938674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0030508041382</t>
   </si>
   <si>
     <t xml:space="preserve">12.3167352676392</t>
@@ -3065,13 +3065,13 @@
     <t xml:space="preserve">13.0548162460327</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3961791992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2854671478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4423093795776</t>
+    <t xml:space="preserve">13.3961782455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2854661941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4423084259033</t>
   </si>
   <si>
     <t xml:space="preserve">13.1286239624023</t>
@@ -3086,13 +3086,13 @@
     <t xml:space="preserve">13.1932067871094</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5437955856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3500499725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5714740753174</t>
+    <t xml:space="preserve">13.543794631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3500490188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5714731216431</t>
   </si>
   <si>
     <t xml:space="preserve">13.368501663208</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">13.1101722717285</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1655302047729</t>
+    <t xml:space="preserve">13.1655292510986</t>
   </si>
   <si>
     <t xml:space="preserve">13.267014503479</t>
@@ -3122,7 +3122,7 @@
     <t xml:space="preserve">13.1747550964355</t>
   </si>
   <si>
-    <t xml:space="preserve">13.331597328186</t>
+    <t xml:space="preserve">13.3315963745117</t>
   </si>
   <si>
     <t xml:space="preserve">13.3869543075562</t>
@@ -3143,19 +3143,19 @@
     <t xml:space="preserve">12.7872619628906</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5068912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4330835342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4515352249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2690601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5735187530518</t>
+    <t xml:space="preserve">13.5068922042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.433084487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4515361785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2690591812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5735197067261</t>
   </si>
   <si>
     <t xml:space="preserve">15.8318471908569</t>
@@ -3170,28 +3170,28 @@
     <t xml:space="preserve">15.4628076553345</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7616300582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5217523574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5955619812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7154998779297</t>
+    <t xml:space="preserve">14.7616291046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5217533111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5955610275269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7154989242554</t>
   </si>
   <si>
     <t xml:space="preserve">14.3556852340698</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9128351211548</t>
+    <t xml:space="preserve">13.9128360748291</t>
   </si>
   <si>
     <t xml:space="preserve">13.6545085906982</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5033025741577</t>
+    <t xml:space="preserve">14.5033016204834</t>
   </si>
   <si>
     <t xml:space="preserve">14.4110412597656</t>
@@ -3200,13 +3200,13 @@
     <t xml:space="preserve">14.650918006897</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1860256195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6750068664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4166765213013</t>
+    <t xml:space="preserve">15.1860265731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6750059127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.416675567627</t>
   </si>
   <si>
     <t xml:space="preserve">15.1029949188232</t>
@@ -3215,67 +3215,67 @@
     <t xml:space="preserve">14.9184722900391</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3890018463135</t>
+    <t xml:space="preserve">15.3889999389648</t>
   </si>
   <si>
     <t xml:space="preserve">15.7764930725098</t>
   </si>
   <si>
-    <t xml:space="preserve">15.582745552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1547603607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8133983612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8410720825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.924108505249</t>
+    <t xml:space="preserve">15.5827445983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1547584533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8133964538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8410749435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9241094589233</t>
   </si>
   <si>
     <t xml:space="preserve">16.1178531646729</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8503007888794</t>
+    <t xml:space="preserve">15.8502998352051</t>
   </si>
   <si>
     <t xml:space="preserve">15.8779773712158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3520956039429</t>
+    <t xml:space="preserve">15.3520946502686</t>
   </si>
   <si>
     <t xml:space="preserve">15.6381034851074</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4351272583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5919704437256</t>
+    <t xml:space="preserve">15.4351282119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5919713973999</t>
   </si>
   <si>
     <t xml:space="preserve">15.9517889022827</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0994033813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0717258453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5145721435547</t>
+    <t xml:space="preserve">16.099401473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0717239379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5145740509033</t>
   </si>
   <si>
     <t xml:space="preserve">17.7877635955811</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3910446166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4648532867432</t>
+    <t xml:space="preserve">17.3910465240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4648551940918</t>
   </si>
   <si>
     <t xml:space="preserve">17.1142635345459</t>
@@ -3284,19 +3284,19 @@
     <t xml:space="preserve">17.2618808746338</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5386619567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4464015960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5663414001465</t>
+    <t xml:space="preserve">17.5386600494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4463996887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5663394927979</t>
   </si>
   <si>
     <t xml:space="preserve">17.3725929260254</t>
   </si>
   <si>
-    <t xml:space="preserve">17.621696472168</t>
+    <t xml:space="preserve">17.6216983795166</t>
   </si>
   <si>
     <t xml:space="preserve">17.547887802124</t>
@@ -3305,10 +3305,10 @@
     <t xml:space="preserve">18.0368671417236</t>
   </si>
   <si>
-    <t xml:space="preserve">18.415132522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7657241821289</t>
+    <t xml:space="preserve">18.4151306152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7657222747803</t>
   </si>
   <si>
     <t xml:space="preserve">19.9835567474365</t>
@@ -3317,7 +3317,7 @@
     <t xml:space="preserve">19.4299945831299</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4484481811523</t>
+    <t xml:space="preserve">19.448450088501</t>
   </si>
   <si>
     <t xml:space="preserve">18.728816986084</t>
@@ -3326,7 +3326,7 @@
     <t xml:space="preserve">19.245475769043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1901187896729</t>
+    <t xml:space="preserve">19.1901206970215</t>
   </si>
   <si>
     <t xml:space="preserve">19.3377323150635</t>
@@ -3335,13 +3335,13 @@
     <t xml:space="preserve">19.2639274597168</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5442962646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5627498626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2029342651367</t>
+    <t xml:space="preserve">18.5442981719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5627517700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2029361724854</t>
   </si>
   <si>
     <t xml:space="preserve">18.4704914093018</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">17.9722843170166</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1844844818115</t>
+    <t xml:space="preserve">18.1844825744629</t>
   </si>
   <si>
     <t xml:space="preserve">19.2823791503906</t>
@@ -3365,7 +3365,7 @@
     <t xml:space="preserve">20.9430618286133</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2567501068115</t>
+    <t xml:space="preserve">21.2567481994629</t>
   </si>
   <si>
     <t xml:space="preserve">21.2198429107666</t>
@@ -3374,7 +3374,7 @@
     <t xml:space="preserve">21.3121032714844</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1829376220703</t>
+    <t xml:space="preserve">21.1829395294189</t>
   </si>
   <si>
     <t xml:space="preserve">22.7513618469238</t>
@@ -3392,10 +3392,10 @@
     <t xml:space="preserve">22.4745826721191</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7180519104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5371170043945</t>
+    <t xml:space="preserve">21.7180500030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5371189117432</t>
   </si>
   <si>
     <t xml:space="preserve">20.6293773651123</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">20.7216377258301</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1865272521973</t>
+    <t xml:space="preserve">20.1865291595459</t>
   </si>
   <si>
     <t xml:space="preserve">21.1275825500488</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">21.2013912200928</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4633102416992</t>
+    <t xml:space="preserve">20.4633083343506</t>
   </si>
   <si>
     <t xml:space="preserve">19.8728466033936</t>
@@ -3425,10 +3425,10 @@
     <t xml:space="preserve">20.6478290557861</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8508033752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0906791687012</t>
+    <t xml:space="preserve">20.8508014678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0906810760498</t>
   </si>
   <si>
     <t xml:space="preserve">21.109130859375</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">20.2234325408936</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9466533660889</t>
+    <t xml:space="preserve">19.9466514587402</t>
   </si>
   <si>
     <t xml:space="preserve">20.1311721801758</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">19.6145153045654</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8543930053711</t>
+    <t xml:space="preserve">19.8543910980225</t>
   </si>
   <si>
     <t xml:space="preserve">20.7954483032227</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">22.5483913421631</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0686378479004</t>
+    <t xml:space="preserve">22.0686359405518</t>
   </si>
   <si>
     <t xml:space="preserve">22.2162532806396</t>
@@ -3476,7 +3476,7 @@
     <t xml:space="preserve">22.1424446105957</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0132789611816</t>
+    <t xml:space="preserve">22.0132808685303</t>
   </si>
   <si>
     <t xml:space="preserve">22.2531585693359</t>
@@ -3491,10 +3491,10 @@
     <t xml:space="preserve">23.7846775054932</t>
   </si>
   <si>
-    <t xml:space="preserve">23.729320526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3935928344727</t>
+    <t xml:space="preserve">23.7293186187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3935947418213</t>
   </si>
   <si>
     <t xml:space="preserve">23.8953876495361</t>
@@ -3509,16 +3509,16 @@
     <t xml:space="preserve">23.3049240112305</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3971843719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5817012786865</t>
+    <t xml:space="preserve">23.3971862792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5817031860352</t>
   </si>
   <si>
     <t xml:space="preserve">23.1388549804688</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5852928161621</t>
+    <t xml:space="preserve">22.5852909088135</t>
   </si>
   <si>
     <t xml:space="preserve">22.8067169189453</t>
@@ -3530,10 +3530,10 @@
     <t xml:space="preserve">23.4894428253174</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7477741241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7662239074707</t>
+    <t xml:space="preserve">23.7477722167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7662258148193</t>
   </si>
   <si>
     <t xml:space="preserve">23.2311153411865</t>
@@ -3542,28 +3542,28 @@
     <t xml:space="preserve">22.7144584655762</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6370601654053</t>
+    <t xml:space="preserve">23.6370620727539</t>
   </si>
   <si>
     <t xml:space="preserve">25.0763206481934</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7554569244385</t>
+    <t xml:space="preserve">26.7554550170898</t>
   </si>
   <si>
     <t xml:space="preserve">26.4786758422852</t>
   </si>
   <si>
-    <t xml:space="preserve">26.976879119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1614017486572</t>
+    <t xml:space="preserve">26.9768772125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1613998413086</t>
   </si>
   <si>
     <t xml:space="preserve">27.3828239440918</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4935359954834</t>
+    <t xml:space="preserve">27.4935340881348</t>
   </si>
   <si>
     <t xml:space="preserve">28.1578102111816</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">27.2721099853516</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5673446655273</t>
+    <t xml:space="preserve">27.5673427581787</t>
   </si>
   <si>
     <t xml:space="preserve">27.4012756347656</t>
@@ -3584,13 +3584,13 @@
     <t xml:space="preserve">27.1060428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9030704498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4971256256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9251155853271</t>
+    <t xml:space="preserve">26.9030723571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.497127532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9251136779785</t>
   </si>
   <si>
     <t xml:space="preserve">25.7221393585205</t>
@@ -3605,10 +3605,10 @@
     <t xml:space="preserve">26.3864135742188</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9989204406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5007171630859</t>
+    <t xml:space="preserve">25.9989223480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5007152557373</t>
   </si>
   <si>
     <t xml:space="preserve">25.9066619873047</t>
@@ -3617,22 +3617,22 @@
     <t xml:space="preserve">26.2572479248047</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1280841827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9620170593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6631946563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3310604095459</t>
+    <t xml:space="preserve">26.1280860900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9620132446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6631927490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3310585021973</t>
   </si>
   <si>
     <t xml:space="preserve">26.5155773162842</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4453601837158</t>
+    <t xml:space="preserve">25.4453582763672</t>
   </si>
   <si>
     <t xml:space="preserve">26.737003326416</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">25.4269065856934</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3715515136719</t>
+    <t xml:space="preserve">25.3715534210205</t>
   </si>
   <si>
     <t xml:space="preserve">26.5893859863281</t>
@@ -3662,25 +3662,25 @@
     <t xml:space="preserve">27.1983032226562</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4750843048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.914342880249</t>
+    <t xml:space="preserve">27.4750862121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9143409729004</t>
   </si>
   <si>
     <t xml:space="preserve">30.4643154144287</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9625225067139</t>
+    <t xml:space="preserve">30.9625205993652</t>
   </si>
   <si>
     <t xml:space="preserve">29.5970706939697</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0322341918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8846187591553</t>
+    <t xml:space="preserve">27.0322360992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8846168518066</t>
   </si>
   <si>
     <t xml:space="preserve">27.3459186553955</t>
@@ -3689,28 +3689,28 @@
     <t xml:space="preserve">27.6227016448975</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7923583984375</t>
+    <t xml:space="preserve">26.7923564910889</t>
   </si>
   <si>
     <t xml:space="preserve">26.9399757385254</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1798515319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8994827270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5857982635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2167549133301</t>
+    <t xml:space="preserve">27.1798496246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8994808197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5857963562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2167568206787</t>
   </si>
   <si>
     <t xml:space="preserve">27.3643703460693</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6262893676758</t>
+    <t xml:space="preserve">26.6262912750244</t>
   </si>
   <si>
     <t xml:space="preserve">27.2536602020264</t>
@@ -3725,10 +3725,10 @@
     <t xml:space="preserve">27.9548377990723</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6744651794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0286445617676</t>
+    <t xml:space="preserve">28.674467086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0286464691162</t>
   </si>
   <si>
     <t xml:space="preserve">27.8072185516357</t>
@@ -3740,31 +3740,31 @@
     <t xml:space="preserve">27.917932510376</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6965084075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0506858825684</t>
+    <t xml:space="preserve">27.6965065002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.050687789917</t>
   </si>
   <si>
     <t xml:space="preserve">27.7518653869629</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8256702423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9732894897461</t>
+    <t xml:space="preserve">27.8256721496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9732875823975</t>
   </si>
   <si>
     <t xml:space="preserve">28.3054256439209</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2869720458984</t>
+    <t xml:space="preserve">28.2869739532471</t>
   </si>
   <si>
     <t xml:space="preserve">28.0840015411377</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7887687683105</t>
+    <t xml:space="preserve">27.7887668609619</t>
   </si>
   <si>
     <t xml:space="preserve">26.2941551208496</t>
@@ -3779,19 +3779,19 @@
     <t xml:space="preserve">25.5191669464111</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6150188446045</t>
+    <t xml:space="preserve">24.6150169372559</t>
   </si>
   <si>
     <t xml:space="preserve">24.0983619689941</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9656066894531</t>
+    <t xml:space="preserve">24.9656047821045</t>
   </si>
   <si>
     <t xml:space="preserve">24.356689453125</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7108688354492</t>
+    <t xml:space="preserve">23.7108669281006</t>
   </si>
   <si>
     <t xml:space="preserve">23.3418273925781</t>
@@ -3818,25 +3818,25 @@
     <t xml:space="preserve">25.0947704315186</t>
   </si>
   <si>
-    <t xml:space="preserve">24.910249710083</t>
+    <t xml:space="preserve">24.9102516174316</t>
   </si>
   <si>
     <t xml:space="preserve">24.984058380127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8179874420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1870288848877</t>
+    <t xml:space="preserve">24.8179893493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1870307922363</t>
   </si>
   <si>
     <t xml:space="preserve">24.6703758239746</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5376205444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8733444213867</t>
+    <t xml:space="preserve">25.537618637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8733463287354</t>
   </si>
   <si>
     <t xml:space="preserve">24.9287033081055</t>
@@ -3845,7 +3845,7 @@
     <t xml:space="preserve">24.8364410400391</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2644271850586</t>
+    <t xml:space="preserve">24.2644290924072</t>
   </si>
   <si>
     <t xml:space="preserve">24.3013343811035</t>
@@ -3857,16 +3857,16 @@
     <t xml:space="preserve">23.5263481140137</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1573047637939</t>
+    <t xml:space="preserve">23.1573066711426</t>
   </si>
   <si>
     <t xml:space="preserve">21.8656635284424</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8287601470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8841152191162</t>
+    <t xml:space="preserve">21.8287620544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8841133117676</t>
   </si>
   <si>
     <t xml:space="preserve">21.0353202819824</t>
@@ -3881,10 +3881,10 @@
     <t xml:space="preserve">21.4597187042236</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5335273742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6591014862061</t>
+    <t xml:space="preserve">21.5335292816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6591033935547</t>
   </si>
   <si>
     <t xml:space="preserve">21.4412670135498</t>
@@ -3905,13 +3905,13 @@
     <t xml:space="preserve">22.5114860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6775550842285</t>
+    <t xml:space="preserve">22.6775531768799</t>
   </si>
   <si>
     <t xml:space="preserve">23.1204032897949</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8620758056641</t>
+    <t xml:space="preserve">22.8620738983154</t>
   </si>
   <si>
     <t xml:space="preserve">22.935884475708</t>
@@ -3929,13 +3929,13 @@
     <t xml:space="preserve">21.8103084564209</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9281997680664</t>
+    <t xml:space="preserve">19.928201675415</t>
   </si>
   <si>
     <t xml:space="preserve">20.0758171081543</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8877067565918</t>
+    <t xml:space="preserve">20.8877048492432</t>
   </si>
   <si>
     <t xml:space="preserve">20.4448585510254</t>
@@ -3950,13 +3950,13 @@
     <t xml:space="preserve">20.8138980865479</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2049789428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5002136230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7585411071777</t>
+    <t xml:space="preserve">20.2049808502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5002117156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7585391998291</t>
   </si>
   <si>
     <t xml:space="preserve">20.3710498809814</t>
@@ -3971,7 +3971,7 @@
     <t xml:space="preserve">18.5073909759521</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6770515441895</t>
+    <t xml:space="preserve">17.6770496368408</t>
   </si>
   <si>
     <t xml:space="preserve">18.1291275024414</t>
@@ -3980,13 +3980,13 @@
     <t xml:space="preserve">18.1198997497559</t>
   </si>
   <si>
-    <t xml:space="preserve">17.06813621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3633651733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0845422744751</t>
+    <t xml:space="preserve">17.0681343078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3633670806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0845413208008</t>
   </si>
   <si>
     <t xml:space="preserve">15.2321577072144</t>
@@ -3995,7 +3995,7 @@
     <t xml:space="preserve">16.2839221954346</t>
   </si>
   <si>
-    <t xml:space="preserve">15.370548248291</t>
+    <t xml:space="preserve">15.3705472946167</t>
   </si>
   <si>
     <t xml:space="preserve">16.23779296875</t>
@@ -4010,7 +4010,7 @@
     <t xml:space="preserve">14.0604524612427</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3372325897217</t>
+    <t xml:space="preserve">14.337233543396</t>
   </si>
   <si>
     <t xml:space="preserve">14.6878223419189</t>
@@ -4019,7 +4019,7 @@
     <t xml:space="preserve">14.8169851303101</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2634248733521</t>
+    <t xml:space="preserve">14.2634239196777</t>
   </si>
   <si>
     <t xml:space="preserve">14.2541990280151</t>
@@ -4031,22 +4031,22 @@
     <t xml:space="preserve">15.82262134552</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6565532684326</t>
+    <t xml:space="preserve">15.6565542221069</t>
   </si>
   <si>
     <t xml:space="preserve">14.0420007705688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9958715438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.820574760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3649120330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8667058944702</t>
+    <t xml:space="preserve">13.99587059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8205757141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3649110794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8667068481445</t>
   </si>
   <si>
     <t xml:space="preserve">13.617603302002</t>
@@ -4055,7 +4055,7 @@
     <t xml:space="preserve">13.8113508224487</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8057136535645</t>
+    <t xml:space="preserve">12.8057146072388</t>
   </si>
   <si>
     <t xml:space="preserve">12.7134532928467</t>
@@ -4070,10 +4070,10 @@
     <t xml:space="preserve">15.0476360321045</t>
   </si>
   <si>
-    <t xml:space="preserve">15.305965423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3428678512573</t>
+    <t xml:space="preserve">15.3059644699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.342869758606</t>
   </si>
   <si>
     <t xml:space="preserve">15.0384101867676</t>
@@ -71169,7 +71169,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6493171296</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>60128</v>
@@ -71190,6 +71190,32 @@
         <v>1910</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6495023148</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>75475</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>7.6399998664856</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>7.34999990463257</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>7.6399998664856</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>1982</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1989" uniqueCount="1989">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="1990">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2523984909058</t>
+    <t xml:space="preserve">13.2523975372314</t>
   </si>
   <si>
     <t xml:space="preserve">BSS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.978798866272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.747950553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3974046707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.243504524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2606067657471</t>
+    <t xml:space="preserve">12.9788017272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7479515075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.397403717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2435054779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2606058120728</t>
   </si>
   <si>
     <t xml:space="preserve">12.1409063339233</t>
@@ -65,52 +65,52 @@
     <t xml:space="preserve">11.4825611114502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8584136962891</t>
+    <t xml:space="preserve">10.8584156036377</t>
   </si>
   <si>
     <t xml:space="preserve">9.79822444915771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3539695739746</t>
+    <t xml:space="preserve">10.3539705276489</t>
   </si>
   <si>
     <t xml:space="preserve">9.84952449798584</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4736680984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2941207885742</t>
+    <t xml:space="preserve">10.4736700057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2941198348999</t>
   </si>
   <si>
     <t xml:space="preserve">10.7814664840698</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8156661987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7301654815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5762691497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.636116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.191520690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4565696716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4907703399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0205211639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03728008270264</t>
+    <t xml:space="preserve">10.8156671524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7301664352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.576268196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.636118888855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1915216445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4565687179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4907693862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0205221176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.037278175354</t>
   </si>
   <si>
     <t xml:space="preserve">8.97743129730225</t>
@@ -122,61 +122,61 @@
     <t xml:space="preserve">9.14842891693115</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43057823181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90082263946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66142463684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4394702911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.345419883728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2000713348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0037641525269</t>
+    <t xml:space="preserve">9.43057727813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90082359313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66142559051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4394693374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3454208374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2000722885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0037651062012</t>
   </si>
   <si>
     <t xml:space="preserve">10.5506181716919</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2257213592529</t>
+    <t xml:space="preserve">10.2257204055786</t>
   </si>
   <si>
     <t xml:space="preserve">10.1829710006714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0379638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9097166061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8074588775635</t>
+    <t xml:space="preserve">11.0379648208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9097156524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8074607849121</t>
   </si>
   <si>
     <t xml:space="preserve">11.9442586898804</t>
   </si>
   <si>
-    <t xml:space="preserve">12.106707572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7732601165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9699068069458</t>
+    <t xml:space="preserve">12.1067066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7732582092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9699087142944</t>
   </si>
   <si>
     <t xml:space="preserve">11.6279106140137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3714151382446</t>
+    <t xml:space="preserve">11.371413230896</t>
   </si>
   <si>
     <t xml:space="preserve">11.3799629211426</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">11.6621103286743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8416576385498</t>
+    <t xml:space="preserve">11.8416585922241</t>
   </si>
   <si>
     <t xml:space="preserve">11.9186067581177</t>
@@ -194,88 +194,88 @@
     <t xml:space="preserve">11.7989082336426</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0468578338623</t>
+    <t xml:space="preserve">12.046856880188</t>
   </si>
   <si>
     <t xml:space="preserve">12.1922063827515</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2007570266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3375549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1323575973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1665563583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2178544998169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9015092849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.568060874939</t>
+    <t xml:space="preserve">12.200756072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3375558853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1323566436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1665544509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2178554534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9015083312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5680599212646</t>
   </si>
   <si>
     <t xml:space="preserve">11.2859125137329</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7390584945679</t>
+    <t xml:space="preserve">11.7390594482422</t>
   </si>
   <si>
     <t xml:space="preserve">11.8844079971313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8160095214844</t>
+    <t xml:space="preserve">11.8160076141357</t>
   </si>
   <si>
     <t xml:space="preserve">11.7048597335815</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6022615432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6364603042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4740104675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1918640136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1063632965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1149158477783</t>
+    <t xml:space="preserve">11.6022605895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6364593505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4740114212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1918649673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1063642501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1149129867554</t>
   </si>
   <si>
     <t xml:space="preserve">11.3201131820679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457622528076</t>
+    <t xml:space="preserve">11.3457632064819</t>
   </si>
   <si>
     <t xml:space="preserve">11.1576633453369</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0550661087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9866666793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1405630111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6019172668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9541397094727</t>
+    <t xml:space="preserve">11.055064201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.986665725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1405639648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.60191822052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9541416168213</t>
   </si>
   <si>
     <t xml:space="preserve">10.4346113204956</t>
@@ -284,34 +284,34 @@
     <t xml:space="preserve">10.3553619384766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2232780456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2673053741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92389011383057</t>
+    <t xml:space="preserve">10.22327709198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2673063278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92388916015625</t>
   </si>
   <si>
     <t xml:space="preserve">10.3201389312744</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0031394958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.302529335022</t>
+    <t xml:space="preserve">10.003137588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3025274276733</t>
   </si>
   <si>
     <t xml:space="preserve">10.2496948242188</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6107244491577</t>
+    <t xml:space="preserve">10.6107225418091</t>
   </si>
   <si>
     <t xml:space="preserve">11.4120311737061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1302528381348</t>
+    <t xml:space="preserve">11.1302518844604</t>
   </si>
   <si>
     <t xml:space="preserve">10.9189186096191</t>
@@ -320,22 +320,22 @@
     <t xml:space="preserve">11.2359199523926</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2799482345581</t>
+    <t xml:space="preserve">11.2799491882324</t>
   </si>
   <si>
     <t xml:space="preserve">11.0069742202759</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8308639526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8396682739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9277238845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9101133346558</t>
+    <t xml:space="preserve">10.830864906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8396692276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9277229309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9101142883301</t>
   </si>
   <si>
     <t xml:space="preserve">10.8132514953613</t>
@@ -347,37 +347,37 @@
     <t xml:space="preserve">10.0647773742676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99433326721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95030403137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68613815307617</t>
+    <t xml:space="preserve">9.9943323135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9503059387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68613719940186</t>
   </si>
   <si>
     <t xml:space="preserve">10.0383596420288</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4962520599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3465566635132</t>
+    <t xml:space="preserve">10.4962511062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3465557098389</t>
   </si>
   <si>
     <t xml:space="preserve">10.4522228240967</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5843067169189</t>
+    <t xml:space="preserve">10.5843076705933</t>
   </si>
   <si>
     <t xml:space="preserve">9.87985992431641</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12258052825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67733192443848</t>
+    <t xml:space="preserve">9.12257957458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67733097076416</t>
   </si>
   <si>
     <t xml:space="preserve">9.57166481018066</t>
@@ -386,13 +386,13 @@
     <t xml:space="preserve">9.932692527771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1880559921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98552703857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18421840667725</t>
+    <t xml:space="preserve">10.1880550384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98552799224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18421936035156</t>
   </si>
   <si>
     <t xml:space="preserve">9.14019203186035</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">9.721360206604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0823888778687</t>
+    <t xml:space="preserve">10.0823879241943</t>
   </si>
   <si>
     <t xml:space="preserve">10.381778717041</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">10.2849178314209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1352233886719</t>
+    <t xml:space="preserve">10.1352224349976</t>
   </si>
   <si>
     <t xml:space="preserve">10.2144737243652</t>
@@ -419,13 +419,13 @@
     <t xml:space="preserve">10.1528339385986</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6987800598145</t>
+    <t xml:space="preserve">10.6987781524658</t>
   </si>
   <si>
     <t xml:space="preserve">11.0774192810059</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0157804489136</t>
+    <t xml:space="preserve">11.0157794952393</t>
   </si>
   <si>
     <t xml:space="preserve">11.0333909988403</t>
@@ -434,31 +434,31 @@
     <t xml:space="preserve">10.9893627166748</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8748903274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0950298309326</t>
+    <t xml:space="preserve">10.8748922348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0950307846069</t>
   </si>
   <si>
     <t xml:space="preserve">11.2535305023193</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3151712417603</t>
+    <t xml:space="preserve">11.3151702880859</t>
   </si>
   <si>
     <t xml:space="preserve">10.7251968383789</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0510015487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9013080596924</t>
+    <t xml:space="preserve">11.0510025024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9013071060181</t>
   </si>
   <si>
     <t xml:space="preserve">11.1654758453369</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0598087310791</t>
+    <t xml:space="preserve">11.0598077774048</t>
   </si>
   <si>
     <t xml:space="preserve">11.2183084487915</t>
@@ -467,28 +467,28 @@
     <t xml:space="preserve">11.1214475631714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1830835342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2623348236084</t>
+    <t xml:space="preserve">11.1830854415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.262336730957</t>
   </si>
   <si>
     <t xml:space="preserve">11.5265045166016</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7466440200806</t>
+    <t xml:space="preserve">11.7466430664062</t>
   </si>
   <si>
     <t xml:space="preserve">11.773060798645</t>
   </si>
   <si>
-    <t xml:space="preserve">11.685004234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7994756698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6497812271118</t>
+    <t xml:space="preserve">11.6850051879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7994775772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6497821807861</t>
   </si>
   <si>
     <t xml:space="preserve">11.6673927307129</t>
@@ -500,55 +500,55 @@
     <t xml:space="preserve">11.3239765167236</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3680028915405</t>
+    <t xml:space="preserve">11.3680047988892</t>
   </si>
   <si>
     <t xml:space="preserve">11.1390581130981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6938095092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6145601272583</t>
+    <t xml:space="preserve">11.693808555603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.614559173584</t>
   </si>
   <si>
     <t xml:space="preserve">11.8258934020996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0372276306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0548391342163</t>
+    <t xml:space="preserve">12.0372285842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.054838180542</t>
   </si>
   <si>
     <t xml:space="preserve">12.0636434555054</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5039234161377</t>
+    <t xml:space="preserve">12.5039224624634</t>
   </si>
   <si>
     <t xml:space="preserve">12.5303392410278</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4070615768433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2837829589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6007843017578</t>
+    <t xml:space="preserve">12.4070625305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2837839126587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6007862091064</t>
   </si>
   <si>
     <t xml:space="preserve">12.9177856445312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8121185302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.856146812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0322580337524</t>
+    <t xml:space="preserve">12.8121175765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8561477661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0322570800781</t>
   </si>
   <si>
     <t xml:space="preserve">13.4108972549438</t>
@@ -557,94 +557,94 @@
     <t xml:space="preserve">13.5782032012939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6838693618774</t>
+    <t xml:space="preserve">13.6838703155518</t>
   </si>
   <si>
     <t xml:space="preserve">13.4285097122192</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3707065582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2210102081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2562341690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1329545974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1241512298584</t>
+    <t xml:space="preserve">14.3707046508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2210111618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.256233215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1329555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1241502761841</t>
   </si>
   <si>
     <t xml:space="preserve">14.0713157653809</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9216232299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7807321548462</t>
+    <t xml:space="preserve">13.9216213226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7807312011719</t>
   </si>
   <si>
     <t xml:space="preserve">13.6046199798584</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7631196975708</t>
+    <t xml:space="preserve">13.7631206512451</t>
   </si>
   <si>
     <t xml:space="preserve">13.8335657119751</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7278995513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1995639801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3756742477417</t>
+    <t xml:space="preserve">13.7278985977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1995630264282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3756771087646</t>
   </si>
   <si>
     <t xml:space="preserve">13.155535697937</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6486482620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5605926513672</t>
+    <t xml:space="preserve">13.6486492156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5605936050415</t>
   </si>
   <si>
     <t xml:space="preserve">13.736704826355</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8775939941406</t>
+    <t xml:space="preserve">13.8775930404663</t>
   </si>
   <si>
     <t xml:space="preserve">14.176983833313</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0977325439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7845697402954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3040962219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.277681350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4890165328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4978218078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3657350540161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4449892044067</t>
+    <t xml:space="preserve">14.0977334976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7845678329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3040952682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2776803970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4890146255493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.497820854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3657379150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4449882507324</t>
   </si>
   <si>
     <t xml:space="preserve">15.3393182754517</t>
@@ -653,28 +653,28 @@
     <t xml:space="preserve">15.5330419540405</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6651268005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5418491363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2424573898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8060150146484</t>
+    <t xml:space="preserve">15.6651258468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5418472290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2424592971802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8060169219971</t>
   </si>
   <si>
     <t xml:space="preserve">16.1934585571289</t>
   </si>
   <si>
-    <t xml:space="preserve">16.369571685791</t>
+    <t xml:space="preserve">16.3695755004883</t>
   </si>
   <si>
     <t xml:space="preserve">16.4664344787598</t>
   </si>
   <si>
-    <t xml:space="preserve">16.510461807251</t>
+    <t xml:space="preserve">16.5104637145996</t>
   </si>
   <si>
     <t xml:space="preserve">17.03879737854</t>
@@ -683,37 +683,37 @@
     <t xml:space="preserve">16.889102935791</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1532707214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7746276855469</t>
+    <t xml:space="preserve">17.1532688140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7746295928955</t>
   </si>
   <si>
     <t xml:space="preserve">16.5544891357422</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2374877929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5897102355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6513519287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5721015930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9947700500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7041816711426</t>
+    <t xml:space="preserve">16.2374897003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5897121429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6513500213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5721035003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9947681427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7041835784912</t>
   </si>
   <si>
     <t xml:space="preserve">16.880298614502</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8538799285889</t>
+    <t xml:space="preserve">16.8538761138916</t>
   </si>
   <si>
     <t xml:space="preserve">17.012378692627</t>
@@ -725,16 +725,16 @@
     <t xml:space="preserve">17.1268520355225</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5368804931641</t>
+    <t xml:space="preserve">16.5368785858154</t>
   </si>
   <si>
     <t xml:space="preserve">17.0828247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8626823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2061023712158</t>
+    <t xml:space="preserve">16.8626842498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2061004638672</t>
   </si>
   <si>
     <t xml:space="preserve">17.3469944000244</t>
@@ -743,37 +743,37 @@
     <t xml:space="preserve">17.6551876068115</t>
   </si>
   <si>
-    <t xml:space="preserve">17.540714263916</t>
+    <t xml:space="preserve">17.5407161712646</t>
   </si>
   <si>
     <t xml:space="preserve">17.5054931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7168273925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4526615142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5583248138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7432422637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8401050567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5759372711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7482109069824</t>
+    <t xml:space="preserve">17.7168292999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4526596069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.55832862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7432441711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8401031494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5759334564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7482147216797</t>
   </si>
   <si>
     <t xml:space="preserve">16.7658233642578</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9507427215576</t>
+    <t xml:space="preserve">16.950740814209</t>
   </si>
   <si>
     <t xml:space="preserve">17.1620750427246</t>
@@ -782,31 +782,31 @@
     <t xml:space="preserve">17.2765483856201</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6865749359131</t>
+    <t xml:space="preserve">16.6865730285645</t>
   </si>
   <si>
     <t xml:space="preserve">17.1092414855957</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8186569213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2325172424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2853507995605</t>
+    <t xml:space="preserve">16.8186588287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.232515335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2853546142578</t>
   </si>
   <si>
     <t xml:space="preserve">17.391019821167</t>
   </si>
   <si>
-    <t xml:space="preserve">17.250129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4350452423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3734073638916</t>
+    <t xml:space="preserve">17.2501316070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4350471496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3734092712402</t>
   </si>
   <si>
     <t xml:space="preserve">17.6463832855225</t>
@@ -815,19 +815,19 @@
     <t xml:space="preserve">17.9457683563232</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3722763061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9358329772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3849182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.596248626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3408908843994</t>
+    <t xml:space="preserve">19.3722743988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9358310699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3849143981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5962524414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3408870697021</t>
   </si>
   <si>
     <t xml:space="preserve">20.8340015411377</t>
@@ -836,25 +836,25 @@
     <t xml:space="preserve">21.0453357696533</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5824737548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0893650054932</t>
+    <t xml:space="preserve">21.5824775695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0893630981445</t>
   </si>
   <si>
     <t xml:space="preserve">21.327112197876</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6529197692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7497806549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9170875549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8114204406738</t>
+    <t xml:space="preserve">21.6529178619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7497844696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9170894622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8114223480225</t>
   </si>
   <si>
     <t xml:space="preserve">22.0139484405518</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">22.286922454834</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2605056762695</t>
+    <t xml:space="preserve">22.2605037689209</t>
   </si>
   <si>
     <t xml:space="preserve">22.348560333252</t>
@@ -872,10 +872,10 @@
     <t xml:space="preserve">22.3221435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1900596618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6303424835205</t>
+    <t xml:space="preserve">22.1900615692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6303405761719</t>
   </si>
   <si>
     <t xml:space="preserve">22.436616897583</t>
@@ -884,67 +884,67 @@
     <t xml:space="preserve">22.4806423187256</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6655616760254</t>
+    <t xml:space="preserve">22.6655597686768</t>
   </si>
   <si>
     <t xml:space="preserve">22.6215343475342</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6743679046631</t>
+    <t xml:space="preserve">22.6743698120117</t>
   </si>
   <si>
     <t xml:space="preserve">22.8945083618164</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0970344543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8328666687012</t>
+    <t xml:space="preserve">23.0970363616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8328704833984</t>
   </si>
   <si>
     <t xml:space="preserve">22.3749771118164</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1938972473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3876190185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5108985900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9159545898438</t>
+    <t xml:space="preserve">23.1938953399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3876171112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5108966827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9159526824951</t>
   </si>
   <si>
     <t xml:space="preserve">24.2417602539062</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7084541320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6556224822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9197902679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0870952606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9638214111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8933753967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4255447387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4879322052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.397008895874</t>
+    <t xml:space="preserve">24.7084579467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6556243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9197883605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0870971679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9638195037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8933734893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4255409240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4879302978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3970069885254</t>
   </si>
   <si>
     <t xml:space="preserve">27.6287326812744</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">28.1545677185059</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6732940673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6804046630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3666725158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8069801330566</t>
+    <t xml:space="preserve">27.6732959747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6804027557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3666706085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8069839477539</t>
   </si>
   <si>
     <t xml:space="preserve">28.4665069580078</t>
@@ -974,109 +974,109 @@
     <t xml:space="preserve">29.4914436340332</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7677326202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8746814727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3024845123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7748432159424</t>
+    <t xml:space="preserve">29.7677345275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.874683380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3024787902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7748374938965</t>
   </si>
   <si>
     <t xml:space="preserve">30.2400951385498</t>
   </si>
   <si>
-    <t xml:space="preserve">30.667896270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8283157348633</t>
+    <t xml:space="preserve">30.6678924560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8283176422119</t>
   </si>
   <si>
     <t xml:space="preserve">30.8996162414551</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0154762268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9976577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9352645874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6500644683838</t>
+    <t xml:space="preserve">31.0154781341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.997652053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.935266494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6500682830811</t>
   </si>
   <si>
     <t xml:space="preserve">30.748104095459</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6857147216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3577537536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5003547668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3131942749023</t>
+    <t xml:space="preserve">30.685718536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3577556610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5003509521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3131923675537</t>
   </si>
   <si>
     <t xml:space="preserve">29.2775421142578</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1687908172607</t>
+    <t xml:space="preserve">30.1687889099121</t>
   </si>
   <si>
     <t xml:space="preserve">30.1331443786621</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9994525909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9281558990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0529346466064</t>
+    <t xml:space="preserve">29.9994564056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9281578063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0529327392578</t>
   </si>
   <si>
     <t xml:space="preserve">29.4825325012207</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8122940063477</t>
+    <t xml:space="preserve">29.8122959136963</t>
   </si>
   <si>
     <t xml:space="preserve">28.9121284484863</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1260299682617</t>
+    <t xml:space="preserve">29.126033782959</t>
   </si>
   <si>
     <t xml:space="preserve">27.7713317871094</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9674053192139</t>
+    <t xml:space="preserve">27.9674072265625</t>
   </si>
   <si>
     <t xml:space="preserve">27.2544078826904</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6911182403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4861335754395</t>
+    <t xml:space="preserve">27.6911201477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4861316680908</t>
   </si>
   <si>
     <t xml:space="preserve">27.5752582550049</t>
   </si>
   <si>
-    <t xml:space="preserve">28.11891746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.350643157959</t>
+    <t xml:space="preserve">28.1189193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3506450653076</t>
   </si>
   <si>
     <t xml:space="preserve">27.7178592681885</t>
@@ -1094,13 +1094,13 @@
     <t xml:space="preserve">28.7873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7855529785156</t>
+    <t xml:space="preserve">29.7855548858643</t>
   </si>
   <si>
     <t xml:space="preserve">29.5360069274902</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3310203552246</t>
+    <t xml:space="preserve">29.331018447876</t>
   </si>
   <si>
     <t xml:space="preserve">29.1705932617188</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">29.232982635498</t>
   </si>
   <si>
-    <t xml:space="preserve">29.143856048584</t>
+    <t xml:space="preserve">29.1438579559326</t>
   </si>
   <si>
     <t xml:space="preserve">29.3221073150635</t>
@@ -1121,31 +1121,31 @@
     <t xml:space="preserve">28.7071437835693</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9923419952393</t>
+    <t xml:space="preserve">28.9923439025879</t>
   </si>
   <si>
     <t xml:space="preserve">28.9477806091309</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6073036193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8568592071533</t>
+    <t xml:space="preserve">29.6073055267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8568572998047</t>
   </si>
   <si>
     <t xml:space="preserve">29.4023208618164</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4112300872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.814094543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6875228881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6162166595459</t>
+    <t xml:space="preserve">29.4112281799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8140964508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.687520980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6162185668945</t>
   </si>
   <si>
     <t xml:space="preserve">29.6786060333252</t>
@@ -1157,19 +1157,19 @@
     <t xml:space="preserve">30.142053604126</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8390312194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.186616897583</t>
+    <t xml:space="preserve">29.8390331268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1866149902344</t>
   </si>
   <si>
     <t xml:space="preserve">29.5181770324707</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1795063018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.437967300415</t>
+    <t xml:space="preserve">29.1795101165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4379634857178</t>
   </si>
   <si>
     <t xml:space="preserve">30.3648681640625</t>
@@ -1178,22 +1178,22 @@
     <t xml:space="preserve">30.4629039764404</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4718170166016</t>
+    <t xml:space="preserve">30.4718151092529</t>
   </si>
   <si>
     <t xml:space="preserve">30.2935695648193</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0974903106689</t>
+    <t xml:space="preserve">30.0974922180176</t>
   </si>
   <si>
     <t xml:space="preserve">30.0618419647217</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2311763763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0849800109863</t>
+    <t xml:space="preserve">30.2311782836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0849838256836</t>
   </si>
   <si>
     <t xml:space="preserve">31.4967517852783</t>
@@ -1202,43 +1202,43 @@
     <t xml:space="preserve">30.819408416748</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9958515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7730388641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6928310394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1830177307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0760688781738</t>
+    <t xml:space="preserve">31.9958572387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7730369567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6928272247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1830139160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0760650634766</t>
   </si>
   <si>
     <t xml:space="preserve">31.9512920379639</t>
   </si>
   <si>
-    <t xml:space="preserve">32.307788848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1990394592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3951148986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7587242126465</t>
+    <t xml:space="preserve">32.3077926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1990432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3951187133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7587280273438</t>
   </si>
   <si>
     <t xml:space="preserve">34.6963386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">34.731990814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5804748535156</t>
+    <t xml:space="preserve">34.7319946289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5804786682129</t>
   </si>
   <si>
     <t xml:space="preserve">34.2239799499512</t>
@@ -1250,61 +1250,61 @@
     <t xml:space="preserve">34.5448226928711</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4271621704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2221755981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6606903076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3754844665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8674774169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8496513366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1437644958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7159652709961</t>
+    <t xml:space="preserve">35.4271659851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2221794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6606941223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.37548828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8674736022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8496551513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1437683105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7159690856934</t>
   </si>
   <si>
     <t xml:space="preserve">34.0635528564453</t>
   </si>
   <si>
-    <t xml:space="preserve">34.313102722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1170272827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.420051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7765502929688</t>
+    <t xml:space="preserve">34.3130989074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1170234680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4200477600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.776554107666</t>
   </si>
   <si>
     <t xml:space="preserve">34.6161270141602</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3041877746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1081123352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8425445556641</t>
+    <t xml:space="preserve">34.3041915893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1081199645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8425407409668</t>
   </si>
   <si>
     <t xml:space="preserve">34.0902900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">35.106315612793</t>
+    <t xml:space="preserve">35.1063117980957</t>
   </si>
   <si>
     <t xml:space="preserve">36.2471122741699</t>
@@ -1313,76 +1313,76 @@
     <t xml:space="preserve">36.3005867004395</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1847229003906</t>
+    <t xml:space="preserve">36.1847305297852</t>
   </si>
   <si>
     <t xml:space="preserve">36.4966659545898</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4146537780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8584785461426</t>
+    <t xml:space="preserve">37.4146499633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.858470916748</t>
   </si>
   <si>
     <t xml:space="preserve">38.9208602905273</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6178359985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5821838378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2702522277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4306755065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2149772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.805004119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8067970275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3504638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0563507080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3682899475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.341552734375</t>
+    <t xml:space="preserve">38.6178398132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5821876525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2702484130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4306716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.214973449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8050003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8068008422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3504600524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0563545227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3682861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3415489196777</t>
   </si>
   <si>
     <t xml:space="preserve">38.5198020935059</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5643653869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6089286804199</t>
+    <t xml:space="preserve">38.5643692016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6089248657227</t>
   </si>
   <si>
     <t xml:space="preserve">38.689136505127</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7337036132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4377861022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0812873840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0545539855957</t>
+    <t xml:space="preserve">38.733699798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4377822875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0812835693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0545463562012</t>
   </si>
   <si>
     <t xml:space="preserve">39.3219299316406</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">38.5554466247559</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2880744934082</t>
+    <t xml:space="preserve">38.2880783081055</t>
   </si>
   <si>
     <t xml:space="preserve">38.3772048950195</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">37.6998481750488</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6125297546387</t>
+    <t xml:space="preserve">36.6125259399414</t>
   </si>
   <si>
     <t xml:space="preserve">37.6820259094238</t>
@@ -1412,16 +1412,16 @@
     <t xml:space="preserve">41.9956703186035</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6551933288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8156280517578</t>
+    <t xml:space="preserve">42.655200958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8156204223633</t>
   </si>
   <si>
     <t xml:space="preserve">42.4234733581543</t>
   </si>
   <si>
-    <t xml:space="preserve">42.031322479248</t>
+    <t xml:space="preserve">42.0313186645508</t>
   </si>
   <si>
     <t xml:space="preserve">42.0847969055176</t>
@@ -1430,7 +1430,7 @@
     <t xml:space="preserve">41.924373626709</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6213417053223</t>
+    <t xml:space="preserve">41.6213455200195</t>
   </si>
   <si>
     <t xml:space="preserve">41.7639465332031</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">41.6926460266113</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5322227478027</t>
+    <t xml:space="preserve">41.5322189331055</t>
   </si>
   <si>
     <t xml:space="preserve">41.7817726135254</t>
@@ -1451,13 +1451,13 @@
     <t xml:space="preserve">41.3539733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">40.819221496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3557739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5874977111816</t>
+    <t xml:space="preserve">40.8192253112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.355770111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5875015258789</t>
   </si>
   <si>
     <t xml:space="preserve">39.8031997680664</t>
@@ -1466,31 +1466,31 @@
     <t xml:space="preserve">39.1436729431152</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6784210205078</t>
+    <t xml:space="preserve">39.6784248352051</t>
   </si>
   <si>
     <t xml:space="preserve">42.779972076416</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4787445068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6802291870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5750770568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2898750305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5893020629883</t>
+    <t xml:space="preserve">41.4787483215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6802253723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5750732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2898712158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.589298248291</t>
   </si>
   <si>
     <t xml:space="preserve">40.1953468322754</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1062240600586</t>
+    <t xml:space="preserve">40.1062278747559</t>
   </si>
   <si>
     <t xml:space="preserve">40.5696716308594</t>
@@ -1502,34 +1502,34 @@
     <t xml:space="preserve">40.9439964294434</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1400718688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9974708557129</t>
+    <t xml:space="preserve">41.1400756835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9974746704102</t>
   </si>
   <si>
     <t xml:space="preserve">40.5161972045898</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9618186950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2506294250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1793251037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2131729125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3914260864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3896179199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6017189025879</t>
+    <t xml:space="preserve">40.9618225097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2506256103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1793212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2131690979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3914184570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3896255493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6017265319824</t>
   </si>
   <si>
     <t xml:space="preserve">44.5446434020996</t>
@@ -1538,31 +1538,31 @@
     <t xml:space="preserve">43.902946472168</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2309074401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8851203918457</t>
+    <t xml:space="preserve">45.2309036254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.885124206543</t>
   </si>
   <si>
     <t xml:space="preserve">44.9635353088379</t>
   </si>
   <si>
-    <t xml:space="preserve">46.033031463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3253479003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9439086914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5874137878418</t>
+    <t xml:space="preserve">46.0330352783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3253402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.943904876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5874099731445</t>
   </si>
   <si>
     <t xml:space="preserve">44.6961631774902</t>
   </si>
   <si>
-    <t xml:space="preserve">44.009895324707</t>
+    <t xml:space="preserve">44.0098991394043</t>
   </si>
   <si>
     <t xml:space="preserve">43.8494758605957</t>
@@ -1571,13 +1571,13 @@
     <t xml:space="preserve">42.9582214355469</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4609260559082</t>
+    <t xml:space="preserve">41.4609222412109</t>
   </si>
   <si>
     <t xml:space="preserve">41.1757202148438</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1578979492188</t>
+    <t xml:space="preserve">41.157901763916</t>
   </si>
   <si>
     <t xml:space="preserve">41.0153007507324</t>
@@ -1586,13 +1586,13 @@
     <t xml:space="preserve">39.7675514221191</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1080284118652</t>
+    <t xml:space="preserve">39.108024597168</t>
   </si>
   <si>
     <t xml:space="preserve">40.7479209899902</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7853775024414</t>
+    <t xml:space="preserve">39.7853736877441</t>
   </si>
   <si>
     <t xml:space="preserve">40.5518493652344</t>
@@ -1604,34 +1604,34 @@
     <t xml:space="preserve">39.3040962219238</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2488250732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9101486206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4288749694824</t>
+    <t xml:space="preserve">40.2488212585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9101448059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.428882598877</t>
   </si>
   <si>
     <t xml:space="preserve">39.0367240905762</t>
   </si>
   <si>
-    <t xml:space="preserve">42.387825012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0509452819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9335746765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0149230957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7087135314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6366577148438</t>
+    <t xml:space="preserve">42.3878288269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.050952911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9335708618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0149269104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7087097167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6366539001465</t>
   </si>
   <si>
     <t xml:space="preserve">40.5285797119141</t>
@@ -1640,49 +1640,49 @@
     <t xml:space="preserve">39.8441009521484</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7366142272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4844360351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3316230773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0521278381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4757270812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6018104553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.007396697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6651496887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3589363098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2241401672363</t>
+    <t xml:space="preserve">37.7366104125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.484432220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3316268920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0521240234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4757232666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6018142700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0073928833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6651458740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3589324951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2241325378418</t>
   </si>
   <si>
     <t xml:space="preserve">33.4135589599609</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6657409667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8818969726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4763107299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6924667358398</t>
+    <t xml:space="preserve">33.6657447814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.881893157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4763069152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6924629211426</t>
   </si>
   <si>
     <t xml:space="preserve">35.1427841186523</t>
@@ -1691,10 +1691,10 @@
     <t xml:space="preserve">34.7284965515137</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5483627319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9899749755859</t>
+    <t xml:space="preserve">34.5483665466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9899787902832</t>
   </si>
   <si>
     <t xml:space="preserve">33.8278579711914</t>
@@ -1703,61 +1703,61 @@
     <t xml:space="preserve">34.4402885437012</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1247711181641</t>
+    <t xml:space="preserve">35.1247673034668</t>
   </si>
   <si>
     <t xml:space="preserve">33.5036277770996</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4048538208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3868370056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4681930541992</t>
+    <t xml:space="preserve">32.4048500061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3868408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4681911468506</t>
   </si>
   <si>
     <t xml:space="preserve">31.7744083404541</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5315322875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.486795425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9371128082275</t>
+    <t xml:space="preserve">30.531530380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4867973327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9371109008789</t>
   </si>
   <si>
     <t xml:space="preserve">29.2346153259277</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1532649993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2166023254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4147434234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8296241760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1265411376953</t>
+    <t xml:space="preserve">30.1532669067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2166004180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4147453308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8296222686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1265392303467</t>
   </si>
   <si>
     <t xml:space="preserve">29.5408325195312</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6035804748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2520389556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6489086151123</t>
+    <t xml:space="preserve">30.6035823822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2520408630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6489105224609</t>
   </si>
   <si>
     <t xml:space="preserve">29.9551239013672</t>
@@ -1766,40 +1766,40 @@
     <t xml:space="preserve">30.1172351837158</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4054393768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.666332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6483154296875</t>
+    <t xml:space="preserve">30.4054412841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6663341522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6483173370361</t>
   </si>
   <si>
     <t xml:space="preserve">32.080623626709</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1079444885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3601169586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9818515777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7383823394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6122932434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8377513885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9190979003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.901086807251</t>
+    <t xml:space="preserve">31.1079368591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3601150512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9818496704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7383804321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6122894287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8377475738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9191017150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9010887145996</t>
   </si>
   <si>
     <t xml:space="preserve">29.6669216156006</t>
@@ -1808,25 +1808,25 @@
     <t xml:space="preserve">29.0905132293701</t>
   </si>
   <si>
-    <t xml:space="preserve">28.730260848999</t>
+    <t xml:space="preserve">28.7302589416504</t>
   </si>
   <si>
     <t xml:space="preserve">28.099817276001</t>
   </si>
   <si>
-    <t xml:space="preserve">27.595458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6407871246338</t>
+    <t xml:space="preserve">27.5954608917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6407852172852</t>
   </si>
   <si>
     <t xml:space="preserve">26.2805328369141</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0463676452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5146980285645</t>
+    <t xml:space="preserve">26.0463695526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5146999359131</t>
   </si>
   <si>
     <t xml:space="preserve">27.2352046966553</t>
@@ -1835,13 +1835,13 @@
     <t xml:space="preserve">27.0550804138184</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1091175079346</t>
+    <t xml:space="preserve">27.1091194152832</t>
   </si>
   <si>
     <t xml:space="preserve">27.0190544128418</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7488651275635</t>
+    <t xml:space="preserve">26.7488632202148</t>
   </si>
   <si>
     <t xml:space="preserve">27.4693737030029</t>
@@ -1850,34 +1850,34 @@
     <t xml:space="preserve">27.9196891784668</t>
   </si>
   <si>
-    <t xml:space="preserve">27.577449798584</t>
+    <t xml:space="preserve">27.5774478912354</t>
   </si>
   <si>
     <t xml:space="preserve">27.9377021789551</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8476390838623</t>
+    <t xml:space="preserve">27.8476409912109</t>
   </si>
   <si>
     <t xml:space="preserve">27.7936019897461</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0457782745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0097560882568</t>
+    <t xml:space="preserve">28.0457763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0097541809082</t>
   </si>
   <si>
     <t xml:space="preserve">27.7755870819092</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6041736602783</t>
+    <t xml:space="preserve">28.6041717529297</t>
   </si>
   <si>
     <t xml:space="preserve">28.5501346588135</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1805820465088</t>
+    <t xml:space="preserve">29.1805801391602</t>
   </si>
   <si>
     <t xml:space="preserve">29.1625671386719</t>
@@ -1886,7 +1886,7 @@
     <t xml:space="preserve">28.6401977539062</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6762237548828</t>
+    <t xml:space="preserve">28.6762218475342</t>
   </si>
   <si>
     <t xml:space="preserve">27.6675090789795</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">27.5594348907471</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7581653594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7320308685303</t>
+    <t xml:space="preserve">25.7581634521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7320327758789</t>
   </si>
   <si>
     <t xml:space="preserve">21.7413330078125</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7233219146729</t>
+    <t xml:space="preserve">21.7233200073242</t>
   </si>
   <si>
     <t xml:space="preserve">22.7860679626465</t>
@@ -1916,13 +1916,13 @@
     <t xml:space="preserve">23.4165134429932</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7047176361084</t>
+    <t xml:space="preserve">23.7047157287598</t>
   </si>
   <si>
     <t xml:space="preserve">23.5606155395508</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2363834381104</t>
+    <t xml:space="preserve">23.2363872528076</t>
   </si>
   <si>
     <t xml:space="preserve">23.4345264434814</t>
@@ -1934,13 +1934,13 @@
     <t xml:space="preserve">21.7053070068359</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8226871490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3630657196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2369747161865</t>
+    <t xml:space="preserve">20.8226852416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3630638122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2369766235352</t>
   </si>
   <si>
     <t xml:space="preserve">21.3450527191162</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">19.7239093780518</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3189182281494</t>
+    <t xml:space="preserve">18.318920135498</t>
   </si>
   <si>
     <t xml:space="preserve">18.2828941345215</t>
@@ -1961,40 +1961,40 @@
     <t xml:space="preserve">19.5437831878662</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8773097991943</t>
+    <t xml:space="preserve">18.877311706543</t>
   </si>
   <si>
     <t xml:space="preserve">18.3909683227539</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0034008026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.003698348999</t>
+    <t xml:space="preserve">19.0033988952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0036964416504</t>
   </si>
   <si>
     <t xml:space="preserve">17.139087677002</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1120700836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2651748657227</t>
+    <t xml:space="preserve">17.1120662689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2651767730713</t>
   </si>
   <si>
     <t xml:space="preserve">16.6617488861084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2024269104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9502477645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7160844802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6800584793091</t>
+    <t xml:space="preserve">16.2024250030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9502487182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.71608543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6800575256348</t>
   </si>
   <si>
     <t xml:space="preserve">15.6170129776001</t>
@@ -2003,25 +2003,25 @@
     <t xml:space="preserve">16.1573944091797</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6077136993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4005661010742</t>
+    <t xml:space="preserve">16.6077117919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4005641937256</t>
   </si>
   <si>
     <t xml:space="preserve">17.4723205566406</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5533790588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4906272888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9406509399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8232746124268</t>
+    <t xml:space="preserve">17.5533771514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.490629196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.94065284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8232727050781</t>
   </si>
   <si>
     <t xml:space="preserve">17.6614570617676</t>
@@ -2033,19 +2033,19 @@
     <t xml:space="preserve">16.0132942199707</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9052171707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2654685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1934185028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7250881195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4008626937866</t>
+    <t xml:space="preserve">15.905216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2654705047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1934204101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7250900268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.400860786438</t>
   </si>
   <si>
     <t xml:space="preserve">15.0496120452881</t>
@@ -2054,16 +2054,16 @@
     <t xml:space="preserve">14.752402305603</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5899925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1486835479736</t>
+    <t xml:space="preserve">15.5899953842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1486825942993</t>
   </si>
   <si>
     <t xml:space="preserve">15.463906288147</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1661071777344</t>
+    <t xml:space="preserve">17.1661052703857</t>
   </si>
   <si>
     <t xml:space="preserve">17.7875442504883</t>
@@ -2072,34 +2072,34 @@
     <t xml:space="preserve">18.1568031311035</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6434440612793</t>
+    <t xml:space="preserve">17.6434421539307</t>
   </si>
   <si>
     <t xml:space="preserve">17.391263961792</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0127048492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0487270355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2288570404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0307159423828</t>
+    <t xml:space="preserve">18.0127010345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0487289428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2288551330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0307178497314</t>
   </si>
   <si>
     <t xml:space="preserve">17.9226379394531</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4543056488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6791706085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8052616119385</t>
+    <t xml:space="preserve">17.454309463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6791725158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8052635192871</t>
   </si>
   <si>
     <t xml:space="preserve">18.6251354217529</t>
@@ -2108,7 +2108,7 @@
     <t xml:space="preserve">18.3369312286377</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9493637084961</t>
+    <t xml:space="preserve">18.9493656158447</t>
   </si>
   <si>
     <t xml:space="preserve">18.7872486114502</t>
@@ -2117,13 +2117,13 @@
     <t xml:space="preserve">18.6971874237061</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3549423217773</t>
+    <t xml:space="preserve">18.354944229126</t>
   </si>
   <si>
     <t xml:space="preserve">18.4269943237305</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9856815338135</t>
+    <t xml:space="preserve">17.9856834411621</t>
   </si>
   <si>
     <t xml:space="preserve">17.3552379608154</t>
@@ -2132,13 +2132,13 @@
     <t xml:space="preserve">17.7244987487793</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3009052276611</t>
+    <t xml:space="preserve">18.3009071350098</t>
   </si>
   <si>
     <t xml:space="preserve">18.6071224212646</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3996810913086</t>
+    <t xml:space="preserve">19.3996829986572</t>
   </si>
   <si>
     <t xml:space="preserve">19.6698722839355</t>
@@ -2147,28 +2147,28 @@
     <t xml:space="preserve">20.2462768554688</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0661487579346</t>
+    <t xml:space="preserve">20.0661506652832</t>
   </si>
   <si>
     <t xml:space="preserve">19.9220504760742</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4176921844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4537181854248</t>
+    <t xml:space="preserve">19.4176902770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4537200927734</t>
   </si>
   <si>
     <t xml:space="preserve">20.2823028564453</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7515163421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7425136566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7965507507324</t>
+    <t xml:space="preserve">17.7515182495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7425117492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7965526580811</t>
   </si>
   <si>
     <t xml:space="preserve">17.5083465576172</t>
@@ -2177,10 +2177,10 @@
     <t xml:space="preserve">17.4182834625244</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8508834838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9859771728516</t>
+    <t xml:space="preserve">16.8508815765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9859790802002</t>
   </si>
   <si>
     <t xml:space="preserve">16.868896484375</t>
@@ -2189,25 +2189,25 @@
     <t xml:space="preserve">17.0490245819092</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9409484863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3462333679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2741813659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3822593688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2831859588623</t>
+    <t xml:space="preserve">16.9409465789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3462314605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2741832733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3822574615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2831878662109</t>
   </si>
   <si>
     <t xml:space="preserve">18.1748180389404</t>
   </si>
   <si>
-    <t xml:space="preserve">17.976676940918</t>
+    <t xml:space="preserve">17.9766750335693</t>
   </si>
   <si>
     <t xml:space="preserve">17.6164226531982</t>
@@ -2219,25 +2219,25 @@
     <t xml:space="preserve">18.1387901306152</t>
   </si>
   <si>
-    <t xml:space="preserve">17.913631439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6974811553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1928291320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9496574401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2381553649902</t>
+    <t xml:space="preserve">17.9136333465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6974792480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1928310394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9496593475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2381534576416</t>
   </si>
   <si>
     <t xml:space="preserve">17.1300811767578</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6794681549072</t>
+    <t xml:space="preserve">17.6794662475586</t>
   </si>
   <si>
     <t xml:space="preserve">17.9676704406738</t>
@@ -2255,16 +2255,16 @@
     <t xml:space="preserve">17.5173530578613</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6074180603027</t>
+    <t xml:space="preserve">17.6074142456055</t>
   </si>
   <si>
     <t xml:space="preserve">17.5894069671631</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7695293426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6365566253662</t>
+    <t xml:space="preserve">17.76953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6365585327148</t>
   </si>
   <si>
     <t xml:space="preserve">17.24342918396</t>
@@ -2273,31 +2273,31 @@
     <t xml:space="preserve">16.6621894836426</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2249755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5330238342285</t>
+    <t xml:space="preserve">17.2249774932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5330257415771</t>
   </si>
   <si>
     <t xml:space="preserve">16.1916618347168</t>
   </si>
   <si>
-    <t xml:space="preserve">15.684229850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6232404708862</t>
+    <t xml:space="preserve">15.6842308044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6232395172119</t>
   </si>
   <si>
     <t xml:space="preserve">13.8021240234375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9405136108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7836723327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3131446838379</t>
+    <t xml:space="preserve">13.9405145645142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7836713790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3131456375122</t>
   </si>
   <si>
     <t xml:space="preserve">13.8943843841553</t>
@@ -2315,22 +2315,22 @@
     <t xml:space="preserve">13.0732688903809</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0179119110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.303918838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3777284622192</t>
+    <t xml:space="preserve">13.0179128646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3039178848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3777275085449</t>
   </si>
   <si>
     <t xml:space="preserve">13.1009464263916</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1378507614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.922061920166</t>
+    <t xml:space="preserve">13.1378517150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9220628738403</t>
   </si>
   <si>
     <t xml:space="preserve">13.7006378173828</t>
@@ -2342,46 +2342,46 @@
     <t xml:space="preserve">14.4202671051025</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5771112442017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8298015594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7928991317749</t>
+    <t xml:space="preserve">14.577109336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8298025131226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7928981781006</t>
   </si>
   <si>
     <t xml:space="preserve">13.6914119720459</t>
   </si>
   <si>
-    <t xml:space="preserve">14.512526512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1803913116455</t>
+    <t xml:space="preserve">14.5125274658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1803903579712</t>
   </si>
   <si>
     <t xml:space="preserve">11.0988998413086</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7575378417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1486206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2132034301758</t>
+    <t xml:space="preserve">10.7575368881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1486196517944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2132024765015</t>
   </si>
   <si>
     <t xml:space="preserve">10.4069490432739</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4161758422852</t>
+    <t xml:space="preserve">10.4161748886108</t>
   </si>
   <si>
     <t xml:space="preserve">10.5914688110352</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8590259552002</t>
+    <t xml:space="preserve">10.8590240478516</t>
   </si>
   <si>
     <t xml:space="preserve">10.9236068725586</t>
@@ -2390,22 +2390,22 @@
     <t xml:space="preserve">10.4807567596436</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6837291717529</t>
+    <t xml:space="preserve">10.6837301254272</t>
   </si>
   <si>
     <t xml:space="preserve">10.5361137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2962369918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3700437545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0471353530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1762981414795</t>
+    <t xml:space="preserve">10.296236038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3700456619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0471343994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1762990951538</t>
   </si>
   <si>
     <t xml:space="preserve">9.9087438583374</t>
@@ -2414,10 +2414,10 @@
     <t xml:space="preserve">9.65964221954346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53047657012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0932636260986</t>
+    <t xml:space="preserve">9.53047752380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0932655334473</t>
   </si>
   <si>
     <t xml:space="preserve">10.4899835586548</t>
@@ -2426,19 +2426,19 @@
     <t xml:space="preserve">10.5730171203613</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4254016876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5176601409912</t>
+    <t xml:space="preserve">10.4254007339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5176610946655</t>
   </si>
   <si>
     <t xml:space="preserve">10.3054628372192</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4438533782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6652774810791</t>
+    <t xml:space="preserve">10.4438524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6652793884277</t>
   </si>
   <si>
     <t xml:space="preserve">10.0286827087402</t>
@@ -2459,16 +2459,16 @@
     <t xml:space="preserve">9.29060077667236</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5766077041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21217823028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40131282806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43821716308594</t>
+    <t xml:space="preserve">9.57660675048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21217918395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40131378173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43821620941162</t>
   </si>
   <si>
     <t xml:space="preserve">9.47512149810791</t>
@@ -2477,16 +2477,16 @@
     <t xml:space="preserve">9.20295333862305</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94001293182373</t>
+    <t xml:space="preserve">8.94001197814941</t>
   </si>
   <si>
     <t xml:space="preserve">8.9861421585083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88004398345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53970336914062</t>
+    <t xml:space="preserve">8.88004302978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53970432281494</t>
   </si>
   <si>
     <t xml:space="preserve">9.24447154998779</t>
@@ -2495,34 +2495,34 @@
     <t xml:space="preserve">9.28137493133545</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11530590057373</t>
+    <t xml:space="preserve">9.11530685424805</t>
   </si>
   <si>
     <t xml:space="preserve">9.88106536865234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97332668304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99177837371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2408809661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4346284866333</t>
+    <t xml:space="preserve">9.97332763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99177742004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2408819198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.434627532959</t>
   </si>
   <si>
     <t xml:space="preserve">10.084038734436</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1024894714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61351203918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66886615753174</t>
+    <t xml:space="preserve">10.1024904251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61351108551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66886711120605</t>
   </si>
   <si>
     <t xml:space="preserve">9.5212516784668</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">9.56738185882568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2629222869873</t>
+    <t xml:space="preserve">9.26292324066162</t>
   </si>
   <si>
     <t xml:space="preserve">9.39208698272705</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">9.65041637420654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31827831268311</t>
+    <t xml:space="preserve">9.31827926635742</t>
   </si>
   <si>
     <t xml:space="preserve">9.71499729156494</t>
@@ -2552,19 +2552,19 @@
     <t xml:space="preserve">9.81648445129395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68731880187988</t>
+    <t xml:space="preserve">9.6873197555542</t>
   </si>
   <si>
     <t xml:space="preserve">9.98255252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75190258026123</t>
+    <t xml:space="preserve">9.7519006729126</t>
   </si>
   <si>
     <t xml:space="preserve">9.49357318878174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2777853012085</t>
+    <t xml:space="preserve">10.2777843475342</t>
   </si>
   <si>
     <t xml:space="preserve">10.0655860900879</t>
@@ -2573,7 +2573,7 @@
     <t xml:space="preserve">10.5822429656982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7298593521118</t>
+    <t xml:space="preserve">10.7298603057861</t>
   </si>
   <si>
     <t xml:space="preserve">10.2870101928711</t>
@@ -2585,19 +2585,19 @@
     <t xml:space="preserve">10.3515939712524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.431037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6340093612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2337007522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9938230514526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1322135925293</t>
+    <t xml:space="preserve">11.4310369491577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6340103149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2337017059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.993824005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1322145462036</t>
   </si>
   <si>
     <t xml:space="preserve">12.0860843658447</t>
@@ -2606,13 +2606,13 @@
     <t xml:space="preserve">12.1414403915405</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1875705718994</t>
+    <t xml:space="preserve">12.1875715255737</t>
   </si>
   <si>
     <t xml:space="preserve">11.9661474227905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9569206237793</t>
+    <t xml:space="preserve">11.956919670105</t>
   </si>
   <si>
     <t xml:space="preserve">11.7539482116699</t>
@@ -2627,13 +2627,13 @@
     <t xml:space="preserve">12.0676326751709</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4551248550415</t>
+    <t xml:space="preserve">12.4551258087158</t>
   </si>
   <si>
     <t xml:space="preserve">13.2577886581421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2485628128052</t>
+    <t xml:space="preserve">13.2485637664795</t>
   </si>
   <si>
     <t xml:space="preserve">13.0824947357178</t>
@@ -2645,43 +2645,43 @@
     <t xml:space="preserve">13.4054040908813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2024326324463</t>
+    <t xml:space="preserve">13.2024335861206</t>
   </si>
   <si>
     <t xml:space="preserve">13.7559938430786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7098627090454</t>
+    <t xml:space="preserve">13.7098636627197</t>
   </si>
   <si>
     <t xml:space="preserve">13.7744464874268</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3408231735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7190895080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7283153533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0143222808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1342601776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1250343322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9497413635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6637344360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6821851730347</t>
+    <t xml:space="preserve">13.3408222198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7190885543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7283163070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0143213272095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.134259223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1250352859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9497404098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6637353897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.682186126709</t>
   </si>
   <si>
     <t xml:space="preserve">14.4571714401245</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">14.1158084869385</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8482542037964</t>
+    <t xml:space="preserve">13.8482532501221</t>
   </si>
   <si>
     <t xml:space="preserve">14.0512256622314</t>
@@ -2702,13 +2702,13 @@
     <t xml:space="preserve">13.9312887191772</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6473264694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7303609848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0865859985352</t>
+    <t xml:space="preserve">15.6473274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7303619384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0865879058838</t>
   </si>
   <si>
     <t xml:space="preserve">16.7913551330566</t>
@@ -2717,31 +2717,31 @@
     <t xml:space="preserve">16.8651638031006</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7452239990234</t>
+    <t xml:space="preserve">16.7452220916748</t>
   </si>
   <si>
     <t xml:space="preserve">16.8190307617188</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1086254119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.997917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9333333969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4720325469971</t>
+    <t xml:space="preserve">16.1086292266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9979152679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9333343505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4720344543457</t>
   </si>
   <si>
     <t xml:space="preserve">14.6785955429077</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3187808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8446645736694</t>
+    <t xml:space="preserve">14.3187818527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8446636199951</t>
   </si>
   <si>
     <t xml:space="preserve">15.2967386245728</t>
@@ -2753,64 +2753,64 @@
     <t xml:space="preserve">14.7247257232666</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8538913726807</t>
+    <t xml:space="preserve">14.8538904190063</t>
   </si>
   <si>
     <t xml:space="preserve">15.1491222381592</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2506103515625</t>
+    <t xml:space="preserve">15.2506093978882</t>
   </si>
   <si>
     <t xml:space="preserve">14.9830532073975</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1583480834961</t>
+    <t xml:space="preserve">15.1583490371704</t>
   </si>
   <si>
     <t xml:space="preserve">15.0753154754639</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1065816879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6027412414551</t>
+    <t xml:space="preserve">14.1065835952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6027421951294</t>
   </si>
   <si>
     <t xml:space="preserve">12.0399541854858</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9753723144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5878791809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.301872253418</t>
+    <t xml:space="preserve">11.9753713607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5878801345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3018732070923</t>
   </si>
   <si>
     <t xml:space="preserve">10.6006956100464</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1301679611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30905342102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06353950500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97589445114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8928599357605</t>
+    <t xml:space="preserve">10.1301670074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30905246734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0635404586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97589302062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89285898208618</t>
   </si>
   <si>
     <t xml:space="preserve">6.5504732131958</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93796634674072</t>
+    <t xml:space="preserve">6.93796586990356</t>
   </si>
   <si>
     <t xml:space="preserve">6.90567541122437</t>
@@ -2819,79 +2819,79 @@
     <t xml:space="preserve">6.98409652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91028738021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01177453994751</t>
+    <t xml:space="preserve">6.91028833389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01177406311035</t>
   </si>
   <si>
     <t xml:space="preserve">7.47307586669922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05431270599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85697746276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33673191070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01382160186768</t>
+    <t xml:space="preserve">8.05431461334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85697937011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33673095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01382064819336</t>
   </si>
   <si>
     <t xml:space="preserve">8.39567756652832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40029048919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34954643249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25728607177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.118896484375</t>
+    <t xml:space="preserve">8.40028953552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34954738616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25728702545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11889743804932</t>
   </si>
   <si>
     <t xml:space="preserve">7.74985551834106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.929762840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78675937652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1096715927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84211492538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42694568634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28855562210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26087617874146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32545900344849</t>
+    <t xml:space="preserve">7.92976331710815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78675985336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10966968536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84211540222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42694520950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28855466842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26087665557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32545948028564</t>
   </si>
   <si>
     <t xml:space="preserve">7.3346848487854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1132607460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55610942840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77753353118896</t>
+    <t xml:space="preserve">7.11326026916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5561089515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77753448486328</t>
   </si>
   <si>
     <t xml:space="preserve">7.93437623977661</t>
@@ -2903,31 +2903,31 @@
     <t xml:space="preserve">7.33929777145386</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51920509338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3070068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14555168151855</t>
+    <t xml:space="preserve">7.51920461654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30700731277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14555072784424</t>
   </si>
   <si>
     <t xml:space="preserve">7.10403442382812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15939044952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06713008880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92874050140381</t>
+    <t xml:space="preserve">7.15939092636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06712961196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92874002456665</t>
   </si>
   <si>
     <t xml:space="preserve">7.56533479690552</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54227113723755</t>
+    <t xml:space="preserve">7.54227018356323</t>
   </si>
   <si>
     <t xml:space="preserve">7.445396900177</t>
@@ -2936,46 +2936,46 @@
     <t xml:space="preserve">7.27010250091553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72217798233032</t>
+    <t xml:space="preserve">7.72217750549316</t>
   </si>
   <si>
     <t xml:space="preserve">8.46948528289795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66784572601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90310668945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54329299926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69090938568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8754301071167</t>
+    <t xml:space="preserve">8.66784477233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90310764312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54329395294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69091033935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87543106079102</t>
   </si>
   <si>
     <t xml:space="preserve">9.32750415802002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0066394805908</t>
+    <t xml:space="preserve">11.0066404342651</t>
   </si>
   <si>
     <t xml:space="preserve">11.4863929748535</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4956188201904</t>
+    <t xml:space="preserve">11.4956197738647</t>
   </si>
   <si>
     <t xml:space="preserve">11.2557430267334</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9420576095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82570934295654</t>
+    <t xml:space="preserve">10.9420585632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82571029663086</t>
   </si>
   <si>
     <t xml:space="preserve">9.74267578125</t>
@@ -2993,10 +2993,10 @@
     <t xml:space="preserve">9.89029216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3792705535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.360818862915</t>
+    <t xml:space="preserve">10.3792715072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3608179092407</t>
   </si>
   <si>
     <t xml:space="preserve">10.2224292755127</t>
@@ -3008,31 +3008,31 @@
     <t xml:space="preserve">10.5453395843506</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7667636871338</t>
+    <t xml:space="preserve">10.7667646408081</t>
   </si>
   <si>
     <t xml:space="preserve">12.0215015411377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4402627944946</t>
+    <t xml:space="preserve">11.4402637481689</t>
   </si>
   <si>
     <t xml:space="preserve">11.5417499542236</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6155576705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8093032836914</t>
+    <t xml:space="preserve">11.6155586242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8093042373657</t>
   </si>
   <si>
     <t xml:space="preserve">11.8185300827026</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7078170776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6616888046265</t>
+    <t xml:space="preserve">11.7078161239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6616868972778</t>
   </si>
   <si>
     <t xml:space="preserve">11.5694274902344</t>
@@ -3041,16 +3041,16 @@
     <t xml:space="preserve">11.3480033874512</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2741956710815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1450300216675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.812894821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0030498504639</t>
+    <t xml:space="preserve">11.2741947174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1450309753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8128938674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0030508041382</t>
   </si>
   <si>
     <t xml:space="preserve">12.3167352676392</t>
@@ -3065,13 +3065,13 @@
     <t xml:space="preserve">13.0548162460327</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3961791992188</t>
+    <t xml:space="preserve">13.3961801528931</t>
   </si>
   <si>
     <t xml:space="preserve">13.2854671478271</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4423093795776</t>
+    <t xml:space="preserve">13.4423084259033</t>
   </si>
   <si>
     <t xml:space="preserve">13.1286239624023</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">13.2301111221313</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0086870193481</t>
+    <t xml:space="preserve">13.0086860656738</t>
   </si>
   <si>
     <t xml:space="preserve">13.1932067871094</t>
@@ -3092,25 +3092,25 @@
     <t xml:space="preserve">13.3500499725342</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5714740753174</t>
+    <t xml:space="preserve">13.5714731216431</t>
   </si>
   <si>
     <t xml:space="preserve">13.368501663208</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1470775604248</t>
+    <t xml:space="preserve">13.1470766067505</t>
   </si>
   <si>
     <t xml:space="preserve">13.4976654052734</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1101722717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1655302047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.267014503479</t>
+    <t xml:space="preserve">13.1101732254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1655282974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2670154571533</t>
   </si>
   <si>
     <t xml:space="preserve">13.2762413024902</t>
@@ -3119,13 +3119,13 @@
     <t xml:space="preserve">13.0455904006958</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1747550964355</t>
+    <t xml:space="preserve">13.1747541427612</t>
   </si>
   <si>
     <t xml:space="preserve">13.331597328186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3869543075562</t>
+    <t xml:space="preserve">13.3869533538818</t>
   </si>
   <si>
     <t xml:space="preserve">12.5104818344116</t>
@@ -3137,13 +3137,13 @@
     <t xml:space="preserve">12.6304187774658</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3351879119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7872619628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5068912506104</t>
+    <t xml:space="preserve">12.3351860046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7872610092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5068922042847</t>
   </si>
   <si>
     <t xml:space="preserve">13.4330835342407</t>
@@ -3155,25 +3155,25 @@
     <t xml:space="preserve">15.2690601348877</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5735187530518</t>
+    <t xml:space="preserve">15.5735197067261</t>
   </si>
   <si>
     <t xml:space="preserve">15.8318471908569</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1455326080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3613214492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4628076553345</t>
+    <t xml:space="preserve">16.1455307006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3613204956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4628086090088</t>
   </si>
   <si>
     <t xml:space="preserve">14.7616300582886</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5217523574829</t>
+    <t xml:space="preserve">14.5217533111572</t>
   </si>
   <si>
     <t xml:space="preserve">14.5955619812012</t>
@@ -3182,55 +3182,55 @@
     <t xml:space="preserve">14.7154998779297</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3556852340698</t>
+    <t xml:space="preserve">14.3556861877441</t>
   </si>
   <si>
     <t xml:space="preserve">13.9128351211548</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6545085906982</t>
+    <t xml:space="preserve">13.6545076370239</t>
   </si>
   <si>
     <t xml:space="preserve">14.5033025741577</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4110412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.650918006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1860256195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6750068664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4166765213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1029949188232</t>
+    <t xml:space="preserve">14.4110403060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6509189605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1860265731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6750049591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.416675567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1029930114746</t>
   </si>
   <si>
     <t xml:space="preserve">14.9184722900391</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3890018463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7764930725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.582745552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1547603607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8133983612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8410720825195</t>
+    <t xml:space="preserve">15.3889989852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7764921188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5827445983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1547565460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8133955001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8410749435425</t>
   </si>
   <si>
     <t xml:space="preserve">15.924108505249</t>
@@ -3242,61 +3242,61 @@
     <t xml:space="preserve">15.8503007888794</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8779773712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3520956039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6381034851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4351272583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5919704437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9517889022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0994033813477</t>
+    <t xml:space="preserve">15.8779783248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3520946502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6381015777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4351291656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5919713973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9517860412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0994052886963</t>
   </si>
   <si>
     <t xml:space="preserve">16.0717258453369</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5145721435547</t>
+    <t xml:space="preserve">16.5145740509033</t>
   </si>
   <si>
     <t xml:space="preserve">17.7877635955811</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3910446166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4648532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1142635345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2618808746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5386619567871</t>
+    <t xml:space="preserve">17.3910465240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4648551940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1142654418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2618770599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5386600494385</t>
   </si>
   <si>
     <t xml:space="preserve">17.4464015960693</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5663414001465</t>
+    <t xml:space="preserve">17.5663394927979</t>
   </si>
   <si>
     <t xml:space="preserve">17.3725929260254</t>
   </si>
   <si>
-    <t xml:space="preserve">17.621696472168</t>
+    <t xml:space="preserve">17.6216983795166</t>
   </si>
   <si>
     <t xml:space="preserve">17.547887802124</t>
@@ -3311,31 +3311,31 @@
     <t xml:space="preserve">18.7657241821289</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9835567474365</t>
+    <t xml:space="preserve">19.9835548400879</t>
   </si>
   <si>
     <t xml:space="preserve">19.4299945831299</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4484481811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.728816986084</t>
+    <t xml:space="preserve">19.4484462738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7288188934326</t>
   </si>
   <si>
     <t xml:space="preserve">19.245475769043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1901187896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3377323150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2639274597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5442962646484</t>
+    <t xml:space="preserve">19.1901168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3377342224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2639255523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5443000793457</t>
   </si>
   <si>
     <t xml:space="preserve">18.5627498626709</t>
@@ -3344,13 +3344,13 @@
     <t xml:space="preserve">18.2029342651367</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4704914093018</t>
+    <t xml:space="preserve">18.4704895019531</t>
   </si>
   <si>
     <t xml:space="preserve">17.9722843170166</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1844844818115</t>
+    <t xml:space="preserve">18.1844806671143</t>
   </si>
   <si>
     <t xml:space="preserve">19.2823791503906</t>
@@ -3362,10 +3362,10 @@
     <t xml:space="preserve">20.6109256744385</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9430618286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2567501068115</t>
+    <t xml:space="preserve">20.9430637359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2567481994629</t>
   </si>
   <si>
     <t xml:space="preserve">21.2198429107666</t>
@@ -3383,7 +3383,7 @@
     <t xml:space="preserve">22.7698135375977</t>
   </si>
   <si>
-    <t xml:space="preserve">22.290060043335</t>
+    <t xml:space="preserve">22.2900619506836</t>
   </si>
   <si>
     <t xml:space="preserve">21.8472137451172</t>
@@ -3392,25 +3392,25 @@
     <t xml:space="preserve">22.4745826721191</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7180519104004</t>
+    <t xml:space="preserve">21.7180480957031</t>
   </si>
   <si>
     <t xml:space="preserve">20.5371170043945</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6293773651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7216377258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1865272521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1275825500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6847343444824</t>
+    <t xml:space="preserve">20.6293792724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7216358184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1865310668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1275806427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6847324371338</t>
   </si>
   <si>
     <t xml:space="preserve">21.2013912200928</t>
@@ -3425,7 +3425,7 @@
     <t xml:space="preserve">20.6478290557861</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8508033752441</t>
+    <t xml:space="preserve">20.8508014678955</t>
   </si>
   <si>
     <t xml:space="preserve">21.0906791687012</t>
@@ -3434,10 +3434,10 @@
     <t xml:space="preserve">21.109130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2234325408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9466533660889</t>
+    <t xml:space="preserve">20.2234344482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9466552734375</t>
   </si>
   <si>
     <t xml:space="preserve">20.1311721801758</t>
@@ -3446,7 +3446,7 @@
     <t xml:space="preserve">20.112720489502</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6145153045654</t>
+    <t xml:space="preserve">19.6145172119141</t>
   </si>
   <si>
     <t xml:space="preserve">19.8543930053711</t>
@@ -3455,19 +3455,19 @@
     <t xml:space="preserve">20.7954483032227</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3156929016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8323516845703</t>
+    <t xml:space="preserve">20.31569480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8323497772217</t>
   </si>
   <si>
     <t xml:space="preserve">22.179349899292</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5483913421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0686378479004</t>
+    <t xml:space="preserve">22.5483894348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0686359405518</t>
   </si>
   <si>
     <t xml:space="preserve">22.2162532806396</t>
@@ -3476,7 +3476,7 @@
     <t xml:space="preserve">22.1424446105957</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0132789611816</t>
+    <t xml:space="preserve">22.0132808685303</t>
   </si>
   <si>
     <t xml:space="preserve">22.2531585693359</t>
@@ -3491,13 +3491,13 @@
     <t xml:space="preserve">23.7846775054932</t>
   </si>
   <si>
-    <t xml:space="preserve">23.729320526123</t>
+    <t xml:space="preserve">23.7293186187744</t>
   </si>
   <si>
     <t xml:space="preserve">24.3935928344727</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8953876495361</t>
+    <t xml:space="preserve">23.8953895568848</t>
   </si>
   <si>
     <t xml:space="preserve">23.046594619751</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">23.3971843719482</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5817012786865</t>
+    <t xml:space="preserve">23.5817031860352</t>
   </si>
   <si>
     <t xml:space="preserve">23.1388549804688</t>
@@ -3530,16 +3530,16 @@
     <t xml:space="preserve">23.4894428253174</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7477741241455</t>
+    <t xml:space="preserve">23.7477722167969</t>
   </si>
   <si>
     <t xml:space="preserve">23.7662239074707</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2311153411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7144584655762</t>
+    <t xml:space="preserve">23.2311172485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7144603729248</t>
   </si>
   <si>
     <t xml:space="preserve">23.6370601654053</t>
@@ -3548,16 +3548,16 @@
     <t xml:space="preserve">25.0763206481934</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7554569244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4786758422852</t>
+    <t xml:space="preserve">26.7554550170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4786739349365</t>
   </si>
   <si>
     <t xml:space="preserve">26.976879119873</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1614017486572</t>
+    <t xml:space="preserve">27.1613998413086</t>
   </si>
   <si>
     <t xml:space="preserve">27.3828239440918</t>
@@ -3569,13 +3569,13 @@
     <t xml:space="preserve">28.1578102111816</t>
   </si>
   <si>
-    <t xml:space="preserve">28.04709815979</t>
+    <t xml:space="preserve">28.0470962524414</t>
   </si>
   <si>
     <t xml:space="preserve">27.2721099853516</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5673446655273</t>
+    <t xml:space="preserve">27.5673427581787</t>
   </si>
   <si>
     <t xml:space="preserve">27.4012756347656</t>
@@ -3587,16 +3587,16 @@
     <t xml:space="preserve">26.9030704498291</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4971256256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9251155853271</t>
+    <t xml:space="preserve">26.497127532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9251136779785</t>
   </si>
   <si>
     <t xml:space="preserve">25.7221393585205</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6447410583496</t>
+    <t xml:space="preserve">26.644739151001</t>
   </si>
   <si>
     <t xml:space="preserve">26.4602222442627</t>
@@ -3605,10 +3605,10 @@
     <t xml:space="preserve">26.3864135742188</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9989204406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5007171630859</t>
+    <t xml:space="preserve">25.9989223480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5007133483887</t>
   </si>
   <si>
     <t xml:space="preserve">25.9066619873047</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">26.6631946563721</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3310604095459</t>
+    <t xml:space="preserve">26.3310565948486</t>
   </si>
   <si>
     <t xml:space="preserve">26.5155773162842</t>
@@ -3641,13 +3641,13 @@
     <t xml:space="preserve">26.7185497283936</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8292617797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4417686462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.534029006958</t>
+    <t xml:space="preserve">26.8292636871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4417705535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5340309143066</t>
   </si>
   <si>
     <t xml:space="preserve">25.4269065856934</t>
@@ -3662,16 +3662,16 @@
     <t xml:space="preserve">27.1983032226562</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4750843048096</t>
+    <t xml:space="preserve">27.4750823974609</t>
   </si>
   <si>
     <t xml:space="preserve">28.914342880249</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4643154144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9625225067139</t>
+    <t xml:space="preserve">30.4643135070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9625205993652</t>
   </si>
   <si>
     <t xml:space="preserve">29.5970706939697</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">27.0322341918945</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8846187591553</t>
+    <t xml:space="preserve">26.8846168518066</t>
   </si>
   <si>
     <t xml:space="preserve">27.3459186553955</t>
@@ -3689,19 +3689,19 @@
     <t xml:space="preserve">27.6227016448975</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7923583984375</t>
+    <t xml:space="preserve">26.7923603057861</t>
   </si>
   <si>
     <t xml:space="preserve">26.9399757385254</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1798515319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8994827270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5857982635498</t>
+    <t xml:space="preserve">27.1798496246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8994808197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5857963562012</t>
   </si>
   <si>
     <t xml:space="preserve">27.2352066040039</t>
@@ -3710,10 +3710,10 @@
     <t xml:space="preserve">27.2167549133301</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3643703460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6262893676758</t>
+    <t xml:space="preserve">27.364372253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6262912750244</t>
   </si>
   <si>
     <t xml:space="preserve">27.2536602020264</t>
@@ -3722,40 +3722,40 @@
     <t xml:space="preserve">27.7703170776367</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3090171813965</t>
+    <t xml:space="preserve">27.3090152740479</t>
   </si>
   <si>
     <t xml:space="preserve">27.9548377990723</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6744651794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0286445617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8072185516357</t>
+    <t xml:space="preserve">28.674467086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0286426544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8072204589844</t>
   </si>
   <si>
     <t xml:space="preserve">28.3423290252686</t>
   </si>
   <si>
-    <t xml:space="preserve">27.917932510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6965084075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0506858825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7518653869629</t>
+    <t xml:space="preserve">27.9179344177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6965065002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.050687789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7518634796143</t>
   </si>
   <si>
     <t xml:space="preserve">27.8256702423096</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9732894897461</t>
+    <t xml:space="preserve">27.9732875823975</t>
   </si>
   <si>
     <t xml:space="preserve">28.3054256439209</t>
@@ -3764,115 +3764,115 @@
     <t xml:space="preserve">28.2869720458984</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0840015411377</t>
+    <t xml:space="preserve">28.0840034484863</t>
   </si>
   <si>
     <t xml:space="preserve">27.7887687683105</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2941551208496</t>
+    <t xml:space="preserve">26.294153213501</t>
   </si>
   <si>
     <t xml:space="preserve">26.9953308105469</t>
   </si>
   <si>
-    <t xml:space="preserve">26.220344543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5191669464111</t>
+    <t xml:space="preserve">26.2203464508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5191688537598</t>
   </si>
   <si>
     <t xml:space="preserve">24.6150188446045</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0983619689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9656066894531</t>
+    <t xml:space="preserve">24.0983638763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9656047821045</t>
   </si>
   <si>
     <t xml:space="preserve">24.356689453125</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7108688354492</t>
+    <t xml:space="preserve">23.7108707427979</t>
   </si>
   <si>
     <t xml:space="preserve">23.3418273925781</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2680187225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0614566802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2090740203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7441825866699</t>
+    <t xml:space="preserve">23.2680206298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0614585876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2090721130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7441806793213</t>
   </si>
   <si>
     <t xml:space="preserve">24.6334705352783</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2423858642578</t>
+    <t xml:space="preserve">25.2423877716064</t>
   </si>
   <si>
     <t xml:space="preserve">25.0947704315186</t>
   </si>
   <si>
-    <t xml:space="preserve">24.910249710083</t>
+    <t xml:space="preserve">24.9102516174316</t>
   </si>
   <si>
     <t xml:space="preserve">24.984058380127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8179874420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1870288848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6703758239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5376205444336</t>
+    <t xml:space="preserve">24.8179912567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1870307922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6703720092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.537618637085</t>
   </si>
   <si>
     <t xml:space="preserve">24.8733444213867</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9287033081055</t>
+    <t xml:space="preserve">24.9287052154541</t>
   </si>
   <si>
     <t xml:space="preserve">24.8364410400391</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2644271850586</t>
+    <t xml:space="preserve">24.2644290924072</t>
   </si>
   <si>
     <t xml:space="preserve">24.3013343811035</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8769359588623</t>
+    <t xml:space="preserve">23.8769340515137</t>
   </si>
   <si>
     <t xml:space="preserve">23.5263481140137</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1573047637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8656635284424</t>
+    <t xml:space="preserve">23.1573066711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8656673431396</t>
   </si>
   <si>
     <t xml:space="preserve">21.8287601470947</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8841152191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0353202819824</t>
+    <t xml:space="preserve">21.8841171264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0353221893311</t>
   </si>
   <si>
     <t xml:space="preserve">20.7031879425049</t>
@@ -3881,19 +3881,19 @@
     <t xml:space="preserve">21.736499786377</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4597187042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5335273742676</t>
+    <t xml:space="preserve">21.4597206115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5335292816162</t>
   </si>
   <si>
     <t xml:space="preserve">22.6591014862061</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4412670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.352596282959</t>
+    <t xml:space="preserve">21.4412651062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3525981903076</t>
   </si>
   <si>
     <t xml:space="preserve">20.9799671173096</t>
@@ -3902,7 +3902,7 @@
     <t xml:space="preserve">21.9948291778564</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5299396514893</t>
+    <t xml:space="preserve">22.529935836792</t>
   </si>
   <si>
     <t xml:space="preserve">22.5114860534668</t>
@@ -3911,22 +3911,22 @@
     <t xml:space="preserve">22.6775550842285</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1204032897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8620758056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.935884475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3085136413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3859119415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3674583435059</t>
+    <t xml:space="preserve">23.1204013824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8620738983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9358825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3085117340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3859100341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3674602508545</t>
   </si>
   <si>
     <t xml:space="preserve">21.8103084564209</t>
@@ -3938,13 +3938,13 @@
     <t xml:space="preserve">20.0758171081543</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8877067565918</t>
+    <t xml:space="preserve">20.8877048492432</t>
   </si>
   <si>
     <t xml:space="preserve">20.4448585510254</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2787895202637</t>
+    <t xml:space="preserve">20.278787612915</t>
   </si>
   <si>
     <t xml:space="preserve">19.8174877166748</t>
@@ -3953,82 +3953,82 @@
     <t xml:space="preserve">20.8138980865479</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2049789428711</t>
+    <t xml:space="preserve">20.2049808502197</t>
   </si>
   <si>
     <t xml:space="preserve">20.5002136230469</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7585411071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3710498809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0204620361328</t>
+    <t xml:space="preserve">20.7585430145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3710479736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0204601287842</t>
   </si>
   <si>
     <t xml:space="preserve">18.9871463775635</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5073909759521</t>
+    <t xml:space="preserve">18.5073947906494</t>
   </si>
   <si>
     <t xml:space="preserve">17.6770515441895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1291275024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1198997497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.06813621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3633651733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0845422744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2321577072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2839221954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.370548248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.23779296875</t>
+    <t xml:space="preserve">18.1291255950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1198978424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0681343078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3633670806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0845403671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.23215675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2839241027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3705472946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2377948760986</t>
   </si>
   <si>
     <t xml:space="preserve">13.4699878692627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2172946929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0604524612427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3372325897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6878223419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8169851303101</t>
+    <t xml:space="preserve">14.2172956466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.060453414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.337233543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6878204345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8169860839844</t>
   </si>
   <si>
     <t xml:space="preserve">14.2634248733521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2541990280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6601438522339</t>
+    <t xml:space="preserve">14.2541999816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6601448059082</t>
   </si>
   <si>
     <t xml:space="preserve">15.82262134552</t>
@@ -4037,16 +4037,16 @@
     <t xml:space="preserve">15.6565532684326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0420007705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9958715438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.820574760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3649120330811</t>
+    <t xml:space="preserve">14.0420017242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9958696365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8205766677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3649110794067</t>
   </si>
   <si>
     <t xml:space="preserve">13.8667058944702</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">13.8113508224487</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8057136535645</t>
+    <t xml:space="preserve">12.8057146072388</t>
   </si>
   <si>
     <t xml:space="preserve">12.7134532928467</t>
@@ -4070,25 +4070,25 @@
     <t xml:space="preserve">14.9461517333984</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0476360321045</t>
+    <t xml:space="preserve">15.0476369857788</t>
   </si>
   <si>
     <t xml:space="preserve">15.305965423584</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3428678512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0384101867676</t>
+    <t xml:space="preserve">15.342869758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0384092330933</t>
   </si>
   <si>
     <t xml:space="preserve">15.2341136932373</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7736368179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9367227554321</t>
+    <t xml:space="preserve">14.7736358642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9367218017578</t>
   </si>
   <si>
     <t xml:space="preserve">15.349232673645</t>
@@ -4097,25 +4097,25 @@
     <t xml:space="preserve">15.4739437103271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9823894500732</t>
+    <t xml:space="preserve">15.9823884963989</t>
   </si>
   <si>
     <t xml:space="preserve">15.5410995483398</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7137765884399</t>
+    <t xml:space="preserve">15.7137775421143</t>
   </si>
   <si>
     <t xml:space="preserve">15.780930519104</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0303535461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8576774597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6466236114502</t>
+    <t xml:space="preserve">16.0303516387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8576784133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6466245651245</t>
   </si>
   <si>
     <t xml:space="preserve">15.3204526901245</t>
@@ -4124,22 +4124,22 @@
     <t xml:space="preserve">14.5529918670654</t>
   </si>
   <si>
-    <t xml:space="preserve">13.612850189209</t>
+    <t xml:space="preserve">13.6128511428833</t>
   </si>
   <si>
     <t xml:space="preserve">13.5456981658936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8430891036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9509143829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1427803039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0180683135986</t>
+    <t xml:space="preserve">13.843090057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9509153366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1427793502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0180673599243</t>
   </si>
   <si>
     <t xml:space="preserve">13.0660343170166</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">12.8070163726807</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7494564056396</t>
+    <t xml:space="preserve">12.749457359314</t>
   </si>
   <si>
     <t xml:space="preserve">12.8453893661499</t>
@@ -4163,13 +4163,13 @@
     <t xml:space="preserve">12.5959644317627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1258945465088</t>
+    <t xml:space="preserve">12.1258935928345</t>
   </si>
   <si>
     <t xml:space="preserve">11.8093156814575</t>
   </si>
   <si>
-    <t xml:space="preserve">11.780535697937</t>
+    <t xml:space="preserve">11.7805366516113</t>
   </si>
   <si>
     <t xml:space="preserve">11.5502977371216</t>
@@ -4199,10 +4199,10 @@
     <t xml:space="preserve">12.8933553695679</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1715593338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1044073104858</t>
+    <t xml:space="preserve">13.1715602874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1044082641602</t>
   </si>
   <si>
     <t xml:space="preserve">13.0948133468628</t>
@@ -4214,16 +4214,16 @@
     <t xml:space="preserve">12.4328784942627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7782363891602</t>
+    <t xml:space="preserve">12.7782354354858</t>
   </si>
   <si>
     <t xml:space="preserve">13.3058662414551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0372552871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3154592514038</t>
+    <t xml:space="preserve">13.0372543334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3154602050781</t>
   </si>
   <si>
     <t xml:space="preserve">12.4808444976807</t>
@@ -4232,7 +4232,7 @@
     <t xml:space="preserve">12.6055583953857</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1738595962524</t>
+    <t xml:space="preserve">12.1738586425781</t>
   </si>
   <si>
     <t xml:space="preserve">12.5096244812012</t>
@@ -4253,22 +4253,22 @@
     <t xml:space="preserve">12.0107755661011</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1546745300293</t>
+    <t xml:space="preserve">12.154673576355</t>
   </si>
   <si>
     <t xml:space="preserve">12.2218265533447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3081655502319</t>
+    <t xml:space="preserve">12.3081665039062</t>
   </si>
   <si>
     <t xml:space="preserve">12.1163005828857</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1834526062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8476886749268</t>
+    <t xml:space="preserve">12.1834535598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8476896286011</t>
   </si>
   <si>
     <t xml:space="preserve">12.164267539978</t>
@@ -4283,7 +4283,7 @@
     <t xml:space="preserve">11.3296527862549</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6654167175293</t>
+    <t xml:space="preserve">11.665415763855</t>
   </si>
   <si>
     <t xml:space="preserve">12.1354866027832</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">11.7421627044678</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7709436416626</t>
+    <t xml:space="preserve">11.7709426879883</t>
   </si>
   <si>
     <t xml:space="preserve">11.3488388061523</t>
@@ -4301,10 +4301,10 @@
     <t xml:space="preserve">11.4063987731934</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1281938552856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3680248260498</t>
+    <t xml:space="preserve">11.12819480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3680257797241</t>
   </si>
   <si>
     <t xml:space="preserve">11.2720928192139</t>
@@ -4316,25 +4316,25 @@
     <t xml:space="preserve">10.9459209442139</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8499898910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7540559768677</t>
+    <t xml:space="preserve">10.8499889373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.754056930542</t>
   </si>
   <si>
     <t xml:space="preserve">10.9555149078369</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1090068817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4159908294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6558227539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5694847106934</t>
+    <t xml:space="preserve">11.1090078353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4159917831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6558237075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5694856643677</t>
   </si>
   <si>
     <t xml:space="preserve">11.5790777206421</t>
@@ -4346,25 +4346,25 @@
     <t xml:space="preserve">11.7613496780396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8764686584473</t>
+    <t xml:space="preserve">11.8764696121216</t>
   </si>
   <si>
     <t xml:space="preserve">12.049147605896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9628086090088</t>
+    <t xml:space="preserve">11.9628076553345</t>
   </si>
   <si>
     <t xml:space="preserve">12.9413213729858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2003402709961</t>
+    <t xml:space="preserve">13.2003393173218</t>
   </si>
   <si>
     <t xml:space="preserve">11.6941967010498</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3104658126831</t>
+    <t xml:space="preserve">11.3104648590088</t>
   </si>
   <si>
     <t xml:space="preserve">10.9267358779907</t>
@@ -4382,10 +4382,10 @@
     <t xml:space="preserve">12.7398624420166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2889795303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0875205993652</t>
+    <t xml:space="preserve">12.2889804840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0875215530396</t>
   </si>
   <si>
     <t xml:space="preserve">12.2601985931396</t>
@@ -4403,7 +4403,7 @@
     <t xml:space="preserve">12.5671844482422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2314195632935</t>
+    <t xml:space="preserve">12.2314205169678</t>
   </si>
   <si>
     <t xml:space="preserve">12.7686433792114</t>
@@ -4424,22 +4424,22 @@
     <t xml:space="preserve">12.4616584777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.991587638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9244356155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0395536422729</t>
+    <t xml:space="preserve">11.9915885925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9244346618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0395545959473</t>
   </si>
   <si>
     <t xml:space="preserve">12.0587406158447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5000305175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8262033462524</t>
+    <t xml:space="preserve">12.5000314712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8262023925781</t>
   </si>
   <si>
     <t xml:space="preserve">13.0852212905884</t>
@@ -4487,10 +4487,10 @@
     <t xml:space="preserve">14.3707180023193</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2939729690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1692609786987</t>
+    <t xml:space="preserve">14.2939720153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1692600250244</t>
   </si>
   <si>
     <t xml:space="preserve">14.7160768508911</t>
@@ -4505,10 +4505,10 @@
     <t xml:space="preserve">14.3899059295654</t>
   </si>
   <si>
-    <t xml:space="preserve">14.313159942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4474649429321</t>
+    <t xml:space="preserve">14.3131589889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4474658966064</t>
   </si>
   <si>
     <t xml:space="preserve">14.3323459625244</t>
@@ -4517,22 +4517,22 @@
     <t xml:space="preserve">14.3515329360962</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5721778869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5242118835449</t>
+    <t xml:space="preserve">14.5721769332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5242109298706</t>
   </si>
   <si>
     <t xml:space="preserve">14.6009578704834</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3611268997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0879135131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8288974761963</t>
+    <t xml:space="preserve">14.3611259460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0879154205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.828896522522</t>
   </si>
   <si>
     <t xml:space="preserve">16.2510013580322</t>
@@ -4559,19 +4559,19 @@
     <t xml:space="preserve">16.0207614898682</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3588256835938</t>
+    <t xml:space="preserve">15.3588266372681</t>
   </si>
   <si>
     <t xml:space="preserve">16.0783214569092</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6297378540039</t>
+    <t xml:space="preserve">14.6297369003296</t>
   </si>
   <si>
     <t xml:space="preserve">14.6105499267578</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6393308639526</t>
+    <t xml:space="preserve">14.639331817627</t>
   </si>
   <si>
     <t xml:space="preserve">14.1308870315552</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">13.3922052383423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6416311264038</t>
+    <t xml:space="preserve">13.6416301727295</t>
   </si>
   <si>
     <t xml:space="preserve">13.5552911758423</t>
@@ -4604,16 +4604,16 @@
     <t xml:space="preserve">13.459358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4497661590576</t>
+    <t xml:space="preserve">13.4497652053833</t>
   </si>
   <si>
     <t xml:space="preserve">13.3826122283936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4305791854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.353832244873</t>
+    <t xml:space="preserve">13.4305782318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3538312911987</t>
   </si>
   <si>
     <t xml:space="preserve">13.2195262908936</t>
@@ -5979,6 +5979,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.57999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44999980926514</t>
   </si>
 </sst>
 </file>
@@ -71395,7 +71398,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6912962963</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>179779</v>
@@ -71416,6 +71419,32 @@
         <v>1988</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.691099537</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>303295</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>5.71000003814697</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>5.42000007629395</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>5.57000017166138</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>5.44999980926514</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1989</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1998" uniqueCount="1998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1999" uniqueCount="1999">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2523984909058</t>
+    <t xml:space="preserve">13.2523965835571</t>
   </si>
   <si>
     <t xml:space="preserve">BSS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9788017272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7479524612427</t>
+    <t xml:space="preserve">12.9788007736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7479515075684</t>
   </si>
   <si>
     <t xml:space="preserve">12.397403717041</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2435064315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2606067657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.140905380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4825630187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8584156036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7982234954834</t>
+    <t xml:space="preserve">12.243504524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2606058120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1409063339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4825620651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.858416557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79822540283203</t>
   </si>
   <si>
     <t xml:space="preserve">10.3539695739746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84952259063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.473669052124</t>
+    <t xml:space="preserve">9.84952354431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4736700057983</t>
   </si>
   <si>
     <t xml:space="preserve">10.2941207885742</t>
@@ -86,52 +86,52 @@
     <t xml:space="preserve">10.7814664840698</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8156671524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.730167388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.576268196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6361169815063</t>
+    <t xml:space="preserve">10.8156661987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7301683425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5762691497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6361179351807</t>
   </si>
   <si>
     <t xml:space="preserve">10.1915216445923</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4565696716309</t>
+    <t xml:space="preserve">10.4565687179565</t>
   </si>
   <si>
     <t xml:space="preserve">10.4907693862915</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0205230712891</t>
+    <t xml:space="preserve">10.0205221176147</t>
   </si>
   <si>
     <t xml:space="preserve">9.03728103637695</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97743034362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40492820739746</t>
+    <t xml:space="preserve">8.97742938995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40492725372314</t>
   </si>
   <si>
     <t xml:space="preserve">9.14842891693115</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43057823181152</t>
+    <t xml:space="preserve">9.43057632446289</t>
   </si>
   <si>
     <t xml:space="preserve">9.90082359313965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66142654418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4394702911377</t>
+    <t xml:space="preserve">9.66142559051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4394683837891</t>
   </si>
   <si>
     <t xml:space="preserve">10.3454208374023</t>
@@ -140,13 +140,13 @@
     <t xml:space="preserve">10.2000713348389</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0037631988525</t>
+    <t xml:space="preserve">11.0037641525269</t>
   </si>
   <si>
     <t xml:space="preserve">10.5506191253662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2257204055786</t>
+    <t xml:space="preserve">10.2257213592529</t>
   </si>
   <si>
     <t xml:space="preserve">10.1829710006714</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">11.0379648208618</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9097156524658</t>
+    <t xml:space="preserve">10.9097166061401</t>
   </si>
   <si>
     <t xml:space="preserve">11.8074588775635</t>
@@ -173,13 +173,13 @@
     <t xml:space="preserve">11.9699077606201</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6279096603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3714122772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3799619674683</t>
+    <t xml:space="preserve">11.6279106140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.371413230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3799629211426</t>
   </si>
   <si>
     <t xml:space="preserve">11.6621103286743</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">11.8416595458984</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9186086654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7989082336426</t>
+    <t xml:space="preserve">11.918607711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7989091873169</t>
   </si>
   <si>
     <t xml:space="preserve">12.0468578338623</t>
@@ -203,10 +203,10 @@
     <t xml:space="preserve">12.200756072998</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3375539779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1323556900024</t>
+    <t xml:space="preserve">12.3375558853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1323575973511</t>
   </si>
   <si>
     <t xml:space="preserve">12.1665563583374</t>
@@ -218,16 +218,16 @@
     <t xml:space="preserve">11.9015083312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5680599212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2859125137329</t>
+    <t xml:space="preserve">11.568060874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2859134674072</t>
   </si>
   <si>
     <t xml:space="preserve">11.7390584945679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8844089508057</t>
+    <t xml:space="preserve">11.884407043457</t>
   </si>
   <si>
     <t xml:space="preserve">11.8160085678101</t>
@@ -236,28 +236,28 @@
     <t xml:space="preserve">11.7048597335815</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6022596359253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6364593505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4740114212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1918621063232</t>
+    <t xml:space="preserve">11.6022605895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6364583969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4740123748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1918630599976</t>
   </si>
   <si>
     <t xml:space="preserve">11.1063642501831</t>
   </si>
   <si>
-    <t xml:space="preserve">11.114914894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3201122283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3457622528076</t>
+    <t xml:space="preserve">11.1149139404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3201112747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3457632064819</t>
   </si>
   <si>
     <t xml:space="preserve">11.1576642990112</t>
@@ -272,58 +272,58 @@
     <t xml:space="preserve">11.1405639648438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6019172668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9541397094727</t>
+    <t xml:space="preserve">10.60191822052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.954140663147</t>
   </si>
   <si>
     <t xml:space="preserve">10.4346113204956</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3553628921509</t>
+    <t xml:space="preserve">10.3553619384766</t>
   </si>
   <si>
     <t xml:space="preserve">10.2232780456543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2673053741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92388916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3201398849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0031385421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3025283813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2496957778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6107244491577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4120321273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1302528381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9189186096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2359189987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2799482345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0069742202759</t>
+    <t xml:space="preserve">10.2673044204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92388725280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3201389312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.003137588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.302529335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2496938705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6107234954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4120302200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1302537918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9189195632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2359199523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2799463272095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0069751739502</t>
   </si>
   <si>
     <t xml:space="preserve">10.8308620452881</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">10.8396692276001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9277238845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9101133346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8132514953613</t>
+    <t xml:space="preserve">10.9277248382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9101123809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8132524490356</t>
   </si>
   <si>
     <t xml:space="preserve">10.5138607025146</t>
@@ -347,37 +347,37 @@
     <t xml:space="preserve">10.0647773742676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9943323135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9503059387207</t>
+    <t xml:space="preserve">9.99433326721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95030498504639</t>
   </si>
   <si>
     <t xml:space="preserve">9.68613815307617</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0383605957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4962520599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3465557098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4522218704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5843076705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87986183166504</t>
+    <t xml:space="preserve">10.0383596420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4962511062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3465566635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4522228240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5843067169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87985992431641</t>
   </si>
   <si>
     <t xml:space="preserve">9.12258052825928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67733001708984</t>
+    <t xml:space="preserve">9.67733192443848</t>
   </si>
   <si>
     <t xml:space="preserve">9.57166481018066</t>
@@ -392,31 +392,31 @@
     <t xml:space="preserve">9.98552703857422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18421936035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14019298553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72135925292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0823888778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3817768096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2849168777466</t>
+    <t xml:space="preserve">9.18422031402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14019107818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72136116027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0823879241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3817777633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2849178314209</t>
   </si>
   <si>
     <t xml:space="preserve">10.1352224349976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2144737243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1528329849243</t>
+    <t xml:space="preserve">10.2144727706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.15283203125</t>
   </si>
   <si>
     <t xml:space="preserve">10.6987791061401</t>
@@ -425,19 +425,19 @@
     <t xml:space="preserve">11.0774183273315</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0157814025879</t>
+    <t xml:space="preserve">11.0157804489136</t>
   </si>
   <si>
     <t xml:space="preserve">11.0333909988403</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9893636703491</t>
+    <t xml:space="preserve">10.9893627166748</t>
   </si>
   <si>
     <t xml:space="preserve">10.8748912811279</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0950317382812</t>
+    <t xml:space="preserve">11.0950307846069</t>
   </si>
   <si>
     <t xml:space="preserve">11.2535305023193</t>
@@ -446,55 +446,55 @@
     <t xml:space="preserve">11.3151702880859</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7251968383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0510025024414</t>
+    <t xml:space="preserve">10.7251958847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0510034561157</t>
   </si>
   <si>
     <t xml:space="preserve">10.9013080596924</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1654748916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0598096847534</t>
+    <t xml:space="preserve">11.1654739379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0598087310791</t>
   </si>
   <si>
     <t xml:space="preserve">11.2183084487915</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1214485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1830854415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2623357772827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5265026092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7466440200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.773060798645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.685004234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7994775772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6497821807861</t>
+    <t xml:space="preserve">11.1214475631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1830863952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.262336730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5265035629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7466430664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7730588912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6850051879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7994766235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6497812271118</t>
   </si>
   <si>
     <t xml:space="preserve">11.6673927307129</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4472541809082</t>
+    <t xml:space="preserve">11.4472532272339</t>
   </si>
   <si>
     <t xml:space="preserve">11.3239755630493</t>
@@ -506,40 +506,40 @@
     <t xml:space="preserve">11.1390581130981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.693808555603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.614559173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8258953094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0372276306152</t>
+    <t xml:space="preserve">11.6938095092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6145572662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8258943557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0372266769409</t>
   </si>
   <si>
     <t xml:space="preserve">12.054838180542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0636444091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5039224624634</t>
+    <t xml:space="preserve">12.0636434555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5039234161377</t>
   </si>
   <si>
     <t xml:space="preserve">12.5303392410278</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4070615768433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2837839126587</t>
+    <t xml:space="preserve">12.4070625305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2837829589844</t>
   </si>
   <si>
     <t xml:space="preserve">12.6007852554321</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9177856445312</t>
+    <t xml:space="preserve">12.9177865982056</t>
   </si>
   <si>
     <t xml:space="preserve">12.8121185302734</t>
@@ -551,16 +551,16 @@
     <t xml:space="preserve">13.0322580337524</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4108972549438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5782032012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6838703155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4285106658936</t>
+    <t xml:space="preserve">13.4108982086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5782041549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6838712692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4285097122192</t>
   </si>
   <si>
     <t xml:space="preserve">14.3707056045532</t>
@@ -569,13 +569,13 @@
     <t xml:space="preserve">14.2210102081299</t>
   </si>
   <si>
-    <t xml:space="preserve">14.256233215332</t>
+    <t xml:space="preserve">14.2562341690063</t>
   </si>
   <si>
     <t xml:space="preserve">14.1329545974731</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1241502761841</t>
+    <t xml:space="preserve">14.1241512298584</t>
   </si>
   <si>
     <t xml:space="preserve">14.0713157653809</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">13.9216222763062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7807321548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6046199798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7631206512451</t>
+    <t xml:space="preserve">13.7807312011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6046209335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7631216049194</t>
   </si>
   <si>
     <t xml:space="preserve">13.8335647583008</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">13.7278985977173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1995649337769</t>
+    <t xml:space="preserve">13.1995639801025</t>
   </si>
   <si>
     <t xml:space="preserve">13.375675201416</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">13.155535697937</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6486492156982</t>
+    <t xml:space="preserve">13.6486473083496</t>
   </si>
   <si>
     <t xml:space="preserve">13.5605926513672</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">13.7367038726807</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8775949478149</t>
+    <t xml:space="preserve">13.8775939941406</t>
   </si>
   <si>
     <t xml:space="preserve">14.176983833313</t>
@@ -626,43 +626,43 @@
     <t xml:space="preserve">14.0977334976196</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7845687866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3040952682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.277681350708</t>
+    <t xml:space="preserve">14.7845697402954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3040981292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2776803970337</t>
   </si>
   <si>
     <t xml:space="preserve">15.4890146255493</t>
   </si>
   <si>
-    <t xml:space="preserve">15.497820854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3657388687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4449882507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.339319229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5330429077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6651248931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5418472290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2424564361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8060150146484</t>
+    <t xml:space="preserve">15.4978227615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3657369613647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4449863433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3393201828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5330410003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6651268005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5418481826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2424573898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8060178756714</t>
   </si>
   <si>
     <t xml:space="preserve">16.1934585571289</t>
@@ -671,10 +671,10 @@
     <t xml:space="preserve">16.3695735931396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4664363861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.510461807251</t>
+    <t xml:space="preserve">16.4664344787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5104598999023</t>
   </si>
   <si>
     <t xml:space="preserve">17.03879737854</t>
@@ -683,58 +683,58 @@
     <t xml:space="preserve">16.889102935791</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1532707214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7746295928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5544891357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2374897003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5897121429443</t>
+    <t xml:space="preserve">17.1532688140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7746276855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5544910430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.237491607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5897102355957</t>
   </si>
   <si>
     <t xml:space="preserve">16.6513500213623</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5721015930176</t>
+    <t xml:space="preserve">16.5720996856689</t>
   </si>
   <si>
     <t xml:space="preserve">16.9947681427002</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7041835784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.880298614502</t>
+    <t xml:space="preserve">16.7041854858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8802947998047</t>
   </si>
   <si>
     <t xml:space="preserve">16.8538780212402</t>
   </si>
   <si>
-    <t xml:space="preserve">17.012378692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2941608428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1268539428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5368785858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0828247070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8626861572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2061023712158</t>
+    <t xml:space="preserve">17.0123805999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2941589355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1268520355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5368804931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0828227996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8626842498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2061042785645</t>
   </si>
   <si>
     <t xml:space="preserve">17.3469924926758</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">17.6551876068115</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5407123565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5054931640625</t>
+    <t xml:space="preserve">17.540714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5054912567139</t>
   </si>
   <si>
     <t xml:space="preserve">17.7168273925781</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">17.4526596069336</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5583248138428</t>
+    <t xml:space="preserve">17.5583267211914</t>
   </si>
   <si>
     <t xml:space="preserve">17.7432422637939</t>
@@ -764,19 +764,19 @@
     <t xml:space="preserve">17.8401031494141</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5759391784668</t>
+    <t xml:space="preserve">17.5759353637695</t>
   </si>
   <si>
     <t xml:space="preserve">16.7482128143311</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7658233642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.950740814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.162073135376</t>
+    <t xml:space="preserve">16.7658252716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9507446289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1620750427246</t>
   </si>
   <si>
     <t xml:space="preserve">17.2765464782715</t>
@@ -788,28 +788,28 @@
     <t xml:space="preserve">17.1092414855957</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8186588287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.232515335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2853507995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3910217285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2501316070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4350471496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3734073638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6463813781738</t>
+    <t xml:space="preserve">16.8186569213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2325191497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2853527069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.391019821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.250129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4350452423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3734111785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6463832855225</t>
   </si>
   <si>
     <t xml:space="preserve">17.9457702636719</t>
@@ -818,34 +818,34 @@
     <t xml:space="preserve">19.3722763061523</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9358329772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.384916305542</t>
+    <t xml:space="preserve">19.9358348846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3849182128906</t>
   </si>
   <si>
     <t xml:space="preserve">20.5962505340576</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3408889770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8340015411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0453319549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5824775695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0893669128418</t>
+    <t xml:space="preserve">20.3408870697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8340034484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0453338623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5824756622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0893630981445</t>
   </si>
   <si>
     <t xml:space="preserve">21.327112197876</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6529197692871</t>
+    <t xml:space="preserve">21.6529216766357</t>
   </si>
   <si>
     <t xml:space="preserve">21.7497825622559</t>
@@ -854,25 +854,25 @@
     <t xml:space="preserve">21.917085647583</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8114242553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0139484405518</t>
+    <t xml:space="preserve">21.8114223480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0139503479004</t>
   </si>
   <si>
     <t xml:space="preserve">22.286922454834</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2605056762695</t>
+    <t xml:space="preserve">22.2605075836182</t>
   </si>
   <si>
     <t xml:space="preserve">22.348560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3221435546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1900634765625</t>
+    <t xml:space="preserve">22.3221454620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1900615692139</t>
   </si>
   <si>
     <t xml:space="preserve">22.6303405761719</t>
@@ -881,139 +881,139 @@
     <t xml:space="preserve">22.436616897583</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4806480407715</t>
+    <t xml:space="preserve">22.4806442260742</t>
   </si>
   <si>
     <t xml:space="preserve">22.6655597686768</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6215343475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6743679046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8945083618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0970325469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8328685760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.374979019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1938953399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3876171112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5108966827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9159564971924</t>
+    <t xml:space="preserve">22.6215324401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6743698120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8945064544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0970344543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8328704833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3749771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1938972473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3876190185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5108985900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9159545898438</t>
   </si>
   <si>
     <t xml:space="preserve">24.2417621612549</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7084560394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6556224822998</t>
+    <t xml:space="preserve">24.7084541320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6556243896484</t>
   </si>
   <si>
     <t xml:space="preserve">24.9197883605957</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0870971679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9638175964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8933734893799</t>
+    <t xml:space="preserve">25.0870990753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9638214111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8933715820312</t>
   </si>
   <si>
     <t xml:space="preserve">26.4255466461182</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4879322052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.397008895874</t>
+    <t xml:space="preserve">26.4879302978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3970069885254</t>
   </si>
   <si>
     <t xml:space="preserve">27.6287326812744</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1545677185059</t>
+    <t xml:space="preserve">28.1545696258545</t>
   </si>
   <si>
     <t xml:space="preserve">27.6732940673828</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6804084777832</t>
+    <t xml:space="preserve">28.6804046630859</t>
   </si>
   <si>
     <t xml:space="preserve">29.3666706085205</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8069801330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4665050506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0190830230713</t>
+    <t xml:space="preserve">27.8069820404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4665069580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0190811157227</t>
   </si>
   <si>
     <t xml:space="preserve">29.4914436340332</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7677345275879</t>
+    <t xml:space="preserve">29.7677326202393</t>
   </si>
   <si>
     <t xml:space="preserve">29.8746814727783</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3024826049805</t>
+    <t xml:space="preserve">30.3024806976318</t>
   </si>
   <si>
     <t xml:space="preserve">30.7748432159424</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2400951385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6678924560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8283176422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8996143341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0154781341553</t>
+    <t xml:space="preserve">30.2400932312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6678943634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8283157348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8996162414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0154819488525</t>
   </si>
   <si>
     <t xml:space="preserve">30.9976577758789</t>
   </si>
   <si>
-    <t xml:space="preserve">30.935266494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6500644683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.748104095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6857204437256</t>
+    <t xml:space="preserve">30.9352645874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6500682830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7481060028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.685718536377</t>
   </si>
   <si>
     <t xml:space="preserve">29.3577556610107</t>
@@ -1028,13 +1028,13 @@
     <t xml:space="preserve">29.2775440216064</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1687889099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1331462860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9994525909424</t>
+    <t xml:space="preserve">30.1687927246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1331443786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.999454498291</t>
   </si>
   <si>
     <t xml:space="preserve">29.9281558990479</t>
@@ -1043,43 +1043,43 @@
     <t xml:space="preserve">30.0529346466064</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4825325012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8122940063477</t>
+    <t xml:space="preserve">29.4825305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8122959136963</t>
   </si>
   <si>
     <t xml:space="preserve">28.9121284484863</t>
   </si>
   <si>
-    <t xml:space="preserve">29.126033782959</t>
+    <t xml:space="preserve">29.1260318756104</t>
   </si>
   <si>
     <t xml:space="preserve">27.771333694458</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9674091339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2544097900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6911220550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4861316680908</t>
+    <t xml:space="preserve">27.9674053192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2544078826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6911201477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4861297607422</t>
   </si>
   <si>
     <t xml:space="preserve">27.5752582550049</t>
   </si>
   <si>
-    <t xml:space="preserve">28.11891746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3506450653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7178592681885</t>
+    <t xml:space="preserve">28.1189193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.350643157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7178573608398</t>
   </si>
   <si>
     <t xml:space="preserve">28.5734577178955</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">28.6180210113525</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5199794769287</t>
+    <t xml:space="preserve">28.5199813842773</t>
   </si>
   <si>
     <t xml:space="preserve">28.7873554229736</t>
@@ -1100,34 +1100,34 @@
     <t xml:space="preserve">29.5360069274902</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3310203552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1705913543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2329807281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.143856048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3221073150635</t>
+    <t xml:space="preserve">29.331018447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1705932617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.232982635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1438541412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3221092224121</t>
   </si>
   <si>
     <t xml:space="preserve">28.9656066894531</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7071437835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9923439025879</t>
+    <t xml:space="preserve">28.707145690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9923419952393</t>
   </si>
   <si>
     <t xml:space="preserve">28.9477806091309</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6073055267334</t>
+    <t xml:space="preserve">29.6073036193848</t>
   </si>
   <si>
     <t xml:space="preserve">29.8568572998047</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">29.4112300872803</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8140964508057</t>
+    <t xml:space="preserve">28.814094543457</t>
   </si>
   <si>
     <t xml:space="preserve">29.687520980835</t>
@@ -1151,73 +1151,73 @@
     <t xml:space="preserve">29.6786060333252</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6964282989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1420497894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8390331268311</t>
+    <t xml:space="preserve">29.6964302062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.142053604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8390312194824</t>
   </si>
   <si>
     <t xml:space="preserve">30.186616897583</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5181789398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1795063018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4379692077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3648662567139</t>
+    <t xml:space="preserve">29.518180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1795101165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.437967300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3648700714111</t>
   </si>
   <si>
     <t xml:space="preserve">30.4629039764404</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4718170166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2935695648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0974922180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0618419647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2311782836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0849800109863</t>
+    <t xml:space="preserve">30.4718151092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2935676574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0974903106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.061840057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2311763763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0849761962891</t>
   </si>
   <si>
     <t xml:space="preserve">31.496753692627</t>
   </si>
   <si>
-    <t xml:space="preserve">30.819408416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9958515167236</t>
+    <t xml:space="preserve">30.8194065093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9958553314209</t>
   </si>
   <si>
     <t xml:space="preserve">31.7730407714844</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6928310394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1830215454102</t>
+    <t xml:space="preserve">31.6928329467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1830139160156</t>
   </si>
   <si>
     <t xml:space="preserve">32.0760688781738</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9512920379639</t>
+    <t xml:space="preserve">31.9512882232666</t>
   </si>
   <si>
     <t xml:space="preserve">32.307788848877</t>
@@ -1226,16 +1226,16 @@
     <t xml:space="preserve">33.1990432739258</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3951148986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7587280273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6963386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7319984436035</t>
+    <t xml:space="preserve">33.3951187133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7587242126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6963348388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.731990814209</t>
   </si>
   <si>
     <t xml:space="preserve">34.5804748535156</t>
@@ -1244,10 +1244,10 @@
     <t xml:space="preserve">34.2239799499512</t>
   </si>
   <si>
-    <t xml:space="preserve">34.437873840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5448226928711</t>
+    <t xml:space="preserve">34.4378776550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5448265075684</t>
   </si>
   <si>
     <t xml:space="preserve">35.4271659851074</t>
@@ -1262,19 +1262,19 @@
     <t xml:space="preserve">34.37548828125</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8674774169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8496513366699</t>
+    <t xml:space="preserve">33.8674812316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8496551513672</t>
   </si>
   <si>
     <t xml:space="preserve">34.1437683105469</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7159729003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0635604858398</t>
+    <t xml:space="preserve">33.7159652709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0635528564453</t>
   </si>
   <si>
     <t xml:space="preserve">34.313102722168</t>
@@ -1286,16 +1286,16 @@
     <t xml:space="preserve">34.420051574707</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7765464782715</t>
+    <t xml:space="preserve">34.7765502929688</t>
   </si>
   <si>
     <t xml:space="preserve">34.6161270141602</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3041915893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1081199645996</t>
+    <t xml:space="preserve">34.3041954040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1081161499023</t>
   </si>
   <si>
     <t xml:space="preserve">32.8425407409668</t>
@@ -1307,13 +1307,13 @@
     <t xml:space="preserve">35.1063117980957</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2471084594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3005867004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1847229003906</t>
+    <t xml:space="preserve">36.2471122741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3005828857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1847267150879</t>
   </si>
   <si>
     <t xml:space="preserve">36.4966621398926</t>
@@ -1328,28 +1328,28 @@
     <t xml:space="preserve">38.9208602905273</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6178359985352</t>
+    <t xml:space="preserve">38.6178321838379</t>
   </si>
   <si>
     <t xml:space="preserve">38.5821876525879</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2702484130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4306755065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2149772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.805004119873</t>
+    <t xml:space="preserve">38.2702445983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4306716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.214973449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8050003051758</t>
   </si>
   <si>
     <t xml:space="preserve">37.8067970275879</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3504638671875</t>
+    <t xml:space="preserve">38.3504600524902</t>
   </si>
   <si>
     <t xml:space="preserve">38.0563507080078</t>
@@ -1358,19 +1358,19 @@
     <t xml:space="preserve">38.3682899475098</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3415489196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5197982788086</t>
+    <t xml:space="preserve">38.341552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5198020935059</t>
   </si>
   <si>
     <t xml:space="preserve">38.5643615722656</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6089286804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.689136505127</t>
+    <t xml:space="preserve">38.6089248657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6891403198242</t>
   </si>
   <si>
     <t xml:space="preserve">38.7336959838867</t>
@@ -1388,10 +1388,10 @@
     <t xml:space="preserve">39.3219261169434</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5554466247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2880783081055</t>
+    <t xml:space="preserve">38.5554504394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2880744934082</t>
   </si>
   <si>
     <t xml:space="preserve">38.3772010803223</t>
@@ -1400,13 +1400,13 @@
     <t xml:space="preserve">37.6998481750488</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6125335693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6820259094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4663314819336</t>
+    <t xml:space="preserve">36.6125259399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6820220947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4663276672363</t>
   </si>
   <si>
     <t xml:space="preserve">41.9956741333008</t>
@@ -1415,22 +1415,22 @@
     <t xml:space="preserve">42.6551933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8156242370605</t>
+    <t xml:space="preserve">42.8156204223633</t>
   </si>
   <si>
     <t xml:space="preserve">42.423469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0313186645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0848007202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.924373626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6213455200195</t>
+    <t xml:space="preserve">42.0313262939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0847969055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9243698120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6213493347168</t>
   </si>
   <si>
     <t xml:space="preserve">41.7639465332031</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">41.6926460266113</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5322265625</t>
+    <t xml:space="preserve">41.5322227478027</t>
   </si>
   <si>
     <t xml:space="preserve">41.7817764282227</t>
@@ -1451,19 +1451,19 @@
     <t xml:space="preserve">41.3539733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">40.819221496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3557739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5875015258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8031959533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1436729431152</t>
+    <t xml:space="preserve">40.8192176818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.355770111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5874977111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8031997680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1436767578125</t>
   </si>
   <si>
     <t xml:space="preserve">39.6784248352051</t>
@@ -1481,55 +1481,55 @@
     <t xml:space="preserve">37.5750732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2898788452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.589298248291</t>
+    <t xml:space="preserve">37.2898750305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5892944335938</t>
   </si>
   <si>
     <t xml:space="preserve">40.1953468322754</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1062240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5696754455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.801399230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9439964294434</t>
+    <t xml:space="preserve">40.1062278747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5696716308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8013954162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9440002441406</t>
   </si>
   <si>
     <t xml:space="preserve">41.1400718688965</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9974708557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5162048339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9618225097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2506256103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1793174743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2131690979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3914222717285</t>
+    <t xml:space="preserve">40.9974746704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5161972045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9618186950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2506294250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1793212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2131729125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3914260864258</t>
   </si>
   <si>
     <t xml:space="preserve">41.3896217346191</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6017189025879</t>
+    <t xml:space="preserve">42.6017227172852</t>
   </si>
   <si>
     <t xml:space="preserve">44.5446472167969</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">43.902946472168</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2309074401855</t>
+    <t xml:space="preserve">45.2309036254883</t>
   </si>
   <si>
     <t xml:space="preserve">43.8851203918457</t>
@@ -1556,28 +1556,28 @@
     <t xml:space="preserve">45.943904876709</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5874099731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.696159362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0098991394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8494720458984</t>
+    <t xml:space="preserve">45.5874137878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6961555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.009895324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8494758605957</t>
   </si>
   <si>
     <t xml:space="preserve">42.9582252502441</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4609222412109</t>
+    <t xml:space="preserve">41.4609184265137</t>
   </si>
   <si>
     <t xml:space="preserve">41.175724029541</t>
   </si>
   <si>
-    <t xml:space="preserve">41.157901763916</t>
+    <t xml:space="preserve">41.1578979492188</t>
   </si>
   <si>
     <t xml:space="preserve">41.0153007507324</t>
@@ -1607,22 +1607,22 @@
     <t xml:space="preserve">40.2488250732422</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9101448059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4288711547852</t>
+    <t xml:space="preserve">39.9101486206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4288749694824</t>
   </si>
   <si>
     <t xml:space="preserve">39.0367240905762</t>
   </si>
   <si>
-    <t xml:space="preserve">42.387825012207</t>
+    <t xml:space="preserve">42.3878211975098</t>
   </si>
   <si>
     <t xml:space="preserve">41.0509490966797</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9335708618164</t>
+    <t xml:space="preserve">41.9335670471191</t>
   </si>
   <si>
     <t xml:space="preserve">41.0149269104004</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">40.7087135314941</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6366500854492</t>
+    <t xml:space="preserve">40.6366539001465</t>
   </si>
   <si>
     <t xml:space="preserve">40.5285797119141</t>
@@ -1649,19 +1649,19 @@
     <t xml:space="preserve">36.3316230773926</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0521278381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4757232666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6018142700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.007396697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6651496887207</t>
+    <t xml:space="preserve">37.0521240234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4757194519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6018104553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0073928833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6651458740234</t>
   </si>
   <si>
     <t xml:space="preserve">35.3589324951172</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">34.2241325378418</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4135589599609</t>
+    <t xml:space="preserve">33.4135627746582</t>
   </si>
   <si>
     <t xml:space="preserve">33.6657447814941</t>
@@ -1679,13 +1679,13 @@
     <t xml:space="preserve">33.881893157959</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4763107299805</t>
+    <t xml:space="preserve">34.4763069152832</t>
   </si>
   <si>
     <t xml:space="preserve">34.6924667358398</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1427764892578</t>
+    <t xml:space="preserve">35.1427803039551</t>
   </si>
   <si>
     <t xml:space="preserve">34.7284927368164</t>
@@ -1694,10 +1694,10 @@
     <t xml:space="preserve">34.5483627319336</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9899749755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8278541564941</t>
+    <t xml:space="preserve">33.9899711608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8278579711914</t>
   </si>
   <si>
     <t xml:space="preserve">34.4402885437012</t>
@@ -1706,13 +1706,13 @@
     <t xml:space="preserve">35.1247673034668</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5036277770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.404857635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3868370056152</t>
+    <t xml:space="preserve">33.5036239624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4048500061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3868408203125</t>
   </si>
   <si>
     <t xml:space="preserve">31.4681911468506</t>
@@ -1724,34 +1724,34 @@
     <t xml:space="preserve">30.5315322875977</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4867935180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9371109008789</t>
+    <t xml:space="preserve">29.4867973327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9371128082275</t>
   </si>
   <si>
     <t xml:space="preserve">29.2346172332764</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1532669067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2166004180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4147415161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8296241760254</t>
+    <t xml:space="preserve">30.1532649993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2166023254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4147434234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8296222686768</t>
   </si>
   <si>
     <t xml:space="preserve">29.1265411376953</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5408325195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6035804748535</t>
+    <t xml:space="preserve">29.5408344268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6035823822021</t>
   </si>
   <si>
     <t xml:space="preserve">31.2520389556885</t>
@@ -1769,16 +1769,16 @@
     <t xml:space="preserve">30.4054412841797</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6663341522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6483173370361</t>
+    <t xml:space="preserve">31.6663303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6483211517334</t>
   </si>
   <si>
     <t xml:space="preserve">32.080623626709</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1079425811768</t>
+    <t xml:space="preserve">31.1079406738281</t>
   </si>
   <si>
     <t xml:space="preserve">31.3601150512695</t>
@@ -1787,10 +1787,10 @@
     <t xml:space="preserve">30.9818496704102</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7383823394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6122932434082</t>
+    <t xml:space="preserve">31.7383842468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6122913360596</t>
   </si>
   <si>
     <t xml:space="preserve">30.8377494812012</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">29.901086807251</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6669216156006</t>
+    <t xml:space="preserve">29.666919708252</t>
   </si>
   <si>
     <t xml:space="preserve">29.0905132293701</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">28.0998153686523</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5954608917236</t>
+    <t xml:space="preserve">27.595458984375</t>
   </si>
   <si>
     <t xml:space="preserve">26.6407871246338</t>
@@ -1823,7 +1823,7 @@
     <t xml:space="preserve">26.2805347442627</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0463676452637</t>
+    <t xml:space="preserve">26.0463695526123</t>
   </si>
   <si>
     <t xml:space="preserve">26.5146999359131</t>
@@ -1838,25 +1838,25 @@
     <t xml:space="preserve">27.1091175079346</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0190544128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7488651275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4693737030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9196910858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.577449798584</t>
+    <t xml:space="preserve">27.0190525054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7488632202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4693717956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9196891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5774478912354</t>
   </si>
   <si>
     <t xml:space="preserve">27.9377021789551</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8476371765137</t>
+    <t xml:space="preserve">27.8476390838623</t>
   </si>
   <si>
     <t xml:space="preserve">27.7936019897461</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">28.0097541809082</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7755870819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6041736602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5501346588135</t>
+    <t xml:space="preserve">27.7755889892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6041717529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5501365661621</t>
   </si>
   <si>
     <t xml:space="preserve">29.1805820465088</t>
@@ -1883,16 +1883,16 @@
     <t xml:space="preserve">29.1625652313232</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6401977539062</t>
+    <t xml:space="preserve">28.6401958465576</t>
   </si>
   <si>
     <t xml:space="preserve">28.6762218475342</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6675109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4513568878174</t>
+    <t xml:space="preserve">27.6675090789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.451358795166</t>
   </si>
   <si>
     <t xml:space="preserve">27.5594348907471</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">22.7860698699951</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4165153503418</t>
+    <t xml:space="preserve">23.4165115356445</t>
   </si>
   <si>
     <t xml:space="preserve">23.7047176361084</t>
@@ -1922,13 +1922,13 @@
     <t xml:space="preserve">23.5606174468994</t>
   </si>
   <si>
-    <t xml:space="preserve">23.236385345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4345264434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5158767700195</t>
+    <t xml:space="preserve">23.2363872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4345283508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5158786773682</t>
   </si>
   <si>
     <t xml:space="preserve">21.7053070068359</t>
@@ -1940,13 +1940,13 @@
     <t xml:space="preserve">21.3630657196045</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2369747161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3450527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5972290039062</t>
+    <t xml:space="preserve">21.2369766235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3450546264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5972309112549</t>
   </si>
   <si>
     <t xml:space="preserve">19.7239093780518</t>
@@ -1964,13 +1964,13 @@
     <t xml:space="preserve">18.8773097991943</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3909683227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0033988952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.003698348999</t>
+    <t xml:space="preserve">18.3909702301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0034008026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0036964416504</t>
   </si>
   <si>
     <t xml:space="preserve">17.139087677002</t>
@@ -1985,13 +1985,13 @@
     <t xml:space="preserve">16.661750793457</t>
   </si>
   <si>
-    <t xml:space="preserve">16.202428817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.950249671936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.71608543396</t>
+    <t xml:space="preserve">16.2024250030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9502458572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7160844802856</t>
   </si>
   <si>
     <t xml:space="preserve">15.6800575256348</t>
@@ -2006,10 +2006,10 @@
     <t xml:space="preserve">16.6077117919922</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4005661010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4723224639893</t>
+    <t xml:space="preserve">16.4005641937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4723205566406</t>
   </si>
   <si>
     <t xml:space="preserve">17.5533771514893</t>
@@ -2033,19 +2033,19 @@
     <t xml:space="preserve">16.0132942199707</t>
   </si>
   <si>
-    <t xml:space="preserve">15.905216217041</t>
+    <t xml:space="preserve">15.9052152633667</t>
   </si>
   <si>
     <t xml:space="preserve">16.2654705047607</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1934185028076</t>
+    <t xml:space="preserve">16.1934204101562</t>
   </si>
   <si>
     <t xml:space="preserve">15.7250890731812</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4008617401123</t>
+    <t xml:space="preserve">15.400860786438</t>
   </si>
   <si>
     <t xml:space="preserve">15.0496120452881</t>
@@ -2054,16 +2054,16 @@
     <t xml:space="preserve">14.7524032592773</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5899925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1486835479736</t>
+    <t xml:space="preserve">15.5899934768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1486825942993</t>
   </si>
   <si>
     <t xml:space="preserve">15.4639053344727</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1661052703857</t>
+    <t xml:space="preserve">17.1661071777344</t>
   </si>
   <si>
     <t xml:space="preserve">17.7875461578369</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">18.2288551330566</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0307140350342</t>
+    <t xml:space="preserve">18.0307159423828</t>
   </si>
   <si>
     <t xml:space="preserve">17.9226398468018</t>
@@ -2105,16 +2105,16 @@
     <t xml:space="preserve">18.6251354217529</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3369312286377</t>
+    <t xml:space="preserve">18.3369331359863</t>
   </si>
   <si>
     <t xml:space="preserve">18.9493637084961</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7872486114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6971874237061</t>
+    <t xml:space="preserve">18.7872505187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6971855163574</t>
   </si>
   <si>
     <t xml:space="preserve">18.3549423217773</t>
@@ -2132,16 +2132,16 @@
     <t xml:space="preserve">17.7244987487793</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3009071350098</t>
+    <t xml:space="preserve">18.3009052276611</t>
   </si>
   <si>
     <t xml:space="preserve">18.6071224212646</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3996810913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6698722839355</t>
+    <t xml:space="preserve">19.3996829986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6698703765869</t>
   </si>
   <si>
     <t xml:space="preserve">20.2462768554688</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">19.9220485687256</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4176940917969</t>
+    <t xml:space="preserve">19.4176921844482</t>
   </si>
   <si>
     <t xml:space="preserve">19.4537181854248</t>
@@ -2165,28 +2165,28 @@
     <t xml:space="preserve">17.7515163421631</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7425117492676</t>
+    <t xml:space="preserve">17.7425136566162</t>
   </si>
   <si>
     <t xml:space="preserve">17.7965507507324</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5083465576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4182834625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8508815765381</t>
+    <t xml:space="preserve">17.5083484649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.418285369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8508834838867</t>
   </si>
   <si>
     <t xml:space="preserve">16.9859790802002</t>
   </si>
   <si>
-    <t xml:space="preserve">16.868896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0490226745605</t>
+    <t xml:space="preserve">16.8688945770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0490245819092</t>
   </si>
   <si>
     <t xml:space="preserve">16.9409465789795</t>
@@ -2201,22 +2201,22 @@
     <t xml:space="preserve">17.3822593688965</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2831878662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1748180389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9766788482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6164226531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4272880554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1387901306152</t>
+    <t xml:space="preserve">17.2831897735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1748161315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.976676940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6164245605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4272899627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1387920379639</t>
   </si>
   <si>
     <t xml:space="preserve">17.913631439209</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">17.9496593475342</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2381553649902</t>
+    <t xml:space="preserve">17.2381534576416</t>
   </si>
   <si>
     <t xml:space="preserve">17.1300811767578</t>
@@ -2243,22 +2243,22 @@
     <t xml:space="preserve">17.9676723480225</t>
   </si>
   <si>
-    <t xml:space="preserve">18.084753036499</t>
+    <t xml:space="preserve">18.0847549438477</t>
   </si>
   <si>
     <t xml:space="preserve">18.0667400360107</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8686008453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.51735496521</t>
+    <t xml:space="preserve">17.8686027526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5173530578613</t>
   </si>
   <si>
     <t xml:space="preserve">17.6074180603027</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5894050598145</t>
+    <t xml:space="preserve">17.5894031524658</t>
   </si>
   <si>
     <t xml:space="preserve">17.76953125</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">16.6621875762939</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2249755859375</t>
+    <t xml:space="preserve">17.2249774932861</t>
   </si>
   <si>
     <t xml:space="preserve">16.5330257415771</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">14.6232395172119</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8021240234375</t>
+    <t xml:space="preserve">13.8021230697632</t>
   </si>
   <si>
     <t xml:space="preserve">13.9405136108398</t>
@@ -2300,31 +2300,31 @@
     <t xml:space="preserve">13.3131456375122</t>
   </si>
   <si>
-    <t xml:space="preserve">13.894383430481</t>
+    <t xml:space="preserve">13.8943843841553</t>
   </si>
   <si>
     <t xml:space="preserve">13.8390283584595</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4792127609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9533309936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0732679367065</t>
+    <t xml:space="preserve">13.4792137145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.953330039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0732688903809</t>
   </si>
   <si>
     <t xml:space="preserve">13.0179128646851</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3039197921753</t>
+    <t xml:space="preserve">13.303918838501</t>
   </si>
   <si>
     <t xml:space="preserve">13.3777275085449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1009473800659</t>
+    <t xml:space="preserve">13.1009464263916</t>
   </si>
   <si>
     <t xml:space="preserve">13.1378498077393</t>
@@ -2333,34 +2333,34 @@
     <t xml:space="preserve">13.9220628738403</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7006378173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4756240844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4202680587769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5771102905273</t>
+    <t xml:space="preserve">13.7006387710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4756231307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4202671051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.577109336853</t>
   </si>
   <si>
     <t xml:space="preserve">13.8298015594482</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7928981781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6914119720459</t>
+    <t xml:space="preserve">13.7928972244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6914129257202</t>
   </si>
   <si>
     <t xml:space="preserve">14.5125274658203</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1803903579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0988998413086</t>
+    <t xml:space="preserve">14.1803913116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0989007949829</t>
   </si>
   <si>
     <t xml:space="preserve">10.7575378417969</t>
@@ -2372,28 +2372,28 @@
     <t xml:space="preserve">10.2132024765015</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4069490432739</t>
+    <t xml:space="preserve">10.4069480895996</t>
   </si>
   <si>
     <t xml:space="preserve">10.4161758422852</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5914697647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8590250015259</t>
+    <t xml:space="preserve">10.5914688110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8590240478516</t>
   </si>
   <si>
     <t xml:space="preserve">10.9236068725586</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4807567596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6837291717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5361127853394</t>
+    <t xml:space="preserve">10.4807558059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6837301254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5361137390137</t>
   </si>
   <si>
     <t xml:space="preserve">10.2962369918823</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">9.9087438583374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65964221954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53047752380371</t>
+    <t xml:space="preserve">9.65964126586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53047657012939</t>
   </si>
   <si>
     <t xml:space="preserve">10.0932645797729</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">10.4438524246216</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6652774810791</t>
+    <t xml:space="preserve">10.6652784347534</t>
   </si>
   <si>
     <t xml:space="preserve">10.0286827087402</t>
@@ -2450,31 +2450,31 @@
     <t xml:space="preserve">10.056360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1209421157837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50279998779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29060077667236</t>
+    <t xml:space="preserve">10.120943069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50280094146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29059982299805</t>
   </si>
   <si>
     <t xml:space="preserve">9.5766077041626</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21218013763428</t>
+    <t xml:space="preserve">9.21218109130859</t>
   </si>
   <si>
     <t xml:space="preserve">9.40131282806396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43821716308594</t>
+    <t xml:space="preserve">9.43821620941162</t>
   </si>
   <si>
     <t xml:space="preserve">9.47512149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20295429229736</t>
+    <t xml:space="preserve">9.20295333862305</t>
   </si>
   <si>
     <t xml:space="preserve">8.94001197814941</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">8.9861421585083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88004302978516</t>
+    <t xml:space="preserve">8.88004398345947</t>
   </si>
   <si>
     <t xml:space="preserve">9.53970336914062</t>
@@ -2498,10 +2498,10 @@
     <t xml:space="preserve">9.11530685424805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88106536865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97332572937012</t>
+    <t xml:space="preserve">9.88106632232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97332668304443</t>
   </si>
   <si>
     <t xml:space="preserve">9.99177837371826</t>
@@ -2522,10 +2522,10 @@
     <t xml:space="preserve">9.61351108551025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66886615753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5212516784668</t>
+    <t xml:space="preserve">9.66886711120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52125072479248</t>
   </si>
   <si>
     <t xml:space="preserve">9.7980318069458</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">9.2629222869873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39208698272705</t>
+    <t xml:space="preserve">9.39208793640137</t>
   </si>
   <si>
     <t xml:space="preserve">9.65041542053223</t>
@@ -2549,19 +2549,19 @@
     <t xml:space="preserve">9.71499729156494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81648349761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6873197555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98255252838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7519006729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49357318878174</t>
+    <t xml:space="preserve">9.81648445129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68732070922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98255157470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75190162658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49357223510742</t>
   </si>
   <si>
     <t xml:space="preserve">10.2777853012085</t>
@@ -2570,19 +2570,19 @@
     <t xml:space="preserve">10.0655860900879</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5822429656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7298593521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2870111465454</t>
+    <t xml:space="preserve">10.5822439193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7298603057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2870101928711</t>
   </si>
   <si>
     <t xml:space="preserve">10.5084362030029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3515939712524</t>
+    <t xml:space="preserve">10.3515930175781</t>
   </si>
   <si>
     <t xml:space="preserve">11.4310369491577</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">11.6340093612671</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2337017059326</t>
+    <t xml:space="preserve">12.2337007522583</t>
   </si>
   <si>
     <t xml:space="preserve">11.993824005127</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">12.1414403915405</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1875715255737</t>
+    <t xml:space="preserve">12.1875705718994</t>
   </si>
   <si>
     <t xml:space="preserve">11.9661464691162</t>
@@ -2624,16 +2624,16 @@
     <t xml:space="preserve">11.7354965209961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0676317214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4551258087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2577886581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2485637664795</t>
+    <t xml:space="preserve">12.0676326751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4551248550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2577877044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2485628128052</t>
   </si>
   <si>
     <t xml:space="preserve">13.0824947357178</t>
@@ -2648,16 +2648,16 @@
     <t xml:space="preserve">13.2024335861206</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7559938430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7098636627197</t>
+    <t xml:space="preserve">13.7559928894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7098627090454</t>
   </si>
   <si>
     <t xml:space="preserve">13.7744464874268</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3408231735229</t>
+    <t xml:space="preserve">13.3408241271973</t>
   </si>
   <si>
     <t xml:space="preserve">13.7190895080566</t>
@@ -2666,34 +2666,34 @@
     <t xml:space="preserve">13.7283163070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0143232345581</t>
+    <t xml:space="preserve">14.0143222808838</t>
   </si>
   <si>
     <t xml:space="preserve">14.1342601776123</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1250352859497</t>
+    <t xml:space="preserve">14.1250343322754</t>
   </si>
   <si>
     <t xml:space="preserve">13.9497404098511</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6637344360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6821851730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4571704864502</t>
+    <t xml:space="preserve">13.6637334823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.682186126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4571714401245</t>
   </si>
   <si>
     <t xml:space="preserve">14.1158094406128</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8482532501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0512256622314</t>
+    <t xml:space="preserve">13.8482542037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0512266159058</t>
   </si>
   <si>
     <t xml:space="preserve">14.0327739715576</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">15.6473274230957</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7303619384766</t>
+    <t xml:space="preserve">15.7303600311279</t>
   </si>
   <si>
     <t xml:space="preserve">17.0865859985352</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">16.7913551330566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.865161895752</t>
+    <t xml:space="preserve">16.8651638031006</t>
   </si>
   <si>
     <t xml:space="preserve">16.7452239990234</t>
@@ -2723,28 +2723,28 @@
     <t xml:space="preserve">16.8190307617188</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1086273193359</t>
+    <t xml:space="preserve">16.1086292266846</t>
   </si>
   <si>
     <t xml:space="preserve">15.9979162216187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9333362579346</t>
+    <t xml:space="preserve">15.9333343505859</t>
   </si>
   <si>
     <t xml:space="preserve">15.4720344543457</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6785955429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3187818527222</t>
+    <t xml:space="preserve">14.678596496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3187808990479</t>
   </si>
   <si>
     <t xml:space="preserve">14.8446645736694</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2967395782471</t>
+    <t xml:space="preserve">15.2967405319214</t>
   </si>
   <si>
     <t xml:space="preserve">15.2044792175293</t>
@@ -2759,31 +2759,31 @@
     <t xml:space="preserve">15.1491222381592</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2506113052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9830541610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1583490371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0753154754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1065826416016</t>
+    <t xml:space="preserve">15.2506093978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9830551147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1583480834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0753145217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1065835952759</t>
   </si>
   <si>
     <t xml:space="preserve">12.6027421951294</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0399551391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9753723144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5878801345825</t>
+    <t xml:space="preserve">12.0399541854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9753713607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5878791809082</t>
   </si>
   <si>
     <t xml:space="preserve">11.301872253418</t>
@@ -2798,16 +2798,16 @@
     <t xml:space="preserve">9.30905342102051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06353950500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97589445114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89285945892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55047369003296</t>
+    <t xml:space="preserve">8.0635404586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97589349746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8928599357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5504732131958</t>
   </si>
   <si>
     <t xml:space="preserve">6.93796634674072</t>
@@ -2816,7 +2816,7 @@
     <t xml:space="preserve">6.90567541122437</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98409652709961</t>
+    <t xml:space="preserve">6.98409605026245</t>
   </si>
   <si>
     <t xml:space="preserve">6.91028785705566</t>
@@ -2825,16 +2825,16 @@
     <t xml:space="preserve">7.01177453994751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47307586669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05431365966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85697937011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33673000335693</t>
+    <t xml:space="preserve">7.47307538986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05431461334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85697841644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33673095703125</t>
   </si>
   <si>
     <t xml:space="preserve">9.01382064819336</t>
@@ -2855,13 +2855,13 @@
     <t xml:space="preserve">8.118896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74985551834106</t>
+    <t xml:space="preserve">7.74985504150391</t>
   </si>
   <si>
     <t xml:space="preserve">7.92976331710815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78675985336304</t>
+    <t xml:space="preserve">7.78675937652588</t>
   </si>
   <si>
     <t xml:space="preserve">8.10967063903809</t>
@@ -2873,37 +2873,37 @@
     <t xml:space="preserve">7.42694520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28855514526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26087665557861</t>
+    <t xml:space="preserve">7.28855466842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26087713241577</t>
   </si>
   <si>
     <t xml:space="preserve">7.32545900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33468437194824</t>
+    <t xml:space="preserve">7.33468389511108</t>
   </si>
   <si>
     <t xml:space="preserve">7.1132607460022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55610942840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77753353118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93437576293945</t>
+    <t xml:space="preserve">7.5561089515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77753448486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93437719345093</t>
   </si>
   <si>
     <t xml:space="preserve">7.60223960876465</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33929777145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51920509338379</t>
+    <t xml:space="preserve">7.33929824829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51920461654663</t>
   </si>
   <si>
     <t xml:space="preserve">7.3070068359375</t>
@@ -2912,10 +2912,10 @@
     <t xml:space="preserve">7.14555168151855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10403442382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15939092636108</t>
+    <t xml:space="preserve">7.10403394699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15939044952393</t>
   </si>
   <si>
     <t xml:space="preserve">7.06713008880615</t>
@@ -2924,25 +2924,25 @@
     <t xml:space="preserve">6.92874002456665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56533432006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54227066040039</t>
+    <t xml:space="preserve">7.56533527374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54227018356323</t>
   </si>
   <si>
     <t xml:space="preserve">7.445396900177</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27010297775269</t>
+    <t xml:space="preserve">7.27010250091553</t>
   </si>
   <si>
     <t xml:space="preserve">7.72217750549316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46948528289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66784477233887</t>
+    <t xml:space="preserve">8.46948623657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66784381866455</t>
   </si>
   <si>
     <t xml:space="preserve">8.90310764312744</t>
@@ -2951,10 +2951,10 @@
     <t xml:space="preserve">8.54329299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69090843200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8754301071167</t>
+    <t xml:space="preserve">8.69090938568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87542915344238</t>
   </si>
   <si>
     <t xml:space="preserve">9.32750511169434</t>
@@ -2963,19 +2963,19 @@
     <t xml:space="preserve">11.0066404342651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4863929748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4956188201904</t>
+    <t xml:space="preserve">11.4863939285278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4956197738647</t>
   </si>
   <si>
     <t xml:space="preserve">11.2557430267334</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9420566558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82571029663086</t>
+    <t xml:space="preserve">10.9420576095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82570934295654</t>
   </si>
   <si>
     <t xml:space="preserve">9.74267578125</t>
@@ -2984,7 +2984,7 @@
     <t xml:space="preserve">10.462306022644</t>
   </si>
   <si>
-    <t xml:space="preserve">10.194751739502</t>
+    <t xml:space="preserve">10.1947507858276</t>
   </si>
   <si>
     <t xml:space="preserve">10.0194549560547</t>
@@ -2993,10 +2993,10 @@
     <t xml:space="preserve">9.89029216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3792695999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.360818862915</t>
+    <t xml:space="preserve">10.3792715072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3608179092407</t>
   </si>
   <si>
     <t xml:space="preserve">10.2224292755127</t>
@@ -3005,13 +3005,13 @@
     <t xml:space="preserve">10.674503326416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5453405380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7667646408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.021502494812</t>
+    <t xml:space="preserve">10.5453395843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7667636871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0215015411377</t>
   </si>
   <si>
     <t xml:space="preserve">11.4402627944946</t>
@@ -3029,22 +3029,22 @@
     <t xml:space="preserve">11.818531036377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7078161239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6616868972778</t>
+    <t xml:space="preserve">11.7078170776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6616878509521</t>
   </si>
   <si>
     <t xml:space="preserve">11.5694274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3480033874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2741956710815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1450300216675</t>
+    <t xml:space="preserve">11.3480024337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2741947174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1450309753418</t>
   </si>
   <si>
     <t xml:space="preserve">10.8128938674927</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">12.0030508041382</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3167352676392</t>
+    <t xml:space="preserve">12.3167362213135</t>
   </si>
   <si>
     <t xml:space="preserve">12.8241662979126</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">13.0548162460327</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3961782455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2854661941528</t>
+    <t xml:space="preserve">13.3961791992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2854671478271</t>
   </si>
   <si>
     <t xml:space="preserve">13.4423084259033</t>
@@ -3077,40 +3077,40 @@
     <t xml:space="preserve">13.1286239624023</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2301111221313</t>
+    <t xml:space="preserve">13.2301120758057</t>
   </si>
   <si>
     <t xml:space="preserve">13.0086870193481</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1932067871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.543794631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3500490188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5714731216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.368501663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1470775604248</t>
+    <t xml:space="preserve">13.1932077407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5437955856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3500499725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5714740753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3685007095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1470766067505</t>
   </si>
   <si>
     <t xml:space="preserve">13.4976654052734</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1101722717285</t>
+    <t xml:space="preserve">13.1101732254028</t>
   </si>
   <si>
     <t xml:space="preserve">13.1655292510986</t>
   </si>
   <si>
-    <t xml:space="preserve">13.267014503479</t>
+    <t xml:space="preserve">13.2670154571533</t>
   </si>
   <si>
     <t xml:space="preserve">13.2762413024902</t>
@@ -3119,43 +3119,43 @@
     <t xml:space="preserve">13.0455904006958</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1747550964355</t>
+    <t xml:space="preserve">13.1747541427612</t>
   </si>
   <si>
     <t xml:space="preserve">13.3315963745117</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3869543075562</t>
+    <t xml:space="preserve">13.3869533538818</t>
   </si>
   <si>
     <t xml:space="preserve">12.5104818344116</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3813180923462</t>
+    <t xml:space="preserve">12.3813171386719</t>
   </si>
   <si>
     <t xml:space="preserve">12.6304187774658</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3351879119873</t>
+    <t xml:space="preserve">12.335186958313</t>
   </si>
   <si>
     <t xml:space="preserve">12.7872619628906</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5068922042847</t>
+    <t xml:space="preserve">13.5068912506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.433084487915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4515361785889</t>
+    <t xml:space="preserve">13.4515342712402</t>
   </si>
   <si>
     <t xml:space="preserve">15.2690591812134</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5735197067261</t>
+    <t xml:space="preserve">15.5735187530518</t>
   </si>
   <si>
     <t xml:space="preserve">15.8318471908569</t>
@@ -3164,22 +3164,22 @@
     <t xml:space="preserve">16.1455326080322</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3613214492798</t>
+    <t xml:space="preserve">15.3613204956055</t>
   </si>
   <si>
     <t xml:space="preserve">15.4628076553345</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7616291046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5217533111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5955610275269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7154989242554</t>
+    <t xml:space="preserve">14.7616300582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5217542648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5955619812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7154998779297</t>
   </si>
   <si>
     <t xml:space="preserve">14.3556852340698</t>
@@ -3206,19 +3206,19 @@
     <t xml:space="preserve">15.6750059127808</t>
   </si>
   <si>
-    <t xml:space="preserve">15.416675567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1029949188232</t>
+    <t xml:space="preserve">15.4166774749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1029939651489</t>
   </si>
   <si>
     <t xml:space="preserve">14.9184722900391</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3889999389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7764930725098</t>
+    <t xml:space="preserve">15.3889989852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7764940261841</t>
   </si>
   <si>
     <t xml:space="preserve">15.5827445983887</t>
@@ -3227,37 +3227,37 @@
     <t xml:space="preserve">16.1547584533691</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8133964538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8410749435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9241094589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1178531646729</t>
+    <t xml:space="preserve">15.8133955001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8410730361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9241075515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1178550720215</t>
   </si>
   <si>
     <t xml:space="preserve">15.8502998352051</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8779773712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3520946502686</t>
+    <t xml:space="preserve">15.8779783248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3520936965942</t>
   </si>
   <si>
     <t xml:space="preserve">15.6381034851074</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4351282119751</t>
+    <t xml:space="preserve">15.4351301193237</t>
   </si>
   <si>
     <t xml:space="preserve">15.5919713973999</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9517889022827</t>
+    <t xml:space="preserve">15.9517869949341</t>
   </si>
   <si>
     <t xml:space="preserve">16.099401473999</t>
@@ -3269,13 +3269,13 @@
     <t xml:space="preserve">16.5145740509033</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7877635955811</t>
+    <t xml:space="preserve">17.7877655029297</t>
   </si>
   <si>
     <t xml:space="preserve">17.3910465240479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4648551940918</t>
+    <t xml:space="preserve">17.4648532867432</t>
   </si>
   <si>
     <t xml:space="preserve">17.1142635345459</t>
@@ -3284,10 +3284,10 @@
     <t xml:space="preserve">17.2618808746338</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5386600494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4463996887207</t>
+    <t xml:space="preserve">17.5386619567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4464015960693</t>
   </si>
   <si>
     <t xml:space="preserve">17.5663394927979</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">17.6216983795166</t>
   </si>
   <si>
-    <t xml:space="preserve">17.547887802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0368671417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4151306152344</t>
+    <t xml:space="preserve">17.5478897094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.036865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.415132522583</t>
   </si>
   <si>
     <t xml:space="preserve">18.7657222747803</t>
@@ -3317,7 +3317,7 @@
     <t xml:space="preserve">19.4299945831299</t>
   </si>
   <si>
-    <t xml:space="preserve">19.448450088501</t>
+    <t xml:space="preserve">19.4484481811523</t>
   </si>
   <si>
     <t xml:space="preserve">18.728816986084</t>
@@ -3326,16 +3326,16 @@
     <t xml:space="preserve">19.245475769043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1901206970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3377323150635</t>
+    <t xml:space="preserve">19.1901187896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3377342224121</t>
   </si>
   <si>
     <t xml:space="preserve">19.2639274597168</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5442981719971</t>
+    <t xml:space="preserve">18.5443000793457</t>
   </si>
   <si>
     <t xml:space="preserve">18.5627517700195</t>
@@ -3350,13 +3350,13 @@
     <t xml:space="preserve">17.9722843170166</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1844825744629</t>
+    <t xml:space="preserve">18.1844806671143</t>
   </si>
   <si>
     <t xml:space="preserve">19.2823791503906</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9651050567627</t>
+    <t xml:space="preserve">19.9651031494141</t>
   </si>
   <si>
     <t xml:space="preserve">20.6109256744385</t>
@@ -3371,19 +3371,19 @@
     <t xml:space="preserve">21.2198429107666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3121032714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1829395294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7513618469238</t>
+    <t xml:space="preserve">21.3121013641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1829376220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7513637542725</t>
   </si>
   <si>
     <t xml:space="preserve">22.7698135375977</t>
   </si>
   <si>
-    <t xml:space="preserve">22.290060043335</t>
+    <t xml:space="preserve">22.2900619506836</t>
   </si>
   <si>
     <t xml:space="preserve">21.8472137451172</t>
@@ -3392,7 +3392,7 @@
     <t xml:space="preserve">22.4745826721191</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7180500030518</t>
+    <t xml:space="preserve">21.7180480957031</t>
   </si>
   <si>
     <t xml:space="preserve">20.5371189117432</t>
@@ -3401,7 +3401,7 @@
     <t xml:space="preserve">20.6293773651123</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7216377258301</t>
+    <t xml:space="preserve">20.7216358184814</t>
   </si>
   <si>
     <t xml:space="preserve">20.1865291595459</t>
@@ -3416,10 +3416,10 @@
     <t xml:space="preserve">21.2013912200928</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4633083343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8728466033936</t>
+    <t xml:space="preserve">20.4633102416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8728446960449</t>
   </si>
   <si>
     <t xml:space="preserve">20.6478290557861</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">20.8508014678955</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0906810760498</t>
+    <t xml:space="preserve">21.0906791687012</t>
   </si>
   <si>
     <t xml:space="preserve">21.109130859375</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">20.2234325408936</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9466514587402</t>
+    <t xml:space="preserve">19.9466533660889</t>
   </si>
   <si>
     <t xml:space="preserve">20.1311721801758</t>
@@ -3446,13 +3446,13 @@
     <t xml:space="preserve">20.112720489502</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6145153045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8543910980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7954483032227</t>
+    <t xml:space="preserve">19.6145172119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8543930053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.795446395874</t>
   </si>
   <si>
     <t xml:space="preserve">20.3156929016113</t>
@@ -3464,13 +3464,13 @@
     <t xml:space="preserve">22.179349899292</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5483913421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0686359405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2162532806396</t>
+    <t xml:space="preserve">22.5483894348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0686378479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.216251373291</t>
   </si>
   <si>
     <t xml:space="preserve">22.1424446105957</t>
@@ -3479,73 +3479,73 @@
     <t xml:space="preserve">22.0132808685303</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2531585693359</t>
+    <t xml:space="preserve">22.2531566619873</t>
   </si>
   <si>
     <t xml:space="preserve">22.0317325592041</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1942100524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7846775054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7293186187744</t>
+    <t xml:space="preserve">23.1942119598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7846755981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.729320526123</t>
   </si>
   <si>
     <t xml:space="preserve">24.3935947418213</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8953876495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.046594619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9174327850342</t>
+    <t xml:space="preserve">23.8953895568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0465927124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9174308776855</t>
   </si>
   <si>
     <t xml:space="preserve">23.3049240112305</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3971862792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5817031860352</t>
+    <t xml:space="preserve">23.3971843719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5817050933838</t>
   </si>
   <si>
     <t xml:space="preserve">23.1388549804688</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5852909088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8067169189453</t>
+    <t xml:space="preserve">22.5852928161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8067188262939</t>
   </si>
   <si>
     <t xml:space="preserve">22.3454170227051</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4894428253174</t>
+    <t xml:space="preserve">23.489444732666</t>
   </si>
   <si>
     <t xml:space="preserve">23.7477722167969</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7662258148193</t>
+    <t xml:space="preserve">23.7662239074707</t>
   </si>
   <si>
     <t xml:space="preserve">23.2311153411865</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7144584655762</t>
+    <t xml:space="preserve">22.7144565582275</t>
   </si>
   <si>
     <t xml:space="preserve">23.6370620727539</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0763206481934</t>
+    <t xml:space="preserve">25.0763187408447</t>
   </si>
   <si>
     <t xml:space="preserve">26.7554550170898</t>
@@ -3560,13 +3560,13 @@
     <t xml:space="preserve">27.1613998413086</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3828239440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4935340881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1578102111816</t>
+    <t xml:space="preserve">27.3828258514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4935359954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.157808303833</t>
   </si>
   <si>
     <t xml:space="preserve">28.04709815979</t>
@@ -3578,16 +3578,16 @@
     <t xml:space="preserve">27.5673427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4012756347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1060428619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9030723571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.497127532959</t>
+    <t xml:space="preserve">27.4012775421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1060409545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9030685424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4971256256104</t>
   </si>
   <si>
     <t xml:space="preserve">25.9251136779785</t>
@@ -3599,19 +3599,19 @@
     <t xml:space="preserve">26.6447410583496</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4602222442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3864135742188</t>
+    <t xml:space="preserve">26.4602241516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3864154815674</t>
   </si>
   <si>
     <t xml:space="preserve">25.9989223480225</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5007152557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9066619873047</t>
+    <t xml:space="preserve">25.5007133483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9066600799561</t>
   </si>
   <si>
     <t xml:space="preserve">26.2572479248047</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">26.1280860900879</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9620132446289</t>
+    <t xml:space="preserve">25.9620151519775</t>
   </si>
   <si>
     <t xml:space="preserve">26.6631927490234</t>
@@ -3629,13 +3629,13 @@
     <t xml:space="preserve">26.3310585021973</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5155773162842</t>
+    <t xml:space="preserve">26.5155754089355</t>
   </si>
   <si>
     <t xml:space="preserve">25.4453582763672</t>
   </si>
   <si>
-    <t xml:space="preserve">26.737003326416</t>
+    <t xml:space="preserve">26.7370014190674</t>
   </si>
   <si>
     <t xml:space="preserve">26.7185497283936</t>
@@ -3644,16 +3644,16 @@
     <t xml:space="preserve">26.8292617797852</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4417686462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.534029006958</t>
+    <t xml:space="preserve">26.4417667388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5340309143066</t>
   </si>
   <si>
     <t xml:space="preserve">25.4269065856934</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3715534210205</t>
+    <t xml:space="preserve">25.3715515136719</t>
   </si>
   <si>
     <t xml:space="preserve">26.5893859863281</t>
@@ -3662,19 +3662,19 @@
     <t xml:space="preserve">27.1983032226562</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4750862121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9143409729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4643154144287</t>
+    <t xml:space="preserve">27.4750843048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.914342880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4643135070801</t>
   </si>
   <si>
     <t xml:space="preserve">30.9625205993652</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5970706939697</t>
+    <t xml:space="preserve">29.5970726013184</t>
   </si>
   <si>
     <t xml:space="preserve">27.0322360992432</t>
@@ -3683,13 +3683,13 @@
     <t xml:space="preserve">26.8846168518066</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3459186553955</t>
+    <t xml:space="preserve">27.3459167480469</t>
   </si>
   <si>
     <t xml:space="preserve">27.6227016448975</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7923564910889</t>
+    <t xml:space="preserve">26.7923583984375</t>
   </si>
   <si>
     <t xml:space="preserve">26.9399757385254</t>
@@ -3701,7 +3701,7 @@
     <t xml:space="preserve">27.8994808197021</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5857963562012</t>
+    <t xml:space="preserve">27.5857944488525</t>
   </si>
   <si>
     <t xml:space="preserve">27.2352066040039</t>
@@ -3710,13 +3710,13 @@
     <t xml:space="preserve">27.2167568206787</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3643703460693</t>
+    <t xml:space="preserve">27.364372253418</t>
   </si>
   <si>
     <t xml:space="preserve">26.6262912750244</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2536602020264</t>
+    <t xml:space="preserve">27.2536582946777</t>
   </si>
   <si>
     <t xml:space="preserve">27.7703170776367</t>
@@ -3731,19 +3731,19 @@
     <t xml:space="preserve">28.674467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0286464691162</t>
+    <t xml:space="preserve">28.0286445617676</t>
   </si>
   <si>
     <t xml:space="preserve">27.8072185516357</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3423290252686</t>
+    <t xml:space="preserve">28.3423271179199</t>
   </si>
   <si>
     <t xml:space="preserve">27.917932510376</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6965065002441</t>
+    <t xml:space="preserve">27.6965084075928</t>
   </si>
   <si>
     <t xml:space="preserve">27.050687789917</t>
@@ -3755,10 +3755,10 @@
     <t xml:space="preserve">27.8256721496582</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9732875823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3054256439209</t>
+    <t xml:space="preserve">27.9732894897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3054275512695</t>
   </si>
   <si>
     <t xml:space="preserve">28.2869739532471</t>
@@ -3767,16 +3767,16 @@
     <t xml:space="preserve">28.0840015411377</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7887668609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2941551208496</t>
+    <t xml:space="preserve">27.7887687683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.294153213501</t>
   </si>
   <si>
     <t xml:space="preserve">26.9953308105469</t>
   </si>
   <si>
-    <t xml:space="preserve">26.220344543457</t>
+    <t xml:space="preserve">26.2203464508057</t>
   </si>
   <si>
     <t xml:space="preserve">25.5191669464111</t>
@@ -3788,13 +3788,13 @@
     <t xml:space="preserve">24.0983619689941</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9656047821045</t>
+    <t xml:space="preserve">24.9656066894531</t>
   </si>
   <si>
     <t xml:space="preserve">24.356689453125</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7108669281006</t>
+    <t xml:space="preserve">23.7108688354492</t>
   </si>
   <si>
     <t xml:space="preserve">23.3418273925781</t>
@@ -3806,37 +3806,37 @@
     <t xml:space="preserve">24.0614566802979</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2090740203857</t>
+    <t xml:space="preserve">24.2090721130371</t>
   </si>
   <si>
     <t xml:space="preserve">24.7441825866699</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6334705352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2423858642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0947704315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9102516174316</t>
+    <t xml:space="preserve">24.633472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2423877716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0947723388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.910249710083</t>
   </si>
   <si>
     <t xml:space="preserve">24.984058380127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8179893493652</t>
+    <t xml:space="preserve">24.8179912567139</t>
   </si>
   <si>
     <t xml:space="preserve">25.1870307922363</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6703758239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.537618637085</t>
+    <t xml:space="preserve">24.670373916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5376205444336</t>
   </si>
   <si>
     <t xml:space="preserve">24.8733463287354</t>
@@ -3845,7 +3845,7 @@
     <t xml:space="preserve">24.9287033081055</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8364410400391</t>
+    <t xml:space="preserve">24.8364429473877</t>
   </si>
   <si>
     <t xml:space="preserve">24.2644290924072</t>
@@ -3854,10 +3854,10 @@
     <t xml:space="preserve">24.3013343811035</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8769359588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5263481140137</t>
+    <t xml:space="preserve">23.8769340515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.526346206665</t>
   </si>
   <si>
     <t xml:space="preserve">23.1573066711426</t>
@@ -3869,22 +3869,22 @@
     <t xml:space="preserve">21.8287620544434</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8841133117676</t>
+    <t xml:space="preserve">21.8841152191162</t>
   </si>
   <si>
     <t xml:space="preserve">21.0353202819824</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7031879425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.736499786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4597187042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5335292816162</t>
+    <t xml:space="preserve">20.7031860351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7365016937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4597206115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5335273742676</t>
   </si>
   <si>
     <t xml:space="preserve">22.6591033935547</t>
@@ -3902,7 +3902,7 @@
     <t xml:space="preserve">21.9948291778564</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5299396514893</t>
+    <t xml:space="preserve">22.5299377441406</t>
   </si>
   <si>
     <t xml:space="preserve">22.5114860534668</t>
@@ -3917,16 +3917,16 @@
     <t xml:space="preserve">22.8620738983154</t>
   </si>
   <si>
-    <t xml:space="preserve">22.935884475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3085136413574</t>
+    <t xml:space="preserve">22.9358825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3085117340088</t>
   </si>
   <si>
     <t xml:space="preserve">21.3859119415283</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3674583435059</t>
+    <t xml:space="preserve">21.3674602508545</t>
   </si>
   <si>
     <t xml:space="preserve">21.8103084564209</t>
@@ -3935,7 +3935,7 @@
     <t xml:space="preserve">19.928201675415</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0758171081543</t>
+    <t xml:space="preserve">20.0758190155029</t>
   </si>
   <si>
     <t xml:space="preserve">20.8877048492432</t>
@@ -3944,13 +3944,13 @@
     <t xml:space="preserve">20.4448585510254</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2787895202637</t>
+    <t xml:space="preserve">20.278787612915</t>
   </si>
   <si>
     <t xml:space="preserve">19.8174877166748</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8138980865479</t>
+    <t xml:space="preserve">20.8138961791992</t>
   </si>
   <si>
     <t xml:space="preserve">20.2049808502197</t>
@@ -3959,7 +3959,7 @@
     <t xml:space="preserve">20.5002117156982</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7585391998291</t>
+    <t xml:space="preserve">20.7585430145264</t>
   </si>
   <si>
     <t xml:space="preserve">20.3710498809814</t>
@@ -3968,13 +3968,13 @@
     <t xml:space="preserve">20.0204620361328</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9871463775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5073909759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6770496368408</t>
+    <t xml:space="preserve">18.9871444702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5073928833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6770515441895</t>
   </si>
   <si>
     <t xml:space="preserve">18.1291275024414</t>
@@ -3989,16 +3989,16 @@
     <t xml:space="preserve">17.3633670806885</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0845413208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2321577072144</t>
+    <t xml:space="preserve">15.0845403671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.23215675354</t>
   </si>
   <si>
     <t xml:space="preserve">16.2839221954346</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3705472946167</t>
+    <t xml:space="preserve">15.3705463409424</t>
   </si>
   <si>
     <t xml:space="preserve">16.23779296875</t>
@@ -4007,7 +4007,7 @@
     <t xml:space="preserve">13.4699878692627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2172946929932</t>
+    <t xml:space="preserve">14.2172956466675</t>
   </si>
   <si>
     <t xml:space="preserve">14.0604524612427</t>
@@ -4022,7 +4022,7 @@
     <t xml:space="preserve">14.8169851303101</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2634239196777</t>
+    <t xml:space="preserve">14.2634248733521</t>
   </si>
   <si>
     <t xml:space="preserve">14.2541990280151</t>
@@ -4034,7 +4034,7 @@
     <t xml:space="preserve">15.82262134552</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6565542221069</t>
+    <t xml:space="preserve">15.6565532684326</t>
   </si>
   <si>
     <t xml:space="preserve">14.0420007705688</t>
@@ -4046,10 +4046,10 @@
     <t xml:space="preserve">13.8205757141113</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3649110794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8667068481445</t>
+    <t xml:space="preserve">14.3649101257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8667058944702</t>
   </si>
   <si>
     <t xml:space="preserve">13.617603302002</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">13.8113508224487</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8057146072388</t>
+    <t xml:space="preserve">12.8057136535645</t>
   </si>
   <si>
     <t xml:space="preserve">12.7134532928467</t>
@@ -4067,28 +4067,28 @@
     <t xml:space="preserve">13.3592748641968</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9461517333984</t>
+    <t xml:space="preserve">14.9461507797241</t>
   </si>
   <si>
     <t xml:space="preserve">15.0476360321045</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3059644699097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.342869758606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0384101867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2341136932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7736368179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9367227554321</t>
+    <t xml:space="preserve">15.305965423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3428688049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0384092330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.234112739563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7736358642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9367218017578</t>
   </si>
   <si>
     <t xml:space="preserve">15.349232673645</t>
@@ -4097,28 +4097,28 @@
     <t xml:space="preserve">15.4739437103271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9823894500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5410995483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7137765884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.780930519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0303535461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8576774597168</t>
+    <t xml:space="preserve">15.9823875427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5410985946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7137756347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7809314727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0303554534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8576755523682</t>
   </si>
   <si>
     <t xml:space="preserve">15.6466236114502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3204526901245</t>
+    <t xml:space="preserve">15.3204536437988</t>
   </si>
   <si>
     <t xml:space="preserve">14.5529918670654</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">13.1427803039551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0180683135986</t>
+    <t xml:space="preserve">13.0180673599243</t>
   </si>
   <si>
     <t xml:space="preserve">13.0660343170166</t>
@@ -4157,10 +4157,10 @@
     <t xml:space="preserve">12.7494564056396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8453893661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5959644317627</t>
+    <t xml:space="preserve">12.8453903198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5959634780884</t>
   </si>
   <si>
     <t xml:space="preserve">12.1258945465088</t>
@@ -4190,13 +4190,13 @@
     <t xml:space="preserve">12.7206764221191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6823034286499</t>
+    <t xml:space="preserve">12.6823043823242</t>
   </si>
   <si>
     <t xml:space="preserve">12.2026405334473</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8933553695679</t>
+    <t xml:space="preserve">12.8933544158936</t>
   </si>
   <si>
     <t xml:space="preserve">13.1715593338013</t>
@@ -4214,7 +4214,7 @@
     <t xml:space="preserve">12.4328784942627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7782363891602</t>
+    <t xml:space="preserve">12.7782354354858</t>
   </si>
   <si>
     <t xml:space="preserve">13.3058662414551</t>
@@ -4226,7 +4226,7 @@
     <t xml:space="preserve">13.3154592514038</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4808444976807</t>
+    <t xml:space="preserve">12.480845451355</t>
   </si>
   <si>
     <t xml:space="preserve">12.6055583953857</t>
@@ -4244,7 +4244,7 @@
     <t xml:space="preserve">12.3945055007935</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2506065368652</t>
+    <t xml:space="preserve">12.2506074905396</t>
   </si>
   <si>
     <t xml:space="preserve">11.8668756484985</t>
@@ -4253,7 +4253,7 @@
     <t xml:space="preserve">12.0107755661011</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1546745300293</t>
+    <t xml:space="preserve">12.154673576355</t>
   </si>
   <si>
     <t xml:space="preserve">12.2218265533447</t>
@@ -4262,25 +4262,25 @@
     <t xml:space="preserve">12.3081655502319</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1163005828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1834526062012</t>
+    <t xml:space="preserve">12.1162996292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1834535598755</t>
   </si>
   <si>
     <t xml:space="preserve">11.8476886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.164267539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4927377700806</t>
+    <t xml:space="preserve">12.1642665863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4927368164062</t>
   </si>
   <si>
     <t xml:space="preserve">11.4639577865601</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3296527862549</t>
+    <t xml:space="preserve">11.3296518325806</t>
   </si>
   <si>
     <t xml:space="preserve">11.6654167175293</t>
@@ -4310,7 +4310,7 @@
     <t xml:space="preserve">11.2720928192139</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9363269805908</t>
+    <t xml:space="preserve">10.9363279342651</t>
   </si>
   <si>
     <t xml:space="preserve">10.9459209442139</t>
@@ -4334,7 +4334,7 @@
     <t xml:space="preserve">11.6558227539062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5694847106934</t>
+    <t xml:space="preserve">11.569483757019</t>
   </si>
   <si>
     <t xml:space="preserve">11.5790777206421</t>
@@ -4376,7 +4376,7 @@
     <t xml:space="preserve">11.8956546783447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7229776382446</t>
+    <t xml:space="preserve">11.7229766845703</t>
   </si>
   <si>
     <t xml:space="preserve">12.7398624420166</t>
@@ -4388,7 +4388,7 @@
     <t xml:space="preserve">12.0875205993652</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2601985931396</t>
+    <t xml:space="preserve">12.260199546814</t>
   </si>
   <si>
     <t xml:space="preserve">12.1930465698242</t>
@@ -4403,7 +4403,7 @@
     <t xml:space="preserve">12.5671844482422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2314195632935</t>
+    <t xml:space="preserve">12.2314186096191</t>
   </si>
   <si>
     <t xml:space="preserve">12.106707572937</t>
@@ -4421,34 +4421,34 @@
     <t xml:space="preserve">12.3273525238037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3177585601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4616584777832</t>
+    <t xml:space="preserve">12.317759513855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4616575241089</t>
   </si>
   <si>
     <t xml:space="preserve">11.991587638855</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9244356155396</t>
+    <t xml:space="preserve">11.9244346618652</t>
   </si>
   <si>
     <t xml:space="preserve">12.0395536422729</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0587406158447</t>
+    <t xml:space="preserve">12.058741569519</t>
   </si>
   <si>
     <t xml:space="preserve">12.5000305175781</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8262033462524</t>
+    <t xml:space="preserve">12.8262023925781</t>
   </si>
   <si>
     <t xml:space="preserve">13.0852212905884</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7471561431885</t>
+    <t xml:space="preserve">13.7471551895142</t>
   </si>
   <si>
     <t xml:space="preserve">13.83349609375</t>
@@ -4469,16 +4469,16 @@
     <t xml:space="preserve">14.2172260284424</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2364130020142</t>
+    <t xml:space="preserve">14.2364139556885</t>
   </si>
   <si>
     <t xml:space="preserve">13.7855291366577</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8143091201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1404809951782</t>
+    <t xml:space="preserve">13.8143100738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1404800415039</t>
   </si>
   <si>
     <t xml:space="preserve">14.1980409622192</t>
@@ -4496,13 +4496,13 @@
     <t xml:space="preserve">14.1692609786987</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7160768508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9463157653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4378719329834</t>
+    <t xml:space="preserve">14.7160778045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9463148117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4378728866577</t>
   </si>
   <si>
     <t xml:space="preserve">14.3899059295654</t>
@@ -4511,22 +4511,22 @@
     <t xml:space="preserve">14.313159942627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4474649429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3323459625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3515329360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5721778869629</t>
+    <t xml:space="preserve">14.4474658966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3323450088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3515319824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5721769332886</t>
   </si>
   <si>
     <t xml:space="preserve">14.5242118835449</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6009578704834</t>
+    <t xml:space="preserve">14.6009588241577</t>
   </si>
   <si>
     <t xml:space="preserve">14.3611268997192</t>
@@ -4535,7 +4535,7 @@
     <t xml:space="preserve">16.0879135131836</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8288974761963</t>
+    <t xml:space="preserve">15.828896522522</t>
   </si>
   <si>
     <t xml:space="preserve">16.2510013580322</t>
@@ -4544,10 +4544,10 @@
     <t xml:space="preserve">16.3373394012451</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7210712432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3277454376221</t>
+    <t xml:space="preserve">16.7210693359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3277473449707</t>
   </si>
   <si>
     <t xml:space="preserve">16.2030334472656</t>
@@ -4556,10 +4556,10 @@
     <t xml:space="preserve">16.2318134307861</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1454753875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0207614898682</t>
+    <t xml:space="preserve">16.1454734802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0207633972168</t>
   </si>
   <si>
     <t xml:space="preserve">15.3588256835938</t>
@@ -4586,22 +4586,22 @@
     <t xml:space="preserve">14.044548034668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9390211105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0541410446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0061750411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3922052383423</t>
+    <t xml:space="preserve">13.939022064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.054141998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.006175994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3922061920166</t>
   </si>
   <si>
     <t xml:space="preserve">13.6416311264038</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5552911758423</t>
+    <t xml:space="preserve">13.555290222168</t>
   </si>
   <si>
     <t xml:space="preserve">13.459358215332</t>
@@ -4616,7 +4616,7 @@
     <t xml:space="preserve">13.4305791854858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.353832244873</t>
+    <t xml:space="preserve">13.3538331985474</t>
   </si>
   <si>
     <t xml:space="preserve">13.2195262908936</t>
@@ -4631,7 +4631,7 @@
     <t xml:space="preserve">12.9701023101807</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2579002380371</t>
+    <t xml:space="preserve">13.2578992843628</t>
   </si>
   <si>
     <t xml:space="preserve">13.0276613235474</t>
@@ -6006,6 +6006,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.82000017166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84999990463257</t>
   </si>
 </sst>
 </file>
@@ -71630,7 +71633,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.6922916667</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>154838</v>
@@ -71651,6 +71654,32 @@
         <v>1997</v>
       </c>
       <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>45978.6928472222</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>146687</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>5.84000015258789</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>5.84999990463257</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>1998</v>
+      </c>
+      <c r="H2513" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1999" uniqueCount="1999">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="2000">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2523965835571</t>
+    <t xml:space="preserve">13.2523994445801</t>
   </si>
   <si>
     <t xml:space="preserve">BSS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9788007736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7479515075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.397403717041</t>
+    <t xml:space="preserve">12.9787998199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.747953414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3974046707153</t>
   </si>
   <si>
     <t xml:space="preserve">12.243504524231</t>
@@ -59,19 +59,19 @@
     <t xml:space="preserve">12.2606058120728</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1409063339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4825620651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.858416557312</t>
+    <t xml:space="preserve">12.140905380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4825611114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8584156036377</t>
   </si>
   <si>
     <t xml:space="preserve">9.79822540283203</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3539695739746</t>
+    <t xml:space="preserve">10.3539705276489</t>
   </si>
   <si>
     <t xml:space="preserve">9.84952354431152</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">10.8156661987305</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7301683425903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5762691497803</t>
+    <t xml:space="preserve">10.730167388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.576268196106</t>
   </si>
   <si>
     <t xml:space="preserve">10.6361179351807</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1915216445923</t>
+    <t xml:space="preserve">10.191520690918</t>
   </si>
   <si>
     <t xml:space="preserve">10.4565687179565</t>
@@ -110,28 +110,28 @@
     <t xml:space="preserve">10.0205221176147</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03728103637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97742938995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40492725372314</t>
+    <t xml:space="preserve">9.03728008270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97743034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40492630004883</t>
   </si>
   <si>
     <t xml:space="preserve">9.14842891693115</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43057632446289</t>
+    <t xml:space="preserve">9.43057727813721</t>
   </si>
   <si>
     <t xml:space="preserve">9.90082359313965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66142559051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4394683837891</t>
+    <t xml:space="preserve">9.66142654418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4394693374634</t>
   </si>
   <si>
     <t xml:space="preserve">10.3454208374023</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">10.2257213592529</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1829710006714</t>
+    <t xml:space="preserve">10.1829719543457</t>
   </si>
   <si>
     <t xml:space="preserve">11.0379648208618</t>
@@ -158,16 +158,16 @@
     <t xml:space="preserve">10.9097166061401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8074588775635</t>
+    <t xml:space="preserve">11.8074598312378</t>
   </si>
   <si>
     <t xml:space="preserve">11.9442577362061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1067066192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7732591629028</t>
+    <t xml:space="preserve">12.106707572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7732601165771</t>
   </si>
   <si>
     <t xml:space="preserve">11.9699077606201</t>
@@ -185,25 +185,25 @@
     <t xml:space="preserve">11.6621103286743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8416595458984</t>
+    <t xml:space="preserve">11.8416604995728</t>
   </si>
   <si>
     <t xml:space="preserve">11.918607711792</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7989091873169</t>
+    <t xml:space="preserve">11.7989082336426</t>
   </si>
   <si>
     <t xml:space="preserve">12.0468578338623</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1922054290771</t>
+    <t xml:space="preserve">12.1922044754028</t>
   </si>
   <si>
     <t xml:space="preserve">12.200756072998</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3375558853149</t>
+    <t xml:space="preserve">12.3375549316406</t>
   </si>
   <si>
     <t xml:space="preserve">12.1323575973511</t>
@@ -212,10 +212,10 @@
     <t xml:space="preserve">12.1665563583374</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2178564071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9015083312988</t>
+    <t xml:space="preserve">12.2178554534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9015073776245</t>
   </si>
   <si>
     <t xml:space="preserve">11.568060874939</t>
@@ -227,25 +227,25 @@
     <t xml:space="preserve">11.7390584945679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.884407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8160085678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7048597335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6022605895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6364583969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4740123748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1918630599976</t>
+    <t xml:space="preserve">11.8844089508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8160076141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7048606872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6022596359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6364593505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4740114212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1918640136719</t>
   </si>
   <si>
     <t xml:space="preserve">11.1063642501831</t>
@@ -257,19 +257,19 @@
     <t xml:space="preserve">11.3201112747192</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457632064819</t>
+    <t xml:space="preserve">11.3457622528076</t>
   </si>
   <si>
     <t xml:space="preserve">11.1576642990112</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0550661087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9866647720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1405639648438</t>
+    <t xml:space="preserve">11.055064201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.986665725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1405630111694</t>
   </si>
   <si>
     <t xml:space="preserve">10.60191822052</t>
@@ -278,40 +278,40 @@
     <t xml:space="preserve">10.954140663147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4346113204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3553619384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2232780456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2673044204712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92388725280762</t>
+    <t xml:space="preserve">10.4346132278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3553628921509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2232789993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2673053741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92388820648193</t>
   </si>
   <si>
     <t xml:space="preserve">10.3201389312744</t>
   </si>
   <si>
-    <t xml:space="preserve">10.003137588501</t>
+    <t xml:space="preserve">10.0031385421753</t>
   </si>
   <si>
     <t xml:space="preserve">10.302529335022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2496938705444</t>
+    <t xml:space="preserve">10.2496948242188</t>
   </si>
   <si>
     <t xml:space="preserve">10.6107234954834</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4120302200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1302537918091</t>
+    <t xml:space="preserve">11.4120311737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1302528381348</t>
   </si>
   <si>
     <t xml:space="preserve">10.9189195632935</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">11.2359199523926</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2799463272095</t>
+    <t xml:space="preserve">11.2799472808838</t>
   </si>
   <si>
     <t xml:space="preserve">11.0069751739502</t>
@@ -335,13 +335,13 @@
     <t xml:space="preserve">10.9277248382568</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9101123809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8132524490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5138607025146</t>
+    <t xml:space="preserve">10.9101133346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8132514953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5138626098633</t>
   </si>
   <si>
     <t xml:space="preserve">10.0647773742676</t>
@@ -350,19 +350,19 @@
     <t xml:space="preserve">9.99433326721191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95030498504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68613815307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0383596420288</t>
+    <t xml:space="preserve">9.9503059387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68613719940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0383605957031</t>
   </si>
   <si>
     <t xml:space="preserve">10.4962511062622</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3465566635132</t>
+    <t xml:space="preserve">10.3465557098389</t>
   </si>
   <si>
     <t xml:space="preserve">10.4522228240967</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">10.5843067169189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87985992431641</t>
+    <t xml:space="preserve">9.87986087799072</t>
   </si>
   <si>
     <t xml:space="preserve">9.12258052825928</t>
@@ -380,13 +380,13 @@
     <t xml:space="preserve">9.67733192443848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57166481018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.932692527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1880559921265</t>
+    <t xml:space="preserve">9.57166576385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93269348144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1880550384521</t>
   </si>
   <si>
     <t xml:space="preserve">9.98552703857422</t>
@@ -398,13 +398,13 @@
     <t xml:space="preserve">9.14019107818604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72136116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0823879241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3817777633667</t>
+    <t xml:space="preserve">9.72135925292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0823888778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.381778717041</t>
   </si>
   <si>
     <t xml:space="preserve">10.2849178314209</t>
@@ -413,10 +413,10 @@
     <t xml:space="preserve">10.1352224349976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2144727706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.15283203125</t>
+    <t xml:space="preserve">10.2144737243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1528329849243</t>
   </si>
   <si>
     <t xml:space="preserve">10.6987791061401</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">11.0774183273315</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0157804489136</t>
+    <t xml:space="preserve">11.0157814025879</t>
   </si>
   <si>
     <t xml:space="preserve">11.0333909988403</t>
@@ -434,31 +434,31 @@
     <t xml:space="preserve">10.9893627166748</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8748912811279</t>
+    <t xml:space="preserve">10.8748931884766</t>
   </si>
   <si>
     <t xml:space="preserve">11.0950307846069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2535305023193</t>
+    <t xml:space="preserve">11.253529548645</t>
   </si>
   <si>
     <t xml:space="preserve">11.3151702880859</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7251958847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0510034561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9013080596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1654739379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0598087310791</t>
+    <t xml:space="preserve">10.7251968383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0510025024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9013071060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1654748916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0598096847534</t>
   </si>
   <si>
     <t xml:space="preserve">11.2183084487915</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">11.1214475631714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1830863952637</t>
+    <t xml:space="preserve">11.1830854415894</t>
   </si>
   <si>
     <t xml:space="preserve">11.262336730957</t>
@@ -485,22 +485,22 @@
     <t xml:space="preserve">11.6850051879883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7994766235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6497812271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6673927307129</t>
+    <t xml:space="preserve">11.7994756698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6497821807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6673917770386</t>
   </si>
   <si>
     <t xml:space="preserve">11.4472532272339</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3239755630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3680038452148</t>
+    <t xml:space="preserve">11.323974609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3680047988892</t>
   </si>
   <si>
     <t xml:space="preserve">11.1390581130981</t>
@@ -509,22 +509,22 @@
     <t xml:space="preserve">11.6938095092773</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6145572662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8258943557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0372266769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.054838180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0636434555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5039234161377</t>
+    <t xml:space="preserve">11.6145601272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8258934020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0372257232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0548391342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0636444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5039215087891</t>
   </si>
   <si>
     <t xml:space="preserve">12.5303392410278</t>
@@ -533,16 +533,16 @@
     <t xml:space="preserve">12.4070625305176</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2837829589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6007852554321</t>
+    <t xml:space="preserve">12.283784866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6007843017578</t>
   </si>
   <si>
     <t xml:space="preserve">12.9177865982056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8121185302734</t>
+    <t xml:space="preserve">12.8121194839478</t>
   </si>
   <si>
     <t xml:space="preserve">12.856146812439</t>
@@ -551,52 +551,52 @@
     <t xml:space="preserve">13.0322580337524</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4108982086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5782041549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6838712692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4285097122192</t>
+    <t xml:space="preserve">13.4108972549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5782022476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6838703155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4285087585449</t>
   </si>
   <si>
     <t xml:space="preserve">14.3707056045532</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2210102081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2562341690063</t>
+    <t xml:space="preserve">14.2210111618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.256233215332</t>
   </si>
   <si>
     <t xml:space="preserve">14.1329545974731</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1241512298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0713157653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9216222763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7807312011719</t>
+    <t xml:space="preserve">14.1241502761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0713167190552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9216203689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7807321548462</t>
   </si>
   <si>
     <t xml:space="preserve">13.6046209335327</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7631216049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8335647583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7278985977173</t>
+    <t xml:space="preserve">13.7631206512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8335657119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7278995513916</t>
   </si>
   <si>
     <t xml:space="preserve">13.1995639801025</t>
@@ -608,43 +608,43 @@
     <t xml:space="preserve">13.155535697937</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6486473083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5605926513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7367038726807</t>
+    <t xml:space="preserve">13.6486492156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5605916976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7367057800293</t>
   </si>
   <si>
     <t xml:space="preserve">13.8775939941406</t>
   </si>
   <si>
-    <t xml:space="preserve">14.176983833313</t>
+    <t xml:space="preserve">14.1769847869873</t>
   </si>
   <si>
     <t xml:space="preserve">14.0977334976196</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7845697402954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3040981292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2776803970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4890146255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4978227615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3657369613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4449863433838</t>
+    <t xml:space="preserve">14.7845687866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3040971755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.277681350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4890165328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.497820854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3657379150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4449853897095</t>
   </si>
   <si>
     <t xml:space="preserve">15.3393201828003</t>
@@ -653,19 +653,19 @@
     <t xml:space="preserve">15.5330410003662</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6651268005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5418481826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2424573898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8060178756714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1934585571289</t>
+    <t xml:space="preserve">15.6651277542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5418491363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2424592971802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8060159683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1934604644775</t>
   </si>
   <si>
     <t xml:space="preserve">16.3695735931396</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">16.4664344787598</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5104598999023</t>
+    <t xml:space="preserve">16.510461807251</t>
   </si>
   <si>
     <t xml:space="preserve">17.03879737854</t>
@@ -689,28 +689,28 @@
     <t xml:space="preserve">16.7746276855469</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5544910430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.237491607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5897102355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6513500213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5720996856689</t>
+    <t xml:space="preserve">16.5544891357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2374877929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5897121429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6513519287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5721015930176</t>
   </si>
   <si>
     <t xml:space="preserve">16.9947681427002</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7041854858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8802947998047</t>
+    <t xml:space="preserve">16.7041835784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8802967071533</t>
   </si>
   <si>
     <t xml:space="preserve">16.8538780212402</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">17.0123805999756</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2941589355469</t>
+    <t xml:space="preserve">17.2941570281982</t>
   </si>
   <si>
     <t xml:space="preserve">17.1268520355225</t>
@@ -728,19 +728,19 @@
     <t xml:space="preserve">16.5368804931641</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0828227996826</t>
+    <t xml:space="preserve">17.0828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">16.8626842498779</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2061042785645</t>
+    <t xml:space="preserve">17.2061023712158</t>
   </si>
   <si>
     <t xml:space="preserve">17.3469924926758</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6551876068115</t>
+    <t xml:space="preserve">17.6551856994629</t>
   </si>
   <si>
     <t xml:space="preserve">17.540714263916</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">17.7168273925781</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4526596069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5583267211914</t>
+    <t xml:space="preserve">17.4526615142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5583248138428</t>
   </si>
   <si>
     <t xml:space="preserve">17.7432422637939</t>
@@ -764,16 +764,16 @@
     <t xml:space="preserve">17.8401031494141</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5759353637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7482128143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7658252716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9507446289062</t>
+    <t xml:space="preserve">17.5759372711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7482147216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7658233642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.950740814209</t>
   </si>
   <si>
     <t xml:space="preserve">17.1620750427246</t>
@@ -785,70 +785,70 @@
     <t xml:space="preserve">16.6865749359131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1092414855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8186569213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2325191497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2853527069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.391019821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.250129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4350452423096</t>
+    <t xml:space="preserve">17.109245300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8186588287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2325172424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2853507995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3910217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2501316070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4350471496582</t>
   </si>
   <si>
     <t xml:space="preserve">17.3734111785889</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6463832855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9457702636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3722763061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9358348846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3849182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5962505340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3408870697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8340034484863</t>
+    <t xml:space="preserve">17.6463813781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9457721710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3722743988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9358329772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3849143981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5962524414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3408908843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8339996337891</t>
   </si>
   <si>
     <t xml:space="preserve">21.0453338623047</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5824756622314</t>
+    <t xml:space="preserve">21.5824775695801</t>
   </si>
   <si>
     <t xml:space="preserve">21.0893630981445</t>
   </si>
   <si>
-    <t xml:space="preserve">21.327112197876</t>
+    <t xml:space="preserve">21.3271141052246</t>
   </si>
   <si>
     <t xml:space="preserve">21.6529216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7497825622559</t>
+    <t xml:space="preserve">21.7497863769531</t>
   </si>
   <si>
     <t xml:space="preserve">21.917085647583</t>
@@ -863,13 +863,13 @@
     <t xml:space="preserve">22.286922454834</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2605075836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.348560333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3221454620361</t>
+    <t xml:space="preserve">22.2605056762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3485584259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3221473693848</t>
   </si>
   <si>
     <t xml:space="preserve">22.1900615692139</t>
@@ -881,31 +881,31 @@
     <t xml:space="preserve">22.436616897583</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4806442260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6655597686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6215324401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6743698120117</t>
+    <t xml:space="preserve">22.4806461334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6655616760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6215343475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6743659973145</t>
   </si>
   <si>
     <t xml:space="preserve">22.8945064544678</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0970344543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8328704833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3749771118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1938972473145</t>
+    <t xml:space="preserve">23.0970325469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8328685760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.374979019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1938953399658</t>
   </si>
   <si>
     <t xml:space="preserve">23.3876190185547</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">24.2417621612549</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7084541320801</t>
+    <t xml:space="preserve">24.7084560394287</t>
   </si>
   <si>
     <t xml:space="preserve">24.6556243896484</t>
@@ -929,40 +929,40 @@
     <t xml:space="preserve">24.9197883605957</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0870990753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9638214111328</t>
+    <t xml:space="preserve">25.0870971679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9638195037842</t>
   </si>
   <si>
     <t xml:space="preserve">24.8933715820312</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4255466461182</t>
+    <t xml:space="preserve">26.4255447387695</t>
   </si>
   <si>
     <t xml:space="preserve">26.4879302978516</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3970069885254</t>
+    <t xml:space="preserve">27.3970050811768</t>
   </si>
   <si>
     <t xml:space="preserve">27.6287326812744</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1545696258545</t>
+    <t xml:space="preserve">28.1545715332031</t>
   </si>
   <si>
     <t xml:space="preserve">27.6732940673828</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6804046630859</t>
+    <t xml:space="preserve">28.6804065704346</t>
   </si>
   <si>
     <t xml:space="preserve">29.3666706085205</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8069820404053</t>
+    <t xml:space="preserve">27.8069839477539</t>
   </si>
   <si>
     <t xml:space="preserve">28.4665069580078</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">29.7677326202393</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8746814727783</t>
+    <t xml:space="preserve">29.8746795654297</t>
   </si>
   <si>
     <t xml:space="preserve">30.3024806976318</t>
@@ -986,37 +986,37 @@
     <t xml:space="preserve">30.7748432159424</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2400932312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6678943634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8283157348633</t>
+    <t xml:space="preserve">30.2400913238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6678905487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8283176422119</t>
   </si>
   <si>
     <t xml:space="preserve">30.8996162414551</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0154819488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9976577758789</t>
+    <t xml:space="preserve">31.0154781341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9976558685303</t>
   </si>
   <si>
     <t xml:space="preserve">30.9352645874023</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6500682830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7481060028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.685718536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3577556610107</t>
+    <t xml:space="preserve">30.6500663757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.748104095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6857166290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3577537536621</t>
   </si>
   <si>
     <t xml:space="preserve">29.5003547668457</t>
@@ -1028,25 +1028,25 @@
     <t xml:space="preserve">29.2775440216064</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1687927246094</t>
+    <t xml:space="preserve">30.1687908172607</t>
   </si>
   <si>
     <t xml:space="preserve">30.1331443786621</t>
   </si>
   <si>
-    <t xml:space="preserve">29.999454498291</t>
+    <t xml:space="preserve">29.9994583129883</t>
   </si>
   <si>
     <t xml:space="preserve">29.9281558990479</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0529346466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4825305938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8122959136963</t>
+    <t xml:space="preserve">30.0529327392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4825325012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8122940063477</t>
   </si>
   <si>
     <t xml:space="preserve">28.9121284484863</t>
@@ -1079,64 +1079,64 @@
     <t xml:space="preserve">28.350643157959</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7178573608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5734577178955</t>
+    <t xml:space="preserve">27.7178592681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5734596252441</t>
   </si>
   <si>
     <t xml:space="preserve">28.6180210113525</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5199813842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7873554229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7855548858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5360069274902</t>
+    <t xml:space="preserve">28.519983291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7873573303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7855529785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5360050201416</t>
   </si>
   <si>
     <t xml:space="preserve">29.331018447876</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1705932617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.232982635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1438541412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3221092224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9656066894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.707145690918</t>
+    <t xml:space="preserve">29.1705913543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2329807281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.143856048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3221073150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9656085968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7071437835693</t>
   </si>
   <si>
     <t xml:space="preserve">28.9923419952393</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9477806091309</t>
+    <t xml:space="preserve">28.9477825164795</t>
   </si>
   <si>
     <t xml:space="preserve">29.6073036193848</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8568572998047</t>
+    <t xml:space="preserve">29.8568553924561</t>
   </si>
   <si>
     <t xml:space="preserve">29.4023208618164</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4112300872803</t>
+    <t xml:space="preserve">29.4112319946289</t>
   </si>
   <si>
     <t xml:space="preserve">28.814094543457</t>
@@ -1151,28 +1151,28 @@
     <t xml:space="preserve">29.6786060333252</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6964302062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.142053604126</t>
+    <t xml:space="preserve">29.6964321136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1420555114746</t>
   </si>
   <si>
     <t xml:space="preserve">29.8390312194824</t>
   </si>
   <si>
-    <t xml:space="preserve">30.186616897583</t>
+    <t xml:space="preserve">30.1866149902344</t>
   </si>
   <si>
     <t xml:space="preserve">29.518180847168</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1795101165771</t>
+    <t xml:space="preserve">29.1795063018799</t>
   </si>
   <si>
     <t xml:space="preserve">29.437967300415</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3648700714111</t>
+    <t xml:space="preserve">30.3648681640625</t>
   </si>
   <si>
     <t xml:space="preserve">30.4629039764404</t>
@@ -1181,19 +1181,19 @@
     <t xml:space="preserve">30.4718151092529</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2935676574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0974903106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.061840057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2311763763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0849761962891</t>
+    <t xml:space="preserve">30.293571472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0974941253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0618419647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2311782836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0849800109863</t>
   </si>
   <si>
     <t xml:space="preserve">31.496753692627</t>
@@ -1205,13 +1205,13 @@
     <t xml:space="preserve">31.9958553314209</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7730407714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6928329467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1830139160156</t>
+    <t xml:space="preserve">31.7730445861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6928291320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1830177307129</t>
   </si>
   <si>
     <t xml:space="preserve">32.0760688781738</t>
@@ -1220,22 +1220,22 @@
     <t xml:space="preserve">31.9512882232666</t>
   </si>
   <si>
-    <t xml:space="preserve">32.307788848877</t>
+    <t xml:space="preserve">32.3077926635742</t>
   </si>
   <si>
     <t xml:space="preserve">33.1990432739258</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3951187133789</t>
+    <t xml:space="preserve">33.3951225280762</t>
   </si>
   <si>
     <t xml:space="preserve">34.7587242126465</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6963348388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.731990814209</t>
+    <t xml:space="preserve">34.6963424682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7319869995117</t>
   </si>
   <si>
     <t xml:space="preserve">34.5804748535156</t>
@@ -1250,10 +1250,10 @@
     <t xml:space="preserve">34.5448265075684</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4271659851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2221794128418</t>
+    <t xml:space="preserve">35.4271697998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2221755981445</t>
   </si>
   <si>
     <t xml:space="preserve">34.6606864929199</t>
@@ -1265,16 +1265,16 @@
     <t xml:space="preserve">33.8674812316895</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8496551513672</t>
+    <t xml:space="preserve">33.8496513366699</t>
   </si>
   <si>
     <t xml:space="preserve">34.1437683105469</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7159652709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0635528564453</t>
+    <t xml:space="preserve">33.7159690856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0635566711426</t>
   </si>
   <si>
     <t xml:space="preserve">34.313102722168</t>
@@ -1286,16 +1286,16 @@
     <t xml:space="preserve">34.420051574707</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7765502929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6161270141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3041954040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1081161499023</t>
+    <t xml:space="preserve">34.776554107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6161308288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3041915893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1081123352051</t>
   </si>
   <si>
     <t xml:space="preserve">32.8425407409668</t>
@@ -1304,13 +1304,13 @@
     <t xml:space="preserve">34.0902900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1063117980957</t>
+    <t xml:space="preserve">35.106315612793</t>
   </si>
   <si>
     <t xml:space="preserve">36.2471122741699</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3005828857422</t>
+    <t xml:space="preserve">36.3005867004395</t>
   </si>
   <si>
     <t xml:space="preserve">36.1847267150879</t>
@@ -1319,22 +1319,22 @@
     <t xml:space="preserve">36.4966621398926</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4146537780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.858470916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9208602905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6178321838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5821876525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2702445983887</t>
+    <t xml:space="preserve">37.4146499633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8584747314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9208641052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6178398132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5821914672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2702484130859</t>
   </si>
   <si>
     <t xml:space="preserve">38.4306716918945</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">39.214973449707</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8050003051758</t>
+    <t xml:space="preserve">38.8049964904785</t>
   </si>
   <si>
     <t xml:space="preserve">37.8067970275879</t>
@@ -1358,19 +1358,19 @@
     <t xml:space="preserve">38.3682899475098</t>
   </si>
   <si>
-    <t xml:space="preserve">38.341552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5198020935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5643615722656</t>
+    <t xml:space="preserve">38.3415565490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5198059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5643653869629</t>
   </si>
   <si>
     <t xml:space="preserve">38.6089248657227</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6891403198242</t>
+    <t xml:space="preserve">38.689136505127</t>
   </si>
   <si>
     <t xml:space="preserve">38.7336959838867</t>
@@ -1385,37 +1385,37 @@
     <t xml:space="preserve">39.0545501708984</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3219261169434</t>
+    <t xml:space="preserve">39.3219223022461</t>
   </si>
   <si>
     <t xml:space="preserve">38.5554504394531</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2880744934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3772010803223</t>
+    <t xml:space="preserve">38.2880783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3771934509277</t>
   </si>
   <si>
     <t xml:space="preserve">37.6998481750488</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6125259399414</t>
+    <t xml:space="preserve">36.6125297546387</t>
   </si>
   <si>
     <t xml:space="preserve">37.6820220947266</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4663276672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9956741333008</t>
+    <t xml:space="preserve">38.4663238525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9956703186035</t>
   </si>
   <si>
     <t xml:space="preserve">42.6551933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8156204223633</t>
+    <t xml:space="preserve">42.8156242370605</t>
   </si>
   <si>
     <t xml:space="preserve">42.423469543457</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">42.0847969055176</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9243698120117</t>
+    <t xml:space="preserve">41.924373626709</t>
   </si>
   <si>
     <t xml:space="preserve">41.6213493347168</t>
@@ -1436,55 +1436,55 @@
     <t xml:space="preserve">41.7639465332031</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1382675170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6926460266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5322227478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7817764282227</t>
+    <t xml:space="preserve">42.1382713317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6926498413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5322189331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7817726135254</t>
   </si>
   <si>
     <t xml:space="preserve">41.3539733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8192176818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.355770111084</t>
+    <t xml:space="preserve">40.819221496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3557739257812</t>
   </si>
   <si>
     <t xml:space="preserve">40.5874977111816</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8031997680664</t>
+    <t xml:space="preserve">39.8031959533691</t>
   </si>
   <si>
     <t xml:space="preserve">39.1436767578125</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6784248352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7799682617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4787483215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6802291870117</t>
+    <t xml:space="preserve">39.6784286499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.779972076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4787521362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6802253723145</t>
   </si>
   <si>
     <t xml:space="preserve">37.5750732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2898750305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5892944335938</t>
+    <t xml:space="preserve">37.2898788452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.589298248291</t>
   </si>
   <si>
     <t xml:space="preserve">40.1953468322754</t>
@@ -1493,40 +1493,40 @@
     <t xml:space="preserve">40.1062278747559</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5696716308594</t>
+    <t xml:space="preserve">40.5696754455566</t>
   </si>
   <si>
     <t xml:space="preserve">40.8013954162598</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9440002441406</t>
+    <t xml:space="preserve">40.9439964294434</t>
   </si>
   <si>
     <t xml:space="preserve">41.1400718688965</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9974746704102</t>
+    <t xml:space="preserve">40.9974708557129</t>
   </si>
   <si>
     <t xml:space="preserve">40.5161972045898</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9618186950684</t>
+    <t xml:space="preserve">40.9618225097656</t>
   </si>
   <si>
     <t xml:space="preserve">39.2506294250488</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1793212890625</t>
+    <t xml:space="preserve">39.1793251037598</t>
   </si>
   <si>
     <t xml:space="preserve">40.2131729125977</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3914260864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3896217346191</t>
+    <t xml:space="preserve">40.3914184570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3896255493164</t>
   </si>
   <si>
     <t xml:space="preserve">42.6017227172852</t>
@@ -1544,73 +1544,73 @@
     <t xml:space="preserve">43.8851203918457</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9635353088379</t>
+    <t xml:space="preserve">44.9635276794434</t>
   </si>
   <si>
     <t xml:space="preserve">46.0330352783203</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3253440856934</t>
+    <t xml:space="preserve">47.3253402709961</t>
   </si>
   <si>
     <t xml:space="preserve">45.943904876709</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5874137878418</t>
+    <t xml:space="preserve">45.5874099731445</t>
   </si>
   <si>
     <t xml:space="preserve">44.6961555480957</t>
   </si>
   <si>
-    <t xml:space="preserve">44.009895324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8494758605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9582252502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4609184265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.175724029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1578979492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0153007507324</t>
+    <t xml:space="preserve">44.0098991394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8494720458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9582214355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4609222412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1757278442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.157901763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0152969360352</t>
   </si>
   <si>
     <t xml:space="preserve">39.7675476074219</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1080284118652</t>
+    <t xml:space="preserve">39.1080207824707</t>
   </si>
   <si>
     <t xml:space="preserve">40.7479248046875</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7853775024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5518455505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7319030761719</t>
+    <t xml:space="preserve">39.7853736877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5518493652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7318992614746</t>
   </si>
   <si>
     <t xml:space="preserve">39.3040962219238</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2488250732422</t>
+    <t xml:space="preserve">40.2488288879395</t>
   </si>
   <si>
     <t xml:space="preserve">39.9101486206055</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4288749694824</t>
+    <t xml:space="preserve">39.4288787841797</t>
   </si>
   <si>
     <t xml:space="preserve">39.0367240905762</t>
@@ -1622,10 +1622,10 @@
     <t xml:space="preserve">41.0509490966797</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9335670471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0149269104004</t>
+    <t xml:space="preserve">41.9335708618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0149230957031</t>
   </si>
   <si>
     <t xml:space="preserve">40.7087135314941</t>
@@ -1634,13 +1634,13 @@
     <t xml:space="preserve">40.6366539001465</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5285797119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8440971374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7366142272949</t>
+    <t xml:space="preserve">40.5285835266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8441009521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7366104125977</t>
   </si>
   <si>
     <t xml:space="preserve">37.484432220459</t>
@@ -1655,37 +1655,37 @@
     <t xml:space="preserve">36.4757194519043</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6018104553223</t>
+    <t xml:space="preserve">36.6018142700195</t>
   </si>
   <si>
     <t xml:space="preserve">36.0073928833008</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6651458740234</t>
+    <t xml:space="preserve">35.6651496887207</t>
   </si>
   <si>
     <t xml:space="preserve">35.3589324951172</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2241325378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4135627746582</t>
+    <t xml:space="preserve">34.2241363525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4135589599609</t>
   </si>
   <si>
     <t xml:space="preserve">33.6657447814941</t>
   </si>
   <si>
-    <t xml:space="preserve">33.881893157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4763069152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6924667358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1427803039551</t>
+    <t xml:space="preserve">33.8818893432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4763107299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6924629211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1427841186523</t>
   </si>
   <si>
     <t xml:space="preserve">34.7284927368164</t>
@@ -1706,7 +1706,7 @@
     <t xml:space="preserve">35.1247673034668</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5036239624023</t>
+    <t xml:space="preserve">33.5036277770996</t>
   </si>
   <si>
     <t xml:space="preserve">32.4048500061035</t>
@@ -1718,19 +1718,19 @@
     <t xml:space="preserve">31.4681911468506</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7744083404541</t>
+    <t xml:space="preserve">31.7744045257568</t>
   </si>
   <si>
     <t xml:space="preserve">30.5315322875977</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4867973327637</t>
+    <t xml:space="preserve">29.4867935180664</t>
   </si>
   <si>
     <t xml:space="preserve">29.9371128082275</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2346172332764</t>
+    <t xml:space="preserve">29.2346153259277</t>
   </si>
   <si>
     <t xml:space="preserve">30.1532649993896</t>
@@ -1742,22 +1742,22 @@
     <t xml:space="preserve">29.4147434234619</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8296222686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1265411376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5408344268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6035823822021</t>
+    <t xml:space="preserve">27.8296241760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1265392303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5408325195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6035785675049</t>
   </si>
   <si>
     <t xml:space="preserve">31.2520389556885</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6489086151123</t>
+    <t xml:space="preserve">29.6489067077637</t>
   </si>
   <si>
     <t xml:space="preserve">29.9551239013672</t>
@@ -1766,28 +1766,28 @@
     <t xml:space="preserve">30.1172351837158</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4054412841797</t>
+    <t xml:space="preserve">30.4054393768311</t>
   </si>
   <si>
     <t xml:space="preserve">31.6663303375244</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6483211517334</t>
+    <t xml:space="preserve">31.6483173370361</t>
   </si>
   <si>
     <t xml:space="preserve">32.080623626709</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1079406738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3601150512695</t>
+    <t xml:space="preserve">31.1079368591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3601169586182</t>
   </si>
   <si>
     <t xml:space="preserve">30.9818496704102</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7383842468262</t>
+    <t xml:space="preserve">31.7383861541748</t>
   </si>
   <si>
     <t xml:space="preserve">31.6122913360596</t>
@@ -1799,25 +1799,25 @@
     <t xml:space="preserve">29.9190979003906</t>
   </si>
   <si>
-    <t xml:space="preserve">29.901086807251</t>
+    <t xml:space="preserve">29.9010887145996</t>
   </si>
   <si>
     <t xml:space="preserve">29.666919708252</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0905132293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.730260848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0998153686523</t>
+    <t xml:space="preserve">29.0905151367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7302627563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.099817276001</t>
   </si>
   <si>
     <t xml:space="preserve">27.595458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6407871246338</t>
+    <t xml:space="preserve">26.6407890319824</t>
   </si>
   <si>
     <t xml:space="preserve">26.2805347442627</t>
@@ -1835,28 +1835,28 @@
     <t xml:space="preserve">27.0550804138184</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1091175079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0190525054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7488632202148</t>
+    <t xml:space="preserve">27.1091194152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0190563201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7488651275635</t>
   </si>
   <si>
     <t xml:space="preserve">27.4693717956543</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9196891784668</t>
+    <t xml:space="preserve">27.9196910858154</t>
   </si>
   <si>
     <t xml:space="preserve">27.5774478912354</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9377021789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8476390838623</t>
+    <t xml:space="preserve">27.9377002716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8476371765137</t>
   </si>
   <si>
     <t xml:space="preserve">27.7936019897461</t>
@@ -1868,7 +1868,7 @@
     <t xml:space="preserve">28.0097541809082</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7755889892578</t>
+    <t xml:space="preserve">27.7755870819092</t>
   </si>
   <si>
     <t xml:space="preserve">28.6041717529297</t>
@@ -1901,25 +1901,25 @@
     <t xml:space="preserve">25.7581653594971</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7320308685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7413311004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7233200073242</t>
+    <t xml:space="preserve">22.7320289611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7413291931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7233219146729</t>
   </si>
   <si>
     <t xml:space="preserve">22.7860698699951</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4165115356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7047176361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5606174468994</t>
+    <t xml:space="preserve">23.4165134429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.704719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5606155395508</t>
   </si>
   <si>
     <t xml:space="preserve">23.2363872528076</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">21.2369766235352</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3450546264648</t>
+    <t xml:space="preserve">21.3450565338135</t>
   </si>
   <si>
     <t xml:space="preserve">21.5972309112549</t>
@@ -1952,16 +1952,16 @@
     <t xml:space="preserve">19.7239093780518</t>
   </si>
   <si>
-    <t xml:space="preserve">18.318920135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2828922271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5437850952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8773097991943</t>
+    <t xml:space="preserve">18.3189182281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2828941345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5437831878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.877311706543</t>
   </si>
   <si>
     <t xml:space="preserve">18.3909702301025</t>
@@ -1976,10 +1976,10 @@
     <t xml:space="preserve">17.139087677002</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1120662689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2651767730713</t>
+    <t xml:space="preserve">17.1120681762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2651748657227</t>
   </si>
   <si>
     <t xml:space="preserve">16.661750793457</t>
@@ -1988,55 +1988,55 @@
     <t xml:space="preserve">16.2024250030518</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9502458572388</t>
+    <t xml:space="preserve">15.9502477645874</t>
   </si>
   <si>
     <t xml:space="preserve">15.7160844802856</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6800575256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6170129776001</t>
+    <t xml:space="preserve">15.6800584793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6170120239258</t>
   </si>
   <si>
     <t xml:space="preserve">16.1573963165283</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6077117919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4005641937256</t>
+    <t xml:space="preserve">16.6077098846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4005661010742</t>
   </si>
   <si>
     <t xml:space="preserve">17.4723205566406</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5533771514893</t>
+    <t xml:space="preserve">17.5533790588379</t>
   </si>
   <si>
     <t xml:space="preserve">16.490629196167</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9406509399414</t>
+    <t xml:space="preserve">17.94065284729</t>
   </si>
   <si>
     <t xml:space="preserve">18.8232746124268</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6614570617676</t>
+    <t xml:space="preserve">17.6614589691162</t>
   </si>
   <si>
     <t xml:space="preserve">16.7968463897705</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0132942199707</t>
+    <t xml:space="preserve">16.0132923126221</t>
   </si>
   <si>
     <t xml:space="preserve">15.9052152633667</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2654705047607</t>
+    <t xml:space="preserve">16.2654685974121</t>
   </si>
   <si>
     <t xml:space="preserve">16.1934204101562</t>
@@ -2048,16 +2048,16 @@
     <t xml:space="preserve">15.400860786438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0496120452881</t>
+    <t xml:space="preserve">15.0496110916138</t>
   </si>
   <si>
     <t xml:space="preserve">14.7524032592773</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5899934768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1486825942993</t>
+    <t xml:space="preserve">15.5899953842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.148681640625</t>
   </si>
   <si>
     <t xml:space="preserve">15.4639053344727</t>
@@ -2066,16 +2066,16 @@
     <t xml:space="preserve">17.1661071777344</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7875461578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1568031311035</t>
+    <t xml:space="preserve">17.7875442504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1568050384521</t>
   </si>
   <si>
     <t xml:space="preserve">17.6434440612793</t>
   </si>
   <si>
-    <t xml:space="preserve">17.391263961792</t>
+    <t xml:space="preserve">17.3912658691406</t>
   </si>
   <si>
     <t xml:space="preserve">18.0127029418945</t>
@@ -2084,13 +2084,13 @@
     <t xml:space="preserve">18.0487270355225</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2288551330566</t>
+    <t xml:space="preserve">18.228853225708</t>
   </si>
   <si>
     <t xml:space="preserve">18.0307159423828</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9226398468018</t>
+    <t xml:space="preserve">17.9226417541504</t>
   </si>
   <si>
     <t xml:space="preserve">17.4543075561523</t>
@@ -2099,40 +2099,40 @@
     <t xml:space="preserve">18.6791706085205</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8052616119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6251354217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3369331359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9493637084961</t>
+    <t xml:space="preserve">18.8052597045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6251373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3369312286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9493618011475</t>
   </si>
   <si>
     <t xml:space="preserve">18.7872505187988</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6971855163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3549423217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4269962310791</t>
+    <t xml:space="preserve">18.6971836090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.354944229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4269924163818</t>
   </si>
   <si>
     <t xml:space="preserve">17.9856834411621</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3552379608154</t>
+    <t xml:space="preserve">17.3552398681641</t>
   </si>
   <si>
     <t xml:space="preserve">17.7244987487793</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3009052276611</t>
+    <t xml:space="preserve">18.3009071350098</t>
   </si>
   <si>
     <t xml:space="preserve">18.6071224212646</t>
@@ -2141,1176 +2141,1179 @@
     <t xml:space="preserve">19.3996829986572</t>
   </si>
   <si>
+    <t xml:space="preserve">19.6698684692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2462768554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0661525726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9220504760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4176921844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4537181854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2823047637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7515163421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7425117492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7965507507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5083465576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4182834625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8508834838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9859790802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.868896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0490226745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9409446716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3462314605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2741813659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3822593688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2831897735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1748161315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.976676940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6164226531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4272899627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1387920379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9136333465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6974792480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1928310394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9496574401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2381553649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1300830841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6794662475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9676704406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0847549438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0667400360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8686008453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5173530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6074180603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5894031524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7695331573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6365604400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.24342918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6621875762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2249774932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5330257415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1916618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.684232711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6232395172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8021230697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9405126571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7836713790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3131456375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.894383430481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8390293121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4792137145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.953330039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0732688903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0179128646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.303918838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3777284622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1009464263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1378507614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9220628738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7006387710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4756231307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4202671051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.577109336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8298015594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7928981781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6914119720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.512526512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1803903579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0989007949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7575378417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1486215591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2132015228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4069480895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4161758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5914688110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8590240478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9236068725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4807567596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6837301254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5361127853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2962369918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.370044708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0471353530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1762981414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9087438583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65964126586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53047657012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0932645797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4899835586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5730180740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4254016876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5176601409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3054628372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4438524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6652784347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0286827087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96410083770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.056360244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1209421157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50279998779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29059982299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5766077041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21218013763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40131282806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43821620941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47512149810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20295333862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94001197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9861421585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88004302978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53970432281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24447059631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28137588500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11530685424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88106632232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97332668304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99177837371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2408809661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.434627532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.084038734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1024904251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61351108551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66886711120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52125072479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79803085327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56737995147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2629222869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39208698272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65041637420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31828022003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71499729156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81648445129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68732070922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98255157470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7519006729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49357318878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2777853012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0655860900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5822429656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7298603057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2870101928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5084362030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3515930175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4310369491577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6340103149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2337017059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.993824005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1322145462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.086085319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1414413452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1875715255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9661464691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9569206237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7539472579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8277559280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7354955673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0676317214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4551258087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2577877044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2485628128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0824947357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5991516113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4054040908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2024335861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7559928894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7098627090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7744464874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3408241271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7190895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7283163070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0143222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.134259223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1250343322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9497404098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6637334823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.682186126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4571714401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1158094406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8482532501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0512256622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0327739715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9312896728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6473255157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7303600311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0865879058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7913551330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8651638031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7452239990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8190307617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1086273193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.99791431427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9333343505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4720344543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6785955429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3187808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8446645736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2967395782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2044792175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7247257232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8538904190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1491222381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2506103515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9830551147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1583490371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0753154754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1065835952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6027421951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0399541854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9753713607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5878801345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3018732070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6006965637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1301679611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30905342102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0635404586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97589349746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8928599357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5504732131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93796634674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90567493438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98409652709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91028785705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01177453994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47307586669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05431365966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85697937011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33673000335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01381969451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39567756652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40028953552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34954738616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25728702545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.118896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74985551834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92976331710815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78675937652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10966968536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.842116355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42694520950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28855466842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26087713241577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32545900344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33468437194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11326026916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5561089515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77753448486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93437623977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60223960876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33929777145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51920461654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30700731277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14555168151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10403442382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15939044952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06712961196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92874002456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56533527374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54227018356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.445396900177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27010250091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72217750549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46948528289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66784477233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90310859680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54329395294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69090843200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87542915344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32750511169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0066404342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4863929748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4956197738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2557430267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9420585632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82571029663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74267578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.462306022644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.194751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.019455909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89029216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3792715072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3608179092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2224292755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.674503326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5453395843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7667636871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0215015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4402637481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5417499542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6155576705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8093042373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.818531036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7078170776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6616868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5694274902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3480033874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2741947174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1450309753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8128938674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0030508041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3167362213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8241662979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7042284011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0548162460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3961791992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2854671478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4423084259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1286239624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2301111221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0086870193481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1932077407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5437955856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3500490188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5714731216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3685007095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1470766067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4976654052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1101732254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1655282974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2670154571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2762413024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0455913543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1747541427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.331597328186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3869533538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5104827880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3813171386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6304197311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.335186958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7872619628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5068922042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4330835342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4515342712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2690601348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5735187530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8318471908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1455326080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3613204956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4628076553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7616300582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5217542648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5955619812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7154998779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3556842803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9128360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6545085906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5033016204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4110412597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.650918006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1860256195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6750049591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.416675567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1029930114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9184722900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3889989852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7764921188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5827436447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1547584533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8133955001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8410749435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9241075515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1178531646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8503007888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8779783248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3520936965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6381025314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4351301193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5919723510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9517869949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0994033813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0717258453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5145740509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7877655029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3910446166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4648532867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1142635345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2618789672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5386619567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4464015960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5663394927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.372594833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6216983795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5478897094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.036865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.415132522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7657222747803</t>
+  </si>
+  <si>
     <t xml:space="preserve">19.6698703765869</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2462768554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0661525726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9220485687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4176921844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4537181854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2823028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7515163421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7425136566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7965507507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5083484649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.418285369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8508834838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9859790802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8688945770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0490245819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9409465789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3462333679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2741813659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3822593688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2831897735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1748161315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.976676940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6164245605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4272899627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1387920379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.913631439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6974792480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1928291320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9496593475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2381534576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1300811767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6794662475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9676723480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0847549438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0667400360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8686027526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5173530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6074180603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5894031524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6365585327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2434272766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6621875762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2249774932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5330257415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1916618347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6842317581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6232395172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8021230697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9405136108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7836713790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3131456375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8943843841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8390283584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4792137145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.953330039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0732688903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0179128646851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.303918838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3777275085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1009464263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1378498077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9220628738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7006387710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4756231307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4202671051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.577109336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8298015594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7928972244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6914129257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5125274658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1803913116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0989007949829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7575378417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1486215591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2132024765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4069480895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4161758422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5914688110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8590240478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9236068725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4807558059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6837301254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5361137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2962369918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.370044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0471353530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1762981414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9087438583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65964126586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53047657012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0932645797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4899835586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5730171203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4254007339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5176601409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3054628372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4438524246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6652784347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286827087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96410083770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.056360244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.120943069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50280094146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29059982299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5766077041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21218109130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40131282806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43821620941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47512149810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20295333862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94001197814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9861421585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88004398345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53970336914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24447059631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28137588500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11530685424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88106632232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97332668304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99177837371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2408809661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.434627532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0840396881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1024904251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61351108551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66886711120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52125072479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7980318069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56738090515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2629222869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39208793640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65041542053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31827926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71499729156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81648445129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68732070922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98255157470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75190162658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49357223510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2777853012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0655860900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5822439193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7298603057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2870101928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5084362030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3515930175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4310369491577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6340093612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2337007522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.993824005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1322145462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.086085319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1414403915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1875705718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9661464691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9569206237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7539472579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8277568817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7354965209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0676326751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4551248550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2577877044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2485628128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0824947357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5991516113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4054050445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2024335861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7559928894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7098627090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7744464874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3408241271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7190895080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7283163070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0143222808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1342601776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1250343322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9497404098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6637334823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.682186126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4571714401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1158094406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8482542037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0512266159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0327739715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9312896728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6473274230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7303600311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0865859985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7913551330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8651638031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7452239990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8190307617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1086292266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9979162216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9333343505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4720344543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.678596496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3187808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8446645736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2967405319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2044792175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7247257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8538904190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1491222381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2506093978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9830551147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1583480834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0753145217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1065835952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6027421951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0399541854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9753713607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5878791809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.301872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6006956100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1301679611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30905342102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0635404586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97589349746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8928599357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5504732131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93796634674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90567541122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98409605026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91028785705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01177453994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47307538986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05431461334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85697841644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33673095703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01382064819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39567756652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40028953552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34954738616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25728702545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.118896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74985504150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92976331710815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78675937652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10967063903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84211587905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42694520950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28855466842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26087713241577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32545900344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33468389511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1132607460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5561089515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77753448486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93437719345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60223960876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33929824829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51920461654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3070068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14555168151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10403394699097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15939044952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06713008880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92874002456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56533527374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54227018356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.445396900177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27010250091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72217750549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46948623657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66784381866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90310764312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54329299926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69090938568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87542915344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32750511169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0066404342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4863939285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4956197738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2557430267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9420576095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82570934295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74267578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.462306022644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1947507858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0194549560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89029216766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3792715072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3608179092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2224292755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.674503326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5453395843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7667636871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0215015411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4402627944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5417499542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6155576705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8093032836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.818531036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7078170776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6616878509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5694274902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3480024337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2741947174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1450309753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8128938674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0030508041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3167362213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8241662979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7042284011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0548162460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3961791992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2854671478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4423084259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1286239624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2301120758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0086870193481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1932077407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5437955856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3500499725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5714740753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3685007095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1470766067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4976654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1101732254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1655292510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2670154571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2762413024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0455904006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1747541427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3315963745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3869533538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5104818344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3813171386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6304187774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.335186958313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7872619628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5068912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.433084487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4515342712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2690591812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5735187530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8318471908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1455326080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3613204956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4628076553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7616300582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5217542648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5955619812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7154998779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3556852340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9128360748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6545085906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5033016204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4110412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.650918006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1860265731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6750059127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4166774749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1029939651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9184722900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3889989852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7764940261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5827445983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1547584533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8133955001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8410730361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9241075515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1178550720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8502998352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8779783248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3520936965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6381034851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4351301193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5919713973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9517869949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.099401473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0717239379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5145740509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7877655029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3910465240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4648532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1142635345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2618808746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5386619567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4464015960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5663394927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3725929260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6216983795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5478897094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.036865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.415132522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7657222747803</t>
-  </si>
-  <si>
     <t xml:space="preserve">19.9835567474365</t>
   </si>
   <si>
@@ -3320,7 +3323,7 @@
     <t xml:space="preserve">19.4484481811523</t>
   </si>
   <si>
-    <t xml:space="preserve">18.728816986084</t>
+    <t xml:space="preserve">18.7288188934326</t>
   </si>
   <si>
     <t xml:space="preserve">19.245475769043</t>
@@ -3332,7 +3335,7 @@
     <t xml:space="preserve">19.3377342224121</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2639274597168</t>
+    <t xml:space="preserve">19.2639255523682</t>
   </si>
   <si>
     <t xml:space="preserve">18.5443000793457</t>
@@ -3365,19 +3368,19 @@
     <t xml:space="preserve">20.9430618286133</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2567481994629</t>
+    <t xml:space="preserve">21.2567462921143</t>
   </si>
   <si>
     <t xml:space="preserve">21.2198429107666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3121013641357</t>
+    <t xml:space="preserve">21.3121032714844</t>
   </si>
   <si>
     <t xml:space="preserve">21.1829376220703</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7513637542725</t>
+    <t xml:space="preserve">22.7513618469238</t>
   </si>
   <si>
     <t xml:space="preserve">22.7698135375977</t>
@@ -3398,7 +3401,7 @@
     <t xml:space="preserve">20.5371189117432</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6293773651123</t>
+    <t xml:space="preserve">20.6293792724609</t>
   </si>
   <si>
     <t xml:space="preserve">20.7216358184814</t>
@@ -3413,7 +3416,7 @@
     <t xml:space="preserve">20.6847343444824</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2013912200928</t>
+    <t xml:space="preserve">21.2013931274414</t>
   </si>
   <si>
     <t xml:space="preserve">20.4633102416992</t>
@@ -3425,7 +3428,7 @@
     <t xml:space="preserve">20.6478290557861</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8508014678955</t>
+    <t xml:space="preserve">20.8508033752441</t>
   </si>
   <si>
     <t xml:space="preserve">21.0906791687012</t>
@@ -3434,7 +3437,7 @@
     <t xml:space="preserve">21.109130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2234325408936</t>
+    <t xml:space="preserve">20.2234344482422</t>
   </si>
   <si>
     <t xml:space="preserve">19.9466533660889</t>
@@ -3455,13 +3458,13 @@
     <t xml:space="preserve">20.795446395874</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3156929016113</t>
+    <t xml:space="preserve">20.31569480896</t>
   </si>
   <si>
     <t xml:space="preserve">20.8323516845703</t>
   </si>
   <si>
-    <t xml:space="preserve">22.179349899292</t>
+    <t xml:space="preserve">22.1793479919434</t>
   </si>
   <si>
     <t xml:space="preserve">22.5483894348145</t>
@@ -3470,7 +3473,7 @@
     <t xml:space="preserve">22.0686378479004</t>
   </si>
   <si>
-    <t xml:space="preserve">22.216251373291</t>
+    <t xml:space="preserve">22.2162532806396</t>
   </si>
   <si>
     <t xml:space="preserve">22.1424446105957</t>
@@ -3479,13 +3482,13 @@
     <t xml:space="preserve">22.0132808685303</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2531566619873</t>
+    <t xml:space="preserve">22.2531585693359</t>
   </si>
   <si>
     <t xml:space="preserve">22.0317325592041</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1942119598389</t>
+    <t xml:space="preserve">23.1942100524902</t>
   </si>
   <si>
     <t xml:space="preserve">23.7846755981445</t>
@@ -3500,7 +3503,7 @@
     <t xml:space="preserve">23.8953895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0465927124023</t>
+    <t xml:space="preserve">23.046594619751</t>
   </si>
   <si>
     <t xml:space="preserve">22.9174308776855</t>
@@ -3524,7 +3527,7 @@
     <t xml:space="preserve">22.8067188262939</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3454170227051</t>
+    <t xml:space="preserve">22.3454189300537</t>
   </si>
   <si>
     <t xml:space="preserve">23.489444732666</t>
@@ -3539,7 +3542,7 @@
     <t xml:space="preserve">23.2311153411865</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7144565582275</t>
+    <t xml:space="preserve">22.7144584655762</t>
   </si>
   <si>
     <t xml:space="preserve">23.6370620727539</t>
@@ -3548,7 +3551,7 @@
     <t xml:space="preserve">25.0763187408447</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7554550170898</t>
+    <t xml:space="preserve">26.7554569244385</t>
   </si>
   <si>
     <t xml:space="preserve">26.4786758422852</t>
@@ -3560,7 +3563,7 @@
     <t xml:space="preserve">27.1613998413086</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3828258514404</t>
+    <t xml:space="preserve">27.3828239440918</t>
   </si>
   <si>
     <t xml:space="preserve">27.4935359954834</t>
@@ -3581,7 +3584,7 @@
     <t xml:space="preserve">27.4012775421143</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1060409545898</t>
+    <t xml:space="preserve">27.1060428619385</t>
   </si>
   <si>
     <t xml:space="preserve">26.9030685424805</t>
@@ -3590,7 +3593,7 @@
     <t xml:space="preserve">26.4971256256104</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9251136779785</t>
+    <t xml:space="preserve">25.9251155853271</t>
   </si>
   <si>
     <t xml:space="preserve">25.7221393585205</t>
@@ -3599,7 +3602,7 @@
     <t xml:space="preserve">26.6447410583496</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4602241516113</t>
+    <t xml:space="preserve">26.4602222442627</t>
   </si>
   <si>
     <t xml:space="preserve">26.3864154815674</t>
@@ -3623,10 +3626,10 @@
     <t xml:space="preserve">25.9620151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6631927490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3310585021973</t>
+    <t xml:space="preserve">26.6631946563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3310565948486</t>
   </si>
   <si>
     <t xml:space="preserve">26.5155754089355</t>
@@ -3644,7 +3647,7 @@
     <t xml:space="preserve">26.8292617797852</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4417667388916</t>
+    <t xml:space="preserve">26.4417686462402</t>
   </si>
   <si>
     <t xml:space="preserve">26.5340309143066</t>
@@ -3674,10 +3677,10 @@
     <t xml:space="preserve">30.9625205993652</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5970726013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0322360992432</t>
+    <t xml:space="preserve">29.5970706939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0322341918945</t>
   </si>
   <si>
     <t xml:space="preserve">26.8846168518066</t>
@@ -3686,13 +3689,13 @@
     <t xml:space="preserve">27.3459167480469</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6227016448975</t>
+    <t xml:space="preserve">27.6226997375488</t>
   </si>
   <si>
     <t xml:space="preserve">26.7923583984375</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9399757385254</t>
+    <t xml:space="preserve">26.939977645874</t>
   </si>
   <si>
     <t xml:space="preserve">27.1798496246338</t>
@@ -3701,7 +3704,7 @@
     <t xml:space="preserve">27.8994808197021</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5857944488525</t>
+    <t xml:space="preserve">27.5857963562012</t>
   </si>
   <si>
     <t xml:space="preserve">27.2352066040039</t>
@@ -3719,7 +3722,7 @@
     <t xml:space="preserve">27.2536582946777</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7703170776367</t>
+    <t xml:space="preserve">27.7703189849854</t>
   </si>
   <si>
     <t xml:space="preserve">27.3090171813965</t>
@@ -3743,10 +3746,10 @@
     <t xml:space="preserve">27.917932510376</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6965084075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.050687789917</t>
+    <t xml:space="preserve">27.6965065002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0506858825684</t>
   </si>
   <si>
     <t xml:space="preserve">27.7518653869629</t>
@@ -3755,7 +3758,7 @@
     <t xml:space="preserve">27.8256721496582</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9732894897461</t>
+    <t xml:space="preserve">27.9732875823975</t>
   </si>
   <si>
     <t xml:space="preserve">28.3054275512695</t>
@@ -3767,7 +3770,7 @@
     <t xml:space="preserve">28.0840015411377</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7887687683105</t>
+    <t xml:space="preserve">27.7887668609619</t>
   </si>
   <si>
     <t xml:space="preserve">26.294153213501</t>
@@ -3785,22 +3788,22 @@
     <t xml:space="preserve">24.6150169372559</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0983619689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9656066894531</t>
+    <t xml:space="preserve">24.0983638763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9656047821045</t>
   </si>
   <si>
     <t xml:space="preserve">24.356689453125</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7108688354492</t>
+    <t xml:space="preserve">23.7108707427979</t>
   </si>
   <si>
     <t xml:space="preserve">23.3418273925781</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2680187225342</t>
+    <t xml:space="preserve">23.2680206298828</t>
   </si>
   <si>
     <t xml:space="preserve">24.0614566802979</t>
@@ -3821,7 +3824,7 @@
     <t xml:space="preserve">25.0947723388672</t>
   </si>
   <si>
-    <t xml:space="preserve">24.910249710083</t>
+    <t xml:space="preserve">24.9102516174316</t>
   </si>
   <si>
     <t xml:space="preserve">24.984058380127</t>
@@ -3839,10 +3842,10 @@
     <t xml:space="preserve">25.5376205444336</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8733463287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9287033081055</t>
+    <t xml:space="preserve">24.8733444213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9287052154541</t>
   </si>
   <si>
     <t xml:space="preserve">24.8364429473877</t>
@@ -3851,25 +3854,25 @@
     <t xml:space="preserve">24.2644290924072</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3013343811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8769340515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.526346206665</t>
+    <t xml:space="preserve">24.3013324737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8769359588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5263481140137</t>
   </si>
   <si>
     <t xml:space="preserve">23.1573066711426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8656635284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8287620544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8841152191162</t>
+    <t xml:space="preserve">21.865665435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8287601470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8841171264648</t>
   </si>
   <si>
     <t xml:space="preserve">21.0353202819824</t>
@@ -3878,7 +3881,7 @@
     <t xml:space="preserve">20.7031860351562</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7365016937256</t>
+    <t xml:space="preserve">21.736499786377</t>
   </si>
   <si>
     <t xml:space="preserve">21.4597206115723</t>
@@ -3935,7 +3938,7 @@
     <t xml:space="preserve">19.928201675415</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0758190155029</t>
+    <t xml:space="preserve">20.0758171081543</t>
   </si>
   <si>
     <t xml:space="preserve">20.8877048492432</t>
@@ -3968,25 +3971,25 @@
     <t xml:space="preserve">20.0204620361328</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9871444702148</t>
+    <t xml:space="preserve">18.9871463775635</t>
   </si>
   <si>
     <t xml:space="preserve">18.5073928833008</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6770515441895</t>
+    <t xml:space="preserve">17.6770496368408</t>
   </si>
   <si>
     <t xml:space="preserve">18.1291275024414</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1198997497559</t>
+    <t xml:space="preserve">18.1198978424072</t>
   </si>
   <si>
     <t xml:space="preserve">17.0681343078613</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3633670806885</t>
+    <t xml:space="preserve">17.3633689880371</t>
   </si>
   <si>
     <t xml:space="preserve">15.0845403671265</t>
@@ -3998,16 +4001,16 @@
     <t xml:space="preserve">16.2839221954346</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3705463409424</t>
+    <t xml:space="preserve">15.3705472946167</t>
   </si>
   <si>
     <t xml:space="preserve">16.23779296875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4699878692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2172956466675</t>
+    <t xml:space="preserve">13.469988822937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2172946929932</t>
   </si>
   <si>
     <t xml:space="preserve">14.0604524612427</t>
@@ -4016,7 +4019,7 @@
     <t xml:space="preserve">14.337233543396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6878223419189</t>
+    <t xml:space="preserve">14.6878213882446</t>
   </si>
   <si>
     <t xml:space="preserve">14.8169851303101</t>
@@ -4025,10 +4028,10 @@
     <t xml:space="preserve">14.2634248733521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2541990280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6601438522339</t>
+    <t xml:space="preserve">14.2541999816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6601448059082</t>
   </si>
   <si>
     <t xml:space="preserve">15.82262134552</t>
@@ -4055,7 +4058,7 @@
     <t xml:space="preserve">13.617603302002</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8113508224487</t>
+    <t xml:space="preserve">13.8113498687744</t>
   </si>
   <si>
     <t xml:space="preserve">12.8057136535645</t>
@@ -4067,13 +4070,13 @@
     <t xml:space="preserve">13.3592748641968</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9461507797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0476360321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.305965423584</t>
+    <t xml:space="preserve">14.9461517333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0476350784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3059644699097</t>
   </si>
   <si>
     <t xml:space="preserve">15.3428688049316</t>
@@ -4406,9 +4409,6 @@
     <t xml:space="preserve">12.2314186096191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.106707572937</t>
-  </si>
-  <si>
     <t xml:space="preserve">12.7686433792114</t>
   </si>
   <si>
@@ -6009,6 +6009,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.84999990463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75</t>
   </si>
 </sst>
 </file>
@@ -39515,7 +39518,7 @@
         <v>21.3199996948242</v>
       </c>
       <c r="G1276" t="s">
-        <v>709</v>
+        <v>1099</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -39541,7 +39544,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1277" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -39567,7 +39570,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G1278" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -39593,7 +39596,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G1279" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -39619,7 +39622,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1280" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -39645,7 +39648,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G1281" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -39671,7 +39674,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1282" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -39697,7 +39700,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G1283" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -39723,7 +39726,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1284" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -39749,7 +39752,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1285" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -39775,7 +39778,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1286" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -39801,7 +39804,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G1287" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -39827,7 +39830,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G1288" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -39853,7 +39856,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G1289" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -39879,7 +39882,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1290" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -39905,7 +39908,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G1291" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -39931,7 +39934,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1292" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -39957,7 +39960,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G1293" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -39983,7 +39986,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G1294" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -40009,7 +40012,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1295" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -40035,7 +40038,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G1296" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -40061,7 +40064,7 @@
         <v>23</v>
       </c>
       <c r="G1297" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -40087,7 +40090,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1298" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -40113,7 +40116,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G1299" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -40139,7 +40142,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G1300" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -40165,7 +40168,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G1301" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -40191,7 +40194,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G1302" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -40217,7 +40220,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G1303" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -40243,7 +40246,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1304" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -40269,7 +40272,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G1305" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -40295,7 +40298,7 @@
         <v>23.5400009155273</v>
       </c>
       <c r="G1306" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -40321,7 +40324,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G1307" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -40347,7 +40350,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G1308" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -40373,7 +40376,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G1309" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -40399,7 +40402,7 @@
         <v>21.8799991607666</v>
       </c>
       <c r="G1310" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -40425,7 +40428,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1311" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -40451,7 +40454,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G1312" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -40477,7 +40480,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G1313" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -40503,7 +40506,7 @@
         <v>22.1800003051758</v>
       </c>
       <c r="G1314" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -40529,7 +40532,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1315" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -40555,7 +40558,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G1316" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -40581,7 +40584,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1317" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -40607,7 +40610,7 @@
         <v>22.8600006103516</v>
       </c>
       <c r="G1318" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -40633,7 +40636,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1319" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -40659,7 +40662,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1320" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -40685,7 +40688,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G1321" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -40711,7 +40714,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1322" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -40737,7 +40740,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G1323" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -40763,7 +40766,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1324" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -40789,7 +40792,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1325" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -40815,7 +40818,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G1326" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -40841,7 +40844,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G1327" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -40867,7 +40870,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1328" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -40893,7 +40896,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G1329" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -40919,7 +40922,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1330" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -40945,7 +40948,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G1331" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -40971,7 +40974,7 @@
         <v>24.0400009155273</v>
       </c>
       <c r="G1332" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -40997,7 +41000,7 @@
         <v>24.4400005340576</v>
       </c>
       <c r="G1333" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -41023,7 +41026,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G1334" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -41049,7 +41052,7 @@
         <v>24.0799999237061</v>
       </c>
       <c r="G1335" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -41075,7 +41078,7 @@
         <v>24</v>
       </c>
       <c r="G1336" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -41101,7 +41104,7 @@
         <v>23.8600006103516</v>
       </c>
       <c r="G1337" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -41127,7 +41130,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G1338" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -41153,7 +41156,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G1339" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -41179,7 +41182,7 @@
         <v>25.1399993896484</v>
       </c>
       <c r="G1340" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -41205,7 +41208,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G1341" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -41231,7 +41234,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1342" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -41257,7 +41260,7 @@
         <v>26.4400005340576</v>
       </c>
       <c r="G1343" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -41283,7 +41286,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1344" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -41309,7 +41312,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G1345" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -41335,7 +41338,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G1346" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -41361,7 +41364,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G1347" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -41387,7 +41390,7 @@
         <v>25.1399993896484</v>
       </c>
       <c r="G1348" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -41413,7 +41416,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G1349" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -41439,7 +41442,7 @@
         <v>25.5599994659424</v>
       </c>
       <c r="G1350" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -41465,7 +41468,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G1351" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -41491,7 +41494,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G1352" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -41517,7 +41520,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G1353" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -41543,7 +41546,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G1354" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -41569,7 +41572,7 @@
         <v>24.2199993133545</v>
       </c>
       <c r="G1355" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -41595,7 +41598,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G1356" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -41621,7 +41624,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1357" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -41647,7 +41650,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1358" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -41673,7 +41676,7 @@
         <v>25.7600002288818</v>
       </c>
       <c r="G1359" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -41699,7 +41702,7 @@
         <v>25.1800003051758</v>
       </c>
       <c r="G1360" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -41725,7 +41728,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G1361" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -41751,7 +41754,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G1362" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -41777,7 +41780,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1363" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -41803,7 +41806,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1364" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -41829,7 +41832,7 @@
         <v>29</v>
       </c>
       <c r="G1365" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -41855,7 +41858,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1366" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -41881,7 +41884,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1367" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -41907,7 +41910,7 @@
         <v>29.4400005340576</v>
       </c>
       <c r="G1368" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -41933,7 +41936,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G1369" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -41959,7 +41962,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1370" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -41985,7 +41988,7 @@
         <v>30.5200004577637</v>
       </c>
       <c r="G1371" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -42011,7 +42014,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1372" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -42037,7 +42040,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1373" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -42063,7 +42066,7 @@
         <v>29.5599994659424</v>
       </c>
       <c r="G1374" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -42089,7 +42092,7 @@
         <v>29.8799991607666</v>
       </c>
       <c r="G1375" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -42115,7 +42118,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G1376" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -42141,7 +42144,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1377" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -42167,7 +42170,7 @@
         <v>29.3799991607666</v>
       </c>
       <c r="G1378" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -42193,7 +42196,7 @@
         <v>29.1599998474121</v>
       </c>
       <c r="G1379" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -42219,7 +42222,7 @@
         <v>28.7199993133545</v>
       </c>
       <c r="G1380" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -42245,7 +42248,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1381" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -42271,7 +42274,7 @@
         <v>27.8799991607666</v>
       </c>
       <c r="G1382" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -42297,7 +42300,7 @@
         <v>28.7199993133545</v>
       </c>
       <c r="G1383" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -42323,7 +42326,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1384" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -42349,7 +42352,7 @@
         <v>28.6800003051758</v>
       </c>
       <c r="G1385" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -42375,7 +42378,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1386" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -42401,7 +42404,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G1387" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -42427,7 +42430,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G1388" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -42453,7 +42456,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G1389" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -42479,7 +42482,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G1390" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -42505,7 +42508,7 @@
         <v>27.8799991607666</v>
       </c>
       <c r="G1391" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -42531,7 +42534,7 @@
         <v>28.4599990844727</v>
       </c>
       <c r="G1392" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -42557,7 +42560,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1393" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -42583,7 +42586,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G1394" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -42609,7 +42612,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1395" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -42635,7 +42638,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G1396" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -42661,7 +42664,7 @@
         <v>28.5400009155273</v>
       </c>
       <c r="G1397" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -42687,7 +42690,7 @@
         <v>28.6800003051758</v>
       </c>
       <c r="G1398" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -42713,7 +42716,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G1399" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -42739,7 +42742,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1400" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -42765,7 +42768,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1401" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -42791,7 +42794,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G1402" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -42817,7 +42820,7 @@
         <v>28.9799995422363</v>
       </c>
       <c r="G1403" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -42843,7 +42846,7 @@
         <v>28.9599990844727</v>
       </c>
       <c r="G1404" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -42869,7 +42872,7 @@
         <v>29.0799999237061</v>
       </c>
       <c r="G1405" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -42895,7 +42898,7 @@
         <v>29</v>
       </c>
       <c r="G1406" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -42921,7 +42924,7 @@
         <v>28.6599998474121</v>
       </c>
       <c r="G1407" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -42947,7 +42950,7 @@
         <v>28.7600002288818</v>
       </c>
       <c r="G1408" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -42973,7 +42976,7 @@
         <v>27.5599994659424</v>
       </c>
       <c r="G1409" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -42999,7 +43002,7 @@
         <v>27.5</v>
       </c>
       <c r="G1410" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -43025,7 +43028,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G1411" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -43051,7 +43054,7 @@
         <v>28.8199996948242</v>
       </c>
       <c r="G1412" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -43077,7 +43080,7 @@
         <v>29.4799995422363</v>
       </c>
       <c r="G1413" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -43103,7 +43106,7 @@
         <v>29.7800006866455</v>
       </c>
       <c r="G1414" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -43129,7 +43132,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G1415" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -43155,7 +43158,7 @@
         <v>33.0200004577637</v>
       </c>
       <c r="G1416" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -43181,7 +43184,7 @@
         <v>33.560001373291</v>
       </c>
       <c r="G1417" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -43207,7 +43210,7 @@
         <v>32.0800018310547</v>
       </c>
       <c r="G1418" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -43233,7 +43236,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1419" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -43259,7 +43262,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G1420" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -43285,7 +43288,7 @@
         <v>29.6399993896484</v>
       </c>
       <c r="G1421" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -43311,7 +43314,7 @@
         <v>29.9400005340576</v>
       </c>
       <c r="G1422" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -43337,7 +43340,7 @@
         <v>29.0400009155273</v>
       </c>
       <c r="G1423" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -43363,7 +43366,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1424" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -43389,7 +43392,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G1425" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -43415,7 +43418,7 @@
         <v>30.2399997711182</v>
       </c>
       <c r="G1426" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -43441,7 +43444,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1427" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -43467,7 +43470,7 @@
         <v>29.5200004577637</v>
       </c>
       <c r="G1428" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -43493,7 +43496,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1429" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -43519,7 +43522,7 @@
         <v>29.5</v>
       </c>
       <c r="G1430" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -43545,7 +43548,7 @@
         <v>29.6599998474121</v>
       </c>
       <c r="G1431" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -43571,7 +43574,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1432" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -43597,7 +43600,7 @@
         <v>28.8600006103516</v>
       </c>
       <c r="G1433" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -43623,7 +43626,7 @@
         <v>29.5</v>
       </c>
       <c r="G1434" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -43649,7 +43652,7 @@
         <v>29.5400009155273</v>
       </c>
       <c r="G1435" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -43675,7 +43678,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1436" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -43701,7 +43704,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1437" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -43727,7 +43730,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1438" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -43753,7 +43756,7 @@
         <v>31.0799999237061</v>
       </c>
       <c r="G1439" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -43779,7 +43782,7 @@
         <v>30.3799991607666</v>
       </c>
       <c r="G1440" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -43805,7 +43808,7 @@
         <v>30.1399993896484</v>
       </c>
       <c r="G1441" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -43831,7 +43834,7 @@
         <v>30.7199993133545</v>
       </c>
       <c r="G1442" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -43857,7 +43860,7 @@
         <v>30.2600002288818</v>
       </c>
       <c r="G1443" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -43883,7 +43886,7 @@
         <v>30.3799991607666</v>
       </c>
       <c r="G1444" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -43909,7 +43912,7 @@
         <v>30.0200004577637</v>
       </c>
       <c r="G1445" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -43935,7 +43938,7 @@
         <v>29.3199996948242</v>
       </c>
       <c r="G1446" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -43961,7 +43964,7 @@
         <v>30.0799999237061</v>
       </c>
       <c r="G1447" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -43987,7 +43990,7 @@
         <v>30.1599998474121</v>
       </c>
       <c r="G1448" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -44013,7 +44016,7 @@
         <v>30.3199996948242</v>
       </c>
       <c r="G1449" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -44039,7 +44042,7 @@
         <v>30.6800003051758</v>
       </c>
       <c r="G1450" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -44065,7 +44068,7 @@
         <v>30.6599998474121</v>
       </c>
       <c r="G1451" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -44091,7 +44094,7 @@
         <v>30.4400005340576</v>
       </c>
       <c r="G1452" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -44117,7 +44120,7 @@
         <v>30.1200008392334</v>
       </c>
       <c r="G1453" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -44143,7 +44146,7 @@
         <v>28.5</v>
       </c>
       <c r="G1454" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -44169,7 +44172,7 @@
         <v>28.6599998474121</v>
       </c>
       <c r="G1455" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -44195,7 +44198,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G1456" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -44221,7 +44224,7 @@
         <v>29.2600002288818</v>
       </c>
       <c r="G1457" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -44247,7 +44250,7 @@
         <v>28.4200000762939</v>
       </c>
       <c r="G1458" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -44273,7 +44276,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G1459" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -44299,7 +44302,7 @@
         <v>26.6800003051758</v>
       </c>
       <c r="G1460" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -44325,7 +44328,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G1461" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -44351,7 +44354,7 @@
         <v>27.0599994659424</v>
       </c>
       <c r="G1462" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -44377,7 +44380,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1463" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -44403,7 +44406,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1464" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -44429,7 +44432,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1465" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -44455,7 +44458,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1466" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -44481,7 +44484,7 @@
         <v>25.2199993133545</v>
       </c>
       <c r="G1467" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -44507,7 +44510,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G1468" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -44533,7 +44536,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G1469" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -44559,7 +44562,7 @@
         <v>26.0799999237061</v>
       </c>
       <c r="G1470" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -44585,7 +44588,7 @@
         <v>26.2399997711182</v>
       </c>
       <c r="G1471" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -44611,7 +44614,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G1472" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -44637,7 +44640,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1473" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -44663,7 +44666,7 @@
         <v>27.3600006103516</v>
       </c>
       <c r="G1474" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -44689,7 +44692,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1475" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -44715,7 +44718,7 @@
         <v>27</v>
       </c>
       <c r="G1476" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -44741,7 +44744,7 @@
         <v>27.0799999237061</v>
       </c>
       <c r="G1477" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -44767,7 +44770,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1478" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -44793,7 +44796,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1479" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -44819,7 +44822,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1480" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -44845,7 +44848,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1481" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -44871,7 +44874,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1482" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -44897,7 +44900,7 @@
         <v>26.7399997711182</v>
       </c>
       <c r="G1483" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -44923,7 +44926,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G1484" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -44949,7 +44952,7 @@
         <v>27</v>
       </c>
       <c r="G1485" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -44975,7 +44978,7 @@
         <v>26.9599990844727</v>
       </c>
       <c r="G1486" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -45001,7 +45004,7 @@
         <v>27.0799999237061</v>
       </c>
       <c r="G1487" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -45027,7 +45030,7 @@
         <v>27.0200004577637</v>
       </c>
       <c r="G1488" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -45053,7 +45056,7 @@
         <v>26.9200000762939</v>
       </c>
       <c r="G1489" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -45079,7 +45082,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1490" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -45105,7 +45108,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G1491" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -45131,7 +45134,7 @@
         <v>25.8799991607666</v>
       </c>
       <c r="G1492" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -45157,7 +45160,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1493" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -45183,7 +45186,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1494" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -45209,7 +45212,7 @@
         <v>25.8799991607666</v>
       </c>
       <c r="G1495" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -45235,7 +45238,7 @@
         <v>25.5</v>
       </c>
       <c r="G1496" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -45261,7 +45264,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1497" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -45287,7 +45290,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G1498" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -45313,7 +45316,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G1499" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -45339,7 +45342,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1500" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -45365,7 +45368,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1501" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -45391,7 +45394,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G1502" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -45417,7 +45420,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1503" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -45443,7 +45446,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1504" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -45469,7 +45472,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G1505" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -45495,7 +45498,7 @@
         <v>23.5599994659424</v>
       </c>
       <c r="G1506" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -45521,7 +45524,7 @@
         <v>23.2600002288818</v>
       </c>
       <c r="G1507" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -45547,7 +45550,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1508" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -45573,7 +45576,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G1509" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -45599,7 +45602,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G1510" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -45625,7 +45628,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1511" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -45651,7 +45654,7 @@
         <v>23.2399997711182</v>
       </c>
       <c r="G1512" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -45677,7 +45680,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1513" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -45703,7 +45706,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G1514" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -45729,7 +45732,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1515" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -45755,7 +45758,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1516" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -45781,7 +45784,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G1517" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -45807,7 +45810,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G1518" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -45833,7 +45836,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1519" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -45859,7 +45862,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G1520" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -45885,7 +45888,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G1521" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -45911,7 +45914,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G1522" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -45937,7 +45940,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G1523" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -45963,7 +45966,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1524" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -45989,7 +45992,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G1525" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -46015,7 +46018,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G1526" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -46041,7 +46044,7 @@
         <v>25.0599994659424</v>
       </c>
       <c r="G1527" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -46067,7 +46070,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G1528" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -46093,7 +46096,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G1529" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -46119,7 +46122,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G1530" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -46145,7 +46148,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1531" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -46171,7 +46174,7 @@
         <v>23.1800003051758</v>
       </c>
       <c r="G1532" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -46197,7 +46200,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G1533" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -46223,7 +46226,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1534" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -46249,7 +46252,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1535" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -46275,7 +46278,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1536" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -46301,7 +46304,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G1537" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -46327,7 +46330,7 @@
         <v>23.2399997711182</v>
       </c>
       <c r="G1538" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -46353,7 +46356,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G1539" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -46379,7 +46382,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G1540" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -46405,7 +46408,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1541" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -46431,7 +46434,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1542" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -46457,7 +46460,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G1543" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -46483,7 +46486,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1544" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -46509,7 +46512,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G1545" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -46535,7 +46538,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G1546" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -46561,7 +46564,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1547" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -46587,7 +46590,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1548" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -46613,7 +46616,7 @@
         <v>23</v>
       </c>
       <c r="G1549" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -46639,7 +46642,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1550" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -46665,7 +46668,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G1551" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -46691,7 +46694,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G1552" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -46717,7 +46720,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G1553" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -46743,7 +46746,7 @@
         <v>22.5599994659424</v>
       </c>
       <c r="G1554" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -46769,7 +46772,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G1555" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -46795,7 +46798,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1556" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -46821,7 +46824,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1557" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -46847,7 +46850,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G1558" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -46873,7 +46876,7 @@
         <v>22.5</v>
       </c>
       <c r="G1559" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -46899,7 +46902,7 @@
         <v>22.0799999237061</v>
       </c>
       <c r="G1560" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -46925,7 +46928,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1561" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -46951,7 +46954,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G1562" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -46977,7 +46980,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G1563" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -47003,7 +47006,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G1564" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -47029,7 +47032,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1565" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -47055,7 +47058,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G1566" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -47081,7 +47084,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G1567" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -47107,7 +47110,7 @@
         <v>18.5</v>
       </c>
       <c r="G1568" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -47133,7 +47136,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1569" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -47211,7 +47214,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1572" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -47237,7 +47240,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G1573" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -47263,7 +47266,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1574" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -47315,7 +47318,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1576" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -47341,7 +47344,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1577" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -47367,7 +47370,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1578" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -47393,7 +47396,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G1579" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -47419,7 +47422,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1580" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -47445,7 +47448,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G1581" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -47471,7 +47474,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1582" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -47497,7 +47500,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1583" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -47549,7 +47552,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1585" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -47575,7 +47578,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1586" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -47601,7 +47604,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G1587" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -47627,7 +47630,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1588" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -47653,7 +47656,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G1589" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -47861,7 +47864,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1597" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -47887,7 +47890,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1598" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -47913,7 +47916,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1599" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -47991,7 +47994,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1602" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -48043,7 +48046,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G1604" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -48069,7 +48072,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G1605" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -48095,7 +48098,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1606" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -48225,7 +48228,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G1611" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -48329,7 +48332,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G1615" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -48355,7 +48358,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1616" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -48381,7 +48384,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1617" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -48433,7 +48436,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1619" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -48459,7 +48462,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G1620" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -48511,7 +48514,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G1622" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -48537,7 +48540,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G1623" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -48563,7 +48566,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1624" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -48589,7 +48592,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1625" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -48615,7 +48618,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1626" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -48641,7 +48644,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G1627" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -48667,7 +48670,7 @@
         <v>16</v>
       </c>
       <c r="G1628" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -48693,7 +48696,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G1629" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -48719,7 +48722,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1630" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -48745,7 +48748,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1631" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -48771,7 +48774,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1632" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -48797,7 +48800,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1633" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -48823,7 +48826,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1634" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -48849,7 +48852,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1635" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -48875,7 +48878,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1636" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -48901,7 +48904,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G1637" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -48927,7 +48930,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G1638" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -48953,7 +48956,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1639" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -48979,7 +48982,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G1640" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -49005,7 +49008,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1641" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -49031,7 +49034,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G1642" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -49057,7 +49060,7 @@
         <v>13.5</v>
       </c>
       <c r="G1643" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -49083,7 +49086,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1644" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -49109,7 +49112,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G1645" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -49135,7 +49138,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1646" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -49161,7 +49164,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1647" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -49187,7 +49190,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1648" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -49213,7 +49216,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1649" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -49239,7 +49242,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G1650" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -49265,7 +49268,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G1651" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -49291,7 +49294,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G1652" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -49317,7 +49320,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1653" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -49343,7 +49346,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G1654" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -49369,7 +49372,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1655" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -49395,7 +49398,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1656" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -49421,7 +49424,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1657" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -49447,7 +49450,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1658" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -49473,7 +49476,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1659" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -49499,7 +49502,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1660" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -49525,7 +49528,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G1661" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -49551,7 +49554,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1662" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -49577,7 +49580,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1663" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -49603,7 +49606,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G1664" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -49629,7 +49632,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1665" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -49655,7 +49658,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G1666" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -49681,7 +49684,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G1667" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -49707,7 +49710,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1668" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -49733,7 +49736,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1669" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -49759,7 +49762,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1670" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -49785,7 +49788,7 @@
         <v>13</v>
       </c>
       <c r="G1671" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -49811,7 +49814,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1672" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -49837,7 +49840,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1673" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -49863,7 +49866,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G1674" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -49889,7 +49892,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G1675" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -49915,7 +49918,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1676" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -49941,7 +49944,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G1677" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -49967,7 +49970,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1678" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -49993,7 +49996,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G1679" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -50019,7 +50022,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1680" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -50045,7 +50048,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G1681" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -50071,7 +50074,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G1682" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -50097,7 +50100,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1683" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -50123,7 +50126,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1684" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -50149,7 +50152,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1685" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -50175,7 +50178,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1686" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -50201,7 +50204,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G1687" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -50227,7 +50230,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1688" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -50253,7 +50256,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1689" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -50279,7 +50282,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G1690" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -50305,7 +50308,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1691" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -50331,7 +50334,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G1692" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -50357,7 +50360,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1693" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -50383,7 +50386,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G1694" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -50409,7 +50412,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G1695" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -50435,7 +50438,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1696" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -50461,7 +50464,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1697" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -50487,7 +50490,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1698" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -50513,7 +50516,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1699" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -50539,7 +50542,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1700" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -50565,7 +50568,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1701" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -50591,7 +50594,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G1702" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -50617,7 +50620,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1703" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -50643,7 +50646,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1704" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -50669,7 +50672,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1705" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -50695,7 +50698,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G1706" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -50721,7 +50724,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1707" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -50747,7 +50750,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G1708" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -50773,7 +50776,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G1709" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -50799,7 +50802,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1710" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -50825,7 +50828,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1711" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -50851,7 +50854,7 @@
         <v>11.75</v>
       </c>
       <c r="G1712" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -50877,7 +50880,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1713" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -50903,7 +50906,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1714" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -50929,7 +50932,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G1715" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -50955,7 +50958,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1716" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -50981,7 +50984,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G1717" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -51007,7 +51010,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1718" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -51033,7 +51036,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1719" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -51059,7 +51062,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1720" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -51085,7 +51088,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1721" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -51111,7 +51114,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1722" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -51137,7 +51140,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1723" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -51163,7 +51166,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1724" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -51189,7 +51192,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1725" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -51215,7 +51218,7 @@
         <v>11.75</v>
       </c>
       <c r="G1726" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -51241,7 +51244,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1727" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -51267,7 +51270,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1728" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -51293,7 +51296,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1729" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -51319,7 +51322,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1730" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -51345,7 +51348,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1731" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -51371,7 +51374,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G1732" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -51397,7 +51400,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G1733" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -51423,7 +51426,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1734" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -51449,7 +51452,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1735" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -51475,7 +51478,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G1736" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -51501,7 +51504,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G1737" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -51527,7 +51530,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1738" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -51553,7 +51556,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G1739" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -51579,7 +51582,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G1740" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -51605,7 +51608,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G1741" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -51631,7 +51634,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1742" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -51657,7 +51660,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1743" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -51683,7 +51686,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1744" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -51709,7 +51712,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1745" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -51735,7 +51738,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1746" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -51761,7 +51764,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1747" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -51787,7 +51790,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1748" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -51813,7 +51816,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G1749" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -51839,7 +51842,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G1750" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -51865,7 +51868,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1751" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -51891,7 +51894,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1752" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -51917,7 +51920,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G1753" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -51943,7 +51946,7 @@
         <v>12.710000038147</v>
       </c>
       <c r="G1754" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -51969,7 +51972,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1755" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -51995,7 +51998,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1756" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -52021,7 +52024,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1757" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -52047,7 +52050,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1758" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -52073,7 +52076,7 @@
         <v>12.75</v>
       </c>
       <c r="G1759" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -52099,7 +52102,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1760" t="s">
-        <v>1464</v>
+        <v>50</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -52125,7 +52128,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1761" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -52177,7 +52180,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1763" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -52229,7 +52232,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1765" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -52359,7 +52362,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1770" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -52437,7 +52440,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1773" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -52463,7 +52466,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1774" t="s">
-        <v>1464</v>
+        <v>50</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -52515,7 +52518,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G1776" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -52619,7 +52622,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G1780" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -52645,7 +52648,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G1781" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -52671,7 +52674,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1782" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -52697,7 +52700,7 @@
         <v>13</v>
       </c>
       <c r="G1783" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -52775,7 +52778,7 @@
         <v>13.5</v>
       </c>
       <c r="G1786" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -53321,7 +53324,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1807" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -53815,7 +53818,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1826" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -54205,7 +54208,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1841" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -54439,7 +54442,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1850" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -54699,7 +54702,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -54855,7 +54858,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G1866" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -54907,7 +54910,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G1868" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -71659,7 +71662,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.6928472222</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>146687</v>
@@ -71680,6 +71683,32 @@
         <v>1998</v>
       </c>
       <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.6910532407</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>105937</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>5.80999994277954</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>5.67000007629395</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>5.80999994277954</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>1999</v>
+      </c>
+      <c r="H2514" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2001" uniqueCount="2001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2002" uniqueCount="2002">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2523975372314</t>
+    <t xml:space="preserve">13.2523984909058</t>
   </si>
   <si>
     <t xml:space="preserve">BSS.MI</t>
@@ -50,19 +50,19 @@
     <t xml:space="preserve">12.7479515075684</t>
   </si>
   <si>
-    <t xml:space="preserve">12.397403717041</t>
+    <t xml:space="preserve">12.3974027633667</t>
   </si>
   <si>
     <t xml:space="preserve">12.2435054779053</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2606058120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.140905380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4825620651245</t>
+    <t xml:space="preserve">12.2606048583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1409063339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4825611114502</t>
   </si>
   <si>
     <t xml:space="preserve">10.858416557312</t>
@@ -71,67 +71,67 @@
     <t xml:space="preserve">9.79822444915771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3539686203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84952449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4736680984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2941198348999</t>
+    <t xml:space="preserve">10.3539705276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84952354431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4736700057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2941217422485</t>
   </si>
   <si>
     <t xml:space="preserve">10.7814664840698</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8156671524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.730167388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.576268196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.636116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1915225982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4565696716309</t>
+    <t xml:space="preserve">10.8156661987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7301664352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5762672424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6361169815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1915197372437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4565687179565</t>
   </si>
   <si>
     <t xml:space="preserve">10.4907693862915</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0205230712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03728103637695</t>
+    <t xml:space="preserve">10.0205221176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03727912902832</t>
   </si>
   <si>
     <t xml:space="preserve">8.97743129730225</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40492820739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14842987060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43057727813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90082454681396</t>
+    <t xml:space="preserve">9.40492725372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14843082427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43057632446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90082359313965</t>
   </si>
   <si>
     <t xml:space="preserve">9.66142559051514</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4394702911377</t>
+    <t xml:space="preserve">10.4394693374634</t>
   </si>
   <si>
     <t xml:space="preserve">10.3454208374023</t>
@@ -140,31 +140,31 @@
     <t xml:space="preserve">10.2000722885132</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0037641525269</t>
+    <t xml:space="preserve">11.0037651062012</t>
   </si>
   <si>
     <t xml:space="preserve">10.5506191253662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2257213592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.18297290802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0379657745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9097156524658</t>
+    <t xml:space="preserve">10.2257204055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1829719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0379667282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9097166061401</t>
   </si>
   <si>
     <t xml:space="preserve">11.8074598312378</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9442577362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1067066192627</t>
+    <t xml:space="preserve">11.9442586898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.106707572937</t>
   </si>
   <si>
     <t xml:space="preserve">11.7732601165771</t>
@@ -179,16 +179,16 @@
     <t xml:space="preserve">11.3714122772217</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3799619674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6621112823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8416604995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9186067581177</t>
+    <t xml:space="preserve">11.3799629211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6621103286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8416595458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9186086654663</t>
   </si>
   <si>
     <t xml:space="preserve">11.7989091873169</t>
@@ -200,55 +200,55 @@
     <t xml:space="preserve">12.1922063827515</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2007579803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3375549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1323556900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1665563583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2178564071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9015073776245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.568060874939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2859134674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7390594482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8844089508057</t>
+    <t xml:space="preserve">12.2007551193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3375558853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1323566436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1665554046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2178544998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9015083312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5680599212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2859125137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7390604019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8844079971313</t>
   </si>
   <si>
     <t xml:space="preserve">11.8160085678101</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7048587799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6022596359253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6364593505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4740123748779</t>
+    <t xml:space="preserve">11.7048597335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6022605895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6364603042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4740104675293</t>
   </si>
   <si>
     <t xml:space="preserve">11.1918649673462</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1063642501831</t>
+    <t xml:space="preserve">11.1063632965088</t>
   </si>
   <si>
     <t xml:space="preserve">11.1149139404297</t>
@@ -257,109 +257,109 @@
     <t xml:space="preserve">11.3201122283936</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457632064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1576642990112</t>
+    <t xml:space="preserve">11.3457622528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1576652526855</t>
   </si>
   <si>
     <t xml:space="preserve">11.0550651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9866647720337</t>
+    <t xml:space="preserve">10.9866666793823</t>
   </si>
   <si>
     <t xml:space="preserve">11.1405630111694</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6019172668457</t>
+    <t xml:space="preserve">10.60191822052</t>
   </si>
   <si>
     <t xml:space="preserve">10.9541397094727</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4346122741699</t>
+    <t xml:space="preserve">10.4346132278442</t>
   </si>
   <si>
     <t xml:space="preserve">10.3553628921509</t>
   </si>
   <si>
-    <t xml:space="preserve">10.22327709198</t>
+    <t xml:space="preserve">10.2232780456543</t>
   </si>
   <si>
     <t xml:space="preserve">10.2673053741455</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92388725280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3201398849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.003137588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.302529335022</t>
+    <t xml:space="preserve">9.92388916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3201389312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0031385421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3025283813477</t>
   </si>
   <si>
     <t xml:space="preserve">10.2496948242188</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6107244491577</t>
+    <t xml:space="preserve">10.6107234954834</t>
   </si>
   <si>
     <t xml:space="preserve">11.4120311737061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1302537918091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9189167022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2359199523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2799472808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0069751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8308629989624</t>
+    <t xml:space="preserve">11.1302528381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9189186096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2359209060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2799491882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0069742202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8308639526367</t>
   </si>
   <si>
     <t xml:space="preserve">10.8396692276001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9277238845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9101123809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8132524490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.513861656189</t>
+    <t xml:space="preserve">10.9277229309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9101142883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.813250541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5138607025146</t>
   </si>
   <si>
     <t xml:space="preserve">10.0647773742676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9943323135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95030498504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68613910675049</t>
+    <t xml:space="preserve">9.99433326721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9503059387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68613719940186</t>
   </si>
   <si>
     <t xml:space="preserve">10.0383605957031</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4962520599365</t>
+    <t xml:space="preserve">10.4962501525879</t>
   </si>
   <si>
     <t xml:space="preserve">10.3465566635132</t>
@@ -368,19 +368,19 @@
     <t xml:space="preserve">10.452223777771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5843076705933</t>
+    <t xml:space="preserve">10.5843067169189</t>
   </si>
   <si>
     <t xml:space="preserve">9.87985992431641</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12257957458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67733192443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57166576385498</t>
+    <t xml:space="preserve">9.12257862091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67733097076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57166385650635</t>
   </si>
   <si>
     <t xml:space="preserve">9.93269348144531</t>
@@ -389,31 +389,31 @@
     <t xml:space="preserve">10.1880559921265</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98552703857422</t>
+    <t xml:space="preserve">9.98552799224854</t>
   </si>
   <si>
     <t xml:space="preserve">9.18422031402588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14019203186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72135925292969</t>
+    <t xml:space="preserve">9.14019107818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.721360206604</t>
   </si>
   <si>
     <t xml:space="preserve">10.0823888778687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3817777633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2849159240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1352233886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2144727706909</t>
+    <t xml:space="preserve">10.3817796707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2849168777466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1352224349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2144737243652</t>
   </si>
   <si>
     <t xml:space="preserve">10.1528329849243</t>
@@ -422,28 +422,28 @@
     <t xml:space="preserve">10.6987791061401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0774183273315</t>
+    <t xml:space="preserve">11.0774192810059</t>
   </si>
   <si>
     <t xml:space="preserve">11.0157804489136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0333909988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9893627166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8748922348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0950298309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2535314559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3151693344116</t>
+    <t xml:space="preserve">11.033390045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9893636703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8748912811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0950307846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2535305023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3151712417603</t>
   </si>
   <si>
     <t xml:space="preserve">10.7251958847046</t>
@@ -452,22 +452,22 @@
     <t xml:space="preserve">11.0510025024414</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9013071060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1654748916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0598087310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2183074951172</t>
+    <t xml:space="preserve">10.9013080596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1654758453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0598068237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2183084487915</t>
   </si>
   <si>
     <t xml:space="preserve">11.1214475631714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1830854415894</t>
+    <t xml:space="preserve">11.1830863952637</t>
   </si>
   <si>
     <t xml:space="preserve">11.2623357772827</t>
@@ -476,19 +476,19 @@
     <t xml:space="preserve">11.5265045166016</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7466430664062</t>
+    <t xml:space="preserve">11.7466421127319</t>
   </si>
   <si>
     <t xml:space="preserve">11.7730598449707</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6850061416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7994775772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6497812271118</t>
+    <t xml:space="preserve">11.685004234314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7994766235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6497821807861</t>
   </si>
   <si>
     <t xml:space="preserve">11.6673927307129</t>
@@ -500,25 +500,25 @@
     <t xml:space="preserve">11.3239755630493</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3680038452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1390581130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6938104629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.614559173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8258943557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0372266769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.054838180542</t>
+    <t xml:space="preserve">11.3680047988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1390562057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.693808555603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6145582199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8258924484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0372276306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0548391342163</t>
   </si>
   <si>
     <t xml:space="preserve">12.0636434555054</t>
@@ -527,19 +527,19 @@
     <t xml:space="preserve">12.5039224624634</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5303392410278</t>
+    <t xml:space="preserve">12.5303401947021</t>
   </si>
   <si>
     <t xml:space="preserve">12.4070615768433</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2837820053101</t>
+    <t xml:space="preserve">12.2837839126587</t>
   </si>
   <si>
     <t xml:space="preserve">12.6007843017578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9177865982056</t>
+    <t xml:space="preserve">12.9177856445312</t>
   </si>
   <si>
     <t xml:space="preserve">12.8121185302734</t>
@@ -548,28 +548,28 @@
     <t xml:space="preserve">12.8561477661133</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0322570800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4108982086182</t>
+    <t xml:space="preserve">13.0322580337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4108972549438</t>
   </si>
   <si>
     <t xml:space="preserve">13.5782041549683</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6838703155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4285087585449</t>
+    <t xml:space="preserve">13.6838712692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4285097122192</t>
   </si>
   <si>
     <t xml:space="preserve">14.3707056045532</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2210102081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2562341690063</t>
+    <t xml:space="preserve">14.2210111618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2562351226807</t>
   </si>
   <si>
     <t xml:space="preserve">14.1329545974731</t>
@@ -581,22 +581,22 @@
     <t xml:space="preserve">14.0713157653809</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9216232299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7807312011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6046209335327</t>
+    <t xml:space="preserve">13.9216213226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7807321548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6046199798584</t>
   </si>
   <si>
     <t xml:space="preserve">13.7631206512451</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8335647583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7278995513916</t>
+    <t xml:space="preserve">13.8335657119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7278985977173</t>
   </si>
   <si>
     <t xml:space="preserve">13.1995630264282</t>
@@ -605,13 +605,13 @@
     <t xml:space="preserve">13.375675201416</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1555337905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6486492156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5605916976929</t>
+    <t xml:space="preserve">13.155535697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6486482620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5605936050415</t>
   </si>
   <si>
     <t xml:space="preserve">13.7367057800293</t>
@@ -620,154 +620,154 @@
     <t xml:space="preserve">13.8775930404663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.176983833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0977325439453</t>
+    <t xml:space="preserve">14.1769847869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0977344512939</t>
   </si>
   <si>
     <t xml:space="preserve">14.7845687866211</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3040971755981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2776803970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4890146255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4978199005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3657350540161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4449872970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3393182754517</t>
+    <t xml:space="preserve">15.3040962219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2776832580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4890155792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.497820854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3657369613647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4449892044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3393211364746</t>
   </si>
   <si>
     <t xml:space="preserve">15.5330419540405</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6651277542114</t>
+    <t xml:space="preserve">15.6651258468628</t>
   </si>
   <si>
     <t xml:space="preserve">15.5418481826782</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2424564361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8060159683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1934623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3695755004883</t>
+    <t xml:space="preserve">15.2424583435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8060150146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1934604644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3695735931396</t>
   </si>
   <si>
     <t xml:space="preserve">16.4664325714111</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5104637145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0387992858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.889102935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1532707214355</t>
+    <t xml:space="preserve">16.510461807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.03879737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8890991210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1532688140869</t>
   </si>
   <si>
     <t xml:space="preserve">16.7746295928955</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5544891357422</t>
+    <t xml:space="preserve">16.5544910430908</t>
   </si>
   <si>
     <t xml:space="preserve">16.2374897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5897121429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6513500213623</t>
+    <t xml:space="preserve">16.589714050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6513519287109</t>
   </si>
   <si>
     <t xml:space="preserve">16.5720996856689</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9947700500488</t>
+    <t xml:space="preserve">16.9947681427002</t>
   </si>
   <si>
     <t xml:space="preserve">16.7041835784912</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8802947998047</t>
+    <t xml:space="preserve">16.880298614502</t>
   </si>
   <si>
     <t xml:space="preserve">16.8538780212402</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0123805999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2941608428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1268520355225</t>
+    <t xml:space="preserve">17.0123767852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2941589355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1268501281738</t>
   </si>
   <si>
     <t xml:space="preserve">16.5368766784668</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0828227996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8626823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2061042785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3469924926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6551837921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5407161712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5054950714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7168254852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4526596069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5583267211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7432460784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8401031494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5759372711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7482147216797</t>
+    <t xml:space="preserve">17.0828266143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8626861572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2061061859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3469944000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6551876068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.540714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5054893493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7168273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4526615142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.55832862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7432422637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8401050567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5759353637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7482109069824</t>
   </si>
   <si>
     <t xml:space="preserve">16.7658252716064</t>
@@ -779,16 +779,16 @@
     <t xml:space="preserve">17.1620750427246</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2765502929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6865711212158</t>
+    <t xml:space="preserve">17.2765483856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6865730285645</t>
   </si>
   <si>
     <t xml:space="preserve">17.1092414855957</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8186588287354</t>
+    <t xml:space="preserve">16.8186569213867</t>
   </si>
   <si>
     <t xml:space="preserve">17.2325172424316</t>
@@ -797,40 +797,40 @@
     <t xml:space="preserve">17.2853527069092</t>
   </si>
   <si>
-    <t xml:space="preserve">17.391019821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.250129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4350471496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3734092712402</t>
+    <t xml:space="preserve">17.3910179138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2501316070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4350452423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3734073638916</t>
   </si>
   <si>
     <t xml:space="preserve">17.6463813781738</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9457683563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.372278213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9358310699463</t>
+    <t xml:space="preserve">17.9457721710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3722743988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9358329772949</t>
   </si>
   <si>
     <t xml:space="preserve">20.3849182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5962505340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3408870697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8340015411377</t>
+    <t xml:space="preserve">20.5962524414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3408889770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8340034484863</t>
   </si>
   <si>
     <t xml:space="preserve">21.0453357696533</t>
@@ -842,85 +842,85 @@
     <t xml:space="preserve">21.0893630981445</t>
   </si>
   <si>
-    <t xml:space="preserve">21.327112197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6529197692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7497844696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9170875549316</t>
+    <t xml:space="preserve">21.3271141052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6529216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7497825622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9170894622803</t>
   </si>
   <si>
     <t xml:space="preserve">21.8114204406738</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0139503479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.286922454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2605075836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.348560333252</t>
+    <t xml:space="preserve">22.0139484405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2869243621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2605056762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3485584259033</t>
   </si>
   <si>
     <t xml:space="preserve">22.3221454620361</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1900596618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6303386688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4366149902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4806480407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6655597686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6215343475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6743659973145</t>
+    <t xml:space="preserve">22.1900615692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6303424835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.436616897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4806442260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6655616760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6215324401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6743698120117</t>
   </si>
   <si>
     <t xml:space="preserve">22.8945064544678</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0970344543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8328685760498</t>
+    <t xml:space="preserve">23.0970363616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8328666687012</t>
   </si>
   <si>
     <t xml:space="preserve">22.3749771118164</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1938953399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3876209259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5109004974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9159564971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2417640686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7084579467773</t>
+    <t xml:space="preserve">23.1938991546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3876171112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5108985900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9159526824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2417602539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7084560394287</t>
   </si>
   <si>
     <t xml:space="preserve">24.6556224822998</t>
@@ -935,10 +935,10 @@
     <t xml:space="preserve">24.9638195037842</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8933734893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4255428314209</t>
+    <t xml:space="preserve">24.8933773040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4255447387695</t>
   </si>
   <si>
     <t xml:space="preserve">26.4879322052002</t>
@@ -947,13 +947,13 @@
     <t xml:space="preserve">27.3970069885254</t>
   </si>
   <si>
-    <t xml:space="preserve">27.628734588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1545715332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6732921600342</t>
+    <t xml:space="preserve">27.6287326812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1545696258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6732940673828</t>
   </si>
   <si>
     <t xml:space="preserve">28.6804065704346</t>
@@ -965,16 +965,16 @@
     <t xml:space="preserve">27.8069839477539</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4665107727051</t>
+    <t xml:space="preserve">28.4665088653564</t>
   </si>
   <si>
     <t xml:space="preserve">29.0190811157227</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4914417266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7677326202393</t>
+    <t xml:space="preserve">29.4914436340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7677345275879</t>
   </si>
   <si>
     <t xml:space="preserve">29.8746814727783</t>
@@ -983,25 +983,25 @@
     <t xml:space="preserve">30.3024806976318</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7748394012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2400951385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6678943634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8283176422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8996181488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0154800415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9976558685303</t>
+    <t xml:space="preserve">30.7748432159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2400894165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6678924560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8283157348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8996162414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0154781341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9976539611816</t>
   </si>
   <si>
     <t xml:space="preserve">30.935266494751</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">30.748104095459</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6857204437256</t>
+    <t xml:space="preserve">30.685718536377</t>
   </si>
   <si>
     <t xml:space="preserve">29.3577556610107</t>
@@ -1022,37 +1022,37 @@
     <t xml:space="preserve">29.5003528594971</t>
   </si>
   <si>
-    <t xml:space="preserve">29.313196182251</t>
+    <t xml:space="preserve">29.3131904602051</t>
   </si>
   <si>
     <t xml:space="preserve">29.2775421142578</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1687908172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1331443786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9994583129883</t>
+    <t xml:space="preserve">30.1687870025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1331405639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.999454498291</t>
   </si>
   <si>
     <t xml:space="preserve">29.9281558990479</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0529327392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4825325012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8122940063477</t>
+    <t xml:space="preserve">30.0529308319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4825344085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.812292098999</t>
   </si>
   <si>
     <t xml:space="preserve">28.9121322631836</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1260299682617</t>
+    <t xml:space="preserve">29.1260318756104</t>
   </si>
   <si>
     <t xml:space="preserve">27.7713317871094</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">27.6911182403564</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4861316680908</t>
+    <t xml:space="preserve">27.4861335754395</t>
   </si>
   <si>
     <t xml:space="preserve">27.5752582550049</t>
@@ -1076,46 +1076,46 @@
     <t xml:space="preserve">28.1189193725586</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3506450653076</t>
+    <t xml:space="preserve">28.350643157959</t>
   </si>
   <si>
     <t xml:space="preserve">27.7178573608398</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5734577178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6180191040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.519983291626</t>
+    <t xml:space="preserve">28.5734596252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6180210113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5199794769287</t>
   </si>
   <si>
     <t xml:space="preserve">28.7873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7855567932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5360069274902</t>
+    <t xml:space="preserve">29.7855529785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.536003112793</t>
   </si>
   <si>
     <t xml:space="preserve">29.3310203552246</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1705932617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2329807281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.143856048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3221111297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9656047821045</t>
+    <t xml:space="preserve">29.1705913543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2329769134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1438579559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3221073150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9656066894531</t>
   </si>
   <si>
     <t xml:space="preserve">28.7071437835693</t>
@@ -1124,46 +1124,46 @@
     <t xml:space="preserve">28.9923439025879</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9477825164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.607307434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8568572998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4023208618164</t>
+    <t xml:space="preserve">28.9477806091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6073055267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8568553924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.402322769165</t>
   </si>
   <si>
     <t xml:space="preserve">29.4112300872803</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8140964508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6875190734863</t>
+    <t xml:space="preserve">28.814094543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.687520980835</t>
   </si>
   <si>
     <t xml:space="preserve">29.6162185668945</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6786060333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6964282989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.142053604126</t>
+    <t xml:space="preserve">29.6786041259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6964340209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1420574188232</t>
   </si>
   <si>
     <t xml:space="preserve">29.8390312194824</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1866149902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5181770324707</t>
+    <t xml:space="preserve">30.1866188049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5181789398193</t>
   </si>
   <si>
     <t xml:space="preserve">29.1795063018799</t>
@@ -1175,70 +1175,70 @@
     <t xml:space="preserve">30.3648681640625</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4629039764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4718189239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2935695648193</t>
+    <t xml:space="preserve">30.4629058837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4718208312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2935676574707</t>
   </si>
   <si>
     <t xml:space="preserve">30.0974922180176</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0618438720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2311782836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0849838256836</t>
+    <t xml:space="preserve">30.0618419647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2311763763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0849800109863</t>
   </si>
   <si>
     <t xml:space="preserve">31.4967517852783</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8194065093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9958572387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.773042678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6928272247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1830139160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0760688781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.951286315918</t>
+    <t xml:space="preserve">30.819408416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9958534240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7730407714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6928310394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1830177307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0760650634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9512920379639</t>
   </si>
   <si>
     <t xml:space="preserve">32.3077926635742</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1990432739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3951187133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7587242126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6963424682617</t>
+    <t xml:space="preserve">33.1990394592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3951148986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.758731842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6963386535645</t>
   </si>
   <si>
     <t xml:space="preserve">34.731990814209</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5804748535156</t>
+    <t xml:space="preserve">34.5804786682129</t>
   </si>
   <si>
     <t xml:space="preserve">34.2239761352539</t>
@@ -1253,31 +1253,31 @@
     <t xml:space="preserve">35.4271659851074</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2221794128418</t>
+    <t xml:space="preserve">35.2221755981445</t>
   </si>
   <si>
     <t xml:space="preserve">34.6606903076172</t>
   </si>
   <si>
-    <t xml:space="preserve">34.37548828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8674812316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8496551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1437644958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7159690856934</t>
+    <t xml:space="preserve">34.3754920959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8674774169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8496513366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1437683105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7159652709961</t>
   </si>
   <si>
     <t xml:space="preserve">34.0635528564453</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3131065368652</t>
+    <t xml:space="preserve">34.3130989074707</t>
   </si>
   <si>
     <t xml:space="preserve">34.1170272827148</t>
@@ -1289,19 +1289,19 @@
     <t xml:space="preserve">34.7765502929688</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6161231994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3041877746582</t>
+    <t xml:space="preserve">34.6161270141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3041954040527</t>
   </si>
   <si>
     <t xml:space="preserve">34.1081161499023</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8425369262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0902900695801</t>
+    <t xml:space="preserve">32.8425407409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0902938842773</t>
   </si>
   <si>
     <t xml:space="preserve">35.106315612793</t>
@@ -1310,13 +1310,13 @@
     <t xml:space="preserve">36.2471122741699</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3005905151367</t>
+    <t xml:space="preserve">36.3005867004395</t>
   </si>
   <si>
     <t xml:space="preserve">36.1847267150879</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4966659545898</t>
+    <t xml:space="preserve">36.4966621398926</t>
   </si>
   <si>
     <t xml:space="preserve">37.4146499633789</t>
@@ -1328,22 +1328,22 @@
     <t xml:space="preserve">38.9208602905273</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6178359985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5821914672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2702484130859</t>
+    <t xml:space="preserve">38.6178398132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5821876525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2702522277832</t>
   </si>
   <si>
     <t xml:space="preserve">38.4306755065918</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2149696350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8050003051758</t>
+    <t xml:space="preserve">39.214973449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8049964904785</t>
   </si>
   <si>
     <t xml:space="preserve">37.8068008422852</t>
@@ -1352,19 +1352,19 @@
     <t xml:space="preserve">38.3504638671875</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0563468933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3682899475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3415565490723</t>
+    <t xml:space="preserve">38.0563507080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3682823181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3415489196777</t>
   </si>
   <si>
     <t xml:space="preserve">38.5198020935059</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5643615722656</t>
+    <t xml:space="preserve">38.5643692016602</t>
   </si>
   <si>
     <t xml:space="preserve">38.6089248657227</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">38.7336959838867</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4377937316895</t>
+    <t xml:space="preserve">39.4377899169922</t>
   </si>
   <si>
     <t xml:space="preserve">39.0812873840332</t>
@@ -1385,19 +1385,19 @@
     <t xml:space="preserve">39.0545501708984</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3219261169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5554504394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2880744934082</t>
+    <t xml:space="preserve">39.3219223022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5554466247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2880783081055</t>
   </si>
   <si>
     <t xml:space="preserve">38.3772010803223</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6998558044434</t>
+    <t xml:space="preserve">37.6998519897461</t>
   </si>
   <si>
     <t xml:space="preserve">36.6125297546387</t>
@@ -1409,10 +1409,10 @@
     <t xml:space="preserve">38.4663238525391</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9956703186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.655200958252</t>
+    <t xml:space="preserve">41.9956665039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6551971435547</t>
   </si>
   <si>
     <t xml:space="preserve">42.8156242370605</t>
@@ -1424,13 +1424,13 @@
     <t xml:space="preserve">42.031322479248</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0847969055176</t>
+    <t xml:space="preserve">42.0848007202148</t>
   </si>
   <si>
     <t xml:space="preserve">41.924373626709</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6213493347168</t>
+    <t xml:space="preserve">41.6213455200195</t>
   </si>
   <si>
     <t xml:space="preserve">41.7639465332031</t>
@@ -1439,10 +1439,10 @@
     <t xml:space="preserve">42.1382713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6926498413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5322189331055</t>
+    <t xml:space="preserve">41.6926460266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5322227478027</t>
   </si>
   <si>
     <t xml:space="preserve">41.7817687988281</t>
@@ -1451,28 +1451,28 @@
     <t xml:space="preserve">41.3539772033691</t>
   </si>
   <si>
-    <t xml:space="preserve">40.819221496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3557777404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5875015258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8031997680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1436729431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6784248352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7799758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4787521362305</t>
+    <t xml:space="preserve">40.8192253112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3557739257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5874977111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8032035827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1436767578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6784210205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.779972076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4787483215332</t>
   </si>
   <si>
     <t xml:space="preserve">38.6802253723145</t>
@@ -1484,67 +1484,67 @@
     <t xml:space="preserve">37.2898750305176</t>
   </si>
   <si>
-    <t xml:space="preserve">39.589298248291</t>
+    <t xml:space="preserve">39.5892944335938</t>
   </si>
   <si>
     <t xml:space="preserve">40.1953468322754</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1062278747559</t>
+    <t xml:space="preserve">40.1062240600586</t>
   </si>
   <si>
     <t xml:space="preserve">40.5696754455566</t>
   </si>
   <si>
-    <t xml:space="preserve">40.801399230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9439964294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1400718688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9974746704102</t>
+    <t xml:space="preserve">40.8014030456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9440002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1400756835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9974708557129</t>
   </si>
   <si>
     <t xml:space="preserve">40.5161972045898</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9618186950684</t>
+    <t xml:space="preserve">40.9618225097656</t>
   </si>
   <si>
     <t xml:space="preserve">39.2506256103516</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1793251037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2131729125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3914222717285</t>
+    <t xml:space="preserve">39.1793212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2131690979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3914260864258</t>
   </si>
   <si>
     <t xml:space="preserve">41.3896217346191</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6017189025879</t>
+    <t xml:space="preserve">42.6017265319824</t>
   </si>
   <si>
     <t xml:space="preserve">44.5446472167969</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9029502868652</t>
+    <t xml:space="preserve">43.9029426574707</t>
   </si>
   <si>
     <t xml:space="preserve">45.2309074401855</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8851165771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9635314941406</t>
+    <t xml:space="preserve">43.885124206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9635353088379</t>
   </si>
   <si>
     <t xml:space="preserve">46.0330352783203</t>
@@ -1556,13 +1556,13 @@
     <t xml:space="preserve">45.943904876709</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5874099731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.696159362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.009895324707</t>
+    <t xml:space="preserve">45.5874061584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6961631774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0098991394043</t>
   </si>
   <si>
     <t xml:space="preserve">43.8494720458984</t>
@@ -1571,22 +1571,22 @@
     <t xml:space="preserve">42.9582252502441</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4609222412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.175724029541</t>
+    <t xml:space="preserve">41.4609260559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1757278442383</t>
   </si>
   <si>
     <t xml:space="preserve">41.1578979492188</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0152969360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7675476074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.108024597168</t>
+    <t xml:space="preserve">41.0153007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7675514221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1080207824707</t>
   </si>
   <si>
     <t xml:space="preserve">40.7479209899902</t>
@@ -1595,13 +1595,13 @@
     <t xml:space="preserve">39.7853736877441</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5518531799316</t>
+    <t xml:space="preserve">40.5518493652344</t>
   </si>
   <si>
     <t xml:space="preserve">39.7318992614746</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3040962219238</t>
+    <t xml:space="preserve">39.3041000366211</t>
   </si>
   <si>
     <t xml:space="preserve">40.2488250732422</t>
@@ -1613,19 +1613,19 @@
     <t xml:space="preserve">39.4288787841797</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0367240905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.387825012207</t>
+    <t xml:space="preserve">39.0367202758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3878288269043</t>
   </si>
   <si>
     <t xml:space="preserve">41.050952911377</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9335746765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0149269104004</t>
+    <t xml:space="preserve">41.9335708618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0149230957031</t>
   </si>
   <si>
     <t xml:space="preserve">40.7087059020996</t>
@@ -1634,25 +1634,25 @@
     <t xml:space="preserve">40.6366539001465</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5285873413086</t>
+    <t xml:space="preserve">40.5285835266113</t>
   </si>
   <si>
     <t xml:space="preserve">39.8441009521484</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7366142272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.484432220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3316192626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0521240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4757270812988</t>
+    <t xml:space="preserve">37.7366104125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4844360351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3316268920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.052131652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4757232666016</t>
   </si>
   <si>
     <t xml:space="preserve">36.6018104553223</t>
@@ -1664,10 +1664,10 @@
     <t xml:space="preserve">35.6651496887207</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3589324951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2241363525391</t>
+    <t xml:space="preserve">35.3589363098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2241325378418</t>
   </si>
   <si>
     <t xml:space="preserve">33.4135627746582</t>
@@ -1676,157 +1676,157 @@
     <t xml:space="preserve">33.6657409667969</t>
   </si>
   <si>
-    <t xml:space="preserve">33.881893157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4763145446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6924667358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1427803039551</t>
+    <t xml:space="preserve">33.8818893432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4763107299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6924705505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1427841186523</t>
   </si>
   <si>
     <t xml:space="preserve">34.7284927368164</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5483665466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9899711608887</t>
+    <t xml:space="preserve">34.5483627319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9899749755859</t>
   </si>
   <si>
     <t xml:space="preserve">33.8278579711914</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4402885437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1247673034668</t>
+    <t xml:space="preserve">34.4402923583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1247711181641</t>
   </si>
   <si>
     <t xml:space="preserve">33.5036277770996</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4048538208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3868370056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4681949615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7744083404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5315341949463</t>
+    <t xml:space="preserve">32.4048461914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3868408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4681911468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7744121551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.531530380249</t>
   </si>
   <si>
     <t xml:space="preserve">29.486795425415</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9371128082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2346153259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.153263092041</t>
+    <t xml:space="preserve">29.9371147155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2346172332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1532649993896</t>
   </si>
   <si>
     <t xml:space="preserve">29.2166042327881</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4147434234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8296222686768</t>
+    <t xml:space="preserve">29.4147415161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8296241760254</t>
   </si>
   <si>
     <t xml:space="preserve">29.1265392303467</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5408325195312</t>
+    <t xml:space="preserve">29.5408306121826</t>
   </si>
   <si>
     <t xml:space="preserve">30.6035804748535</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2520389556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6489086151123</t>
+    <t xml:space="preserve">31.2520408630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6489105224609</t>
   </si>
   <si>
     <t xml:space="preserve">29.9551239013672</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1172389984131</t>
+    <t xml:space="preserve">30.1172370910645</t>
   </si>
   <si>
     <t xml:space="preserve">30.4054393768311</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6663360595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6483173370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.080623626709</t>
+    <t xml:space="preserve">31.6663303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6483211517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0806198120117</t>
   </si>
   <si>
     <t xml:space="preserve">31.1079368591309</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3601131439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9818534851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7383842468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6122913360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8377494812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9190998077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9010887145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6669216156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0905132293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7302627563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0998191833496</t>
+    <t xml:space="preserve">31.3601188659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9818477630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7383823394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6122932434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8377456665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9191017150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.901086807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.666919708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0905151367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7302589416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.099817276001</t>
   </si>
   <si>
     <t xml:space="preserve">27.5954608917236</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6407890319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2805328369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0463695526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5146999359131</t>
+    <t xml:space="preserve">26.6407871246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2805347442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0463676452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5146980285645</t>
   </si>
   <si>
     <t xml:space="preserve">27.2352046966553</t>
@@ -1844,13 +1844,13 @@
     <t xml:space="preserve">26.7488651275635</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4693717956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9196910858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5774478912354</t>
+    <t xml:space="preserve">27.4693737030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9196891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.577449798584</t>
   </si>
   <si>
     <t xml:space="preserve">27.9377021789551</t>
@@ -1865,34 +1865,34 @@
     <t xml:space="preserve">28.0457763671875</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0097541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7755889892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6041717529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5501346588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1805801391602</t>
+    <t xml:space="preserve">28.0097503662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7755870819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6041736602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5501327514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1805782318115</t>
   </si>
   <si>
     <t xml:space="preserve">29.1625652313232</t>
   </si>
   <si>
-    <t xml:space="preserve">28.640193939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6762237548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6675090789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.451358795166</t>
+    <t xml:space="preserve">28.6401977539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6762218475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6675109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4513607025146</t>
   </si>
   <si>
     <t xml:space="preserve">27.5594348907471</t>
@@ -1901,31 +1901,31 @@
     <t xml:space="preserve">25.7581653594971</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7320289611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7413311004639</t>
+    <t xml:space="preserve">22.7320308685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">21.7233200073242</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7860698699951</t>
+    <t xml:space="preserve">22.7860679626465</t>
   </si>
   <si>
     <t xml:space="preserve">23.4165134429932</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7047176361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5606174468994</t>
+    <t xml:space="preserve">23.7047157287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5606155395508</t>
   </si>
   <si>
     <t xml:space="preserve">23.2363872528076</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4345283508301</t>
+    <t xml:space="preserve">23.4345264434814</t>
   </si>
   <si>
     <t xml:space="preserve">22.5158786773682</t>
@@ -1934,10 +1934,10 @@
     <t xml:space="preserve">21.7053089141846</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8226871490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3630619049072</t>
+    <t xml:space="preserve">20.8226833343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3630638122559</t>
   </si>
   <si>
     <t xml:space="preserve">21.2369766235352</t>
@@ -1946,19 +1946,19 @@
     <t xml:space="preserve">21.3450546264648</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5972290039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7239093780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3189182281494</t>
+    <t xml:space="preserve">21.5972309112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7239074707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.318920135498</t>
   </si>
   <si>
     <t xml:space="preserve">18.2828922271729</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5437831878662</t>
+    <t xml:space="preserve">19.5437812805176</t>
   </si>
   <si>
     <t xml:space="preserve">18.877311706543</t>
@@ -1967,16 +1967,16 @@
     <t xml:space="preserve">18.3909702301025</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0033988952637</t>
+    <t xml:space="preserve">19.0034008026123</t>
   </si>
   <si>
     <t xml:space="preserve">18.0036964416504</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1390857696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1120681762695</t>
+    <t xml:space="preserve">17.1390895843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1120662689209</t>
   </si>
   <si>
     <t xml:space="preserve">17.2651767730713</t>
@@ -1985,73 +1985,73 @@
     <t xml:space="preserve">16.6617488861084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2024269104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9502477645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.716082572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6800565719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6170139312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1573944091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6077136993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4005641937256</t>
+    <t xml:space="preserve">16.2024230957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9502487182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.71608543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6800594329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6170148849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1573925018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6077117919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4005661010742</t>
   </si>
   <si>
     <t xml:space="preserve">17.4723205566406</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5533809661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.490629196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9406509399414</t>
+    <t xml:space="preserve">17.5533790588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4906272888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.94065284729</t>
   </si>
   <si>
     <t xml:space="preserve">18.8232746124268</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6614589691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7968444824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0132904052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.905216217041</t>
+    <t xml:space="preserve">17.6614551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7968425750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0132923126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9052181243896</t>
   </si>
   <si>
     <t xml:space="preserve">16.2654685974121</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1934185028076</t>
+    <t xml:space="preserve">16.1934204101562</t>
   </si>
   <si>
     <t xml:space="preserve">15.7250900268555</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4008626937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0496139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7524032592773</t>
+    <t xml:space="preserve">15.400860786438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0496129989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7524042129517</t>
   </si>
   <si>
     <t xml:space="preserve">15.5899934768677</t>
@@ -2060,10 +2060,10 @@
     <t xml:space="preserve">15.1486835479736</t>
   </si>
   <si>
-    <t xml:space="preserve">15.463903427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1661052703857</t>
+    <t xml:space="preserve">15.4639053344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1661033630371</t>
   </si>
   <si>
     <t xml:space="preserve">17.7875442504883</t>
@@ -2072,19 +2072,19 @@
     <t xml:space="preserve">18.1568031311035</t>
   </si>
   <si>
-    <t xml:space="preserve">17.643440246582</t>
+    <t xml:space="preserve">17.6434421539307</t>
   </si>
   <si>
     <t xml:space="preserve">17.391263961792</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0127048492432</t>
+    <t xml:space="preserve">18.0127010345459</t>
   </si>
   <si>
     <t xml:space="preserve">18.0487289428711</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2288551330566</t>
+    <t xml:space="preserve">18.2288570404053</t>
   </si>
   <si>
     <t xml:space="preserve">18.0307159423828</t>
@@ -2093,25 +2093,25 @@
     <t xml:space="preserve">17.9226398468018</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4543075561523</t>
+    <t xml:space="preserve">17.454309463501</t>
   </si>
   <si>
     <t xml:space="preserve">18.6791744232178</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8052616119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6251335144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3369331359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9493618011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7872505187988</t>
+    <t xml:space="preserve">18.8052635192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6251354217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3369312286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9493656158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7872486114502</t>
   </si>
   <si>
     <t xml:space="preserve">18.6971855163574</t>
@@ -2120,16 +2120,16 @@
     <t xml:space="preserve">18.354944229126</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4269924163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9856853485107</t>
+    <t xml:space="preserve">18.4269943237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9856815338135</t>
   </si>
   <si>
     <t xml:space="preserve">17.3552398681641</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7244987487793</t>
+    <t xml:space="preserve">17.7245006561279</t>
   </si>
   <si>
     <t xml:space="preserve">18.3009052276611</t>
@@ -2138,25 +2138,25 @@
     <t xml:space="preserve">18.6071224212646</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3996810913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6698684692383</t>
+    <t xml:space="preserve">19.3996829986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6698703765869</t>
   </si>
   <si>
     <t xml:space="preserve">20.2462768554688</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0661525726318</t>
+    <t xml:space="preserve">20.0661506652832</t>
   </si>
   <si>
     <t xml:space="preserve">19.9220504760742</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4176940917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4537200927734</t>
+    <t xml:space="preserve">19.4176921844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4537181854248</t>
   </si>
   <si>
     <t xml:space="preserve">20.2823047637939</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">17.7515182495117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7425117492676</t>
+    <t xml:space="preserve">17.7425136566162</t>
   </si>
   <si>
     <t xml:space="preserve">17.7965507507324</t>
@@ -2177,10 +2177,10 @@
     <t xml:space="preserve">17.4182834625244</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8508853912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9859790802002</t>
+    <t xml:space="preserve">16.8508834838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9859771728516</t>
   </si>
   <si>
     <t xml:space="preserve">16.868896484375</t>
@@ -2189,40 +2189,40 @@
     <t xml:space="preserve">17.0490226745605</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9409465789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3462333679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2741832733154</t>
+    <t xml:space="preserve">16.9409446716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3462352752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2741813659668</t>
   </si>
   <si>
     <t xml:space="preserve">17.3822574615479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2831878662109</t>
+    <t xml:space="preserve">17.2831897735596</t>
   </si>
   <si>
     <t xml:space="preserve">18.1748180389404</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9766788482666</t>
+    <t xml:space="preserve">17.976676940918</t>
   </si>
   <si>
     <t xml:space="preserve">17.6164226531982</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4272918701172</t>
+    <t xml:space="preserve">17.4272899627686</t>
   </si>
   <si>
     <t xml:space="preserve">18.1387920379639</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9136333465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6974811553955</t>
+    <t xml:space="preserve">17.913631439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6974792480469</t>
   </si>
   <si>
     <t xml:space="preserve">18.1928291320801</t>
@@ -2231,13 +2231,13 @@
     <t xml:space="preserve">17.9496574401855</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2381572723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1300830841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6794662475586</t>
+    <t xml:space="preserve">17.2381553649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1300792694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6794681549072</t>
   </si>
   <si>
     <t xml:space="preserve">17.9676704406738</t>
@@ -2246,7 +2246,7 @@
     <t xml:space="preserve">18.0847549438477</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0667400360107</t>
+    <t xml:space="preserve">18.0667419433594</t>
   </si>
   <si>
     <t xml:space="preserve">17.8686008453369</t>
@@ -2258,13 +2258,13 @@
     <t xml:space="preserve">17.6074161529541</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5894069671631</t>
+    <t xml:space="preserve">17.5894050598145</t>
   </si>
   <si>
     <t xml:space="preserve">17.76953125</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6365585327148</t>
+    <t xml:space="preserve">18.6365566253662</t>
   </si>
   <si>
     <t xml:space="preserve">17.24342918396</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">16.5330257415771</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1916637420654</t>
+    <t xml:space="preserve">16.1916618347168</t>
   </si>
   <si>
     <t xml:space="preserve">15.684232711792</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">14.6232395172119</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8021230697632</t>
+    <t xml:space="preserve">13.8021240234375</t>
   </si>
   <si>
     <t xml:space="preserve">13.9405145645142</t>
@@ -2300,10 +2300,10 @@
     <t xml:space="preserve">13.3131456375122</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8943853378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8390274047852</t>
+    <t xml:space="preserve">13.894383430481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8390283584595</t>
   </si>
   <si>
     <t xml:space="preserve">13.4792137145996</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">12.9533309936523</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0732688903809</t>
+    <t xml:space="preserve">13.0732679367065</t>
   </si>
   <si>
     <t xml:space="preserve">13.0179128646851</t>
@@ -2321,43 +2321,43 @@
     <t xml:space="preserve">13.303918838501</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3777265548706</t>
+    <t xml:space="preserve">13.3777275085449</t>
   </si>
   <si>
     <t xml:space="preserve">13.1009464263916</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1378498077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.922061920166</t>
+    <t xml:space="preserve">13.1378507614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9220628738403</t>
   </si>
   <si>
     <t xml:space="preserve">13.7006387710571</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4756231307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4202671051025</t>
+    <t xml:space="preserve">14.475622177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4202661514282</t>
   </si>
   <si>
     <t xml:space="preserve">14.5771102905273</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8298015594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7928972244263</t>
+    <t xml:space="preserve">13.8298025131226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7928981781006</t>
   </si>
   <si>
     <t xml:space="preserve">13.6914119720459</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5125284194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1803913116455</t>
+    <t xml:space="preserve">14.5125274658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1803903579712</t>
   </si>
   <si>
     <t xml:space="preserve">11.0988998413086</t>
@@ -2366,10 +2366,10 @@
     <t xml:space="preserve">10.7575378417969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1486206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2132034301758</t>
+    <t xml:space="preserve">10.1486196517944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2132015228271</t>
   </si>
   <si>
     <t xml:space="preserve">10.4069480895996</t>
@@ -2381,28 +2381,28 @@
     <t xml:space="preserve">10.5914688110352</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8590240478516</t>
+    <t xml:space="preserve">10.8590250015259</t>
   </si>
   <si>
     <t xml:space="preserve">10.9236068725586</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4807558059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6837301254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5361127853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2962369918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3700456619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0471353530884</t>
+    <t xml:space="preserve">10.4807567596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6837291717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5361137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.296236038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.370044708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0471343994141</t>
   </si>
   <si>
     <t xml:space="preserve">10.1762981414795</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">9.9087438583374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65964126586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53047657012939</t>
+    <t xml:space="preserve">9.65964221954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53047752380371</t>
   </si>
   <si>
     <t xml:space="preserve">10.0932645797729</t>
@@ -2426,22 +2426,22 @@
     <t xml:space="preserve">10.5730171203613</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4254016876221</t>
+    <t xml:space="preserve">10.4254007339478</t>
   </si>
   <si>
     <t xml:space="preserve">10.5176610946655</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3054618835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4438533782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6652793884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286827087402</t>
+    <t xml:space="preserve">10.3054628372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4438524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6652774810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0286817550659</t>
   </si>
   <si>
     <t xml:space="preserve">9.96410083770752</t>
@@ -2453,22 +2453,22 @@
     <t xml:space="preserve">10.120943069458</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50280094146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29059982299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5766077041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21218013763428</t>
+    <t xml:space="preserve">9.50279903411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29060077667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57660675048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21217823028564</t>
   </si>
   <si>
     <t xml:space="preserve">9.40131282806396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43821620941162</t>
+    <t xml:space="preserve">9.43821716308594</t>
   </si>
   <si>
     <t xml:space="preserve">9.47512149810791</t>
@@ -2483,43 +2483,43 @@
     <t xml:space="preserve">8.9861421585083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88004398345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53970241546631</t>
+    <t xml:space="preserve">8.88004302978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53970336914062</t>
   </si>
   <si>
     <t xml:space="preserve">9.24447059631348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28137493133545</t>
+    <t xml:space="preserve">9.28137588500977</t>
   </si>
   <si>
     <t xml:space="preserve">9.11530685424805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88106632232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97332763671875</t>
+    <t xml:space="preserve">9.88106536865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97332668304443</t>
   </si>
   <si>
     <t xml:space="preserve">9.99177742004395</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2408800125122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4346284866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0840396881104</t>
+    <t xml:space="preserve">10.2408819198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.434627532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.084038734436</t>
   </si>
   <si>
     <t xml:space="preserve">10.1024904251099</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61351108551025</t>
+    <t xml:space="preserve">9.61351203918457</t>
   </si>
   <si>
     <t xml:space="preserve">9.66886806488037</t>
@@ -2537,13 +2537,13 @@
     <t xml:space="preserve">9.26292324066162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39208793640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65041542053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31827926635742</t>
+    <t xml:space="preserve">9.39208698272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65041637420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31827831268311</t>
   </si>
   <si>
     <t xml:space="preserve">9.71499729156494</t>
@@ -2558,16 +2558,16 @@
     <t xml:space="preserve">9.98255252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75190162658691</t>
+    <t xml:space="preserve">9.7519006729126</t>
   </si>
   <si>
     <t xml:space="preserve">9.49357318878174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2777853012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0655851364136</t>
+    <t xml:space="preserve">10.2777843475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0655860900879</t>
   </si>
   <si>
     <t xml:space="preserve">10.5822439193726</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">10.7298603057861</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2870111465454</t>
+    <t xml:space="preserve">10.2870092391968</t>
   </si>
   <si>
     <t xml:space="preserve">10.5084362030029</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">11.431037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6340084075928</t>
+    <t xml:space="preserve">11.6340093612671</t>
   </si>
   <si>
     <t xml:space="preserve">12.2337007522583</t>
@@ -2600,31 +2600,31 @@
     <t xml:space="preserve">12.1322145462036</t>
   </si>
   <si>
-    <t xml:space="preserve">12.086085319519</t>
+    <t xml:space="preserve">12.0860843658447</t>
   </si>
   <si>
     <t xml:space="preserve">12.1414403915405</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1875705718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9661464691162</t>
+    <t xml:space="preserve">12.1875715255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9661474227905</t>
   </si>
   <si>
     <t xml:space="preserve">11.9569206237793</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7539472579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8277568817139</t>
+    <t xml:space="preserve">11.7539482116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8277559280396</t>
   </si>
   <si>
     <t xml:space="preserve">11.7354965209961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0676336288452</t>
+    <t xml:space="preserve">12.0676317214966</t>
   </si>
   <si>
     <t xml:space="preserve">12.4551248550415</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">13.2485628128052</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0824947357178</t>
+    <t xml:space="preserve">13.0824956893921</t>
   </si>
   <si>
     <t xml:space="preserve">13.5991516113281</t>
@@ -2651,7 +2651,7 @@
     <t xml:space="preserve">13.7559938430786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7098636627197</t>
+    <t xml:space="preserve">13.7098627090454</t>
   </si>
   <si>
     <t xml:space="preserve">13.7744464874268</t>
@@ -2663,10 +2663,10 @@
     <t xml:space="preserve">13.7190895080566</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7283163070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0143222808838</t>
+    <t xml:space="preserve">13.7283153533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0143213272095</t>
   </si>
   <si>
     <t xml:space="preserve">14.1342611312866</t>
@@ -2675,13 +2675,13 @@
     <t xml:space="preserve">14.1250352859497</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9497404098511</t>
+    <t xml:space="preserve">13.9497394561768</t>
   </si>
   <si>
     <t xml:space="preserve">13.6637344360352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6821851730347</t>
+    <t xml:space="preserve">13.6821870803833</t>
   </si>
   <si>
     <t xml:space="preserve">14.4571714401245</t>
@@ -2693,34 +2693,34 @@
     <t xml:space="preserve">13.8482542037964</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0512275695801</t>
+    <t xml:space="preserve">14.0512266159058</t>
   </si>
   <si>
     <t xml:space="preserve">14.0327739715576</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9312896728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6473274230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7303600311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0865859985352</t>
+    <t xml:space="preserve">13.9312887191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6473255157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7303619384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0865879058838</t>
   </si>
   <si>
     <t xml:space="preserve">16.7913551330566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.865161895752</t>
+    <t xml:space="preserve">16.8651638031006</t>
   </si>
   <si>
     <t xml:space="preserve">16.7452220916748</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8190326690674</t>
+    <t xml:space="preserve">16.8190307617188</t>
   </si>
   <si>
     <t xml:space="preserve">16.1086292266846</t>
@@ -2729,67 +2729,67 @@
     <t xml:space="preserve">15.997917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9333333969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4720335006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.678596496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3187808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8446636199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2967405319214</t>
+    <t xml:space="preserve">15.9333343505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4720344543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6785945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3187818527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8446645736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2967395782471</t>
   </si>
   <si>
     <t xml:space="preserve">15.204478263855</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7247257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8538904190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1491222381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2506084442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9830551147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1583480834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0753145217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1065835952759</t>
+    <t xml:space="preserve">14.7247266769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8538913726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1491231918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2506093978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9830541610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1583490371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0753154754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1065826416016</t>
   </si>
   <si>
     <t xml:space="preserve">12.6027421951294</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0399541854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9753713607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5878791809082</t>
+    <t xml:space="preserve">12.0399560928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9753723144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5878801345825</t>
   </si>
   <si>
     <t xml:space="preserve">11.3018732070923</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6006956100464</t>
+    <t xml:space="preserve">10.6006946563721</t>
   </si>
   <si>
     <t xml:space="preserve">10.1301679611206</t>
@@ -2798,28 +2798,28 @@
     <t xml:space="preserve">9.30905246734619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0635404586792</t>
+    <t xml:space="preserve">8.06353950500488</t>
   </si>
   <si>
     <t xml:space="preserve">7.9758939743042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89285945892334</t>
+    <t xml:space="preserve">7.89285898208618</t>
   </si>
   <si>
     <t xml:space="preserve">6.5504732131958</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93796634674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90567588806152</t>
+    <t xml:space="preserve">6.93796586990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90567541122437</t>
   </si>
   <si>
     <t xml:space="preserve">6.98409605026245</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91028833389282</t>
+    <t xml:space="preserve">6.91028738021851</t>
   </si>
   <si>
     <t xml:space="preserve">7.01177406311035</t>
@@ -2834,10 +2834,10 @@
     <t xml:space="preserve">8.85697841644287</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33673191070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01382064819336</t>
+    <t xml:space="preserve">9.33673095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01382160186768</t>
   </si>
   <si>
     <t xml:space="preserve">8.39567756652832</t>
@@ -2846,31 +2846,31 @@
     <t xml:space="preserve">8.40029048919678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34954738616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25728702545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.118896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74985504150391</t>
+    <t xml:space="preserve">8.34954643249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25728607177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11889553070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74985551834106</t>
   </si>
   <si>
     <t xml:space="preserve">7.92976331710815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78675937652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10967063903809</t>
+    <t xml:space="preserve">7.78675889968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10966968536377</t>
   </si>
   <si>
     <t xml:space="preserve">7.842116355896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42694520950317</t>
+    <t xml:space="preserve">7.42694568634033</t>
   </si>
   <si>
     <t xml:space="preserve">7.28855514526367</t>
@@ -2879,43 +2879,43 @@
     <t xml:space="preserve">7.26087713241577</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32545900344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33468437194824</t>
+    <t xml:space="preserve">7.32545948028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33468532562256</t>
   </si>
   <si>
     <t xml:space="preserve">7.1132607460022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5561089515686</t>
+    <t xml:space="preserve">7.55610942840576</t>
   </si>
   <si>
     <t xml:space="preserve">7.77753400802612</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93437719345093</t>
+    <t xml:space="preserve">7.93437623977661</t>
   </si>
   <si>
     <t xml:space="preserve">7.60223913192749</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33929824829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51920509338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30700635910034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14555168151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10403394699097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15939044952393</t>
+    <t xml:space="preserve">7.3392972946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51920557022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3070068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1455512046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10403490066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15939092636108</t>
   </si>
   <si>
     <t xml:space="preserve">7.06713056564331</t>
@@ -2924,13 +2924,13 @@
     <t xml:space="preserve">6.92874002456665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56533527374268</t>
+    <t xml:space="preserve">7.56533479690552</t>
   </si>
   <si>
     <t xml:space="preserve">7.54227018356323</t>
   </si>
   <si>
-    <t xml:space="preserve">7.445396900177</t>
+    <t xml:space="preserve">7.44539737701416</t>
   </si>
   <si>
     <t xml:space="preserve">7.27010250091553</t>
@@ -2942,13 +2942,13 @@
     <t xml:space="preserve">8.46948623657227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66784381866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90310668945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54329299926758</t>
+    <t xml:space="preserve">8.66784477233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90310764312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54329395294189</t>
   </si>
   <si>
     <t xml:space="preserve">8.69091033935547</t>
@@ -2957,22 +2957,22 @@
     <t xml:space="preserve">8.8754301071167</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32750511169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0066394805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4863939285278</t>
+    <t xml:space="preserve">9.32750415802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0066404342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4863929748535</t>
   </si>
   <si>
     <t xml:space="preserve">11.4956197738647</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2557430267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9420566558838</t>
+    <t xml:space="preserve">11.2557420730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9420576095581</t>
   </si>
   <si>
     <t xml:space="preserve">9.82570934295654</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">9.74267673492432</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4623050689697</t>
+    <t xml:space="preserve">10.462306022644</t>
   </si>
   <si>
     <t xml:space="preserve">10.1947507858276</t>
@@ -2993,52 +2993,52 @@
     <t xml:space="preserve">9.89029216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3792715072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3608179092407</t>
+    <t xml:space="preserve">10.3792724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.360818862915</t>
   </si>
   <si>
     <t xml:space="preserve">10.2224283218384</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6745042800903</t>
+    <t xml:space="preserve">10.674503326416</t>
   </si>
   <si>
     <t xml:space="preserve">10.5453395843506</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7667636871338</t>
+    <t xml:space="preserve">10.7667646408081</t>
   </si>
   <si>
     <t xml:space="preserve">12.021502494812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4402627944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5417509078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6155586242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8093032836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8185300827026</t>
+    <t xml:space="preserve">11.4402637481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5417490005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6155576705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8093042373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.818531036377</t>
   </si>
   <si>
     <t xml:space="preserve">11.7078170776367</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6616888046265</t>
+    <t xml:space="preserve">11.6616878509521</t>
   </si>
   <si>
     <t xml:space="preserve">11.5694274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3480024337769</t>
+    <t xml:space="preserve">11.3480033874512</t>
   </si>
   <si>
     <t xml:space="preserve">11.2741947174072</t>
@@ -3050,22 +3050,22 @@
     <t xml:space="preserve">10.8128938674927</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0030517578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3167362213135</t>
+    <t xml:space="preserve">12.0030508041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3167352676392</t>
   </si>
   <si>
     <t xml:space="preserve">12.8241662979126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7042293548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0548162460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3961791992188</t>
+    <t xml:space="preserve">12.7042284011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0548152923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3961801528931</t>
   </si>
   <si>
     <t xml:space="preserve">13.2854671478271</t>
@@ -3077,22 +3077,22 @@
     <t xml:space="preserve">13.1286239624023</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2301120758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0086870193481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1932077407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5437955856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3500509262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5714740753174</t>
+    <t xml:space="preserve">13.2301111221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0086879730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1932067871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5437965393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3500499725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5714731216431</t>
   </si>
   <si>
     <t xml:space="preserve">13.3685007095337</t>
@@ -3104,37 +3104,37 @@
     <t xml:space="preserve">13.4976654052734</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1101732254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1655292510986</t>
+    <t xml:space="preserve">13.1101722717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1655282974243</t>
   </si>
   <si>
     <t xml:space="preserve">13.2670154571533</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2762403488159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0455894470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1747550964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3315963745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3869524002075</t>
+    <t xml:space="preserve">13.2762413024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0455904006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1747541427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.331597328186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3869543075562</t>
   </si>
   <si>
     <t xml:space="preserve">12.5104808807373</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3813171386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6304187774658</t>
+    <t xml:space="preserve">12.3813161849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6304197311401</t>
   </si>
   <si>
     <t xml:space="preserve">12.335186958313</t>
@@ -3146,19 +3146,19 @@
     <t xml:space="preserve">13.5068912506104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4330835342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4515342712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2690591812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5735187530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8318481445312</t>
+    <t xml:space="preserve">13.4330825805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4515352249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2690601348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5735177993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8318471908569</t>
   </si>
   <si>
     <t xml:space="preserve">16.1455326080322</t>
@@ -3167,10 +3167,10 @@
     <t xml:space="preserve">15.3613204956055</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4628086090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7616310119629</t>
+    <t xml:space="preserve">15.4628067016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7616300582886</t>
   </si>
   <si>
     <t xml:space="preserve">14.5217542648315</t>
@@ -3179,37 +3179,37 @@
     <t xml:space="preserve">14.5955619812012</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7154998779297</t>
+    <t xml:space="preserve">14.7154989242554</t>
   </si>
   <si>
     <t xml:space="preserve">14.3556861877441</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9128351211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6545085906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5033016204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4110412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.650918006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1860265731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6750059127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4166774749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1029939651489</t>
+    <t xml:space="preserve">13.9128360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6545076370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5033025741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4110403060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6509189605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1860275268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6750049591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4166765213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1029930114746</t>
   </si>
   <si>
     <t xml:space="preserve">14.9184722900391</t>
@@ -3218,28 +3218,28 @@
     <t xml:space="preserve">15.3889989852905</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7764940261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.582745552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1547584533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8133955001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8410739898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9241075515747</t>
+    <t xml:space="preserve">15.7764921188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5827465057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1547565460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8133974075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8410749435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.924108505249</t>
   </si>
   <si>
     <t xml:space="preserve">16.1178550720215</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8502998352051</t>
+    <t xml:space="preserve">15.8503007888794</t>
   </si>
   <si>
     <t xml:space="preserve">15.8779783248901</t>
@@ -3248,10 +3248,10 @@
     <t xml:space="preserve">15.3520946502686</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6381034851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4351291656494</t>
+    <t xml:space="preserve">15.6381015777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4351282119751</t>
   </si>
   <si>
     <t xml:space="preserve">15.5919713973999</t>
@@ -3260,13 +3260,13 @@
     <t xml:space="preserve">15.9517879486084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.099401473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0717239379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5145740509033</t>
+    <t xml:space="preserve">16.0994052886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0717258453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5145721435547</t>
   </si>
   <si>
     <t xml:space="preserve">17.7877635955811</t>
@@ -3281,13 +3281,13 @@
     <t xml:space="preserve">17.1142654418945</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2618827819824</t>
+    <t xml:space="preserve">17.2618808746338</t>
   </si>
   <si>
     <t xml:space="preserve">17.5386619567871</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4464015960693</t>
+    <t xml:space="preserve">17.446403503418</t>
   </si>
   <si>
     <t xml:space="preserve">17.5663394927979</t>
@@ -3299,10 +3299,10 @@
     <t xml:space="preserve">17.621696472168</t>
   </si>
   <si>
-    <t xml:space="preserve">17.547887802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.036865234375</t>
+    <t xml:space="preserve">17.5478858947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0368671417236</t>
   </si>
   <si>
     <t xml:space="preserve">18.415132522583</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">18.7657222747803</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6698703765869</t>
+    <t xml:space="preserve">19.6698722839355</t>
   </si>
   <si>
     <t xml:space="preserve">19.9835548400879</t>
@@ -3323,13 +3323,13 @@
     <t xml:space="preserve">19.4484481811523</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7288150787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.245475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1901168823242</t>
+    <t xml:space="preserve">18.728816986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2454738616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1901187896729</t>
   </si>
   <si>
     <t xml:space="preserve">19.3377361297607</t>
@@ -3341,10 +3341,10 @@
     <t xml:space="preserve">18.5443000793457</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5627498626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2029361724854</t>
+    <t xml:space="preserve">18.5627517700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2029342651367</t>
   </si>
   <si>
     <t xml:space="preserve">18.4704895019531</t>
@@ -3362,25 +3362,25 @@
     <t xml:space="preserve">19.9651050567627</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6109237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9430618286133</t>
+    <t xml:space="preserve">20.6109256744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9430637359619</t>
   </si>
   <si>
     <t xml:space="preserve">21.2567481994629</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2198448181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3121013641357</t>
+    <t xml:space="preserve">21.2198429107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.312105178833</t>
   </si>
   <si>
     <t xml:space="preserve">21.1829376220703</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7513637542725</t>
+    <t xml:space="preserve">22.7513618469238</t>
   </si>
   <si>
     <t xml:space="preserve">22.7698154449463</t>
@@ -3395,16 +3395,16 @@
     <t xml:space="preserve">22.4745826721191</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7180480957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5371189117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6293773651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7216358184814</t>
+    <t xml:space="preserve">21.7180500030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5371170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6293792724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7216377258301</t>
   </si>
   <si>
     <t xml:space="preserve">20.1865291595459</t>
@@ -3416,34 +3416,34 @@
     <t xml:space="preserve">20.6847343444824</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2013912200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4633083343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8728446960449</t>
+    <t xml:space="preserve">21.2013893127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4633102416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8728466033936</t>
   </si>
   <si>
     <t xml:space="preserve">20.6478290557861</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8508033752441</t>
+    <t xml:space="preserve">20.8508014678955</t>
   </si>
   <si>
     <t xml:space="preserve">21.0906791687012</t>
   </si>
   <si>
-    <t xml:space="preserve">21.109130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2234325408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9466552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1311702728271</t>
+    <t xml:space="preserve">21.1091289520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2234344482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9466533660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1311721801758</t>
   </si>
   <si>
     <t xml:space="preserve">20.112720489502</t>
@@ -3455,7 +3455,7 @@
     <t xml:space="preserve">19.8543930053711</t>
   </si>
   <si>
-    <t xml:space="preserve">20.795446395874</t>
+    <t xml:space="preserve">20.7954483032227</t>
   </si>
   <si>
     <t xml:space="preserve">20.3156929016113</t>
@@ -3470,37 +3470,37 @@
     <t xml:space="preserve">22.5483894348145</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0686378479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.216251373291</t>
+    <t xml:space="preserve">22.0686359405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2162532806396</t>
   </si>
   <si>
     <t xml:space="preserve">22.1424465179443</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0132789611816</t>
+    <t xml:space="preserve">22.0132808685303</t>
   </si>
   <si>
     <t xml:space="preserve">22.2531585693359</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0317325592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1942119598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7846775054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.729320526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3935947418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8953895568848</t>
+    <t xml:space="preserve">22.0317306518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1942100524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7846794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7293186187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3935928344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8953876495361</t>
   </si>
   <si>
     <t xml:space="preserve">23.0465927124023</t>
@@ -3509,58 +3509,58 @@
     <t xml:space="preserve">22.9174308776855</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3049240112305</t>
+    <t xml:space="preserve">23.3049221038818</t>
   </si>
   <si>
     <t xml:space="preserve">23.3971843719482</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5817031860352</t>
+    <t xml:space="preserve">23.5817012786865</t>
   </si>
   <si>
     <t xml:space="preserve">23.1388549804688</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5852928161621</t>
+    <t xml:space="preserve">22.5852947235107</t>
   </si>
   <si>
     <t xml:space="preserve">22.8067169189453</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3454151153564</t>
+    <t xml:space="preserve">22.3454170227051</t>
   </si>
   <si>
     <t xml:space="preserve">23.4894428253174</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7477703094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7662220001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2311172485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7144565582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6370601654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0763206481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7554531097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4786758422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.976879119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1614017486572</t>
+    <t xml:space="preserve">23.7477722167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7662258148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2311153411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7144603729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6370620727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0763187408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7554550170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4786739349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9768772125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.16139793396</t>
   </si>
   <si>
     <t xml:space="preserve">27.3828239440918</t>
@@ -3569,13 +3569,13 @@
     <t xml:space="preserve">27.4935340881348</t>
   </si>
   <si>
-    <t xml:space="preserve">28.157808303833</t>
+    <t xml:space="preserve">28.1578102111816</t>
   </si>
   <si>
     <t xml:space="preserve">28.0470962524414</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2721118927002</t>
+    <t xml:space="preserve">27.2721099853516</t>
   </si>
   <si>
     <t xml:space="preserve">27.5673427581787</t>
@@ -3584,10 +3584,10 @@
     <t xml:space="preserve">27.4012775421143</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1060409545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9030685424805</t>
+    <t xml:space="preserve">27.1060447692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9030704498291</t>
   </si>
   <si>
     <t xml:space="preserve">26.4971256256104</t>
@@ -3596,22 +3596,22 @@
     <t xml:space="preserve">25.9251117706299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7221393585205</t>
+    <t xml:space="preserve">25.7221412658691</t>
   </si>
   <si>
     <t xml:space="preserve">26.6447410583496</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4602241516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3864154815674</t>
+    <t xml:space="preserve">26.4602222442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3864135742188</t>
   </si>
   <si>
     <t xml:space="preserve">25.9989223480225</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5007133483887</t>
+    <t xml:space="preserve">25.5007152557373</t>
   </si>
   <si>
     <t xml:space="preserve">25.9066619873047</t>
@@ -3620,16 +3620,16 @@
     <t xml:space="preserve">26.2572479248047</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1280860900879</t>
+    <t xml:space="preserve">26.1280841827393</t>
   </si>
   <si>
     <t xml:space="preserve">25.9620151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6631927490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3310585021973</t>
+    <t xml:space="preserve">26.6631946563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3310565948486</t>
   </si>
   <si>
     <t xml:space="preserve">26.5155773162842</t>
@@ -3641,13 +3641,13 @@
     <t xml:space="preserve">26.7370014190674</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7185497283936</t>
+    <t xml:space="preserve">26.7185478210449</t>
   </si>
   <si>
     <t xml:space="preserve">26.8292636871338</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4417667388916</t>
+    <t xml:space="preserve">26.4417686462402</t>
   </si>
   <si>
     <t xml:space="preserve">26.5340309143066</t>
@@ -3674,7 +3674,7 @@
     <t xml:space="preserve">30.4643135070801</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9625186920166</t>
+    <t xml:space="preserve">30.9625225067139</t>
   </si>
   <si>
     <t xml:space="preserve">29.5970706939697</t>
@@ -3686,13 +3686,13 @@
     <t xml:space="preserve">26.8846168518066</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3459167480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6227035522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7923583984375</t>
+    <t xml:space="preserve">27.3459205627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6227016448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7923603057861</t>
   </si>
   <si>
     <t xml:space="preserve">26.9399757385254</t>
@@ -3701,31 +3701,31 @@
     <t xml:space="preserve">27.1798496246338</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8994808197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5857944488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2352066040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2167549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3643703460693</t>
+    <t xml:space="preserve">27.8994789123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5857963562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2352085113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2167568206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3643741607666</t>
   </si>
   <si>
     <t xml:space="preserve">26.6262912750244</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2536582946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7703170776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3090171813965</t>
+    <t xml:space="preserve">27.2536602020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7703151702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3090152740479</t>
   </si>
   <si>
     <t xml:space="preserve">27.9548377990723</t>
@@ -3734,10 +3734,10 @@
     <t xml:space="preserve">28.674467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0286445617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8072185516357</t>
+    <t xml:space="preserve">28.0286426544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8072204589844</t>
   </si>
   <si>
     <t xml:space="preserve">28.3423290252686</t>
@@ -3752,25 +3752,25 @@
     <t xml:space="preserve">27.050687789917</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7518653869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8256702423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9732894897461</t>
+    <t xml:space="preserve">27.7518634796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8256721496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9732875823975</t>
   </si>
   <si>
     <t xml:space="preserve">28.3054256439209</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2869720458984</t>
+    <t xml:space="preserve">28.2869739532471</t>
   </si>
   <si>
     <t xml:space="preserve">28.0840015411377</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7887706756592</t>
+    <t xml:space="preserve">27.7887668609619</t>
   </si>
   <si>
     <t xml:space="preserve">26.294153213501</t>
@@ -3779,19 +3779,19 @@
     <t xml:space="preserve">26.9953308105469</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2203464508057</t>
+    <t xml:space="preserve">26.220344543457</t>
   </si>
   <si>
     <t xml:space="preserve">25.5191669464111</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6150188446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0983600616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9656085968018</t>
+    <t xml:space="preserve">24.6150169372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0983619689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9656066894531</t>
   </si>
   <si>
     <t xml:space="preserve">24.356689453125</t>
@@ -3800,28 +3800,28 @@
     <t xml:space="preserve">23.7108688354492</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3418273925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2680168151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0614566802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2090702056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7441825866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.633472442627</t>
+    <t xml:space="preserve">23.3418254852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2680187225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0614585876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2090740203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7441806793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6334705352783</t>
   </si>
   <si>
     <t xml:space="preserve">25.2423877716064</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0947723388672</t>
+    <t xml:space="preserve">25.0947704315186</t>
   </si>
   <si>
     <t xml:space="preserve">24.910249710083</t>
@@ -3839,13 +3839,13 @@
     <t xml:space="preserve">24.670373916626</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5376205444336</t>
+    <t xml:space="preserve">25.537618637085</t>
   </si>
   <si>
     <t xml:space="preserve">24.8733463287354</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9287014007568</t>
+    <t xml:space="preserve">24.9287033081055</t>
   </si>
   <si>
     <t xml:space="preserve">24.8364429473877</t>
@@ -3860,19 +3860,19 @@
     <t xml:space="preserve">23.8769340515137</t>
   </si>
   <si>
-    <t xml:space="preserve">23.526346206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1573066711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8656635284424</t>
+    <t xml:space="preserve">23.5263481140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1573085784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.865665435791</t>
   </si>
   <si>
     <t xml:space="preserve">21.8287620544434</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8841133117676</t>
+    <t xml:space="preserve">21.8841152191162</t>
   </si>
   <si>
     <t xml:space="preserve">21.0353221893311</t>
@@ -3881,13 +3881,13 @@
     <t xml:space="preserve">20.7031860351562</t>
   </si>
   <si>
-    <t xml:space="preserve">21.736499786377</t>
+    <t xml:space="preserve">21.7364978790283</t>
   </si>
   <si>
     <t xml:space="preserve">21.4597206115723</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5335273742676</t>
+    <t xml:space="preserve">21.5335292816162</t>
   </si>
   <si>
     <t xml:space="preserve">22.6591014862061</t>
@@ -3902,13 +3902,13 @@
     <t xml:space="preserve">20.9799671173096</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9948291778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5299377441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5114860534668</t>
+    <t xml:space="preserve">21.9948272705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.529935836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5114841461182</t>
   </si>
   <si>
     <t xml:space="preserve">22.6775531768799</t>
@@ -3926,10 +3926,10 @@
     <t xml:space="preserve">22.3085136413574</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3859100341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3674602508545</t>
+    <t xml:space="preserve">21.3859119415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3674583435059</t>
   </si>
   <si>
     <t xml:space="preserve">21.8103084564209</t>
@@ -3938,16 +3938,16 @@
     <t xml:space="preserve">19.928201675415</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0758190155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8877067565918</t>
+    <t xml:space="preserve">20.0758171081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8877048492432</t>
   </si>
   <si>
     <t xml:space="preserve">20.4448566436768</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2787895202637</t>
+    <t xml:space="preserve">20.278787612915</t>
   </si>
   <si>
     <t xml:space="preserve">19.8174877166748</t>
@@ -3962,10 +3962,10 @@
     <t xml:space="preserve">20.5002136230469</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7585430145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3710479736328</t>
+    <t xml:space="preserve">20.758544921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3710498809814</t>
   </si>
   <si>
     <t xml:space="preserve">20.0204601287842</t>
@@ -3974,7 +3974,7 @@
     <t xml:space="preserve">18.9871463775635</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5073928833008</t>
+    <t xml:space="preserve">18.5073947906494</t>
   </si>
   <si>
     <t xml:space="preserve">17.6770515441895</t>
@@ -4001,10 +4001,10 @@
     <t xml:space="preserve">16.2839221954346</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3705463409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.23779296875</t>
+    <t xml:space="preserve">15.3705472946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2377910614014</t>
   </si>
   <si>
     <t xml:space="preserve">13.4699878692627</t>
@@ -4013,28 +4013,28 @@
     <t xml:space="preserve">14.2172946929932</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0604524612427</t>
+    <t xml:space="preserve">14.060453414917</t>
   </si>
   <si>
     <t xml:space="preserve">14.337233543396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6878223419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8169860839844</t>
+    <t xml:space="preserve">14.6878213882446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8169851303101</t>
   </si>
   <si>
     <t xml:space="preserve">14.2634248733521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2541980743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6601438522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8226203918457</t>
+    <t xml:space="preserve">14.2541990280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6601448059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.82262134552</t>
   </si>
   <si>
     <t xml:space="preserve">15.6565532684326</t>
@@ -4046,7 +4046,7 @@
     <t xml:space="preserve">13.99587059021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8205766677856</t>
+    <t xml:space="preserve">13.820574760437</t>
   </si>
   <si>
     <t xml:space="preserve">14.3649110794067</t>
@@ -4055,19 +4055,19 @@
     <t xml:space="preserve">13.8667058944702</t>
   </si>
   <si>
-    <t xml:space="preserve">13.617603302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.811351776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8057126998901</t>
+    <t xml:space="preserve">13.6176042556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8113508224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8057146072388</t>
   </si>
   <si>
     <t xml:space="preserve">12.713454246521</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3592748641968</t>
+    <t xml:space="preserve">13.3592739105225</t>
   </si>
   <si>
     <t xml:space="preserve">14.9461507797241</t>
@@ -4076,19 +4076,19 @@
     <t xml:space="preserve">15.0476369857788</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3059663772583</t>
+    <t xml:space="preserve">15.305965423584</t>
   </si>
   <si>
     <t xml:space="preserve">15.3428688049316</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0384101867676</t>
+    <t xml:space="preserve">15.0384111404419</t>
   </si>
   <si>
     <t xml:space="preserve">15.2341136932373</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7736358642578</t>
+    <t xml:space="preserve">14.7736368179321</t>
   </si>
   <si>
     <t xml:space="preserve">14.9367218017578</t>
@@ -4100,25 +4100,25 @@
     <t xml:space="preserve">15.4739437103271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9823875427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5410985946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7137765884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7809314727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0303554534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8576755523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6466236114502</t>
+    <t xml:space="preserve">15.9823884963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5410995483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7137775421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.780930519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0303535461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8576765060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6466245651245</t>
   </si>
   <si>
     <t xml:space="preserve">15.3204526901245</t>
@@ -4130,28 +4130,28 @@
     <t xml:space="preserve">13.612850189209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5456972122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8430891036987</t>
+    <t xml:space="preserve">13.5456981658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.843090057373</t>
   </si>
   <si>
     <t xml:space="preserve">12.9509143829346</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1427793502808</t>
+    <t xml:space="preserve">13.1427803039551</t>
   </si>
   <si>
     <t xml:space="preserve">13.0180673599243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0660343170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7590503692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4040985107422</t>
+    <t xml:space="preserve">13.0660352706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7590494155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4040994644165</t>
   </si>
   <si>
     <t xml:space="preserve">12.8070163726807</t>
@@ -4163,7 +4163,7 @@
     <t xml:space="preserve">12.8453893661499</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5959634780884</t>
+    <t xml:space="preserve">12.5959644317627</t>
   </si>
   <si>
     <t xml:space="preserve">12.1258945465088</t>
@@ -4172,19 +4172,19 @@
     <t xml:space="preserve">11.8093156814575</t>
   </si>
   <si>
-    <t xml:space="preserve">11.780535697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5502977371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9724006652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6247444152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0468482971191</t>
+    <t xml:space="preserve">11.7805366516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5502986907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9724016189575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6247434616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0468473434448</t>
   </si>
   <si>
     <t xml:space="preserve">12.7974224090576</t>
@@ -4193,25 +4193,25 @@
     <t xml:space="preserve">12.7206764221191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6823034286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2026395797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8933544158936</t>
+    <t xml:space="preserve">12.6823043823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2026405334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8933553695679</t>
   </si>
   <si>
     <t xml:space="preserve">13.1715602874756</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1044073104858</t>
+    <t xml:space="preserve">13.1044082641602</t>
   </si>
   <si>
     <t xml:space="preserve">13.0948133468628</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4712514877319</t>
+    <t xml:space="preserve">12.4712505340576</t>
   </si>
   <si>
     <t xml:space="preserve">12.4328784942627</t>
@@ -4223,25 +4223,25 @@
     <t xml:space="preserve">13.3058652877808</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0372552871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3154592514038</t>
+    <t xml:space="preserve">13.0372543334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3154602050781</t>
   </si>
   <si>
     <t xml:space="preserve">12.480845451355</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6055583953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1738595962524</t>
+    <t xml:space="preserve">12.6055574417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1738586425781</t>
   </si>
   <si>
     <t xml:space="preserve">12.5096244812012</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2793865203857</t>
+    <t xml:space="preserve">12.2793855667114</t>
   </si>
   <si>
     <t xml:space="preserve">12.3945055007935</t>
@@ -4256,16 +4256,16 @@
     <t xml:space="preserve">12.0107755661011</t>
   </si>
   <si>
-    <t xml:space="preserve">12.154673576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2218255996704</t>
+    <t xml:space="preserve">12.1546726226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2218265533447</t>
   </si>
   <si>
     <t xml:space="preserve">12.3081665039062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1162996292114</t>
+    <t xml:space="preserve">12.1163005828857</t>
   </si>
   <si>
     <t xml:space="preserve">12.1834535598755</t>
@@ -4280,10 +4280,10 @@
     <t xml:space="preserve">11.4927368164062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4639577865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3296518325806</t>
+    <t xml:space="preserve">11.4639587402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3296527862549</t>
   </si>
   <si>
     <t xml:space="preserve">11.6654167175293</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">12.1354866027832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7421627044678</t>
+    <t xml:space="preserve">11.7421636581421</t>
   </si>
   <si>
     <t xml:space="preserve">11.7709426879883</t>
@@ -4310,55 +4310,55 @@
     <t xml:space="preserve">11.3680257797241</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2720937728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9363279342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9459209442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8499898910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7540559768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9555149078369</t>
+    <t xml:space="preserve">11.2720928192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9363269805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9459218978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8499889373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.754056930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9555139541626</t>
   </si>
   <si>
     <t xml:space="preserve">11.1090068817139</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4159917831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6558227539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5694847106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5790777206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5311117172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7613496780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8764696121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0491485595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9628086090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9413223266602</t>
+    <t xml:space="preserve">11.4159908294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6558237075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5694856643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5790767669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5311126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7613506317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8764686584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.049147605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9628076553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9413213729858</t>
   </si>
   <si>
     <t xml:space="preserve">13.2003402709961</t>
@@ -4370,37 +4370,37 @@
     <t xml:space="preserve">11.3104658126831</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9267349243164</t>
+    <t xml:space="preserve">10.9267358779907</t>
   </si>
   <si>
     <t xml:space="preserve">10.8212089538574</t>
   </si>
   <si>
-    <t xml:space="preserve">11.895655632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7229766845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7398633956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2889795303345</t>
+    <t xml:space="preserve">11.8956546783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7229776382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7398624420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2889804840088</t>
   </si>
   <si>
     <t xml:space="preserve">12.0875205993652</t>
   </si>
   <si>
-    <t xml:space="preserve">12.260199546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1930475234985</t>
+    <t xml:space="preserve">12.2601985931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1930456161499</t>
   </si>
   <si>
     <t xml:space="preserve">12.3369455337524</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136905670166</t>
+    <t xml:space="preserve">12.4136915206909</t>
   </si>
   <si>
     <t xml:space="preserve">12.5671844482422</t>
@@ -4409,7 +4409,7 @@
     <t xml:space="preserve">12.2314195632935</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7686433792114</t>
+    <t xml:space="preserve">12.7686443328857</t>
   </si>
   <si>
     <t xml:space="preserve">12.7014894485474</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">12.4616584777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.991587638855</t>
+    <t xml:space="preserve">11.9915885925293</t>
   </si>
   <si>
     <t xml:space="preserve">11.9244346618652</t>
@@ -4439,7 +4439,7 @@
     <t xml:space="preserve">12.0587406158447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5000305175781</t>
+    <t xml:space="preserve">12.5000314712524</t>
   </si>
   <si>
     <t xml:space="preserve">12.8262023925781</t>
@@ -4457,7 +4457,7 @@
     <t xml:space="preserve">13.8718690872192</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7663440704346</t>
+    <t xml:space="preserve">13.7663431167603</t>
   </si>
   <si>
     <t xml:space="preserve">14.0733280181885</t>
@@ -4466,34 +4466,34 @@
     <t xml:space="preserve">14.3803119659424</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2172260284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2364139556885</t>
+    <t xml:space="preserve">14.2172269821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2364130020142</t>
   </si>
   <si>
     <t xml:space="preserve">13.7855291366577</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8143100738525</t>
+    <t xml:space="preserve">13.8143091201782</t>
   </si>
   <si>
     <t xml:space="preserve">14.1404800415039</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1980400085449</t>
+    <t xml:space="preserve">14.1980409622192</t>
   </si>
   <si>
     <t xml:space="preserve">14.4090929031372</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3707189559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2939729690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1692600250244</t>
+    <t xml:space="preserve">14.3707180023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2939720153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1692609786987</t>
   </si>
   <si>
     <t xml:space="preserve">14.7160768508911</t>
@@ -4511,7 +4511,7 @@
     <t xml:space="preserve">14.3131589889526</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4474649429321</t>
+    <t xml:space="preserve">14.4474658966064</t>
   </si>
   <si>
     <t xml:space="preserve">14.3323450088501</t>
@@ -4523,34 +4523,34 @@
     <t xml:space="preserve">14.5721769332886</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5242118835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6009578704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3611268997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0879154205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8288955688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2509994506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3373394012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7210693359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3277473449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2030334472656</t>
+    <t xml:space="preserve">14.5242109298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6009588241577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3611259460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0879135131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.828896522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2510013580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3373413085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7210712432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3277454376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2030353546143</t>
   </si>
   <si>
     <t xml:space="preserve">16.2318134307861</t>
@@ -4562,7 +4562,7 @@
     <t xml:space="preserve">16.0207633972168</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3588256835938</t>
+    <t xml:space="preserve">15.3588266372681</t>
   </si>
   <si>
     <t xml:space="preserve">16.0783214569092</t>
@@ -4574,13 +4574,13 @@
     <t xml:space="preserve">14.6105499267578</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6393308639526</t>
+    <t xml:space="preserve">14.639331817627</t>
   </si>
   <si>
     <t xml:space="preserve">14.1308870315552</t>
   </si>
   <si>
-    <t xml:space="preserve">13.948616027832</t>
+    <t xml:space="preserve">13.9486150741577</t>
   </si>
   <si>
     <t xml:space="preserve">14.044548034668</t>
@@ -4601,7 +4601,7 @@
     <t xml:space="preserve">13.6416311264038</t>
   </si>
   <si>
-    <t xml:space="preserve">13.555290222168</t>
+    <t xml:space="preserve">13.5552911758423</t>
   </si>
   <si>
     <t xml:space="preserve">13.459358215332</t>
@@ -4616,25 +4616,25 @@
     <t xml:space="preserve">13.4305782318115</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3538331985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2195272445679</t>
+    <t xml:space="preserve">13.353832244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2195262908936</t>
   </si>
   <si>
     <t xml:space="preserve">13.1619672775269</t>
   </si>
   <si>
-    <t xml:space="preserve">13.190746307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9701023101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2578983306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0276613235474</t>
+    <t xml:space="preserve">13.1907472610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9701013565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2579002380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.027660369873</t>
   </si>
   <si>
     <t xml:space="preserve">13.1811532974243</t>
@@ -6015,6 +6015,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.67000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30999994277954</t>
   </si>
 </sst>
 </file>
@@ -71795,7 +71798,7 @@
     </row>
     <row r="2518">
       <c r="A2518" s="1" t="n">
-        <v>45985.6912847222</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2518" t="n">
         <v>215110</v>
@@ -71816,6 +71819,32 @@
         <v>1984</v>
       </c>
       <c r="H2518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>45986.6909837963</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>159791</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>6.34999990463257</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>6.01000022888184</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>6.30999994277954</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>2001</v>
+      </c>
+      <c r="H2519" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2002" uniqueCount="2002">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="2003">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">BSS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9788007736206</t>
+    <t xml:space="preserve">12.9787998199463</t>
   </si>
   <si>
     <t xml:space="preserve">12.7479515075684</t>
@@ -53,10 +53,10 @@
     <t xml:space="preserve">12.397403717041</t>
   </si>
   <si>
-    <t xml:space="preserve">12.243504524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2606058120728</t>
+    <t xml:space="preserve">12.2435064315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2606048583984</t>
   </si>
   <si>
     <t xml:space="preserve">12.1409063339233</t>
@@ -65,19 +65,19 @@
     <t xml:space="preserve">11.4825611114502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8584156036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79822444915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3539695739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84952354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4736700057983</t>
+    <t xml:space="preserve">10.858416557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79822540283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3539705276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84952449798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.473669052124</t>
   </si>
   <si>
     <t xml:space="preserve">10.2941207885742</t>
@@ -86,58 +86,58 @@
     <t xml:space="preserve">10.7814655303955</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8156652450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7301683425903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5762691497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6361169815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.191520690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4565696716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4907712936401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0205240249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03728103637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97743034362793</t>
+    <t xml:space="preserve">10.8156661987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7301664352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.576268196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6361179351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1915225982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4565687179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4907693862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0205230712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03728008270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97743129730225</t>
   </si>
   <si>
     <t xml:space="preserve">9.40492820739746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14842891693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43057632446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90082263946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66142654418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4394702911377</t>
+    <t xml:space="preserve">9.14842987060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43057823181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90082359313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66142559051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4394693374634</t>
   </si>
   <si>
     <t xml:space="preserve">10.345419883728</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2000722885132</t>
+    <t xml:space="preserve">10.2000713348389</t>
   </si>
   <si>
     <t xml:space="preserve">11.0037651062012</t>
@@ -149,10 +149,10 @@
     <t xml:space="preserve">10.2257213592529</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1829710006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0379638671875</t>
+    <t xml:space="preserve">10.1829700469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0379648208618</t>
   </si>
   <si>
     <t xml:space="preserve">10.9097156524658</t>
@@ -173,25 +173,25 @@
     <t xml:space="preserve">11.9699087142944</t>
   </si>
   <si>
-    <t xml:space="preserve">11.627911567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.371413230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3799638748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8416576385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9186067581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7989091873169</t>
+    <t xml:space="preserve">11.6279096603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3714113235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3799619674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6621103286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8416595458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.918607711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7989101409912</t>
   </si>
   <si>
     <t xml:space="preserve">12.046856880188</t>
@@ -200,34 +200,34 @@
     <t xml:space="preserve">12.1922054290771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2007551193237</t>
+    <t xml:space="preserve">12.2007579803467</t>
   </si>
   <si>
     <t xml:space="preserve">12.3375549316406</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1323566436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1665554046631</t>
+    <t xml:space="preserve">12.1323547363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1665563583374</t>
   </si>
   <si>
     <t xml:space="preserve">12.2178564071655</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9015092849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5680599212646</t>
+    <t xml:space="preserve">11.9015083312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.568060874939</t>
   </si>
   <si>
     <t xml:space="preserve">11.2859134674072</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7390594482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.884407043457</t>
+    <t xml:space="preserve">11.7390575408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8844079971313</t>
   </si>
   <si>
     <t xml:space="preserve">11.8160076141357</t>
@@ -236,13 +236,13 @@
     <t xml:space="preserve">11.7048597335815</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6022615432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6364603042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4740133285522</t>
+    <t xml:space="preserve">11.6022596359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6364593505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4740123748779</t>
   </si>
   <si>
     <t xml:space="preserve">11.1918640136719</t>
@@ -251,22 +251,22 @@
     <t xml:space="preserve">11.1063642501831</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1149139404297</t>
+    <t xml:space="preserve">11.1149129867554</t>
   </si>
   <si>
     <t xml:space="preserve">11.3201112747192</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457622528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1576642990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0550661087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9866666793823</t>
+    <t xml:space="preserve">11.3457632064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1576633453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.055064201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.986665725708</t>
   </si>
   <si>
     <t xml:space="preserve">11.1405630111694</t>
@@ -278,28 +278,28 @@
     <t xml:space="preserve">10.954140663147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4346132278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3553628921509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2232789993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2673063278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92388820648193</t>
+    <t xml:space="preserve">10.4346113204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3553619384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.22327709198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2673053741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92388916015625</t>
   </si>
   <si>
     <t xml:space="preserve">10.3201398849487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0031366348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.302529335022</t>
+    <t xml:space="preserve">10.003137588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3025283813477</t>
   </si>
   <si>
     <t xml:space="preserve">10.2496957778931</t>
@@ -308,79 +308,79 @@
     <t xml:space="preserve">10.6107234954834</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4120302200317</t>
+    <t xml:space="preserve">11.4120311737061</t>
   </si>
   <si>
     <t xml:space="preserve">11.1302528381348</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9189195632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2359199523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2799482345581</t>
+    <t xml:space="preserve">10.9189186096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2359189987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2799472808838</t>
   </si>
   <si>
     <t xml:space="preserve">11.0069742202759</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8308629989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8396701812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9277238845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9101123809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8132514953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5138626098633</t>
+    <t xml:space="preserve">10.8308620452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8396692276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9277248382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9101133346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8132524490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.513861656189</t>
   </si>
   <si>
     <t xml:space="preserve">10.0647783279419</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99433326721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9503059387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68613910675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0383596420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4962501525879</t>
+    <t xml:space="preserve">9.9943323135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95030498504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68613815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0383605957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4962520599365</t>
   </si>
   <si>
     <t xml:space="preserve">10.3465557098389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4522218704224</t>
+    <t xml:space="preserve">10.4522228240967</t>
   </si>
   <si>
     <t xml:space="preserve">10.5843076705933</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87985992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12258052825928</t>
+    <t xml:space="preserve">9.87986087799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12257957458496</t>
   </si>
   <si>
     <t xml:space="preserve">9.67733192443848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57166481018066</t>
+    <t xml:space="preserve">9.57166576385498</t>
   </si>
   <si>
     <t xml:space="preserve">9.93269348144531</t>
@@ -389,34 +389,34 @@
     <t xml:space="preserve">10.1880550384521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98552703857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1842212677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14019203186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.721360206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0823879241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.381778717041</t>
+    <t xml:space="preserve">9.98552799224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18421936035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14019107818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72135925292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.08238697052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3817777633667</t>
   </si>
   <si>
     <t xml:space="preserve">10.2849178314209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1352224349976</t>
+    <t xml:space="preserve">10.1352233886719</t>
   </si>
   <si>
     <t xml:space="preserve">10.2144727706909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1528339385986</t>
+    <t xml:space="preserve">10.15283203125</t>
   </si>
   <si>
     <t xml:space="preserve">10.6987781524658</t>
@@ -428,73 +428,73 @@
     <t xml:space="preserve">11.0157804489136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0333909988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9893636703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8748912811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0950298309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.253532409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3151712417603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7251958847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0510034561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9013071060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1654748916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0598087310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2183074951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1214475631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1830854415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2623376846313</t>
+    <t xml:space="preserve">11.0333919525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9893627166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8748903274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0950307846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2535305023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3151702880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7251949310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0510015487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9013080596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1654758453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0598077774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2183094024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1214466094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1830863952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2623357772827</t>
   </si>
   <si>
     <t xml:space="preserve">11.5265045166016</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7466421127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.773060798645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.685004234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7994775772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6497812271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6673927307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4472541809082</t>
+    <t xml:space="preserve">11.7466440200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7730598449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6850051879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7994756698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6497821807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6673917770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4472522735596</t>
   </si>
   <si>
     <t xml:space="preserve">11.3239755630493</t>
@@ -503,10 +503,10 @@
     <t xml:space="preserve">11.3680028915405</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1390571594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.693808555603</t>
+    <t xml:space="preserve">11.1390581130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6938095092773</t>
   </si>
   <si>
     <t xml:space="preserve">11.614559173584</t>
@@ -515,19 +515,19 @@
     <t xml:space="preserve">11.8258934020996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0372266769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0548391342163</t>
+    <t xml:space="preserve">12.0372285842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.054838180542</t>
   </si>
   <si>
     <t xml:space="preserve">12.0636434555054</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5039224624634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5303392410278</t>
+    <t xml:space="preserve">12.5039234161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5303401947021</t>
   </si>
   <si>
     <t xml:space="preserve">12.4070615768433</t>
@@ -539,34 +539,34 @@
     <t xml:space="preserve">12.6007843017578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9177875518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8121175765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.856146812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0322570800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4108982086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5782032012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6838703155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4285097122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3707046508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2210102081299</t>
+    <t xml:space="preserve">12.9177846908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8121185302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8561477661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0322580337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4108972549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5782041549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6838712692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4285087585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3707056045532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2210111618042</t>
   </si>
   <si>
     <t xml:space="preserve">14.2562341690063</t>
@@ -578,25 +578,25 @@
     <t xml:space="preserve">14.1241512298584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0713167190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9216232299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7807321548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6046190261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7631206512451</t>
+    <t xml:space="preserve">14.0713148117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9216213226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7807312011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6046209335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7631216049194</t>
   </si>
   <si>
     <t xml:space="preserve">13.8335657119751</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7278985977173</t>
+    <t xml:space="preserve">13.727897644043</t>
   </si>
   <si>
     <t xml:space="preserve">13.1995639801025</t>
@@ -605,19 +605,19 @@
     <t xml:space="preserve">13.375675201416</t>
   </si>
   <si>
-    <t xml:space="preserve">13.155535697937</t>
+    <t xml:space="preserve">13.1555347442627</t>
   </si>
   <si>
     <t xml:space="preserve">13.6486492156982</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5605926513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7367038726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8775930404663</t>
+    <t xml:space="preserve">13.5605916976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.736704826355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.877592086792</t>
   </si>
   <si>
     <t xml:space="preserve">14.176983833313</t>
@@ -626,58 +626,58 @@
     <t xml:space="preserve">14.0977334976196</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7845697402954</t>
+    <t xml:space="preserve">14.7845687866211</t>
   </si>
   <si>
     <t xml:space="preserve">15.3040971755981</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2776803970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4890146255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.497820854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3657360076904</t>
+    <t xml:space="preserve">15.2776823043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4890165328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4978199005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3657369613647</t>
   </si>
   <si>
     <t xml:space="preserve">15.4449872970581</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3393201828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5330419540405</t>
+    <t xml:space="preserve">15.339319229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5330429077148</t>
   </si>
   <si>
     <t xml:space="preserve">15.6651277542114</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5418491363525</t>
+    <t xml:space="preserve">15.5418481826782</t>
   </si>
   <si>
     <t xml:space="preserve">15.2424592971802</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8060188293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1934585571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3695755004883</t>
+    <t xml:space="preserve">15.8060150146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1934604644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3695735931396</t>
   </si>
   <si>
     <t xml:space="preserve">16.4664344787598</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5104598999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.03879737854</t>
+    <t xml:space="preserve">16.510461807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0387954711914</t>
   </si>
   <si>
     <t xml:space="preserve">16.8891010284424</t>
@@ -689,43 +689,43 @@
     <t xml:space="preserve">16.7746276855469</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5544891357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.237491607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5897121429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6513481140137</t>
+    <t xml:space="preserve">16.5544872283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2374897003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.589714050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6513519287109</t>
   </si>
   <si>
     <t xml:space="preserve">16.5721015930176</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9947681427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7041854858398</t>
+    <t xml:space="preserve">16.9947700500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7041835784912</t>
   </si>
   <si>
     <t xml:space="preserve">16.880298614502</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8538780212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.012378692627</t>
+    <t xml:space="preserve">16.8538818359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0123767852783</t>
   </si>
   <si>
     <t xml:space="preserve">17.2941589355469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1268501281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5368785858154</t>
+    <t xml:space="preserve">17.1268520355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5368804931641</t>
   </si>
   <si>
     <t xml:space="preserve">17.0828227996826</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">16.8626842498779</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2061023712158</t>
+    <t xml:space="preserve">17.2061061859131</t>
   </si>
   <si>
     <t xml:space="preserve">17.3469924926758</t>
@@ -743,22 +743,22 @@
     <t xml:space="preserve">17.6551876068115</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5407161712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5054912567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7168292999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4526596069336</t>
+    <t xml:space="preserve">17.540714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5054931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7168312072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.452657699585</t>
   </si>
   <si>
     <t xml:space="preserve">17.5583267211914</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7432441711426</t>
+    <t xml:space="preserve">17.7432460784912</t>
   </si>
   <si>
     <t xml:space="preserve">17.8401050567627</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">16.7482128143311</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7658252716064</t>
+    <t xml:space="preserve">16.7658271789551</t>
   </si>
   <si>
     <t xml:space="preserve">16.9507427215576</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">17.2765483856201</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6865749359131</t>
+    <t xml:space="preserve">16.6865730285645</t>
   </si>
   <si>
     <t xml:space="preserve">17.1092395782471</t>
@@ -791,43 +791,43 @@
     <t xml:space="preserve">16.8186588287354</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2325172424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2853546142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3910179138184</t>
+    <t xml:space="preserve">17.2325191497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2853507995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3910217285156</t>
   </si>
   <si>
     <t xml:space="preserve">17.250129699707</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4350471496582</t>
+    <t xml:space="preserve">17.4350452423096</t>
   </si>
   <si>
     <t xml:space="preserve">17.3734092712402</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6463851928711</t>
+    <t xml:space="preserve">17.6463813781738</t>
   </si>
   <si>
     <t xml:space="preserve">17.9457702636719</t>
   </si>
   <si>
-    <t xml:space="preserve">19.372278213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9358329772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3849143981934</t>
+    <t xml:space="preserve">19.3722763061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9358348846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3849201202393</t>
   </si>
   <si>
     <t xml:space="preserve">20.5962524414062</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3408851623535</t>
+    <t xml:space="preserve">20.3408889770508</t>
   </si>
   <si>
     <t xml:space="preserve">20.8340015411377</t>
@@ -836,31 +836,31 @@
     <t xml:space="preserve">21.0453357696533</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5824756622314</t>
+    <t xml:space="preserve">21.5824775695801</t>
   </si>
   <si>
     <t xml:space="preserve">21.0893630981445</t>
   </si>
   <si>
-    <t xml:space="preserve">21.327112197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6529197692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7497825622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.917085647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8114204406738</t>
+    <t xml:space="preserve">21.3271141052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6529216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7497806549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9170875549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8114242553711</t>
   </si>
   <si>
     <t xml:space="preserve">22.0139484405518</t>
   </si>
   <si>
-    <t xml:space="preserve">22.286922454834</t>
+    <t xml:space="preserve">22.2869205474854</t>
   </si>
   <si>
     <t xml:space="preserve">22.2605056762695</t>
@@ -869,16 +869,16 @@
     <t xml:space="preserve">22.348560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3221435546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1900596618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6303424835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4366149902344</t>
+    <t xml:space="preserve">22.3221454620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1900615692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6303405761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4366188049316</t>
   </si>
   <si>
     <t xml:space="preserve">22.4806461334229</t>
@@ -887,55 +887,55 @@
     <t xml:space="preserve">22.6655616760254</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6215343475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6743698120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8945083618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0970363616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8328704833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3749771118164</t>
+    <t xml:space="preserve">22.6215362548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6743679046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8945045471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0970344543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8328685760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.374979019165</t>
   </si>
   <si>
     <t xml:space="preserve">23.1938972473145</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3876171112061</t>
+    <t xml:space="preserve">23.3876190185547</t>
   </si>
   <si>
     <t xml:space="preserve">23.5108985900879</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9159564971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2417602539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7084579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6556262969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.919792175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0870971679688</t>
+    <t xml:space="preserve">23.9159526824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2417621612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7084560394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6556243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9197902679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0870952606201</t>
   </si>
   <si>
     <t xml:space="preserve">24.9638175964355</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8933753967285</t>
+    <t xml:space="preserve">24.8933734893799</t>
   </si>
   <si>
     <t xml:space="preserve">26.4255447387695</t>
@@ -950,43 +950,43 @@
     <t xml:space="preserve">27.6287326812744</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1545715332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6732959747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6804046630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3666687011719</t>
+    <t xml:space="preserve">28.1545696258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6732940673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6804065704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3666706085205</t>
   </si>
   <si>
     <t xml:space="preserve">27.8069839477539</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4665069580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0190830230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4914417266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7677326202393</t>
+    <t xml:space="preserve">28.4665088653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0190811157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4914398193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7677345275879</t>
   </si>
   <si>
     <t xml:space="preserve">29.8746814727783</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3024768829346</t>
+    <t xml:space="preserve">30.3024787902832</t>
   </si>
   <si>
     <t xml:space="preserve">30.7748413085938</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2400951385498</t>
+    <t xml:space="preserve">30.2400970458984</t>
   </si>
   <si>
     <t xml:space="preserve">30.6678924560547</t>
@@ -995,10 +995,10 @@
     <t xml:space="preserve">30.8283176422119</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8996143341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.015474319458</t>
+    <t xml:space="preserve">30.8996162414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0154781341553</t>
   </si>
   <si>
     <t xml:space="preserve">30.9976558685303</t>
@@ -1007,13 +1007,13 @@
     <t xml:space="preserve">30.935266494751</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6500682830811</t>
+    <t xml:space="preserve">30.6500663757324</t>
   </si>
   <si>
     <t xml:space="preserve">30.748104095459</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6857204437256</t>
+    <t xml:space="preserve">30.685718536377</t>
   </si>
   <si>
     <t xml:space="preserve">29.3577556610107</t>
@@ -1025,10 +1025,10 @@
     <t xml:space="preserve">29.3131942749023</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2775421142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.168794631958</t>
+    <t xml:space="preserve">29.2775402069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1687927246094</t>
   </si>
   <si>
     <t xml:space="preserve">30.1331443786621</t>
@@ -1037,70 +1037,70 @@
     <t xml:space="preserve">29.999454498291</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9281597137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0529327392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4825325012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8122940063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.912130355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.126033782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7713317871094</t>
+    <t xml:space="preserve">29.9281558990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0529346466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4825305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8122978210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9121322631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1260318756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7713298797607</t>
   </si>
   <si>
     <t xml:space="preserve">27.9674072265625</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2544059753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6911182403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4861335754395</t>
+    <t xml:space="preserve">27.2544078826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6911201477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4861354827881</t>
   </si>
   <si>
     <t xml:space="preserve">27.5752582550049</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1189212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.350643157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7178573608398</t>
+    <t xml:space="preserve">28.1189155578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3506412506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7178592681885</t>
   </si>
   <si>
     <t xml:space="preserve">28.5734577178955</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6180210113525</t>
+    <t xml:space="preserve">28.6180229187012</t>
   </si>
   <si>
     <t xml:space="preserve">28.5199813842773</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7873554229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7855529785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.536003112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3310203552246</t>
+    <t xml:space="preserve">28.7873573303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7855567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5360069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3310222625732</t>
   </si>
   <si>
     <t xml:space="preserve">29.1705932617188</t>
@@ -1109,43 +1109,43 @@
     <t xml:space="preserve">29.2329807281494</t>
   </si>
   <si>
-    <t xml:space="preserve">29.143856048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3221073150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9656085968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7071437835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9923458099365</t>
+    <t xml:space="preserve">29.1438579559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3221092224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9656047821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7071418762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9923419952393</t>
   </si>
   <si>
     <t xml:space="preserve">28.9477806091309</t>
   </si>
   <si>
-    <t xml:space="preserve">29.607307434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8568572998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4023189544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4112300872803</t>
+    <t xml:space="preserve">29.6073055267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8568553924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4023208618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4112319946289</t>
   </si>
   <si>
     <t xml:space="preserve">28.814094543457</t>
   </si>
   <si>
-    <t xml:space="preserve">29.687520980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6162166595459</t>
+    <t xml:space="preserve">29.6875171661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6162185668945</t>
   </si>
   <si>
     <t xml:space="preserve">29.6786060333252</t>
@@ -1157,64 +1157,64 @@
     <t xml:space="preserve">30.1420574188232</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8390274047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.186616897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5181789398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1795101165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4379653930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3648662567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4629077911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4718170166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2935657501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0974941253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0618419647217</t>
+    <t xml:space="preserve">29.8390331268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1866149902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.518180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1795063018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.437967300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3648681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4629039764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4718208312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2935695648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0974922180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0618438720703</t>
   </si>
   <si>
     <t xml:space="preserve">30.23118019104</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0849761962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4967555999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8194065093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9958534240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7730369567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6928310394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1830177307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0760650634766</t>
+    <t xml:space="preserve">32.0849800109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4967517852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8194046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9958591461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7730464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6928291320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1830139160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0760726928711</t>
   </si>
   <si>
     <t xml:space="preserve">31.9512920379639</t>
@@ -1223,40 +1223,40 @@
     <t xml:space="preserve">32.3077926635742</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1990394592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3951148986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7587242126465</t>
+    <t xml:space="preserve">33.1990432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3951187133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7587280273438</t>
   </si>
   <si>
     <t xml:space="preserve">34.6963386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7319869995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5804786682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2239799499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4378776550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5448226928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4271697998047</t>
+    <t xml:space="preserve">34.7319946289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5804710388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2239761352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.437873840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5448303222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4271659851074</t>
   </si>
   <si>
     <t xml:space="preserve">35.2221794128418</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6606864929199</t>
+    <t xml:space="preserve">34.6606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">34.3754920959473</t>
@@ -1268,25 +1268,25 @@
     <t xml:space="preserve">33.8496551513672</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1437683105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7159690856934</t>
+    <t xml:space="preserve">34.1437644958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7159652709961</t>
   </si>
   <si>
     <t xml:space="preserve">34.0635528564453</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3130989074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1170234680176</t>
+    <t xml:space="preserve">34.3131065368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1170310974121</t>
   </si>
   <si>
     <t xml:space="preserve">34.420051574707</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7765502929688</t>
+    <t xml:space="preserve">34.7765579223633</t>
   </si>
   <si>
     <t xml:space="preserve">34.6161270141602</t>
@@ -1295,13 +1295,13 @@
     <t xml:space="preserve">34.3041954040527</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1081199645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8425369262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0902900695801</t>
+    <t xml:space="preserve">34.1081161499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8425407409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0902938842773</t>
   </si>
   <si>
     <t xml:space="preserve">35.106315612793</t>
@@ -1310,31 +1310,31 @@
     <t xml:space="preserve">36.2471084594727</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3005867004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1847305297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4966659545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4146537780762</t>
+    <t xml:space="preserve">36.3005905151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1847229003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4966621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4146499633789</t>
   </si>
   <si>
     <t xml:space="preserve">38.8584747314453</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9208641052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6178436279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5821876525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2702522277832</t>
+    <t xml:space="preserve">38.9208602905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6178359985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5821914672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2702445983887</t>
   </si>
   <si>
     <t xml:space="preserve">38.4306755065918</t>
@@ -1343,28 +1343,28 @@
     <t xml:space="preserve">39.214973449707</t>
   </si>
   <si>
-    <t xml:space="preserve">38.805004119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8068008422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3504600524902</t>
+    <t xml:space="preserve">38.8050003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8067970275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3504638671875</t>
   </si>
   <si>
     <t xml:space="preserve">38.0563545227051</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3682823181152</t>
+    <t xml:space="preserve">38.3682861328125</t>
   </si>
   <si>
     <t xml:space="preserve">38.3415489196777</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5197982788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5643615722656</t>
+    <t xml:space="preserve">38.5198059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5643653869629</t>
   </si>
   <si>
     <t xml:space="preserve">38.6089248657227</t>
@@ -1376,25 +1376,25 @@
     <t xml:space="preserve">38.7336959838867</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4377822875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0812835693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0545425415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3219223022461</t>
+    <t xml:space="preserve">39.4377937316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0812873840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0545501708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3219261169434</t>
   </si>
   <si>
     <t xml:space="preserve">38.5554466247559</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2880744934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3772010803223</t>
+    <t xml:space="preserve">38.2880783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3772048950195</t>
   </si>
   <si>
     <t xml:space="preserve">37.6998519897461</t>
@@ -1406,13 +1406,13 @@
     <t xml:space="preserve">37.6820259094238</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4663238525391</t>
+    <t xml:space="preserve">38.4663276672363</t>
   </si>
   <si>
     <t xml:space="preserve">41.9956703186035</t>
   </si>
   <si>
-    <t xml:space="preserve">42.655200958252</t>
+    <t xml:space="preserve">42.6551971435547</t>
   </si>
   <si>
     <t xml:space="preserve">42.8156242370605</t>
@@ -1421,73 +1421,73 @@
     <t xml:space="preserve">42.423469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">42.031322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0847969055176</t>
+    <t xml:space="preserve">42.0313186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0848007202148</t>
   </si>
   <si>
     <t xml:space="preserve">41.924373626709</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6213455200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7639503479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1382713317871</t>
+    <t xml:space="preserve">41.6213493347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7639465332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1382751464844</t>
   </si>
   <si>
     <t xml:space="preserve">41.6926498413086</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5322227478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7817726135254</t>
+    <t xml:space="preserve">41.5322189331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7817764282227</t>
   </si>
   <si>
     <t xml:space="preserve">41.3539733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8192253112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3557739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5874977111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8031959533691</t>
+    <t xml:space="preserve">40.819221496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3557777404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5875015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8031997680664</t>
   </si>
   <si>
     <t xml:space="preserve">39.1436729431152</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6784286499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7799758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4787483215332</t>
+    <t xml:space="preserve">39.6784248352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7799682617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4787521362305</t>
   </si>
   <si>
     <t xml:space="preserve">38.6802215576172</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5750732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2898750305176</t>
+    <t xml:space="preserve">37.5750770568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2898788452148</t>
   </si>
   <si>
     <t xml:space="preserve">39.589298248291</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1953468322754</t>
+    <t xml:space="preserve">40.1953506469727</t>
   </si>
   <si>
     <t xml:space="preserve">40.1062240600586</t>
@@ -1496,22 +1496,22 @@
     <t xml:space="preserve">40.5696716308594</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8013954162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9440002441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1400718688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9974784851074</t>
+    <t xml:space="preserve">40.801399230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9439964294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1400756835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9974708557129</t>
   </si>
   <si>
     <t xml:space="preserve">40.5161972045898</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9618263244629</t>
+    <t xml:space="preserve">40.9618225097656</t>
   </si>
   <si>
     <t xml:space="preserve">39.2506256103516</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">39.1793212890625</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2131767272949</t>
+    <t xml:space="preserve">40.2131729125977</t>
   </si>
   <si>
     <t xml:space="preserve">40.3914222717285</t>
@@ -1529,76 +1529,76 @@
     <t xml:space="preserve">41.3896217346191</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6017265319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.5446472167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9029502868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2309074401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.885124206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9635353088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.033031463623</t>
+    <t xml:space="preserve">42.6017189025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.5446434020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.902946472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2309036254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8851203918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9635314941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0330352783203</t>
   </si>
   <si>
     <t xml:space="preserve">47.3253440856934</t>
   </si>
   <si>
-    <t xml:space="preserve">45.943904876709</t>
+    <t xml:space="preserve">45.9439086914062</t>
   </si>
   <si>
     <t xml:space="preserve">45.5874099731445</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6961631774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0099029541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8494758605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9582176208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4609222412109</t>
+    <t xml:space="preserve">44.696159362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0098991394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8494682312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9582214355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4609260559082</t>
   </si>
   <si>
     <t xml:space="preserve">41.175724029541</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1579055786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0153007507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7675476074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1080207824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7479209899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7853736877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5518455505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7319030761719</t>
+    <t xml:space="preserve">41.1578941345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0152969360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7675514221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.108024597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7479248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7853698730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5518493652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7318992614746</t>
   </si>
   <si>
     <t xml:space="preserve">39.3041000366211</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">40.2488250732422</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9101448059082</t>
+    <t xml:space="preserve">39.9101486206055</t>
   </si>
   <si>
     <t xml:space="preserve">39.4288787841797</t>
@@ -1616,10 +1616,10 @@
     <t xml:space="preserve">39.0367240905762</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3878288269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0509567260742</t>
+    <t xml:space="preserve">42.3878211975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0509490966797</t>
   </si>
   <si>
     <t xml:space="preserve">41.9335746765137</t>
@@ -1628,40 +1628,40 @@
     <t xml:space="preserve">41.0149269104004</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7087097167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6366539001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5285758972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8440971374512</t>
+    <t xml:space="preserve">40.7087059020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6366577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5285797119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8441009521484</t>
   </si>
   <si>
     <t xml:space="preserve">37.7366142272949</t>
   </si>
   <si>
-    <t xml:space="preserve">37.484432220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3316230773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0521278381348</t>
+    <t xml:space="preserve">37.4844360351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.331615447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0521240234375</t>
   </si>
   <si>
     <t xml:space="preserve">36.4757232666016</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6018142700195</t>
+    <t xml:space="preserve">36.6018104553223</t>
   </si>
   <si>
     <t xml:space="preserve">36.007396697998</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6651496887207</t>
+    <t xml:space="preserve">35.6651458740234</t>
   </si>
   <si>
     <t xml:space="preserve">35.3589324951172</t>
@@ -1673,28 +1673,28 @@
     <t xml:space="preserve">33.4135589599609</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6657447814941</t>
+    <t xml:space="preserve">33.6657409667969</t>
   </si>
   <si>
     <t xml:space="preserve">33.881893157959</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4763107299805</t>
+    <t xml:space="preserve">34.4763145446777</t>
   </si>
   <si>
     <t xml:space="preserve">34.6924667358398</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1427803039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7284965515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5483665466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9899749755859</t>
+    <t xml:space="preserve">35.1427879333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7284927368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5483627319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9899673461914</t>
   </si>
   <si>
     <t xml:space="preserve">33.8278579711914</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">34.4402885437012</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1247673034668</t>
+    <t xml:space="preserve">35.1247711181641</t>
   </si>
   <si>
     <t xml:space="preserve">33.5036277770996</t>
@@ -1715,34 +1715,34 @@
     <t xml:space="preserve">32.3868408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4681911468506</t>
+    <t xml:space="preserve">31.4681930541992</t>
   </si>
   <si>
     <t xml:space="preserve">31.7744083404541</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5315322875977</t>
+    <t xml:space="preserve">30.5315341949463</t>
   </si>
   <si>
     <t xml:space="preserve">29.486795425415</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9371109008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2346172332764</t>
+    <t xml:space="preserve">29.9371166229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2346153259277</t>
   </si>
   <si>
     <t xml:space="preserve">30.1532669067383</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2166004180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4147434234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8296241760254</t>
+    <t xml:space="preserve">29.2166042327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4147415161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.829626083374</t>
   </si>
   <si>
     <t xml:space="preserve">29.1265411376953</t>
@@ -1751,76 +1751,76 @@
     <t xml:space="preserve">29.5408325195312</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6035804748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2520408630371</t>
+    <t xml:space="preserve">30.6035842895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2520427703857</t>
   </si>
   <si>
     <t xml:space="preserve">29.6489086151123</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9551239013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1172351837158</t>
+    <t xml:space="preserve">29.9551219940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1172389984131</t>
   </si>
   <si>
     <t xml:space="preserve">30.4054412841797</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6663341522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6483154296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.080623626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1079406738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3601150512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9818496704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7383804321289</t>
+    <t xml:space="preserve">31.6663360595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6483116149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0806198120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1079368591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3601131439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9818477630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7383861541748</t>
   </si>
   <si>
     <t xml:space="preserve">31.6122932434082</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8377494812012</t>
+    <t xml:space="preserve">30.8377475738525</t>
   </si>
   <si>
     <t xml:space="preserve">29.9190998077393</t>
   </si>
   <si>
-    <t xml:space="preserve">29.901086807251</t>
+    <t xml:space="preserve">29.9010906219482</t>
   </si>
   <si>
     <t xml:space="preserve">29.6669216156006</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0905132293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.730260848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0998153686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.595458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6407852172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2805328369141</t>
+    <t xml:space="preserve">29.0905151367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7302627563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.099817276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5954608917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6407871246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2805347442627</t>
   </si>
   <si>
     <t xml:space="preserve">26.0463676452637</t>
@@ -1829,13 +1829,13 @@
     <t xml:space="preserve">26.5146999359131</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2352046966553</t>
+    <t xml:space="preserve">27.2352066040039</t>
   </si>
   <si>
     <t xml:space="preserve">27.055082321167</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1091175079346</t>
+    <t xml:space="preserve">27.1091194152832</t>
   </si>
   <si>
     <t xml:space="preserve">27.0190544128418</t>
@@ -1844,64 +1844,64 @@
     <t xml:space="preserve">26.7488651275635</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4693737030029</t>
+    <t xml:space="preserve">27.4693717956543</t>
   </si>
   <si>
     <t xml:space="preserve">27.9196891784668</t>
   </si>
   <si>
-    <t xml:space="preserve">27.577449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9377021789551</t>
+    <t xml:space="preserve">27.5774478912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9377002716064</t>
   </si>
   <si>
     <t xml:space="preserve">27.8476390838623</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7936019897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0457763671875</t>
+    <t xml:space="preserve">27.7936000823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0457782745361</t>
   </si>
   <si>
     <t xml:space="preserve">28.0097541809082</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7755870819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6041736602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5501346588135</t>
+    <t xml:space="preserve">27.7755908966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6041698455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5501365661621</t>
   </si>
   <si>
     <t xml:space="preserve">29.1805801391602</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1625652313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6401977539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6762218475342</t>
+    <t xml:space="preserve">29.1625671386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6401958465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6762237548828</t>
   </si>
   <si>
     <t xml:space="preserve">27.6675109863281</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4513568878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5594348907471</t>
+    <t xml:space="preserve">27.451358795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5594387054443</t>
   </si>
   <si>
     <t xml:space="preserve">25.7581653594971</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7320327758789</t>
+    <t xml:space="preserve">22.7320308685303</t>
   </si>
   <si>
     <t xml:space="preserve">21.7413330078125</t>
@@ -1910,25 +1910,25 @@
     <t xml:space="preserve">21.7233200073242</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7860698699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4165153503418</t>
+    <t xml:space="preserve">22.7860679626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4165115356445</t>
   </si>
   <si>
     <t xml:space="preserve">23.7047157287598</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5606155395508</t>
+    <t xml:space="preserve">23.5606136322021</t>
   </si>
   <si>
     <t xml:space="preserve">23.236385345459</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4345264434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5158767700195</t>
+    <t xml:space="preserve">23.4345283508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5158786773682</t>
   </si>
   <si>
     <t xml:space="preserve">21.7053070068359</t>
@@ -1937,13 +1937,13 @@
     <t xml:space="preserve">20.8226871490479</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3630657196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2369766235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3450527191162</t>
+    <t xml:space="preserve">21.3630638122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2369747161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3450508117676</t>
   </si>
   <si>
     <t xml:space="preserve">21.5972290039062</t>
@@ -1958,13 +1958,13 @@
     <t xml:space="preserve">18.2828922271729</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5437831878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.877311706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3909683227539</t>
+    <t xml:space="preserve">19.5437812805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8773097991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3909702301025</t>
   </si>
   <si>
     <t xml:space="preserve">19.0033988952637</t>
@@ -1973,13 +1973,13 @@
     <t xml:space="preserve">18.003698348999</t>
   </si>
   <si>
-    <t xml:space="preserve">17.139087677002</t>
+    <t xml:space="preserve">17.1390857696533</t>
   </si>
   <si>
     <t xml:space="preserve">17.1120681762695</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2651767730713</t>
+    <t xml:space="preserve">17.2651748657227</t>
   </si>
   <si>
     <t xml:space="preserve">16.6617488861084</t>
@@ -1988,31 +1988,31 @@
     <t xml:space="preserve">16.2024269104004</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9502487182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.71608543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6800575256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6170129776001</t>
+    <t xml:space="preserve">15.950249671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.716082572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6800565719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.617015838623</t>
   </si>
   <si>
     <t xml:space="preserve">16.1573944091797</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6077117919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4005661010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4723205566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5533771514893</t>
+    <t xml:space="preserve">16.6077136993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4005680084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.472318649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5533809661865</t>
   </si>
   <si>
     <t xml:space="preserve">16.490629196167</t>
@@ -2030,43 +2030,43 @@
     <t xml:space="preserve">16.7968444824219</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0132942199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.905216217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2654705047607</t>
+    <t xml:space="preserve">16.0132923126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9052171707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2654685974121</t>
   </si>
   <si>
     <t xml:space="preserve">16.1934204101562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7250881195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.400860786438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0496120452881</t>
+    <t xml:space="preserve">15.7250890731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4008626937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0496139526367</t>
   </si>
   <si>
     <t xml:space="preserve">14.752402305603</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5899934768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1486825942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.463906288147</t>
+    <t xml:space="preserve">15.589994430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1486835479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4639024734497</t>
   </si>
   <si>
     <t xml:space="preserve">17.1661052703857</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7875442504883</t>
+    <t xml:space="preserve">17.7875461578369</t>
   </si>
   <si>
     <t xml:space="preserve">18.1568031311035</t>
@@ -2084,28 +2084,28 @@
     <t xml:space="preserve">18.0487289428711</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2288551330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0307159423828</t>
+    <t xml:space="preserve">18.2288570404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0307178497314</t>
   </si>
   <si>
     <t xml:space="preserve">17.9226379394531</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4543075561523</t>
+    <t xml:space="preserve">17.454309463501</t>
   </si>
   <si>
     <t xml:space="preserve">18.6791725158691</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8052635192871</t>
+    <t xml:space="preserve">18.8052616119385</t>
   </si>
   <si>
     <t xml:space="preserve">18.6251354217529</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3369312286377</t>
+    <t xml:space="preserve">18.3369331359863</t>
   </si>
   <si>
     <t xml:space="preserve">18.9493656158447</t>
@@ -2120,10 +2120,10 @@
     <t xml:space="preserve">18.354944229126</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4269943237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9856834411621</t>
+    <t xml:space="preserve">18.4269924163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9856815338135</t>
   </si>
   <si>
     <t xml:space="preserve">17.3552379608154</t>
@@ -2132,10 +2132,10 @@
     <t xml:space="preserve">17.7244987487793</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3009071350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6071224212646</t>
+    <t xml:space="preserve">18.3009052276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.607120513916</t>
   </si>
   <si>
     <t xml:space="preserve">19.3996829986572</t>
@@ -2144,16 +2144,16 @@
     <t xml:space="preserve">19.6698722839355</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2462768554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0661525726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9220485687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4176921844482</t>
+    <t xml:space="preserve">20.2462749481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0661506652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9220504760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4176940917969</t>
   </si>
   <si>
     <t xml:space="preserve">19.4537181854248</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">20.2823028564453</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7515182495117</t>
+    <t xml:space="preserve">17.7515163421631</t>
   </si>
   <si>
     <t xml:space="preserve">17.7425117492676</t>
@@ -2174,19 +2174,19 @@
     <t xml:space="preserve">17.5083465576172</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4182834625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8508815765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9859771728516</t>
+    <t xml:space="preserve">17.418285369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8508834838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9859790802002</t>
   </si>
   <si>
     <t xml:space="preserve">16.868896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0490245819092</t>
+    <t xml:space="preserve">17.0490226745605</t>
   </si>
   <si>
     <t xml:space="preserve">16.9409465789795</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">17.3462333679199</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2741832733154</t>
+    <t xml:space="preserve">17.2741813659668</t>
   </si>
   <si>
     <t xml:space="preserve">17.3822574615479</t>
@@ -2207,34 +2207,34 @@
     <t xml:space="preserve">18.1748180389404</t>
   </si>
   <si>
-    <t xml:space="preserve">17.976676940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6164226531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4272880554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1387901306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.913631439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6974792480469</t>
+    <t xml:space="preserve">17.9766750335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6164207458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4272899627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1387920379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9136333465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6974811553955</t>
   </si>
   <si>
     <t xml:space="preserve">18.1928291320801</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9496593475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2381553649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1300792694092</t>
+    <t xml:space="preserve">17.9496574401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2381572723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1300811767578</t>
   </si>
   <si>
     <t xml:space="preserve">17.6794662475586</t>
@@ -2258,16 +2258,16 @@
     <t xml:space="preserve">17.6074161529541</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5894069671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7695293426514</t>
+    <t xml:space="preserve">17.5894050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7695331573486</t>
   </si>
   <si>
     <t xml:space="preserve">18.6365585327148</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2434272766113</t>
+    <t xml:space="preserve">17.24342918396</t>
   </si>
   <si>
     <t xml:space="preserve">16.6621894836426</t>
@@ -2282,40 +2282,40 @@
     <t xml:space="preserve">16.1916618347168</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6842308044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6232395172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8021240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9405145645142</t>
+    <t xml:space="preserve">15.6842317581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6232404708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8021230697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9405136108398</t>
   </si>
   <si>
     <t xml:space="preserve">13.7836713790894</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3131456375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8943843841553</t>
+    <t xml:space="preserve">13.3131446838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8943853378296</t>
   </si>
   <si>
     <t xml:space="preserve">13.8390283584595</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4792127609253</t>
+    <t xml:space="preserve">13.4792137145996</t>
   </si>
   <si>
     <t xml:space="preserve">12.9533309936523</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0732679367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0179128646851</t>
+    <t xml:space="preserve">13.0732688903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0179119110107</t>
   </si>
   <si>
     <t xml:space="preserve">13.303918838501</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">13.3777275085449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1009473800659</t>
+    <t xml:space="preserve">13.1009464263916</t>
   </si>
   <si>
     <t xml:space="preserve">13.1378507614136</t>
@@ -2333,34 +2333,34 @@
     <t xml:space="preserve">13.9220628738403</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7006378173828</t>
+    <t xml:space="preserve">13.7006387710571</t>
   </si>
   <si>
     <t xml:space="preserve">14.4756231307983</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4202680587769</t>
+    <t xml:space="preserve">14.4202661514282</t>
   </si>
   <si>
     <t xml:space="preserve">14.5771102905273</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8298025131226</t>
+    <t xml:space="preserve">13.8298015594482</t>
   </si>
   <si>
     <t xml:space="preserve">13.7928981781006</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6914119720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5125274658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1803903579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0988988876343</t>
+    <t xml:space="preserve">13.6914129257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.512526512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1803913116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0988998413086</t>
   </si>
   <si>
     <t xml:space="preserve">10.7575378417969</t>
@@ -2369,7 +2369,7 @@
     <t xml:space="preserve">10.1486206054688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2132024765015</t>
+    <t xml:space="preserve">10.2132034301758</t>
   </si>
   <si>
     <t xml:space="preserve">10.4069490432739</t>
@@ -2396,22 +2396,22 @@
     <t xml:space="preserve">10.5361137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2962369918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.370044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0471343994141</t>
+    <t xml:space="preserve">10.296236038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3700437545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0471353530884</t>
   </si>
   <si>
     <t xml:space="preserve">10.1762981414795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9087438583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65964221954346</t>
+    <t xml:space="preserve">9.90874481201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65964126586914</t>
   </si>
   <si>
     <t xml:space="preserve">9.53047752380371</t>
@@ -2435,16 +2435,16 @@
     <t xml:space="preserve">10.3054628372192</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4438524246216</t>
+    <t xml:space="preserve">10.4438543319702</t>
   </si>
   <si>
     <t xml:space="preserve">10.6652784347534</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0286827087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9640998840332</t>
+    <t xml:space="preserve">10.0286836624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96409893035889</t>
   </si>
   <si>
     <t xml:space="preserve">10.056360244751</t>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">10.120943069458</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50279903411865</t>
+    <t xml:space="preserve">9.50279998779297</t>
   </si>
   <si>
     <t xml:space="preserve">9.29060077667236</t>
@@ -2468,28 +2468,28 @@
     <t xml:space="preserve">9.40131282806396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43821716308594</t>
+    <t xml:space="preserve">9.43821620941162</t>
   </si>
   <si>
     <t xml:space="preserve">9.47512149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20295429229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94001197814941</t>
+    <t xml:space="preserve">9.20295333862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94001293182373</t>
   </si>
   <si>
     <t xml:space="preserve">8.9861421585083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88004302978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53970336914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24447059631348</t>
+    <t xml:space="preserve">8.88004398345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53970432281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24447154998779</t>
   </si>
   <si>
     <t xml:space="preserve">9.28137588500977</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">9.11530685424805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88106536865234</t>
+    <t xml:space="preserve">9.88106632232666</t>
   </si>
   <si>
     <t xml:space="preserve">9.97332668304443</t>
@@ -2507,19 +2507,19 @@
     <t xml:space="preserve">9.99177837371826</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2408819198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.434627532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0840396881104</t>
+    <t xml:space="preserve">10.2408809661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4346284866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.084038734436</t>
   </si>
   <si>
     <t xml:space="preserve">10.1024904251099</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61351108551025</t>
+    <t xml:space="preserve">9.61351203918457</t>
   </si>
   <si>
     <t xml:space="preserve">9.66886615753174</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">9.2629222869873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39208698272705</t>
+    <t xml:space="preserve">9.39208793640137</t>
   </si>
   <si>
     <t xml:space="preserve">9.65041637420654</t>
@@ -2549,7 +2549,7 @@
     <t xml:space="preserve">9.71499729156494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81648349761963</t>
+    <t xml:space="preserve">9.81648445129395</t>
   </si>
   <si>
     <t xml:space="preserve">9.6873197555542</t>
@@ -2558,25 +2558,25 @@
     <t xml:space="preserve">9.98255252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7519006729126</t>
+    <t xml:space="preserve">9.75190258026123</t>
   </si>
   <si>
     <t xml:space="preserve">9.49357318878174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2777843475342</t>
+    <t xml:space="preserve">10.2777853012085</t>
   </si>
   <si>
     <t xml:space="preserve">10.0655860900879</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5822429656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7298593521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2870111465454</t>
+    <t xml:space="preserve">10.5822439193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7298603057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2870101928711</t>
   </si>
   <si>
     <t xml:space="preserve">10.5084362030029</t>
@@ -2585,16 +2585,16 @@
     <t xml:space="preserve">10.3515939712524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4310369491577</t>
+    <t xml:space="preserve">11.431037902832</t>
   </si>
   <si>
     <t xml:space="preserve">11.6340093612671</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2337017059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.993824005127</t>
+    <t xml:space="preserve">12.2337007522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9938230514526</t>
   </si>
   <si>
     <t xml:space="preserve">12.1322145462036</t>
@@ -2606,34 +2606,34 @@
     <t xml:space="preserve">12.1414403915405</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1875715255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9661464691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.956919670105</t>
+    <t xml:space="preserve">12.1875705718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9661474227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9569206237793</t>
   </si>
   <si>
     <t xml:space="preserve">11.7539482116699</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8277559280396</t>
+    <t xml:space="preserve">11.8277568817139</t>
   </si>
   <si>
     <t xml:space="preserve">11.7354965209961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0676317214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4551258087158</t>
+    <t xml:space="preserve">12.0676326751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4551248550415</t>
   </si>
   <si>
     <t xml:space="preserve">13.2577886581421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2485637664795</t>
+    <t xml:space="preserve">13.2485628128052</t>
   </si>
   <si>
     <t xml:space="preserve">13.0824947357178</t>
@@ -2645,52 +2645,52 @@
     <t xml:space="preserve">13.4054050445557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2024335861206</t>
+    <t xml:space="preserve">13.2024326324463</t>
   </si>
   <si>
     <t xml:space="preserve">13.7559938430786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7098636627197</t>
+    <t xml:space="preserve">13.7098627090454</t>
   </si>
   <si>
     <t xml:space="preserve">13.7744464874268</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3408222198486</t>
+    <t xml:space="preserve">13.3408231735229</t>
   </si>
   <si>
     <t xml:space="preserve">13.7190895080566</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7283163070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0143222808838</t>
+    <t xml:space="preserve">13.7283153533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0143213272095</t>
   </si>
   <si>
     <t xml:space="preserve">14.1342601776123</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1250352859497</t>
+    <t xml:space="preserve">14.1250343322754</t>
   </si>
   <si>
     <t xml:space="preserve">13.9497404098511</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6637353897095</t>
+    <t xml:space="preserve">13.6637344360352</t>
   </si>
   <si>
     <t xml:space="preserve">13.6821851730347</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4571704864502</t>
+    <t xml:space="preserve">14.4571723937988</t>
   </si>
   <si>
     <t xml:space="preserve">14.1158094406128</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8482532501221</t>
+    <t xml:space="preserve">13.8482542037964</t>
   </si>
   <si>
     <t xml:space="preserve">14.0512256622314</t>
@@ -2699,19 +2699,19 @@
     <t xml:space="preserve">14.0327739715576</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9312887191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6473274230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7303619384766</t>
+    <t xml:space="preserve">13.9312896728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6473264694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7303609848022</t>
   </si>
   <si>
     <t xml:space="preserve">17.0865859985352</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7913551330566</t>
+    <t xml:space="preserve">16.791353225708</t>
   </si>
   <si>
     <t xml:space="preserve">16.8651638031006</t>
@@ -2723,154 +2723,154 @@
     <t xml:space="preserve">16.8190307617188</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1086292266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.997917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9333362579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4720344543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6785955429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3187818527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8446645736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2967386245728</t>
+    <t xml:space="preserve">16.1086273193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9979190826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9333333969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4720325469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.678596496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3187808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8446636199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2967395782471</t>
   </si>
   <si>
     <t xml:space="preserve">15.2044792175293</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7247257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8538904190063</t>
+    <t xml:space="preserve">14.7247247695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8538913726807</t>
   </si>
   <si>
     <t xml:space="preserve">15.1491222381592</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2506103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9830532073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1583490371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0753154754639</t>
+    <t xml:space="preserve">15.2506084442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9830541610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1583480834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0753145217896</t>
   </si>
   <si>
     <t xml:space="preserve">14.1065826416016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6027421951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0399551391602</t>
+    <t xml:space="preserve">12.6027412414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0399541854858</t>
   </si>
   <si>
     <t xml:space="preserve">11.9753723144531</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5878801345825</t>
+    <t xml:space="preserve">11.5878791809082</t>
   </si>
   <si>
     <t xml:space="preserve">11.301872253418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6006956100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1301670074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30905246734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06353950500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9758939743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89285898208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55047369003296</t>
+    <t xml:space="preserve">10.6006946563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1301679611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30905342102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0635404586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97589349746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8928599357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5504732131958</t>
   </si>
   <si>
     <t xml:space="preserve">6.93796634674072</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90567588806152</t>
+    <t xml:space="preserve">6.90567541122437</t>
   </si>
   <si>
     <t xml:space="preserve">6.98409652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91028785705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01177453994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47307586669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05431461334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85697937011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33673095703125</t>
+    <t xml:space="preserve">6.91028738021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01177406311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47307538986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05431365966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85697746276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33673191070557</t>
   </si>
   <si>
     <t xml:space="preserve">9.01382160186768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39567756652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40028953552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34954738616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25728702545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.118896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74985551834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92976331710815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78675985336304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10967063903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84211540222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42694520950317</t>
+    <t xml:space="preserve">8.395676612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40029048919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34954643249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25728607177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11889743804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74985456466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.929762840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78675937652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1096715927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84211587905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42694568634033</t>
   </si>
   <si>
     <t xml:space="preserve">7.28855514526367</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">7.26087665557861</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32545948028564</t>
+    <t xml:space="preserve">7.32545852661133</t>
   </si>
   <si>
     <t xml:space="preserve">7.3346848487854</t>
@@ -2888,10 +2888,10 @@
     <t xml:space="preserve">7.1132607460022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55610942840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77753353118896</t>
+    <t xml:space="preserve">7.5561089515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77753448486328</t>
   </si>
   <si>
     <t xml:space="preserve">7.93437623977661</t>
@@ -2900,34 +2900,34 @@
     <t xml:space="preserve">7.60223960876465</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33929777145386</t>
+    <t xml:space="preserve">7.33929824829102</t>
   </si>
   <si>
     <t xml:space="preserve">7.51920509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3070068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1455512046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10403442382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15939092636108</t>
+    <t xml:space="preserve">7.30700635910034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14555168151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10403394699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15939044952393</t>
   </si>
   <si>
     <t xml:space="preserve">7.06713008880615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92874002456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56533432006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54227066040039</t>
+    <t xml:space="preserve">6.92874050140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56533527374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54227113723755</t>
   </si>
   <si>
     <t xml:space="preserve">7.445396900177</t>
@@ -2936,34 +2936,34 @@
     <t xml:space="preserve">7.27010250091553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72217750549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46948623657227</t>
+    <t xml:space="preserve">7.72217798233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46948528289795</t>
   </si>
   <si>
     <t xml:space="preserve">8.66784477233887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90310668945312</t>
+    <t xml:space="preserve">8.90310764312744</t>
   </si>
   <si>
     <t xml:space="preserve">8.54329299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69090938568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87543106079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32750415802002</t>
+    <t xml:space="preserve">8.69091033935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8754301071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32750511169434</t>
   </si>
   <si>
     <t xml:space="preserve">11.0066404342651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4863939285278</t>
+    <t xml:space="preserve">11.4863929748535</t>
   </si>
   <si>
     <t xml:space="preserve">11.4956188201904</t>
@@ -2975,19 +2975,19 @@
     <t xml:space="preserve">10.9420576095581</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82571029663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74267578125</t>
+    <t xml:space="preserve">9.82570934295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74267673492432</t>
   </si>
   <si>
     <t xml:space="preserve">10.4623050689697</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1947507858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0194549560547</t>
+    <t xml:space="preserve">10.1947498321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.019455909729</t>
   </si>
   <si>
     <t xml:space="preserve">9.89029216766357</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">10.360818862915</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2224292755127</t>
+    <t xml:space="preserve">10.2224283218384</t>
   </si>
   <si>
     <t xml:space="preserve">10.674503326416</t>
@@ -3008,10 +3008,10 @@
     <t xml:space="preserve">10.5453395843506</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7667646408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.021502494812</t>
+    <t xml:space="preserve">10.7667636871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0215015411377</t>
   </si>
   <si>
     <t xml:space="preserve">11.4402627944946</t>
@@ -3020,34 +3020,34 @@
     <t xml:space="preserve">11.5417499542236</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6155586242676</t>
+    <t xml:space="preserve">11.6155576705933</t>
   </si>
   <si>
     <t xml:space="preserve">11.8093032836914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.818531036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7078161239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6616868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5694274902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3480033874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2741956710815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1450300216675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8128938674927</t>
+    <t xml:space="preserve">11.8185300827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7078170776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6616888046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5694284439087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3480024337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2741947174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1450309753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.812894821167</t>
   </si>
   <si>
     <t xml:space="preserve">12.0030508041382</t>
@@ -3062,16 +3062,16 @@
     <t xml:space="preserve">12.7042284011841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0548162460327</t>
+    <t xml:space="preserve">13.054817199707</t>
   </si>
   <si>
     <t xml:space="preserve">13.3961791992188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2854671478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4423084259033</t>
+    <t xml:space="preserve">13.2854681015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4423093795776</t>
   </si>
   <si>
     <t xml:space="preserve">13.1286239624023</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">13.0086870193481</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1932058334351</t>
+    <t xml:space="preserve">13.1932067871094</t>
   </si>
   <si>
     <t xml:space="preserve">13.5437955856323</t>
@@ -3092,13 +3092,13 @@
     <t xml:space="preserve">13.3500499725342</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5714731216431</t>
+    <t xml:space="preserve">13.5714740753174</t>
   </si>
   <si>
     <t xml:space="preserve">13.368501663208</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1470775604248</t>
+    <t xml:space="preserve">13.1470766067505</t>
   </si>
   <si>
     <t xml:space="preserve">13.4976654052734</t>
@@ -3107,10 +3107,10 @@
     <t xml:space="preserve">13.1101722717285</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1655292510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2670154571533</t>
+    <t xml:space="preserve">13.1655302047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.267014503479</t>
   </si>
   <si>
     <t xml:space="preserve">13.2762413024902</t>
@@ -3119,22 +3119,22 @@
     <t xml:space="preserve">13.0455904006958</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1747541427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3315963745117</t>
+    <t xml:space="preserve">13.1747550964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.331597328186</t>
   </si>
   <si>
     <t xml:space="preserve">13.3869533538818</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5104818344116</t>
+    <t xml:space="preserve">12.5104808807373</t>
   </si>
   <si>
     <t xml:space="preserve">12.3813180923462</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6304178237915</t>
+    <t xml:space="preserve">12.6304187774658</t>
   </si>
   <si>
     <t xml:space="preserve">12.335186958313</t>
@@ -3143,28 +3143,28 @@
     <t xml:space="preserve">12.7872619628906</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5068922042847</t>
+    <t xml:space="preserve">13.5068912506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.4330835342407</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4515361785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2690591812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5735197067261</t>
+    <t xml:space="preserve">13.4515342712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2690601348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5735187530518</t>
   </si>
   <si>
     <t xml:space="preserve">15.8318471908569</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1455307006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3613204956055</t>
+    <t xml:space="preserve">16.1455326080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3613214492798</t>
   </si>
   <si>
     <t xml:space="preserve">15.4628076553345</t>
@@ -3176,16 +3176,16 @@
     <t xml:space="preserve">14.5217533111572</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5955610275269</t>
+    <t xml:space="preserve">14.5955619812012</t>
   </si>
   <si>
     <t xml:space="preserve">14.7154998779297</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3556861877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9128360748291</t>
+    <t xml:space="preserve">14.3556852340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9128351211548</t>
   </si>
   <si>
     <t xml:space="preserve">13.6545085906982</t>
@@ -3194,10 +3194,10 @@
     <t xml:space="preserve">14.5033025741577</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4110403060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6509189605713</t>
+    <t xml:space="preserve">14.4110412597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6509170532227</t>
   </si>
   <si>
     <t xml:space="preserve">15.1860265731812</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">15.6750068664551</t>
   </si>
   <si>
-    <t xml:space="preserve">15.416675567627</t>
+    <t xml:space="preserve">15.4166774749756</t>
   </si>
   <si>
     <t xml:space="preserve">15.1029939651489</t>
@@ -3218,46 +3218,46 @@
     <t xml:space="preserve">15.3889999389648</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7764940261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5827445983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1547584533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8133955001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8410749435425</t>
+    <t xml:space="preserve">15.7764930725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.582745552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1547603607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8133964538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8410720825195</t>
   </si>
   <si>
     <t xml:space="preserve">15.924108505249</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1178531646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8502988815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8779783248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3520956039429</t>
+    <t xml:space="preserve">16.1178550720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8503007888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8779792785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3520936965942</t>
   </si>
   <si>
     <t xml:space="preserve">15.6381034851074</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4351282119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5919713973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9517879486084</t>
+    <t xml:space="preserve">15.4351291656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5919704437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9517869949341</t>
   </si>
   <si>
     <t xml:space="preserve">16.0994033813477</t>
@@ -3266,49 +3266,49 @@
     <t xml:space="preserve">16.0717258453369</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5145740509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7877616882324</t>
+    <t xml:space="preserve">16.5145721435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7877655029297</t>
   </si>
   <si>
     <t xml:space="preserve">17.3910465240479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4648551940918</t>
+    <t xml:space="preserve">17.4648532867432</t>
   </si>
   <si>
     <t xml:space="preserve">17.1142635345459</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2618789672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5386600494385</t>
+    <t xml:space="preserve">17.2618808746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5386638641357</t>
   </si>
   <si>
     <t xml:space="preserve">17.4464015960693</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5663394927979</t>
+    <t xml:space="preserve">17.5663414001465</t>
   </si>
   <si>
     <t xml:space="preserve">17.3725929260254</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6216983795166</t>
+    <t xml:space="preserve">17.621696472168</t>
   </si>
   <si>
     <t xml:space="preserve">17.547887802124</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0368671417236</t>
+    <t xml:space="preserve">18.036865234375</t>
   </si>
   <si>
     <t xml:space="preserve">18.4151306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7657241821289</t>
+    <t xml:space="preserve">18.7657222747803</t>
   </si>
   <si>
     <t xml:space="preserve">19.9835567474365</t>
@@ -3320,13 +3320,13 @@
     <t xml:space="preserve">19.4484481811523</t>
   </si>
   <si>
-    <t xml:space="preserve">18.728816986084</t>
+    <t xml:space="preserve">18.7288150787354</t>
   </si>
   <si>
     <t xml:space="preserve">19.245475769043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1901187896729</t>
+    <t xml:space="preserve">19.1901168823242</t>
   </si>
   <si>
     <t xml:space="preserve">19.3377323150635</t>
@@ -3335,13 +3335,13 @@
     <t xml:space="preserve">19.2639274597168</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5443000793457</t>
+    <t xml:space="preserve">18.5442981719971</t>
   </si>
   <si>
     <t xml:space="preserve">18.5627517700195</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2029361724854</t>
+    <t xml:space="preserve">18.2029342651367</t>
   </si>
   <si>
     <t xml:space="preserve">18.4704914093018</t>
@@ -3362,10 +3362,10 @@
     <t xml:space="preserve">20.6109256744385</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9430637359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2567481994629</t>
+    <t xml:space="preserve">20.9430618286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2567501068115</t>
   </si>
   <si>
     <t xml:space="preserve">21.2198429107666</t>
@@ -3383,7 +3383,7 @@
     <t xml:space="preserve">22.7698135375977</t>
   </si>
   <si>
-    <t xml:space="preserve">22.290060043335</t>
+    <t xml:space="preserve">22.2900619506836</t>
   </si>
   <si>
     <t xml:space="preserve">21.8472137451172</t>
@@ -3413,16 +3413,16 @@
     <t xml:space="preserve">20.6847343444824</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2013912200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4633083343506</t>
+    <t xml:space="preserve">21.2013893127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4633102416992</t>
   </si>
   <si>
     <t xml:space="preserve">19.8728466033936</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6478290557861</t>
+    <t xml:space="preserve">20.6478309631348</t>
   </si>
   <si>
     <t xml:space="preserve">20.8508014678955</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">21.0906791687012</t>
   </si>
   <si>
-    <t xml:space="preserve">21.109130859375</t>
+    <t xml:space="preserve">21.1091327667236</t>
   </si>
   <si>
     <t xml:space="preserve">20.2234325408936</t>
@@ -3455,7 +3455,7 @@
     <t xml:space="preserve">20.7954483032227</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3156929016113</t>
+    <t xml:space="preserve">20.31569480896</t>
   </si>
   <si>
     <t xml:space="preserve">20.8323497772217</t>
@@ -3464,10 +3464,10 @@
     <t xml:space="preserve">22.179349899292</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5483913421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0686359405518</t>
+    <t xml:space="preserve">22.5483894348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0686378479004</t>
   </si>
   <si>
     <t xml:space="preserve">22.2162532806396</t>
@@ -3479,22 +3479,22 @@
     <t xml:space="preserve">22.0132808685303</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2531585693359</t>
+    <t xml:space="preserve">22.2531566619873</t>
   </si>
   <si>
     <t xml:space="preserve">22.0317325592041</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1942100524902</t>
+    <t xml:space="preserve">23.1942119598389</t>
   </si>
   <si>
     <t xml:space="preserve">23.7846775054932</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7293186187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3935928344727</t>
+    <t xml:space="preserve">23.729320526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3935947418213</t>
   </si>
   <si>
     <t xml:space="preserve">23.8953876495361</t>
@@ -3503,19 +3503,19 @@
     <t xml:space="preserve">23.046594619751</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9174327850342</t>
+    <t xml:space="preserve">22.9174308776855</t>
   </si>
   <si>
     <t xml:space="preserve">23.3049221038818</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3971843719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5817012786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1388549804688</t>
+    <t xml:space="preserve">23.3971824645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5817031860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1388568878174</t>
   </si>
   <si>
     <t xml:space="preserve">22.5852928161621</t>
@@ -3533,16 +3533,16 @@
     <t xml:space="preserve">23.7477722167969</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7662258148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2311172485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7144603729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6370620727539</t>
+    <t xml:space="preserve">23.7662220001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2311153411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7144584655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6370601654053</t>
   </si>
   <si>
     <t xml:space="preserve">25.0763206481934</t>
@@ -3551,25 +3551,25 @@
     <t xml:space="preserve">26.7554550170898</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4786739349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9768772125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1613998413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3828239440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4935340881348</t>
+    <t xml:space="preserve">26.4786758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.976879119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1614017486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3828258514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4935359954834</t>
   </si>
   <si>
     <t xml:space="preserve">28.1578102111816</t>
   </si>
   <si>
-    <t xml:space="preserve">28.04709815979</t>
+    <t xml:space="preserve">28.0470962524414</t>
   </si>
   <si>
     <t xml:space="preserve">27.2721099853516</t>
@@ -3578,16 +3578,16 @@
     <t xml:space="preserve">27.5673427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4012756347656</t>
+    <t xml:space="preserve">27.4012775421143</t>
   </si>
   <si>
     <t xml:space="preserve">27.1060428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9030723571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.497127532959</t>
+    <t xml:space="preserve">26.9030685424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4971256256104</t>
   </si>
   <si>
     <t xml:space="preserve">25.9251136779785</t>
@@ -3596,16 +3596,16 @@
     <t xml:space="preserve">25.7221393585205</t>
   </si>
   <si>
-    <t xml:space="preserve">26.644739151001</t>
+    <t xml:space="preserve">26.6447410583496</t>
   </si>
   <si>
     <t xml:space="preserve">26.4602222442627</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3864116668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9989223480225</t>
+    <t xml:space="preserve">26.3864135742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9989204406738</t>
   </si>
   <si>
     <t xml:space="preserve">25.5007152557373</t>
@@ -3617,16 +3617,16 @@
     <t xml:space="preserve">26.2572479248047</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1280841827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9620151519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6631927490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3310585021973</t>
+    <t xml:space="preserve">26.1280860900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9620170593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6631946563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3310604095459</t>
   </si>
   <si>
     <t xml:space="preserve">26.5155773162842</t>
@@ -3641,19 +3641,19 @@
     <t xml:space="preserve">26.7185497283936</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8292636871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4417705535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5340309143066</t>
+    <t xml:space="preserve">26.8292617797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4417667388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.534029006958</t>
   </si>
   <si>
     <t xml:space="preserve">25.4269065856934</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3715534210205</t>
+    <t xml:space="preserve">25.3715515136719</t>
   </si>
   <si>
     <t xml:space="preserve">26.5893859863281</t>
@@ -3665,13 +3665,13 @@
     <t xml:space="preserve">27.4750843048096</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9143409729004</t>
+    <t xml:space="preserve">28.9143447875977</t>
   </si>
   <si>
     <t xml:space="preserve">30.4643135070801</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9625205993652</t>
+    <t xml:space="preserve">30.9625225067139</t>
   </si>
   <si>
     <t xml:space="preserve">29.5970706939697</t>
@@ -3680,22 +3680,22 @@
     <t xml:space="preserve">27.0322360992432</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8846168518066</t>
+    <t xml:space="preserve">26.8846187591553</t>
   </si>
   <si>
     <t xml:space="preserve">27.3459186553955</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6227035522461</t>
+    <t xml:space="preserve">27.6227016448975</t>
   </si>
   <si>
     <t xml:space="preserve">26.7923583984375</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9399738311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1798496246338</t>
+    <t xml:space="preserve">26.939977645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1798515319824</t>
   </si>
   <si>
     <t xml:space="preserve">27.8994808197021</t>
@@ -3704,22 +3704,19 @@
     <t xml:space="preserve">27.5857963562012</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2352066040039</t>
-  </si>
-  <si>
     <t xml:space="preserve">27.2167549133301</t>
   </si>
   <si>
     <t xml:space="preserve">27.3643703460693</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6262912750244</t>
+    <t xml:space="preserve">26.6262893676758</t>
   </si>
   <si>
     <t xml:space="preserve">27.2536602020264</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7703151702881</t>
+    <t xml:space="preserve">27.7703189849854</t>
   </si>
   <si>
     <t xml:space="preserve">27.3090171813965</t>
@@ -3731,7 +3728,7 @@
     <t xml:space="preserve">28.674467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0286445617676</t>
+    <t xml:space="preserve">28.0286426544189</t>
   </si>
   <si>
     <t xml:space="preserve">27.8072185516357</t>
@@ -3740,37 +3737,37 @@
     <t xml:space="preserve">28.3423290252686</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9179344177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6965065002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.050687789917</t>
+    <t xml:space="preserve">27.917932510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6965084075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0506858825684</t>
   </si>
   <si>
     <t xml:space="preserve">27.7518653869629</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8256721496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9732875823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3054256439209</t>
+    <t xml:space="preserve">27.8256702423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9732894897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3054275512695</t>
   </si>
   <si>
     <t xml:space="preserve">28.2869720458984</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0840015411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7887687683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2941551208496</t>
+    <t xml:space="preserve">28.0840034484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7887706756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.294153213501</t>
   </si>
   <si>
     <t xml:space="preserve">26.9953308105469</t>
@@ -3779,19 +3776,19 @@
     <t xml:space="preserve">26.220344543457</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5191669464111</t>
+    <t xml:space="preserve">25.5191688537598</t>
   </si>
   <si>
     <t xml:space="preserve">24.6150188446045</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0983638763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9656047821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3566913604736</t>
+    <t xml:space="preserve">24.0983619689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9656066894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.356689453125</t>
   </si>
   <si>
     <t xml:space="preserve">23.7108688354492</t>
@@ -3803,13 +3800,13 @@
     <t xml:space="preserve">23.2680187225342</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0614585876465</t>
+    <t xml:space="preserve">24.0614566802979</t>
   </si>
   <si>
     <t xml:space="preserve">24.2090721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7441806793213</t>
+    <t xml:space="preserve">24.7441825866699</t>
   </si>
   <si>
     <t xml:space="preserve">24.6334705352783</t>
@@ -3821,7 +3818,7 @@
     <t xml:space="preserve">25.0947704315186</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9102516174316</t>
+    <t xml:space="preserve">24.910249710083</t>
   </si>
   <si>
     <t xml:space="preserve">24.984058380127</t>
@@ -3830,22 +3827,22 @@
     <t xml:space="preserve">24.8179893493652</t>
   </si>
   <si>
-    <t xml:space="preserve">25.187032699585</t>
+    <t xml:space="preserve">25.1870288848877</t>
   </si>
   <si>
     <t xml:space="preserve">24.670373916626</t>
   </si>
   <si>
-    <t xml:space="preserve">25.537618637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8733463287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9287052154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8364410400391</t>
+    <t xml:space="preserve">25.5376224517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8733444213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9287033081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8364429473877</t>
   </si>
   <si>
     <t xml:space="preserve">24.2644290924072</t>
@@ -3854,19 +3851,19 @@
     <t xml:space="preserve">24.3013343811035</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8769340515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5263481140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1573066711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.865665435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8287620544434</t>
+    <t xml:space="preserve">23.8769359588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.526346206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1573047637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8656635284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8287601470947</t>
   </si>
   <si>
     <t xml:space="preserve">21.8841152191162</t>
@@ -3881,16 +3878,16 @@
     <t xml:space="preserve">21.736499786377</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4597187042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5335292816162</t>
+    <t xml:space="preserve">21.4597206115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5335273742676</t>
   </si>
   <si>
     <t xml:space="preserve">22.6591014862061</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4412651062012</t>
+    <t xml:space="preserve">21.4412670135498</t>
   </si>
   <si>
     <t xml:space="preserve">20.352596282959</t>
@@ -3902,7 +3899,7 @@
     <t xml:space="preserve">21.9948291778564</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5299377441406</t>
+    <t xml:space="preserve">22.5299396514893</t>
   </si>
   <si>
     <t xml:space="preserve">22.5114860534668</t>
@@ -3911,19 +3908,19 @@
     <t xml:space="preserve">22.6775550842285</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1204013824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8620738983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.935884475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3085136413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3859100341797</t>
+    <t xml:space="preserve">23.1204032897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8620758056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9358825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3085155487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3859119415283</t>
   </si>
   <si>
     <t xml:space="preserve">21.3674583435059</t>
@@ -3932,22 +3929,22 @@
     <t xml:space="preserve">21.8103084564209</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9281997680664</t>
+    <t xml:space="preserve">19.9281978607178</t>
   </si>
   <si>
     <t xml:space="preserve">20.0758171081543</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8877048492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4448585510254</t>
+    <t xml:space="preserve">20.8877086639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4448566436768</t>
   </si>
   <si>
     <t xml:space="preserve">20.2787895202637</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8174877166748</t>
+    <t xml:space="preserve">19.8174896240234</t>
   </si>
   <si>
     <t xml:space="preserve">20.8138980865479</t>
@@ -3962,22 +3959,22 @@
     <t xml:space="preserve">20.7585411071777</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3710498809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0204620361328</t>
+    <t xml:space="preserve">20.3710479736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0204601287842</t>
   </si>
   <si>
     <t xml:space="preserve">18.9871463775635</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5073928833008</t>
+    <t xml:space="preserve">18.5073909759521</t>
   </si>
   <si>
     <t xml:space="preserve">17.6770515441895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1291255950928</t>
+    <t xml:space="preserve">18.1291275024414</t>
   </si>
   <si>
     <t xml:space="preserve">18.1198997497559</t>
@@ -3986,10 +3983,10 @@
     <t xml:space="preserve">17.0681343078613</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3633651733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0845413208008</t>
+    <t xml:space="preserve">17.3633670806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0845422744751</t>
   </si>
   <si>
     <t xml:space="preserve">15.23215675354</t>
@@ -3998,16 +3995,16 @@
     <t xml:space="preserve">16.2839221954346</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3705472946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.23779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4699869155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2172956466675</t>
+    <t xml:space="preserve">15.3705463409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2377948760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.469988822937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2172946929932</t>
   </si>
   <si>
     <t xml:space="preserve">14.0604524612427</t>
@@ -4016,13 +4013,13 @@
     <t xml:space="preserve">14.337233543396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6878213882446</t>
+    <t xml:space="preserve">14.6878223419189</t>
   </si>
   <si>
     <t xml:space="preserve">14.8169851303101</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2634239196777</t>
+    <t xml:space="preserve">14.2634248733521</t>
   </si>
   <si>
     <t xml:space="preserve">14.2541990280151</t>
@@ -4031,19 +4028,19 @@
     <t xml:space="preserve">14.6601438522339</t>
   </si>
   <si>
-    <t xml:space="preserve">15.82262134552</t>
+    <t xml:space="preserve">15.8226222991943</t>
   </si>
   <si>
     <t xml:space="preserve">15.6565532684326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0420007705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9958696365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8205757141113</t>
+    <t xml:space="preserve">14.0420017242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9958715438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.820574760437</t>
   </si>
   <si>
     <t xml:space="preserve">14.3649110794067</t>
@@ -4055,10 +4052,10 @@
     <t xml:space="preserve">13.617603302002</t>
   </si>
   <si>
-    <t xml:space="preserve">13.811351776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8057146072388</t>
+    <t xml:space="preserve">13.8113508224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8057136535645</t>
   </si>
   <si>
     <t xml:space="preserve">12.7134532928467</t>
@@ -4067,22 +4064,22 @@
     <t xml:space="preserve">13.3592748641968</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9461517333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0476369857788</t>
+    <t xml:space="preserve">14.9461507797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0476360321045</t>
   </si>
   <si>
     <t xml:space="preserve">15.305965423584</t>
   </si>
   <si>
-    <t xml:space="preserve">15.342869758606</t>
+    <t xml:space="preserve">15.3428678512573</t>
   </si>
   <si>
     <t xml:space="preserve">15.0384101867676</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2341136932373</t>
+    <t xml:space="preserve">15.234112739563</t>
   </si>
   <si>
     <t xml:space="preserve">14.7736358642578</t>
@@ -4097,46 +4094,46 @@
     <t xml:space="preserve">15.4739437103271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9823884963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5410995483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7137775421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.780930519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0303516387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8576784133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6466245651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3204526901245</t>
+    <t xml:space="preserve">15.9823875427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5410985946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7137756347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7809314727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0303554534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8576755523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6466236114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3204536437988</t>
   </si>
   <si>
     <t xml:space="preserve">14.5529918670654</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6128511428833</t>
+    <t xml:space="preserve">13.612850189209</t>
   </si>
   <si>
     <t xml:space="preserve">13.5456981658936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.843090057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9509153366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1427793502808</t>
+    <t xml:space="preserve">13.8430891036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9509143829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1427803039551</t>
   </si>
   <si>
     <t xml:space="preserve">13.0180673599243</t>
@@ -4154,22 +4151,22 @@
     <t xml:space="preserve">12.8070163726807</t>
   </si>
   <si>
-    <t xml:space="preserve">12.749457359314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8453893661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5959644317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1258935928345</t>
+    <t xml:space="preserve">12.7494564056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8453903198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5959634780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1258945465088</t>
   </si>
   <si>
     <t xml:space="preserve">11.8093156814575</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7805366516113</t>
+    <t xml:space="preserve">11.780535697937</t>
   </si>
   <si>
     <t xml:space="preserve">11.5502977371216</t>
@@ -4190,19 +4187,19 @@
     <t xml:space="preserve">12.7206764221191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6823034286499</t>
+    <t xml:space="preserve">12.6823043823242</t>
   </si>
   <si>
     <t xml:space="preserve">12.2026405334473</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8933553695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1715602874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1044082641602</t>
+    <t xml:space="preserve">12.8933544158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1715593338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1044073104858</t>
   </si>
   <si>
     <t xml:space="preserve">13.0948133468628</t>
@@ -4220,19 +4217,19 @@
     <t xml:space="preserve">13.3058662414551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0372543334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3154602050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4808444976807</t>
+    <t xml:space="preserve">13.0372552871704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3154592514038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.480845451355</t>
   </si>
   <si>
     <t xml:space="preserve">12.6055583953857</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1738586425781</t>
+    <t xml:space="preserve">12.1738595962524</t>
   </si>
   <si>
     <t xml:space="preserve">12.5096244812012</t>
@@ -4244,7 +4241,7 @@
     <t xml:space="preserve">12.3945055007935</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2506065368652</t>
+    <t xml:space="preserve">12.2506074905396</t>
   </si>
   <si>
     <t xml:space="preserve">11.8668756484985</t>
@@ -4259,31 +4256,31 @@
     <t xml:space="preserve">12.2218265533447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3081665039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1163005828857</t>
+    <t xml:space="preserve">12.3081655502319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1162996292114</t>
   </si>
   <si>
     <t xml:space="preserve">12.1834535598755</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8476896286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.164267539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4927377700806</t>
+    <t xml:space="preserve">11.8476886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1642665863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4927368164062</t>
   </si>
   <si>
     <t xml:space="preserve">11.4639577865601</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3296527862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.665415763855</t>
+    <t xml:space="preserve">11.3296518325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6654167175293</t>
   </si>
   <si>
     <t xml:space="preserve">12.1354866027832</t>
@@ -4292,7 +4289,7 @@
     <t xml:space="preserve">11.7421627044678</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7709426879883</t>
+    <t xml:space="preserve">11.7709436416626</t>
   </si>
   <si>
     <t xml:space="preserve">11.3488388061523</t>
@@ -4301,40 +4298,40 @@
     <t xml:space="preserve">11.4063987731934</t>
   </si>
   <si>
-    <t xml:space="preserve">11.12819480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3680257797241</t>
+    <t xml:space="preserve">11.1281938552856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3680248260498</t>
   </si>
   <si>
     <t xml:space="preserve">11.2720928192139</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9363269805908</t>
+    <t xml:space="preserve">10.9363279342651</t>
   </si>
   <si>
     <t xml:space="preserve">10.9459209442139</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8499889373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.754056930542</t>
+    <t xml:space="preserve">10.8499898910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7540559768677</t>
   </si>
   <si>
     <t xml:space="preserve">10.9555149078369</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1090078353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4159917831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6558237075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5694856643677</t>
+    <t xml:space="preserve">11.1090068817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4159908294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6558227539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.569483757019</t>
   </si>
   <si>
     <t xml:space="preserve">11.5790777206421</t>
@@ -4346,25 +4343,25 @@
     <t xml:space="preserve">11.7613496780396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8764696121216</t>
+    <t xml:space="preserve">11.8764686584473</t>
   </si>
   <si>
     <t xml:space="preserve">12.049147605896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9628076553345</t>
+    <t xml:space="preserve">11.9628086090088</t>
   </si>
   <si>
     <t xml:space="preserve">12.9413213729858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2003393173218</t>
+    <t xml:space="preserve">13.2003402709961</t>
   </si>
   <si>
     <t xml:space="preserve">11.6941967010498</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3104648590088</t>
+    <t xml:space="preserve">11.3104658126831</t>
   </si>
   <si>
     <t xml:space="preserve">10.9267358779907</t>
@@ -4376,19 +4373,19 @@
     <t xml:space="preserve">11.8956546783447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7229776382446</t>
+    <t xml:space="preserve">11.7229766845703</t>
   </si>
   <si>
     <t xml:space="preserve">12.7398624420166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2889804840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0875215530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2601985931396</t>
+    <t xml:space="preserve">12.2889795303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0875205993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.260199546814</t>
   </si>
   <si>
     <t xml:space="preserve">12.1930465698242</t>
@@ -4403,7 +4400,10 @@
     <t xml:space="preserve">12.5671844482422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2314205169678</t>
+    <t xml:space="preserve">12.2314186096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.106707572937</t>
   </si>
   <si>
     <t xml:space="preserve">12.7686433792114</t>
@@ -4418,25 +4418,25 @@
     <t xml:space="preserve">12.3273525238037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3177585601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4616584777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9915885925293</t>
+    <t xml:space="preserve">12.317759513855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4616575241089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.991587638855</t>
   </si>
   <si>
     <t xml:space="preserve">11.9244346618652</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0395545959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0587406158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5000314712524</t>
+    <t xml:space="preserve">12.0395536422729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.058741569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5000305175781</t>
   </si>
   <si>
     <t xml:space="preserve">12.8262023925781</t>
@@ -4445,7 +4445,7 @@
     <t xml:space="preserve">13.0852212905884</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7471561431885</t>
+    <t xml:space="preserve">13.7471551895142</t>
   </si>
   <si>
     <t xml:space="preserve">13.83349609375</t>
@@ -4466,16 +4466,16 @@
     <t xml:space="preserve">14.2172260284424</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2364130020142</t>
+    <t xml:space="preserve">14.2364139556885</t>
   </si>
   <si>
     <t xml:space="preserve">13.7855291366577</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8143091201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1404809951782</t>
+    <t xml:space="preserve">13.8143100738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1404800415039</t>
   </si>
   <si>
     <t xml:space="preserve">14.1980409622192</t>
@@ -4487,49 +4487,49 @@
     <t xml:space="preserve">14.3707180023193</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2939720153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1692600250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7160768508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9463157653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4378719329834</t>
+    <t xml:space="preserve">14.2939729690552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1692609786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7160778045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9463148117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4378728866577</t>
   </si>
   <si>
     <t xml:space="preserve">14.3899059295654</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3131589889526</t>
+    <t xml:space="preserve">14.313159942627</t>
   </si>
   <si>
     <t xml:space="preserve">14.4474658966064</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3323459625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3515329360962</t>
+    <t xml:space="preserve">14.3323450088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3515319824219</t>
   </si>
   <si>
     <t xml:space="preserve">14.5721769332886</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5242109298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6009578704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3611259460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0879154205322</t>
+    <t xml:space="preserve">14.5242118835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6009588241577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3611268997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0879135131836</t>
   </si>
   <si>
     <t xml:space="preserve">15.828896522522</t>
@@ -4541,10 +4541,10 @@
     <t xml:space="preserve">16.3373394012451</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7210712432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3277454376221</t>
+    <t xml:space="preserve">16.7210693359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3277473449707</t>
   </si>
   <si>
     <t xml:space="preserve">16.2030334472656</t>
@@ -4553,25 +4553,25 @@
     <t xml:space="preserve">16.2318134307861</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1454753875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0207614898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3588266372681</t>
+    <t xml:space="preserve">16.1454734802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0207633972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3588256835938</t>
   </si>
   <si>
     <t xml:space="preserve">16.0783214569092</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6297369003296</t>
+    <t xml:space="preserve">14.6297378540039</t>
   </si>
   <si>
     <t xml:space="preserve">14.6105499267578</t>
   </si>
   <si>
-    <t xml:space="preserve">14.639331817627</t>
+    <t xml:space="preserve">14.6393308639526</t>
   </si>
   <si>
     <t xml:space="preserve">14.1308870315552</t>
@@ -4583,37 +4583,37 @@
     <t xml:space="preserve">14.044548034668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9390211105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0541410446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0061750411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3922052383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6416301727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5552911758423</t>
+    <t xml:space="preserve">13.939022064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.054141998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.006175994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3922061920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6416311264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.555290222168</t>
   </si>
   <si>
     <t xml:space="preserve">13.459358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4497652053833</t>
+    <t xml:space="preserve">13.4497661590576</t>
   </si>
   <si>
     <t xml:space="preserve">13.3826122283936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4305782318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3538312911987</t>
+    <t xml:space="preserve">13.4305791854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3538331985474</t>
   </si>
   <si>
     <t xml:space="preserve">13.2195262908936</t>
@@ -4628,7 +4628,7 @@
     <t xml:space="preserve">12.9701023101807</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2579002380371</t>
+    <t xml:space="preserve">13.2578992843628</t>
   </si>
   <si>
     <t xml:space="preserve">13.0276613235474</t>
@@ -6018,6 +6018,9 @@
   </si>
   <si>
     <t xml:space="preserve">6.36999988555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44999980926514</t>
   </si>
 </sst>
 </file>
@@ -43476,7 +43479,7 @@
         <v>29.5200004577637</v>
       </c>
       <c r="G1428" t="s">
-        <v>1230</v>
+        <v>605</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -43528,7 +43531,7 @@
         <v>29.5</v>
       </c>
       <c r="G1430" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -43554,7 +43557,7 @@
         <v>29.6599998474121</v>
       </c>
       <c r="G1431" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -43606,7 +43609,7 @@
         <v>28.8600006103516</v>
       </c>
       <c r="G1433" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -43632,7 +43635,7 @@
         <v>29.5</v>
       </c>
       <c r="G1434" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -43658,7 +43661,7 @@
         <v>29.5400009155273</v>
       </c>
       <c r="G1435" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -43684,7 +43687,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1436" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -43710,7 +43713,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1437" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -43736,7 +43739,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1438" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -43762,7 +43765,7 @@
         <v>31.0799999237061</v>
       </c>
       <c r="G1439" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -43788,7 +43791,7 @@
         <v>30.3799991607666</v>
       </c>
       <c r="G1440" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -43814,7 +43817,7 @@
         <v>30.1399993896484</v>
       </c>
       <c r="G1441" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -43840,7 +43843,7 @@
         <v>30.7199993133545</v>
       </c>
       <c r="G1442" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -43866,7 +43869,7 @@
         <v>30.2600002288818</v>
       </c>
       <c r="G1443" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -43892,7 +43895,7 @@
         <v>30.3799991607666</v>
       </c>
       <c r="G1444" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -43918,7 +43921,7 @@
         <v>30.0200004577637</v>
       </c>
       <c r="G1445" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -43944,7 +43947,7 @@
         <v>29.3199996948242</v>
       </c>
       <c r="G1446" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -43970,7 +43973,7 @@
         <v>30.0799999237061</v>
       </c>
       <c r="G1447" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -43996,7 +43999,7 @@
         <v>30.1599998474121</v>
       </c>
       <c r="G1448" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -44022,7 +44025,7 @@
         <v>30.3199996948242</v>
       </c>
       <c r="G1449" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -44048,7 +44051,7 @@
         <v>30.6800003051758</v>
       </c>
       <c r="G1450" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -44074,7 +44077,7 @@
         <v>30.6599998474121</v>
       </c>
       <c r="G1451" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -44100,7 +44103,7 @@
         <v>30.4400005340576</v>
       </c>
       <c r="G1452" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -44126,7 +44129,7 @@
         <v>30.1200008392334</v>
       </c>
       <c r="G1453" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -44152,7 +44155,7 @@
         <v>28.5</v>
       </c>
       <c r="G1454" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -44230,7 +44233,7 @@
         <v>29.2600002288818</v>
       </c>
       <c r="G1457" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -44256,7 +44259,7 @@
         <v>28.4200000762939</v>
       </c>
       <c r="G1458" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -44282,7 +44285,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G1459" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -44308,7 +44311,7 @@
         <v>26.6800003051758</v>
       </c>
       <c r="G1460" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -44334,7 +44337,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G1461" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -44360,7 +44363,7 @@
         <v>27.0599994659424</v>
       </c>
       <c r="G1462" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -44386,7 +44389,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1463" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -44412,7 +44415,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1464" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -44464,7 +44467,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1466" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -44490,7 +44493,7 @@
         <v>25.2199993133545</v>
       </c>
       <c r="G1467" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -44568,7 +44571,7 @@
         <v>26.0799999237061</v>
       </c>
       <c r="G1470" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -44594,7 +44597,7 @@
         <v>26.2399997711182</v>
       </c>
       <c r="G1471" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -44620,7 +44623,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G1472" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -44646,7 +44649,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1473" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -44672,7 +44675,7 @@
         <v>27.3600006103516</v>
       </c>
       <c r="G1474" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -44698,7 +44701,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1475" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -44724,7 +44727,7 @@
         <v>27</v>
       </c>
       <c r="G1476" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -44750,7 +44753,7 @@
         <v>27.0799999237061</v>
       </c>
       <c r="G1477" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -44802,7 +44805,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1479" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -44828,7 +44831,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1480" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -44854,7 +44857,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1481" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -44880,7 +44883,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1482" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -44906,7 +44909,7 @@
         <v>26.7399997711182</v>
       </c>
       <c r="G1483" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -44932,7 +44935,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G1484" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -44958,7 +44961,7 @@
         <v>27</v>
       </c>
       <c r="G1485" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -44984,7 +44987,7 @@
         <v>26.9599990844727</v>
       </c>
       <c r="G1486" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -45010,7 +45013,7 @@
         <v>27.0799999237061</v>
       </c>
       <c r="G1487" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -45036,7 +45039,7 @@
         <v>27.0200004577637</v>
       </c>
       <c r="G1488" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -45062,7 +45065,7 @@
         <v>26.9200000762939</v>
       </c>
       <c r="G1489" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -45088,7 +45091,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1490" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -45114,7 +45117,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G1491" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -45140,7 +45143,7 @@
         <v>25.8799991607666</v>
       </c>
       <c r="G1492" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -45218,7 +45221,7 @@
         <v>25.8799991607666</v>
       </c>
       <c r="G1495" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -45244,7 +45247,7 @@
         <v>25.5</v>
       </c>
       <c r="G1496" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -45270,7 +45273,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1497" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -45348,7 +45351,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1500" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -45374,7 +45377,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1501" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -45400,7 +45403,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G1502" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -45452,7 +45455,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1504" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -45478,7 +45481,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G1505" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -45504,7 +45507,7 @@
         <v>23.5599994659424</v>
       </c>
       <c r="G1506" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -45530,7 +45533,7 @@
         <v>23.2600002288818</v>
       </c>
       <c r="G1507" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -45556,7 +45559,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1508" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -45582,7 +45585,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G1509" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -45608,7 +45611,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G1510" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -45634,7 +45637,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1511" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -45660,7 +45663,7 @@
         <v>23.2399997711182</v>
       </c>
       <c r="G1512" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -45712,7 +45715,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G1514" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -45738,7 +45741,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1515" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -45842,7 +45845,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1519" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -45868,7 +45871,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G1520" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -45894,7 +45897,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G1521" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -45946,7 +45949,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G1523" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -45972,7 +45975,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1524" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -45998,7 +46001,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G1525" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -46024,7 +46027,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G1526" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -46050,7 +46053,7 @@
         <v>25.0599994659424</v>
       </c>
       <c r="G1527" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -46076,7 +46079,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G1528" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -46102,7 +46105,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G1529" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -46128,7 +46131,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G1530" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -46154,7 +46157,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1531" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -46180,7 +46183,7 @@
         <v>23.1800003051758</v>
       </c>
       <c r="G1532" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -46206,7 +46209,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G1533" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -46336,7 +46339,7 @@
         <v>23.2399997711182</v>
       </c>
       <c r="G1538" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -46362,7 +46365,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G1539" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -46388,7 +46391,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G1540" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -46414,7 +46417,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1541" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -46440,7 +46443,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1542" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -46466,7 +46469,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G1543" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -46518,7 +46521,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G1545" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -46674,7 +46677,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G1551" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -46700,7 +46703,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G1552" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -46726,7 +46729,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G1553" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -46752,7 +46755,7 @@
         <v>22.5599994659424</v>
       </c>
       <c r="G1554" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -46804,7 +46807,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1556" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -46856,7 +46859,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G1558" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -46882,7 +46885,7 @@
         <v>22.5</v>
       </c>
       <c r="G1559" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -46908,7 +46911,7 @@
         <v>22.0799999237061</v>
       </c>
       <c r="G1560" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -46934,7 +46937,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1561" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -46960,7 +46963,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G1562" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -46986,7 +46989,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G1563" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -47012,7 +47015,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G1564" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -47038,7 +47041,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1565" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -47064,7 +47067,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G1566" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -47090,7 +47093,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G1567" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -47116,7 +47119,7 @@
         <v>18.5</v>
       </c>
       <c r="G1568" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -47142,7 +47145,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1569" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -47220,7 +47223,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1572" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -47246,7 +47249,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G1573" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -47272,7 +47275,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1574" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -47324,7 +47327,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1576" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -47350,7 +47353,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1577" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -47376,7 +47379,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1578" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -47402,7 +47405,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G1579" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -47428,7 +47431,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1580" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -47454,7 +47457,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G1581" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -47480,7 +47483,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1582" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -47506,7 +47509,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1583" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -47558,7 +47561,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1585" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -47584,7 +47587,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1586" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -47610,7 +47613,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G1587" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -47636,7 +47639,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1588" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -47662,7 +47665,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G1589" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -47870,7 +47873,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1597" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -47896,7 +47899,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1598" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -47922,7 +47925,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1599" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -48000,7 +48003,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1602" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -48052,7 +48055,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G1604" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -48078,7 +48081,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G1605" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -48104,7 +48107,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1606" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -48234,7 +48237,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G1611" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -48338,7 +48341,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G1615" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -48364,7 +48367,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1616" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -48390,7 +48393,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1617" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -48442,7 +48445,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1619" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -48468,7 +48471,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G1620" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -48520,7 +48523,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G1622" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -48546,7 +48549,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G1623" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -48572,7 +48575,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1624" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -48598,7 +48601,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1625" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -48624,7 +48627,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1626" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -48650,7 +48653,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G1627" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -48676,7 +48679,7 @@
         <v>16</v>
       </c>
       <c r="G1628" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -48702,7 +48705,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G1629" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -48728,7 +48731,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1630" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -48754,7 +48757,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1631" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -48780,7 +48783,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1632" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -48806,7 +48809,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1633" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -48832,7 +48835,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1634" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -48858,7 +48861,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1635" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -48884,7 +48887,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1636" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -48910,7 +48913,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G1637" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -48936,7 +48939,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G1638" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -48962,7 +48965,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1639" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -48988,7 +48991,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G1640" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -49014,7 +49017,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1641" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -49040,7 +49043,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G1642" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -49066,7 +49069,7 @@
         <v>13.5</v>
       </c>
       <c r="G1643" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -49092,7 +49095,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1644" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -49118,7 +49121,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G1645" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -49144,7 +49147,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1646" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -49170,7 +49173,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1647" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -49196,7 +49199,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1648" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -49222,7 +49225,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1649" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -49248,7 +49251,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G1650" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -49274,7 +49277,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G1651" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -49300,7 +49303,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G1652" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -49326,7 +49329,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1653" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -49352,7 +49355,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G1654" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -49378,7 +49381,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1655" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -49404,7 +49407,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1656" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -49430,7 +49433,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1657" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -49456,7 +49459,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1658" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -49482,7 +49485,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1659" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -49508,7 +49511,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1660" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -49534,7 +49537,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G1661" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -49560,7 +49563,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1662" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -49586,7 +49589,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1663" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -49612,7 +49615,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G1664" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -49638,7 +49641,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1665" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -49664,7 +49667,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G1666" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -49690,7 +49693,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G1667" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -49716,7 +49719,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1668" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -49742,7 +49745,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1669" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -49768,7 +49771,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1670" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -49794,7 +49797,7 @@
         <v>13</v>
       </c>
       <c r="G1671" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -49820,7 +49823,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1672" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -49846,7 +49849,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1673" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -49872,7 +49875,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G1674" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -49898,7 +49901,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G1675" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -49924,7 +49927,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1676" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -49950,7 +49953,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G1677" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -49976,7 +49979,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1678" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -50002,7 +50005,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G1679" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -50028,7 +50031,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1680" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -50054,7 +50057,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G1681" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -50080,7 +50083,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G1682" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -50106,7 +50109,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1683" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -50132,7 +50135,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1684" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -50158,7 +50161,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G1685" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -50184,7 +50187,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1686" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -50210,7 +50213,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G1687" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -50236,7 +50239,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1688" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -50262,7 +50265,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1689" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -50288,7 +50291,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G1690" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -50314,7 +50317,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G1691" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -50340,7 +50343,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G1692" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -50366,7 +50369,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1693" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -50392,7 +50395,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G1694" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -50418,7 +50421,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G1695" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -50444,7 +50447,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1696" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -50470,7 +50473,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1697" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -50496,7 +50499,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1698" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -50522,7 +50525,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1699" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -50548,7 +50551,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1700" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -50574,7 +50577,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1701" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -50600,7 +50603,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G1702" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -50626,7 +50629,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1703" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -50652,7 +50655,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1704" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -50678,7 +50681,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1705" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -50704,7 +50707,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G1706" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -50730,7 +50733,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1707" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -50756,7 +50759,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G1708" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -50782,7 +50785,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G1709" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -50808,7 +50811,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1710" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -50834,7 +50837,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1711" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -50860,7 +50863,7 @@
         <v>11.75</v>
       </c>
       <c r="G1712" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -50886,7 +50889,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1713" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -50912,7 +50915,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1714" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -50938,7 +50941,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G1715" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -50964,7 +50967,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1716" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -50990,7 +50993,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G1717" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -51016,7 +51019,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1718" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -51042,7 +51045,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1719" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -51068,7 +51071,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1720" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -51094,7 +51097,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1721" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -51120,7 +51123,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1722" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -51146,7 +51149,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1723" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -51172,7 +51175,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1724" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -51198,7 +51201,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1725" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -51224,7 +51227,7 @@
         <v>11.75</v>
       </c>
       <c r="G1726" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -51250,7 +51253,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1727" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -51276,7 +51279,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1728" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -51302,7 +51305,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1729" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -51328,7 +51331,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1730" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -51354,7 +51357,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1731" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -51380,7 +51383,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G1732" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -51406,7 +51409,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G1733" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -51432,7 +51435,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1734" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -51458,7 +51461,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1735" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -51484,7 +51487,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G1736" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -51510,7 +51513,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G1737" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -51536,7 +51539,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1738" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -51562,7 +51565,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G1739" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -51588,7 +51591,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G1740" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -51614,7 +51617,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G1741" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -51640,7 +51643,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1742" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -51666,7 +51669,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1743" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -51692,7 +51695,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1744" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -51718,7 +51721,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1745" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -51744,7 +51747,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1746" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -51770,7 +51773,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1747" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -51796,7 +51799,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1748" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -51822,7 +51825,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G1749" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -51848,7 +51851,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G1750" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -51874,7 +51877,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1751" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -51900,7 +51903,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1752" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -51926,7 +51929,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G1753" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -51952,7 +51955,7 @@
         <v>12.710000038147</v>
       </c>
       <c r="G1754" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -51978,7 +51981,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1755" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -52004,7 +52007,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1756" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -52030,7 +52033,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1757" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -52056,7 +52059,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1758" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -52082,7 +52085,7 @@
         <v>12.75</v>
       </c>
       <c r="G1759" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -52108,7 +52111,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1760" t="s">
-        <v>50</v>
+        <v>1463</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -52134,7 +52137,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1761" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -52186,7 +52189,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1763" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -52238,7 +52241,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1765" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -52368,7 +52371,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1770" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -52446,7 +52449,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1773" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -52472,7 +52475,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1774" t="s">
-        <v>50</v>
+        <v>1463</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -52524,7 +52527,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G1776" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -52628,7 +52631,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G1780" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -52654,7 +52657,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G1781" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -52680,7 +52683,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1782" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -52706,7 +52709,7 @@
         <v>13</v>
       </c>
       <c r="G1783" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -52784,7 +52787,7 @@
         <v>13.5</v>
       </c>
       <c r="G1786" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -53330,7 +53333,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1807" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -53824,7 +53827,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1826" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -54214,7 +54217,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1841" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -54448,7 +54451,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1850" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -54708,7 +54711,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -54864,7 +54867,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G1866" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -54916,7 +54919,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G1868" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -71850,7 +71853,7 @@
     </row>
     <row r="2520">
       <c r="A2520" s="1" t="n">
-        <v>45987.6912152778</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2520" t="n">
         <v>121865</v>
@@ -71871,6 +71874,32 @@
         <v>2001</v>
       </c>
       <c r="H2520" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" s="1" t="n">
+        <v>45988.69125</v>
+      </c>
+      <c r="B2521" t="n">
+        <v>97762</v>
+      </c>
+      <c r="C2521" t="n">
+        <v>6.46000003814697</v>
+      </c>
+      <c r="D2521" t="n">
+        <v>6.28000020980835</v>
+      </c>
+      <c r="E2521" t="n">
+        <v>6.28000020980835</v>
+      </c>
+      <c r="F2521" t="n">
+        <v>6.44999980926514</v>
+      </c>
+      <c r="G2521" t="s">
+        <v>2002</v>
+      </c>
+      <c r="H2521" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2523975372314</t>
+    <t xml:space="preserve">13.2523984909058</t>
   </si>
   <si>
     <t xml:space="preserve">BSS.MI</t>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">12.9788007736206</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7479515075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3974046707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.243504524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2606058120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1409072875977</t>
+    <t xml:space="preserve">12.7479524612427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.397403717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2435054779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2606048583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1409063339233</t>
   </si>
   <si>
     <t xml:space="preserve">11.4825620651245</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">10.858416557312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79822540283203</t>
+    <t xml:space="preserve">9.79822444915771</t>
   </si>
   <si>
     <t xml:space="preserve">10.3539695739746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84952354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4736700057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2941198348999</t>
+    <t xml:space="preserve">9.84952449798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.473669052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2941217422485</t>
   </si>
   <si>
     <t xml:space="preserve">10.7814664840698</t>
@@ -89,31 +89,31 @@
     <t xml:space="preserve">10.8156661987305</t>
   </si>
   <si>
-    <t xml:space="preserve">10.730167388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.576268196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6361169815063</t>
+    <t xml:space="preserve">10.7301664352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5762672424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.636118888855</t>
   </si>
   <si>
     <t xml:space="preserve">10.191520690918</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4565696716309</t>
+    <t xml:space="preserve">10.4565677642822</t>
   </si>
   <si>
     <t xml:space="preserve">10.4907703399658</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0205240249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03728008270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97743225097656</t>
+    <t xml:space="preserve">10.0205221176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03727912902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97743129730225</t>
   </si>
   <si>
     <t xml:space="preserve">9.40492725372314</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">9.43057727813721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90082263946533</t>
+    <t xml:space="preserve">9.90082359313965</t>
   </si>
   <si>
     <t xml:space="preserve">9.66142559051514</t>
@@ -134,19 +134,19 @@
     <t xml:space="preserve">10.4394702911377</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3454208374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2000732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0037641525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5506181716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2257213592529</t>
+    <t xml:space="preserve">10.345419883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2000713348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0037651062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5506191253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2257204055786</t>
   </si>
   <si>
     <t xml:space="preserve">10.1829719543457</t>
@@ -161,22 +161,22 @@
     <t xml:space="preserve">11.8074588775635</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9442596435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1067066192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7732601165771</t>
+    <t xml:space="preserve">11.9442586898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1067056655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7732582092285</t>
   </si>
   <si>
     <t xml:space="preserve">11.9699077606201</t>
   </si>
   <si>
-    <t xml:space="preserve">11.627911567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.371413230896</t>
+    <t xml:space="preserve">11.6279096603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3714122772217</t>
   </si>
   <si>
     <t xml:space="preserve">11.3799629211426</t>
@@ -185,10 +185,10 @@
     <t xml:space="preserve">11.662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8416585922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9186086654663</t>
+    <t xml:space="preserve">11.8416595458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.918607711792</t>
   </si>
   <si>
     <t xml:space="preserve">11.7989091873169</t>
@@ -197,13 +197,13 @@
     <t xml:space="preserve">12.046856880188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1922054290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.200756072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3375558853149</t>
+    <t xml:space="preserve">12.1922073364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2007551193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3375549316406</t>
   </si>
   <si>
     <t xml:space="preserve">12.1323556900024</t>
@@ -212,79 +212,79 @@
     <t xml:space="preserve">12.1665563583374</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2178564071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9015073776245</t>
+    <t xml:space="preserve">12.2178554534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9015092849731</t>
   </si>
   <si>
     <t xml:space="preserve">11.5680599212646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2859125137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7390594482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.884407043457</t>
+    <t xml:space="preserve">11.2859134674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7390584945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8844079971313</t>
   </si>
   <si>
     <t xml:space="preserve">11.8160085678101</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7048597335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6022605895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6364603042603</t>
+    <t xml:space="preserve">11.7048587799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6022596359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6364593505859</t>
   </si>
   <si>
     <t xml:space="preserve">11.4740114212036</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1918649673462</t>
+    <t xml:space="preserve">11.1918640136719</t>
   </si>
   <si>
     <t xml:space="preserve">11.1063652038574</t>
   </si>
   <si>
-    <t xml:space="preserve">11.114914894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3201122283936</t>
+    <t xml:space="preserve">11.1149139404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3201112747192</t>
   </si>
   <si>
     <t xml:space="preserve">11.3457622528076</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1576642990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0550661087036</t>
+    <t xml:space="preserve">11.1576633453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0550670623779</t>
   </si>
   <si>
     <t xml:space="preserve">10.986665725708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1405630111694</t>
+    <t xml:space="preserve">11.1405639648438</t>
   </si>
   <si>
     <t xml:space="preserve">10.60191822052</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9541416168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4346122741699</t>
+    <t xml:space="preserve">10.954140663147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4346132278442</t>
   </si>
   <si>
     <t xml:space="preserve">10.3553619384766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2232780456543</t>
+    <t xml:space="preserve">10.2232789993286</t>
   </si>
   <si>
     <t xml:space="preserve">10.2673063278198</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">10.003137588501</t>
   </si>
   <si>
-    <t xml:space="preserve">10.302526473999</t>
+    <t xml:space="preserve">10.3025274276733</t>
   </si>
   <si>
     <t xml:space="preserve">10.2496948242188</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">10.6107234954834</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4120311737061</t>
+    <t xml:space="preserve">11.4120302200317</t>
   </si>
   <si>
     <t xml:space="preserve">11.1302528381348</t>
@@ -317,55 +317,55 @@
     <t xml:space="preserve">10.9189186096191</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2359209060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2799482345581</t>
+    <t xml:space="preserve">11.2359199523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2799472808838</t>
   </si>
   <si>
     <t xml:space="preserve">11.0069742202759</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8308639526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8396682739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9277238845825</t>
+    <t xml:space="preserve">10.8308629989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8396692276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9277229309082</t>
   </si>
   <si>
     <t xml:space="preserve">10.9101133346558</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8132514953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5138626098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0647783279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99433326721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95030689239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68613815307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0383596420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4962501525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3465557098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4522228240967</t>
+    <t xml:space="preserve">10.813250541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.513861656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0647792816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99433422088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9503059387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68613719940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0383605957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4962511062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3465566635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4522218704224</t>
   </si>
   <si>
     <t xml:space="preserve">10.5843076705933</t>
@@ -380,19 +380,19 @@
     <t xml:space="preserve">9.67733097076416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57166576385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93269443511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1880559921265</t>
+    <t xml:space="preserve">9.57166481018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93269348144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1880569458008</t>
   </si>
   <si>
     <t xml:space="preserve">9.98552703857422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18422031402588</t>
+    <t xml:space="preserve">9.1842212677002</t>
   </si>
   <si>
     <t xml:space="preserve">9.14019203186035</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">9.721360206604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0823888778687</t>
+    <t xml:space="preserve">10.0823879241943</t>
   </si>
   <si>
     <t xml:space="preserve">10.381778717041</t>
@@ -416,25 +416,25 @@
     <t xml:space="preserve">10.2144718170166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1528348922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6987791061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0774202346802</t>
+    <t xml:space="preserve">10.1528329849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6987781524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0774192810059</t>
   </si>
   <si>
     <t xml:space="preserve">11.0157804489136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0333919525146</t>
+    <t xml:space="preserve">11.0333909988403</t>
   </si>
   <si>
     <t xml:space="preserve">10.9893636703491</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8748922348022</t>
+    <t xml:space="preserve">10.8748912811279</t>
   </si>
   <si>
     <t xml:space="preserve">11.0950298309326</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">10.7251958847046</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0510025024414</t>
+    <t xml:space="preserve">11.0510015487671</t>
   </si>
   <si>
     <t xml:space="preserve">10.9013080596924</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">11.1654758453369</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0598087310791</t>
+    <t xml:space="preserve">11.0598077774048</t>
   </si>
   <si>
     <t xml:space="preserve">11.2183074951172</t>
@@ -467,16 +467,16 @@
     <t xml:space="preserve">11.1214475631714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1830863952637</t>
+    <t xml:space="preserve">11.1830854415894</t>
   </si>
   <si>
     <t xml:space="preserve">11.2623357772827</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5265045166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7466430664062</t>
+    <t xml:space="preserve">11.5265054702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7466440200806</t>
   </si>
   <si>
     <t xml:space="preserve">11.773060798645</t>
@@ -485,25 +485,25 @@
     <t xml:space="preserve">11.6850051879883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7994766235352</t>
+    <t xml:space="preserve">11.7994775772095</t>
   </si>
   <si>
     <t xml:space="preserve">11.6497821807861</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6673936843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4472532272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.323974609375</t>
+    <t xml:space="preserve">11.6673927307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4472541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3239755630493</t>
   </si>
   <si>
     <t xml:space="preserve">11.3680038452148</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1390571594238</t>
+    <t xml:space="preserve">11.1390581130981</t>
   </si>
   <si>
     <t xml:space="preserve">11.6938095092773</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">12.0548391342163</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0636444091797</t>
+    <t xml:space="preserve">12.0636434555054</t>
   </si>
   <si>
     <t xml:space="preserve">12.5039234161377</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5303392410278</t>
+    <t xml:space="preserve">12.5303401947021</t>
   </si>
   <si>
     <t xml:space="preserve">12.4070615768433</t>
@@ -545,16 +545,16 @@
     <t xml:space="preserve">12.8121194839478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8561477661133</t>
+    <t xml:space="preserve">12.856146812439</t>
   </si>
   <si>
     <t xml:space="preserve">13.0322580337524</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4108963012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5782051086426</t>
+    <t xml:space="preserve">13.4108972549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5782041549683</t>
   </si>
   <si>
     <t xml:space="preserve">13.6838703155518</t>
@@ -569,19 +569,19 @@
     <t xml:space="preserve">14.2210111618042</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2562351226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1329545974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1241502761841</t>
+    <t xml:space="preserve">14.2562341690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1329555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1241512298584</t>
   </si>
   <si>
     <t xml:space="preserve">14.0713157653809</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9216213226318</t>
+    <t xml:space="preserve">13.9216203689575</t>
   </si>
   <si>
     <t xml:space="preserve">13.7807321548462</t>
@@ -605,40 +605,40 @@
     <t xml:space="preserve">13.375675201416</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1555347442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6486492156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5605926513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.736704826355</t>
+    <t xml:space="preserve">13.155535697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6486482620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5605916976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7367038726807</t>
   </si>
   <si>
     <t xml:space="preserve">13.8775939941406</t>
   </si>
   <si>
-    <t xml:space="preserve">14.176983833313</t>
+    <t xml:space="preserve">14.1769847869873</t>
   </si>
   <si>
     <t xml:space="preserve">14.0977334976196</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7845697402954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3040952682495</t>
+    <t xml:space="preserve">14.7845706939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3040971755981</t>
   </si>
   <si>
     <t xml:space="preserve">15.2776803970337</t>
   </si>
   <si>
-    <t xml:space="preserve">15.489013671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4978170394897</t>
+    <t xml:space="preserve">15.4890165328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.497820854187</t>
   </si>
   <si>
     <t xml:space="preserve">15.3657388687134</t>
@@ -647,10 +647,10 @@
     <t xml:space="preserve">15.4449882507324</t>
   </si>
   <si>
-    <t xml:space="preserve">15.339319229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5330448150635</t>
+    <t xml:space="preserve">15.3393211364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5330429077148</t>
   </si>
   <si>
     <t xml:space="preserve">15.6651258468628</t>
@@ -659,46 +659,46 @@
     <t xml:space="preserve">15.5418491363525</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2424583435059</t>
+    <t xml:space="preserve">15.2424602508545</t>
   </si>
   <si>
     <t xml:space="preserve">15.8060150146484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1934604644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3695735931396</t>
+    <t xml:space="preserve">16.1934585571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.369571685791</t>
   </si>
   <si>
     <t xml:space="preserve">16.4664325714111</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5104637145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0387992858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8891010284424</t>
+    <t xml:space="preserve">16.510461807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.03879737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8890991210938</t>
   </si>
   <si>
     <t xml:space="preserve">17.1532688140869</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7746295928955</t>
+    <t xml:space="preserve">16.7746276855469</t>
   </si>
   <si>
     <t xml:space="preserve">16.5544891357422</t>
   </si>
   <si>
-    <t xml:space="preserve">16.237491607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5897121429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6513500213623</t>
+    <t xml:space="preserve">16.2374897003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5897102355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6513519287109</t>
   </si>
   <si>
     <t xml:space="preserve">16.5721015930176</t>
@@ -710,13 +710,13 @@
     <t xml:space="preserve">16.7041835784912</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8802947998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8538780212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0123805999756</t>
+    <t xml:space="preserve">16.8802967071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8538761138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.012378692627</t>
   </si>
   <si>
     <t xml:space="preserve">17.2941589355469</t>
@@ -728,34 +728,34 @@
     <t xml:space="preserve">16.5368785858154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0828247070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8626861572266</t>
+    <t xml:space="preserve">17.0828266143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8626842498779</t>
   </si>
   <si>
     <t xml:space="preserve">17.2061061859131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3469905853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6551876068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.540714263916</t>
+    <t xml:space="preserve">17.3469924926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6551895141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5407123565674</t>
   </si>
   <si>
     <t xml:space="preserve">17.5054912567139</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7168273925781</t>
+    <t xml:space="preserve">17.7168292999268</t>
   </si>
   <si>
     <t xml:space="preserve">17.4526596069336</t>
   </si>
   <si>
-    <t xml:space="preserve">17.55832862854</t>
+    <t xml:space="preserve">17.5583267211914</t>
   </si>
   <si>
     <t xml:space="preserve">17.7432441711426</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">17.5759353637695</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7482147216797</t>
+    <t xml:space="preserve">16.7482128143311</t>
   </si>
   <si>
     <t xml:space="preserve">16.7658233642578</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">17.162073135376</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2765483856201</t>
+    <t xml:space="preserve">17.2765502929688</t>
   </si>
   <si>
     <t xml:space="preserve">16.6865749359131</t>
@@ -800,40 +800,40 @@
     <t xml:space="preserve">17.391019821167</t>
   </si>
   <si>
-    <t xml:space="preserve">17.250129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4350452423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.373405456543</t>
+    <t xml:space="preserve">17.2501316070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4350471496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3734073638916</t>
   </si>
   <si>
     <t xml:space="preserve">17.6463832855225</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9457702636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3722763061523</t>
+    <t xml:space="preserve">17.9457721710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3722743988037</t>
   </si>
   <si>
     <t xml:space="preserve">19.9358310699463</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3849182128906</t>
+    <t xml:space="preserve">20.384916305542</t>
   </si>
   <si>
     <t xml:space="preserve">20.5962524414062</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3408889770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8340015411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0453338623047</t>
+    <t xml:space="preserve">20.3408908843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8340034484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.045337677002</t>
   </si>
   <si>
     <t xml:space="preserve">21.5824737548828</t>
@@ -842,16 +842,16 @@
     <t xml:space="preserve">21.0893630981445</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3271141052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6529159545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7497844696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9170894622803</t>
+    <t xml:space="preserve">21.327112197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6529178619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7497825622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9170875549316</t>
   </si>
   <si>
     <t xml:space="preserve">21.8114204406738</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">22.0139484405518</t>
   </si>
   <si>
-    <t xml:space="preserve">22.286922454834</t>
+    <t xml:space="preserve">22.2869205474854</t>
   </si>
   <si>
     <t xml:space="preserve">22.2605056762695</t>
   </si>
   <si>
-    <t xml:space="preserve">22.348560333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3221473693848</t>
+    <t xml:space="preserve">22.3485584259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3221454620361</t>
   </si>
   <si>
     <t xml:space="preserve">22.1900596618652</t>
@@ -884,25 +884,25 @@
     <t xml:space="preserve">22.4806461334229</t>
   </si>
   <si>
-    <t xml:space="preserve">22.665563583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6215324401855</t>
+    <t xml:space="preserve">22.6655616760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6215343475342</t>
   </si>
   <si>
     <t xml:space="preserve">22.6743679046631</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8945064544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0970344543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8328685760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3749771118164</t>
+    <t xml:space="preserve">22.8945083618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0970363616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8328666687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.374979019165</t>
   </si>
   <si>
     <t xml:space="preserve">23.1938991546631</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">23.3876190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5108985900879</t>
+    <t xml:space="preserve">23.5108966827393</t>
   </si>
   <si>
     <t xml:space="preserve">23.9159545898438</t>
@@ -923,19 +923,19 @@
     <t xml:space="preserve">24.7084560394287</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6556224822998</t>
+    <t xml:space="preserve">24.6556243896484</t>
   </si>
   <si>
     <t xml:space="preserve">24.9197902679443</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0870971679688</t>
+    <t xml:space="preserve">25.0870952606201</t>
   </si>
   <si>
     <t xml:space="preserve">24.9638175964355</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8933753967285</t>
+    <t xml:space="preserve">24.8933715820312</t>
   </si>
   <si>
     <t xml:space="preserve">26.4255447387695</t>
@@ -71969,7 +71969,7 @@
     </row>
     <row r="2524">
       <c r="A2524" s="1" t="n">
-        <v>45993.6912268518</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B2524" t="n">
         <v>101773</v>
@@ -71990,6 +71990,32 @@
         <v>2006</v>
       </c>
       <c r="H2524" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" s="1" t="n">
+        <v>45994.6911805556</v>
+      </c>
+      <c r="B2525" t="n">
+        <v>293362</v>
+      </c>
+      <c r="C2525" t="n">
+        <v>7.13000011444092</v>
+      </c>
+      <c r="D2525" t="n">
+        <v>6.57000017166138</v>
+      </c>
+      <c r="E2525" t="n">
+        <v>6.63000011444092</v>
+      </c>
+      <c r="F2525" t="n">
+        <v>7.05000019073486</v>
+      </c>
+      <c r="G2525" t="s">
+        <v>1921</v>
+      </c>
+      <c r="H2525" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2010" uniqueCount="2010">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2011" uniqueCount="2011">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,61 +38,61 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2523975372314</t>
+    <t xml:space="preserve">13.2523965835571</t>
   </si>
   <si>
     <t xml:space="preserve">BSS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9787998199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7479515075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.397403717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2435064315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2606048583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1409072875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4825630187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.858416557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79822540283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3539695739746</t>
+    <t xml:space="preserve">12.9788007736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7479524612427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3974056243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2435054779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2606058120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.140905380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4825611114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8584156036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7982234954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3539714813232</t>
   </si>
   <si>
     <t xml:space="preserve">9.84952354431152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4736680984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2941207885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7814655303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8156652450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.730167388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5762672424316</t>
+    <t xml:space="preserve">10.4736700057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2941217422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7814664840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8156661987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7301664352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.576268196106</t>
   </si>
   <si>
     <t xml:space="preserve">10.636118888855</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">10.1915216445923</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4565687179565</t>
+    <t xml:space="preserve">10.4565696716309</t>
   </si>
   <si>
     <t xml:space="preserve">10.4907703399658</t>
@@ -113,19 +113,19 @@
     <t xml:space="preserve">9.03728008270264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97743225097656</t>
+    <t xml:space="preserve">8.97743034362793</t>
   </si>
   <si>
     <t xml:space="preserve">9.40492725372314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14842891693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43057823181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90082454681396</t>
+    <t xml:space="preserve">9.14842987060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43057727813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90082359313965</t>
   </si>
   <si>
     <t xml:space="preserve">9.66142559051514</t>
@@ -134,22 +134,22 @@
     <t xml:space="preserve">10.4394693374634</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3454208374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2000722885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0037670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5506200790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2257194519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1829710006714</t>
+    <t xml:space="preserve">10.3454217910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2000713348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0037660598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5506191253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2257213592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.18297290802</t>
   </si>
   <si>
     <t xml:space="preserve">11.0379648208618</t>
@@ -164,70 +164,70 @@
     <t xml:space="preserve">11.9442577362061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1067056655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7732601165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9699068069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6279106140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.371413230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3799629211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6621103286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8416576385498</t>
+    <t xml:space="preserve">12.1067066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7732591629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9699077606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.627911567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3714122772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3799619674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6621112823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8416566848755</t>
   </si>
   <si>
     <t xml:space="preserve">11.9186086654663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7989082336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0468559265137</t>
+    <t xml:space="preserve">11.7989091873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0468578338623</t>
   </si>
   <si>
     <t xml:space="preserve">12.1922054290771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.200756072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3375549316406</t>
+    <t xml:space="preserve">12.2007551193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3375558853149</t>
   </si>
   <si>
     <t xml:space="preserve">12.1323556900024</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1665563583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2178554534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9015083312988</t>
+    <t xml:space="preserve">12.1665554046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2178573608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9015073776245</t>
   </si>
   <si>
     <t xml:space="preserve">11.568060874939</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2859125137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7390584945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.884407043457</t>
+    <t xml:space="preserve">11.2859134674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7390594482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8844079971313</t>
   </si>
   <si>
     <t xml:space="preserve">11.8160085678101</t>
@@ -236,16 +236,16 @@
     <t xml:space="preserve">11.7048597335815</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6022615432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6364603042603</t>
+    <t xml:space="preserve">11.6022605895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6364612579346</t>
   </si>
   <si>
     <t xml:space="preserve">11.4740114212036</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1918649673462</t>
+    <t xml:space="preserve">11.1918630599976</t>
   </si>
   <si>
     <t xml:space="preserve">11.1063642501831</t>
@@ -257,22 +257,22 @@
     <t xml:space="preserve">11.3201122283936</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457622528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1576642990112</t>
+    <t xml:space="preserve">11.3457632064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1576633453369</t>
   </si>
   <si>
     <t xml:space="preserve">11.0550651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.986665725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1405639648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.60191822052</t>
+    <t xml:space="preserve">10.9866666793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1405630111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6019172668457</t>
   </si>
   <si>
     <t xml:space="preserve">10.9541416168213</t>
@@ -284,10 +284,10 @@
     <t xml:space="preserve">10.3553619384766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2232780456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2673063278198</t>
+    <t xml:space="preserve">10.2232789993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2673044204712</t>
   </si>
   <si>
     <t xml:space="preserve">9.92388820648193</t>
@@ -299,10 +299,10 @@
     <t xml:space="preserve">10.003137588501</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3025274276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2496948242188</t>
+    <t xml:space="preserve">10.302529335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2496938705444</t>
   </si>
   <si>
     <t xml:space="preserve">10.6107234954834</t>
@@ -311,16 +311,16 @@
     <t xml:space="preserve">11.4120311737061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1302528381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9189195632935</t>
+    <t xml:space="preserve">11.1302518844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9189176559448</t>
   </si>
   <si>
     <t xml:space="preserve">11.2359189987183</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2799472808838</t>
+    <t xml:space="preserve">11.2799482345581</t>
   </si>
   <si>
     <t xml:space="preserve">11.0069742202759</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">10.8308629989624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8396682739258</t>
+    <t xml:space="preserve">10.8396692276001</t>
   </si>
   <si>
     <t xml:space="preserve">10.9277229309082</t>
@@ -344,118 +344,118 @@
     <t xml:space="preserve">10.513861656189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0647792816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99433326721191</t>
+    <t xml:space="preserve">10.0647783279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9943323135376</t>
   </si>
   <si>
     <t xml:space="preserve">9.95030498504639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68613815307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0383596420288</t>
+    <t xml:space="preserve">9.68613719940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0383605957031</t>
   </si>
   <si>
     <t xml:space="preserve">10.4962511062622</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3465557098389</t>
+    <t xml:space="preserve">10.3465566635132</t>
   </si>
   <si>
     <t xml:space="preserve">10.452223777771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5843086242676</t>
+    <t xml:space="preserve">10.5843067169189</t>
   </si>
   <si>
     <t xml:space="preserve">9.87986087799072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12257957458496</t>
+    <t xml:space="preserve">9.12258052825928</t>
   </si>
   <si>
     <t xml:space="preserve">9.67733097076416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57166481018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93269348144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1880540847778</t>
+    <t xml:space="preserve">9.57166576385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.932692527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1880550384521</t>
   </si>
   <si>
     <t xml:space="preserve">9.98552703857422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18421840667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14019107818604</t>
+    <t xml:space="preserve">9.18421936035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14019203186035</t>
   </si>
   <si>
     <t xml:space="preserve">9.721360206604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0823888778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3817777633667</t>
+    <t xml:space="preserve">10.0823879241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.381778717041</t>
   </si>
   <si>
     <t xml:space="preserve">10.2849178314209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1352224349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2144718170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1528339385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6987791061401</t>
+    <t xml:space="preserve">10.1352233886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2144727706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.15283203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6987800598145</t>
   </si>
   <si>
     <t xml:space="preserve">11.0774192810059</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0157794952393</t>
+    <t xml:space="preserve">11.0157804489136</t>
   </si>
   <si>
     <t xml:space="preserve">11.0333909988403</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9893636703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8748912811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0950307846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2535305023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3151702880859</t>
+    <t xml:space="preserve">10.9893627166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8748922348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0950298309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2535314559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3151712417603</t>
   </si>
   <si>
     <t xml:space="preserve">10.7251968383789</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0510025024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9013080596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1654758453369</t>
+    <t xml:space="preserve">11.0510015487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9013071060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1654748916626</t>
   </si>
   <si>
     <t xml:space="preserve">11.0598077774048</t>
@@ -467,37 +467,37 @@
     <t xml:space="preserve">11.1214475631714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1830863952637</t>
+    <t xml:space="preserve">11.1830854415894</t>
   </si>
   <si>
     <t xml:space="preserve">11.2623357772827</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5265045166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7466430664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.773060798645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.685004234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7994756698608</t>
+    <t xml:space="preserve">11.5265035629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7466440200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7730598449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6850051879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7994766235352</t>
   </si>
   <si>
     <t xml:space="preserve">11.6497821807861</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6673936843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4472541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.323974609375</t>
+    <t xml:space="preserve">11.6673946380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4472532272339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3239755630493</t>
   </si>
   <si>
     <t xml:space="preserve">11.3680038452148</t>
@@ -506,49 +506,49 @@
     <t xml:space="preserve">11.1390571594238</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6938095092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.614559173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8258943557739</t>
+    <t xml:space="preserve">11.6938104629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6145601272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8258934020996</t>
   </si>
   <si>
     <t xml:space="preserve">12.0372276306152</t>
   </si>
   <si>
-    <t xml:space="preserve">12.054838180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0636434555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5039234161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5303401947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4070615768433</t>
+    <t xml:space="preserve">12.0548391342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0636444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5039224624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5303382873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4070625305176</t>
   </si>
   <si>
     <t xml:space="preserve">12.2837829589844</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6007843017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9177856445312</t>
+    <t xml:space="preserve">12.6007852554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9177865982056</t>
   </si>
   <si>
     <t xml:space="preserve">12.8121194839478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8561477661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0322589874268</t>
+    <t xml:space="preserve">12.856146812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0322580337524</t>
   </si>
   <si>
     <t xml:space="preserve">13.4108972549438</t>
@@ -557,76 +557,76 @@
     <t xml:space="preserve">13.5782032012939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6838722229004</t>
+    <t xml:space="preserve">13.6838703155518</t>
   </si>
   <si>
     <t xml:space="preserve">13.4285087585449</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3707056045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2210111618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2562351226807</t>
+    <t xml:space="preserve">14.3707065582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2210121154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2562341690063</t>
   </si>
   <si>
     <t xml:space="preserve">14.1329545974731</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1241512298584</t>
+    <t xml:space="preserve">14.1241502761841</t>
   </si>
   <si>
     <t xml:space="preserve">14.0713148117065</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9216213226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7807312011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6046199798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7631206512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8335657119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.727897644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1995630264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.375675201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1555347442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6486492156982</t>
+    <t xml:space="preserve">13.9216222763062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7807321548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6046209335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7631196975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8335647583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7278985977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1995639801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3756761550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.155535697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6486482620239</t>
   </si>
   <si>
     <t xml:space="preserve">13.5605926513672</t>
   </si>
   <si>
-    <t xml:space="preserve">13.736704826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8775930404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.176983833313</t>
+    <t xml:space="preserve">13.7367038726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8775939941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1769828796387</t>
   </si>
   <si>
     <t xml:space="preserve">14.0977334976196</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7845706939697</t>
+    <t xml:space="preserve">14.7845678329468</t>
   </si>
   <si>
     <t xml:space="preserve">15.3040971755981</t>
@@ -635,46 +635,46 @@
     <t xml:space="preserve">15.2776823043823</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4890127182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4978199005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3657388687134</t>
+    <t xml:space="preserve">15.4890146255493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4978227615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3657369613647</t>
   </si>
   <si>
     <t xml:space="preserve">15.4449872970581</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3393211364746</t>
+    <t xml:space="preserve">15.3393201828003</t>
   </si>
   <si>
     <t xml:space="preserve">15.5330429077148</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6651258468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5418481826782</t>
+    <t xml:space="preserve">15.6651277542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5418491363525</t>
   </si>
   <si>
     <t xml:space="preserve">15.2424573898315</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8060150146484</t>
+    <t xml:space="preserve">15.8060169219971</t>
   </si>
   <si>
     <t xml:space="preserve">16.1934604644775</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3695755004883</t>
+    <t xml:space="preserve">16.3695774078369</t>
   </si>
   <si>
     <t xml:space="preserve">16.4664363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.510461807251</t>
+    <t xml:space="preserve">16.5104656219482</t>
   </si>
   <si>
     <t xml:space="preserve">17.0387954711914</t>
@@ -686,13 +686,13 @@
     <t xml:space="preserve">17.1532688140869</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7746276855469</t>
+    <t xml:space="preserve">16.7746257781982</t>
   </si>
   <si>
     <t xml:space="preserve">16.5544891357422</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2374897003174</t>
+    <t xml:space="preserve">16.2374877929688</t>
   </si>
   <si>
     <t xml:space="preserve">16.5897121429443</t>
@@ -701,67 +701,67 @@
     <t xml:space="preserve">16.6513519287109</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5721015930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9947719573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7041835784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8802967071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8538761138916</t>
+    <t xml:space="preserve">16.5720996856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9947681427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7041854858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8802947998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8538799285889</t>
   </si>
   <si>
     <t xml:space="preserve">17.012378692627</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2941589355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1268520355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5368766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0828266143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8626861572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2061042785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3469924926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6551876068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.540714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5054931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7168292999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.452657699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5583248138428</t>
+    <t xml:space="preserve">17.2941551208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1268539428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5368804931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0828227996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8626842498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2061023712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3469944000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6551856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5407161712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5054912567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7168254852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4526596069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5583267211914</t>
   </si>
   <si>
     <t xml:space="preserve">17.7432422637939</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8401050567627</t>
+    <t xml:space="preserve">17.8401031494141</t>
   </si>
   <si>
     <t xml:space="preserve">17.5759372711182</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">16.7482109069824</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7658252716064</t>
+    <t xml:space="preserve">16.7658233642578</t>
   </si>
   <si>
     <t xml:space="preserve">16.9507389068604</t>
@@ -779,13 +779,13 @@
     <t xml:space="preserve">17.1620750427246</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2765502929688</t>
+    <t xml:space="preserve">17.2765464782715</t>
   </si>
   <si>
     <t xml:space="preserve">16.6865730285645</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1092395782471</t>
+    <t xml:space="preserve">17.1092414855957</t>
   </si>
   <si>
     <t xml:space="preserve">16.8186588287354</t>
@@ -794,64 +794,64 @@
     <t xml:space="preserve">17.2325191497803</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2853527069092</t>
+    <t xml:space="preserve">17.2853507995605</t>
   </si>
   <si>
     <t xml:space="preserve">17.391019821167</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2501316070557</t>
+    <t xml:space="preserve">17.250129699707</t>
   </si>
   <si>
     <t xml:space="preserve">17.4350471496582</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3734092712402</t>
+    <t xml:space="preserve">17.3734073638916</t>
   </si>
   <si>
     <t xml:space="preserve">17.6463813781738</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9457721710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3722763061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9358310699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3849201202393</t>
+    <t xml:space="preserve">17.9457702636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3722743988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9358329772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3849182128906</t>
   </si>
   <si>
     <t xml:space="preserve">20.5962524414062</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3408908843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8340034484863</t>
+    <t xml:space="preserve">20.3408889770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8339996337891</t>
   </si>
   <si>
     <t xml:space="preserve">21.0453357696533</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5824756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0893650054932</t>
+    <t xml:space="preserve">21.5824775695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0893669128418</t>
   </si>
   <si>
     <t xml:space="preserve">21.3271141052246</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6529197692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7497825622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.917085647583</t>
+    <t xml:space="preserve">21.6529216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7497844696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9170875549316</t>
   </si>
   <si>
     <t xml:space="preserve">21.8114223480225</t>
@@ -863,19 +863,19 @@
     <t xml:space="preserve">22.2869205474854</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2605056762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3485584259033</t>
+    <t xml:space="preserve">22.2605037689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3485565185547</t>
   </si>
   <si>
     <t xml:space="preserve">22.3221454620361</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1900615692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6303405761719</t>
+    <t xml:space="preserve">22.1900596618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6303424835205</t>
   </si>
   <si>
     <t xml:space="preserve">22.4366149902344</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">22.4806461334229</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6655654907227</t>
+    <t xml:space="preserve">22.665563583374</t>
   </si>
   <si>
     <t xml:space="preserve">22.6215343475342</t>
@@ -893,13 +893,13 @@
     <t xml:space="preserve">22.6743679046631</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8945083618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0970363616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8328685760498</t>
+    <t xml:space="preserve">22.8945064544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0970344543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8328666687012</t>
   </si>
   <si>
     <t xml:space="preserve">22.3749771118164</t>
@@ -908,28 +908,28 @@
     <t xml:space="preserve">23.1938972473145</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3876190185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5108985900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9159545898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2417602539062</t>
+    <t xml:space="preserve">23.3876209259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5109004974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9159526824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2417621612549</t>
   </si>
   <si>
     <t xml:space="preserve">24.7084560394287</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6556224822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9197902679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0870933532715</t>
+    <t xml:space="preserve">24.6556243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9197883605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0870952606201</t>
   </si>
   <si>
     <t xml:space="preserve">24.9638195037842</t>
@@ -938,76 +938,76 @@
     <t xml:space="preserve">24.8933734893799</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4255466461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4879302978516</t>
+    <t xml:space="preserve">26.4255447387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4879322052002</t>
   </si>
   <si>
     <t xml:space="preserve">27.3970069885254</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6287326812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1545677185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6732940673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6804084777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3666687011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8069839477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4665069580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0190811157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4914455413818</t>
+    <t xml:space="preserve">27.6287307739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1545696258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6732921600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6804046630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3666706085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8069820404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4665050506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0190830230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4914436340332</t>
   </si>
   <si>
     <t xml:space="preserve">29.7677345275879</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8746776580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3024787902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7748413085938</t>
+    <t xml:space="preserve">29.8746814727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3024806976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7748432159424</t>
   </si>
   <si>
     <t xml:space="preserve">30.2400913238525</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6678924560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8283176422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8996162414551</t>
+    <t xml:space="preserve">30.6678943634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8283157348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8996181488037</t>
   </si>
   <si>
     <t xml:space="preserve">31.0154781341553</t>
   </si>
   <si>
-    <t xml:space="preserve">30.997652053833</t>
+    <t xml:space="preserve">30.9976539611816</t>
   </si>
   <si>
     <t xml:space="preserve">30.935266494751</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6500663757324</t>
+    <t xml:space="preserve">30.6500701904297</t>
   </si>
   <si>
     <t xml:space="preserve">30.7481079101562</t>
@@ -1016,16 +1016,16 @@
     <t xml:space="preserve">30.685718536377</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3577556610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5003528594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3131923675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2775421142578</t>
+    <t xml:space="preserve">29.3577537536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5003547668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3131942749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2775440216064</t>
   </si>
   <si>
     <t xml:space="preserve">30.1687908172607</t>
@@ -1034,19 +1034,19 @@
     <t xml:space="preserve">30.1331424713135</t>
   </si>
   <si>
-    <t xml:space="preserve">29.999454498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9281597137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0529327392578</t>
+    <t xml:space="preserve">29.9994564056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9281539916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0529308319092</t>
   </si>
   <si>
     <t xml:space="preserve">29.4825344085693</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8122940063477</t>
+    <t xml:space="preserve">29.8122959136963</t>
   </si>
   <si>
     <t xml:space="preserve">28.9121322631836</t>
@@ -1058,34 +1058,34 @@
     <t xml:space="preserve">27.7713317871094</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9674072265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2544078826904</t>
+    <t xml:space="preserve">27.9674034118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2544040679932</t>
   </si>
   <si>
     <t xml:space="preserve">27.6911182403564</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4861335754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5752563476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1189193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.350643157959</t>
+    <t xml:space="preserve">27.4861316680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5752582550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.11891746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3506412506104</t>
   </si>
   <si>
     <t xml:space="preserve">27.7178573608398</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5734596252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6180229187012</t>
+    <t xml:space="preserve">28.5734577178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6180210113525</t>
   </si>
   <si>
     <t xml:space="preserve">28.5199813842773</t>
@@ -1094,13 +1094,13 @@
     <t xml:space="preserve">28.7873573303223</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7855567932129</t>
+    <t xml:space="preserve">29.7855548858643</t>
   </si>
   <si>
     <t xml:space="preserve">29.5360050201416</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3310203552246</t>
+    <t xml:space="preserve">29.3310165405273</t>
   </si>
   <si>
     <t xml:space="preserve">29.1705932617188</t>
@@ -1115,55 +1115,55 @@
     <t xml:space="preserve">29.3221054077148</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9656028747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7071437835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9923439025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9477806091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6073055267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8568572998047</t>
+    <t xml:space="preserve">28.9656085968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7071418762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9923419952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9477825164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.607307434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8568534851074</t>
   </si>
   <si>
     <t xml:space="preserve">29.4023208618164</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4112319946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8140926361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.687520980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6162204742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6786022186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6964302062988</t>
+    <t xml:space="preserve">29.4112300872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.814094543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6875190734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6162185668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6786041259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6964321136475</t>
   </si>
   <si>
     <t xml:space="preserve">30.1420555114746</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8390312194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.186616897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5181789398193</t>
+    <t xml:space="preserve">29.8390293121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1866130828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.518180847168</t>
   </si>
   <si>
     <t xml:space="preserve">29.1795063018799</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">29.437967300415</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3648681640625</t>
+    <t xml:space="preserve">30.3648662567139</t>
   </si>
   <si>
     <t xml:space="preserve">30.4629039764404</t>
@@ -1184,73 +1184,73 @@
     <t xml:space="preserve">30.2935676574707</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0974922180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0618438720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2311744689941</t>
+    <t xml:space="preserve">30.0974941253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.061840057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2311763763428</t>
   </si>
   <si>
     <t xml:space="preserve">32.0849800109863</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4967555999756</t>
+    <t xml:space="preserve">31.4967517852783</t>
   </si>
   <si>
     <t xml:space="preserve">30.8194046020508</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9958553314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.773042678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6928329467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1830177307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0760688781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9512958526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.307788848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1990394592285</t>
+    <t xml:space="preserve">31.9958572387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7730407714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6928310394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1830139160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0760650634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9512882232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3077926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1990356445312</t>
   </si>
   <si>
     <t xml:space="preserve">33.3951187133789</t>
   </si>
   <si>
-    <t xml:space="preserve">34.758731842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6963424682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7319946289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5804786682129</t>
+    <t xml:space="preserve">34.7587242126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6963386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.731990814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5804748535156</t>
   </si>
   <si>
     <t xml:space="preserve">34.2239761352539</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4378776550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5448303222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4271659851074</t>
+    <t xml:space="preserve">34.437873840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5448265075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4271697998047</t>
   </si>
   <si>
     <t xml:space="preserve">35.2221794128418</t>
@@ -1259,19 +1259,19 @@
     <t xml:space="preserve">34.6606864929199</t>
   </si>
   <si>
-    <t xml:space="preserve">34.37548828125</t>
+    <t xml:space="preserve">34.3754920959473</t>
   </si>
   <si>
     <t xml:space="preserve">33.8674812316895</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8496589660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1437683105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7159690856934</t>
+    <t xml:space="preserve">33.8496513366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1437721252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7159652709961</t>
   </si>
   <si>
     <t xml:space="preserve">34.0635528564453</t>
@@ -1280,64 +1280,64 @@
     <t xml:space="preserve">34.3130989074707</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1170234680176</t>
+    <t xml:space="preserve">34.1170272827148</t>
   </si>
   <si>
     <t xml:space="preserve">34.420051574707</t>
   </si>
   <si>
-    <t xml:space="preserve">34.776554107666</t>
+    <t xml:space="preserve">34.7765579223633</t>
   </si>
   <si>
     <t xml:space="preserve">34.6161270141602</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3041954040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1081161499023</t>
+    <t xml:space="preserve">34.3041915893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1081199645996</t>
   </si>
   <si>
     <t xml:space="preserve">32.8425407409668</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0902900695801</t>
+    <t xml:space="preserve">34.0902938842773</t>
   </si>
   <si>
     <t xml:space="preserve">35.106315612793</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2471122741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3005867004395</t>
+    <t xml:space="preserve">36.2471160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3005905151367</t>
   </si>
   <si>
     <t xml:space="preserve">36.1847267150879</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4966583251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4146461486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8584747314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9208641052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6178359985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5821914672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2702445983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4306755065918</t>
+    <t xml:space="preserve">36.4966621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4146499633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.858470916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9208602905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6178398132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5821876525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2702522277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4306716918945</t>
   </si>
   <si>
     <t xml:space="preserve">39.214973449707</t>
@@ -1346,19 +1346,19 @@
     <t xml:space="preserve">38.8050003051758</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8067970275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3504638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0563545227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3682861328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3415489196777</t>
+    <t xml:space="preserve">37.8068008422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3504600524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0563507080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3682823181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.341552734375</t>
   </si>
   <si>
     <t xml:space="preserve">38.5198059082031</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">38.6089248657227</t>
   </si>
   <si>
-    <t xml:space="preserve">38.689136505127</t>
+    <t xml:space="preserve">38.6891403198242</t>
   </si>
   <si>
     <t xml:space="preserve">38.733699798584</t>
@@ -1379,10 +1379,10 @@
     <t xml:space="preserve">39.4377861022949</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0812873840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0545539855957</t>
+    <t xml:space="preserve">39.0812835693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0545425415039</t>
   </si>
   <si>
     <t xml:space="preserve">39.3219261169434</t>
@@ -1391,43 +1391,43 @@
     <t xml:space="preserve">38.5554504394531</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2880744934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3772048950195</t>
+    <t xml:space="preserve">38.2880783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3772010803223</t>
   </si>
   <si>
     <t xml:space="preserve">37.6998519897461</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6125297546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6820220947266</t>
+    <t xml:space="preserve">36.6125335693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6820259094238</t>
   </si>
   <si>
     <t xml:space="preserve">38.4663276672363</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9956741333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6551971435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8156242370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.423469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0313186645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0848007202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9243698120117</t>
+    <t xml:space="preserve">41.9956703186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.655200958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8156204223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4234733581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.031322479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0847969055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.924373626709</t>
   </si>
   <si>
     <t xml:space="preserve">41.6213493347168</t>
@@ -1448,37 +1448,37 @@
     <t xml:space="preserve">41.7817726135254</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3539695739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8192253112793</t>
+    <t xml:space="preserve">41.3539733886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.819221496582</t>
   </si>
   <si>
     <t xml:space="preserve">40.3557739257812</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5874977111816</t>
+    <t xml:space="preserve">40.5874938964844</t>
   </si>
   <si>
     <t xml:space="preserve">39.8031997680664</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1436729431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6784248352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7799682617188</t>
+    <t xml:space="preserve">39.143669128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6784286499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.779972076416</t>
   </si>
   <si>
     <t xml:space="preserve">41.4787483215332</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6802215576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5750770568848</t>
+    <t xml:space="preserve">38.6802291870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5750732421875</t>
   </si>
   <si>
     <t xml:space="preserve">37.2898788452148</t>
@@ -1487,28 +1487,28 @@
     <t xml:space="preserve">39.5892944335938</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1953506469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1062278747559</t>
+    <t xml:space="preserve">40.1953468322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1062202453613</t>
   </si>
   <si>
     <t xml:space="preserve">40.5696716308594</t>
   </si>
   <si>
-    <t xml:space="preserve">40.801399230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9439926147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1400756835938</t>
+    <t xml:space="preserve">40.8013954162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9439964294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1400718688965</t>
   </si>
   <si>
     <t xml:space="preserve">40.9974746704102</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5161972045898</t>
+    <t xml:space="preserve">40.5161933898926</t>
   </si>
   <si>
     <t xml:space="preserve">40.9618263244629</t>
@@ -1517,10 +1517,10 @@
     <t xml:space="preserve">39.2506256103516</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1793174743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2131729125977</t>
+    <t xml:space="preserve">39.1793212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2131690979004</t>
   </si>
   <si>
     <t xml:space="preserve">40.3914260864258</t>
@@ -1532,16 +1532,16 @@
     <t xml:space="preserve">42.6017227172852</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5446472167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.902946472168</t>
+    <t xml:space="preserve">44.5446434020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9029502868652</t>
   </si>
   <si>
     <t xml:space="preserve">45.2309074401855</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8851203918457</t>
+    <t xml:space="preserve">43.885124206543</t>
   </si>
   <si>
     <t xml:space="preserve">44.9635314941406</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">47.3253402709961</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9439086914062</t>
+    <t xml:space="preserve">45.943904876709</t>
   </si>
   <si>
     <t xml:space="preserve">45.5874099731445</t>
@@ -1571,40 +1571,40 @@
     <t xml:space="preserve">42.9582214355469</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4609260559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1757278442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1578979492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0152931213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7675514221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.108024597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7479286193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7853736877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5518493652344</t>
+    <t xml:space="preserve">41.4609222412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.175724029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.157901763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0153007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7675476074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1080207824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7479248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7853698730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5518455505371</t>
   </si>
   <si>
     <t xml:space="preserve">39.7318992614746</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3040962219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2488288879395</t>
+    <t xml:space="preserve">39.3041000366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2488212585449</t>
   </si>
   <si>
     <t xml:space="preserve">39.9101486206055</t>
@@ -1613,13 +1613,13 @@
     <t xml:space="preserve">39.4288787841797</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0367240905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.387825012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0509490966797</t>
+    <t xml:space="preserve">39.0367202758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3878288269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.050952911377</t>
   </si>
   <si>
     <t xml:space="preserve">41.9335708618164</t>
@@ -1631,28 +1631,28 @@
     <t xml:space="preserve">40.7087097167969</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6366577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5285835266113</t>
+    <t xml:space="preserve">40.6366539001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5285797119141</t>
   </si>
   <si>
     <t xml:space="preserve">39.8441009521484</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7366142272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4844360351562</t>
+    <t xml:space="preserve">37.7366104125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.484432220459</t>
   </si>
   <si>
     <t xml:space="preserve">36.3316192626953</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0521278381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4757270812988</t>
+    <t xml:space="preserve">37.0521240234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4757232666016</t>
   </si>
   <si>
     <t xml:space="preserve">36.6018104553223</t>
@@ -1664,46 +1664,46 @@
     <t xml:space="preserve">35.6651496887207</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3589363098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2241401672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4135627746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6657409667969</t>
+    <t xml:space="preserve">35.3589324951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2241363525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4135665893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6657447814941</t>
   </si>
   <si>
     <t xml:space="preserve">33.881893157959</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4763069152832</t>
+    <t xml:space="preserve">34.4763107299805</t>
   </si>
   <si>
     <t xml:space="preserve">34.6924667358398</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1427841186523</t>
+    <t xml:space="preserve">35.1427879333496</t>
   </si>
   <si>
     <t xml:space="preserve">34.7284927368164</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5483589172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9899749755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8278541564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4402885437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1247749328613</t>
+    <t xml:space="preserve">34.5483665466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9899711608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8278579711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4402923583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1247673034668</t>
   </si>
   <si>
     <t xml:space="preserve">33.5036277770996</t>
@@ -1721,28 +1721,28 @@
     <t xml:space="preserve">31.7744083404541</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5315341949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.486795425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9371147155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2346172332764</t>
+    <t xml:space="preserve">30.5315322875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4867935180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9371128082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2346153259277</t>
   </si>
   <si>
     <t xml:space="preserve">30.1532649993896</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2166042327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4147415161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8296241760254</t>
+    <t xml:space="preserve">29.2166023254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4147453308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.829626083374</t>
   </si>
   <si>
     <t xml:space="preserve">29.1265392303467</t>
@@ -1751,58 +1751,58 @@
     <t xml:space="preserve">29.5408325195312</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6035823822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2520427703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6489086151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9551258087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1172370910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4054393768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.666332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6483192443848</t>
+    <t xml:space="preserve">30.6035804748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2520408630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6489067077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9551239013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1172351837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4054412841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6663265228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6483173370361</t>
   </si>
   <si>
     <t xml:space="preserve">32.080623626709</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1079406738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3601169586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9818477630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7383823394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6122894287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8377513885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9190998077393</t>
+    <t xml:space="preserve">31.1079330444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3601188659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9818496704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7383861541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6122932434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8377456665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9191017150879</t>
   </si>
   <si>
     <t xml:space="preserve">29.9010887145996</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6669216156006</t>
+    <t xml:space="preserve">29.666919708252</t>
   </si>
   <si>
     <t xml:space="preserve">29.0905151367188</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">28.099817276001</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5954608917236</t>
+    <t xml:space="preserve">27.595458984375</t>
   </si>
   <si>
     <t xml:space="preserve">26.6407871246338</t>
@@ -1823,13 +1823,13 @@
     <t xml:space="preserve">26.2805328369141</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0463676452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5146999359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2352046966553</t>
+    <t xml:space="preserve">26.046365737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5146980285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2352066040039</t>
   </si>
   <si>
     <t xml:space="preserve">27.0550785064697</t>
@@ -1838,55 +1838,55 @@
     <t xml:space="preserve">27.1091194152832</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0190544128418</t>
+    <t xml:space="preserve">27.0190525054932</t>
   </si>
   <si>
     <t xml:space="preserve">26.7488651275635</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4693698883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9196891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5774478912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9377002716064</t>
+    <t xml:space="preserve">27.4693717956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9196872711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.577449798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9377021789551</t>
   </si>
   <si>
     <t xml:space="preserve">27.8476409912109</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7936019897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0457782745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0097522735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7755889892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6041698455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5501327514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1805820465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1625690460205</t>
+    <t xml:space="preserve">27.7936000823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0457763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0097541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7755870819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6041717529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5501346588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1805801391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1625671386719</t>
   </si>
   <si>
     <t xml:space="preserve">28.6401958465576</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6762237548828</t>
+    <t xml:space="preserve">28.6762218475342</t>
   </si>
   <si>
     <t xml:space="preserve">27.6675109863281</t>
@@ -1895,37 +1895,37 @@
     <t xml:space="preserve">27.451358795166</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5594367980957</t>
+    <t xml:space="preserve">27.5594348907471</t>
   </si>
   <si>
     <t xml:space="preserve">25.7581653594971</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7320308685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7413330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7233238220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7860660552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4165153503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7047157287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5606136322021</t>
+    <t xml:space="preserve">22.7320289611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7413311004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7233200073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7860698699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4165134429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7047176361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5606155395508</t>
   </si>
   <si>
     <t xml:space="preserve">23.236385345459</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4345283508301</t>
+    <t xml:space="preserve">23.4345264434814</t>
   </si>
   <si>
     <t xml:space="preserve">22.5158786773682</t>
@@ -1937,34 +1937,34 @@
     <t xml:space="preserve">20.8226852416992</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3630657196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2369747161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3450527191162</t>
+    <t xml:space="preserve">21.3630638122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2369766235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3450546264648</t>
   </si>
   <si>
     <t xml:space="preserve">21.5972309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7239093780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3189182281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2828941345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5437812805176</t>
+    <t xml:space="preserve">19.7239074707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.318920135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2828922271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5437831878662</t>
   </si>
   <si>
     <t xml:space="preserve">18.877311706543</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3909702301025</t>
+    <t xml:space="preserve">18.3909683227539</t>
   </si>
   <si>
     <t xml:space="preserve">19.0034027099609</t>
@@ -1976,52 +1976,52 @@
     <t xml:space="preserve">17.139087677002</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1120700836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2651748657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.661750793457</t>
+    <t xml:space="preserve">17.1120681762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2651767730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6617488861084</t>
   </si>
   <si>
     <t xml:space="preserve">16.2024250030518</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9502458572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7160844802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6800584793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6170139312744</t>
+    <t xml:space="preserve">15.9502468109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7160835266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6800594329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6170129776001</t>
   </si>
   <si>
     <t xml:space="preserve">16.1573944091797</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6077136993408</t>
+    <t xml:space="preserve">16.6077098846436</t>
   </si>
   <si>
     <t xml:space="preserve">16.4005661010742</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4723224639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5533790588379</t>
+    <t xml:space="preserve">17.4723205566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5533771514893</t>
   </si>
   <si>
     <t xml:space="preserve">16.490629196167</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9406509399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8232727050781</t>
+    <t xml:space="preserve">17.9406547546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8232746124268</t>
   </si>
   <si>
     <t xml:space="preserve">17.6614551544189</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">16.0132942199707</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9052152633667</t>
+    <t xml:space="preserve">15.905216217041</t>
   </si>
   <si>
     <t xml:space="preserve">16.2654685974121</t>
@@ -2042,25 +2042,25 @@
     <t xml:space="preserve">16.1934204101562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7250881195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4008626937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0496139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7524032592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5899925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1486835479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.463906288147</t>
+    <t xml:space="preserve">15.7250900268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4008598327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0496120452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.752402305603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5899934768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1486825942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4639053344727</t>
   </si>
   <si>
     <t xml:space="preserve">17.1661052703857</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">18.1568031311035</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6434421539307</t>
+    <t xml:space="preserve">17.643440246582</t>
   </si>
   <si>
     <t xml:space="preserve">17.391263961792</t>
@@ -2084,31 +2084,31 @@
     <t xml:space="preserve">18.0487289428711</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2288551330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0307178497314</t>
+    <t xml:space="preserve">18.2288570404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0307140350342</t>
   </si>
   <si>
     <t xml:space="preserve">17.9226379394531</t>
   </si>
   <si>
-    <t xml:space="preserve">17.454309463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6791706085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8052635192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6251335144043</t>
+    <t xml:space="preserve">17.4543113708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6791744232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8052616119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6251354217529</t>
   </si>
   <si>
     <t xml:space="preserve">18.3369312286377</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9493675231934</t>
+    <t xml:space="preserve">18.9493656158447</t>
   </si>
   <si>
     <t xml:space="preserve">18.7872486114502</t>
@@ -2123,40 +2123,40 @@
     <t xml:space="preserve">18.4269924163818</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9856815338135</t>
+    <t xml:space="preserve">17.9856834411621</t>
   </si>
   <si>
     <t xml:space="preserve">17.3552398681641</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7244987487793</t>
+    <t xml:space="preserve">17.7245025634766</t>
   </si>
   <si>
     <t xml:space="preserve">18.3009052276611</t>
   </si>
   <si>
-    <t xml:space="preserve">18.607120513916</t>
+    <t xml:space="preserve">18.6071224212646</t>
   </si>
   <si>
     <t xml:space="preserve">19.3996810913086</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6698741912842</t>
+    <t xml:space="preserve">19.6698722839355</t>
   </si>
   <si>
     <t xml:space="preserve">20.2462768554688</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0661487579346</t>
+    <t xml:space="preserve">20.0661525726318</t>
   </si>
   <si>
     <t xml:space="preserve">19.9220504760742</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4176940917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4537200927734</t>
+    <t xml:space="preserve">19.4176902770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4537181854248</t>
   </si>
   <si>
     <t xml:space="preserve">20.2823028564453</t>
@@ -2177,16 +2177,16 @@
     <t xml:space="preserve">17.4182834625244</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8508834838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9859771728516</t>
+    <t xml:space="preserve">16.8508815765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9859790802002</t>
   </si>
   <si>
     <t xml:space="preserve">16.868896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0490226745605</t>
+    <t xml:space="preserve">17.0490245819092</t>
   </si>
   <si>
     <t xml:space="preserve">16.9409465789795</t>
@@ -2195,22 +2195,22 @@
     <t xml:space="preserve">17.3462333679199</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2741794586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3822593688965</t>
+    <t xml:space="preserve">17.2741832733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3822574615479</t>
   </si>
   <si>
     <t xml:space="preserve">17.2831878662109</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1748180389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.976676940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6164245605469</t>
+    <t xml:space="preserve">18.1748161315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9766788482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6164226531982</t>
   </si>
   <si>
     <t xml:space="preserve">17.4272899627686</t>
@@ -2222,28 +2222,28 @@
     <t xml:space="preserve">17.913631439209</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6974792480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1928291320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9496574401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2381534576416</t>
+    <t xml:space="preserve">17.6974811553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1928310394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9496612548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2381553649902</t>
   </si>
   <si>
     <t xml:space="preserve">17.1300792694092</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6794681549072</t>
+    <t xml:space="preserve">17.6794662475586</t>
   </si>
   <si>
     <t xml:space="preserve">17.9676723480225</t>
   </si>
   <si>
-    <t xml:space="preserve">18.084753036499</t>
+    <t xml:space="preserve">18.0847549438477</t>
   </si>
   <si>
     <t xml:space="preserve">18.0667419433594</t>
@@ -2255,13 +2255,13 @@
     <t xml:space="preserve">17.5173530578613</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6074180603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5894050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7695331573486</t>
+    <t xml:space="preserve">17.6074161529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5894069671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.76953125</t>
   </si>
   <si>
     <t xml:space="preserve">18.6365585327148</t>
@@ -2273,25 +2273,25 @@
     <t xml:space="preserve">16.6621894836426</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2249774932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5330257415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1916618347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6842317581177</t>
+    <t xml:space="preserve">17.2249755859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5330238342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1916637420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.684232711792</t>
   </si>
   <si>
     <t xml:space="preserve">14.6232395172119</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8021230697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9405145645142</t>
+    <t xml:space="preserve">13.8021240234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9405136108398</t>
   </si>
   <si>
     <t xml:space="preserve">13.7836713790894</t>
@@ -2300,52 +2300,52 @@
     <t xml:space="preserve">13.3131456375122</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8943853378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8390283584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4792137145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9533309936523</t>
+    <t xml:space="preserve">13.894383430481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8390293121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4792127609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.953330039978</t>
   </si>
   <si>
     <t xml:space="preserve">13.0732688903809</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0179119110107</t>
+    <t xml:space="preserve">13.0179128646851</t>
   </si>
   <si>
     <t xml:space="preserve">13.303918838501</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3777275085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1009454727173</t>
+    <t xml:space="preserve">13.3777284622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1009464263916</t>
   </si>
   <si>
     <t xml:space="preserve">13.1378507614136</t>
   </si>
   <si>
-    <t xml:space="preserve">13.922061920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7006378173828</t>
+    <t xml:space="preserve">13.9220628738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7006387710571</t>
   </si>
   <si>
     <t xml:space="preserve">14.4756231307983</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4202671051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5771102905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8298015594482</t>
+    <t xml:space="preserve">14.4202661514282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.577109336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8298025131226</t>
   </si>
   <si>
     <t xml:space="preserve">13.7928981781006</t>
@@ -2354,10 +2354,10 @@
     <t xml:space="preserve">13.6914119720459</t>
   </si>
   <si>
-    <t xml:space="preserve">14.512526512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1803913116455</t>
+    <t xml:space="preserve">14.5125274658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1803903579712</t>
   </si>
   <si>
     <t xml:space="preserve">11.0988998413086</t>
@@ -2366,13 +2366,13 @@
     <t xml:space="preserve">10.7575378417969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1486206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2132015228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4069490432739</t>
+    <t xml:space="preserve">10.1486196517944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2132024765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4069480895996</t>
   </si>
   <si>
     <t xml:space="preserve">10.4161748886108</t>
@@ -2390,10 +2390,10 @@
     <t xml:space="preserve">10.4807567596436</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6837291717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5361127853394</t>
+    <t xml:space="preserve">10.6837301254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5361137390137</t>
   </si>
   <si>
     <t xml:space="preserve">10.296236038208</t>
@@ -2402,22 +2402,22 @@
     <t xml:space="preserve">10.370044708252</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0471343994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1762981414795</t>
+    <t xml:space="preserve">10.0471353530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1762990951538</t>
   </si>
   <si>
     <t xml:space="preserve">9.9087438583374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65964126586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53047847747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0932636260986</t>
+    <t xml:space="preserve">9.65964221954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53047752380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0932645797729</t>
   </si>
   <si>
     <t xml:space="preserve">10.4899835586548</t>
@@ -2429,25 +2429,25 @@
     <t xml:space="preserve">10.4254016876221</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5176601409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3054628372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4438533782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6652774810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286817550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9640998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0563611984253</t>
+    <t xml:space="preserve">10.5176610946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3054637908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4438524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6652784347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0286827087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96410083770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0563592910767</t>
   </si>
   <si>
     <t xml:space="preserve">10.120943069458</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">9.29060077667236</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57660675048828</t>
+    <t xml:space="preserve">9.5766077041626</t>
   </si>
   <si>
     <t xml:space="preserve">9.21217918395996</t>
@@ -2492,7 +2492,7 @@
     <t xml:space="preserve">9.24447059631348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28137493133545</t>
+    <t xml:space="preserve">9.28137588500977</t>
   </si>
   <si>
     <t xml:space="preserve">9.11530685424805</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">9.88106536865234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97332572937012</t>
+    <t xml:space="preserve">9.97332668304443</t>
   </si>
   <si>
     <t xml:space="preserve">9.99177742004395</t>
@@ -2510,31 +2510,31 @@
     <t xml:space="preserve">10.2408819198608</t>
   </si>
   <si>
-    <t xml:space="preserve">10.434627532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.084038734436</t>
+    <t xml:space="preserve">10.4346265792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0840396881104</t>
   </si>
   <si>
     <t xml:space="preserve">10.1024904251099</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61351203918457</t>
+    <t xml:space="preserve">9.61351108551025</t>
   </si>
   <si>
     <t xml:space="preserve">9.66886711120605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52125072479248</t>
+    <t xml:space="preserve">9.5212516784668</t>
   </si>
   <si>
     <t xml:space="preserve">9.7980318069458</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56738090515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2629222869873</t>
+    <t xml:space="preserve">9.56738185882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26292324066162</t>
   </si>
   <si>
     <t xml:space="preserve">9.39208698272705</t>
@@ -2546,31 +2546,31 @@
     <t xml:space="preserve">9.31827926635742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71499824523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81648540496826</t>
+    <t xml:space="preserve">9.71499729156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81648445129395</t>
   </si>
   <si>
     <t xml:space="preserve">9.6873197555542</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98255157470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75190258026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49357318878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2777853012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0655851364136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5822439193726</t>
+    <t xml:space="preserve">9.98255252838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7519006729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49357414245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2777843475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0655860900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5822429656982</t>
   </si>
   <si>
     <t xml:space="preserve">10.7298603057861</t>
@@ -2594,7 +2594,7 @@
     <t xml:space="preserve">12.2337007522583</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9938230514526</t>
+    <t xml:space="preserve">11.993824005127</t>
   </si>
   <si>
     <t xml:space="preserve">12.1322145462036</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">12.1414403915405</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1875705718994</t>
+    <t xml:space="preserve">12.1875715255737</t>
   </si>
   <si>
     <t xml:space="preserve">11.9661474227905</t>
@@ -2624,16 +2624,16 @@
     <t xml:space="preserve">11.7354965209961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0676326751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4551248550415</t>
+    <t xml:space="preserve">12.0676317214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4551258087158</t>
   </si>
   <si>
     <t xml:space="preserve">13.2577886581421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2485628128052</t>
+    <t xml:space="preserve">13.2485637664795</t>
   </si>
   <si>
     <t xml:space="preserve">13.0824947357178</t>
@@ -2645,19 +2645,19 @@
     <t xml:space="preserve">13.4054050445557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2024326324463</t>
+    <t xml:space="preserve">13.2024335861206</t>
   </si>
   <si>
     <t xml:space="preserve">13.7559947967529</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7098627090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7744474411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3408231735229</t>
+    <t xml:space="preserve">13.7098636627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7744464874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3408222198486</t>
   </si>
   <si>
     <t xml:space="preserve">13.7190895080566</t>
@@ -2666,7 +2666,7 @@
     <t xml:space="preserve">13.7283153533936</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0143213272095</t>
+    <t xml:space="preserve">14.0143222808838</t>
   </si>
   <si>
     <t xml:space="preserve">14.1342601776123</t>
@@ -2675,7 +2675,7 @@
     <t xml:space="preserve">14.1250352859497</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9497394561768</t>
+    <t xml:space="preserve">13.9497404098511</t>
   </si>
   <si>
     <t xml:space="preserve">13.6637344360352</t>
@@ -2684,34 +2684,34 @@
     <t xml:space="preserve">13.682186126709</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4571704864502</t>
+    <t xml:space="preserve">14.4571714401245</t>
   </si>
   <si>
     <t xml:space="preserve">14.1158084869385</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8482542037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0512256622314</t>
+    <t xml:space="preserve">13.8482532501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0512266159058</t>
   </si>
   <si>
     <t xml:space="preserve">14.0327739715576</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9312877655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6473264694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7303609848022</t>
+    <t xml:space="preserve">13.9312896728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6473255157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7303600311279</t>
   </si>
   <si>
     <t xml:space="preserve">17.0865879058838</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7913551330566</t>
+    <t xml:space="preserve">16.791353225708</t>
   </si>
   <si>
     <t xml:space="preserve">16.8651638031006</t>
@@ -2723,16 +2723,16 @@
     <t xml:space="preserve">16.8190307617188</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1086273193359</t>
+    <t xml:space="preserve">16.1086292266846</t>
   </si>
   <si>
     <t xml:space="preserve">15.997917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9333333969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4720325469971</t>
+    <t xml:space="preserve">15.9333343505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4720344543457</t>
   </si>
   <si>
     <t xml:space="preserve">14.6785955429077</t>
@@ -2741,25 +2741,25 @@
     <t xml:space="preserve">14.3187808990479</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8446655273438</t>
+    <t xml:space="preserve">14.8446636199951</t>
   </si>
   <si>
     <t xml:space="preserve">15.2967395782471</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2044773101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7247257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8538913726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1491241455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2506093978882</t>
+    <t xml:space="preserve">15.2044792175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7247266769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8538904190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1491222381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2506103515625</t>
   </si>
   <si>
     <t xml:space="preserve">14.9830541610718</t>
@@ -2768,10 +2768,10 @@
     <t xml:space="preserve">15.1583490371704</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0753164291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1065816879272</t>
+    <t xml:space="preserve">15.0753154754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1065826416016</t>
   </si>
   <si>
     <t xml:space="preserve">12.6027421951294</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">12.0399551391602</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9753723144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5878791809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.301872253418</t>
+    <t xml:space="preserve">11.9753713607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5878801345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3018732070923</t>
   </si>
   <si>
     <t xml:space="preserve">10.6006956100464</t>
@@ -2795,55 +2795,55 @@
     <t xml:space="preserve">10.1301679611206</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30905342102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06353950500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97589445114136</t>
+    <t xml:space="preserve">9.30905246734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0635404586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9758939743042</t>
   </si>
   <si>
     <t xml:space="preserve">7.8928599357605</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55047273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93796634674072</t>
+    <t xml:space="preserve">6.5504732131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93796586990356</t>
   </si>
   <si>
     <t xml:space="preserve">6.90567493438721</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98409605026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91028738021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01177453994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47307586669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05431365966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85697746276855</t>
+    <t xml:space="preserve">6.98409652709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91028785705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01177358627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47307538986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05431461334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85697841644287</t>
   </si>
   <si>
     <t xml:space="preserve">9.33673095703125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01382160186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39567756652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40028953552246</t>
+    <t xml:space="preserve">9.01382064819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.395676612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40029048919678</t>
   </si>
   <si>
     <t xml:space="preserve">8.34954643249512</t>
@@ -2855,31 +2855,31 @@
     <t xml:space="preserve">8.118896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74985456466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.929762840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78675937652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10967063903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84211587905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42694568634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28855514526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26087665557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32545900344849</t>
+    <t xml:space="preserve">7.74985551834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92976331710815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78675985336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10966968536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.842116355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42694520950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28855466842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26087713241577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32545948028564</t>
   </si>
   <si>
     <t xml:space="preserve">7.3346848487854</t>
@@ -2888,25 +2888,25 @@
     <t xml:space="preserve">7.1132607460022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55610942840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77753448486328</t>
+    <t xml:space="preserve">7.5561089515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77753496170044</t>
   </si>
   <si>
     <t xml:space="preserve">7.93437623977661</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60223865509033</t>
+    <t xml:space="preserve">7.60223960876465</t>
   </si>
   <si>
     <t xml:space="preserve">7.33929777145386</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51920557022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3070068359375</t>
+    <t xml:space="preserve">7.51920509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30700731277466</t>
   </si>
   <si>
     <t xml:space="preserve">7.1455512046814</t>
@@ -2921,31 +2921,31 @@
     <t xml:space="preserve">7.06713008880615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92874050140381</t>
+    <t xml:space="preserve">6.92874002456665</t>
   </si>
   <si>
     <t xml:space="preserve">7.56533479690552</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54227066040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44539737701416</t>
+    <t xml:space="preserve">7.54227018356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.445396900177</t>
   </si>
   <si>
     <t xml:space="preserve">7.27010250091553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72217798233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46948528289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66784572601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90310859680176</t>
+    <t xml:space="preserve">7.72217750549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46948623657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66784477233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90310764312744</t>
   </si>
   <si>
     <t xml:space="preserve">8.54329395294189</t>
@@ -2954,85 +2954,85 @@
     <t xml:space="preserve">8.69090938568115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87542915344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32750511169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0066413879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4863920211792</t>
+    <t xml:space="preserve">8.8754301071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32750415802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0066404342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4863929748535</t>
   </si>
   <si>
     <t xml:space="preserve">11.4956197738647</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2557430267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9420576095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82570934295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74267673492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4623050689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1947498321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0194568634033</t>
+    <t xml:space="preserve">11.2557420730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9420585632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82571029663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74267578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.462306022644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1947507858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.019455909729</t>
   </si>
   <si>
     <t xml:space="preserve">9.89029216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3792715072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3608198165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2224292755127</t>
+    <t xml:space="preserve">10.3792724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3608179092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2224283218384</t>
   </si>
   <si>
     <t xml:space="preserve">10.674503326416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5453405380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7667636871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.021502494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4402627944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5417490005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6155576705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8093032836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.818531036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7078161239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6616888046265</t>
+    <t xml:space="preserve">10.5453395843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7667646408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0215015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4402637481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5417499542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6155586242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8093042373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8185300827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7078170776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6616878509521</t>
   </si>
   <si>
     <t xml:space="preserve">11.5694274902344</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">11.3480033874512</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2741956710815</t>
+    <t xml:space="preserve">11.2741947174072</t>
   </si>
   <si>
     <t xml:space="preserve">11.1450309753418</t>
@@ -3056,22 +3056,22 @@
     <t xml:space="preserve">12.3167352676392</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8241662979126</t>
+    <t xml:space="preserve">12.8241653442383</t>
   </si>
   <si>
     <t xml:space="preserve">12.7042284011841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0548162460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3961791992188</t>
+    <t xml:space="preserve">13.0548152923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3961801528931</t>
   </si>
   <si>
     <t xml:space="preserve">13.2854671478271</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4423093795776</t>
+    <t xml:space="preserve">13.4423084259033</t>
   </si>
   <si>
     <t xml:space="preserve">13.1286239624023</t>
@@ -3086,13 +3086,13 @@
     <t xml:space="preserve">13.1932067871094</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5437955856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3500499725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5714750289917</t>
+    <t xml:space="preserve">13.5437965393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3500490188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5714731216431</t>
   </si>
   <si>
     <t xml:space="preserve">13.3685007095337</t>
@@ -3104,49 +3104,49 @@
     <t xml:space="preserve">13.4976654052734</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1101722717285</t>
+    <t xml:space="preserve">13.1101732254028</t>
   </si>
   <si>
     <t xml:space="preserve">13.1655282974243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.267014503479</t>
+    <t xml:space="preserve">13.2670154571533</t>
   </si>
   <si>
     <t xml:space="preserve">13.2762413024902</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0455913543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1747550964355</t>
+    <t xml:space="preserve">13.0455904006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1747541427612</t>
   </si>
   <si>
     <t xml:space="preserve">13.331597328186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3869543075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5104808807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3813180923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6304187774658</t>
+    <t xml:space="preserve">13.3869533538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5104818344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3813171386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6304197311401</t>
   </si>
   <si>
     <t xml:space="preserve">12.335186958313</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7872619628906</t>
+    <t xml:space="preserve">12.7872610092163</t>
   </si>
   <si>
     <t xml:space="preserve">13.5068912506104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4330835342407</t>
+    <t xml:space="preserve">13.4330825805664</t>
   </si>
   <si>
     <t xml:space="preserve">13.4515352249146</t>
@@ -3155,25 +3155,25 @@
     <t xml:space="preserve">15.2690601348877</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5735187530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8318471908569</t>
+    <t xml:space="preserve">15.5735197067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8318490982056</t>
   </si>
   <si>
     <t xml:space="preserve">16.1455326080322</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3613195419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4628076553345</t>
+    <t xml:space="preserve">15.3613204956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4628086090088</t>
   </si>
   <si>
     <t xml:space="preserve">14.7616300582886</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5217533111572</t>
+    <t xml:space="preserve">14.5217542648315</t>
   </si>
   <si>
     <t xml:space="preserve">14.5955619812012</t>
@@ -3182,58 +3182,58 @@
     <t xml:space="preserve">14.7154989242554</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3556852340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9128351211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6545085906982</t>
+    <t xml:space="preserve">14.3556861877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9128360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6545076370239</t>
   </si>
   <si>
     <t xml:space="preserve">14.5033025741577</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4110412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.650918006897</t>
+    <t xml:space="preserve">14.4110403060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6509189605713</t>
   </si>
   <si>
     <t xml:space="preserve">15.1860265731812</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6750068664551</t>
+    <t xml:space="preserve">15.6750049591064</t>
   </si>
   <si>
     <t xml:space="preserve">15.4166765213013</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1029920578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9184713363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3889999389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7764930725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5827474594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1547603607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8133964538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8410739898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.924108505249</t>
+    <t xml:space="preserve">15.1029930114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9184722900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3889980316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7764911651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5827445983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1547565460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8133974075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8410749435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9241065979004</t>
   </si>
   <si>
     <t xml:space="preserve">16.1178550720215</t>
@@ -3242,7 +3242,7 @@
     <t xml:space="preserve">15.8503007888794</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8779792785645</t>
+    <t xml:space="preserve">15.8779764175415</t>
   </si>
   <si>
     <t xml:space="preserve">15.3520946502686</t>
@@ -3251,16 +3251,16 @@
     <t xml:space="preserve">15.6381015777588</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4351272583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5919723510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9517889022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0994033813477</t>
+    <t xml:space="preserve">15.4351291656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5919713973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9517879486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0994052886963</t>
   </si>
   <si>
     <t xml:space="preserve">16.0717258453369</t>
@@ -3272,16 +3272,16 @@
     <t xml:space="preserve">17.7877655029297</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3910446166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4648532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1142635345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2618808746338</t>
+    <t xml:space="preserve">17.3910465240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4648551940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1142654418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2618789672852</t>
   </si>
   <si>
     <t xml:space="preserve">17.5386619567871</t>
@@ -3290,19 +3290,19 @@
     <t xml:space="preserve">17.4464015960693</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5663414001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.372594833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.621696472168</t>
+    <t xml:space="preserve">17.5663394927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3725929260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6216983795166</t>
   </si>
   <si>
     <t xml:space="preserve">17.5478858947754</t>
   </si>
   <si>
-    <t xml:space="preserve">18.036865234375</t>
+    <t xml:space="preserve">18.0368671417236</t>
   </si>
   <si>
     <t xml:space="preserve">18.415132522583</t>
@@ -3314,52 +3314,52 @@
     <t xml:space="preserve">19.9835548400879</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4299964904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4484481811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.728816986084</t>
+    <t xml:space="preserve">19.4299945831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4484462738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7288188934326</t>
   </si>
   <si>
     <t xml:space="preserve">19.245475769043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1901187896729</t>
+    <t xml:space="preserve">19.1901168823242</t>
   </si>
   <si>
     <t xml:space="preserve">19.3377342224121</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2639293670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5442981719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5627498626709</t>
+    <t xml:space="preserve">19.2639255523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5443000793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5627517700195</t>
   </si>
   <si>
     <t xml:space="preserve">18.2029342651367</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4704914093018</t>
+    <t xml:space="preserve">18.4704895019531</t>
   </si>
   <si>
     <t xml:space="preserve">17.9722843170166</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1844825744629</t>
+    <t xml:space="preserve">18.1844806671143</t>
   </si>
   <si>
     <t xml:space="preserve">19.2823791503906</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9651031494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6109256744385</t>
+    <t xml:space="preserve">19.9651050567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6109275817871</t>
   </si>
   <si>
     <t xml:space="preserve">20.9430637359619</t>
@@ -3371,13 +3371,13 @@
     <t xml:space="preserve">21.2198429107666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.312105178833</t>
+    <t xml:space="preserve">21.3121032714844</t>
   </si>
   <si>
     <t xml:space="preserve">21.1829376220703</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7513618469238</t>
+    <t xml:space="preserve">22.7513599395752</t>
   </si>
   <si>
     <t xml:space="preserve">22.7698135375977</t>
@@ -3398,25 +3398,25 @@
     <t xml:space="preserve">20.5371170043945</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6293773651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7216396331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1865272521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1275825500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6847362518311</t>
+    <t xml:space="preserve">20.6293792724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7216358184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1865291595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1275806427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6847343444824</t>
   </si>
   <si>
     <t xml:space="preserve">21.2013912200928</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4633083343506</t>
+    <t xml:space="preserve">20.4633102416992</t>
   </si>
   <si>
     <t xml:space="preserve">19.8728466033936</t>
@@ -3428,31 +3428,31 @@
     <t xml:space="preserve">20.8508033752441</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0906810760498</t>
+    <t xml:space="preserve">21.0906791687012</t>
   </si>
   <si>
     <t xml:space="preserve">21.109130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2234325408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9466514587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1311702728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1127223968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6145153045654</t>
+    <t xml:space="preserve">20.2234344482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9466533660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1311721801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1127185821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6145172119141</t>
   </si>
   <si>
     <t xml:space="preserve">19.8543930053711</t>
   </si>
   <si>
-    <t xml:space="preserve">20.795446395874</t>
+    <t xml:space="preserve">20.7954483032227</t>
   </si>
   <si>
     <t xml:space="preserve">20.31569480896</t>
@@ -3461,49 +3461,49 @@
     <t xml:space="preserve">20.8323497772217</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1793518066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5483913421631</t>
+    <t xml:space="preserve">22.179349899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5483894348145</t>
   </si>
   <si>
     <t xml:space="preserve">22.0686359405518</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2162551879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1424446105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0132827758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2531604766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0317306518555</t>
+    <t xml:space="preserve">22.2162532806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1424465179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0132808685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2531585693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0317325592041</t>
   </si>
   <si>
     <t xml:space="preserve">23.1942100524902</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7846755981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.729320526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3935947418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8953895568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0465927124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9174327850342</t>
+    <t xml:space="preserve">23.7846775054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7293186187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3935928344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8953876495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.046594619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9174308776855</t>
   </si>
   <si>
     <t xml:space="preserve">23.3049240112305</t>
@@ -3512,13 +3512,13 @@
     <t xml:space="preserve">23.3971843719482</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5817012786865</t>
+    <t xml:space="preserve">23.5817031860352</t>
   </si>
   <si>
     <t xml:space="preserve">23.1388549804688</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5852947235107</t>
+    <t xml:space="preserve">22.5852928161621</t>
   </si>
   <si>
     <t xml:space="preserve">22.8067169189453</t>
@@ -3527,31 +3527,31 @@
     <t xml:space="preserve">22.3454170227051</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4894428253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7477741241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7662239074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2311153411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7144584655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6370620727539</t>
+    <t xml:space="preserve">23.489444732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7477722167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7662258148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2311172485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7144603729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6370601654053</t>
   </si>
   <si>
     <t xml:space="preserve">25.0763187408447</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7554550170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4786739349365</t>
+    <t xml:space="preserve">26.7554569244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4786758422852</t>
   </si>
   <si>
     <t xml:space="preserve">26.976879119873</t>
@@ -3566,10 +3566,10 @@
     <t xml:space="preserve">27.4935340881348</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1578121185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.04709815979</t>
+    <t xml:space="preserve">28.1578102111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0470943450928</t>
   </si>
   <si>
     <t xml:space="preserve">27.2721099853516</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">27.5673427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4012756347656</t>
+    <t xml:space="preserve">27.4012775421143</t>
   </si>
   <si>
     <t xml:space="preserve">27.1060428619385</t>
@@ -3587,13 +3587,13 @@
     <t xml:space="preserve">26.9030704498291</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4971256256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9251117706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7221393585205</t>
+    <t xml:space="preserve">26.497127532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9251136779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7221412658691</t>
   </si>
   <si>
     <t xml:space="preserve">26.6447410583496</t>
@@ -3605,13 +3605,13 @@
     <t xml:space="preserve">26.3864135742188</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9989185333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5007171630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9066619873047</t>
+    <t xml:space="preserve">25.9989223480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5007133483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9066600799561</t>
   </si>
   <si>
     <t xml:space="preserve">26.2572479248047</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">26.1280841827393</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9620151519775</t>
+    <t xml:space="preserve">25.9620170593262</t>
   </si>
   <si>
     <t xml:space="preserve">26.6631946563721</t>
@@ -3641,31 +3641,31 @@
     <t xml:space="preserve">26.7185497283936</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8292617797852</t>
+    <t xml:space="preserve">26.8292636871338</t>
   </si>
   <si>
     <t xml:space="preserve">26.4417686462402</t>
   </si>
   <si>
-    <t xml:space="preserve">26.534029006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4269065856934</t>
+    <t xml:space="preserve">26.5340309143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.426908493042</t>
   </si>
   <si>
     <t xml:space="preserve">25.3715515136719</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5893859863281</t>
+    <t xml:space="preserve">26.5893840789795</t>
   </si>
   <si>
     <t xml:space="preserve">27.1983032226562</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4750843048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9143409729004</t>
+    <t xml:space="preserve">27.4750823974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.914342880249</t>
   </si>
   <si>
     <t xml:space="preserve">30.4643135070801</t>
@@ -3677,10 +3677,10 @@
     <t xml:space="preserve">29.5970706939697</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0322341918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8846187591553</t>
+    <t xml:space="preserve">27.0322322845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8846168518066</t>
   </si>
   <si>
     <t xml:space="preserve">27.3459205627441</t>
@@ -3689,22 +3689,22 @@
     <t xml:space="preserve">27.6226997375488</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7923583984375</t>
+    <t xml:space="preserve">26.7923603057861</t>
   </si>
   <si>
     <t xml:space="preserve">26.9399757385254</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1798515319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8994789123535</t>
+    <t xml:space="preserve">27.1798496246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8994808197021</t>
   </si>
   <si>
     <t xml:space="preserve">27.5857963562012</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2352066040039</t>
+    <t xml:space="preserve">27.2352085113525</t>
   </si>
   <si>
     <t xml:space="preserve">27.2167549133301</t>
@@ -3722,7 +3722,7 @@
     <t xml:space="preserve">27.7703170776367</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3090171813965</t>
+    <t xml:space="preserve">27.3090152740479</t>
   </si>
   <si>
     <t xml:space="preserve">27.9548377990723</t>
@@ -3731,28 +3731,28 @@
     <t xml:space="preserve">28.6744651794434</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0286426544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8072185516357</t>
+    <t xml:space="preserve">28.0286445617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8072204589844</t>
   </si>
   <si>
     <t xml:space="preserve">28.3423290252686</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9179344177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6965084075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0506858825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7518653869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8256702423096</t>
+    <t xml:space="preserve">27.917932510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6965065002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.050687789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7518634796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8256721496582</t>
   </si>
   <si>
     <t xml:space="preserve">27.9732875823975</t>
@@ -3764,10 +3764,10 @@
     <t xml:space="preserve">28.2869739532471</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0840034484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7887706756592</t>
+    <t xml:space="preserve">28.0840015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7887668609619</t>
   </si>
   <si>
     <t xml:space="preserve">26.294153213501</t>
@@ -3776,25 +3776,25 @@
     <t xml:space="preserve">26.9953308105469</t>
   </si>
   <si>
-    <t xml:space="preserve">26.220344543457</t>
+    <t xml:space="preserve">26.2203464508057</t>
   </si>
   <si>
     <t xml:space="preserve">25.5191669464111</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6150169372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0983619689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9656085968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.356689453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7108707427979</t>
+    <t xml:space="preserve">24.6150188446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0983638763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9656047821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3566913604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7108688354492</t>
   </si>
   <si>
     <t xml:space="preserve">23.3418273925781</t>
@@ -3803,88 +3803,88 @@
     <t xml:space="preserve">23.2680187225342</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0614566802979</t>
+    <t xml:space="preserve">24.0614585876465</t>
   </si>
   <si>
     <t xml:space="preserve">24.2090721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7441825866699</t>
+    <t xml:space="preserve">24.7441806793213</t>
   </si>
   <si>
     <t xml:space="preserve">24.6334705352783</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2423877716064</t>
+    <t xml:space="preserve">25.2423858642578</t>
   </si>
   <si>
     <t xml:space="preserve">25.0947704315186</t>
   </si>
   <si>
-    <t xml:space="preserve">24.910249710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9840564727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8179893493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1870288848877</t>
+    <t xml:space="preserve">24.9102516174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.984058380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8179912567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1870307922363</t>
   </si>
   <si>
     <t xml:space="preserve">24.670373916626</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5376224517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8733444213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9287052154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8364410400391</t>
+    <t xml:space="preserve">25.537618637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8733463287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9287033081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8364429473877</t>
   </si>
   <si>
     <t xml:space="preserve">24.2644290924072</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3013343811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8769359588623</t>
+    <t xml:space="preserve">24.3013324737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8769340515137</t>
   </si>
   <si>
     <t xml:space="preserve">23.5263481140137</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1573066711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.865665435791</t>
+    <t xml:space="preserve">23.1573085784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8656673431396</t>
   </si>
   <si>
     <t xml:space="preserve">21.8287601470947</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8841152191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0353202819824</t>
+    <t xml:space="preserve">21.8841171264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0353221893311</t>
   </si>
   <si>
     <t xml:space="preserve">20.7031860351562</t>
   </si>
   <si>
-    <t xml:space="preserve">21.736499786377</t>
+    <t xml:space="preserve">21.7364978790283</t>
   </si>
   <si>
     <t xml:space="preserve">21.4597206115723</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5335273742676</t>
+    <t xml:space="preserve">21.5335292816162</t>
   </si>
   <si>
     <t xml:space="preserve">22.6591033935547</t>
@@ -3893,25 +3893,25 @@
     <t xml:space="preserve">21.4412670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">20.352596282959</t>
+    <t xml:space="preserve">20.3525981903076</t>
   </si>
   <si>
     <t xml:space="preserve">20.9799671173096</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9948272705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5299377441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5114860534668</t>
+    <t xml:space="preserve">21.9948291778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.529935836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5114841461182</t>
   </si>
   <si>
     <t xml:space="preserve">22.6775531768799</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1204032897949</t>
+    <t xml:space="preserve">23.1204013824463</t>
   </si>
   <si>
     <t xml:space="preserve">22.8620758056641</t>
@@ -3923,73 +3923,73 @@
     <t xml:space="preserve">22.3085136413574</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3859119415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3674583435059</t>
+    <t xml:space="preserve">21.3859100341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3674602508545</t>
   </si>
   <si>
     <t xml:space="preserve">21.8103084564209</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9281997680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0758190155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8877067565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4448585510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2787895202637</t>
+    <t xml:space="preserve">19.928201675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0758171081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8877048492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4448566436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2787857055664</t>
   </si>
   <si>
     <t xml:space="preserve">19.8174877166748</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8138980865479</t>
+    <t xml:space="preserve">20.8138961791992</t>
   </si>
   <si>
     <t xml:space="preserve">20.2049808502197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5002117156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7585430145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3710498809814</t>
+    <t xml:space="preserve">20.5002136230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.758544921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3710479736328</t>
   </si>
   <si>
     <t xml:space="preserve">20.0204601287842</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9871463775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5073928833008</t>
+    <t xml:space="preserve">18.9871482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5073947906494</t>
   </si>
   <si>
     <t xml:space="preserve">17.6770515441895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1291275024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1198978424072</t>
+    <t xml:space="preserve">18.1291255950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1198997497559</t>
   </si>
   <si>
     <t xml:space="preserve">17.0681343078613</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3633670806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0845413208008</t>
+    <t xml:space="preserve">17.3633689880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0845403671265</t>
   </si>
   <si>
     <t xml:space="preserve">15.23215675354</t>
@@ -4007,7 +4007,7 @@
     <t xml:space="preserve">13.4699878692627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2172937393188</t>
+    <t xml:space="preserve">14.2172956466675</t>
   </si>
   <si>
     <t xml:space="preserve">14.060453414917</t>
@@ -4016,19 +4016,19 @@
     <t xml:space="preserve">14.3372325897217</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6878223419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8169851303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2634258270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2541980743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6601438522339</t>
+    <t xml:space="preserve">14.6878213882446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8169860839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2634248733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2541990280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6601448059082</t>
   </si>
   <si>
     <t xml:space="preserve">15.82262134552</t>
@@ -4037,13 +4037,13 @@
     <t xml:space="preserve">15.6565532684326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0420017242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9958715438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.820574760437</t>
+    <t xml:space="preserve">14.0420007705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.99587059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8205757141113</t>
   </si>
   <si>
     <t xml:space="preserve">14.3649110794067</t>
@@ -4052,7 +4052,7 @@
     <t xml:space="preserve">13.8667058944702</t>
   </si>
   <si>
-    <t xml:space="preserve">13.617603302002</t>
+    <t xml:space="preserve">13.6176042556763</t>
   </si>
   <si>
     <t xml:space="preserve">13.8113498687744</t>
@@ -4061,25 +4061,25 @@
     <t xml:space="preserve">12.8057146072388</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7134532928467</t>
+    <t xml:space="preserve">12.713454246521</t>
   </si>
   <si>
     <t xml:space="preserve">13.3592748641968</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9461517333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0476369857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3059663772583</t>
+    <t xml:space="preserve">14.9461507797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0476360321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3059644699097</t>
   </si>
   <si>
     <t xml:space="preserve">15.3428688049316</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0384111404419</t>
+    <t xml:space="preserve">15.0384101867676</t>
   </si>
   <si>
     <t xml:space="preserve">15.2341136932373</t>
@@ -6042,6 +6042,9 @@
   </si>
   <si>
     <t xml:space="preserve">6.65999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15000009536743</t>
   </si>
 </sst>
 </file>
@@ -72082,7 +72085,7 @@
     </row>
     <row r="2528">
       <c r="A2528" s="1" t="n">
-        <v>45999.6911805556</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B2528" t="n">
         <v>53424</v>
@@ -72103,6 +72106,32 @@
         <v>2009</v>
       </c>
       <c r="H2528" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" s="1" t="n">
+        <v>46000.6913078704</v>
+      </c>
+      <c r="B2529" t="n">
+        <v>225199</v>
+      </c>
+      <c r="C2529" t="n">
+        <v>7.19999980926514</v>
+      </c>
+      <c r="D2529" t="n">
+        <v>6.73000001907349</v>
+      </c>
+      <c r="E2529" t="n">
+        <v>6.73999977111816</v>
+      </c>
+      <c r="F2529" t="n">
+        <v>7.15000009536743</v>
+      </c>
+      <c r="G2529" t="s">
+        <v>2010</v>
+      </c>
+      <c r="H2529" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2523984909058</t>
+    <t xml:space="preserve">13.2523975372314</t>
   </si>
   <si>
     <t xml:space="preserve">BSS.MI</t>
@@ -50,37 +50,37 @@
     <t xml:space="preserve">12.747950553894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.397403717041</t>
+    <t xml:space="preserve">12.3974046707153</t>
   </si>
   <si>
     <t xml:space="preserve">12.2435054779053</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2606048583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1409044265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4825611114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8584156036377</t>
+    <t xml:space="preserve">12.2606058120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1409063339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4825620651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.858416557312</t>
   </si>
   <si>
     <t xml:space="preserve">9.79822444915771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3539705276489</t>
+    <t xml:space="preserve">10.3539695739746</t>
   </si>
   <si>
     <t xml:space="preserve">9.84952354431152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.473669052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2941217422485</t>
+    <t xml:space="preserve">10.4736700057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2941198348999</t>
   </si>
   <si>
     <t xml:space="preserve">10.7814664840698</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">10.8156661987305</t>
   </si>
   <si>
-    <t xml:space="preserve">10.730167388916</t>
+    <t xml:space="preserve">10.7301664352417</t>
   </si>
   <si>
     <t xml:space="preserve">10.576268196106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6361169815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.191520690918</t>
+    <t xml:space="preserve">10.6361179351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1915216445923</t>
   </si>
   <si>
     <t xml:space="preserve">10.4565687179565</t>
@@ -107,25 +107,25 @@
     <t xml:space="preserve">10.4907693862915</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0205230712891</t>
+    <t xml:space="preserve">10.0205221176147</t>
   </si>
   <si>
     <t xml:space="preserve">9.03728008270264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97743129730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40492630004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14842987060547</t>
+    <t xml:space="preserve">8.97743034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40492820739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14842891693115</t>
   </si>
   <si>
     <t xml:space="preserve">9.43057632446289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90082263946533</t>
+    <t xml:space="preserve">9.90082359313965</t>
   </si>
   <si>
     <t xml:space="preserve">9.66142654418945</t>
@@ -134,13 +134,13 @@
     <t xml:space="preserve">10.4394693374634</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3454208374023</t>
+    <t xml:space="preserve">10.345419883728</t>
   </si>
   <si>
     <t xml:space="preserve">10.2000713348389</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0037660598755</t>
+    <t xml:space="preserve">11.0037651062012</t>
   </si>
   <si>
     <t xml:space="preserve">10.5506191253662</t>
@@ -149,49 +149,49 @@
     <t xml:space="preserve">10.2257213592529</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1829710006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0379667282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9097156524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8074598312378</t>
+    <t xml:space="preserve">10.1829719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0379638671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9097175598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8074607849121</t>
   </si>
   <si>
     <t xml:space="preserve">11.9442586898804</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1067056655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7732591629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9699077606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.627911567688</t>
+    <t xml:space="preserve">12.1067066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7732601165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9699068069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6279096603394</t>
   </si>
   <si>
     <t xml:space="preserve">11.3714122772217</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3799638748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6621112823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8416585922241</t>
+    <t xml:space="preserve">11.3799629211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6621103286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8416595458984</t>
   </si>
   <si>
     <t xml:space="preserve">11.918607711792</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7989091873169</t>
+    <t xml:space="preserve">11.7989082336426</t>
   </si>
   <si>
     <t xml:space="preserve">12.046856880188</t>
@@ -200,40 +200,40 @@
     <t xml:space="preserve">12.1922073364258</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2007551193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3375558853149</t>
+    <t xml:space="preserve">12.200756072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3375539779663</t>
   </si>
   <si>
     <t xml:space="preserve">12.1323566436768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1665563583374</t>
+    <t xml:space="preserve">12.1665554046631</t>
   </si>
   <si>
     <t xml:space="preserve">12.2178554534912</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9015083312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.568060874939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2859134674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7390594482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.88440990448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8160095214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7048587799072</t>
+    <t xml:space="preserve">11.9015073776245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5680618286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2859125137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7390584945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8844079971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8160085678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7048597335815</t>
   </si>
   <si>
     <t xml:space="preserve">11.6022605895996</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">11.4740114212036</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1918640136719</t>
+    <t xml:space="preserve">11.1918630599976</t>
   </si>
   <si>
     <t xml:space="preserve">11.1063642501831</t>
@@ -272,16 +272,16 @@
     <t xml:space="preserve">11.1405639648438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6019191741943</t>
+    <t xml:space="preserve">10.6019172668457</t>
   </si>
   <si>
     <t xml:space="preserve">10.954140663147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4346113204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3553628921509</t>
+    <t xml:space="preserve">10.4346122741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3553619384766</t>
   </si>
   <si>
     <t xml:space="preserve">10.2232780456543</t>
@@ -290,40 +290,40 @@
     <t xml:space="preserve">10.2673053741455</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92388916015625</t>
+    <t xml:space="preserve">9.92388820648193</t>
   </si>
   <si>
     <t xml:space="preserve">10.3201389312744</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0031385421753</t>
+    <t xml:space="preserve">10.003137588501</t>
   </si>
   <si>
     <t xml:space="preserve">10.3025283813477</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2496948242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6107244491577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4120302200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1302537918091</t>
+    <t xml:space="preserve">10.2496957778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6107234954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4120311737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1302528381348</t>
   </si>
   <si>
     <t xml:space="preserve">10.9189186096191</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2359199523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2799472808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0069742202759</t>
+    <t xml:space="preserve">11.2359209060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2799482345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0069751739502</t>
   </si>
   <si>
     <t xml:space="preserve">10.8308639526367</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">10.8396692276001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9277238845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9101142883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8132524490356</t>
+    <t xml:space="preserve">10.9277248382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9101133346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8132514953613</t>
   </si>
   <si>
     <t xml:space="preserve">10.513861656189</t>
@@ -347,94 +347,94 @@
     <t xml:space="preserve">10.0647773742676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9943323135376</t>
+    <t xml:space="preserve">9.99433326721191</t>
   </si>
   <si>
     <t xml:space="preserve">9.95030498504639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68613719940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0383605957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4962501525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3465557098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.452223777771</t>
+    <t xml:space="preserve">9.68613815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0383586883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4962511062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3465566635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4522218704224</t>
   </si>
   <si>
     <t xml:space="preserve">10.5843076705933</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87985992431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12257862091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67733192443848</t>
+    <t xml:space="preserve">9.87986087799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12258052825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67733097076416</t>
   </si>
   <si>
     <t xml:space="preserve">9.57166481018066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.932692527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1880540847778</t>
+    <t xml:space="preserve">9.93269348144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1880569458008</t>
   </si>
   <si>
     <t xml:space="preserve">9.98552799224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18421936035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14019203186035</t>
+    <t xml:space="preserve">9.18422031402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14019107818604</t>
   </si>
   <si>
     <t xml:space="preserve">9.72136116027832</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0823888778687</t>
+    <t xml:space="preserve">10.082389831543</t>
   </si>
   <si>
     <t xml:space="preserve">10.3817777633667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2849159240723</t>
+    <t xml:space="preserve">10.2849178314209</t>
   </si>
   <si>
     <t xml:space="preserve">10.1352224349976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2144718170166</t>
+    <t xml:space="preserve">10.2144737243652</t>
   </si>
   <si>
     <t xml:space="preserve">10.1528329849243</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6987781524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0774192810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0157794952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0333909988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9893627166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8748912811279</t>
+    <t xml:space="preserve">10.6987800598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0774183273315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0157814025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.033390045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9893636703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8748922348022</t>
   </si>
   <si>
     <t xml:space="preserve">11.0950307846069</t>
@@ -443,31 +443,31 @@
     <t xml:space="preserve">11.2535305023193</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3151702880859</t>
+    <t xml:space="preserve">11.3151693344116</t>
   </si>
   <si>
     <t xml:space="preserve">10.7251968383789</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0510025024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9013071060181</t>
+    <t xml:space="preserve">11.0510015487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9013080596924</t>
   </si>
   <si>
     <t xml:space="preserve">11.1654758453369</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0598087310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2183094024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1214466094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1830854415894</t>
+    <t xml:space="preserve">11.0598077774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2183084487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1214475631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1830863952637</t>
   </si>
   <si>
     <t xml:space="preserve">11.262336730957</t>
@@ -476,55 +476,55 @@
     <t xml:space="preserve">11.5265045166016</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7466421127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.773060798645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6850051879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7994766235352</t>
+    <t xml:space="preserve">11.7466440200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7730588912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.685004234314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7994756698608</t>
   </si>
   <si>
     <t xml:space="preserve">11.6497812271118</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6673936843872</t>
+    <t xml:space="preserve">11.6673927307129</t>
   </si>
   <si>
     <t xml:space="preserve">11.4472532272339</t>
   </si>
   <si>
-    <t xml:space="preserve">11.323974609375</t>
+    <t xml:space="preserve">11.3239755630493</t>
   </si>
   <si>
     <t xml:space="preserve">11.3680038452148</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1390571594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.693808555603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6145601272583</t>
+    <t xml:space="preserve">11.1390581130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6938104629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6145582199097</t>
   </si>
   <si>
     <t xml:space="preserve">11.8258943557739</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0372276306152</t>
+    <t xml:space="preserve">12.0372285842896</t>
   </si>
   <si>
     <t xml:space="preserve">12.054838180542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0636434555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5039224624634</t>
+    <t xml:space="preserve">12.0636444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5039234161377</t>
   </si>
   <si>
     <t xml:space="preserve">12.5303392410278</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">12.4070615768433</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2837839126587</t>
+    <t xml:space="preserve">12.2837820053101</t>
   </si>
   <si>
     <t xml:space="preserve">12.6007843017578</t>
@@ -545,19 +545,19 @@
     <t xml:space="preserve">12.8121185302734</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8561477661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0322570800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4108982086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5782041549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6838703155518</t>
+    <t xml:space="preserve">12.856146812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0322580337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4108972549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5782032012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6838712692261</t>
   </si>
   <si>
     <t xml:space="preserve">13.4285097122192</t>
@@ -566,28 +566,28 @@
     <t xml:space="preserve">14.3707056045532</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2210102081299</t>
+    <t xml:space="preserve">14.2210111618042</t>
   </si>
   <si>
     <t xml:space="preserve">14.2562341690063</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1329536437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1241493225098</t>
+    <t xml:space="preserve">14.1329555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1241512298584</t>
   </si>
   <si>
     <t xml:space="preserve">14.0713157653809</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9216222763062</t>
+    <t xml:space="preserve">13.9216213226318</t>
   </si>
   <si>
     <t xml:space="preserve">13.7807312011719</t>
   </si>
   <si>
-    <t xml:space="preserve">13.604621887207</t>
+    <t xml:space="preserve">13.6046209335327</t>
   </si>
   <si>
     <t xml:space="preserve">13.7631206512451</t>
@@ -599,10 +599,10 @@
     <t xml:space="preserve">13.7278985977173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1995630264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3756742477417</t>
+    <t xml:space="preserve">13.1995639801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.375675201416</t>
   </si>
   <si>
     <t xml:space="preserve">13.1555347442627</t>
@@ -611,52 +611,52 @@
     <t xml:space="preserve">13.6486492156982</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5605945587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.736704826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8775930404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.176983833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0977334976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7845687866211</t>
+    <t xml:space="preserve">13.5605926513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7367038726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8775939941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1769828796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0977344512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7845706939697</t>
   </si>
   <si>
     <t xml:space="preserve">15.3040962219238</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2776803970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4890155792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4978179931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3657369613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4449892044067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3393211364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5330410003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6651258468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5418472290039</t>
+    <t xml:space="preserve">15.2776823043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4890127182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4978227615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3657388687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4449863433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3393182754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5330429077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6651268005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5418462753296</t>
   </si>
   <si>
     <t xml:space="preserve">15.2424573898315</t>
@@ -668,16 +668,16 @@
     <t xml:space="preserve">16.1934604644775</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3695755004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4664363861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5104656219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0387954711914</t>
+    <t xml:space="preserve">16.369571685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4664325714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.510461807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.03879737854</t>
   </si>
   <si>
     <t xml:space="preserve">16.8891010284424</t>
@@ -686,37 +686,37 @@
     <t xml:space="preserve">17.1532688140869</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7746276855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5544910430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2374877929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5897121429443</t>
+    <t xml:space="preserve">16.7746295928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5544891357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2374897003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.589714050293</t>
   </si>
   <si>
     <t xml:space="preserve">16.6513500213623</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5721015930176</t>
+    <t xml:space="preserve">16.5720996856689</t>
   </si>
   <si>
     <t xml:space="preserve">16.9947681427002</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7041816711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8802928924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8538799285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0123805999756</t>
+    <t xml:space="preserve">16.7041835784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8802967071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8538780212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0123825073242</t>
   </si>
   <si>
     <t xml:space="preserve">17.2941589355469</t>
@@ -725,37 +725,37 @@
     <t xml:space="preserve">17.1268520355225</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5368766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0828247070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8626842498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2061061859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3469944000244</t>
+    <t xml:space="preserve">16.5368785858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0828227996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8626861572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2061042785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3469924926758</t>
   </si>
   <si>
     <t xml:space="preserve">17.6551876068115</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5407161712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5054931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7168273925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4526615142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5583267211914</t>
+    <t xml:space="preserve">17.540714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5054912567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7168254852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4526596069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5583248138428</t>
   </si>
   <si>
     <t xml:space="preserve">17.7432441711426</t>
@@ -764,7 +764,7 @@
     <t xml:space="preserve">17.8401050567627</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5759391784668</t>
+    <t xml:space="preserve">17.5759353637695</t>
   </si>
   <si>
     <t xml:space="preserve">16.7482109069824</t>
@@ -773,49 +773,49 @@
     <t xml:space="preserve">16.7658252716064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9507389068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1620750427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2765502929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6865711212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1092433929443</t>
+    <t xml:space="preserve">16.950740814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1620769500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2765483856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6865768432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1092414855957</t>
   </si>
   <si>
     <t xml:space="preserve">16.8186569213867</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2325172424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2853527069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.391019821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2501316070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4350471496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3734073638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6463813781738</t>
+    <t xml:space="preserve">17.2325191497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2853507995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3910217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.250129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4350452423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3734111785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6463832855225</t>
   </si>
   <si>
     <t xml:space="preserve">17.9457683563232</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3722743988037</t>
+    <t xml:space="preserve">19.3722763061523</t>
   </si>
   <si>
     <t xml:space="preserve">19.9358310699463</t>
@@ -824,64 +824,64 @@
     <t xml:space="preserve">20.3849182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5962505340576</t>
+    <t xml:space="preserve">20.5962524414062</t>
   </si>
   <si>
     <t xml:space="preserve">20.3408889770508</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8340015411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0453357696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5824756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0893650054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3271141052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6529178619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7497825622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9170875549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8114204406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0139484405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2869243621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2605075836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3485622406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3221435546875</t>
+    <t xml:space="preserve">20.8340034484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0453338623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5824775695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0893630981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.327112197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6529197692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7497844696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.917085647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8114223480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0139503479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2869205474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2605056762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.348560333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3221454620361</t>
   </si>
   <si>
     <t xml:space="preserve">22.1900615692139</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6303405761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4366188049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4806461334229</t>
+    <t xml:space="preserve">22.6303386688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.436616897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4806480407715</t>
   </si>
   <si>
     <t xml:space="preserve">22.6655616760254</t>
@@ -905,10 +905,10 @@
     <t xml:space="preserve">22.374979019165</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1938972473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3876171112061</t>
+    <t xml:space="preserve">23.1938991546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3876209259033</t>
   </si>
   <si>
     <t xml:space="preserve">23.5108985900879</t>
@@ -917,31 +917,31 @@
     <t xml:space="preserve">23.9159526824951</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2417621612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7084560394287</t>
+    <t xml:space="preserve">24.2417602539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7084541320801</t>
   </si>
   <si>
     <t xml:space="preserve">24.6556243896484</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9197902679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0870933532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9638175964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8933753967285</t>
+    <t xml:space="preserve">24.9197883605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0870990753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9638195037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8933734893799</t>
   </si>
   <si>
     <t xml:space="preserve">26.4255466461182</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4879322052002</t>
+    <t xml:space="preserve">26.4879302978516</t>
   </si>
   <si>
     <t xml:space="preserve">27.3970069885254</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">27.6732940673828</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6804084777832</t>
+    <t xml:space="preserve">28.6804065704346</t>
   </si>
   <si>
     <t xml:space="preserve">29.3666687011719</t>
@@ -968,19 +968,19 @@
     <t xml:space="preserve">28.4665088653564</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0190811157227</t>
+    <t xml:space="preserve">29.0190830230713</t>
   </si>
   <si>
     <t xml:space="preserve">29.4914436340332</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7677345275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8746814727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3024806976318</t>
+    <t xml:space="preserve">29.7677307128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8746795654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3024768829346</t>
   </si>
   <si>
     <t xml:space="preserve">30.7748432159424</t>
@@ -989,13 +989,13 @@
     <t xml:space="preserve">30.2400932312012</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6678924560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8283195495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8996181488037</t>
+    <t xml:space="preserve">30.6678943634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8283157348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8996124267578</t>
   </si>
   <si>
     <t xml:space="preserve">31.0154781341553</t>
@@ -1004,31 +1004,31 @@
     <t xml:space="preserve">30.9976539611816</t>
   </si>
   <si>
-    <t xml:space="preserve">30.935266494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6500682830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7481060028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6857204437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3577556610107</t>
+    <t xml:space="preserve">30.9352645874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6500644683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.748104095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.685718536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3577575683594</t>
   </si>
   <si>
     <t xml:space="preserve">29.5003547668457</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3131923675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2775440216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1687889099121</t>
+    <t xml:space="preserve">29.3131942749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2775421142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1687927246094</t>
   </si>
   <si>
     <t xml:space="preserve">30.1331443786621</t>
@@ -1037,34 +1037,34 @@
     <t xml:space="preserve">29.9994564056396</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9281558990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0529308319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4825344085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8122901916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9121322631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1260318756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7713317871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9674034118652</t>
+    <t xml:space="preserve">29.9281597137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0529346466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4825325012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8122959136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9121284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.126033782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.771333694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9674072265625</t>
   </si>
   <si>
     <t xml:space="preserve">27.2544059753418</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6911182403564</t>
+    <t xml:space="preserve">27.6911201477051</t>
   </si>
   <si>
     <t xml:space="preserve">27.4861316680908</t>
@@ -1076,13 +1076,13 @@
     <t xml:space="preserve">28.1189212799072</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3506450653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7178554534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5734596252441</t>
+    <t xml:space="preserve">28.350643157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7178573608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5734577178955</t>
   </si>
   <si>
     <t xml:space="preserve">28.6180210113525</t>
@@ -1100,31 +1100,31 @@
     <t xml:space="preserve">29.536003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3310203552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1705894470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2329788208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.143856048584</t>
+    <t xml:space="preserve">29.3310222625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1705913543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2329807281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1438541412354</t>
   </si>
   <si>
     <t xml:space="preserve">29.3221073150635</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9656066894531</t>
+    <t xml:space="preserve">28.9656085968018</t>
   </si>
   <si>
     <t xml:space="preserve">28.707145690918</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9923419952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9477825164795</t>
+    <t xml:space="preserve">28.9923439025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9477787017822</t>
   </si>
   <si>
     <t xml:space="preserve">29.607307434082</t>
@@ -1133,49 +1133,49 @@
     <t xml:space="preserve">29.8568572998047</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4023208618164</t>
+    <t xml:space="preserve">29.4023189544678</t>
   </si>
   <si>
     <t xml:space="preserve">29.4112319946289</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8140964508057</t>
+    <t xml:space="preserve">28.814094543457</t>
   </si>
   <si>
     <t xml:space="preserve">29.6875190734863</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6162204742432</t>
+    <t xml:space="preserve">29.6162147521973</t>
   </si>
   <si>
     <t xml:space="preserve">29.6786060333252</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6964321136475</t>
+    <t xml:space="preserve">29.6964282989502</t>
   </si>
   <si>
     <t xml:space="preserve">30.1420555114746</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8390312194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1866188049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5181789398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1795063018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.437967300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3648681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4629039764404</t>
+    <t xml:space="preserve">29.8390274047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1866149902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5181827545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1795101165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4379692077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3648700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4629077911377</t>
   </si>
   <si>
     <t xml:space="preserve">30.4718189239502</t>
@@ -1187,28 +1187,28 @@
     <t xml:space="preserve">30.0974922180176</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0618438720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2311763763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0849800109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4967517852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.819408416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9958572387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.773042678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6928310394287</t>
+    <t xml:space="preserve">30.061840057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.23118019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0849761962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.496753692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8194065093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9958515167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7730407714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6928291320801</t>
   </si>
   <si>
     <t xml:space="preserve">32.1830177307129</t>
@@ -1217,19 +1217,19 @@
     <t xml:space="preserve">32.0760688781738</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9512901306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3077926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1990394592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3951148986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.758731842041</t>
+    <t xml:space="preserve">31.9512920379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.307788848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1990432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3951187133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7587242126465</t>
   </si>
   <si>
     <t xml:space="preserve">34.6963386535645</t>
@@ -1238,40 +1238,40 @@
     <t xml:space="preserve">34.731990814209</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5804786682129</t>
+    <t xml:space="preserve">34.5804710388184</t>
   </si>
   <si>
     <t xml:space="preserve">34.2239799499512</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4378776550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5448303222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4271621704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2221794128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6606941223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3754920959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8674774169922</t>
+    <t xml:space="preserve">34.4378814697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5448265075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4271659851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2221755981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6606864929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.37548828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8674812316895</t>
   </si>
   <si>
     <t xml:space="preserve">33.8496551513672</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1437644958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7159690856934</t>
+    <t xml:space="preserve">34.1437683105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7159652709961</t>
   </si>
   <si>
     <t xml:space="preserve">34.0635528564453</t>
@@ -1292,40 +1292,40 @@
     <t xml:space="preserve">34.6161270141602</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3041915893555</t>
+    <t xml:space="preserve">34.3041954040527</t>
   </si>
   <si>
     <t xml:space="preserve">34.1081161499023</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8425369262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0902938842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.106315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2471122741699</t>
+    <t xml:space="preserve">32.8425407409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0902900695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1063117980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2471084594727</t>
   </si>
   <si>
     <t xml:space="preserve">36.3005867004395</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1847267150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4966659545898</t>
+    <t xml:space="preserve">36.1847305297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4966621398926</t>
   </si>
   <si>
     <t xml:space="preserve">37.4146499633789</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8584785461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9208602905273</t>
+    <t xml:space="preserve">38.8584747314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9208641052246</t>
   </si>
   <si>
     <t xml:space="preserve">38.6178398132324</t>
@@ -1334,25 +1334,25 @@
     <t xml:space="preserve">38.5821914672852</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2702522277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4306755065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2149696350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8049964904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8068008422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3504638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0563468933105</t>
+    <t xml:space="preserve">38.2702484130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4306716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2149772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8050003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8067970275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3504600524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0563507080078</t>
   </si>
   <si>
     <t xml:space="preserve">38.3682899475098</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">38.341552734375</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5197982788086</t>
+    <t xml:space="preserve">38.5198020935059</t>
   </si>
   <si>
     <t xml:space="preserve">38.5643615722656</t>
@@ -1373,46 +1373,46 @@
     <t xml:space="preserve">38.6891403198242</t>
   </si>
   <si>
-    <t xml:space="preserve">38.733699798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4377899169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0812873840332</t>
+    <t xml:space="preserve">38.7336959838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4377861022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0812835693359</t>
   </si>
   <si>
     <t xml:space="preserve">39.0545463562012</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3219261169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5554466247559</t>
+    <t xml:space="preserve">39.3219223022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5554504394531</t>
   </si>
   <si>
     <t xml:space="preserve">38.2880744934082</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3772048950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6998519897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6125297546387</t>
+    <t xml:space="preserve">38.377197265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6998481750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6125259399414</t>
   </si>
   <si>
     <t xml:space="preserve">37.6820220947266</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4663238525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9956665039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.655200958252</t>
+    <t xml:space="preserve">38.4663276672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9956741333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6551933288574</t>
   </si>
   <si>
     <t xml:space="preserve">42.8156204223633</t>
@@ -1421,13 +1421,13 @@
     <t xml:space="preserve">42.423469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0313186645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0848045349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.924373626709</t>
+    <t xml:space="preserve">42.0313262939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0847969055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9243698120117</t>
   </si>
   <si>
     <t xml:space="preserve">41.6213493347168</t>
@@ -1439,22 +1439,22 @@
     <t xml:space="preserve">42.1382713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6926460266113</t>
+    <t xml:space="preserve">41.6926498413086</t>
   </si>
   <si>
     <t xml:space="preserve">41.5322189331055</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7817687988281</t>
+    <t xml:space="preserve">41.7817726135254</t>
   </si>
   <si>
     <t xml:space="preserve">41.3539733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8192253112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3557777404785</t>
+    <t xml:space="preserve">40.819221496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3557739257812</t>
   </si>
   <si>
     <t xml:space="preserve">40.5874977111816</t>
@@ -1463,16 +1463,16 @@
     <t xml:space="preserve">39.8031997680664</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1436729431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6784248352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7799758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4787521362305</t>
+    <t xml:space="preserve">39.1436767578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6784286499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.779972076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4787483215332</t>
   </si>
   <si>
     <t xml:space="preserve">38.6802253723145</t>
@@ -1481,13 +1481,13 @@
     <t xml:space="preserve">37.5750770568848</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2898750305176</t>
+    <t xml:space="preserve">37.2898788452148</t>
   </si>
   <si>
     <t xml:space="preserve">39.5892944335938</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1953506469727</t>
+    <t xml:space="preserve">40.1953430175781</t>
   </si>
   <si>
     <t xml:space="preserve">40.1062278747559</t>
@@ -1496,103 +1496,103 @@
     <t xml:space="preserve">40.5696754455566</t>
   </si>
   <si>
-    <t xml:space="preserve">40.801399230957</t>
+    <t xml:space="preserve">40.8013954162598</t>
   </si>
   <si>
     <t xml:space="preserve">40.9439964294434</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1400718688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9974708557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5161972045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9618186950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2506256103516</t>
+    <t xml:space="preserve">41.1400680541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9974746704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5162010192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9618225097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2506294250488</t>
   </si>
   <si>
     <t xml:space="preserve">39.1793251037598</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2131729125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3914260864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3896217346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6017189025879</t>
+    <t xml:space="preserve">40.2131767272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3914222717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3896179199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6017227172852</t>
   </si>
   <si>
     <t xml:space="preserve">44.5446472167969</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9029426574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2309074401855</t>
+    <t xml:space="preserve">43.902946472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2309036254883</t>
   </si>
   <si>
     <t xml:space="preserve">43.8851203918457</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9635353088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0330352783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3253402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.943904876709</t>
+    <t xml:space="preserve">44.9635314941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.033031463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3253440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9439086914062</t>
   </si>
   <si>
     <t xml:space="preserve">45.5874099731445</t>
   </si>
   <si>
-    <t xml:space="preserve">44.696159362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.009895324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8494720458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9582252502441</t>
+    <t xml:space="preserve">44.6961555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0098991394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8494758605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9582214355469</t>
   </si>
   <si>
     <t xml:space="preserve">41.4609222412109</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1757278442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1578979492188</t>
+    <t xml:space="preserve">41.175724029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.157901763916</t>
   </si>
   <si>
     <t xml:space="preserve">41.0153007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7675514221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.108024597168</t>
+    <t xml:space="preserve">39.7675437927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1080284118652</t>
   </si>
   <si>
     <t xml:space="preserve">40.7479248046875</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7853736877441</t>
+    <t xml:space="preserve">39.7853775024414</t>
   </si>
   <si>
     <t xml:space="preserve">40.5518493652344</t>
@@ -1607,61 +1607,61 @@
     <t xml:space="preserve">40.2488250732422</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9101448059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4288787841797</t>
+    <t xml:space="preserve">39.9101486206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4288749694824</t>
   </si>
   <si>
     <t xml:space="preserve">39.0367240905762</t>
   </si>
   <si>
-    <t xml:space="preserve">42.387825012207</t>
+    <t xml:space="preserve">42.3878211975098</t>
   </si>
   <si>
     <t xml:space="preserve">41.050952911377</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9335708618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0149230957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7087097167969</t>
+    <t xml:space="preserve">41.9335670471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0149269104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7087135314941</t>
   </si>
   <si>
     <t xml:space="preserve">40.6366539001465</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5285873413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8441009521484</t>
+    <t xml:space="preserve">40.5285797119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8440971374512</t>
   </si>
   <si>
     <t xml:space="preserve">37.7366142272949</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4844360351562</t>
+    <t xml:space="preserve">37.484432220459</t>
   </si>
   <si>
     <t xml:space="preserve">36.3316230773926</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0521278381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4757270812988</t>
+    <t xml:space="preserve">37.0521240234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4757194519043</t>
   </si>
   <si>
     <t xml:space="preserve">36.6018104553223</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0073890686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6651496887207</t>
+    <t xml:space="preserve">36.0073928833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6651458740234</t>
   </si>
   <si>
     <t xml:space="preserve">35.3589324951172</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">34.2241325378418</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4135665893555</t>
+    <t xml:space="preserve">33.4135627746582</t>
   </si>
   <si>
     <t xml:space="preserve">33.6657447814941</t>
@@ -1679,10 +1679,10 @@
     <t xml:space="preserve">33.881893157959</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4763145446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6924705505371</t>
+    <t xml:space="preserve">34.4763069152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6924667358398</t>
   </si>
   <si>
     <t xml:space="preserve">35.1427803039551</t>
@@ -1697,61 +1697,61 @@
     <t xml:space="preserve">33.9899711608887</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8278541564941</t>
+    <t xml:space="preserve">33.8278579711914</t>
   </si>
   <si>
     <t xml:space="preserve">34.4402885437012</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1247749328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5036277770996</t>
+    <t xml:space="preserve">35.1247673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5036239624023</t>
   </si>
   <si>
     <t xml:space="preserve">32.4048500061035</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3868370056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.468189239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7744045257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.531530380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.486795425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9371147155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2346153259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.153263092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2166042327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4147415161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.829626083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1265392303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5408306121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6035804748535</t>
+    <t xml:space="preserve">32.3868408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4681911468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7744083404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5315322875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4867973327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9371128082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2346172332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1532649993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2166023254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4147434234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8296222686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1265411376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5408344268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6035823822021</t>
   </si>
   <si>
     <t xml:space="preserve">31.2520389556885</t>
@@ -1760,25 +1760,25 @@
     <t xml:space="preserve">29.6489086151123</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9551219940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1172370910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4054393768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6663284301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6483173370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0806198120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1079387664795</t>
+    <t xml:space="preserve">29.9551239013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1172351837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4054412841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6663303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6483211517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.080623626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1079406738281</t>
   </si>
   <si>
     <t xml:space="preserve">31.3601150512695</t>
@@ -1787,34 +1787,34 @@
     <t xml:space="preserve">30.9818496704102</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7383804321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6122894287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8377475738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9190998077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9010887145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6669216156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0905151367188</t>
+    <t xml:space="preserve">31.7383842468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6122913360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8377494812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9190979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.901086807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.666919708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0905132293701</t>
   </si>
   <si>
     <t xml:space="preserve">28.730260848999</t>
   </si>
   <si>
-    <t xml:space="preserve">28.099817276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5954627990723</t>
+    <t xml:space="preserve">28.0998153686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.595458984375</t>
   </si>
   <si>
     <t xml:space="preserve">26.6407871246338</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">26.0463695526123</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5146980285645</t>
+    <t xml:space="preserve">26.5146999359131</t>
   </si>
   <si>
     <t xml:space="preserve">27.2352046966553</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">27.1091175079346</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0190544128418</t>
+    <t xml:space="preserve">27.0190525054932</t>
   </si>
   <si>
     <t xml:space="preserve">26.7488632202148</t>
@@ -1850,22 +1850,22 @@
     <t xml:space="preserve">27.9196891784668</t>
   </si>
   <si>
-    <t xml:space="preserve">27.577449798584</t>
+    <t xml:space="preserve">27.5774478912354</t>
   </si>
   <si>
     <t xml:space="preserve">27.9377021789551</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8476409912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7936000823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0457763671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0097522735596</t>
+    <t xml:space="preserve">27.8476390838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7936019897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0457782745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0097541809082</t>
   </si>
   <si>
     <t xml:space="preserve">27.7755889892578</t>
@@ -1874,34 +1874,34 @@
     <t xml:space="preserve">28.6041717529297</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5501327514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1805801391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1625671386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6401977539062</t>
+    <t xml:space="preserve">28.5501365661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1805820465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1625652313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6401958465576</t>
   </si>
   <si>
     <t xml:space="preserve">28.6762218475342</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6675109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4513607025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5594367980957</t>
+    <t xml:space="preserve">27.6675090789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.451358795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5594348907471</t>
   </si>
   <si>
     <t xml:space="preserve">25.7581653594971</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7320327758789</t>
+    <t xml:space="preserve">22.7320308685303</t>
   </si>
   <si>
     <t xml:space="preserve">21.7413311004639</t>
@@ -1910,67 +1910,67 @@
     <t xml:space="preserve">21.7233200073242</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7860679626465</t>
+    <t xml:space="preserve">22.7860698699951</t>
   </si>
   <si>
     <t xml:space="preserve">23.4165115356445</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7047157287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5606155395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.236385345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4345264434814</t>
+    <t xml:space="preserve">23.7047176361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5606174468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2363872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4345283508301</t>
   </si>
   <si>
     <t xml:space="preserve">22.5158786773682</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7053089141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8226833343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3630619049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2369747161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3450527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5972290039062</t>
+    <t xml:space="preserve">21.7053070068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8226871490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3630657196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2369766235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3450546264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5972309112549</t>
   </si>
   <si>
     <t xml:space="preserve">19.7239093780518</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3189182281494</t>
+    <t xml:space="preserve">18.318920135498</t>
   </si>
   <si>
     <t xml:space="preserve">18.2828922271729</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5437831878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.877311706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3909683227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0034027099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0036945343018</t>
+    <t xml:space="preserve">19.5437850952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8773097991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3909702301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0034008026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0036964416504</t>
   </si>
   <si>
     <t xml:space="preserve">17.139087677002</t>
@@ -1979,16 +1979,16 @@
     <t xml:space="preserve">17.1120662689209</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2651748657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6617488861084</t>
+    <t xml:space="preserve">17.2651767730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.661750793457</t>
   </si>
   <si>
     <t xml:space="preserve">16.2024250030518</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9502477645874</t>
+    <t xml:space="preserve">15.9502458572388</t>
   </si>
   <si>
     <t xml:space="preserve">15.7160844802856</t>
@@ -1997,22 +1997,22 @@
     <t xml:space="preserve">15.6800575256348</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6170139312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1573944091797</t>
+    <t xml:space="preserve">15.6170129776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1573963165283</t>
   </si>
   <si>
     <t xml:space="preserve">16.6077117919922</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4005661010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4723224639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5533790588379</t>
+    <t xml:space="preserve">16.4005641937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4723205566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5533771514893</t>
   </si>
   <si>
     <t xml:space="preserve">16.490629196167</t>
@@ -2021,58 +2021,58 @@
     <t xml:space="preserve">17.9406509399414</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8232727050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6614551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7968444824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0132923126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.905216217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2654685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1934185028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7250881195068</t>
+    <t xml:space="preserve">18.8232746124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6614570617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7968463897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0132942199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9052152633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2654705047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1934204101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7250890731812</t>
   </si>
   <si>
     <t xml:space="preserve">15.400860786438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0496129989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7524042129517</t>
+    <t xml:space="preserve">15.0496120452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7524032592773</t>
   </si>
   <si>
     <t xml:space="preserve">15.5899934768677</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1486845016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.463906288147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1661052703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7875442504883</t>
+    <t xml:space="preserve">15.1486825942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4639053344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1661071777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7875461578369</t>
   </si>
   <si>
     <t xml:space="preserve">18.1568031311035</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6434421539307</t>
+    <t xml:space="preserve">17.6434440612793</t>
   </si>
   <si>
     <t xml:space="preserve">17.391263961792</t>
@@ -2081,7 +2081,7 @@
     <t xml:space="preserve">18.0127029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0487289428711</t>
+    <t xml:space="preserve">18.0487270355225</t>
   </si>
   <si>
     <t xml:space="preserve">18.2288551330566</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">17.9226398468018</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4543113708496</t>
+    <t xml:space="preserve">17.4543075561523</t>
   </si>
   <si>
     <t xml:space="preserve">18.6791706085205</t>
@@ -2102,16 +2102,16 @@
     <t xml:space="preserve">18.8052616119385</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6251335144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3369312286377</t>
+    <t xml:space="preserve">18.6251354217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3369331359863</t>
   </si>
   <si>
     <t xml:space="preserve">18.9493637084961</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7872467041016</t>
+    <t xml:space="preserve">18.7872505187988</t>
   </si>
   <si>
     <t xml:space="preserve">18.6971855163574</t>
@@ -2120,16 +2120,16 @@
     <t xml:space="preserve">18.3549423217773</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4269924163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9856815338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3552398681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7245006561279</t>
+    <t xml:space="preserve">18.4269962310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9856834411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3552379608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7244987487793</t>
   </si>
   <si>
     <t xml:space="preserve">18.3009052276611</t>
@@ -2138,31 +2138,31 @@
     <t xml:space="preserve">18.6071224212646</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3996810913086</t>
+    <t xml:space="preserve">19.3996829986572</t>
   </si>
   <si>
     <t xml:space="preserve">19.6698703765869</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2462787628174</t>
+    <t xml:space="preserve">20.2462768554688</t>
   </si>
   <si>
     <t xml:space="preserve">20.0661525726318</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9220504760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4176940917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4537200927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2823047637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7515182495117</t>
+    <t xml:space="preserve">19.9220485687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4176921844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4537181854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2823028564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7515163421631</t>
   </si>
   <si>
     <t xml:space="preserve">17.7425136566162</t>
@@ -2171,43 +2171,43 @@
     <t xml:space="preserve">17.7965507507324</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5083465576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4182834625244</t>
+    <t xml:space="preserve">17.5083484649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.418285369873</t>
   </si>
   <si>
     <t xml:space="preserve">16.8508834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9859771728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.868896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0490207672119</t>
+    <t xml:space="preserve">16.9859790802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8688945770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0490245819092</t>
   </si>
   <si>
     <t xml:space="preserve">16.9409465789795</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3462352752686</t>
+    <t xml:space="preserve">17.3462333679199</t>
   </si>
   <si>
     <t xml:space="preserve">17.2741813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3822574615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2831878662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1748199462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9766788482666</t>
+    <t xml:space="preserve">17.3822593688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2831897735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1748161315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.976676940918</t>
   </si>
   <si>
     <t xml:space="preserve">17.6164245605469</t>
@@ -2219,34 +2219,34 @@
     <t xml:space="preserve">18.1387920379639</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9136333465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6974773406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1928310394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9496574401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2381572723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1300792694092</t>
+    <t xml:space="preserve">17.913631439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6974792480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1928291320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9496593475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2381534576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1300811767578</t>
   </si>
   <si>
     <t xml:space="preserve">17.6794662475586</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9676704406738</t>
+    <t xml:space="preserve">17.9676723480225</t>
   </si>
   <si>
     <t xml:space="preserve">18.0847549438477</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0667419433594</t>
+    <t xml:space="preserve">18.0667400360107</t>
   </si>
   <si>
     <t xml:space="preserve">17.8686027526855</t>
@@ -2255,22 +2255,22 @@
     <t xml:space="preserve">17.5173530578613</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6074161529541</t>
+    <t xml:space="preserve">17.6074180603027</t>
   </si>
   <si>
     <t xml:space="preserve">17.5894031524658</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7695293426514</t>
+    <t xml:space="preserve">17.76953125</t>
   </si>
   <si>
     <t xml:space="preserve">18.6365585327148</t>
   </si>
   <si>
-    <t xml:space="preserve">17.24342918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6621894836426</t>
+    <t xml:space="preserve">17.2434272766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6621875762939</t>
   </si>
   <si>
     <t xml:space="preserve">17.2249774932861</t>
@@ -2282,16 +2282,16 @@
     <t xml:space="preserve">16.1916618347168</t>
   </si>
   <si>
-    <t xml:space="preserve">15.684232711792</t>
+    <t xml:space="preserve">15.6842317581177</t>
   </si>
   <si>
     <t xml:space="preserve">14.6232395172119</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8021240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9405145645142</t>
+    <t xml:space="preserve">13.8021230697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9405136108398</t>
   </si>
   <si>
     <t xml:space="preserve">13.7836713790894</t>
@@ -2303,70 +2303,70 @@
     <t xml:space="preserve">13.8943843841553</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8390274047852</t>
+    <t xml:space="preserve">13.8390283584595</t>
   </si>
   <si>
     <t xml:space="preserve">13.4792137145996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9533309936523</t>
+    <t xml:space="preserve">12.953330039978</t>
   </si>
   <si>
     <t xml:space="preserve">13.0732688903809</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0179119110107</t>
+    <t xml:space="preserve">13.0179128646851</t>
   </si>
   <si>
     <t xml:space="preserve">13.303918838501</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3777265548706</t>
+    <t xml:space="preserve">13.3777275085449</t>
   </si>
   <si>
     <t xml:space="preserve">13.1009464263916</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1378507614136</t>
+    <t xml:space="preserve">13.1378498077393</t>
   </si>
   <si>
     <t xml:space="preserve">13.9220628738403</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7006378173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.475622177124</t>
+    <t xml:space="preserve">13.7006387710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4756231307983</t>
   </si>
   <si>
     <t xml:space="preserve">14.4202671051025</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5771102905273</t>
+    <t xml:space="preserve">14.577109336853</t>
   </si>
   <si>
     <t xml:space="preserve">13.8298015594482</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7928981781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6914110183716</t>
+    <t xml:space="preserve">13.7928972244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6914129257202</t>
   </si>
   <si>
     <t xml:space="preserve">14.5125274658203</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1803903579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0988998413086</t>
+    <t xml:space="preserve">14.1803913116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0989007949829</t>
   </si>
   <si>
     <t xml:space="preserve">10.7575378417969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1486196517944</t>
+    <t xml:space="preserve">10.1486215591431</t>
   </si>
   <si>
     <t xml:space="preserve">10.2132024765015</t>
@@ -2375,34 +2375,34 @@
     <t xml:space="preserve">10.4069480895996</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4161748886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5914697647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8590250015259</t>
+    <t xml:space="preserve">10.4161758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5914688110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8590240478516</t>
   </si>
   <si>
     <t xml:space="preserve">10.9236068725586</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4807567596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6837291717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5361127853394</t>
+    <t xml:space="preserve">10.4807558059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6837301254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5361137390137</t>
   </si>
   <si>
     <t xml:space="preserve">10.2962369918823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3700456619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0471343994141</t>
+    <t xml:space="preserve">10.370044708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0471353530884</t>
   </si>
   <si>
     <t xml:space="preserve">10.1762981414795</t>
@@ -2411,13 +2411,13 @@
     <t xml:space="preserve">9.9087438583374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65964221954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53047752380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0932636260986</t>
+    <t xml:space="preserve">9.65964126586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53047657012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0932645797729</t>
   </si>
   <si>
     <t xml:space="preserve">10.4899835586548</t>
@@ -2426,34 +2426,34 @@
     <t xml:space="preserve">10.5730171203613</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4254016876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5176610946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3054618835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4438533782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6652774810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286817550659</t>
+    <t xml:space="preserve">10.4254007339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5176601409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3054628372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4438524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6652784347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0286827087402</t>
   </si>
   <si>
     <t xml:space="preserve">9.96410083770752</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0563611984253</t>
+    <t xml:space="preserve">10.056360244751</t>
   </si>
   <si>
     <t xml:space="preserve">10.120943069458</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50279903411865</t>
+    <t xml:space="preserve">9.50280094146729</t>
   </si>
   <si>
     <t xml:space="preserve">9.29059982299805</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">9.5766077041626</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21217823028564</t>
+    <t xml:space="preserve">9.21218109130859</t>
   </si>
   <si>
     <t xml:space="preserve">9.40131282806396</t>
@@ -2471,19 +2471,19 @@
     <t xml:space="preserve">9.43821620941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47512245178223</t>
+    <t xml:space="preserve">9.47512149810791</t>
   </si>
   <si>
     <t xml:space="preserve">9.20295333862305</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94001293182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98614120483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88004302978516</t>
+    <t xml:space="preserve">8.94001197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9861421585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88004398345947</t>
   </si>
   <si>
     <t xml:space="preserve">9.53970336914062</t>
@@ -2492,55 +2492,55 @@
     <t xml:space="preserve">9.24447059631348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28137493133545</t>
+    <t xml:space="preserve">9.28137588500977</t>
   </si>
   <si>
     <t xml:space="preserve">9.11530685424805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88106536865234</t>
+    <t xml:space="preserve">9.88106632232666</t>
   </si>
   <si>
     <t xml:space="preserve">9.97332668304443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99177742004395</t>
+    <t xml:space="preserve">9.99177837371826</t>
   </si>
   <si>
     <t xml:space="preserve">10.2408809661865</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4346284866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0840377807617</t>
+    <t xml:space="preserve">10.434627532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0840396881104</t>
   </si>
   <si>
     <t xml:space="preserve">10.1024904251099</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61351203918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66886806488037</t>
+    <t xml:space="preserve">9.61351108551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66886711120605</t>
   </si>
   <si>
     <t xml:space="preserve">9.52125072479248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79803276062012</t>
+    <t xml:space="preserve">9.7980318069458</t>
   </si>
   <si>
     <t xml:space="preserve">9.56738090515137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26292324066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39208698272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65041637420654</t>
+    <t xml:space="preserve">9.2629222869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39208793640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65041542053223</t>
   </si>
   <si>
     <t xml:space="preserve">9.31827926635742</t>
@@ -2552,16 +2552,16 @@
     <t xml:space="preserve">9.81648445129395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6873197555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98255252838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7519006729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49357318878174</t>
+    <t xml:space="preserve">9.68732070922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98255157470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75190162658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49357223510742</t>
   </si>
   <si>
     <t xml:space="preserve">10.2777853012085</t>
@@ -2570,7 +2570,7 @@
     <t xml:space="preserve">10.0655860900879</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5822448730469</t>
+    <t xml:space="preserve">10.5822439193726</t>
   </si>
   <si>
     <t xml:space="preserve">10.7298603057861</t>
@@ -2585,13 +2585,13 @@
     <t xml:space="preserve">10.3515930175781</t>
   </si>
   <si>
-    <t xml:space="preserve">11.431037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6340084075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2337017059326</t>
+    <t xml:space="preserve">11.4310369491577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6340093612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2337007522583</t>
   </si>
   <si>
     <t xml:space="preserve">11.993824005127</t>
@@ -2609,19 +2609,19 @@
     <t xml:space="preserve">12.1875705718994</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9661474227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.956919670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7539482116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8277559280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7354955673218</t>
+    <t xml:space="preserve">11.9661464691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9569206237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7539472579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8277568817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7354965209961</t>
   </si>
   <si>
     <t xml:space="preserve">12.0676326751709</t>
@@ -2630,28 +2630,28 @@
     <t xml:space="preserve">12.4551248550415</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2577886581421</t>
+    <t xml:space="preserve">13.2577877044678</t>
   </si>
   <si>
     <t xml:space="preserve">13.2485628128052</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0824956893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5991506576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.40540599823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2024326324463</t>
+    <t xml:space="preserve">13.0824947357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5991516113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4054050445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2024335861206</t>
   </si>
   <si>
     <t xml:space="preserve">13.7559928894043</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7098636627197</t>
+    <t xml:space="preserve">13.7098627090454</t>
   </si>
   <si>
     <t xml:space="preserve">13.7744464874268</t>
@@ -2660,25 +2660,25 @@
     <t xml:space="preserve">13.3408241271973</t>
   </si>
   <si>
-    <t xml:space="preserve">13.719090461731</t>
+    <t xml:space="preserve">13.7190895080566</t>
   </si>
   <si>
     <t xml:space="preserve">13.7283163070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0143213272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1342620849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1250352859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9497394561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6637353897095</t>
+    <t xml:space="preserve">14.0143222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1342601776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1250343322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9497404098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6637334823608</t>
   </si>
   <si>
     <t xml:space="preserve">13.682186126709</t>
@@ -2696,67 +2696,67 @@
     <t xml:space="preserve">14.0512266159058</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0327749252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9312887191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6473264694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7303628921509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0865879058838</t>
+    <t xml:space="preserve">14.0327739715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9312896728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6473274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7303600311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0865859985352</t>
   </si>
   <si>
     <t xml:space="preserve">16.7913551330566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.865161895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7452220916748</t>
+    <t xml:space="preserve">16.8651638031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7452239990234</t>
   </si>
   <si>
     <t xml:space="preserve">16.8190307617188</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1086273193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.997917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9333353042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4720335006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6785955429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3187818527222</t>
+    <t xml:space="preserve">16.1086292266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9979162216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9333343505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4720344543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.678596496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3187808990479</t>
   </si>
   <si>
     <t xml:space="preserve">14.8446645736694</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2967395782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.204478263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7247266769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8538913726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1491241455078</t>
+    <t xml:space="preserve">15.2967405319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2044792175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7247257232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8538904190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1491222381592</t>
   </si>
   <si>
     <t xml:space="preserve">15.2506093978882</t>
@@ -2765,46 +2765,46 @@
     <t xml:space="preserve">14.9830551147461</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1583490371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0753154754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1065826416016</t>
+    <t xml:space="preserve">15.1583480834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0753145217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1065835952759</t>
   </si>
   <si>
     <t xml:space="preserve">12.6027421951294</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0399551391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9753723144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5878801345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3018732070923</t>
+    <t xml:space="preserve">12.0399541854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9753713607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5878791809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.301872253418</t>
   </si>
   <si>
     <t xml:space="preserve">10.6006956100464</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1301689147949</t>
+    <t xml:space="preserve">10.1301679611206</t>
   </si>
   <si>
     <t xml:space="preserve">9.30905342102051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06353950500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9758939743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89285898208618</t>
+    <t xml:space="preserve">8.0635404586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97589349746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8928599357605</t>
   </si>
   <si>
     <t xml:space="preserve">6.5504732131958</t>
@@ -2822,13 +2822,13 @@
     <t xml:space="preserve">6.91028785705566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01177406311035</t>
+    <t xml:space="preserve">7.01177453994751</t>
   </si>
   <si>
     <t xml:space="preserve">7.47307538986206</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05431365966797</t>
+    <t xml:space="preserve">8.05431461334229</t>
   </si>
   <si>
     <t xml:space="preserve">8.85697841644287</t>
@@ -2837,22 +2837,22 @@
     <t xml:space="preserve">9.33673095703125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01382160186768</t>
+    <t xml:space="preserve">9.01382064819336</t>
   </si>
   <si>
     <t xml:space="preserve">8.39567756652832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40029048919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34954643249512</t>
+    <t xml:space="preserve">8.40028953552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34954738616943</t>
   </si>
   <si>
     <t xml:space="preserve">8.25728702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11889553070068</t>
+    <t xml:space="preserve">8.118896484375</t>
   </si>
   <si>
     <t xml:space="preserve">7.74985504150391</t>
@@ -2861,19 +2861,19 @@
     <t xml:space="preserve">7.92976331710815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78675889968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10966968536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.842116355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42694568634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28855514526367</t>
+    <t xml:space="preserve">7.78675937652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10967063903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84211587905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42694520950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28855466842651</t>
   </si>
   <si>
     <t xml:space="preserve">7.26087713241577</t>
@@ -2882,28 +2882,28 @@
     <t xml:space="preserve">7.32545900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33468532562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11326026916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55610942840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77753353118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93437623977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60223913192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33929777145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51920557022095</t>
+    <t xml:space="preserve">7.33468389511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1132607460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5561089515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77753448486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93437719345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60223960876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33929824829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51920461654663</t>
   </si>
   <si>
     <t xml:space="preserve">7.3070068359375</t>
@@ -2912,25 +2912,25 @@
     <t xml:space="preserve">7.14555168151855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10403490066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15939092636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06713104248047</t>
+    <t xml:space="preserve">7.10403394699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15939044952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06713008880615</t>
   </si>
   <si>
     <t xml:space="preserve">6.92874002456665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56533479690552</t>
+    <t xml:space="preserve">7.56533527374268</t>
   </si>
   <si>
     <t xml:space="preserve">7.54227018356323</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44539737701416</t>
+    <t xml:space="preserve">7.445396900177</t>
   </si>
   <si>
     <t xml:space="preserve">7.27010250091553</t>
@@ -2942,19 +2942,19 @@
     <t xml:space="preserve">8.46948623657227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66784477233887</t>
+    <t xml:space="preserve">8.66784381866455</t>
   </si>
   <si>
     <t xml:space="preserve">8.90310764312744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54329395294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69091033935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8754301071167</t>
+    <t xml:space="preserve">8.54329299926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69090938568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87542915344238</t>
   </si>
   <si>
     <t xml:space="preserve">9.32750511169434</t>
@@ -2963,31 +2963,31 @@
     <t xml:space="preserve">11.0066404342651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4863929748535</t>
+    <t xml:space="preserve">11.4863939285278</t>
   </si>
   <si>
     <t xml:space="preserve">11.4956197738647</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2557420730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9420566558838</t>
+    <t xml:space="preserve">11.2557430267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9420576095581</t>
   </si>
   <si>
     <t xml:space="preserve">9.82570934295654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74267768859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4623050689697</t>
+    <t xml:space="preserve">9.74267578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.462306022644</t>
   </si>
   <si>
     <t xml:space="preserve">10.1947507858276</t>
   </si>
   <si>
-    <t xml:space="preserve">10.019455909729</t>
+    <t xml:space="preserve">10.0194549560547</t>
   </si>
   <si>
     <t xml:space="preserve">9.89029216766357</t>
@@ -2996,10 +2996,10 @@
     <t xml:space="preserve">10.3792715072632</t>
   </si>
   <si>
-    <t xml:space="preserve">10.360818862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2224283218384</t>
+    <t xml:space="preserve">10.3608179092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2224292755127</t>
   </si>
   <si>
     <t xml:space="preserve">10.674503326416</t>
@@ -3008,13 +3008,13 @@
     <t xml:space="preserve">10.5453395843506</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7667646408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.021502494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4402637481689</t>
+    <t xml:space="preserve">10.7667636871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0215015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4402627944946</t>
   </si>
   <si>
     <t xml:space="preserve">11.5417499542236</t>
@@ -3023,13 +3023,13 @@
     <t xml:space="preserve">11.6155576705933</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8093042373657</t>
+    <t xml:space="preserve">11.8093032836914</t>
   </si>
   <si>
     <t xml:space="preserve">11.818531036377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.707818031311</t>
+    <t xml:space="preserve">11.7078170776367</t>
   </si>
   <si>
     <t xml:space="preserve">11.6616878509521</t>
@@ -3038,10 +3038,10 @@
     <t xml:space="preserve">11.5694274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3480033874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2741956710815</t>
+    <t xml:space="preserve">11.3480024337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2741947174072</t>
   </si>
   <si>
     <t xml:space="preserve">11.1450309753418</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">12.0030508041382</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3167352676392</t>
+    <t xml:space="preserve">12.3167362213135</t>
   </si>
   <si>
     <t xml:space="preserve">12.8241662979126</t>
@@ -3062,10 +3062,10 @@
     <t xml:space="preserve">12.7042284011841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0548152923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3961801528931</t>
+    <t xml:space="preserve">13.0548162460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3961791992188</t>
   </si>
   <si>
     <t xml:space="preserve">13.2854671478271</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">13.1286239624023</t>
   </si>
   <si>
-    <t xml:space="preserve">13.230110168457</t>
+    <t xml:space="preserve">13.2301120758057</t>
   </si>
   <si>
     <t xml:space="preserve">13.0086870193481</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">13.5437955856323</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3500509262085</t>
+    <t xml:space="preserve">13.3500499725342</t>
   </si>
   <si>
     <t xml:space="preserve">13.5714740753174</t>
@@ -3101,19 +3101,19 @@
     <t xml:space="preserve">13.1470766067505</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4976663589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1101722717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1655282974243</t>
+    <t xml:space="preserve">13.4976654052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1101732254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1655292510986</t>
   </si>
   <si>
     <t xml:space="preserve">13.2670154571533</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2762403488159</t>
+    <t xml:space="preserve">13.2762413024902</t>
   </si>
   <si>
     <t xml:space="preserve">13.0455904006958</t>
@@ -3122,19 +3122,19 @@
     <t xml:space="preserve">13.1747541427612</t>
   </si>
   <si>
-    <t xml:space="preserve">13.331597328186</t>
+    <t xml:space="preserve">13.3315963745117</t>
   </si>
   <si>
     <t xml:space="preserve">13.3869533538818</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5104808807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3813161849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6304197311401</t>
+    <t xml:space="preserve">12.5104818344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3813171386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6304187774658</t>
   </si>
   <si>
     <t xml:space="preserve">12.335186958313</t>
@@ -3143,22 +3143,22 @@
     <t xml:space="preserve">12.7872619628906</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5068922042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4330825805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4515352249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2690601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5735177993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8318462371826</t>
+    <t xml:space="preserve">13.5068912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.433084487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4515342712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2690591812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5735187530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8318471908569</t>
   </si>
   <si>
     <t xml:space="preserve">16.1455326080322</t>
@@ -3182,13 +3182,13 @@
     <t xml:space="preserve">14.7154998779297</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3556861877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9128351211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6545076370239</t>
+    <t xml:space="preserve">14.3556852340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9128360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6545085906982</t>
   </si>
   <si>
     <t xml:space="preserve">14.5033016204834</t>
@@ -3206,10 +3206,10 @@
     <t xml:space="preserve">15.6750059127808</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4166765213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1029930114746</t>
+    <t xml:space="preserve">15.4166774749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1029939651489</t>
   </si>
   <si>
     <t xml:space="preserve">14.9184722900391</t>
@@ -3218,25 +3218,25 @@
     <t xml:space="preserve">15.3889989852905</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7764930725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5827465057373</t>
+    <t xml:space="preserve">15.7764940261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5827445983887</t>
   </si>
   <si>
     <t xml:space="preserve">16.1547584533691</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8133964538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8410758972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9241094589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1178531646729</t>
+    <t xml:space="preserve">15.8133955001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8410730361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9241075515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1178550720215</t>
   </si>
   <si>
     <t xml:space="preserve">15.8502998352051</t>
@@ -3245,40 +3245,40 @@
     <t xml:space="preserve">15.8779783248901</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3520946502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6381015777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4351282119751</t>
+    <t xml:space="preserve">15.3520936965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6381034851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4351301193237</t>
   </si>
   <si>
     <t xml:space="preserve">15.5919713973999</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9517879486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0994033813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0717258453369</t>
+    <t xml:space="preserve">15.9517869949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.099401473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0717239379883</t>
   </si>
   <si>
     <t xml:space="preserve">16.5145740509033</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7877635955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3910446166992</t>
+    <t xml:space="preserve">17.7877655029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3910465240479</t>
   </si>
   <si>
     <t xml:space="preserve">17.4648532867432</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1142654418945</t>
+    <t xml:space="preserve">17.1142635345459</t>
   </si>
   <si>
     <t xml:space="preserve">17.2618808746338</t>
@@ -3287,22 +3287,22 @@
     <t xml:space="preserve">17.5386619567871</t>
   </si>
   <si>
-    <t xml:space="preserve">17.446403503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5663414001465</t>
+    <t xml:space="preserve">17.4464015960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5663394927979</t>
   </si>
   <si>
     <t xml:space="preserve">17.3725929260254</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6216945648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5478858947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0368671417236</t>
+    <t xml:space="preserve">17.6216983795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5478897094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.036865234375</t>
   </si>
   <si>
     <t xml:space="preserve">18.415132522583</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">18.7657222747803</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9835548400879</t>
+    <t xml:space="preserve">19.9835567474365</t>
   </si>
   <si>
     <t xml:space="preserve">19.4299945831299</t>
@@ -3323,13 +3323,13 @@
     <t xml:space="preserve">18.728816986084</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2454738616943</t>
+    <t xml:space="preserve">19.245475769043</t>
   </si>
   <si>
     <t xml:space="preserve">19.1901187896729</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3377361297607</t>
+    <t xml:space="preserve">19.3377342224121</t>
   </si>
   <si>
     <t xml:space="preserve">19.2639274597168</t>
@@ -3338,49 +3338,49 @@
     <t xml:space="preserve">18.5443000793457</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5627498626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2029342651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4704895019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.972282409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1844825744629</t>
+    <t xml:space="preserve">18.5627517700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2029361724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4704914093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9722843170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1844806671143</t>
   </si>
   <si>
     <t xml:space="preserve">19.2823791503906</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9651050567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6109237670898</t>
+    <t xml:space="preserve">19.9651031494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6109256744385</t>
   </si>
   <si>
     <t xml:space="preserve">20.9430618286133</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2567462921143</t>
+    <t xml:space="preserve">21.2567481994629</t>
   </si>
   <si>
     <t xml:space="preserve">21.2198429107666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.312105178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1829395294189</t>
+    <t xml:space="preserve">21.3121013641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1829376220703</t>
   </si>
   <si>
     <t xml:space="preserve">22.7513637542725</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7698173522949</t>
+    <t xml:space="preserve">22.7698135375977</t>
   </si>
   <si>
     <t xml:space="preserve">22.2900619506836</t>
@@ -3389,10 +3389,10 @@
     <t xml:space="preserve">21.8472137451172</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4745845794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7180500030518</t>
+    <t xml:space="preserve">22.4745826721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7180480957031</t>
   </si>
   <si>
     <t xml:space="preserve">20.5371189117432</t>
@@ -3401,10 +3401,10 @@
     <t xml:space="preserve">20.6293773651123</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7216377258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1865272521973</t>
+    <t xml:space="preserve">20.7216358184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1865291595459</t>
   </si>
   <si>
     <t xml:space="preserve">21.1275825500488</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">21.2013912200928</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4633083343506</t>
+    <t xml:space="preserve">20.4633102416992</t>
   </si>
   <si>
     <t xml:space="preserve">19.8728446960449</t>
@@ -3425,16 +3425,16 @@
     <t xml:space="preserve">20.6478290557861</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8508033752441</t>
+    <t xml:space="preserve">20.8508014678955</t>
   </si>
   <si>
     <t xml:space="preserve">21.0906791687012</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1091289520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2234344482422</t>
+    <t xml:space="preserve">21.109130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2234325408936</t>
   </si>
   <si>
     <t xml:space="preserve">19.9466533660889</t>
@@ -3443,7 +3443,7 @@
     <t xml:space="preserve">20.1311721801758</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1127223968506</t>
+    <t xml:space="preserve">20.112720489502</t>
   </si>
   <si>
     <t xml:space="preserve">19.6145172119141</t>
@@ -3452,52 +3452,52 @@
     <t xml:space="preserve">19.8543930053711</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7954483032227</t>
+    <t xml:space="preserve">20.795446395874</t>
   </si>
   <si>
     <t xml:space="preserve">20.3156929016113</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8323497772217</t>
+    <t xml:space="preserve">20.8323516845703</t>
   </si>
   <si>
     <t xml:space="preserve">22.179349899292</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5483913421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0686359405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2162532806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1424465179443</t>
+    <t xml:space="preserve">22.5483894348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0686378479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.216251373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1424446105957</t>
   </si>
   <si>
     <t xml:space="preserve">22.0132808685303</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2531585693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0317306518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1942100524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7846775054932</t>
+    <t xml:space="preserve">22.2531566619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0317325592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1942119598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7846755981445</t>
   </si>
   <si>
     <t xml:space="preserve">23.729320526123</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3935928344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8953876495361</t>
+    <t xml:space="preserve">24.3935947418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8953895568848</t>
   </si>
   <si>
     <t xml:space="preserve">23.0465927124023</t>
@@ -3506,28 +3506,28 @@
     <t xml:space="preserve">22.9174308776855</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3049221038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3971862792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5817012786865</t>
+    <t xml:space="preserve">23.3049240112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3971843719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5817050933838</t>
   </si>
   <si>
     <t xml:space="preserve">23.1388549804688</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5852947235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8067169189453</t>
+    <t xml:space="preserve">22.5852928161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8067188262939</t>
   </si>
   <si>
     <t xml:space="preserve">22.3454170227051</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4894409179688</t>
+    <t xml:space="preserve">23.489444732666</t>
   </si>
   <si>
     <t xml:space="preserve">23.7477722167969</t>
@@ -3539,7 +3539,7 @@
     <t xml:space="preserve">23.2311153411865</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7144584655762</t>
+    <t xml:space="preserve">22.7144565582275</t>
   </si>
   <si>
     <t xml:space="preserve">23.6370620727539</t>
@@ -3548,10 +3548,10 @@
     <t xml:space="preserve">25.0763187408447</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7554531097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4786739349365</t>
+    <t xml:space="preserve">26.7554550170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4786758422852</t>
   </si>
   <si>
     <t xml:space="preserve">26.9768772125244</t>
@@ -3560,16 +3560,16 @@
     <t xml:space="preserve">27.1613998413086</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3828220367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4935340881348</t>
+    <t xml:space="preserve">27.3828258514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4935359954834</t>
   </si>
   <si>
     <t xml:space="preserve">28.157808303833</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0470962524414</t>
+    <t xml:space="preserve">28.04709815979</t>
   </si>
   <si>
     <t xml:space="preserve">27.2721099853516</t>
@@ -3578,79 +3578,79 @@
     <t xml:space="preserve">27.5673427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4012756347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1060447692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9030704498291</t>
+    <t xml:space="preserve">27.4012775421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1060409545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9030685424805</t>
   </si>
   <si>
     <t xml:space="preserve">26.4971256256104</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9251098632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7221412658691</t>
+    <t xml:space="preserve">25.9251136779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7221393585205</t>
   </si>
   <si>
     <t xml:space="preserve">26.6447410583496</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4602203369141</t>
+    <t xml:space="preserve">26.4602241516113</t>
   </si>
   <si>
     <t xml:space="preserve">26.3864154815674</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9989204406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5007152557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9066619873047</t>
+    <t xml:space="preserve">25.9989223480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5007133483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9066600799561</t>
   </si>
   <si>
     <t xml:space="preserve">26.2572479248047</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1280841827393</t>
+    <t xml:space="preserve">26.1280860900879</t>
   </si>
   <si>
     <t xml:space="preserve">25.9620151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6631946563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3310565948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5155773162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4453601837158</t>
+    <t xml:space="preserve">26.6631927490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3310585021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5155754089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4453582763672</t>
   </si>
   <si>
     <t xml:space="preserve">26.7370014190674</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7185478210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8292636871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4417686462402</t>
+    <t xml:space="preserve">26.7185497283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8292617797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4417667388916</t>
   </si>
   <si>
     <t xml:space="preserve">26.5340309143066</t>
   </si>
   <si>
-    <t xml:space="preserve">25.426908493042</t>
+    <t xml:space="preserve">25.4269065856934</t>
   </si>
   <si>
     <t xml:space="preserve">25.3715515136719</t>
@@ -3659,10 +3659,10 @@
     <t xml:space="preserve">26.5893859863281</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1983013153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4750862121582</t>
+    <t xml:space="preserve">27.1983032226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4750843048096</t>
   </si>
   <si>
     <t xml:space="preserve">28.914342880249</t>
@@ -3674,22 +3674,22 @@
     <t xml:space="preserve">30.9625205993652</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5970687866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0322341918945</t>
+    <t xml:space="preserve">29.5970726013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0322360992432</t>
   </si>
   <si>
     <t xml:space="preserve">26.8846168518066</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3459186553955</t>
+    <t xml:space="preserve">27.3459167480469</t>
   </si>
   <si>
     <t xml:space="preserve">27.6227016448975</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7923603057861</t>
+    <t xml:space="preserve">26.7923583984375</t>
   </si>
   <si>
     <t xml:space="preserve">26.9399757385254</t>
@@ -3698,13 +3698,13 @@
     <t xml:space="preserve">27.1798496246338</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8994789123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5857963562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2352085113525</t>
+    <t xml:space="preserve">27.8994808197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5857944488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2352066040039</t>
   </si>
   <si>
     <t xml:space="preserve">27.2167568206787</t>
@@ -3716,13 +3716,13 @@
     <t xml:space="preserve">26.6262912750244</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2536602020264</t>
+    <t xml:space="preserve">27.2536582946777</t>
   </si>
   <si>
     <t xml:space="preserve">27.7703170776367</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3090152740479</t>
+    <t xml:space="preserve">27.3090171813965</t>
   </si>
   <si>
     <t xml:space="preserve">27.9548377990723</t>
@@ -3731,13 +3731,13 @@
     <t xml:space="preserve">28.674467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0286426544189</t>
+    <t xml:space="preserve">28.0286445617676</t>
   </si>
   <si>
     <t xml:space="preserve">27.8072185516357</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3423290252686</t>
+    <t xml:space="preserve">28.3423271179199</t>
   </si>
   <si>
     <t xml:space="preserve">27.917932510376</t>
@@ -3746,25 +3746,25 @@
     <t xml:space="preserve">27.6965084075928</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0506858825684</t>
+    <t xml:space="preserve">27.050687789917</t>
   </si>
   <si>
     <t xml:space="preserve">27.7518653869629</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8256702423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9732875823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3054256439209</t>
+    <t xml:space="preserve">27.8256721496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9732894897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3054275512695</t>
   </si>
   <si>
     <t xml:space="preserve">28.2869739532471</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0840034484863</t>
+    <t xml:space="preserve">28.0840015411377</t>
   </si>
   <si>
     <t xml:space="preserve">27.7887687683105</t>
@@ -3773,19 +3773,19 @@
     <t xml:space="preserve">26.294153213501</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9953327178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.220344543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5191688537598</t>
+    <t xml:space="preserve">26.9953308105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2203464508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5191669464111</t>
   </si>
   <si>
     <t xml:space="preserve">24.6150169372559</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0983600616455</t>
+    <t xml:space="preserve">24.0983619689941</t>
   </si>
   <si>
     <t xml:space="preserve">24.9656066894531</t>
@@ -3794,13 +3794,13 @@
     <t xml:space="preserve">24.356689453125</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7108707427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3418254852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2680168151855</t>
+    <t xml:space="preserve">23.7108688354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3418273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2680187225342</t>
   </si>
   <si>
     <t xml:space="preserve">24.0614566802979</t>
@@ -3809,13 +3809,13 @@
     <t xml:space="preserve">24.2090721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7441806793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6334705352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2423896789551</t>
+    <t xml:space="preserve">24.7441825866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.633472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2423877716064</t>
   </si>
   <si>
     <t xml:space="preserve">25.0947723388672</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">24.8179912567139</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1870288848877</t>
+    <t xml:space="preserve">25.1870307922363</t>
   </si>
   <si>
     <t xml:space="preserve">24.670373916626</t>
@@ -3845,7 +3845,7 @@
     <t xml:space="preserve">24.9287033081055</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8364410400391</t>
+    <t xml:space="preserve">24.8364429473877</t>
   </si>
   <si>
     <t xml:space="preserve">24.2644290924072</t>
@@ -3854,10 +3854,10 @@
     <t xml:space="preserve">24.3013343811035</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8769359588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5263481140137</t>
+    <t xml:space="preserve">23.8769340515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.526346206665</t>
   </si>
   <si>
     <t xml:space="preserve">23.1573066711426</t>
@@ -3869,25 +3869,25 @@
     <t xml:space="preserve">21.8287620544434</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8841133117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0353221893311</t>
+    <t xml:space="preserve">21.8841152191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0353202819824</t>
   </si>
   <si>
     <t xml:space="preserve">20.7031860351562</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7364978790283</t>
+    <t xml:space="preserve">21.7365016937256</t>
   </si>
   <si>
     <t xml:space="preserve">21.4597206115723</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5335292816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6591014862061</t>
+    <t xml:space="preserve">21.5335273742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6591033935547</t>
   </si>
   <si>
     <t xml:space="preserve">21.4412670135498</t>
@@ -3899,34 +3899,34 @@
     <t xml:space="preserve">20.9799671173096</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9948272705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.529935836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5114841461182</t>
+    <t xml:space="preserve">21.9948291778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5299377441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5114860534668</t>
   </si>
   <si>
     <t xml:space="preserve">22.6775531768799</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1204013824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8620758056641</t>
+    <t xml:space="preserve">23.1204032897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8620738983154</t>
   </si>
   <si>
     <t xml:space="preserve">22.9358825683594</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3085136413574</t>
+    <t xml:space="preserve">22.3085117340088</t>
   </si>
   <si>
     <t xml:space="preserve">21.3859119415283</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3674583435059</t>
+    <t xml:space="preserve">21.3674602508545</t>
   </si>
   <si>
     <t xml:space="preserve">21.8103084564209</t>
@@ -3935,16 +3935,16 @@
     <t xml:space="preserve">19.928201675415</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0758171081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8877067565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4448566436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2787895202637</t>
+    <t xml:space="preserve">20.0758190155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8877048492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4448585510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.278787612915</t>
   </si>
   <si>
     <t xml:space="preserve">19.8174877166748</t>
@@ -3965,19 +3965,19 @@
     <t xml:space="preserve">20.3710498809814</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0204601287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9871463775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5073947906494</t>
+    <t xml:space="preserve">20.0204620361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9871444702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5073928833008</t>
   </si>
   <si>
     <t xml:space="preserve">17.6770515441895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1291236877441</t>
+    <t xml:space="preserve">18.1291275024414</t>
   </si>
   <si>
     <t xml:space="preserve">18.1198997497559</t>
@@ -3998,16 +3998,16 @@
     <t xml:space="preserve">16.2839221954346</t>
   </si>
   <si>
-    <t xml:space="preserve">15.370548248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2377910614014</t>
+    <t xml:space="preserve">15.3705463409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.23779296875</t>
   </si>
   <si>
     <t xml:space="preserve">13.4699878692627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2172937393188</t>
+    <t xml:space="preserve">14.2172956466675</t>
   </si>
   <si>
     <t xml:space="preserve">14.0604524612427</t>
@@ -4016,13 +4016,13 @@
     <t xml:space="preserve">14.337233543396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6878213882446</t>
+    <t xml:space="preserve">14.6878223419189</t>
   </si>
   <si>
     <t xml:space="preserve">14.8169851303101</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2634258270264</t>
+    <t xml:space="preserve">14.2634248733521</t>
   </si>
   <si>
     <t xml:space="preserve">14.2541990280151</t>
@@ -4031,13 +4031,13 @@
     <t xml:space="preserve">14.6601438522339</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8226222991943</t>
+    <t xml:space="preserve">15.82262134552</t>
   </si>
   <si>
     <t xml:space="preserve">15.6565532684326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0420017242432</t>
+    <t xml:space="preserve">14.0420007705688</t>
   </si>
   <si>
     <t xml:space="preserve">13.99587059021</t>
@@ -4046,13 +4046,13 @@
     <t xml:space="preserve">13.8205757141113</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3649110794067</t>
+    <t xml:space="preserve">14.3649101257324</t>
   </si>
   <si>
     <t xml:space="preserve">13.8667058944702</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6176042556763</t>
+    <t xml:space="preserve">13.617603302002</t>
   </si>
   <si>
     <t xml:space="preserve">13.8113508224487</t>
@@ -4061,31 +4061,31 @@
     <t xml:space="preserve">12.8057136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">12.713454246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3592739105225</t>
+    <t xml:space="preserve">12.7134532928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3592748641968</t>
   </si>
   <si>
     <t xml:space="preserve">14.9461507797241</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0476369857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3059663772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3428678512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0384111404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2341136932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7736368179321</t>
+    <t xml:space="preserve">15.0476360321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.305965423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3428688049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0384092330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.234112739563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7736358642578</t>
   </si>
   <si>
     <t xml:space="preserve">14.9367218017578</t>
@@ -4103,13 +4103,13 @@
     <t xml:space="preserve">15.5410985946655</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7137775421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.780930519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0303535461426</t>
+    <t xml:space="preserve">15.7137756347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7809314727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0303554534912</t>
   </si>
   <si>
     <t xml:space="preserve">15.8576755523682</t>
@@ -4118,10 +4118,10 @@
     <t xml:space="preserve">15.6466236114502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3204526901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5529909133911</t>
+    <t xml:space="preserve">15.3204536437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5529918670654</t>
   </si>
   <si>
     <t xml:space="preserve">13.612850189209</t>
@@ -4130,7 +4130,7 @@
     <t xml:space="preserve">13.5456981658936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.843090057373</t>
+    <t xml:space="preserve">13.8430891036987</t>
   </si>
   <si>
     <t xml:space="preserve">12.9509143829346</t>
@@ -4145,10 +4145,10 @@
     <t xml:space="preserve">13.0660343170166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7590503692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4040994644165</t>
+    <t xml:space="preserve">12.7590494155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4040985107422</t>
   </si>
   <si>
     <t xml:space="preserve">12.8070163726807</t>
@@ -4157,10 +4157,10 @@
     <t xml:space="preserve">12.7494564056396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8453893661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5959644317627</t>
+    <t xml:space="preserve">12.8453903198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5959634780884</t>
   </si>
   <si>
     <t xml:space="preserve">12.1258945465088</t>
@@ -4169,10 +4169,10 @@
     <t xml:space="preserve">11.8093156814575</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7805366516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5502986907959</t>
+    <t xml:space="preserve">11.780535697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5502977371216</t>
   </si>
   <si>
     <t xml:space="preserve">11.9724006652832</t>
@@ -4184,31 +4184,31 @@
     <t xml:space="preserve">13.0468473434448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7974224090576</t>
+    <t xml:space="preserve">12.7974233627319</t>
   </si>
   <si>
     <t xml:space="preserve">12.7206764221191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6823034286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2026395797729</t>
+    <t xml:space="preserve">12.6823043823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2026405334473</t>
   </si>
   <si>
     <t xml:space="preserve">12.8933544158936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1715602874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1044082641602</t>
+    <t xml:space="preserve">13.1715593338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1044073104858</t>
   </si>
   <si>
     <t xml:space="preserve">13.0948133468628</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4712514877319</t>
+    <t xml:space="preserve">12.4712505340576</t>
   </si>
   <si>
     <t xml:space="preserve">12.4328784942627</t>
@@ -4217,19 +4217,19 @@
     <t xml:space="preserve">12.7782354354858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3058652877808</t>
+    <t xml:space="preserve">13.3058662414551</t>
   </si>
   <si>
     <t xml:space="preserve">13.0372552871704</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3154602050781</t>
+    <t xml:space="preserve">13.3154592514038</t>
   </si>
   <si>
     <t xml:space="preserve">12.480845451355</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6055574417114</t>
+    <t xml:space="preserve">12.6055583953857</t>
   </si>
   <si>
     <t xml:space="preserve">12.1738595962524</t>
@@ -4238,13 +4238,13 @@
     <t xml:space="preserve">12.5096244812012</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2793865203857</t>
+    <t xml:space="preserve">12.2793855667114</t>
   </si>
   <si>
     <t xml:space="preserve">12.3945055007935</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2506055831909</t>
+    <t xml:space="preserve">12.2506074905396</t>
   </si>
   <si>
     <t xml:space="preserve">11.8668756484985</t>
@@ -4259,19 +4259,19 @@
     <t xml:space="preserve">12.2218265533447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3081665039062</t>
+    <t xml:space="preserve">12.3081655502319</t>
   </si>
   <si>
     <t xml:space="preserve">12.1162996292114</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1834526062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8476896286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.164267539978</t>
+    <t xml:space="preserve">12.1834535598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8476886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1642665863037</t>
   </si>
   <si>
     <t xml:space="preserve">11.4927368164062</t>
@@ -4280,19 +4280,19 @@
     <t xml:space="preserve">11.4639577865601</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3296527862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6654176712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1354856491089</t>
+    <t xml:space="preserve">11.3296518325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6654167175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1354866027832</t>
   </si>
   <si>
     <t xml:space="preserve">11.7421627044678</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7709426879883</t>
+    <t xml:space="preserve">11.7709436416626</t>
   </si>
   <si>
     <t xml:space="preserve">11.3488388061523</t>
@@ -4304,7 +4304,7 @@
     <t xml:space="preserve">11.1281938552856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3680257797241</t>
+    <t xml:space="preserve">11.3680248260498</t>
   </si>
   <si>
     <t xml:space="preserve">11.2720928192139</t>
@@ -4319,13 +4319,13 @@
     <t xml:space="preserve">10.8499898910522</t>
   </si>
   <si>
-    <t xml:space="preserve">10.754056930542</t>
+    <t xml:space="preserve">10.7540559768677</t>
   </si>
   <si>
     <t xml:space="preserve">10.9555149078369</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1090059280396</t>
+    <t xml:space="preserve">11.1090068817139</t>
   </si>
   <si>
     <t xml:space="preserve">11.4159908294678</t>
@@ -4334,10 +4334,10 @@
     <t xml:space="preserve">11.6558227539062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5694856643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5790767669678</t>
+    <t xml:space="preserve">11.569483757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5790777206421</t>
   </si>
   <si>
     <t xml:space="preserve">11.5311117172241</t>
@@ -4349,31 +4349,31 @@
     <t xml:space="preserve">11.8764686584473</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0491485595703</t>
+    <t xml:space="preserve">12.049147605896</t>
   </si>
   <si>
     <t xml:space="preserve">11.9628086090088</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9413223266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2003412246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6941957473755</t>
+    <t xml:space="preserve">12.9413213729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2003402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6941967010498</t>
   </si>
   <si>
     <t xml:space="preserve">11.3104658126831</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9267349243164</t>
+    <t xml:space="preserve">10.9267358779907</t>
   </si>
   <si>
     <t xml:space="preserve">10.8212089538574</t>
   </si>
   <si>
-    <t xml:space="preserve">11.895655632019</t>
+    <t xml:space="preserve">11.8956546783447</t>
   </si>
   <si>
     <t xml:space="preserve">11.7229766845703</t>
@@ -4382,7 +4382,7 @@
     <t xml:space="preserve">12.7398624420166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2889804840088</t>
+    <t xml:space="preserve">12.2889795303345</t>
   </si>
   <si>
     <t xml:space="preserve">12.0875205993652</t>
@@ -4397,13 +4397,13 @@
     <t xml:space="preserve">12.3369455337524</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136905670166</t>
+    <t xml:space="preserve">12.4136915206909</t>
   </si>
   <si>
     <t xml:space="preserve">12.5671844482422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2314195632935</t>
+    <t xml:space="preserve">12.2314186096191</t>
   </si>
   <si>
     <t xml:space="preserve">12.106707572937</t>
@@ -4418,16 +4418,16 @@
     <t xml:space="preserve">12.2410135269165</t>
   </si>
   <si>
-    <t xml:space="preserve">12.327353477478</t>
+    <t xml:space="preserve">12.3273525238037</t>
   </si>
   <si>
     <t xml:space="preserve">12.317759513855</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4616584777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9915885925293</t>
+    <t xml:space="preserve">12.4616575241089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.991587638855</t>
   </si>
   <si>
     <t xml:space="preserve">11.9244346618652</t>
@@ -4436,19 +4436,19 @@
     <t xml:space="preserve">12.0395536422729</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0587406158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5000314712524</t>
+    <t xml:space="preserve">12.058741569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5000305175781</t>
   </si>
   <si>
     <t xml:space="preserve">12.8262023925781</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0852222442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7471561431885</t>
+    <t xml:space="preserve">13.0852212905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7471551895142</t>
   </si>
   <si>
     <t xml:space="preserve">13.83349609375</t>
@@ -4457,7 +4457,7 @@
     <t xml:space="preserve">13.8718690872192</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7663431167603</t>
+    <t xml:space="preserve">13.7663440704346</t>
   </si>
   <si>
     <t xml:space="preserve">14.0733280181885</t>
@@ -4469,19 +4469,19 @@
     <t xml:space="preserve">14.2172260284424</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2364130020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7855281829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8143091201782</t>
+    <t xml:space="preserve">14.2364139556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7855291366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8143100738525</t>
   </si>
   <si>
     <t xml:space="preserve">14.1404800415039</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1980400085449</t>
+    <t xml:space="preserve">14.1980409622192</t>
   </si>
   <si>
     <t xml:space="preserve">14.4090929031372</t>
@@ -4496,22 +4496,22 @@
     <t xml:space="preserve">14.1692609786987</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7160768508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9463157653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4378719329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3899049758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3131589889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4474649429321</t>
+    <t xml:space="preserve">14.7160778045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9463148117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4378728866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3899059295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.313159942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4474658966064</t>
   </si>
   <si>
     <t xml:space="preserve">14.3323450088501</t>
@@ -4520,13 +4520,13 @@
     <t xml:space="preserve">14.3515319824219</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5721778869629</t>
+    <t xml:space="preserve">14.5721769332886</t>
   </si>
   <si>
     <t xml:space="preserve">14.5242118835449</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6009578704834</t>
+    <t xml:space="preserve">14.6009588241577</t>
   </si>
   <si>
     <t xml:space="preserve">14.3611268997192</t>
@@ -4535,7 +4535,7 @@
     <t xml:space="preserve">16.0879135131836</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8288974761963</t>
+    <t xml:space="preserve">15.828896522522</t>
   </si>
   <si>
     <t xml:space="preserve">16.2510013580322</t>
@@ -4544,13 +4544,13 @@
     <t xml:space="preserve">16.3373394012451</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7210712432861</t>
+    <t xml:space="preserve">16.7210693359375</t>
   </si>
   <si>
     <t xml:space="preserve">16.3277473449707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2030353546143</t>
+    <t xml:space="preserve">16.2030334472656</t>
   </si>
   <si>
     <t xml:space="preserve">16.2318134307861</t>
@@ -4562,22 +4562,22 @@
     <t xml:space="preserve">16.0207633972168</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3588266372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0783195495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6297369003296</t>
+    <t xml:space="preserve">15.3588256835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0783214569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6297378540039</t>
   </si>
   <si>
     <t xml:space="preserve">14.6105499267578</t>
   </si>
   <si>
-    <t xml:space="preserve">14.639331817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1308879852295</t>
+    <t xml:space="preserve">14.6393308639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1308870315552</t>
   </si>
   <si>
     <t xml:space="preserve">13.9486150741577</t>
@@ -4589,13 +4589,13 @@
     <t xml:space="preserve">13.939022064209</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0541410446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0061750411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3922052383423</t>
+    <t xml:space="preserve">14.054141998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.006175994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3922061920166</t>
   </si>
   <si>
     <t xml:space="preserve">13.6416311264038</t>
@@ -4604,7 +4604,7 @@
     <t xml:space="preserve">13.555290222168</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4593572616577</t>
+    <t xml:space="preserve">13.459358215332</t>
   </si>
   <si>
     <t xml:space="preserve">13.4497661590576</t>
@@ -4619,22 +4619,22 @@
     <t xml:space="preserve">13.3538331985474</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2195272445679</t>
+    <t xml:space="preserve">13.2195262908936</t>
   </si>
   <si>
     <t xml:space="preserve">13.1619672775269</t>
   </si>
   <si>
-    <t xml:space="preserve">13.190746307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9701013565063</t>
+    <t xml:space="preserve">13.1907472610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9701023101807</t>
   </si>
   <si>
     <t xml:space="preserve">13.2578992843628</t>
   </si>
   <si>
-    <t xml:space="preserve">13.027660369873</t>
+    <t xml:space="preserve">13.0276613235474</t>
   </si>
   <si>
     <t xml:space="preserve">13.1811532974243</t>
@@ -4649,10 +4649,10 @@
     <t xml:space="preserve">12.807638168335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8862733840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2768526077271</t>
+    <t xml:space="preserve">12.8862724304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2768535614014</t>
   </si>
   <si>
     <t xml:space="preserve">12.257194519043</t>
@@ -4661,13 +4661,13 @@
     <t xml:space="preserve">12.0900964736938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2080488204956</t>
+    <t xml:space="preserve">12.2080478668213</t>
   </si>
   <si>
     <t xml:space="preserve">12.3554878234863</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7093458175659</t>
+    <t xml:space="preserve">12.7093448638916</t>
   </si>
   <si>
     <t xml:space="preserve">12.5029287338257</t>
@@ -4682,7 +4682,7 @@
     <t xml:space="preserve">11.8050451278687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7165803909302</t>
+    <t xml:space="preserve">11.7165813446045</t>
   </si>
   <si>
     <t xml:space="preserve">11.6477756500244</t>
@@ -4691,7 +4691,7 @@
     <t xml:space="preserve">11.5003347396851</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5593109130859</t>
+    <t xml:space="preserve">11.5593118667603</t>
   </si>
   <si>
     <t xml:space="preserve">11.8836793899536</t>
@@ -4706,10 +4706,10 @@
     <t xml:space="preserve">11.7657279968262</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6969213485718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7755556106567</t>
+    <t xml:space="preserve">11.6969223022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7755565643311</t>
   </si>
   <si>
     <t xml:space="preserve">11.9328269958496</t>
@@ -4718,7 +4718,7 @@
     <t xml:space="preserve">12.0606079101562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9524850845337</t>
+    <t xml:space="preserve">11.9524841308594</t>
   </si>
   <si>
     <t xml:space="preserve">11.8541927337646</t>
@@ -4733,7 +4733,7 @@
     <t xml:space="preserve">11.6182870864868</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5887994766235</t>
+    <t xml:space="preserve">11.5887985229492</t>
   </si>
   <si>
     <t xml:space="preserve">11.6084585189819</t>
@@ -4754,7 +4754,7 @@
     <t xml:space="preserve">11.2939186096191</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4217004776001</t>
+    <t xml:space="preserve">11.4216995239258</t>
   </si>
   <si>
     <t xml:space="preserve">11.4610176086426</t>
@@ -4766,34 +4766,34 @@
     <t xml:space="preserve">11.4511880874634</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7952156066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7460689544678</t>
+    <t xml:space="preserve">11.7952146530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7460680007935</t>
   </si>
   <si>
     <t xml:space="preserve">11.7853860855103</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7264108657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8738508224487</t>
+    <t xml:space="preserve">11.7264099121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8738498687744</t>
   </si>
   <si>
     <t xml:space="preserve">12.0409488677979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1097545623779</t>
+    <t xml:space="preserve">12.1097536087036</t>
   </si>
   <si>
     <t xml:space="preserve">11.6379461288452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5986280441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4020414352417</t>
+    <t xml:space="preserve">11.5986289978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.402042388916</t>
   </si>
   <si>
     <t xml:space="preserve">11.1759672164917</t>
@@ -4802,19 +4802,19 @@
     <t xml:space="preserve">11.2054538726807</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2251129150391</t>
+    <t xml:space="preserve">11.2251138687134</t>
   </si>
   <si>
     <t xml:space="preserve">11.9033374786377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8345336914062</t>
+    <t xml:space="preserve">11.8345327377319</t>
   </si>
   <si>
     <t xml:space="preserve">12.1392431259155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2473659515381</t>
+    <t xml:space="preserve">12.2473649978638</t>
   </si>
   <si>
     <t xml:space="preserve">11.9623146057129</t>
@@ -4823,10 +4823,10 @@
     <t xml:space="preserve">12.1490716934204</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2375354766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2670240402222</t>
+    <t xml:space="preserve">12.2375364303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2670230865479</t>
   </si>
   <si>
     <t xml:space="preserve">12.6995153427124</t>
@@ -4841,7 +4841,7 @@
     <t xml:space="preserve">12.2866830825806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8935098648071</t>
+    <t xml:space="preserve">11.8935089111328</t>
   </si>
   <si>
     <t xml:space="preserve">11.9426555633545</t>
@@ -4853,16 +4853,16 @@
     <t xml:space="preserve">11.3922128677368</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3725538253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3823823928833</t>
+    <t xml:space="preserve">11.3725528717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3823833465576</t>
   </si>
   <si>
     <t xml:space="preserve">11.0186977386475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0481853485107</t>
+    <t xml:space="preserve">11.0481843948364</t>
   </si>
   <si>
     <t xml:space="preserve">10.9400625228882</t>
@@ -4877,13 +4877,13 @@
     <t xml:space="preserve">10.7533044815063</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8614273071289</t>
+    <t xml:space="preserve">10.8614282608032</t>
   </si>
   <si>
     <t xml:space="preserve">10.802451133728</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6746702194214</t>
+    <t xml:space="preserve">10.6746692657471</t>
   </si>
   <si>
     <t xml:space="preserve">10.6156940460205</t>
@@ -4898,10 +4898,10 @@
     <t xml:space="preserve">11.0383558273315</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1563091278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0580148696899</t>
+    <t xml:space="preserve">11.1563081741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0580139160156</t>
   </si>
   <si>
     <t xml:space="preserve">10.7336463928223</t>
@@ -4919,16 +4919,16 @@
     <t xml:space="preserve">10.2225198745728</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0455913543701</t>
+    <t xml:space="preserve">10.0455923080444</t>
   </si>
   <si>
     <t xml:space="preserve">9.90798091888428</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79985904693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53938007354736</t>
+    <t xml:space="preserve">9.79985809326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53938102722168</t>
   </si>
   <si>
     <t xml:space="preserve">9.42634296417236</t>
@@ -4940,7 +4940,7 @@
     <t xml:space="preserve">9.73105239868164</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0161037445068</t>
+    <t xml:space="preserve">10.0161027908325</t>
   </si>
   <si>
     <t xml:space="preserve">10.3306427001953</t>
@@ -4985,25 +4985,25 @@
     <t xml:space="preserve">11.3037481307983</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8122806549072</t>
+    <t xml:space="preserve">10.8122816085815</t>
   </si>
   <si>
     <t xml:space="preserve">11.0678443908691</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1366500854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0285263061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2742605209351</t>
+    <t xml:space="preserve">11.1366491317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0285272598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2742595672607</t>
   </si>
   <si>
     <t xml:space="preserve">11.7362384796143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4341220855713</t>
+    <t xml:space="preserve">12.4341230392456</t>
   </si>
   <si>
     <t xml:space="preserve">12.5619039535522</t>
@@ -5018,7 +5018,7 @@
     <t xml:space="preserve">12.1195840835571</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0507793426514</t>
+    <t xml:space="preserve">12.0507783889771</t>
   </si>
   <si>
     <t xml:space="preserve">11.6576042175293</t>
@@ -5027,13 +5027,13 @@
     <t xml:space="preserve">12.0114622116089</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0802659988403</t>
+    <t xml:space="preserve">12.0802669525146</t>
   </si>
   <si>
     <t xml:space="preserve">11.9721441268921</t>
   </si>
   <si>
-    <t xml:space="preserve">11.706750869751</t>
+    <t xml:space="preserve">11.7067518234253</t>
   </si>
   <si>
     <t xml:space="preserve">11.57896900177</t>
@@ -5048,28 +5048,28 @@
     <t xml:space="preserve">12.5520753860474</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5396518707275</t>
+    <t xml:space="preserve">11.5396528244019</t>
   </si>
   <si>
     <t xml:space="preserve">11.4413595199585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5298233032227</t>
+    <t xml:space="preserve">11.5298223495483</t>
   </si>
   <si>
     <t xml:space="preserve">11.480676651001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9695501327515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2152843475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4315299987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1687307357788</t>
+    <t xml:space="preserve">10.9695510864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2152833938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.431529045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1687316894531</t>
   </si>
   <si>
     <t xml:space="preserve">12.1883888244629</t>
@@ -5084,7 +5084,7 @@
     <t xml:space="preserve">11.9918022155762</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3430652618408</t>
+    <t xml:space="preserve">11.3430662155151</t>
   </si>
   <si>
     <t xml:space="preserve">11.3332366943359</t>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -44,43 +44,43 @@
     <t xml:space="preserve">BSS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9787998199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.747950553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3974046707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2435054779053</t>
+    <t xml:space="preserve">12.9788007736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7479515075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3974027633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.243504524231</t>
   </si>
   <si>
     <t xml:space="preserve">12.2606058120728</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1409063339233</t>
+    <t xml:space="preserve">12.140905380249</t>
   </si>
   <si>
     <t xml:space="preserve">11.4825620651245</t>
   </si>
   <si>
-    <t xml:space="preserve">10.858416557312</t>
+    <t xml:space="preserve">10.8584175109863</t>
   </si>
   <si>
     <t xml:space="preserve">9.79822444915771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3539695739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84952354431152</t>
+    <t xml:space="preserve">10.3539686203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84952449798584</t>
   </si>
   <si>
     <t xml:space="preserve">10.4736700057983</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2941198348999</t>
+    <t xml:space="preserve">10.2941207885742</t>
   </si>
   <si>
     <t xml:space="preserve">10.7814664840698</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">10.8156661987305</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7301664352417</t>
+    <t xml:space="preserve">10.730167388916</t>
   </si>
   <si>
     <t xml:space="preserve">10.576268196106</t>
@@ -98,22 +98,22 @@
     <t xml:space="preserve">10.6361179351807</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1915216445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4565687179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4907693862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0205221176147</t>
+    <t xml:space="preserve">10.1915225982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4565696716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4907684326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0205230712891</t>
   </si>
   <si>
     <t xml:space="preserve">9.03728008270264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97743034362793</t>
+    <t xml:space="preserve">8.97743129730225</t>
   </si>
   <si>
     <t xml:space="preserve">9.40492820739746</t>
@@ -128,25 +128,25 @@
     <t xml:space="preserve">9.90082359313965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66142654418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4394693374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.345419883728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2000713348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0037651062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5506191253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2257213592529</t>
+    <t xml:space="preserve">9.66142559051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4394683837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3454208374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2000722885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0037641525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5506181716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2257204055786</t>
   </si>
   <si>
     <t xml:space="preserve">10.1829719543457</t>
@@ -155,34 +155,34 @@
     <t xml:space="preserve">11.0379638671875</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9097175598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8074607849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9442586898804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1067066192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7732601165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9699068069458</t>
+    <t xml:space="preserve">10.9097166061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8074588775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9442577362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.106707572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7732610702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9699077606201</t>
   </si>
   <si>
     <t xml:space="preserve">11.6279096603394</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3714122772217</t>
+    <t xml:space="preserve">11.371413230896</t>
   </si>
   <si>
     <t xml:space="preserve">11.3799629211426</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6621103286743</t>
+    <t xml:space="preserve">11.6621112823486</t>
   </si>
   <si>
     <t xml:space="preserve">11.8416595458984</t>
@@ -194,58 +194,58 @@
     <t xml:space="preserve">11.7989082336426</t>
   </si>
   <si>
-    <t xml:space="preserve">12.046856880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1922073364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.200756072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3375539779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1323566436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1665554046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2178554534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9015073776245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5680618286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2859125137329</t>
+    <t xml:space="preserve">12.0468578338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1922063827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2007570266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3375558853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1323575973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1665563583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2178573608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9015083312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.568060874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2859134674072</t>
   </si>
   <si>
     <t xml:space="preserve">11.7390584945679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8844079971313</t>
+    <t xml:space="preserve">11.884407043457</t>
   </si>
   <si>
     <t xml:space="preserve">11.8160085678101</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7048597335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6022605895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6364603042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4740114212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1918630599976</t>
+    <t xml:space="preserve">11.7048587799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6022596359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6364593505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4740104675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1918640136719</t>
   </si>
   <si>
     <t xml:space="preserve">11.1063642501831</t>
@@ -254,19 +254,19 @@
     <t xml:space="preserve">11.1149139404297</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3201131820679</t>
+    <t xml:space="preserve">11.3201122283936</t>
   </si>
   <si>
     <t xml:space="preserve">11.3457622528076</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1576642990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0550651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.986665725708</t>
+    <t xml:space="preserve">11.1576633453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0550661087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9866647720337</t>
   </si>
   <si>
     <t xml:space="preserve">11.1405639648438</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">10.3553619384766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2232780456543</t>
+    <t xml:space="preserve">10.22327709198</t>
   </si>
   <si>
     <t xml:space="preserve">10.2673053741455</t>
@@ -293,49 +293,49 @@
     <t xml:space="preserve">9.92388820648193</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3201389312744</t>
+    <t xml:space="preserve">10.3201398849487</t>
   </si>
   <si>
     <t xml:space="preserve">10.003137588501</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3025283813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2496957778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6107234954834</t>
+    <t xml:space="preserve">10.302529335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2496948242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6107244491577</t>
   </si>
   <si>
     <t xml:space="preserve">11.4120311737061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1302528381348</t>
+    <t xml:space="preserve">11.1302518844604</t>
   </si>
   <si>
     <t xml:space="preserve">10.9189186096191</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2359209060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2799482345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0069751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8308639526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8396692276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9277248382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9101133346558</t>
+    <t xml:space="preserve">11.2359199523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2799463272095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0069761276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8308629989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8396701812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9277238845825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9101123809814</t>
   </si>
   <si>
     <t xml:space="preserve">10.8132514953613</t>
@@ -347,43 +347,43 @@
     <t xml:space="preserve">10.0647773742676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99433326721191</t>
+    <t xml:space="preserve">9.9943323135376</t>
   </si>
   <si>
     <t xml:space="preserve">9.95030498504639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68613815307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0383586883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4962511062622</t>
+    <t xml:space="preserve">9.68613910675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0383605957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4962520599365</t>
   </si>
   <si>
     <t xml:space="preserve">10.3465566635132</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4522218704224</t>
+    <t xml:space="preserve">10.4522228240967</t>
   </si>
   <si>
     <t xml:space="preserve">10.5843076705933</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87986087799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12258052825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67733097076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57166481018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93269348144531</t>
+    <t xml:space="preserve">9.87985992431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12258148193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67733287811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57166576385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93269443511963</t>
   </si>
   <si>
     <t xml:space="preserve">10.1880569458008</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">9.98552799224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18422031402588</t>
+    <t xml:space="preserve">9.18421936035156</t>
   </si>
   <si>
     <t xml:space="preserve">9.14019107818604</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">9.72136116027832</t>
   </si>
   <si>
-    <t xml:space="preserve">10.082389831543</t>
+    <t xml:space="preserve">10.0823888778687</t>
   </si>
   <si>
     <t xml:space="preserve">10.3817777633667</t>
@@ -410,76 +410,76 @@
     <t xml:space="preserve">10.2849178314209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1352224349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2144737243652</t>
+    <t xml:space="preserve">10.1352233886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2144727706909</t>
   </si>
   <si>
     <t xml:space="preserve">10.1528329849243</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6987800598145</t>
+    <t xml:space="preserve">10.6987791061401</t>
   </si>
   <si>
     <t xml:space="preserve">11.0774183273315</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0157814025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.033390045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9893636703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8748922348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0950307846069</t>
+    <t xml:space="preserve">11.0157804489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0333909988403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9893627166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8748912811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0950317382812</t>
   </si>
   <si>
     <t xml:space="preserve">11.2535305023193</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3151693344116</t>
+    <t xml:space="preserve">11.3151702880859</t>
   </si>
   <si>
     <t xml:space="preserve">10.7251968383789</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0510015487671</t>
+    <t xml:space="preserve">11.0510025024414</t>
   </si>
   <si>
     <t xml:space="preserve">10.9013080596924</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1654758453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0598077774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2183084487915</t>
+    <t xml:space="preserve">11.1654739379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0598087310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2183074951172</t>
   </si>
   <si>
     <t xml:space="preserve">11.1214475631714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1830863952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.262336730957</t>
+    <t xml:space="preserve">11.183087348938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2623357772827</t>
   </si>
   <si>
     <t xml:space="preserve">11.5265045166016</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7466440200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7730588912964</t>
+    <t xml:space="preserve">11.7466430664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7730598449707</t>
   </si>
   <si>
     <t xml:space="preserve">11.685004234314</t>
@@ -488,19 +488,19 @@
     <t xml:space="preserve">11.7994756698608</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6497812271118</t>
+    <t xml:space="preserve">11.6497821807861</t>
   </si>
   <si>
     <t xml:space="preserve">11.6673927307129</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4472532272339</t>
+    <t xml:space="preserve">11.4472522735596</t>
   </si>
   <si>
     <t xml:space="preserve">11.3239755630493</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3680038452148</t>
+    <t xml:space="preserve">11.3680028915405</t>
   </si>
   <si>
     <t xml:space="preserve">11.1390581130981</t>
@@ -509,28 +509,28 @@
     <t xml:space="preserve">11.6938104629517</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6145582199097</t>
+    <t xml:space="preserve">11.6145572662354</t>
   </si>
   <si>
     <t xml:space="preserve">11.8258943557739</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0372285842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.054838180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0636444091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5039234161377</t>
+    <t xml:space="preserve">12.0372266769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0548372268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0636434555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5039224624634</t>
   </si>
   <si>
     <t xml:space="preserve">12.5303392410278</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4070615768433</t>
+    <t xml:space="preserve">12.4070625305176</t>
   </si>
   <si>
     <t xml:space="preserve">12.2837820053101</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">12.6007843017578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9177856445312</t>
+    <t xml:space="preserve">12.9177875518799</t>
   </si>
   <si>
     <t xml:space="preserve">12.8121185302734</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">12.856146812439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0322580337524</t>
+    <t xml:space="preserve">13.0322589874268</t>
   </si>
   <si>
     <t xml:space="preserve">13.4108972549438</t>
@@ -557,13 +557,13 @@
     <t xml:space="preserve">13.5782032012939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6838712692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4285097122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3707056045532</t>
+    <t xml:space="preserve">13.6838703155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4285087585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3707046508789</t>
   </si>
   <si>
     <t xml:space="preserve">14.2210111618042</t>
@@ -572,19 +572,19 @@
     <t xml:space="preserve">14.2562341690063</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1329555511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1241512298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0713157653809</t>
+    <t xml:space="preserve">14.1329545974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1241502761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0713176727295</t>
   </si>
   <si>
     <t xml:space="preserve">13.9216213226318</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7807312011719</t>
+    <t xml:space="preserve">13.7807321548462</t>
   </si>
   <si>
     <t xml:space="preserve">13.6046209335327</t>
@@ -593,82 +593,82 @@
     <t xml:space="preserve">13.7631206512451</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8335647583008</t>
+    <t xml:space="preserve">13.8335657119751</t>
   </si>
   <si>
     <t xml:space="preserve">13.7278985977173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1995639801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.375675201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1555347442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6486492156982</t>
+    <t xml:space="preserve">13.1995649337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3756761550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.155535697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6486482620239</t>
   </si>
   <si>
     <t xml:space="preserve">13.5605926513672</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7367038726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8775939941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1769828796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0977344512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7845706939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3040962219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2776823043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4890127182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4978227615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3657388687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4449863433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3393182754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5330429077148</t>
+    <t xml:space="preserve">13.736704826355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8775930404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.176983833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0977334976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7845687866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3040971755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.277681350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4890146255493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4978218078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3657360076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4449853897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3393201828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5330400466919</t>
   </si>
   <si>
     <t xml:space="preserve">15.6651268005371</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5418462753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2424573898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8060159683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1934604644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.369571685791</t>
+    <t xml:space="preserve">15.5418472290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2424564361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8060178756714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1934585571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3695735931396</t>
   </si>
   <si>
     <t xml:space="preserve">16.4664325714111</t>
@@ -677,10 +677,10 @@
     <t xml:space="preserve">16.510461807251</t>
   </si>
   <si>
-    <t xml:space="preserve">17.03879737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8891010284424</t>
+    <t xml:space="preserve">17.0387992858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.889102935791</t>
   </si>
   <si>
     <t xml:space="preserve">17.1532688140869</t>
@@ -689,37 +689,37 @@
     <t xml:space="preserve">16.7746295928955</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5544891357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2374897003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.589714050293</t>
+    <t xml:space="preserve">16.5544910430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2374877929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5897121429443</t>
   </si>
   <si>
     <t xml:space="preserve">16.6513500213623</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5720996856689</t>
+    <t xml:space="preserve">16.5721015930176</t>
   </si>
   <si>
     <t xml:space="preserve">16.9947681427002</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7041835784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8802967071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8538780212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0123825073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2941589355469</t>
+    <t xml:space="preserve">16.7041854858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8802947998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8538799285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0123805999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2941608428955</t>
   </si>
   <si>
     <t xml:space="preserve">17.1268520355225</t>
@@ -731,10 +731,10 @@
     <t xml:space="preserve">17.0828227996826</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8626861572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2061042785645</t>
+    <t xml:space="preserve">16.8626842498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2061023712158</t>
   </si>
   <si>
     <t xml:space="preserve">17.3469924926758</t>
@@ -749,46 +749,46 @@
     <t xml:space="preserve">17.5054912567139</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7168254852295</t>
+    <t xml:space="preserve">17.7168273925781</t>
   </si>
   <si>
     <t xml:space="preserve">17.4526596069336</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5583248138428</t>
+    <t xml:space="preserve">17.5583267211914</t>
   </si>
   <si>
     <t xml:space="preserve">17.7432441711426</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8401050567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5759353637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7482109069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7658252716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.950740814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1620769500732</t>
+    <t xml:space="preserve">17.8401012420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5759372711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7482128143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7658214569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9507427215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1620750427246</t>
   </si>
   <si>
     <t xml:space="preserve">17.2765483856201</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6865768432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1092414855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8186569213867</t>
+    <t xml:space="preserve">16.6865730285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1092395782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8186588287354</t>
   </si>
   <si>
     <t xml:space="preserve">17.2325191497803</t>
@@ -797,13 +797,13 @@
     <t xml:space="preserve">17.2853507995605</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3910217285156</t>
+    <t xml:space="preserve">17.391019821167</t>
   </si>
   <si>
     <t xml:space="preserve">17.250129699707</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4350452423096</t>
+    <t xml:space="preserve">17.4350433349609</t>
   </si>
   <si>
     <t xml:space="preserve">17.3734111785889</t>
@@ -812,34 +812,34 @@
     <t xml:space="preserve">17.6463832855225</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9457683563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3722763061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9358310699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3849182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5962524414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3408889770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8340034484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0453338623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5824775695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0893630981445</t>
+    <t xml:space="preserve">17.9457721710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.372278213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9358329772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.384916305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.596248626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3408908843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8340015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0453357696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5824756622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0893650054932</t>
   </si>
   <si>
     <t xml:space="preserve">21.327112197876</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">21.6529197692871</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7497844696045</t>
+    <t xml:space="preserve">21.7497825622559</t>
   </si>
   <si>
     <t xml:space="preserve">21.917085647583</t>
@@ -857,55 +857,55 @@
     <t xml:space="preserve">21.8114223480225</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0139503479004</t>
+    <t xml:space="preserve">22.013952255249</t>
   </si>
   <si>
     <t xml:space="preserve">22.2869205474854</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2605056762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.348560333252</t>
+    <t xml:space="preserve">22.2605037689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3485622406006</t>
   </si>
   <si>
     <t xml:space="preserve">22.3221454620361</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1900615692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6303386688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.436616897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4806480407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6655616760254</t>
+    <t xml:space="preserve">22.1900634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6303405761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4366149902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4806461334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6655597686768</t>
   </si>
   <si>
     <t xml:space="preserve">22.6215343475342</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6743679046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8945064544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0970344543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8328685760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.374979019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1938991546631</t>
+    <t xml:space="preserve">22.6743659973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8945045471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0970363616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8328704833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3749771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1938972473145</t>
   </si>
   <si>
     <t xml:space="preserve">23.3876209259033</t>
@@ -914,10 +914,10 @@
     <t xml:space="preserve">23.5108985900879</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9159526824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2417602539062</t>
+    <t xml:space="preserve">23.9159564971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2417621612549</t>
   </si>
   <si>
     <t xml:space="preserve">24.7084541320801</t>
@@ -926,16 +926,16 @@
     <t xml:space="preserve">24.6556243896484</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9197883605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0870990753174</t>
+    <t xml:space="preserve">24.9197902679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0870971679688</t>
   </si>
   <si>
     <t xml:space="preserve">24.9638195037842</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8933734893799</t>
+    <t xml:space="preserve">24.8933715820312</t>
   </si>
   <si>
     <t xml:space="preserve">26.4255466461182</t>
@@ -944,13 +944,13 @@
     <t xml:space="preserve">26.4879302978516</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3970069885254</t>
+    <t xml:space="preserve">27.3970050811768</t>
   </si>
   <si>
     <t xml:space="preserve">27.6287326812744</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1545696258545</t>
+    <t xml:space="preserve">28.1545715332031</t>
   </si>
   <si>
     <t xml:space="preserve">27.6732940673828</t>
@@ -959,64 +959,64 @@
     <t xml:space="preserve">28.6804065704346</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3666687011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8069820404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4665088653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0190830230713</t>
+    <t xml:space="preserve">29.3666706085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8069839477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4665069580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0190811157227</t>
   </si>
   <si>
     <t xml:space="preserve">29.4914436340332</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7677307128906</t>
+    <t xml:space="preserve">29.7677326202393</t>
   </si>
   <si>
     <t xml:space="preserve">29.8746795654297</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3024768829346</t>
+    <t xml:space="preserve">30.3024806976318</t>
   </si>
   <si>
     <t xml:space="preserve">30.7748432159424</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2400932312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6678943634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8283157348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8996124267578</t>
+    <t xml:space="preserve">30.2400913238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6678905487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8283176422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8996162414551</t>
   </si>
   <si>
     <t xml:space="preserve">31.0154781341553</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9976539611816</t>
+    <t xml:space="preserve">30.9976558685303</t>
   </si>
   <si>
     <t xml:space="preserve">30.9352645874023</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6500644683838</t>
+    <t xml:space="preserve">30.6500663757324</t>
   </si>
   <si>
     <t xml:space="preserve">30.748104095459</t>
   </si>
   <si>
-    <t xml:space="preserve">30.685718536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3577575683594</t>
+    <t xml:space="preserve">30.6857166290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3577537536621</t>
   </si>
   <si>
     <t xml:space="preserve">29.5003547668457</t>
@@ -1025,82 +1025,82 @@
     <t xml:space="preserve">29.3131942749023</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2775421142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1687927246094</t>
+    <t xml:space="preserve">29.2775440216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1687908172607</t>
   </si>
   <si>
     <t xml:space="preserve">30.1331443786621</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9994564056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9281597137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0529346466064</t>
+    <t xml:space="preserve">29.9994583129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9281558990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0529327392578</t>
   </si>
   <si>
     <t xml:space="preserve">29.4825325012207</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8122959136963</t>
+    <t xml:space="preserve">29.8122940063477</t>
   </si>
   <si>
     <t xml:space="preserve">28.9121284484863</t>
   </si>
   <si>
-    <t xml:space="preserve">29.126033782959</t>
+    <t xml:space="preserve">29.1260318756104</t>
   </si>
   <si>
     <t xml:space="preserve">27.771333694458</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9674072265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2544059753418</t>
+    <t xml:space="preserve">27.9674053192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2544078826904</t>
   </si>
   <si>
     <t xml:space="preserve">27.6911201477051</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4861316680908</t>
+    <t xml:space="preserve">27.4861297607422</t>
   </si>
   <si>
     <t xml:space="preserve">27.5752582550049</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1189212799072</t>
+    <t xml:space="preserve">28.1189193725586</t>
   </si>
   <si>
     <t xml:space="preserve">28.350643157959</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7178573608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5734577178955</t>
+    <t xml:space="preserve">27.7178592681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5734596252441</t>
   </si>
   <si>
     <t xml:space="preserve">28.6180210113525</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5199813842773</t>
+    <t xml:space="preserve">28.519983291626</t>
   </si>
   <si>
     <t xml:space="preserve">28.7873573303223</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7855548858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.536003112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3310222625732</t>
+    <t xml:space="preserve">29.7855529785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5360050201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.331018447876</t>
   </si>
   <si>
     <t xml:space="preserve">29.1705913543701</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">29.2329807281494</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1438541412354</t>
+    <t xml:space="preserve">29.143856048584</t>
   </si>
   <si>
     <t xml:space="preserve">29.3221073150635</t>
@@ -1118,22 +1118,22 @@
     <t xml:space="preserve">28.9656085968018</t>
   </si>
   <si>
-    <t xml:space="preserve">28.707145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9923439025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9477787017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.607307434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8568572998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4023189544678</t>
+    <t xml:space="preserve">28.7071437835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9923419952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9477825164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6073036193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8568553924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4023208618164</t>
   </si>
   <si>
     <t xml:space="preserve">29.4112319946289</t>
@@ -1142,58 +1142,58 @@
     <t xml:space="preserve">28.814094543457</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6875190734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6162147521973</t>
+    <t xml:space="preserve">29.687520980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6162166595459</t>
   </si>
   <si>
     <t xml:space="preserve">29.6786060333252</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6964282989502</t>
+    <t xml:space="preserve">29.6964321136475</t>
   </si>
   <si>
     <t xml:space="preserve">30.1420555114746</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8390274047852</t>
+    <t xml:space="preserve">29.8390312194824</t>
   </si>
   <si>
     <t xml:space="preserve">30.1866149902344</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5181827545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1795101165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4379692077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3648700714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4629077911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4718189239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2935676574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0974922180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.061840057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.23118019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0849761962891</t>
+    <t xml:space="preserve">29.518180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1795063018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.437967300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3648681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4629039764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4718151092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.293571472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0974941253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0618419647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2311782836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0849800109863</t>
   </si>
   <si>
     <t xml:space="preserve">31.496753692627</t>
@@ -1202,10 +1202,10 @@
     <t xml:space="preserve">30.8194065093994</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9958515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7730407714844</t>
+    <t xml:space="preserve">31.9958553314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7730445861816</t>
   </si>
   <si>
     <t xml:space="preserve">31.6928291320801</t>
@@ -1217,40 +1217,40 @@
     <t xml:space="preserve">32.0760688781738</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9512920379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.307788848877</t>
+    <t xml:space="preserve">31.9512882232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3077926635742</t>
   </si>
   <si>
     <t xml:space="preserve">33.1990432739258</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3951187133789</t>
+    <t xml:space="preserve">33.3951225280762</t>
   </si>
   <si>
     <t xml:space="preserve">34.7587242126465</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6963386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.731990814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5804710388184</t>
+    <t xml:space="preserve">34.6963424682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7319869995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5804748535156</t>
   </si>
   <si>
     <t xml:space="preserve">34.2239799499512</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4378814697266</t>
+    <t xml:space="preserve">34.4378776550293</t>
   </si>
   <si>
     <t xml:space="preserve">34.5448265075684</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4271659851074</t>
+    <t xml:space="preserve">35.4271697998047</t>
   </si>
   <si>
     <t xml:space="preserve">35.2221755981445</t>
@@ -1265,19 +1265,19 @@
     <t xml:space="preserve">33.8674812316895</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8496551513672</t>
+    <t xml:space="preserve">33.8496513366699</t>
   </si>
   <si>
     <t xml:space="preserve">34.1437683105469</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7159652709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0635528564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3130989074707</t>
+    <t xml:space="preserve">33.7159690856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0635566711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.313102722168</t>
   </si>
   <si>
     <t xml:space="preserve">34.1170272827148</t>
@@ -1286,16 +1286,16 @@
     <t xml:space="preserve">34.420051574707</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7765502929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6161270141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3041954040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1081161499023</t>
+    <t xml:space="preserve">34.776554107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6161308288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3041915893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1081123352051</t>
   </si>
   <si>
     <t xml:space="preserve">32.8425407409668</t>
@@ -1304,16 +1304,16 @@
     <t xml:space="preserve">34.0902900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1063117980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2471084594727</t>
+    <t xml:space="preserve">35.106315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2471122741699</t>
   </si>
   <si>
     <t xml:space="preserve">36.3005867004395</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1847305297852</t>
+    <t xml:space="preserve">36.1847267150879</t>
   </si>
   <si>
     <t xml:space="preserve">36.4966621398926</t>
@@ -1340,10 +1340,10 @@
     <t xml:space="preserve">38.4306716918945</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2149772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8050003051758</t>
+    <t xml:space="preserve">39.214973449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8049964904785</t>
   </si>
   <si>
     <t xml:space="preserve">37.8067970275879</t>
@@ -1358,31 +1358,31 @@
     <t xml:space="preserve">38.3682899475098</t>
   </si>
   <si>
-    <t xml:space="preserve">38.341552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5198020935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5643615722656</t>
+    <t xml:space="preserve">38.3415565490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5198059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5643653869629</t>
   </si>
   <si>
     <t xml:space="preserve">38.6089248657227</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6891403198242</t>
+    <t xml:space="preserve">38.689136505127</t>
   </si>
   <si>
     <t xml:space="preserve">38.7336959838867</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4377861022949</t>
+    <t xml:space="preserve">39.4377899169922</t>
   </si>
   <si>
     <t xml:space="preserve">39.0812835693359</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0545463562012</t>
+    <t xml:space="preserve">39.0545501708984</t>
   </si>
   <si>
     <t xml:space="preserve">39.3219223022461</t>
@@ -1391,31 +1391,31 @@
     <t xml:space="preserve">38.5554504394531</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2880744934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.377197265625</t>
+    <t xml:space="preserve">38.2880783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3771934509277</t>
   </si>
   <si>
     <t xml:space="preserve">37.6998481750488</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6125259399414</t>
+    <t xml:space="preserve">36.6125297546387</t>
   </si>
   <si>
     <t xml:space="preserve">37.6820220947266</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4663276672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9956741333008</t>
+    <t xml:space="preserve">38.4663238525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9956703186035</t>
   </si>
   <si>
     <t xml:space="preserve">42.6551933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8156204223633</t>
+    <t xml:space="preserve">42.8156242370605</t>
   </si>
   <si>
     <t xml:space="preserve">42.423469543457</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">42.0847969055176</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9243698120117</t>
+    <t xml:space="preserve">41.924373626709</t>
   </si>
   <si>
     <t xml:space="preserve">41.6213493347168</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">40.5874977111816</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8031997680664</t>
+    <t xml:space="preserve">39.8031959533691</t>
   </si>
   <si>
     <t xml:space="preserve">39.1436767578125</t>
@@ -1472,22 +1472,22 @@
     <t xml:space="preserve">42.779972076416</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4787483215332</t>
+    <t xml:space="preserve">41.4787521362305</t>
   </si>
   <si>
     <t xml:space="preserve">38.6802253723145</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5750770568848</t>
+    <t xml:space="preserve">37.5750732421875</t>
   </si>
   <si>
     <t xml:space="preserve">37.2898788452148</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5892944335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1953430175781</t>
+    <t xml:space="preserve">39.589298248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1953468322754</t>
   </si>
   <si>
     <t xml:space="preserve">40.1062278747559</t>
@@ -1502,13 +1502,13 @@
     <t xml:space="preserve">40.9439964294434</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1400680541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9974746704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5162010192871</t>
+    <t xml:space="preserve">41.1400718688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9974708557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5161972045898</t>
   </si>
   <si>
     <t xml:space="preserve">40.9618225097656</t>
@@ -1520,13 +1520,13 @@
     <t xml:space="preserve">39.1793251037598</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2131767272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3914222717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3896179199219</t>
+    <t xml:space="preserve">40.2131729125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3914184570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3896255493164</t>
   </si>
   <si>
     <t xml:space="preserve">42.6017227172852</t>
@@ -1544,16 +1544,16 @@
     <t xml:space="preserve">43.8851203918457</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9635314941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.033031463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3253440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9439086914062</t>
+    <t xml:space="preserve">44.9635276794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0330352783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3253402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.943904876709</t>
   </si>
   <si>
     <t xml:space="preserve">45.5874099731445</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">44.0098991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8494758605957</t>
+    <t xml:space="preserve">43.8494720458984</t>
   </si>
   <si>
     <t xml:space="preserve">42.9582214355469</t>
@@ -1574,25 +1574,25 @@
     <t xml:space="preserve">41.4609222412109</t>
   </si>
   <si>
-    <t xml:space="preserve">41.175724029541</t>
+    <t xml:space="preserve">41.1757278442383</t>
   </si>
   <si>
     <t xml:space="preserve">41.157901763916</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0153007507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7675437927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1080284118652</t>
+    <t xml:space="preserve">41.0152969360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7675476074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1080207824707</t>
   </si>
   <si>
     <t xml:space="preserve">40.7479248046875</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7853775024414</t>
+    <t xml:space="preserve">39.7853736877441</t>
   </si>
   <si>
     <t xml:space="preserve">40.5518493652344</t>
@@ -1604,13 +1604,13 @@
     <t xml:space="preserve">39.3040962219238</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2488250732422</t>
+    <t xml:space="preserve">40.2488288879395</t>
   </si>
   <si>
     <t xml:space="preserve">39.9101486206055</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4288749694824</t>
+    <t xml:space="preserve">39.4288787841797</t>
   </si>
   <si>
     <t xml:space="preserve">39.0367240905762</t>
@@ -1619,13 +1619,13 @@
     <t xml:space="preserve">42.3878211975098</t>
   </si>
   <si>
-    <t xml:space="preserve">41.050952911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9335670471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0149269104004</t>
+    <t xml:space="preserve">41.0509490966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9335708618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0149230957031</t>
   </si>
   <si>
     <t xml:space="preserve">40.7087135314941</t>
@@ -1634,13 +1634,13 @@
     <t xml:space="preserve">40.6366539001465</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5285797119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8440971374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7366142272949</t>
+    <t xml:space="preserve">40.5285835266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8441009521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7366104125977</t>
   </si>
   <si>
     <t xml:space="preserve">37.484432220459</t>
@@ -1655,37 +1655,37 @@
     <t xml:space="preserve">36.4757194519043</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6018104553223</t>
+    <t xml:space="preserve">36.6018142700195</t>
   </si>
   <si>
     <t xml:space="preserve">36.0073928833008</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6651458740234</t>
+    <t xml:space="preserve">35.6651496887207</t>
   </si>
   <si>
     <t xml:space="preserve">35.3589324951172</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2241325378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4135627746582</t>
+    <t xml:space="preserve">34.2241363525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4135589599609</t>
   </si>
   <si>
     <t xml:space="preserve">33.6657447814941</t>
   </si>
   <si>
-    <t xml:space="preserve">33.881893157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4763069152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6924667358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1427803039551</t>
+    <t xml:space="preserve">33.8818893432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4763107299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6924629211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1427841186523</t>
   </si>
   <si>
     <t xml:space="preserve">34.7284927368164</t>
@@ -1706,7 +1706,7 @@
     <t xml:space="preserve">35.1247673034668</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5036239624023</t>
+    <t xml:space="preserve">33.5036277770996</t>
   </si>
   <si>
     <t xml:space="preserve">32.4048500061035</t>
@@ -1718,19 +1718,19 @@
     <t xml:space="preserve">31.4681911468506</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7744083404541</t>
+    <t xml:space="preserve">31.7744045257568</t>
   </si>
   <si>
     <t xml:space="preserve">30.5315322875977</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4867973327637</t>
+    <t xml:space="preserve">29.4867935180664</t>
   </si>
   <si>
     <t xml:space="preserve">29.9371128082275</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2346172332764</t>
+    <t xml:space="preserve">29.2346153259277</t>
   </si>
   <si>
     <t xml:space="preserve">30.1532649993896</t>
@@ -1742,22 +1742,22 @@
     <t xml:space="preserve">29.4147434234619</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8296222686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1265411376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5408344268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6035823822021</t>
+    <t xml:space="preserve">27.8296241760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1265392303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5408325195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6035785675049</t>
   </si>
   <si>
     <t xml:space="preserve">31.2520389556885</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6489086151123</t>
+    <t xml:space="preserve">29.6489067077637</t>
   </si>
   <si>
     <t xml:space="preserve">29.9551239013672</t>
@@ -1766,28 +1766,28 @@
     <t xml:space="preserve">30.1172351837158</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4054412841797</t>
+    <t xml:space="preserve">30.4054393768311</t>
   </si>
   <si>
     <t xml:space="preserve">31.6663303375244</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6483211517334</t>
+    <t xml:space="preserve">31.6483173370361</t>
   </si>
   <si>
     <t xml:space="preserve">32.080623626709</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1079406738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3601150512695</t>
+    <t xml:space="preserve">31.1079368591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3601169586182</t>
   </si>
   <si>
     <t xml:space="preserve">30.9818496704102</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7383842468262</t>
+    <t xml:space="preserve">31.7383861541748</t>
   </si>
   <si>
     <t xml:space="preserve">31.6122913360596</t>
@@ -1799,25 +1799,25 @@
     <t xml:space="preserve">29.9190979003906</t>
   </si>
   <si>
-    <t xml:space="preserve">29.901086807251</t>
+    <t xml:space="preserve">29.9010887145996</t>
   </si>
   <si>
     <t xml:space="preserve">29.666919708252</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0905132293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.730260848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0998153686523</t>
+    <t xml:space="preserve">29.0905151367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7302627563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.099817276001</t>
   </si>
   <si>
     <t xml:space="preserve">27.595458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6407871246338</t>
+    <t xml:space="preserve">26.6407890319824</t>
   </si>
   <si>
     <t xml:space="preserve">26.2805347442627</t>
@@ -1835,28 +1835,28 @@
     <t xml:space="preserve">27.0550804138184</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1091175079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0190525054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7488632202148</t>
+    <t xml:space="preserve">27.1091194152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0190563201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7488651275635</t>
   </si>
   <si>
     <t xml:space="preserve">27.4693717956543</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9196891784668</t>
+    <t xml:space="preserve">27.9196910858154</t>
   </si>
   <si>
     <t xml:space="preserve">27.5774478912354</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9377021789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8476390838623</t>
+    <t xml:space="preserve">27.9377002716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8476371765137</t>
   </si>
   <si>
     <t xml:space="preserve">27.7936019897461</t>
@@ -1868,7 +1868,7 @@
     <t xml:space="preserve">28.0097541809082</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7755889892578</t>
+    <t xml:space="preserve">27.7755870819092</t>
   </si>
   <si>
     <t xml:space="preserve">28.6041717529297</t>
@@ -1901,25 +1901,25 @@
     <t xml:space="preserve">25.7581653594971</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7320308685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7413311004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7233200073242</t>
+    <t xml:space="preserve">22.7320289611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7413291931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7233219146729</t>
   </si>
   <si>
     <t xml:space="preserve">22.7860698699951</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4165115356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7047176361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5606174468994</t>
+    <t xml:space="preserve">23.4165134429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.704719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5606155395508</t>
   </si>
   <si>
     <t xml:space="preserve">23.2363872528076</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">21.2369766235352</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3450546264648</t>
+    <t xml:space="preserve">21.3450565338135</t>
   </si>
   <si>
     <t xml:space="preserve">21.5972309112549</t>
@@ -1952,16 +1952,16 @@
     <t xml:space="preserve">19.7239093780518</t>
   </si>
   <si>
-    <t xml:space="preserve">18.318920135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2828922271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5437850952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8773097991943</t>
+    <t xml:space="preserve">18.3189182281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2828941345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5437831878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.877311706543</t>
   </si>
   <si>
     <t xml:space="preserve">18.3909702301025</t>
@@ -1976,10 +1976,10 @@
     <t xml:space="preserve">17.139087677002</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1120662689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2651767730713</t>
+    <t xml:space="preserve">17.1120681762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2651748657227</t>
   </si>
   <si>
     <t xml:space="preserve">16.661750793457</t>
@@ -1988,55 +1988,55 @@
     <t xml:space="preserve">16.2024250030518</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9502458572388</t>
+    <t xml:space="preserve">15.9502477645874</t>
   </si>
   <si>
     <t xml:space="preserve">15.7160844802856</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6800575256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6170129776001</t>
+    <t xml:space="preserve">15.6800584793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6170120239258</t>
   </si>
   <si>
     <t xml:space="preserve">16.1573963165283</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6077117919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4005641937256</t>
+    <t xml:space="preserve">16.6077098846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4005661010742</t>
   </si>
   <si>
     <t xml:space="preserve">17.4723205566406</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5533771514893</t>
+    <t xml:space="preserve">17.5533790588379</t>
   </si>
   <si>
     <t xml:space="preserve">16.490629196167</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9406509399414</t>
+    <t xml:space="preserve">17.94065284729</t>
   </si>
   <si>
     <t xml:space="preserve">18.8232746124268</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6614570617676</t>
+    <t xml:space="preserve">17.6614589691162</t>
   </si>
   <si>
     <t xml:space="preserve">16.7968463897705</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0132942199707</t>
+    <t xml:space="preserve">16.0132923126221</t>
   </si>
   <si>
     <t xml:space="preserve">15.9052152633667</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2654705047607</t>
+    <t xml:space="preserve">16.2654685974121</t>
   </si>
   <si>
     <t xml:space="preserve">16.1934204101562</t>
@@ -2048,16 +2048,16 @@
     <t xml:space="preserve">15.400860786438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0496120452881</t>
+    <t xml:space="preserve">15.0496110916138</t>
   </si>
   <si>
     <t xml:space="preserve">14.7524032592773</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5899934768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1486825942993</t>
+    <t xml:space="preserve">15.5899953842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.148681640625</t>
   </si>
   <si>
     <t xml:space="preserve">15.4639053344727</t>
@@ -2066,16 +2066,16 @@
     <t xml:space="preserve">17.1661071777344</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7875461578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1568031311035</t>
+    <t xml:space="preserve">17.7875442504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1568050384521</t>
   </si>
   <si>
     <t xml:space="preserve">17.6434440612793</t>
   </si>
   <si>
-    <t xml:space="preserve">17.391263961792</t>
+    <t xml:space="preserve">17.3912658691406</t>
   </si>
   <si>
     <t xml:space="preserve">18.0127029418945</t>
@@ -2084,13 +2084,13 @@
     <t xml:space="preserve">18.0487270355225</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2288551330566</t>
+    <t xml:space="preserve">18.228853225708</t>
   </si>
   <si>
     <t xml:space="preserve">18.0307159423828</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9226398468018</t>
+    <t xml:space="preserve">17.9226417541504</t>
   </si>
   <si>
     <t xml:space="preserve">17.4543075561523</t>
@@ -2099,40 +2099,40 @@
     <t xml:space="preserve">18.6791706085205</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8052616119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6251354217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3369331359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9493637084961</t>
+    <t xml:space="preserve">18.8052597045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6251373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3369312286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9493618011475</t>
   </si>
   <si>
     <t xml:space="preserve">18.7872505187988</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6971855163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3549423217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4269962310791</t>
+    <t xml:space="preserve">18.6971836090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.354944229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4269924163818</t>
   </si>
   <si>
     <t xml:space="preserve">17.9856834411621</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3552379608154</t>
+    <t xml:space="preserve">17.3552398681641</t>
   </si>
   <si>
     <t xml:space="preserve">17.7244987487793</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3009052276611</t>
+    <t xml:space="preserve">18.3009071350098</t>
   </si>
   <si>
     <t xml:space="preserve">18.6071224212646</t>
@@ -2141,1176 +2141,1179 @@
     <t xml:space="preserve">19.3996829986572</t>
   </si>
   <si>
+    <t xml:space="preserve">19.6698684692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2462768554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0661525726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9220504760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4176921844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4537181854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2823047637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7515163421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7425117492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7965507507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5083465576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4182834625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8508834838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9859790802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.868896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0490226745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9409446716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3462314605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2741813659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3822593688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2831897735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1748161315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.976676940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6164226531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4272899627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1387920379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9136333465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6974792480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1928310394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9496574401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2381553649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1300830841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6794662475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9676704406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0847549438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0667400360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8686008453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5173530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6074180603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5894031524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7695331573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6365604400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.24342918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6621875762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2249774932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5330257415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1916618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.684232711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6232395172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8021230697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9405126571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7836713790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3131456375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.894383430481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8390293121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4792137145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.953330039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0732688903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0179128646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.303918838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3777284622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1009464263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1378507614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9220628738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7006387710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4756231307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4202671051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.577109336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8298015594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7928981781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6914119720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.512526512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1803903579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0989007949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7575378417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1486215591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2132015228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4069480895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4161758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5914688110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8590240478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9236068725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4807567596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6837301254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5361127853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2962369918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.370044708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0471353530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1762981414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9087438583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65964126586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53047657012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0932645797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4899835586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5730180740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4254016876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5176601409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3054628372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4438524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6652784347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0286827087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96410083770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.056360244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1209421157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50279998779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29059982299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5766077041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21218013763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40131282806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43821620941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47512149810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20295333862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94001197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9861421585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88004302978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53970432281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24447059631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28137588500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11530685424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88106632232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97332668304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99177837371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2408809661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.434627532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.084038734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1024904251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61351108551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66886711120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52125072479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79803085327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56737995147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2629222869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39208698272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65041637420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31828022003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71499729156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81648445129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68732070922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98255157470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7519006729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49357318878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2777853012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0655860900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5822429656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7298603057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2870101928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5084362030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3515930175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4310369491577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6340103149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2337017059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.993824005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1322145462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.086085319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1414413452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1875715255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9661464691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9569206237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7539472579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8277559280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7354955673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0676317214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4551258087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2577877044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2485628128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0824947357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5991516113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4054040908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2024335861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7559928894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7098627090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7744464874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3408241271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7190895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7283163070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0143222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.134259223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1250343322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9497404098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6637334823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.682186126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4571714401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1158094406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8482532501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0512256622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0327739715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9312896728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6473255157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7303600311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0865879058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7913551330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8651638031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7452239990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8190307617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1086273193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.99791431427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9333343505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4720344543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6785955429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3187808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8446645736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2967395782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2044792175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7247257232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8538904190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1491222381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2506103515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9830551147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1583490371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0753154754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1065835952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6027421951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0399541854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9753713607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5878801345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3018732070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6006965637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1301679611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30905342102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0635404586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97589349746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8928599357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5504732131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93796634674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90567493438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98409652709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91028785705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01177453994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47307586669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05431365966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85697937011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33673000335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01381969451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39567756652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40028953552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34954738616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25728702545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.118896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74985551834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92976331710815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78675937652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10966968536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.842116355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42694520950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28855466842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26087713241577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32545900344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33468437194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11326026916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5561089515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77753448486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93437623977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60223960876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33929777145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51920461654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30700731277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14555168151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10403442382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15939044952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06712961196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92874002456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56533527374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54227018356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.445396900177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27010250091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72217750549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46948528289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66784477233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90310859680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54329395294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69090843200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87542915344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32750511169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0066404342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4863929748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4956197738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2557430267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9420585632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82571029663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74267578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.462306022644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.194751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.019455909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89029216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3792715072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3608179092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2224292755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.674503326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5453395843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7667636871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0215015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4402637481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5417499542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6155576705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8093042373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.818531036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7078170776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6616868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5694274902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3480033874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2741947174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1450309753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8128938674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0030508041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3167362213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8241662979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7042284011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0548162460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3961791992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2854671478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4423084259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1286239624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2301111221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0086870193481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1932077407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5437955856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3500490188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5714731216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3685007095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1470766067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4976654052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1101732254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1655282974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2670154571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2762413024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0455913543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1747541427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.331597328186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3869533538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5104827880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3813171386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6304197311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.335186958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7872619628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5068922042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4330835342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4515342712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2690601348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5735187530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8318471908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1455326080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3613204956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4628076553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7616300582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5217542648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5955619812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7154998779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3556842803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9128360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6545085906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5033016204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4110412597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.650918006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1860256195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6750049591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.416675567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1029930114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9184722900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3889989852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7764921188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5827436447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1547584533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8133955001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8410749435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9241075515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1178531646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8503007888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8779783248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3520936965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6381025314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4351301193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5919723510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9517869949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0994033813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0717258453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5145740509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7877655029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3910446166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4648532867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1142635345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2618789672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5386619567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4464015960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5663394927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.372594833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6216983795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5478897094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.036865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.415132522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7657222747803</t>
+  </si>
+  <si>
     <t xml:space="preserve">19.6698703765869</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2462768554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0661525726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9220485687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4176921844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4537181854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2823028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7515163421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7425136566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7965507507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5083484649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.418285369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8508834838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9859790802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8688945770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0490245819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9409465789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3462333679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2741813659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3822593688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2831897735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1748161315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.976676940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6164245605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4272899627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1387920379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.913631439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6974792480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1928291320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9496593475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2381534576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1300811767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6794662475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9676723480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0847549438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0667400360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8686027526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5173530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6074180603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5894031524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.76953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6365585327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2434272766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6621875762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2249774932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5330257415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1916618347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6842317581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6232395172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8021230697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9405136108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7836713790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3131456375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8943843841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8390283584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4792137145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.953330039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0732688903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0179128646851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.303918838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3777275085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1009464263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1378498077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9220628738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7006387710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4756231307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4202671051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.577109336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8298015594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7928972244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6914129257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5125274658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1803913116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0989007949829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7575378417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1486215591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2132024765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4069480895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4161758422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5914688110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8590240478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9236068725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4807558059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6837301254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5361137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2962369918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.370044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0471353530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1762981414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9087438583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65964126586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53047657012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0932645797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4899835586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5730171203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4254007339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5176601409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3054628372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4438524246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6652784347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0286827087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96410083770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.056360244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.120943069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50280094146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29059982299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5766077041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21218109130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40131282806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43821620941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47512149810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20295333862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94001197814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9861421585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88004398345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53970336914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24447059631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28137588500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11530685424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88106632232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97332668304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99177837371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2408809661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.434627532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0840396881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1024904251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61351108551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66886711120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52125072479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7980318069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56738090515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2629222869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39208793640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65041542053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31827926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71499729156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81648445129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68732070922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98255157470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75190162658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49357223510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2777853012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0655860900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5822439193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7298603057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2870101928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5084362030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3515930175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4310369491577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6340093612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2337007522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.993824005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1322145462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.086085319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1414403915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1875705718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9661464691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9569206237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7539472579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8277568817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7354965209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0676326751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4551248550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2577877044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2485628128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0824947357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5991516113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4054050445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2024335861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7559928894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7098627090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7744464874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3408241271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7190895080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7283163070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0143222808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1342601776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1250343322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9497404098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6637334823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.682186126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4571714401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1158094406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8482542037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0512266159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0327739715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9312896728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6473274230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7303600311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0865859985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7913551330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8651638031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7452239990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8190307617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1086292266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9979162216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9333343505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4720344543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.678596496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3187808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8446645736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2967405319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2044792175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7247257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8538904190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1491222381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2506093978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9830551147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1583480834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0753145217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1065835952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6027421951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0399541854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9753713607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5878791809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.301872253418</t>
-  </si>